--- a/app/borsa/yeni-is-anlasmalari/data/yeni-is-anlasmalari.xlsx
+++ b/app/borsa/yeni-is-anlasmalari/data/yeni-is-anlasmalari.xlsx
@@ -424,12 +424,12 @@
     <x:t>2025-12-29</x:t>
   </x:si>
   <x:si>
+    <x:t>HOROZ</x:t>
+  </x:si>
+  <x:si>
     <x:t>ANELE</x:t>
   </x:si>
   <x:si>
-    <x:t>HOROZ</x:t>
-  </x:si>
-  <x:si>
     <x:t>2025-12-26</x:t>
   </x:si>
   <x:si>
@@ -992,12 +992,6 @@
   </x:si>
   <x:si>
     <x:t>2025-04-21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2025-04-18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAHKM</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1348,7 +1342,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I550"/>
+  <x:dimension ref="A1:I547"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -1385,10 +1379,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>53</x:v>
+        <x:v>53.3</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>0.5</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>10</x:v>
@@ -1414,10 +1408,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>40.7</x:v>
+        <x:v>40.08</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>0.66</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>13</x:v>
@@ -1443,10 +1437,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>15.99</x:v>
+        <x:v>16.38</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.39</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>15</x:v>
@@ -1472,10 +1466,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>62.5</x:v>
+        <x:v>60.9</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>-1.6</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>15</x:v>
@@ -1501,10 +1495,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>41.76</x:v>
+        <x:v>42.88</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>-0.42</x:v>
+        <x:v>1.12</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>15</x:v>
@@ -1530,10 +1524,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>283.5</x:v>
+        <x:v>286.25</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>2.5</x:v>
+        <x:v>2.75</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>15</x:v>
@@ -1559,10 +1553,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>5.07</x:v>
+        <x:v>4.92</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>-0.03</x:v>
+        <x:v>-0.15</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>15</x:v>
@@ -1588,10 +1582,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>5.07</x:v>
+        <x:v>4.92</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>-0.03</x:v>
+        <x:v>-0.15</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
         <x:v>15</x:v>
@@ -1617,10 +1611,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>34.66</x:v>
+        <x:v>34.62</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>-0.92</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
         <x:v>23</x:v>
@@ -1646,10 +1640,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>232.7</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>3.4</x:v>
+        <x:v>-2.7</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
         <x:v>23</x:v>
@@ -1675,10 +1669,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>53</x:v>
+        <x:v>53.3</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>0.5</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
         <x:v>23</x:v>
@@ -1704,10 +1698,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>48.42</x:v>
+        <x:v>47.82</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>-0.54</x:v>
+        <x:v>-0.6</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
         <x:v>26</x:v>
@@ -1733,10 +1727,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>48.42</x:v>
+        <x:v>47.82</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>-0.54</x:v>
+        <x:v>-0.6</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
         <x:v>26</x:v>
@@ -1762,10 +1756,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>48.42</x:v>
+        <x:v>47.82</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>-0.54</x:v>
+        <x:v>-0.6</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
         <x:v>26</x:v>
@@ -1791,10 +1785,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>53</x:v>
+        <x:v>53.3</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>0.5</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
         <x:v>26</x:v>
@@ -1820,10 +1814,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>114.2</x:v>
+        <x:v>115.2</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>-1</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
         <x:v>29</x:v>
@@ -1849,10 +1843,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>41.76</x:v>
+        <x:v>42.88</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>-0.42</x:v>
+        <x:v>1.12</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
         <x:v>29</x:v>
@@ -1878,10 +1872,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>95.95</x:v>
+        <x:v>95.4</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>-2.2</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
         <x:v>31</x:v>
@@ -1907,10 +1901,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>62.5</x:v>
+        <x:v>60.9</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>-1.6</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
         <x:v>32</x:v>
@@ -1936,10 +1930,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>34.66</x:v>
+        <x:v>34.62</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>-0.92</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
         <x:v>32</x:v>
@@ -1965,10 +1959,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>24.58</x:v>
+        <x:v>24.56</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>0.44</x:v>
+        <x:v>-0.02</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
         <x:v>32</x:v>
@@ -1994,10 +1988,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>5.94</x:v>
+        <x:v>5.87</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>0.07</x:v>
+        <x:v>-0.07</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
         <x:v>32</x:v>
@@ -2023,10 +2017,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>5.94</x:v>
+        <x:v>5.87</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>0.07</x:v>
+        <x:v>-0.07</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
         <x:v>32</x:v>
@@ -2052,10 +2046,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>47.7</x:v>
+        <x:v>47.26</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>0.14</x:v>
+        <x:v>-0.44</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
         <x:v>36</x:v>
@@ -2081,10 +2075,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>350</x:v>
+        <x:v>347.5</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>6</x:v>
+        <x:v>-2.5</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
         <x:v>36</x:v>
@@ -2110,10 +2104,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>79.8</x:v>
+        <x:v>82.15</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
         <x:v>39</x:v>
@@ -2139,10 +2133,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>232.7</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>3.4</x:v>
+        <x:v>-2.7</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
         <x:v>39</x:v>
@@ -2168,10 +2162,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>4.5</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>0.04</x:v>
+        <x:v>-0.17</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
         <x:v>39</x:v>
@@ -2197,10 +2191,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>24.58</x:v>
+        <x:v>24.56</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>0.44</x:v>
+        <x:v>-0.02</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
         <x:v>41</x:v>
@@ -2226,10 +2220,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>24.58</x:v>
+        <x:v>24.56</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>0.44</x:v>
+        <x:v>-0.02</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
         <x:v>41</x:v>
@@ -2255,10 +2249,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>47</x:v>
+        <x:v>47.02</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>0.32</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
         <x:v>41</x:v>
@@ -2284,10 +2278,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>24.1</x:v>
+        <x:v>23.76</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>0.24</x:v>
+        <x:v>-0.34</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
         <x:v>41</x:v>
@@ -2313,10 +2307,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>66.75</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.35</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
         <x:v>45</x:v>
@@ -2342,10 +2336,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>47.7</x:v>
+        <x:v>47.26</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>0.14</x:v>
+        <x:v>-0.44</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
         <x:v>45</x:v>
@@ -2371,10 +2365,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>920</x:v>
+        <x:v>940</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>35.5</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
         <x:v>47</x:v>
@@ -2400,10 +2394,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>64.65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>0.5</x:v>
+        <x:v>-1.65</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
         <x:v>49</x:v>
@@ -2429,10 +2423,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>34.66</x:v>
+        <x:v>34.62</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>-0.92</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
         <x:v>49</x:v>
@@ -2458,10 +2452,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>79.8</x:v>
+        <x:v>82.15</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
         <x:v>50</x:v>
@@ -2487,10 +2481,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>15.71</x:v>
+        <x:v>15.12</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>-0.09</x:v>
+        <x:v>-0.59</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
         <x:v>50</x:v>
@@ -2516,10 +2510,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>41.76</x:v>
+        <x:v>42.88</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>-0.42</x:v>
+        <x:v>1.12</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
         <x:v>50</x:v>
@@ -2545,10 +2539,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>24.58</x:v>
+        <x:v>24.56</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>0.44</x:v>
+        <x:v>-0.02</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
         <x:v>50</x:v>
@@ -2574,10 +2568,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>3.51</x:v>
+        <x:v>3.7</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>-0.32</x:v>
+        <x:v>0.19</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
         <x:v>50</x:v>
@@ -2603,10 +2597,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>3.51</x:v>
+        <x:v>3.7</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>-0.32</x:v>
+        <x:v>0.19</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
         <x:v>50</x:v>
@@ -2632,10 +2626,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>25.2</x:v>
+        <x:v>24.48</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>0.12</x:v>
+        <x:v>-0.72</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
         <x:v>50</x:v>
@@ -2661,10 +2655,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>15.99</x:v>
+        <x:v>16.38</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.39</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
         <x:v>54</x:v>
@@ -2690,10 +2684,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>15.99</x:v>
+        <x:v>16.38</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.39</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
         <x:v>54</x:v>
@@ -2719,10 +2713,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>62.5</x:v>
+        <x:v>60.9</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>-1.6</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
         <x:v>54</x:v>
@@ -2748,10 +2742,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>41.12</x:v>
+        <x:v>45.22</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>-0.18</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
         <x:v>54</x:v>
@@ -2777,10 +2771,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>95.95</x:v>
+        <x:v>95.4</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>-2.2</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
         <x:v>56</x:v>
@@ -2806,10 +2800,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>205.7</x:v>
+        <x:v>214.5</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>9</x:v>
+        <x:v>8.8</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
         <x:v>56</x:v>
@@ -2835,10 +2829,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>53</x:v>
+        <x:v>53.3</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>0.5</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
         <x:v>56</x:v>
@@ -2864,10 +2858,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B53" s="0">
-        <x:v>12.74</x:v>
+        <x:v>14.01</x:v>
       </x:c>
       <x:c r="C53" s="0">
-        <x:v>1.15</x:v>
+        <x:v>1.27</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
         <x:v>59</x:v>
@@ -2893,10 +2887,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B54" s="0">
-        <x:v>232.7</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C54" s="0">
-        <x:v>3.4</x:v>
+        <x:v>-2.7</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
         <x:v>60</x:v>
@@ -2922,10 +2916,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B55" s="0">
-        <x:v>232.7</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C55" s="0">
-        <x:v>3.4</x:v>
+        <x:v>-2.7</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
         <x:v>60</x:v>
@@ -2951,10 +2945,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B56" s="0">
-        <x:v>28.82</x:v>
+        <x:v>27.92</x:v>
       </x:c>
       <x:c r="C56" s="0">
-        <x:v>-0.24</x:v>
+        <x:v>-0.9</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
         <x:v>60</x:v>
@@ -2980,10 +2974,10 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B57" s="0">
-        <x:v>4.96</x:v>
+        <x:v>4.77</x:v>
       </x:c>
       <x:c r="C57" s="0">
-        <x:v>-0.11</x:v>
+        <x:v>-0.19</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
         <x:v>63</x:v>
@@ -3009,10 +3003,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="B58" s="0">
-        <x:v>11.7</x:v>
+        <x:v>11.85</x:v>
       </x:c>
       <x:c r="C58" s="0">
-        <x:v>0.5</x:v>
+        <x:v>0.15</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
         <x:v>63</x:v>
@@ -3038,10 +3032,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B59" s="0">
-        <x:v>114.2</x:v>
+        <x:v>115.2</x:v>
       </x:c>
       <x:c r="C59" s="0">
-        <x:v>-1</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
         <x:v>65</x:v>
@@ -3067,10 +3061,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B60" s="0">
-        <x:v>408</x:v>
+        <x:v>396.5</x:v>
       </x:c>
       <x:c r="C60" s="0">
-        <x:v>-6</x:v>
+        <x:v>-11.5</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
         <x:v>67</x:v>
@@ -3096,10 +3090,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B61" s="0">
-        <x:v>408</x:v>
+        <x:v>396.5</x:v>
       </x:c>
       <x:c r="C61" s="0">
-        <x:v>-6</x:v>
+        <x:v>-11.5</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
         <x:v>67</x:v>
@@ -3125,10 +3119,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B62" s="0">
-        <x:v>41.76</x:v>
+        <x:v>42.88</x:v>
       </x:c>
       <x:c r="C62" s="0">
-        <x:v>-0.42</x:v>
+        <x:v>1.12</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
         <x:v>67</x:v>
@@ -3154,10 +3148,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B63" s="0">
-        <x:v>25.2</x:v>
+        <x:v>24.48</x:v>
       </x:c>
       <x:c r="C63" s="0">
-        <x:v>0.12</x:v>
+        <x:v>-0.72</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
         <x:v>68</x:v>
@@ -3183,10 +3177,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B64" s="0">
-        <x:v>920</x:v>
+        <x:v>940</x:v>
       </x:c>
       <x:c r="C64" s="0">
-        <x:v>35.5</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
         <x:v>69</x:v>
@@ -3212,10 +3206,10 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="B65" s="0">
-        <x:v>24.18</x:v>
+        <x:v>24.04</x:v>
       </x:c>
       <x:c r="C65" s="0">
-        <x:v>0.06</x:v>
+        <x:v>-0.14</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
         <x:v>71</x:v>
@@ -3241,10 +3235,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B66" s="0">
-        <x:v>79.8</x:v>
+        <x:v>82.15</x:v>
       </x:c>
       <x:c r="C66" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
         <x:v>72</x:v>
@@ -3270,10 +3264,10 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B67" s="0">
-        <x:v>7.85</x:v>
+        <x:v>7.53</x:v>
       </x:c>
       <x:c r="C67" s="0">
-        <x:v>0.39</x:v>
+        <x:v>-0.32</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
         <x:v>72</x:v>
@@ -3299,10 +3293,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B68" s="0">
-        <x:v>15.99</x:v>
+        <x:v>16.38</x:v>
       </x:c>
       <x:c r="C68" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.39</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
         <x:v>74</x:v>
@@ -3328,10 +3322,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B69" s="0">
-        <x:v>15.71</x:v>
+        <x:v>15.12</x:v>
       </x:c>
       <x:c r="C69" s="0">
-        <x:v>-0.09</x:v>
+        <x:v>-0.59</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
         <x:v>75</x:v>
@@ -3357,10 +3351,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B70" s="0">
-        <x:v>41.76</x:v>
+        <x:v>42.88</x:v>
       </x:c>
       <x:c r="C70" s="0">
-        <x:v>-0.42</x:v>
+        <x:v>1.12</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
         <x:v>75</x:v>
@@ -3386,10 +3380,10 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="B71" s="0">
-        <x:v>25.66</x:v>
+        <x:v>24.52</x:v>
       </x:c>
       <x:c r="C71" s="0">
-        <x:v>0.68</x:v>
+        <x:v>-1.14</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
         <x:v>77</x:v>
@@ -3415,10 +3409,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B72" s="0">
-        <x:v>53</x:v>
+        <x:v>53.3</x:v>
       </x:c>
       <x:c r="C72" s="0">
-        <x:v>0.5</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
         <x:v>77</x:v>
@@ -3444,10 +3438,10 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="B73" s="0">
-        <x:v>61.25</x:v>
+        <x:v>61.45</x:v>
       </x:c>
       <x:c r="C73" s="0">
-        <x:v>-1.4</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
         <x:v>79</x:v>
@@ -3473,10 +3467,10 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B74" s="0">
-        <x:v>4.96</x:v>
+        <x:v>4.77</x:v>
       </x:c>
       <x:c r="C74" s="0">
-        <x:v>-0.11</x:v>
+        <x:v>-0.19</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
         <x:v>80</x:v>
@@ -3502,10 +3496,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B75" s="0">
-        <x:v>41.76</x:v>
+        <x:v>42.88</x:v>
       </x:c>
       <x:c r="C75" s="0">
-        <x:v>-0.42</x:v>
+        <x:v>1.12</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
         <x:v>80</x:v>
@@ -3531,10 +3525,10 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B76" s="0">
-        <x:v>33.44</x:v>
+        <x:v>30.1</x:v>
       </x:c>
       <x:c r="C76" s="0">
-        <x:v>1.54</x:v>
+        <x:v>-3.34</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
         <x:v>80</x:v>
@@ -3560,10 +3554,10 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B77" s="0">
-        <x:v>33.44</x:v>
+        <x:v>30.1</x:v>
       </x:c>
       <x:c r="C77" s="0">
-        <x:v>1.54</x:v>
+        <x:v>-3.34</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
         <x:v>80</x:v>
@@ -3589,10 +3583,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B78" s="0">
-        <x:v>79.8</x:v>
+        <x:v>82.15</x:v>
       </x:c>
       <x:c r="C78" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
         <x:v>82</x:v>
@@ -3618,10 +3612,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B79" s="0">
-        <x:v>47.7</x:v>
+        <x:v>47.26</x:v>
       </x:c>
       <x:c r="C79" s="0">
-        <x:v>0.14</x:v>
+        <x:v>-0.44</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
         <x:v>82</x:v>
@@ -3647,10 +3641,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B80" s="0">
-        <x:v>35.52</x:v>
+        <x:v>33.74</x:v>
       </x:c>
       <x:c r="C80" s="0">
-        <x:v>-0.88</x:v>
+        <x:v>-1.78</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
         <x:v>82</x:v>
@@ -3676,10 +3670,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B81" s="0">
-        <x:v>5.52</x:v>
+        <x:v>5.49</x:v>
       </x:c>
       <x:c r="C81" s="0">
-        <x:v>-0.15</x:v>
+        <x:v>-0.03</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
         <x:v>85</x:v>
@@ -3705,10 +3699,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B82" s="0">
-        <x:v>79.8</x:v>
+        <x:v>82.15</x:v>
       </x:c>
       <x:c r="C82" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
         <x:v>86</x:v>
@@ -3734,10 +3728,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B83" s="0">
-        <x:v>62.5</x:v>
+        <x:v>60.9</x:v>
       </x:c>
       <x:c r="C83" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>-1.6</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
         <x:v>87</x:v>
@@ -3763,10 +3757,10 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="B84" s="0">
-        <x:v>40.56</x:v>
+        <x:v>41.52</x:v>
       </x:c>
       <x:c r="C84" s="0">
-        <x:v>0.36</x:v>
+        <x:v>0.96</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
         <x:v>87</x:v>
@@ -3792,10 +3786,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B85" s="0">
-        <x:v>53</x:v>
+        <x:v>53.3</x:v>
       </x:c>
       <x:c r="C85" s="0">
-        <x:v>0.5</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
         <x:v>87</x:v>
@@ -3821,10 +3815,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B86" s="0">
-        <x:v>4.5</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="C86" s="0">
-        <x:v>0.04</x:v>
+        <x:v>-0.17</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
         <x:v>89</x:v>
@@ -3850,10 +3844,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B87" s="0">
-        <x:v>4.5</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="C87" s="0">
-        <x:v>0.04</x:v>
+        <x:v>-0.17</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
         <x:v>89</x:v>
@@ -3879,10 +3873,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B88" s="0">
-        <x:v>920</x:v>
+        <x:v>940</x:v>
       </x:c>
       <x:c r="C88" s="0">
-        <x:v>35.5</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
         <x:v>89</x:v>
@@ -3908,10 +3902,10 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="B89" s="0">
-        <x:v>79.55</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C89" s="0">
-        <x:v>-0.75</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
         <x:v>89</x:v>
@@ -3937,10 +3931,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B90" s="0">
-        <x:v>95.95</x:v>
+        <x:v>95.4</x:v>
       </x:c>
       <x:c r="C90" s="0">
-        <x:v>-2.2</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
         <x:v>92</x:v>
@@ -3966,10 +3960,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B91" s="0">
-        <x:v>15.99</x:v>
+        <x:v>16.38</x:v>
       </x:c>
       <x:c r="C91" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.39</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
         <x:v>93</x:v>
@@ -3995,10 +3989,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B92" s="0">
-        <x:v>114.2</x:v>
+        <x:v>115.2</x:v>
       </x:c>
       <x:c r="C92" s="0">
-        <x:v>-1</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
         <x:v>93</x:v>
@@ -4024,10 +4018,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B93" s="0">
-        <x:v>95.95</x:v>
+        <x:v>95.4</x:v>
       </x:c>
       <x:c r="C93" s="0">
-        <x:v>-2.2</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
         <x:v>94</x:v>
@@ -4053,10 +4047,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B94" s="0">
-        <x:v>62.5</x:v>
+        <x:v>60.9</x:v>
       </x:c>
       <x:c r="C94" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>-1.6</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
         <x:v>95</x:v>
@@ -4082,10 +4076,10 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="B95" s="0">
-        <x:v>103</x:v>
+        <x:v>104.9</x:v>
       </x:c>
       <x:c r="C95" s="0">
-        <x:v>5.3</x:v>
+        <x:v>1.9</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
         <x:v>95</x:v>
@@ -4111,10 +4105,10 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="B96" s="0">
-        <x:v>103</x:v>
+        <x:v>104.9</x:v>
       </x:c>
       <x:c r="C96" s="0">
-        <x:v>5.3</x:v>
+        <x:v>1.9</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
         <x:v>95</x:v>
@@ -4140,10 +4134,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B97" s="0">
-        <x:v>42.78</x:v>
+        <x:v>40.48</x:v>
       </x:c>
       <x:c r="C97" s="0">
-        <x:v>0.62</x:v>
+        <x:v>-2.3</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
         <x:v>98</x:v>
@@ -4169,10 +4163,10 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="B98" s="0">
-        <x:v>14.43</x:v>
+        <x:v>12.99</x:v>
       </x:c>
       <x:c r="C98" s="0">
-        <x:v>1.31</x:v>
+        <x:v>-1.44</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
         <x:v>98</x:v>
@@ -4198,10 +4192,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B99" s="0">
-        <x:v>232.7</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C99" s="0">
-        <x:v>3.4</x:v>
+        <x:v>-2.7</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
         <x:v>100</x:v>
@@ -4227,10 +4221,10 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="B100" s="0">
-        <x:v>239.2</x:v>
+        <x:v>249.4</x:v>
       </x:c>
       <x:c r="C100" s="0">
-        <x:v>-26.55</x:v>
+        <x:v>10.2</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
         <x:v>102</x:v>
@@ -4256,10 +4250,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B101" s="0">
-        <x:v>47.7</x:v>
+        <x:v>47.26</x:v>
       </x:c>
       <x:c r="C101" s="0">
-        <x:v>0.14</x:v>
+        <x:v>-0.44</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
         <x:v>103</x:v>
@@ -4285,10 +4279,10 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="B102" s="0">
-        <x:v>79.55</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C102" s="0">
-        <x:v>-0.75</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
         <x:v>103</x:v>
@@ -4314,10 +4308,10 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B103" s="0">
-        <x:v>35.42</x:v>
+        <x:v>34.5</x:v>
       </x:c>
       <x:c r="C103" s="0">
-        <x:v>0.52</x:v>
+        <x:v>-0.92</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
         <x:v>105</x:v>
@@ -4343,10 +4337,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B104" s="0">
-        <x:v>53</x:v>
+        <x:v>53.3</x:v>
       </x:c>
       <x:c r="C104" s="0">
-        <x:v>0.5</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
         <x:v>105</x:v>
@@ -4372,10 +4366,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B105" s="0">
-        <x:v>34.66</x:v>
+        <x:v>34.62</x:v>
       </x:c>
       <x:c r="C105" s="0">
-        <x:v>-0.92</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
         <x:v>106</x:v>
@@ -4401,10 +4395,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B106" s="0">
-        <x:v>34.66</x:v>
+        <x:v>34.62</x:v>
       </x:c>
       <x:c r="C106" s="0">
-        <x:v>-0.92</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
         <x:v>106</x:v>
@@ -4430,10 +4424,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B107" s="0">
-        <x:v>34.66</x:v>
+        <x:v>34.62</x:v>
       </x:c>
       <x:c r="C107" s="0">
-        <x:v>-0.92</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
         <x:v>106</x:v>
@@ -4459,10 +4453,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B108" s="0">
-        <x:v>41.76</x:v>
+        <x:v>42.88</x:v>
       </x:c>
       <x:c r="C108" s="0">
-        <x:v>-0.42</x:v>
+        <x:v>1.12</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
         <x:v>106</x:v>
@@ -4488,10 +4482,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B109" s="0">
-        <x:v>205.7</x:v>
+        <x:v>214.5</x:v>
       </x:c>
       <x:c r="C109" s="0">
-        <x:v>9</x:v>
+        <x:v>8.8</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
         <x:v>106</x:v>
@@ -4517,10 +4511,10 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B110" s="0">
-        <x:v>33.44</x:v>
+        <x:v>30.1</x:v>
       </x:c>
       <x:c r="C110" s="0">
-        <x:v>1.54</x:v>
+        <x:v>-3.34</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
         <x:v>106</x:v>
@@ -4546,10 +4540,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B111" s="0">
-        <x:v>79.8</x:v>
+        <x:v>82.15</x:v>
       </x:c>
       <x:c r="C111" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
         <x:v>107</x:v>
@@ -4575,10 +4569,10 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="B112" s="0">
-        <x:v>239.2</x:v>
+        <x:v>249.4</x:v>
       </x:c>
       <x:c r="C112" s="0">
-        <x:v>-26.55</x:v>
+        <x:v>10.2</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
         <x:v>108</x:v>
@@ -4604,10 +4598,10 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B113" s="0">
-        <x:v>33.44</x:v>
+        <x:v>30.1</x:v>
       </x:c>
       <x:c r="C113" s="0">
-        <x:v>1.54</x:v>
+        <x:v>-3.34</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
         <x:v>108</x:v>
@@ -4633,10 +4627,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B114" s="0">
-        <x:v>34.66</x:v>
+        <x:v>34.62</x:v>
       </x:c>
       <x:c r="C114" s="0">
-        <x:v>-0.92</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
         <x:v>109</x:v>
@@ -4662,10 +4656,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B115" s="0">
-        <x:v>24.58</x:v>
+        <x:v>24.56</x:v>
       </x:c>
       <x:c r="C115" s="0">
-        <x:v>0.44</x:v>
+        <x:v>-0.02</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
         <x:v>109</x:v>
@@ -4691,10 +4685,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B116" s="0">
-        <x:v>40.7</x:v>
+        <x:v>40.08</x:v>
       </x:c>
       <x:c r="C116" s="0">
-        <x:v>0.66</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D116" s="0" t="s">
         <x:v>109</x:v>
@@ -4720,10 +4714,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B117" s="0">
-        <x:v>42.78</x:v>
+        <x:v>40.48</x:v>
       </x:c>
       <x:c r="C117" s="0">
-        <x:v>0.62</x:v>
+        <x:v>-2.3</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
         <x:v>110</x:v>
@@ -4749,10 +4743,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B118" s="0">
-        <x:v>408</x:v>
+        <x:v>396.5</x:v>
       </x:c>
       <x:c r="C118" s="0">
-        <x:v>-6</x:v>
+        <x:v>-11.5</x:v>
       </x:c>
       <x:c r="D118" s="0" t="s">
         <x:v>110</x:v>
@@ -4778,10 +4772,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B119" s="0">
-        <x:v>114.2</x:v>
+        <x:v>115.2</x:v>
       </x:c>
       <x:c r="C119" s="0">
-        <x:v>-1</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
         <x:v>110</x:v>
@@ -4807,10 +4801,10 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="B120" s="0">
-        <x:v>13.7</x:v>
+        <x:v>13.36</x:v>
       </x:c>
       <x:c r="C120" s="0">
-        <x:v>0.45</x:v>
+        <x:v>-0.34</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
         <x:v>110</x:v>
@@ -4836,10 +4830,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B121" s="0">
-        <x:v>41.76</x:v>
+        <x:v>42.88</x:v>
       </x:c>
       <x:c r="C121" s="0">
-        <x:v>-0.42</x:v>
+        <x:v>1.12</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
         <x:v>110</x:v>
@@ -4865,10 +4859,10 @@
         <x:v>112</x:v>
       </x:c>
       <x:c r="B122" s="0">
-        <x:v>26.32</x:v>
+        <x:v>25.88</x:v>
       </x:c>
       <x:c r="C122" s="0">
-        <x:v>0.02</x:v>
+        <x:v>-0.44</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
         <x:v>113</x:v>
@@ -4894,10 +4888,10 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B123" s="0">
-        <x:v>50.7</x:v>
+        <x:v>50.35</x:v>
       </x:c>
       <x:c r="C123" s="0">
-        <x:v>-0.55</x:v>
+        <x:v>-0.35</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
         <x:v>113</x:v>
@@ -4923,10 +4917,10 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="B124" s="0">
-        <x:v>61.25</x:v>
+        <x:v>61.45</x:v>
       </x:c>
       <x:c r="C124" s="0">
-        <x:v>-1.4</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
         <x:v>113</x:v>
@@ -4952,10 +4946,10 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="B125" s="0">
-        <x:v>61.25</x:v>
+        <x:v>61.45</x:v>
       </x:c>
       <x:c r="C125" s="0">
-        <x:v>-1.4</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="D125" s="0" t="s">
         <x:v>113</x:v>
@@ -4981,10 +4975,10 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="B126" s="0">
-        <x:v>79.55</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C126" s="0">
-        <x:v>-0.75</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
         <x:v>113</x:v>
@@ -5010,10 +5004,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B127" s="0">
-        <x:v>5.52</x:v>
+        <x:v>5.49</x:v>
       </x:c>
       <x:c r="C127" s="0">
-        <x:v>-0.15</x:v>
+        <x:v>-0.03</x:v>
       </x:c>
       <x:c r="D127" s="0" t="s">
         <x:v>115</x:v>
@@ -5039,10 +5033,10 @@
         <x:v>116</x:v>
       </x:c>
       <x:c r="B128" s="0">
-        <x:v>21.8</x:v>
+        <x:v>22.28</x:v>
       </x:c>
       <x:c r="C128" s="0">
-        <x:v>0.64</x:v>
+        <x:v>0.48</x:v>
       </x:c>
       <x:c r="D128" s="0" t="s">
         <x:v>115</x:v>
@@ -5068,10 +5062,10 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B129" s="0">
-        <x:v>7.85</x:v>
+        <x:v>7.53</x:v>
       </x:c>
       <x:c r="C129" s="0">
-        <x:v>0.39</x:v>
+        <x:v>-0.32</x:v>
       </x:c>
       <x:c r="D129" s="0" t="s">
         <x:v>115</x:v>
@@ -5097,10 +5091,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B130" s="0">
-        <x:v>66.75</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C130" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.35</x:v>
       </x:c>
       <x:c r="D130" s="0" t="s">
         <x:v>117</x:v>
@@ -5126,10 +5120,10 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="B131" s="0">
-        <x:v>239.2</x:v>
+        <x:v>249.4</x:v>
       </x:c>
       <x:c r="C131" s="0">
-        <x:v>-26.55</x:v>
+        <x:v>10.2</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
         <x:v>117</x:v>
@@ -5155,10 +5149,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B132" s="0">
-        <x:v>40.7</x:v>
+        <x:v>40.08</x:v>
       </x:c>
       <x:c r="C132" s="0">
-        <x:v>0.66</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
         <x:v>117</x:v>
@@ -5184,10 +5178,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B133" s="0">
-        <x:v>41.76</x:v>
+        <x:v>42.88</x:v>
       </x:c>
       <x:c r="C133" s="0">
-        <x:v>-0.42</x:v>
+        <x:v>1.12</x:v>
       </x:c>
       <x:c r="D133" s="0" t="s">
         <x:v>118</x:v>
@@ -5213,10 +5207,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B134" s="0">
-        <x:v>3.51</x:v>
+        <x:v>3.7</x:v>
       </x:c>
       <x:c r="C134" s="0">
-        <x:v>-0.32</x:v>
+        <x:v>0.19</x:v>
       </x:c>
       <x:c r="D134" s="0" t="s">
         <x:v>118</x:v>
@@ -5242,10 +5236,10 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B135" s="0">
-        <x:v>50.7</x:v>
+        <x:v>50.35</x:v>
       </x:c>
       <x:c r="C135" s="0">
-        <x:v>-0.55</x:v>
+        <x:v>-0.35</x:v>
       </x:c>
       <x:c r="D135" s="0" t="s">
         <x:v>118</x:v>
@@ -5271,10 +5265,10 @@
         <x:v>119</x:v>
       </x:c>
       <x:c r="B136" s="0">
-        <x:v>11.27</x:v>
+        <x:v>11.38</x:v>
       </x:c>
       <x:c r="C136" s="0">
-        <x:v>-0.28</x:v>
+        <x:v>0.11</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
         <x:v>118</x:v>
@@ -5300,10 +5294,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B137" s="0">
-        <x:v>47.7</x:v>
+        <x:v>47.26</x:v>
       </x:c>
       <x:c r="C137" s="0">
-        <x:v>0.14</x:v>
+        <x:v>-0.44</x:v>
       </x:c>
       <x:c r="D137" s="0" t="s">
         <x:v>118</x:v>
@@ -5329,10 +5323,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B138" s="0">
-        <x:v>205.7</x:v>
+        <x:v>214.5</x:v>
       </x:c>
       <x:c r="C138" s="0">
-        <x:v>9</x:v>
+        <x:v>8.8</x:v>
       </x:c>
       <x:c r="D138" s="0" t="s">
         <x:v>118</x:v>
@@ -5358,10 +5352,10 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="B139" s="0">
-        <x:v>59.25</x:v>
+        <x:v>55.95</x:v>
       </x:c>
       <x:c r="C139" s="0">
-        <x:v>5.35</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="D139" s="0" t="s">
         <x:v>121</x:v>
@@ -5387,10 +5381,10 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B140" s="0">
-        <x:v>50.7</x:v>
+        <x:v>50.35</x:v>
       </x:c>
       <x:c r="C140" s="0">
-        <x:v>-0.55</x:v>
+        <x:v>-0.35</x:v>
       </x:c>
       <x:c r="D140" s="0" t="s">
         <x:v>122</x:v>
@@ -5416,10 +5410,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B141" s="0">
-        <x:v>15.71</x:v>
+        <x:v>15.12</x:v>
       </x:c>
       <x:c r="C141" s="0">
-        <x:v>-0.09</x:v>
+        <x:v>-0.59</x:v>
       </x:c>
       <x:c r="D141" s="0" t="s">
         <x:v>123</x:v>
@@ -5445,10 +5439,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B142" s="0">
-        <x:v>95.95</x:v>
+        <x:v>95.4</x:v>
       </x:c>
       <x:c r="C142" s="0">
-        <x:v>-2.2</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="D142" s="0" t="s">
         <x:v>123</x:v>
@@ -5474,10 +5468,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B143" s="0">
-        <x:v>15.99</x:v>
+        <x:v>16.38</x:v>
       </x:c>
       <x:c r="C143" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.39</x:v>
       </x:c>
       <x:c r="D143" s="0" t="s">
         <x:v>124</x:v>
@@ -5503,10 +5497,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B144" s="0">
-        <x:v>79.8</x:v>
+        <x:v>82.15</x:v>
       </x:c>
       <x:c r="C144" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D144" s="0" t="s">
         <x:v>125</x:v>
@@ -5535,7 +5529,7 @@
         <x:v>4.34</x:v>
       </x:c>
       <x:c r="C145" s="0">
-        <x:v>-0.1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D145" s="0" t="s">
         <x:v>127</x:v>
@@ -5561,10 +5555,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B146" s="0">
-        <x:v>114.2</x:v>
+        <x:v>115.2</x:v>
       </x:c>
       <x:c r="C146" s="0">
-        <x:v>-1</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D146" s="0" t="s">
         <x:v>128</x:v>
@@ -5590,10 +5584,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B147" s="0">
-        <x:v>41.76</x:v>
+        <x:v>42.88</x:v>
       </x:c>
       <x:c r="C147" s="0">
-        <x:v>-0.42</x:v>
+        <x:v>1.12</x:v>
       </x:c>
       <x:c r="D147" s="0" t="s">
         <x:v>128</x:v>
@@ -5619,10 +5613,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B148" s="0">
-        <x:v>3.51</x:v>
+        <x:v>3.7</x:v>
       </x:c>
       <x:c r="C148" s="0">
-        <x:v>-0.32</x:v>
+        <x:v>0.19</x:v>
       </x:c>
       <x:c r="D148" s="0" t="s">
         <x:v>129</x:v>
@@ -5648,10 +5642,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B149" s="0">
-        <x:v>41.76</x:v>
+        <x:v>42.88</x:v>
       </x:c>
       <x:c r="C149" s="0">
-        <x:v>-0.42</x:v>
+        <x:v>1.12</x:v>
       </x:c>
       <x:c r="D149" s="0" t="s">
         <x:v>130</x:v>
@@ -5677,10 +5671,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B150" s="0">
-        <x:v>95.95</x:v>
+        <x:v>95.4</x:v>
       </x:c>
       <x:c r="C150" s="0">
-        <x:v>-2.2</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="D150" s="0" t="s">
         <x:v>130</x:v>
@@ -5706,10 +5700,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B151" s="0">
-        <x:v>95.95</x:v>
+        <x:v>95.4</x:v>
       </x:c>
       <x:c r="C151" s="0">
-        <x:v>-2.2</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="D151" s="0" t="s">
         <x:v>130</x:v>
@@ -5735,10 +5729,10 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B152" s="0">
-        <x:v>7.85</x:v>
+        <x:v>7.53</x:v>
       </x:c>
       <x:c r="C152" s="0">
-        <x:v>0.39</x:v>
+        <x:v>-0.32</x:v>
       </x:c>
       <x:c r="D152" s="0" t="s">
         <x:v>130</x:v>
@@ -5764,10 +5758,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B153" s="0">
-        <x:v>41.76</x:v>
+        <x:v>42.88</x:v>
       </x:c>
       <x:c r="C153" s="0">
-        <x:v>-0.42</x:v>
+        <x:v>1.12</x:v>
       </x:c>
       <x:c r="D153" s="0" t="s">
         <x:v>131</x:v>
@@ -5793,10 +5787,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B154" s="0">
-        <x:v>205.7</x:v>
+        <x:v>214.5</x:v>
       </x:c>
       <x:c r="C154" s="0">
-        <x:v>9</x:v>
+        <x:v>8.8</x:v>
       </x:c>
       <x:c r="D154" s="0" t="s">
         <x:v>131</x:v>
@@ -5822,10 +5816,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B155" s="0">
-        <x:v>920</x:v>
+        <x:v>940</x:v>
       </x:c>
       <x:c r="C155" s="0">
-        <x:v>35.5</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D155" s="0" t="s">
         <x:v>131</x:v>
@@ -5851,10 +5845,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B156" s="0">
-        <x:v>408</x:v>
+        <x:v>396.5</x:v>
       </x:c>
       <x:c r="C156" s="0">
-        <x:v>-6</x:v>
+        <x:v>-11.5</x:v>
       </x:c>
       <x:c r="D156" s="0" t="s">
         <x:v>132</x:v>
@@ -5880,10 +5874,10 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B157" s="0">
-        <x:v>4.96</x:v>
+        <x:v>4.77</x:v>
       </x:c>
       <x:c r="C157" s="0">
-        <x:v>-0.11</x:v>
+        <x:v>-0.19</x:v>
       </x:c>
       <x:c r="D157" s="0" t="s">
         <x:v>132</x:v>
@@ -5909,10 +5903,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B158" s="0">
-        <x:v>41.76</x:v>
+        <x:v>42.88</x:v>
       </x:c>
       <x:c r="C158" s="0">
-        <x:v>-0.42</x:v>
+        <x:v>1.12</x:v>
       </x:c>
       <x:c r="D158" s="0" t="s">
         <x:v>133</x:v>
@@ -5938,10 +5932,10 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="B159" s="0">
-        <x:v>239.2</x:v>
+        <x:v>249.4</x:v>
       </x:c>
       <x:c r="C159" s="0">
-        <x:v>-26.55</x:v>
+        <x:v>10.2</x:v>
       </x:c>
       <x:c r="D159" s="0" t="s">
         <x:v>133</x:v>
@@ -5967,10 +5961,10 @@
         <x:v>134</x:v>
       </x:c>
       <x:c r="B160" s="0">
-        <x:v>147.8</x:v>
+        <x:v>145.7</x:v>
       </x:c>
       <x:c r="C160" s="0">
-        <x:v>3.3</x:v>
+        <x:v>-2.1</x:v>
       </x:c>
       <x:c r="D160" s="0" t="s">
         <x:v>135</x:v>
@@ -5993,193 +5987,193 @@
     </x:row>
     <x:row r="161" spans="1:9">
       <x:c r="A161" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B161" s="0">
-        <x:v>38.28</x:v>
+        <x:v>115.2</x:v>
       </x:c>
       <x:c r="C161" s="0">
-        <x:v>3.48</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D161" s="0" t="s">
         <x:v>135</x:v>
       </x:c>
       <x:c r="E161" s="0">
-        <x:v>519168</x:v>
+        <x:v>1875000</x:v>
       </x:c>
       <x:c r="F161" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G161" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H161" s="0">
-        <x:v>5924046435</x:v>
+        <x:v>1742315226</x:v>
       </x:c>
       <x:c r="I161" s="0">
-        <x:v>0.0038</x:v>
+        <x:v>0.0543</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:9">
       <x:c r="A162" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B162" s="0">
-        <x:v>114.2</x:v>
+        <x:v>34.62</x:v>
       </x:c>
       <x:c r="C162" s="0">
-        <x:v>-1</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D162" s="0" t="s">
         <x:v>135</x:v>
       </x:c>
       <x:c r="E162" s="0">
-        <x:v>1875000</x:v>
+        <x:v>13766860</x:v>
       </x:c>
       <x:c r="F162" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G162" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H162" s="0">
-        <x:v>1742315226</x:v>
+        <x:v>11899043692</x:v>
       </x:c>
       <x:c r="I162" s="0">
-        <x:v>0.0543</x:v>
+        <x:v>0.0495</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:9">
       <x:c r="A163" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B163" s="0">
-        <x:v>34.66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C163" s="0">
-        <x:v>-0.92</x:v>
+        <x:v>5.05</x:v>
       </x:c>
       <x:c r="D163" s="0" t="s">
         <x:v>135</x:v>
       </x:c>
       <x:c r="E163" s="0">
-        <x:v>13766860</x:v>
+        <x:v>300000000</x:v>
       </x:c>
       <x:c r="F163" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G163" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H163" s="0">
-        <x:v>11899043692</x:v>
+        <x:v>8901819021</x:v>
       </x:c>
       <x:c r="I163" s="0">
-        <x:v>0.0495</x:v>
+        <x:v>0.0337</x:v>
       </x:c>
     </x:row>
     <x:row r="164" spans="1:9">
       <x:c r="A164" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B164" s="0">
-        <x:v>58.95</x:v>
+        <x:v>7.53</x:v>
       </x:c>
       <x:c r="C164" s="0">
-        <x:v>0.65</x:v>
+        <x:v>-0.32</x:v>
       </x:c>
       <x:c r="D164" s="0" t="s">
         <x:v>135</x:v>
       </x:c>
       <x:c r="E164" s="0">
-        <x:v>300000000</x:v>
+        <x:v>5553000</x:v>
       </x:c>
       <x:c r="F164" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G164" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H164" s="0">
-        <x:v>8901819021</x:v>
+        <x:v>9028523851</x:v>
       </x:c>
       <x:c r="I164" s="0">
-        <x:v>0.0337</x:v>
+        <x:v>0.0263</x:v>
       </x:c>
     </x:row>
     <x:row r="165" spans="1:9">
       <x:c r="A165" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B165" s="0">
-        <x:v>7.85</x:v>
+        <x:v>24.48</x:v>
       </x:c>
       <x:c r="C165" s="0">
-        <x:v>0.39</x:v>
+        <x:v>-0.72</x:v>
       </x:c>
       <x:c r="D165" s="0" t="s">
         <x:v>135</x:v>
       </x:c>
       <x:c r="E165" s="0">
-        <x:v>5553000</x:v>
+        <x:v>3375868924</x:v>
       </x:c>
       <x:c r="F165" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G165" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H165" s="0">
-        <x:v>9028523851</x:v>
+        <x:v>4975075028</x:v>
       </x:c>
       <x:c r="I165" s="0">
-        <x:v>0.0263</x:v>
+        <x:v>0.6786</x:v>
       </x:c>
     </x:row>
     <x:row r="166" spans="1:9">
       <x:c r="A166" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B166" s="0">
-        <x:v>25.2</x:v>
+        <x:v>53.3</x:v>
       </x:c>
       <x:c r="C166" s="0">
-        <x:v>0.12</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D166" s="0" t="s">
         <x:v>135</x:v>
       </x:c>
       <x:c r="E166" s="0">
-        <x:v>3375868924</x:v>
+        <x:v>28000000</x:v>
       </x:c>
       <x:c r="F166" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G166" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H166" s="0">
-        <x:v>4975075028</x:v>
+        <x:v>10597063406</x:v>
       </x:c>
       <x:c r="I166" s="0">
-        <x:v>0.6786</x:v>
+        <x:v>0.1131</x:v>
       </x:c>
     </x:row>
     <x:row r="167" spans="1:9">
       <x:c r="A167" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B167" s="0">
-        <x:v>53</x:v>
+        <x:v>42.1</x:v>
       </x:c>
       <x:c r="C167" s="0">
-        <x:v>0.5</x:v>
+        <x:v>3.82</x:v>
       </x:c>
       <x:c r="D167" s="0" t="s">
         <x:v>135</x:v>
       </x:c>
       <x:c r="E167" s="0">
-        <x:v>28000000</x:v>
+        <x:v>519168</x:v>
       </x:c>
       <x:c r="F167" s="0" t="s">
         <x:v>11</x:v>
@@ -6188,10 +6182,10 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H167" s="0">
-        <x:v>10597063406</x:v>
+        <x:v>5924046435</x:v>
       </x:c>
       <x:c r="I167" s="0">
-        <x:v>0.1131</x:v>
+        <x:v>0.0038</x:v>
       </x:c>
     </x:row>
     <x:row r="168" spans="1:9">
@@ -6199,10 +6193,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B168" s="0">
-        <x:v>41.76</x:v>
+        <x:v>42.88</x:v>
       </x:c>
       <x:c r="C168" s="0">
-        <x:v>-0.42</x:v>
+        <x:v>1.12</x:v>
       </x:c>
       <x:c r="D168" s="0" t="s">
         <x:v>138</x:v>
@@ -6228,10 +6222,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B169" s="0">
-        <x:v>41.76</x:v>
+        <x:v>42.88</x:v>
       </x:c>
       <x:c r="C169" s="0">
-        <x:v>-0.42</x:v>
+        <x:v>1.12</x:v>
       </x:c>
       <x:c r="D169" s="0" t="s">
         <x:v>138</x:v>
@@ -6257,10 +6251,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B170" s="0">
-        <x:v>95.95</x:v>
+        <x:v>95.4</x:v>
       </x:c>
       <x:c r="C170" s="0">
-        <x:v>-2.2</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="D170" s="0" t="s">
         <x:v>138</x:v>
@@ -6286,10 +6280,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B171" s="0">
-        <x:v>205.7</x:v>
+        <x:v>214.5</x:v>
       </x:c>
       <x:c r="C171" s="0">
-        <x:v>9</x:v>
+        <x:v>8.8</x:v>
       </x:c>
       <x:c r="D171" s="0" t="s">
         <x:v>138</x:v>
@@ -6315,10 +6309,10 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B172" s="0">
-        <x:v>7.85</x:v>
+        <x:v>7.53</x:v>
       </x:c>
       <x:c r="C172" s="0">
-        <x:v>0.39</x:v>
+        <x:v>-0.32</x:v>
       </x:c>
       <x:c r="D172" s="0" t="s">
         <x:v>138</x:v>
@@ -6344,10 +6338,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B173" s="0">
-        <x:v>53</x:v>
+        <x:v>53.3</x:v>
       </x:c>
       <x:c r="C173" s="0">
-        <x:v>0.5</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D173" s="0" t="s">
         <x:v>138</x:v>
@@ -6373,10 +6367,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B174" s="0">
-        <x:v>15.99</x:v>
+        <x:v>16.38</x:v>
       </x:c>
       <x:c r="C174" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.39</x:v>
       </x:c>
       <x:c r="D174" s="0" t="s">
         <x:v>139</x:v>
@@ -6402,10 +6396,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B175" s="0">
-        <x:v>15.99</x:v>
+        <x:v>16.38</x:v>
       </x:c>
       <x:c r="C175" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.39</x:v>
       </x:c>
       <x:c r="D175" s="0" t="s">
         <x:v>139</x:v>
@@ -6431,10 +6425,10 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B176" s="0">
-        <x:v>4.96</x:v>
+        <x:v>4.77</x:v>
       </x:c>
       <x:c r="C176" s="0">
-        <x:v>-0.11</x:v>
+        <x:v>-0.19</x:v>
       </x:c>
       <x:c r="D176" s="0" t="s">
         <x:v>139</x:v>
@@ -6460,10 +6454,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="B177" s="0">
-        <x:v>11.7</x:v>
+        <x:v>11.85</x:v>
       </x:c>
       <x:c r="C177" s="0">
-        <x:v>0.5</x:v>
+        <x:v>0.15</x:v>
       </x:c>
       <x:c r="D177" s="0" t="s">
         <x:v>139</x:v>
@@ -6489,10 +6483,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B178" s="0">
-        <x:v>114.2</x:v>
+        <x:v>115.2</x:v>
       </x:c>
       <x:c r="C178" s="0">
-        <x:v>-1</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D178" s="0" t="s">
         <x:v>139</x:v>
@@ -6518,10 +6512,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B179" s="0">
-        <x:v>95.95</x:v>
+        <x:v>95.4</x:v>
       </x:c>
       <x:c r="C179" s="0">
-        <x:v>-2.2</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="D179" s="0" t="s">
         <x:v>139</x:v>
@@ -6547,10 +6541,10 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="B180" s="0">
-        <x:v>14.43</x:v>
+        <x:v>12.99</x:v>
       </x:c>
       <x:c r="C180" s="0">
-        <x:v>1.31</x:v>
+        <x:v>-1.44</x:v>
       </x:c>
       <x:c r="D180" s="0" t="s">
         <x:v>139</x:v>
@@ -6576,10 +6570,10 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="B181" s="0">
-        <x:v>61.25</x:v>
+        <x:v>61.45</x:v>
       </x:c>
       <x:c r="C181" s="0">
-        <x:v>-1.4</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="D181" s="0" t="s">
         <x:v>139</x:v>
@@ -6605,10 +6599,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B182" s="0">
-        <x:v>66.75</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C182" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.35</x:v>
       </x:c>
       <x:c r="D182" s="0" t="s">
         <x:v>140</x:v>
@@ -6634,10 +6628,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B183" s="0">
-        <x:v>41.76</x:v>
+        <x:v>42.88</x:v>
       </x:c>
       <x:c r="C183" s="0">
-        <x:v>-0.42</x:v>
+        <x:v>1.12</x:v>
       </x:c>
       <x:c r="D183" s="0" t="s">
         <x:v>140</x:v>
@@ -6663,10 +6657,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B184" s="0">
-        <x:v>41.76</x:v>
+        <x:v>42.88</x:v>
       </x:c>
       <x:c r="C184" s="0">
-        <x:v>-0.42</x:v>
+        <x:v>1.12</x:v>
       </x:c>
       <x:c r="D184" s="0" t="s">
         <x:v>140</x:v>
@@ -6692,10 +6686,10 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="B185" s="0">
-        <x:v>22.1</x:v>
+        <x:v>21.8</x:v>
       </x:c>
       <x:c r="C185" s="0">
-        <x:v>-0.7</x:v>
+        <x:v>-0.3</x:v>
       </x:c>
       <x:c r="D185" s="0" t="s">
         <x:v>140</x:v>
@@ -6721,10 +6715,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B186" s="0">
-        <x:v>114.2</x:v>
+        <x:v>115.2</x:v>
       </x:c>
       <x:c r="C186" s="0">
-        <x:v>-1</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D186" s="0" t="s">
         <x:v>142</x:v>
@@ -6750,10 +6744,10 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="B187" s="0">
-        <x:v>22.1</x:v>
+        <x:v>21.8</x:v>
       </x:c>
       <x:c r="C187" s="0">
-        <x:v>-0.7</x:v>
+        <x:v>-0.3</x:v>
       </x:c>
       <x:c r="D187" s="0" t="s">
         <x:v>142</x:v>
@@ -6779,10 +6773,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B188" s="0">
-        <x:v>232.7</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C188" s="0">
-        <x:v>3.4</x:v>
+        <x:v>-2.7</x:v>
       </x:c>
       <x:c r="D188" s="0" t="s">
         <x:v>142</x:v>
@@ -6808,10 +6802,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B189" s="0">
-        <x:v>53</x:v>
+        <x:v>53.3</x:v>
       </x:c>
       <x:c r="C189" s="0">
-        <x:v>0.5</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D189" s="0" t="s">
         <x:v>142</x:v>
@@ -6837,10 +6831,10 @@
         <x:v>143</x:v>
       </x:c>
       <x:c r="B190" s="0">
-        <x:v>8.82</x:v>
+        <x:v>8.54</x:v>
       </x:c>
       <x:c r="C190" s="0">
-        <x:v>0.03</x:v>
+        <x:v>-0.28</x:v>
       </x:c>
       <x:c r="D190" s="0" t="s">
         <x:v>144</x:v>
@@ -6866,10 +6860,10 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B191" s="0">
-        <x:v>4.96</x:v>
+        <x:v>4.77</x:v>
       </x:c>
       <x:c r="C191" s="0">
-        <x:v>-0.11</x:v>
+        <x:v>-0.19</x:v>
       </x:c>
       <x:c r="D191" s="0" t="s">
         <x:v>144</x:v>
@@ -6895,10 +6889,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B192" s="0">
-        <x:v>3.51</x:v>
+        <x:v>3.7</x:v>
       </x:c>
       <x:c r="C192" s="0">
-        <x:v>-0.32</x:v>
+        <x:v>0.19</x:v>
       </x:c>
       <x:c r="D192" s="0" t="s">
         <x:v>144</x:v>
@@ -6924,10 +6918,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B193" s="0">
-        <x:v>408</x:v>
+        <x:v>396.5</x:v>
       </x:c>
       <x:c r="C193" s="0">
-        <x:v>-6</x:v>
+        <x:v>-11.5</x:v>
       </x:c>
       <x:c r="D193" s="0" t="s">
         <x:v>145</x:v>
@@ -6953,10 +6947,10 @@
         <x:v>146</x:v>
       </x:c>
       <x:c r="B194" s="0">
-        <x:v>564</x:v>
+        <x:v>554.5</x:v>
       </x:c>
       <x:c r="C194" s="0">
-        <x:v>-2</x:v>
+        <x:v>-9.5</x:v>
       </x:c>
       <x:c r="D194" s="0" t="s">
         <x:v>145</x:v>
@@ -6982,10 +6976,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B195" s="0">
-        <x:v>114.2</x:v>
+        <x:v>115.2</x:v>
       </x:c>
       <x:c r="C195" s="0">
-        <x:v>-1</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D195" s="0" t="s">
         <x:v>145</x:v>
@@ -7011,10 +7005,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B196" s="0">
-        <x:v>114.2</x:v>
+        <x:v>115.2</x:v>
       </x:c>
       <x:c r="C196" s="0">
-        <x:v>-1</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D196" s="0" t="s">
         <x:v>145</x:v>
@@ -7040,10 +7034,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B197" s="0">
-        <x:v>114.2</x:v>
+        <x:v>115.2</x:v>
       </x:c>
       <x:c r="C197" s="0">
-        <x:v>-1</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D197" s="0" t="s">
         <x:v>147</x:v>
@@ -7069,10 +7063,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B198" s="0">
-        <x:v>41.76</x:v>
+        <x:v>42.88</x:v>
       </x:c>
       <x:c r="C198" s="0">
-        <x:v>-0.42</x:v>
+        <x:v>1.12</x:v>
       </x:c>
       <x:c r="D198" s="0" t="s">
         <x:v>147</x:v>
@@ -7098,10 +7092,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B199" s="0">
-        <x:v>95.95</x:v>
+        <x:v>95.4</x:v>
       </x:c>
       <x:c r="C199" s="0">
-        <x:v>-2.2</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="D199" s="0" t="s">
         <x:v>147</x:v>
@@ -7127,10 +7121,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B200" s="0">
-        <x:v>3.51</x:v>
+        <x:v>3.7</x:v>
       </x:c>
       <x:c r="C200" s="0">
-        <x:v>-0.32</x:v>
+        <x:v>0.19</x:v>
       </x:c>
       <x:c r="D200" s="0" t="s">
         <x:v>147</x:v>
@@ -7156,10 +7150,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B201" s="0">
-        <x:v>3.51</x:v>
+        <x:v>3.7</x:v>
       </x:c>
       <x:c r="C201" s="0">
-        <x:v>-0.32</x:v>
+        <x:v>0.19</x:v>
       </x:c>
       <x:c r="D201" s="0" t="s">
         <x:v>147</x:v>
@@ -7185,10 +7179,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B202" s="0">
-        <x:v>3.51</x:v>
+        <x:v>3.7</x:v>
       </x:c>
       <x:c r="C202" s="0">
-        <x:v>-0.32</x:v>
+        <x:v>0.19</x:v>
       </x:c>
       <x:c r="D202" s="0" t="s">
         <x:v>147</x:v>
@@ -7214,10 +7208,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B203" s="0">
-        <x:v>47.7</x:v>
+        <x:v>47.26</x:v>
       </x:c>
       <x:c r="C203" s="0">
-        <x:v>0.14</x:v>
+        <x:v>-0.44</x:v>
       </x:c>
       <x:c r="D203" s="0" t="s">
         <x:v>147</x:v>
@@ -7243,10 +7237,10 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="B204" s="0">
-        <x:v>239.2</x:v>
+        <x:v>249.4</x:v>
       </x:c>
       <x:c r="C204" s="0">
-        <x:v>-26.55</x:v>
+        <x:v>10.2</x:v>
       </x:c>
       <x:c r="D204" s="0" t="s">
         <x:v>148</x:v>
@@ -7272,10 +7266,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B205" s="0">
-        <x:v>47.7</x:v>
+        <x:v>47.26</x:v>
       </x:c>
       <x:c r="C205" s="0">
-        <x:v>0.14</x:v>
+        <x:v>-0.44</x:v>
       </x:c>
       <x:c r="D205" s="0" t="s">
         <x:v>148</x:v>
@@ -7301,10 +7295,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B206" s="0">
-        <x:v>47.7</x:v>
+        <x:v>47.26</x:v>
       </x:c>
       <x:c r="C206" s="0">
-        <x:v>0.14</x:v>
+        <x:v>-0.44</x:v>
       </x:c>
       <x:c r="D206" s="0" t="s">
         <x:v>148</x:v>
@@ -7330,10 +7324,10 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B207" s="0">
-        <x:v>7.85</x:v>
+        <x:v>7.53</x:v>
       </x:c>
       <x:c r="C207" s="0">
-        <x:v>0.39</x:v>
+        <x:v>-0.32</x:v>
       </x:c>
       <x:c r="D207" s="0" t="s">
         <x:v>148</x:v>
@@ -7359,10 +7353,10 @@
         <x:v>149</x:v>
       </x:c>
       <x:c r="B208" s="0">
-        <x:v>17.8</x:v>
+        <x:v>19.25</x:v>
       </x:c>
       <x:c r="C208" s="0">
-        <x:v>0.24</x:v>
+        <x:v>1.45</x:v>
       </x:c>
       <x:c r="D208" s="0" t="s">
         <x:v>148</x:v>
@@ -7388,10 +7382,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B209" s="0">
-        <x:v>66.75</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C209" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.35</x:v>
       </x:c>
       <x:c r="D209" s="0" t="s">
         <x:v>150</x:v>
@@ -7417,10 +7411,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B210" s="0">
-        <x:v>41.76</x:v>
+        <x:v>42.88</x:v>
       </x:c>
       <x:c r="C210" s="0">
-        <x:v>-0.42</x:v>
+        <x:v>1.12</x:v>
       </x:c>
       <x:c r="D210" s="0" t="s">
         <x:v>150</x:v>
@@ -7443,13 +7437,13 @@
     </x:row>
     <x:row r="211" spans="1:9">
       <x:c r="A211" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B211" s="0">
-        <x:v>58.95</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C211" s="0">
-        <x:v>0.65</x:v>
+        <x:v>5.05</x:v>
       </x:c>
       <x:c r="D211" s="0" t="s">
         <x:v>150</x:v>
@@ -7475,10 +7469,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B212" s="0">
-        <x:v>79.8</x:v>
+        <x:v>82.15</x:v>
       </x:c>
       <x:c r="C212" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D212" s="0" t="s">
         <x:v>151</x:v>
@@ -7504,10 +7498,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B213" s="0">
-        <x:v>34.66</x:v>
+        <x:v>34.62</x:v>
       </x:c>
       <x:c r="C213" s="0">
-        <x:v>-0.92</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D213" s="0" t="s">
         <x:v>151</x:v>
@@ -7533,10 +7527,10 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="B214" s="0">
-        <x:v>22.1</x:v>
+        <x:v>21.8</x:v>
       </x:c>
       <x:c r="C214" s="0">
-        <x:v>-0.7</x:v>
+        <x:v>-0.3</x:v>
       </x:c>
       <x:c r="D214" s="0" t="s">
         <x:v>151</x:v>
@@ -7562,10 +7556,10 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="B215" s="0">
-        <x:v>22.1</x:v>
+        <x:v>21.8</x:v>
       </x:c>
       <x:c r="C215" s="0">
-        <x:v>-0.7</x:v>
+        <x:v>-0.3</x:v>
       </x:c>
       <x:c r="D215" s="0" t="s">
         <x:v>151</x:v>
@@ -7591,10 +7585,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B216" s="0">
-        <x:v>283.5</x:v>
+        <x:v>286.25</x:v>
       </x:c>
       <x:c r="C216" s="0">
-        <x:v>2.5</x:v>
+        <x:v>2.75</x:v>
       </x:c>
       <x:c r="D216" s="0" t="s">
         <x:v>152</x:v>
@@ -7620,10 +7614,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B217" s="0">
-        <x:v>283.5</x:v>
+        <x:v>286.25</x:v>
       </x:c>
       <x:c r="C217" s="0">
-        <x:v>2.5</x:v>
+        <x:v>2.75</x:v>
       </x:c>
       <x:c r="D217" s="0" t="s">
         <x:v>152</x:v>
@@ -7649,10 +7643,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B218" s="0">
-        <x:v>35.52</x:v>
+        <x:v>33.74</x:v>
       </x:c>
       <x:c r="C218" s="0">
-        <x:v>-0.88</x:v>
+        <x:v>-1.78</x:v>
       </x:c>
       <x:c r="D218" s="0" t="s">
         <x:v>152</x:v>
@@ -7678,10 +7672,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B219" s="0">
-        <x:v>79.8</x:v>
+        <x:v>82.15</x:v>
       </x:c>
       <x:c r="C219" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D219" s="0" t="s">
         <x:v>153</x:v>
@@ -7707,10 +7701,10 @@
         <x:v>154</x:v>
       </x:c>
       <x:c r="B220" s="0">
-        <x:v>20.54</x:v>
+        <x:v>20.02</x:v>
       </x:c>
       <x:c r="C220" s="0">
-        <x:v>0.14</x:v>
+        <x:v>-0.52</x:v>
       </x:c>
       <x:c r="D220" s="0" t="s">
         <x:v>153</x:v>
@@ -7736,10 +7730,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B221" s="0">
-        <x:v>41.76</x:v>
+        <x:v>42.88</x:v>
       </x:c>
       <x:c r="C221" s="0">
-        <x:v>-0.42</x:v>
+        <x:v>1.12</x:v>
       </x:c>
       <x:c r="D221" s="0" t="s">
         <x:v>155</x:v>
@@ -7762,13 +7756,13 @@
     </x:row>
     <x:row r="222" spans="1:9">
       <x:c r="A222" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B222" s="0">
-        <x:v>58.95</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C222" s="0">
-        <x:v>0.65</x:v>
+        <x:v>5.05</x:v>
       </x:c>
       <x:c r="D222" s="0" t="s">
         <x:v>155</x:v>
@@ -7794,10 +7788,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B223" s="0">
-        <x:v>25.2</x:v>
+        <x:v>24.48</x:v>
       </x:c>
       <x:c r="C223" s="0">
-        <x:v>0.12</x:v>
+        <x:v>-0.72</x:v>
       </x:c>
       <x:c r="D223" s="0" t="s">
         <x:v>155</x:v>
@@ -7823,10 +7817,10 @@
         <x:v>143</x:v>
       </x:c>
       <x:c r="B224" s="0">
-        <x:v>8.82</x:v>
+        <x:v>8.54</x:v>
       </x:c>
       <x:c r="C224" s="0">
-        <x:v>0.03</x:v>
+        <x:v>-0.28</x:v>
       </x:c>
       <x:c r="D224" s="0" t="s">
         <x:v>156</x:v>
@@ -7852,10 +7846,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B225" s="0">
-        <x:v>79.8</x:v>
+        <x:v>82.15</x:v>
       </x:c>
       <x:c r="C225" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D225" s="0" t="s">
         <x:v>156</x:v>
@@ -7881,10 +7875,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B226" s="0">
-        <x:v>47.7</x:v>
+        <x:v>47.26</x:v>
       </x:c>
       <x:c r="C226" s="0">
-        <x:v>0.14</x:v>
+        <x:v>-0.44</x:v>
       </x:c>
       <x:c r="D226" s="0" t="s">
         <x:v>157</x:v>
@@ -7910,10 +7904,10 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="B227" s="0">
-        <x:v>61.25</x:v>
+        <x:v>61.45</x:v>
       </x:c>
       <x:c r="C227" s="0">
-        <x:v>-1.4</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="D227" s="0" t="s">
         <x:v>157</x:v>
@@ -7939,10 +7933,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B228" s="0">
-        <x:v>42.78</x:v>
+        <x:v>40.48</x:v>
       </x:c>
       <x:c r="C228" s="0">
-        <x:v>0.62</x:v>
+        <x:v>-2.3</x:v>
       </x:c>
       <x:c r="D228" s="0" t="s">
         <x:v>158</x:v>
@@ -7968,10 +7962,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B229" s="0">
-        <x:v>34.66</x:v>
+        <x:v>34.62</x:v>
       </x:c>
       <x:c r="C229" s="0">
-        <x:v>-0.92</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D229" s="0" t="s">
         <x:v>158</x:v>
@@ -7997,10 +7991,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B230" s="0">
-        <x:v>41.76</x:v>
+        <x:v>42.88</x:v>
       </x:c>
       <x:c r="C230" s="0">
-        <x:v>-0.42</x:v>
+        <x:v>1.12</x:v>
       </x:c>
       <x:c r="D230" s="0" t="s">
         <x:v>158</x:v>
@@ -8026,10 +8020,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B231" s="0">
-        <x:v>62.5</x:v>
+        <x:v>60.9</x:v>
       </x:c>
       <x:c r="C231" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>-1.6</x:v>
       </x:c>
       <x:c r="D231" s="0" t="s">
         <x:v>159</x:v>
@@ -8055,10 +8049,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B232" s="0">
-        <x:v>5.52</x:v>
+        <x:v>5.49</x:v>
       </x:c>
       <x:c r="C232" s="0">
-        <x:v>-0.15</x:v>
+        <x:v>-0.03</x:v>
       </x:c>
       <x:c r="D232" s="0" t="s">
         <x:v>159</x:v>
@@ -8084,10 +8078,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B233" s="0">
-        <x:v>41.76</x:v>
+        <x:v>42.88</x:v>
       </x:c>
       <x:c r="C233" s="0">
-        <x:v>-0.42</x:v>
+        <x:v>1.12</x:v>
       </x:c>
       <x:c r="D233" s="0" t="s">
         <x:v>159</x:v>
@@ -8113,10 +8107,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B234" s="0">
-        <x:v>41.76</x:v>
+        <x:v>42.88</x:v>
       </x:c>
       <x:c r="C234" s="0">
-        <x:v>-0.42</x:v>
+        <x:v>1.12</x:v>
       </x:c>
       <x:c r="D234" s="0" t="s">
         <x:v>160</x:v>
@@ -8142,10 +8136,10 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="B235" s="0">
-        <x:v>61.25</x:v>
+        <x:v>61.45</x:v>
       </x:c>
       <x:c r="C235" s="0">
-        <x:v>-1.4</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="D235" s="0" t="s">
         <x:v>160</x:v>
@@ -8171,10 +8165,10 @@
         <x:v>143</x:v>
       </x:c>
       <x:c r="B236" s="0">
-        <x:v>8.82</x:v>
+        <x:v>8.54</x:v>
       </x:c>
       <x:c r="C236" s="0">
-        <x:v>0.03</x:v>
+        <x:v>-0.28</x:v>
       </x:c>
       <x:c r="D236" s="0" t="s">
         <x:v>161</x:v>
@@ -8200,10 +8194,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B237" s="0">
-        <x:v>4.5</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="C237" s="0">
-        <x:v>0.04</x:v>
+        <x:v>-0.17</x:v>
       </x:c>
       <x:c r="D237" s="0" t="s">
         <x:v>161</x:v>
@@ -8229,10 +8223,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B238" s="0">
-        <x:v>66.75</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C238" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.35</x:v>
       </x:c>
       <x:c r="D238" s="0" t="s">
         <x:v>162</x:v>
@@ -8258,10 +8252,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B239" s="0">
-        <x:v>66.75</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C239" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.35</x:v>
       </x:c>
       <x:c r="D239" s="0" t="s">
         <x:v>162</x:v>
@@ -8287,10 +8281,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B240" s="0">
-        <x:v>15.71</x:v>
+        <x:v>15.12</x:v>
       </x:c>
       <x:c r="C240" s="0">
-        <x:v>-0.09</x:v>
+        <x:v>-0.59</x:v>
       </x:c>
       <x:c r="D240" s="0" t="s">
         <x:v>162</x:v>
@@ -8316,10 +8310,10 @@
         <x:v>163</x:v>
       </x:c>
       <x:c r="B241" s="0">
-        <x:v>122.1</x:v>
+        <x:v>126.6</x:v>
       </x:c>
       <x:c r="C241" s="0">
-        <x:v>11.1</x:v>
+        <x:v>4.5</x:v>
       </x:c>
       <x:c r="D241" s="0" t="s">
         <x:v>162</x:v>
@@ -8345,10 +8339,10 @@
         <x:v>164</x:v>
       </x:c>
       <x:c r="B242" s="0">
-        <x:v>40.94</x:v>
+        <x:v>40.9</x:v>
       </x:c>
       <x:c r="C242" s="0">
-        <x:v>-0.72</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D242" s="0" t="s">
         <x:v>165</x:v>
@@ -8374,10 +8368,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B243" s="0">
-        <x:v>66.75</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C243" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.35</x:v>
       </x:c>
       <x:c r="D243" s="0" t="s">
         <x:v>166</x:v>
@@ -8403,10 +8397,10 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="B244" s="0">
-        <x:v>239.2</x:v>
+        <x:v>249.4</x:v>
       </x:c>
       <x:c r="C244" s="0">
-        <x:v>-26.55</x:v>
+        <x:v>10.2</x:v>
       </x:c>
       <x:c r="D244" s="0" t="s">
         <x:v>166</x:v>
@@ -8432,10 +8426,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B245" s="0">
-        <x:v>283.5</x:v>
+        <x:v>286.25</x:v>
       </x:c>
       <x:c r="C245" s="0">
-        <x:v>2.5</x:v>
+        <x:v>2.75</x:v>
       </x:c>
       <x:c r="D245" s="0" t="s">
         <x:v>166</x:v>
@@ -8461,10 +8455,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B246" s="0">
-        <x:v>232.7</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C246" s="0">
-        <x:v>3.4</x:v>
+        <x:v>-2.7</x:v>
       </x:c>
       <x:c r="D246" s="0" t="s">
         <x:v>166</x:v>
@@ -8490,10 +8484,10 @@
         <x:v>167</x:v>
       </x:c>
       <x:c r="B247" s="0">
-        <x:v>1127</x:v>
+        <x:v>1085</x:v>
       </x:c>
       <x:c r="C247" s="0">
-        <x:v>102</x:v>
+        <x:v>-42</x:v>
       </x:c>
       <x:c r="D247" s="0" t="s">
         <x:v>166</x:v>
@@ -8519,10 +8513,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B248" s="0">
-        <x:v>53</x:v>
+        <x:v>53.3</x:v>
       </x:c>
       <x:c r="C248" s="0">
-        <x:v>0.5</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D248" s="0" t="s">
         <x:v>166</x:v>
@@ -8548,10 +8542,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B249" s="0">
-        <x:v>62.5</x:v>
+        <x:v>60.9</x:v>
       </x:c>
       <x:c r="C249" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>-1.6</x:v>
       </x:c>
       <x:c r="D249" s="0" t="s">
         <x:v>168</x:v>
@@ -8577,10 +8571,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B250" s="0">
-        <x:v>15.99</x:v>
+        <x:v>16.38</x:v>
       </x:c>
       <x:c r="C250" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.39</x:v>
       </x:c>
       <x:c r="D250" s="0" t="s">
         <x:v>169</x:v>
@@ -8606,10 +8600,10 @@
         <x:v>170</x:v>
       </x:c>
       <x:c r="B251" s="0">
-        <x:v>16.13</x:v>
+        <x:v>15.61</x:v>
       </x:c>
       <x:c r="C251" s="0">
-        <x:v>0.24</x:v>
+        <x:v>-0.52</x:v>
       </x:c>
       <x:c r="D251" s="0" t="s">
         <x:v>169</x:v>
@@ -8635,10 +8629,10 @@
         <x:v>171</x:v>
       </x:c>
       <x:c r="B252" s="0">
-        <x:v>39.42</x:v>
+        <x:v>37.94</x:v>
       </x:c>
       <x:c r="C252" s="0">
-        <x:v>1.02</x:v>
+        <x:v>-1.48</x:v>
       </x:c>
       <x:c r="D252" s="0" t="s">
         <x:v>169</x:v>
@@ -8664,10 +8658,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B253" s="0">
-        <x:v>232.7</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C253" s="0">
-        <x:v>3.4</x:v>
+        <x:v>-2.7</x:v>
       </x:c>
       <x:c r="D253" s="0" t="s">
         <x:v>169</x:v>
@@ -8693,10 +8687,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B254" s="0">
-        <x:v>3.51</x:v>
+        <x:v>3.7</x:v>
       </x:c>
       <x:c r="C254" s="0">
-        <x:v>-0.32</x:v>
+        <x:v>0.19</x:v>
       </x:c>
       <x:c r="D254" s="0" t="s">
         <x:v>169</x:v>
@@ -8722,10 +8716,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B255" s="0">
-        <x:v>47.7</x:v>
+        <x:v>47.26</x:v>
       </x:c>
       <x:c r="C255" s="0">
-        <x:v>0.14</x:v>
+        <x:v>-0.44</x:v>
       </x:c>
       <x:c r="D255" s="0" t="s">
         <x:v>169</x:v>
@@ -8751,10 +8745,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B256" s="0">
-        <x:v>34.66</x:v>
+        <x:v>34.62</x:v>
       </x:c>
       <x:c r="C256" s="0">
-        <x:v>-0.92</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D256" s="0" t="s">
         <x:v>172</x:v>
@@ -8780,10 +8774,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B257" s="0">
-        <x:v>47.7</x:v>
+        <x:v>47.26</x:v>
       </x:c>
       <x:c r="C257" s="0">
-        <x:v>0.14</x:v>
+        <x:v>-0.44</x:v>
       </x:c>
       <x:c r="D257" s="0" t="s">
         <x:v>172</x:v>
@@ -8809,10 +8803,10 @@
         <x:v>164</x:v>
       </x:c>
       <x:c r="B258" s="0">
-        <x:v>40.94</x:v>
+        <x:v>40.9</x:v>
       </x:c>
       <x:c r="C258" s="0">
-        <x:v>-0.72</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D258" s="0" t="s">
         <x:v>172</x:v>
@@ -8838,10 +8832,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B259" s="0">
-        <x:v>408</x:v>
+        <x:v>396.5</x:v>
       </x:c>
       <x:c r="C259" s="0">
-        <x:v>-6</x:v>
+        <x:v>-11.5</x:v>
       </x:c>
       <x:c r="D259" s="0" t="s">
         <x:v>173</x:v>
@@ -8867,10 +8861,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B260" s="0">
-        <x:v>79.8</x:v>
+        <x:v>82.15</x:v>
       </x:c>
       <x:c r="C260" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D260" s="0" t="s">
         <x:v>174</x:v>
@@ -8896,10 +8890,10 @@
         <x:v>175</x:v>
       </x:c>
       <x:c r="B261" s="0">
-        <x:v>18.59</x:v>
+        <x:v>18.9</x:v>
       </x:c>
       <x:c r="C261" s="0">
-        <x:v>0.08</x:v>
+        <x:v>0.31</x:v>
       </x:c>
       <x:c r="D261" s="0" t="s">
         <x:v>174</x:v>
@@ -8925,10 +8919,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B262" s="0">
-        <x:v>408</x:v>
+        <x:v>396.5</x:v>
       </x:c>
       <x:c r="C262" s="0">
-        <x:v>-6</x:v>
+        <x:v>-11.5</x:v>
       </x:c>
       <x:c r="D262" s="0" t="s">
         <x:v>176</x:v>
@@ -8954,10 +8948,10 @@
         <x:v>143</x:v>
       </x:c>
       <x:c r="B263" s="0">
-        <x:v>8.82</x:v>
+        <x:v>8.54</x:v>
       </x:c>
       <x:c r="C263" s="0">
-        <x:v>0.03</x:v>
+        <x:v>-0.28</x:v>
       </x:c>
       <x:c r="D263" s="0" t="s">
         <x:v>176</x:v>
@@ -8983,10 +8977,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B264" s="0">
-        <x:v>79.8</x:v>
+        <x:v>82.15</x:v>
       </x:c>
       <x:c r="C264" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D264" s="0" t="s">
         <x:v>176</x:v>
@@ -9012,10 +9006,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B265" s="0">
-        <x:v>34.66</x:v>
+        <x:v>34.62</x:v>
       </x:c>
       <x:c r="C265" s="0">
-        <x:v>-0.92</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D265" s="0" t="s">
         <x:v>176</x:v>
@@ -9041,10 +9035,10 @@
         <x:v>177</x:v>
       </x:c>
       <x:c r="B266" s="0">
-        <x:v>41.02</x:v>
+        <x:v>40.6</x:v>
       </x:c>
       <x:c r="C266" s="0">
-        <x:v>0.56</x:v>
+        <x:v>-0.42</x:v>
       </x:c>
       <x:c r="D266" s="0" t="s">
         <x:v>176</x:v>
@@ -9070,10 +9064,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B267" s="0">
-        <x:v>47</x:v>
+        <x:v>47.02</x:v>
       </x:c>
       <x:c r="C267" s="0">
-        <x:v>0.32</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="D267" s="0" t="s">
         <x:v>176</x:v>
@@ -9099,10 +9093,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B268" s="0">
-        <x:v>408</x:v>
+        <x:v>396.5</x:v>
       </x:c>
       <x:c r="C268" s="0">
-        <x:v>-6</x:v>
+        <x:v>-11.5</x:v>
       </x:c>
       <x:c r="D268" s="0" t="s">
         <x:v>178</x:v>
@@ -9128,10 +9122,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B269" s="0">
-        <x:v>34.66</x:v>
+        <x:v>34.62</x:v>
       </x:c>
       <x:c r="C269" s="0">
-        <x:v>-0.92</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D269" s="0" t="s">
         <x:v>178</x:v>
@@ -9157,10 +9151,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B270" s="0">
-        <x:v>34.66</x:v>
+        <x:v>34.62</x:v>
       </x:c>
       <x:c r="C270" s="0">
-        <x:v>-0.92</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D270" s="0" t="s">
         <x:v>179</x:v>
@@ -9186,10 +9180,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B271" s="0">
-        <x:v>283.5</x:v>
+        <x:v>286.25</x:v>
       </x:c>
       <x:c r="C271" s="0">
-        <x:v>2.5</x:v>
+        <x:v>2.75</x:v>
       </x:c>
       <x:c r="D271" s="0" t="s">
         <x:v>179</x:v>
@@ -9215,10 +9209,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B272" s="0">
-        <x:v>66.75</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C272" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.35</x:v>
       </x:c>
       <x:c r="D272" s="0" t="s">
         <x:v>180</x:v>
@@ -9244,10 +9238,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B273" s="0">
-        <x:v>47.7</x:v>
+        <x:v>47.26</x:v>
       </x:c>
       <x:c r="C273" s="0">
-        <x:v>0.14</x:v>
+        <x:v>-0.44</x:v>
       </x:c>
       <x:c r="D273" s="0" t="s">
         <x:v>180</x:v>
@@ -9273,10 +9267,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B274" s="0">
-        <x:v>408</x:v>
+        <x:v>396.5</x:v>
       </x:c>
       <x:c r="C274" s="0">
-        <x:v>-6</x:v>
+        <x:v>-11.5</x:v>
       </x:c>
       <x:c r="D274" s="0" t="s">
         <x:v>181</x:v>
@@ -9302,10 +9296,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B275" s="0">
-        <x:v>15.71</x:v>
+        <x:v>15.12</x:v>
       </x:c>
       <x:c r="C275" s="0">
-        <x:v>-0.09</x:v>
+        <x:v>-0.59</x:v>
       </x:c>
       <x:c r="D275" s="0" t="s">
         <x:v>181</x:v>
@@ -9331,10 +9325,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B276" s="0">
-        <x:v>114.2</x:v>
+        <x:v>115.2</x:v>
       </x:c>
       <x:c r="C276" s="0">
-        <x:v>-1</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D276" s="0" t="s">
         <x:v>181</x:v>
@@ -9360,10 +9354,10 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="B277" s="0">
-        <x:v>61.25</x:v>
+        <x:v>61.45</x:v>
       </x:c>
       <x:c r="C277" s="0">
-        <x:v>-1.4</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="D277" s="0" t="s">
         <x:v>181</x:v>
@@ -9389,10 +9383,10 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="B278" s="0">
-        <x:v>22.1</x:v>
+        <x:v>21.8</x:v>
       </x:c>
       <x:c r="C278" s="0">
-        <x:v>-0.7</x:v>
+        <x:v>-0.3</x:v>
       </x:c>
       <x:c r="D278" s="0" t="s">
         <x:v>182</x:v>
@@ -9418,10 +9412,10 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="B279" s="0">
-        <x:v>239.2</x:v>
+        <x:v>249.4</x:v>
       </x:c>
       <x:c r="C279" s="0">
-        <x:v>-26.55</x:v>
+        <x:v>10.2</x:v>
       </x:c>
       <x:c r="D279" s="0" t="s">
         <x:v>182</x:v>
@@ -9447,10 +9441,10 @@
         <x:v>177</x:v>
       </x:c>
       <x:c r="B280" s="0">
-        <x:v>41.02</x:v>
+        <x:v>40.6</x:v>
       </x:c>
       <x:c r="C280" s="0">
-        <x:v>0.56</x:v>
+        <x:v>-0.42</x:v>
       </x:c>
       <x:c r="D280" s="0" t="s">
         <x:v>182</x:v>
@@ -9476,10 +9470,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B281" s="0">
-        <x:v>62.5</x:v>
+        <x:v>60.9</x:v>
       </x:c>
       <x:c r="C281" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>-1.6</x:v>
       </x:c>
       <x:c r="D281" s="0" t="s">
         <x:v>183</x:v>
@@ -9505,10 +9499,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B282" s="0">
-        <x:v>79.8</x:v>
+        <x:v>82.15</x:v>
       </x:c>
       <x:c r="C282" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D282" s="0" t="s">
         <x:v>183</x:v>
@@ -9534,10 +9528,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B283" s="0">
-        <x:v>79.8</x:v>
+        <x:v>82.15</x:v>
       </x:c>
       <x:c r="C283" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D283" s="0" t="s">
         <x:v>183</x:v>
@@ -9563,10 +9557,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B284" s="0">
-        <x:v>34.66</x:v>
+        <x:v>34.62</x:v>
       </x:c>
       <x:c r="C284" s="0">
-        <x:v>-0.92</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D284" s="0" t="s">
         <x:v>183</x:v>
@@ -9592,10 +9586,10 @@
         <x:v>184</x:v>
       </x:c>
       <x:c r="B285" s="0">
-        <x:v>34.54</x:v>
+        <x:v>37.32</x:v>
       </x:c>
       <x:c r="C285" s="0">
-        <x:v>-1.34</x:v>
+        <x:v>2.78</x:v>
       </x:c>
       <x:c r="D285" s="0" t="s">
         <x:v>183</x:v>
@@ -9621,10 +9615,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B286" s="0">
-        <x:v>920</x:v>
+        <x:v>940</x:v>
       </x:c>
       <x:c r="C286" s="0">
-        <x:v>35.5</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D286" s="0" t="s">
         <x:v>185</x:v>
@@ -9650,10 +9644,10 @@
         <x:v>186</x:v>
       </x:c>
       <x:c r="B287" s="0">
-        <x:v>7.02</x:v>
+        <x:v>7.72</x:v>
       </x:c>
       <x:c r="C287" s="0">
-        <x:v>0.63</x:v>
+        <x:v>0.7</x:v>
       </x:c>
       <x:c r="D287" s="0" t="s">
         <x:v>187</x:v>
@@ -9679,10 +9673,10 @@
         <x:v>167</x:v>
       </x:c>
       <x:c r="B288" s="0">
-        <x:v>1127</x:v>
+        <x:v>1085</x:v>
       </x:c>
       <x:c r="C288" s="0">
-        <x:v>102</x:v>
+        <x:v>-42</x:v>
       </x:c>
       <x:c r="D288" s="0" t="s">
         <x:v>187</x:v>
@@ -9708,10 +9702,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B289" s="0">
-        <x:v>62.5</x:v>
+        <x:v>60.9</x:v>
       </x:c>
       <x:c r="C289" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>-1.6</x:v>
       </x:c>
       <x:c r="D289" s="0" t="s">
         <x:v>188</x:v>
@@ -9737,10 +9731,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B290" s="0">
-        <x:v>34.66</x:v>
+        <x:v>34.62</x:v>
       </x:c>
       <x:c r="C290" s="0">
-        <x:v>-0.92</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D290" s="0" t="s">
         <x:v>188</x:v>
@@ -9766,10 +9760,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B291" s="0">
-        <x:v>232.7</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C291" s="0">
-        <x:v>3.4</x:v>
+        <x:v>-2.7</x:v>
       </x:c>
       <x:c r="D291" s="0" t="s">
         <x:v>188</x:v>
@@ -9795,10 +9789,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B292" s="0">
-        <x:v>95.95</x:v>
+        <x:v>95.4</x:v>
       </x:c>
       <x:c r="C292" s="0">
-        <x:v>-2.2</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="D292" s="0" t="s">
         <x:v>188</x:v>
@@ -9824,10 +9818,10 @@
         <x:v>146</x:v>
       </x:c>
       <x:c r="B293" s="0">
-        <x:v>564</x:v>
+        <x:v>554.5</x:v>
       </x:c>
       <x:c r="C293" s="0">
-        <x:v>-2</x:v>
+        <x:v>-9.5</x:v>
       </x:c>
       <x:c r="D293" s="0" t="s">
         <x:v>189</x:v>
@@ -9853,10 +9847,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B294" s="0">
-        <x:v>114.2</x:v>
+        <x:v>115.2</x:v>
       </x:c>
       <x:c r="C294" s="0">
-        <x:v>-1</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D294" s="0" t="s">
         <x:v>189</x:v>
@@ -9882,10 +9876,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B295" s="0">
-        <x:v>47</x:v>
+        <x:v>47.02</x:v>
       </x:c>
       <x:c r="C295" s="0">
-        <x:v>0.32</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="D295" s="0" t="s">
         <x:v>189</x:v>
@@ -9911,10 +9905,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B296" s="0">
-        <x:v>205.7</x:v>
+        <x:v>214.5</x:v>
       </x:c>
       <x:c r="C296" s="0">
-        <x:v>9</x:v>
+        <x:v>8.8</x:v>
       </x:c>
       <x:c r="D296" s="0" t="s">
         <x:v>189</x:v>
@@ -9940,10 +9934,10 @@
         <x:v>154</x:v>
       </x:c>
       <x:c r="B297" s="0">
-        <x:v>20.54</x:v>
+        <x:v>20.02</x:v>
       </x:c>
       <x:c r="C297" s="0">
-        <x:v>0.14</x:v>
+        <x:v>-0.52</x:v>
       </x:c>
       <x:c r="D297" s="0" t="s">
         <x:v>190</x:v>
@@ -9969,10 +9963,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B298" s="0">
-        <x:v>232.7</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C298" s="0">
-        <x:v>3.4</x:v>
+        <x:v>-2.7</x:v>
       </x:c>
       <x:c r="D298" s="0" t="s">
         <x:v>190</x:v>
@@ -9998,10 +9992,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B299" s="0">
-        <x:v>15.99</x:v>
+        <x:v>16.38</x:v>
       </x:c>
       <x:c r="C299" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.39</x:v>
       </x:c>
       <x:c r="D299" s="0" t="s">
         <x:v>191</x:v>
@@ -10027,10 +10021,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B300" s="0">
-        <x:v>283.5</x:v>
+        <x:v>286.25</x:v>
       </x:c>
       <x:c r="C300" s="0">
-        <x:v>2.5</x:v>
+        <x:v>2.75</x:v>
       </x:c>
       <x:c r="D300" s="0" t="s">
         <x:v>191</x:v>
@@ -10056,10 +10050,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B301" s="0">
-        <x:v>15.99</x:v>
+        <x:v>16.38</x:v>
       </x:c>
       <x:c r="C301" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.39</x:v>
       </x:c>
       <x:c r="D301" s="0" t="s">
         <x:v>192</x:v>
@@ -10085,10 +10079,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B302" s="0">
-        <x:v>15.99</x:v>
+        <x:v>16.38</x:v>
       </x:c>
       <x:c r="C302" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.39</x:v>
       </x:c>
       <x:c r="D302" s="0" t="s">
         <x:v>192</x:v>
@@ -10114,10 +10108,10 @@
         <x:v>154</x:v>
       </x:c>
       <x:c r="B303" s="0">
-        <x:v>20.54</x:v>
+        <x:v>20.02</x:v>
       </x:c>
       <x:c r="C303" s="0">
-        <x:v>0.14</x:v>
+        <x:v>-0.52</x:v>
       </x:c>
       <x:c r="D303" s="0" t="s">
         <x:v>192</x:v>
@@ -10143,10 +10137,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B304" s="0">
-        <x:v>3.51</x:v>
+        <x:v>3.7</x:v>
       </x:c>
       <x:c r="C304" s="0">
-        <x:v>-0.32</x:v>
+        <x:v>0.19</x:v>
       </x:c>
       <x:c r="D304" s="0" t="s">
         <x:v>192</x:v>
@@ -10172,10 +10166,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B305" s="0">
-        <x:v>3.51</x:v>
+        <x:v>3.7</x:v>
       </x:c>
       <x:c r="C305" s="0">
-        <x:v>-0.32</x:v>
+        <x:v>0.19</x:v>
       </x:c>
       <x:c r="D305" s="0" t="s">
         <x:v>192</x:v>
@@ -10201,10 +10195,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B306" s="0">
-        <x:v>4.5</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="C306" s="0">
-        <x:v>0.04</x:v>
+        <x:v>-0.17</x:v>
       </x:c>
       <x:c r="D306" s="0" t="s">
         <x:v>192</x:v>
@@ -10230,10 +10224,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B307" s="0">
-        <x:v>66.75</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C307" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.35</x:v>
       </x:c>
       <x:c r="D307" s="0" t="s">
         <x:v>193</x:v>
@@ -10259,10 +10253,10 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="B308" s="0">
-        <x:v>103</x:v>
+        <x:v>104.9</x:v>
       </x:c>
       <x:c r="C308" s="0">
-        <x:v>5.3</x:v>
+        <x:v>1.9</x:v>
       </x:c>
       <x:c r="D308" s="0" t="s">
         <x:v>193</x:v>
@@ -10288,10 +10282,10 @@
         <x:v>163</x:v>
       </x:c>
       <x:c r="B309" s="0">
-        <x:v>122.1</x:v>
+        <x:v>126.6</x:v>
       </x:c>
       <x:c r="C309" s="0">
-        <x:v>11.1</x:v>
+        <x:v>4.5</x:v>
       </x:c>
       <x:c r="D309" s="0" t="s">
         <x:v>194</x:v>
@@ -10317,10 +10311,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B310" s="0">
-        <x:v>114.2</x:v>
+        <x:v>115.2</x:v>
       </x:c>
       <x:c r="C310" s="0">
-        <x:v>-1</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D310" s="0" t="s">
         <x:v>195</x:v>
@@ -10346,10 +10340,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B311" s="0">
-        <x:v>232.7</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C311" s="0">
-        <x:v>3.4</x:v>
+        <x:v>-2.7</x:v>
       </x:c>
       <x:c r="D311" s="0" t="s">
         <x:v>195</x:v>
@@ -10375,10 +10369,10 @@
         <x:v>196</x:v>
       </x:c>
       <x:c r="B312" s="0">
-        <x:v>292</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="C312" s="0">
-        <x:v>-2.5</x:v>
+        <x:v>-3</x:v>
       </x:c>
       <x:c r="D312" s="0" t="s">
         <x:v>197</x:v>
@@ -10404,10 +10398,10 @@
         <x:v>154</x:v>
       </x:c>
       <x:c r="B313" s="0">
-        <x:v>20.54</x:v>
+        <x:v>20.02</x:v>
       </x:c>
       <x:c r="C313" s="0">
-        <x:v>0.14</x:v>
+        <x:v>-0.52</x:v>
       </x:c>
       <x:c r="D313" s="0" t="s">
         <x:v>197</x:v>
@@ -10433,10 +10427,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B314" s="0">
-        <x:v>283.5</x:v>
+        <x:v>286.25</x:v>
       </x:c>
       <x:c r="C314" s="0">
-        <x:v>2.5</x:v>
+        <x:v>2.75</x:v>
       </x:c>
       <x:c r="D314" s="0" t="s">
         <x:v>198</x:v>
@@ -10462,10 +10456,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B315" s="0">
-        <x:v>4.5</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="C315" s="0">
-        <x:v>0.04</x:v>
+        <x:v>-0.17</x:v>
       </x:c>
       <x:c r="D315" s="0" t="s">
         <x:v>199</x:v>
@@ -10491,10 +10485,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B316" s="0">
-        <x:v>5.94</x:v>
+        <x:v>5.87</x:v>
       </x:c>
       <x:c r="C316" s="0">
-        <x:v>0.07</x:v>
+        <x:v>-0.07</x:v>
       </x:c>
       <x:c r="D316" s="0" t="s">
         <x:v>199</x:v>
@@ -10520,10 +10514,10 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="B317" s="0">
-        <x:v>24.18</x:v>
+        <x:v>24.04</x:v>
       </x:c>
       <x:c r="C317" s="0">
-        <x:v>0.06</x:v>
+        <x:v>-0.14</x:v>
       </x:c>
       <x:c r="D317" s="0" t="s">
         <x:v>200</x:v>
@@ -10549,10 +10543,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B318" s="0">
-        <x:v>34.66</x:v>
+        <x:v>34.62</x:v>
       </x:c>
       <x:c r="C318" s="0">
-        <x:v>-0.92</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D318" s="0" t="s">
         <x:v>201</x:v>
@@ -10578,10 +10572,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B319" s="0">
-        <x:v>5.52</x:v>
+        <x:v>5.49</x:v>
       </x:c>
       <x:c r="C319" s="0">
-        <x:v>-0.15</x:v>
+        <x:v>-0.03</x:v>
       </x:c>
       <x:c r="D319" s="0" t="s">
         <x:v>202</x:v>
@@ -10607,10 +10601,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B320" s="0">
-        <x:v>34.66</x:v>
+        <x:v>34.62</x:v>
       </x:c>
       <x:c r="C320" s="0">
-        <x:v>-0.92</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D320" s="0" t="s">
         <x:v>202</x:v>
@@ -10636,10 +10630,10 @@
         <x:v>154</x:v>
       </x:c>
       <x:c r="B321" s="0">
-        <x:v>20.54</x:v>
+        <x:v>20.02</x:v>
       </x:c>
       <x:c r="C321" s="0">
-        <x:v>0.14</x:v>
+        <x:v>-0.52</x:v>
       </x:c>
       <x:c r="D321" s="0" t="s">
         <x:v>202</x:v>
@@ -10665,10 +10659,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B322" s="0">
-        <x:v>283.5</x:v>
+        <x:v>286.25</x:v>
       </x:c>
       <x:c r="C322" s="0">
-        <x:v>2.5</x:v>
+        <x:v>2.75</x:v>
       </x:c>
       <x:c r="D322" s="0" t="s">
         <x:v>202</x:v>
@@ -10694,10 +10688,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B323" s="0">
-        <x:v>53</x:v>
+        <x:v>53.3</x:v>
       </x:c>
       <x:c r="C323" s="0">
-        <x:v>0.5</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D323" s="0" t="s">
         <x:v>202</x:v>
@@ -10723,10 +10717,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B324" s="0">
-        <x:v>48.42</x:v>
+        <x:v>47.82</x:v>
       </x:c>
       <x:c r="C324" s="0">
-        <x:v>-0.54</x:v>
+        <x:v>-0.6</x:v>
       </x:c>
       <x:c r="D324" s="0" t="s">
         <x:v>203</x:v>
@@ -10752,10 +10746,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B325" s="0">
-        <x:v>48.42</x:v>
+        <x:v>47.82</x:v>
       </x:c>
       <x:c r="C325" s="0">
-        <x:v>-0.54</x:v>
+        <x:v>-0.6</x:v>
       </x:c>
       <x:c r="D325" s="0" t="s">
         <x:v>203</x:v>
@@ -10781,10 +10775,10 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B326" s="0">
-        <x:v>4.96</x:v>
+        <x:v>4.77</x:v>
       </x:c>
       <x:c r="C326" s="0">
-        <x:v>-0.11</x:v>
+        <x:v>-0.19</x:v>
       </x:c>
       <x:c r="D326" s="0" t="s">
         <x:v>203</x:v>
@@ -10810,10 +10804,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B327" s="0">
-        <x:v>53</x:v>
+        <x:v>53.3</x:v>
       </x:c>
       <x:c r="C327" s="0">
-        <x:v>0.5</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D327" s="0" t="s">
         <x:v>203</x:v>
@@ -10839,10 +10833,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B328" s="0">
-        <x:v>34.66</x:v>
+        <x:v>34.62</x:v>
       </x:c>
       <x:c r="C328" s="0">
-        <x:v>-0.92</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D328" s="0" t="s">
         <x:v>204</x:v>
@@ -10868,10 +10862,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B329" s="0">
-        <x:v>283.5</x:v>
+        <x:v>286.25</x:v>
       </x:c>
       <x:c r="C329" s="0">
-        <x:v>2.5</x:v>
+        <x:v>2.75</x:v>
       </x:c>
       <x:c r="D329" s="0" t="s">
         <x:v>204</x:v>
@@ -10897,10 +10891,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B330" s="0">
-        <x:v>47.7</x:v>
+        <x:v>47.26</x:v>
       </x:c>
       <x:c r="C330" s="0">
-        <x:v>0.14</x:v>
+        <x:v>-0.44</x:v>
       </x:c>
       <x:c r="D330" s="0" t="s">
         <x:v>204</x:v>
@@ -10926,10 +10920,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B331" s="0">
-        <x:v>920</x:v>
+        <x:v>940</x:v>
       </x:c>
       <x:c r="C331" s="0">
-        <x:v>35.5</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D331" s="0" t="s">
         <x:v>204</x:v>
@@ -10955,10 +10949,10 @@
         <x:v>112</x:v>
       </x:c>
       <x:c r="B332" s="0">
-        <x:v>26.32</x:v>
+        <x:v>25.88</x:v>
       </x:c>
       <x:c r="C332" s="0">
-        <x:v>0.02</x:v>
+        <x:v>-0.44</x:v>
       </x:c>
       <x:c r="D332" s="0" t="s">
         <x:v>205</x:v>
@@ -10984,10 +10978,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B333" s="0">
-        <x:v>34.66</x:v>
+        <x:v>34.62</x:v>
       </x:c>
       <x:c r="C333" s="0">
-        <x:v>-0.92</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D333" s="0" t="s">
         <x:v>205</x:v>
@@ -11013,10 +11007,10 @@
         <x:v>206</x:v>
       </x:c>
       <x:c r="B334" s="0">
-        <x:v>30.94</x:v>
+        <x:v>28.04</x:v>
       </x:c>
       <x:c r="C334" s="0">
-        <x:v>1.5</x:v>
+        <x:v>-2.9</x:v>
       </x:c>
       <x:c r="D334" s="0" t="s">
         <x:v>207</x:v>
@@ -11042,10 +11036,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B335" s="0">
-        <x:v>66.75</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C335" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.35</x:v>
       </x:c>
       <x:c r="D335" s="0" t="s">
         <x:v>208</x:v>
@@ -11071,10 +11065,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B336" s="0">
-        <x:v>5.52</x:v>
+        <x:v>5.49</x:v>
       </x:c>
       <x:c r="C336" s="0">
-        <x:v>-0.15</x:v>
+        <x:v>-0.03</x:v>
       </x:c>
       <x:c r="D336" s="0" t="s">
         <x:v>208</x:v>
@@ -11100,10 +11094,10 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B337" s="0">
-        <x:v>4.96</x:v>
+        <x:v>4.77</x:v>
       </x:c>
       <x:c r="C337" s="0">
-        <x:v>-0.11</x:v>
+        <x:v>-0.19</x:v>
       </x:c>
       <x:c r="D337" s="0" t="s">
         <x:v>208</x:v>
@@ -11129,10 +11123,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B338" s="0">
-        <x:v>114.2</x:v>
+        <x:v>115.2</x:v>
       </x:c>
       <x:c r="C338" s="0">
-        <x:v>-1</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D338" s="0" t="s">
         <x:v>209</x:v>
@@ -11158,10 +11152,10 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="B339" s="0">
-        <x:v>59.25</x:v>
+        <x:v>55.95</x:v>
       </x:c>
       <x:c r="C339" s="0">
-        <x:v>5.35</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="D339" s="0" t="s">
         <x:v>209</x:v>
@@ -11187,10 +11181,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B340" s="0">
-        <x:v>5.52</x:v>
+        <x:v>5.49</x:v>
       </x:c>
       <x:c r="C340" s="0">
-        <x:v>-0.15</x:v>
+        <x:v>-0.03</x:v>
       </x:c>
       <x:c r="D340" s="0" t="s">
         <x:v>210</x:v>
@@ -11216,10 +11210,10 @@
         <x:v>206</x:v>
       </x:c>
       <x:c r="B341" s="0">
-        <x:v>30.94</x:v>
+        <x:v>28.04</x:v>
       </x:c>
       <x:c r="C341" s="0">
-        <x:v>1.5</x:v>
+        <x:v>-2.9</x:v>
       </x:c>
       <x:c r="D341" s="0" t="s">
         <x:v>210</x:v>
@@ -11245,10 +11239,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B342" s="0">
-        <x:v>35.52</x:v>
+        <x:v>33.74</x:v>
       </x:c>
       <x:c r="C342" s="0">
-        <x:v>-0.88</x:v>
+        <x:v>-1.78</x:v>
       </x:c>
       <x:c r="D342" s="0" t="s">
         <x:v>210</x:v>
@@ -11274,10 +11268,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B343" s="0">
-        <x:v>114.2</x:v>
+        <x:v>115.2</x:v>
       </x:c>
       <x:c r="C343" s="0">
-        <x:v>-1</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D343" s="0" t="s">
         <x:v>211</x:v>
@@ -11303,10 +11297,10 @@
         <x:v>167</x:v>
       </x:c>
       <x:c r="B344" s="0">
-        <x:v>1127</x:v>
+        <x:v>1085</x:v>
       </x:c>
       <x:c r="C344" s="0">
-        <x:v>102</x:v>
+        <x:v>-42</x:v>
       </x:c>
       <x:c r="D344" s="0" t="s">
         <x:v>212</x:v>
@@ -11332,10 +11326,10 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="B345" s="0">
-        <x:v>239.2</x:v>
+        <x:v>249.4</x:v>
       </x:c>
       <x:c r="C345" s="0">
-        <x:v>-26.55</x:v>
+        <x:v>10.2</x:v>
       </x:c>
       <x:c r="D345" s="0" t="s">
         <x:v>213</x:v>
@@ -11361,10 +11355,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B346" s="0">
-        <x:v>3.51</x:v>
+        <x:v>3.7</x:v>
       </x:c>
       <x:c r="C346" s="0">
-        <x:v>-0.32</x:v>
+        <x:v>0.19</x:v>
       </x:c>
       <x:c r="D346" s="0" t="s">
         <x:v>213</x:v>
@@ -11390,10 +11384,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B347" s="0">
-        <x:v>66.75</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C347" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.35</x:v>
       </x:c>
       <x:c r="D347" s="0" t="s">
         <x:v>214</x:v>
@@ -11419,10 +11413,10 @@
         <x:v>215</x:v>
       </x:c>
       <x:c r="B348" s="0">
-        <x:v>81</x:v>
+        <x:v>82.25</x:v>
       </x:c>
       <x:c r="C348" s="0">
-        <x:v>4.6</x:v>
+        <x:v>1.25</x:v>
       </x:c>
       <x:c r="D348" s="0" t="s">
         <x:v>214</x:v>
@@ -11448,10 +11442,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B349" s="0">
-        <x:v>232.7</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C349" s="0">
-        <x:v>3.4</x:v>
+        <x:v>-2.7</x:v>
       </x:c>
       <x:c r="D349" s="0" t="s">
         <x:v>214</x:v>
@@ -11477,10 +11471,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B350" s="0">
-        <x:v>95.95</x:v>
+        <x:v>95.4</x:v>
       </x:c>
       <x:c r="C350" s="0">
-        <x:v>-2.2</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="D350" s="0" t="s">
         <x:v>214</x:v>
@@ -11506,10 +11500,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B351" s="0">
-        <x:v>95.95</x:v>
+        <x:v>95.4</x:v>
       </x:c>
       <x:c r="C351" s="0">
-        <x:v>-2.2</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="D351" s="0" t="s">
         <x:v>214</x:v>
@@ -11535,10 +11529,10 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B352" s="0">
-        <x:v>7.85</x:v>
+        <x:v>7.53</x:v>
       </x:c>
       <x:c r="C352" s="0">
-        <x:v>0.39</x:v>
+        <x:v>-0.32</x:v>
       </x:c>
       <x:c r="D352" s="0" t="s">
         <x:v>214</x:v>
@@ -11564,10 +11558,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B353" s="0">
-        <x:v>15.99</x:v>
+        <x:v>16.38</x:v>
       </x:c>
       <x:c r="C353" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.39</x:v>
       </x:c>
       <x:c r="D353" s="0" t="s">
         <x:v>216</x:v>
@@ -11593,10 +11587,10 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="B354" s="0">
-        <x:v>103</x:v>
+        <x:v>104.9</x:v>
       </x:c>
       <x:c r="C354" s="0">
-        <x:v>5.3</x:v>
+        <x:v>1.9</x:v>
       </x:c>
       <x:c r="D354" s="0" t="s">
         <x:v>216</x:v>
@@ -11622,10 +11616,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B355" s="0">
-        <x:v>34.66</x:v>
+        <x:v>34.62</x:v>
       </x:c>
       <x:c r="C355" s="0">
-        <x:v>-0.92</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D355" s="0" t="s">
         <x:v>217</x:v>
@@ -11651,10 +11645,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B356" s="0">
-        <x:v>53</x:v>
+        <x:v>53.3</x:v>
       </x:c>
       <x:c r="C356" s="0">
-        <x:v>0.5</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D356" s="0" t="s">
         <x:v>217</x:v>
@@ -11680,10 +11674,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B357" s="0">
-        <x:v>66.75</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C357" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.35</x:v>
       </x:c>
       <x:c r="D357" s="0" t="s">
         <x:v>218</x:v>
@@ -11709,10 +11703,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B358" s="0">
-        <x:v>95.95</x:v>
+        <x:v>95.4</x:v>
       </x:c>
       <x:c r="C358" s="0">
-        <x:v>-2.2</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="D358" s="0" t="s">
         <x:v>218</x:v>
@@ -11738,10 +11732,10 @@
         <x:v>167</x:v>
       </x:c>
       <x:c r="B359" s="0">
-        <x:v>1127</x:v>
+        <x:v>1085</x:v>
       </x:c>
       <x:c r="C359" s="0">
-        <x:v>102</x:v>
+        <x:v>-42</x:v>
       </x:c>
       <x:c r="D359" s="0" t="s">
         <x:v>219</x:v>
@@ -11767,10 +11761,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B360" s="0">
-        <x:v>42.78</x:v>
+        <x:v>40.48</x:v>
       </x:c>
       <x:c r="C360" s="0">
-        <x:v>0.62</x:v>
+        <x:v>-2.3</x:v>
       </x:c>
       <x:c r="D360" s="0" t="s">
         <x:v>220</x:v>
@@ -11796,10 +11790,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B361" s="0">
-        <x:v>4.5</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="C361" s="0">
-        <x:v>0.04</x:v>
+        <x:v>-0.17</x:v>
       </x:c>
       <x:c r="D361" s="0" t="s">
         <x:v>220</x:v>
@@ -11825,10 +11819,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B362" s="0">
-        <x:v>47.7</x:v>
+        <x:v>47.26</x:v>
       </x:c>
       <x:c r="C362" s="0">
-        <x:v>0.14</x:v>
+        <x:v>-0.44</x:v>
       </x:c>
       <x:c r="D362" s="0" t="s">
         <x:v>220</x:v>
@@ -11854,10 +11848,10 @@
         <x:v>184</x:v>
       </x:c>
       <x:c r="B363" s="0">
-        <x:v>34.54</x:v>
+        <x:v>37.32</x:v>
       </x:c>
       <x:c r="C363" s="0">
-        <x:v>-1.34</x:v>
+        <x:v>2.78</x:v>
       </x:c>
       <x:c r="D363" s="0" t="s">
         <x:v>220</x:v>
@@ -11883,10 +11877,10 @@
         <x:v>184</x:v>
       </x:c>
       <x:c r="B364" s="0">
-        <x:v>34.54</x:v>
+        <x:v>37.32</x:v>
       </x:c>
       <x:c r="C364" s="0">
-        <x:v>-1.34</x:v>
+        <x:v>2.78</x:v>
       </x:c>
       <x:c r="D364" s="0" t="s">
         <x:v>220</x:v>
@@ -11912,10 +11906,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B365" s="0">
-        <x:v>408</x:v>
+        <x:v>396.5</x:v>
       </x:c>
       <x:c r="C365" s="0">
-        <x:v>-6</x:v>
+        <x:v>-11.5</x:v>
       </x:c>
       <x:c r="D365" s="0" t="s">
         <x:v>221</x:v>
@@ -11941,10 +11935,10 @@
         <x:v>119</x:v>
       </x:c>
       <x:c r="B366" s="0">
-        <x:v>11.27</x:v>
+        <x:v>11.38</x:v>
       </x:c>
       <x:c r="C366" s="0">
-        <x:v>-0.28</x:v>
+        <x:v>0.11</x:v>
       </x:c>
       <x:c r="D366" s="0" t="s">
         <x:v>221</x:v>
@@ -11970,10 +11964,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B367" s="0">
-        <x:v>34.66</x:v>
+        <x:v>34.62</x:v>
       </x:c>
       <x:c r="C367" s="0">
-        <x:v>-0.92</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D367" s="0" t="s">
         <x:v>222</x:v>
@@ -11999,10 +11993,10 @@
         <x:v>223</x:v>
       </x:c>
       <x:c r="B368" s="0">
-        <x:v>59.8</x:v>
+        <x:v>59.05</x:v>
       </x:c>
       <x:c r="C368" s="0">
-        <x:v>-1.35</x:v>
+        <x:v>-0.75</x:v>
       </x:c>
       <x:c r="D368" s="0" t="s">
         <x:v>222</x:v>
@@ -12028,10 +12022,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B369" s="0">
-        <x:v>232.7</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C369" s="0">
-        <x:v>3.4</x:v>
+        <x:v>-2.7</x:v>
       </x:c>
       <x:c r="D369" s="0" t="s">
         <x:v>222</x:v>
@@ -12057,10 +12051,10 @@
         <x:v>167</x:v>
       </x:c>
       <x:c r="B370" s="0">
-        <x:v>1127</x:v>
+        <x:v>1085</x:v>
       </x:c>
       <x:c r="C370" s="0">
-        <x:v>102</x:v>
+        <x:v>-42</x:v>
       </x:c>
       <x:c r="D370" s="0" t="s">
         <x:v>222</x:v>
@@ -12086,10 +12080,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B371" s="0">
-        <x:v>5.94</x:v>
+        <x:v>5.87</x:v>
       </x:c>
       <x:c r="C371" s="0">
-        <x:v>0.07</x:v>
+        <x:v>-0.07</x:v>
       </x:c>
       <x:c r="D371" s="0" t="s">
         <x:v>224</x:v>
@@ -12115,10 +12109,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B372" s="0">
-        <x:v>5.94</x:v>
+        <x:v>5.87</x:v>
       </x:c>
       <x:c r="C372" s="0">
-        <x:v>0.07</x:v>
+        <x:v>-0.07</x:v>
       </x:c>
       <x:c r="D372" s="0" t="s">
         <x:v>224</x:v>
@@ -12144,10 +12138,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B373" s="0">
-        <x:v>114.2</x:v>
+        <x:v>115.2</x:v>
       </x:c>
       <x:c r="C373" s="0">
-        <x:v>-1</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D373" s="0" t="s">
         <x:v>226</x:v>
@@ -12173,10 +12167,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B374" s="0">
-        <x:v>15.71</x:v>
+        <x:v>15.12</x:v>
       </x:c>
       <x:c r="C374" s="0">
-        <x:v>-0.09</x:v>
+        <x:v>-0.59</x:v>
       </x:c>
       <x:c r="D374" s="0" t="s">
         <x:v>227</x:v>
@@ -12202,10 +12196,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B375" s="0">
-        <x:v>114.2</x:v>
+        <x:v>115.2</x:v>
       </x:c>
       <x:c r="C375" s="0">
-        <x:v>-1</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D375" s="0" t="s">
         <x:v>227</x:v>
@@ -12231,10 +12225,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B376" s="0">
-        <x:v>34.66</x:v>
+        <x:v>34.62</x:v>
       </x:c>
       <x:c r="C376" s="0">
-        <x:v>-0.92</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D376" s="0" t="s">
         <x:v>227</x:v>
@@ -12260,10 +12254,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B377" s="0">
-        <x:v>53</x:v>
+        <x:v>53.3</x:v>
       </x:c>
       <x:c r="C377" s="0">
-        <x:v>0.5</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D377" s="0" t="s">
         <x:v>227</x:v>
@@ -12289,10 +12283,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B378" s="0">
-        <x:v>53</x:v>
+        <x:v>53.3</x:v>
       </x:c>
       <x:c r="C378" s="0">
-        <x:v>0.5</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D378" s="0" t="s">
         <x:v>227</x:v>
@@ -12318,10 +12312,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B379" s="0">
-        <x:v>232.7</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C379" s="0">
-        <x:v>3.4</x:v>
+        <x:v>-2.7</x:v>
       </x:c>
       <x:c r="D379" s="0" t="s">
         <x:v>228</x:v>
@@ -12347,10 +12341,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B380" s="0">
-        <x:v>79.8</x:v>
+        <x:v>82.15</x:v>
       </x:c>
       <x:c r="C380" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D380" s="0" t="s">
         <x:v>229</x:v>
@@ -12376,10 +12370,10 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="B381" s="0">
-        <x:v>239.2</x:v>
+        <x:v>249.4</x:v>
       </x:c>
       <x:c r="C381" s="0">
-        <x:v>-26.55</x:v>
+        <x:v>10.2</x:v>
       </x:c>
       <x:c r="D381" s="0" t="s">
         <x:v>229</x:v>
@@ -12405,10 +12399,10 @@
         <x:v>230</x:v>
       </x:c>
       <x:c r="B382" s="0">
-        <x:v>18.64</x:v>
+        <x:v>18.43</x:v>
       </x:c>
       <x:c r="C382" s="0">
-        <x:v>-0.26</x:v>
+        <x:v>-0.21</x:v>
       </x:c>
       <x:c r="D382" s="0" t="s">
         <x:v>231</x:v>
@@ -12434,10 +12428,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B383" s="0">
-        <x:v>66.75</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C383" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.35</x:v>
       </x:c>
       <x:c r="D383" s="0" t="s">
         <x:v>232</x:v>
@@ -12463,10 +12457,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B384" s="0">
-        <x:v>62.5</x:v>
+        <x:v>60.9</x:v>
       </x:c>
       <x:c r="C384" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>-1.6</x:v>
       </x:c>
       <x:c r="D384" s="0" t="s">
         <x:v>232</x:v>
@@ -12492,10 +12486,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B385" s="0">
-        <x:v>34.66</x:v>
+        <x:v>34.62</x:v>
       </x:c>
       <x:c r="C385" s="0">
-        <x:v>-0.92</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D385" s="0" t="s">
         <x:v>232</x:v>
@@ -12521,10 +12515,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B386" s="0">
-        <x:v>283.5</x:v>
+        <x:v>286.25</x:v>
       </x:c>
       <x:c r="C386" s="0">
-        <x:v>2.5</x:v>
+        <x:v>2.75</x:v>
       </x:c>
       <x:c r="D386" s="0" t="s">
         <x:v>232</x:v>
@@ -12550,10 +12544,10 @@
         <x:v>233</x:v>
       </x:c>
       <x:c r="B387" s="0">
-        <x:v>17.04</x:v>
+        <x:v>16.75</x:v>
       </x:c>
       <x:c r="C387" s="0">
-        <x:v>-1.24</x:v>
+        <x:v>-0.29</x:v>
       </x:c>
       <x:c r="D387" s="0" t="s">
         <x:v>232</x:v>
@@ -12579,10 +12573,10 @@
         <x:v>167</x:v>
       </x:c>
       <x:c r="B388" s="0">
-        <x:v>1127</x:v>
+        <x:v>1085</x:v>
       </x:c>
       <x:c r="C388" s="0">
-        <x:v>102</x:v>
+        <x:v>-42</x:v>
       </x:c>
       <x:c r="D388" s="0" t="s">
         <x:v>232</x:v>
@@ -12608,10 +12602,10 @@
         <x:v>146</x:v>
       </x:c>
       <x:c r="B389" s="0">
-        <x:v>564</x:v>
+        <x:v>554.5</x:v>
       </x:c>
       <x:c r="C389" s="0">
-        <x:v>-2</x:v>
+        <x:v>-9.5</x:v>
       </x:c>
       <x:c r="D389" s="0" t="s">
         <x:v>234</x:v>
@@ -12637,10 +12631,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B390" s="0">
-        <x:v>232.7</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C390" s="0">
-        <x:v>3.4</x:v>
+        <x:v>-2.7</x:v>
       </x:c>
       <x:c r="D390" s="0" t="s">
         <x:v>234</x:v>
@@ -12666,10 +12660,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B391" s="0">
-        <x:v>3.51</x:v>
+        <x:v>3.7</x:v>
       </x:c>
       <x:c r="C391" s="0">
-        <x:v>-0.32</x:v>
+        <x:v>0.19</x:v>
       </x:c>
       <x:c r="D391" s="0" t="s">
         <x:v>234</x:v>
@@ -12695,10 +12689,10 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B392" s="0">
-        <x:v>7.85</x:v>
+        <x:v>7.53</x:v>
       </x:c>
       <x:c r="C392" s="0">
-        <x:v>0.39</x:v>
+        <x:v>-0.32</x:v>
       </x:c>
       <x:c r="D392" s="0" t="s">
         <x:v>235</x:v>
@@ -12724,10 +12718,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B393" s="0">
-        <x:v>66.75</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C393" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.35</x:v>
       </x:c>
       <x:c r="D393" s="0" t="s">
         <x:v>236</x:v>
@@ -12753,10 +12747,10 @@
         <x:v>237</x:v>
       </x:c>
       <x:c r="B394" s="0">
-        <x:v>23.92</x:v>
+        <x:v>23.28</x:v>
       </x:c>
       <x:c r="C394" s="0">
-        <x:v>-1.64</x:v>
+        <x:v>-0.64</x:v>
       </x:c>
       <x:c r="D394" s="0" t="s">
         <x:v>236</x:v>
@@ -12782,10 +12776,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B395" s="0">
-        <x:v>42.78</x:v>
+        <x:v>40.48</x:v>
       </x:c>
       <x:c r="C395" s="0">
-        <x:v>0.62</x:v>
+        <x:v>-2.3</x:v>
       </x:c>
       <x:c r="D395" s="0" t="s">
         <x:v>238</x:v>
@@ -12811,10 +12805,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B396" s="0">
-        <x:v>66.75</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C396" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.35</x:v>
       </x:c>
       <x:c r="D396" s="0" t="s">
         <x:v>238</x:v>
@@ -12840,10 +12834,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B397" s="0">
-        <x:v>5.52</x:v>
+        <x:v>5.49</x:v>
       </x:c>
       <x:c r="C397" s="0">
-        <x:v>-0.15</x:v>
+        <x:v>-0.03</x:v>
       </x:c>
       <x:c r="D397" s="0" t="s">
         <x:v>239</x:v>
@@ -12869,10 +12863,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B398" s="0">
-        <x:v>42.78</x:v>
+        <x:v>40.48</x:v>
       </x:c>
       <x:c r="C398" s="0">
-        <x:v>0.62</x:v>
+        <x:v>-2.3</x:v>
       </x:c>
       <x:c r="D398" s="0" t="s">
         <x:v>240</x:v>
@@ -12898,10 +12892,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B399" s="0">
-        <x:v>114.2</x:v>
+        <x:v>115.2</x:v>
       </x:c>
       <x:c r="C399" s="0">
-        <x:v>-1</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D399" s="0" t="s">
         <x:v>240</x:v>
@@ -12927,10 +12921,10 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="B400" s="0">
-        <x:v>239.2</x:v>
+        <x:v>249.4</x:v>
       </x:c>
       <x:c r="C400" s="0">
-        <x:v>-26.55</x:v>
+        <x:v>10.2</x:v>
       </x:c>
       <x:c r="D400" s="0" t="s">
         <x:v>240</x:v>
@@ -12956,10 +12950,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B401" s="0">
-        <x:v>34.66</x:v>
+        <x:v>34.62</x:v>
       </x:c>
       <x:c r="C401" s="0">
-        <x:v>-0.92</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D401" s="0" t="s">
         <x:v>241</x:v>
@@ -12985,10 +12979,10 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="B402" s="0">
-        <x:v>61.25</x:v>
+        <x:v>61.45</x:v>
       </x:c>
       <x:c r="C402" s="0">
-        <x:v>-1.4</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="D402" s="0" t="s">
         <x:v>241</x:v>
@@ -13014,10 +13008,10 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="B403" s="0">
-        <x:v>14.43</x:v>
+        <x:v>12.99</x:v>
       </x:c>
       <x:c r="C403" s="0">
-        <x:v>1.31</x:v>
+        <x:v>-1.44</x:v>
       </x:c>
       <x:c r="D403" s="0" t="s">
         <x:v>242</x:v>
@@ -13043,10 +13037,10 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="B404" s="0">
-        <x:v>239.2</x:v>
+        <x:v>249.4</x:v>
       </x:c>
       <x:c r="C404" s="0">
-        <x:v>-26.55</x:v>
+        <x:v>10.2</x:v>
       </x:c>
       <x:c r="D404" s="0" t="s">
         <x:v>243</x:v>
@@ -13072,10 +13066,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B405" s="0">
-        <x:v>66.75</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C405" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.35</x:v>
       </x:c>
       <x:c r="D405" s="0" t="s">
         <x:v>244</x:v>
@@ -13101,10 +13095,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B406" s="0">
-        <x:v>408</x:v>
+        <x:v>396.5</x:v>
       </x:c>
       <x:c r="C406" s="0">
-        <x:v>-6</x:v>
+        <x:v>-11.5</x:v>
       </x:c>
       <x:c r="D406" s="0" t="s">
         <x:v>245</x:v>
@@ -13130,10 +13124,10 @@
         <x:v>167</x:v>
       </x:c>
       <x:c r="B407" s="0">
-        <x:v>1127</x:v>
+        <x:v>1085</x:v>
       </x:c>
       <x:c r="C407" s="0">
-        <x:v>102</x:v>
+        <x:v>-42</x:v>
       </x:c>
       <x:c r="D407" s="0" t="s">
         <x:v>246</x:v>
@@ -13159,10 +13153,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B408" s="0">
-        <x:v>66.75</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C408" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.35</x:v>
       </x:c>
       <x:c r="D408" s="0" t="s">
         <x:v>247</x:v>
@@ -13188,10 +13182,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B409" s="0">
-        <x:v>408</x:v>
+        <x:v>396.5</x:v>
       </x:c>
       <x:c r="C409" s="0">
-        <x:v>-6</x:v>
+        <x:v>-11.5</x:v>
       </x:c>
       <x:c r="D409" s="0" t="s">
         <x:v>247</x:v>
@@ -13217,10 +13211,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B410" s="0">
-        <x:v>95.95</x:v>
+        <x:v>95.4</x:v>
       </x:c>
       <x:c r="C410" s="0">
-        <x:v>-2.2</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="D410" s="0" t="s">
         <x:v>247</x:v>
@@ -13246,10 +13240,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B411" s="0">
-        <x:v>114.2</x:v>
+        <x:v>115.2</x:v>
       </x:c>
       <x:c r="C411" s="0">
-        <x:v>-1</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D411" s="0" t="s">
         <x:v>248</x:v>
@@ -13275,10 +13269,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B412" s="0">
-        <x:v>40.7</x:v>
+        <x:v>40.08</x:v>
       </x:c>
       <x:c r="C412" s="0">
-        <x:v>0.66</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D412" s="0" t="s">
         <x:v>248</x:v>
@@ -13304,10 +13298,10 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="B413" s="0">
-        <x:v>13.7</x:v>
+        <x:v>13.36</x:v>
       </x:c>
       <x:c r="C413" s="0">
-        <x:v>0.45</x:v>
+        <x:v>-0.34</x:v>
       </x:c>
       <x:c r="D413" s="0" t="s">
         <x:v>249</x:v>
@@ -13333,10 +13327,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B414" s="0">
-        <x:v>95.95</x:v>
+        <x:v>95.4</x:v>
       </x:c>
       <x:c r="C414" s="0">
-        <x:v>-2.2</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="D414" s="0" t="s">
         <x:v>250</x:v>
@@ -13362,10 +13356,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B415" s="0">
-        <x:v>5.94</x:v>
+        <x:v>5.87</x:v>
       </x:c>
       <x:c r="C415" s="0">
-        <x:v>0.07</x:v>
+        <x:v>-0.07</x:v>
       </x:c>
       <x:c r="D415" s="0" t="s">
         <x:v>250</x:v>
@@ -13391,10 +13385,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B416" s="0">
-        <x:v>95.95</x:v>
+        <x:v>95.4</x:v>
       </x:c>
       <x:c r="C416" s="0">
-        <x:v>-2.2</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="D416" s="0" t="s">
         <x:v>251</x:v>
@@ -13420,10 +13414,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B417" s="0">
-        <x:v>66.75</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C417" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.35</x:v>
       </x:c>
       <x:c r="D417" s="0" t="s">
         <x:v>252</x:v>
@@ -13449,10 +13443,10 @@
         <x:v>154</x:v>
       </x:c>
       <x:c r="B418" s="0">
-        <x:v>20.54</x:v>
+        <x:v>20.02</x:v>
       </x:c>
       <x:c r="C418" s="0">
-        <x:v>0.14</x:v>
+        <x:v>-0.52</x:v>
       </x:c>
       <x:c r="D418" s="0" t="s">
         <x:v>253</x:v>
@@ -13478,10 +13472,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B419" s="0">
-        <x:v>95.95</x:v>
+        <x:v>95.4</x:v>
       </x:c>
       <x:c r="C419" s="0">
-        <x:v>-2.2</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="D419" s="0" t="s">
         <x:v>254</x:v>
@@ -13507,10 +13501,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B420" s="0">
-        <x:v>95.95</x:v>
+        <x:v>95.4</x:v>
       </x:c>
       <x:c r="C420" s="0">
-        <x:v>-2.2</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="D420" s="0" t="s">
         <x:v>254</x:v>
@@ -13536,10 +13530,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B421" s="0">
-        <x:v>4.5</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="C421" s="0">
-        <x:v>0.04</x:v>
+        <x:v>-0.17</x:v>
       </x:c>
       <x:c r="D421" s="0" t="s">
         <x:v>254</x:v>
@@ -13565,10 +13559,10 @@
         <x:v>184</x:v>
       </x:c>
       <x:c r="B422" s="0">
-        <x:v>34.54</x:v>
+        <x:v>37.32</x:v>
       </x:c>
       <x:c r="C422" s="0">
-        <x:v>-1.34</x:v>
+        <x:v>2.78</x:v>
       </x:c>
       <x:c r="D422" s="0" t="s">
         <x:v>254</x:v>
@@ -13594,10 +13588,10 @@
         <x:v>184</x:v>
       </x:c>
       <x:c r="B423" s="0">
-        <x:v>34.54</x:v>
+        <x:v>37.32</x:v>
       </x:c>
       <x:c r="C423" s="0">
-        <x:v>-1.34</x:v>
+        <x:v>2.78</x:v>
       </x:c>
       <x:c r="D423" s="0" t="s">
         <x:v>254</x:v>
@@ -13623,10 +13617,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B424" s="0">
-        <x:v>232.7</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C424" s="0">
-        <x:v>3.4</x:v>
+        <x:v>-2.7</x:v>
       </x:c>
       <x:c r="D424" s="0" t="s">
         <x:v>255</x:v>
@@ -13652,10 +13646,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B425" s="0">
-        <x:v>47.7</x:v>
+        <x:v>47.26</x:v>
       </x:c>
       <x:c r="C425" s="0">
-        <x:v>0.14</x:v>
+        <x:v>-0.44</x:v>
       </x:c>
       <x:c r="D425" s="0" t="s">
         <x:v>255</x:v>
@@ -13681,10 +13675,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B426" s="0">
-        <x:v>66.75</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C426" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.35</x:v>
       </x:c>
       <x:c r="D426" s="0" t="s">
         <x:v>256</x:v>
@@ -13710,10 +13704,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B427" s="0">
-        <x:v>408</x:v>
+        <x:v>396.5</x:v>
       </x:c>
       <x:c r="C427" s="0">
-        <x:v>-6</x:v>
+        <x:v>-11.5</x:v>
       </x:c>
       <x:c r="D427" s="0" t="s">
         <x:v>257</x:v>
@@ -13739,10 +13733,10 @@
         <x:v>154</x:v>
       </x:c>
       <x:c r="B428" s="0">
-        <x:v>20.54</x:v>
+        <x:v>20.02</x:v>
       </x:c>
       <x:c r="C428" s="0">
-        <x:v>0.14</x:v>
+        <x:v>-0.52</x:v>
       </x:c>
       <x:c r="D428" s="0" t="s">
         <x:v>258</x:v>
@@ -13768,10 +13762,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B429" s="0">
-        <x:v>4.5</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="C429" s="0">
-        <x:v>0.04</x:v>
+        <x:v>-0.17</x:v>
       </x:c>
       <x:c r="D429" s="0" t="s">
         <x:v>258</x:v>
@@ -13797,10 +13791,10 @@
         <x:v>259</x:v>
       </x:c>
       <x:c r="B430" s="0">
-        <x:v>56</x:v>
+        <x:v>53.45</x:v>
       </x:c>
       <x:c r="C430" s="0">
-        <x:v>1</x:v>
+        <x:v>-2.55</x:v>
       </x:c>
       <x:c r="D430" s="0" t="s">
         <x:v>258</x:v>
@@ -13826,10 +13820,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B431" s="0">
-        <x:v>66.75</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C431" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.35</x:v>
       </x:c>
       <x:c r="D431" s="0" t="s">
         <x:v>260</x:v>
@@ -13855,10 +13849,10 @@
         <x:v>112</x:v>
       </x:c>
       <x:c r="B432" s="0">
-        <x:v>26.32</x:v>
+        <x:v>25.88</x:v>
       </x:c>
       <x:c r="C432" s="0">
-        <x:v>0.02</x:v>
+        <x:v>-0.44</x:v>
       </x:c>
       <x:c r="D432" s="0" t="s">
         <x:v>260</x:v>
@@ -13884,10 +13878,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B433" s="0">
-        <x:v>408</x:v>
+        <x:v>396.5</x:v>
       </x:c>
       <x:c r="C433" s="0">
-        <x:v>-6</x:v>
+        <x:v>-11.5</x:v>
       </x:c>
       <x:c r="D433" s="0" t="s">
         <x:v>260</x:v>
@@ -13913,10 +13907,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B434" s="0">
-        <x:v>79.8</x:v>
+        <x:v>82.15</x:v>
       </x:c>
       <x:c r="C434" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D434" s="0" t="s">
         <x:v>260</x:v>
@@ -13942,10 +13936,10 @@
         <x:v>167</x:v>
       </x:c>
       <x:c r="B435" s="0">
-        <x:v>1127</x:v>
+        <x:v>1085</x:v>
       </x:c>
       <x:c r="C435" s="0">
-        <x:v>102</x:v>
+        <x:v>-42</x:v>
       </x:c>
       <x:c r="D435" s="0" t="s">
         <x:v>260</x:v>
@@ -13971,10 +13965,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B436" s="0">
-        <x:v>408</x:v>
+        <x:v>396.5</x:v>
       </x:c>
       <x:c r="C436" s="0">
-        <x:v>-6</x:v>
+        <x:v>-11.5</x:v>
       </x:c>
       <x:c r="D436" s="0" t="s">
         <x:v>261</x:v>
@@ -14000,10 +13994,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B437" s="0">
-        <x:v>47</x:v>
+        <x:v>47.02</x:v>
       </x:c>
       <x:c r="C437" s="0">
-        <x:v>0.32</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="D437" s="0" t="s">
         <x:v>261</x:v>
@@ -14029,10 +14023,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B438" s="0">
-        <x:v>95.95</x:v>
+        <x:v>95.4</x:v>
       </x:c>
       <x:c r="C438" s="0">
-        <x:v>-2.2</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="D438" s="0" t="s">
         <x:v>262</x:v>
@@ -14058,10 +14052,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B439" s="0">
-        <x:v>66.75</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C439" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.35</x:v>
       </x:c>
       <x:c r="D439" s="0" t="s">
         <x:v>263</x:v>
@@ -14087,10 +14081,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B440" s="0">
-        <x:v>41.76</x:v>
+        <x:v>42.88</x:v>
       </x:c>
       <x:c r="C440" s="0">
-        <x:v>-0.42</x:v>
+        <x:v>1.12</x:v>
       </x:c>
       <x:c r="D440" s="0" t="s">
         <x:v>263</x:v>
@@ -14116,10 +14110,10 @@
         <x:v>154</x:v>
       </x:c>
       <x:c r="B441" s="0">
-        <x:v>20.54</x:v>
+        <x:v>20.02</x:v>
       </x:c>
       <x:c r="C441" s="0">
-        <x:v>0.14</x:v>
+        <x:v>-0.52</x:v>
       </x:c>
       <x:c r="D441" s="0" t="s">
         <x:v>263</x:v>
@@ -14145,10 +14139,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B442" s="0">
-        <x:v>95.95</x:v>
+        <x:v>95.4</x:v>
       </x:c>
       <x:c r="C442" s="0">
-        <x:v>-2.2</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="D442" s="0" t="s">
         <x:v>263</x:v>
@@ -14174,10 +14168,10 @@
         <x:v>264</x:v>
       </x:c>
       <x:c r="B443" s="0">
-        <x:v>9.06</x:v>
+        <x:v>9.18</x:v>
       </x:c>
       <x:c r="C443" s="0">
-        <x:v>-0.06</x:v>
+        <x:v>0.12</x:v>
       </x:c>
       <x:c r="D443" s="0" t="s">
         <x:v>265</x:v>
@@ -14203,10 +14197,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B444" s="0">
-        <x:v>95.95</x:v>
+        <x:v>95.4</x:v>
       </x:c>
       <x:c r="C444" s="0">
-        <x:v>-2.2</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="D444" s="0" t="s">
         <x:v>265</x:v>
@@ -14232,10 +14226,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B445" s="0">
-        <x:v>4.5</x:v>
+        <x:v>4.33</x:v>
       </x:c>
       <x:c r="C445" s="0">
-        <x:v>0.04</x:v>
+        <x:v>-0.17</x:v>
       </x:c>
       <x:c r="D445" s="0" t="s">
         <x:v>265</x:v>
@@ -14261,10 +14255,10 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B446" s="0">
-        <x:v>7.85</x:v>
+        <x:v>7.53</x:v>
       </x:c>
       <x:c r="C446" s="0">
-        <x:v>0.39</x:v>
+        <x:v>-0.32</x:v>
       </x:c>
       <x:c r="D446" s="0" t="s">
         <x:v>265</x:v>
@@ -14290,10 +14284,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B447" s="0">
-        <x:v>95.95</x:v>
+        <x:v>95.4</x:v>
       </x:c>
       <x:c r="C447" s="0">
-        <x:v>-2.2</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="D447" s="0" t="s">
         <x:v>266</x:v>
@@ -14316,13 +14310,13 @@
     </x:row>
     <x:row r="448" spans="1:9">
       <x:c r="A448" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B448" s="0">
-        <x:v>58.95</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C448" s="0">
-        <x:v>0.65</x:v>
+        <x:v>5.05</x:v>
       </x:c>
       <x:c r="D448" s="0" t="s">
         <x:v>267</x:v>
@@ -14348,10 +14342,10 @@
         <x:v>268</x:v>
       </x:c>
       <x:c r="B449" s="0">
-        <x:v>86</x:v>
+        <x:v>86.9</x:v>
       </x:c>
       <x:c r="C449" s="0">
-        <x:v>-3</x:v>
+        <x:v>0.9</x:v>
       </x:c>
       <x:c r="D449" s="0" t="s">
         <x:v>269</x:v>
@@ -14377,10 +14371,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B450" s="0">
-        <x:v>920</x:v>
+        <x:v>940</x:v>
       </x:c>
       <x:c r="C450" s="0">
-        <x:v>35.5</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D450" s="0" t="s">
         <x:v>270</x:v>
@@ -14406,10 +14400,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B451" s="0">
-        <x:v>15.99</x:v>
+        <x:v>16.38</x:v>
       </x:c>
       <x:c r="C451" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.39</x:v>
       </x:c>
       <x:c r="D451" s="0" t="s">
         <x:v>271</x:v>
@@ -14435,10 +14429,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B452" s="0">
-        <x:v>34.66</x:v>
+        <x:v>34.62</x:v>
       </x:c>
       <x:c r="C452" s="0">
-        <x:v>-0.92</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D452" s="0" t="s">
         <x:v>272</x:v>
@@ -14464,10 +14458,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B453" s="0">
-        <x:v>920</x:v>
+        <x:v>940</x:v>
       </x:c>
       <x:c r="C453" s="0">
-        <x:v>35.5</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D453" s="0" t="s">
         <x:v>273</x:v>
@@ -14493,10 +14487,10 @@
         <x:v>274</x:v>
       </x:c>
       <x:c r="B454" s="0">
-        <x:v>21.5</x:v>
+        <x:v>21.64</x:v>
       </x:c>
       <x:c r="C454" s="0">
-        <x:v>-0.3</x:v>
+        <x:v>0.14</x:v>
       </x:c>
       <x:c r="D454" s="0" t="s">
         <x:v>273</x:v>
@@ -14522,10 +14516,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B455" s="0">
-        <x:v>53</x:v>
+        <x:v>53.3</x:v>
       </x:c>
       <x:c r="C455" s="0">
-        <x:v>0.5</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D455" s="0" t="s">
         <x:v>273</x:v>
@@ -14551,10 +14545,10 @@
         <x:v>275</x:v>
       </x:c>
       <x:c r="B456" s="0">
-        <x:v>5.33</x:v>
+        <x:v>5.35</x:v>
       </x:c>
       <x:c r="C456" s="0">
-        <x:v>-0.04</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="D456" s="0" t="s">
         <x:v>273</x:v>
@@ -14580,10 +14574,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B457" s="0">
-        <x:v>408</x:v>
+        <x:v>396.5</x:v>
       </x:c>
       <x:c r="C457" s="0">
-        <x:v>-6</x:v>
+        <x:v>-11.5</x:v>
       </x:c>
       <x:c r="D457" s="0" t="s">
         <x:v>276</x:v>
@@ -14609,10 +14603,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B458" s="0">
-        <x:v>40.7</x:v>
+        <x:v>40.08</x:v>
       </x:c>
       <x:c r="C458" s="0">
-        <x:v>0.66</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D458" s="0" t="s">
         <x:v>276</x:v>
@@ -14638,10 +14632,10 @@
         <x:v>274</x:v>
       </x:c>
       <x:c r="B459" s="0">
-        <x:v>21.5</x:v>
+        <x:v>21.64</x:v>
       </x:c>
       <x:c r="C459" s="0">
-        <x:v>-0.3</x:v>
+        <x:v>0.14</x:v>
       </x:c>
       <x:c r="D459" s="0" t="s">
         <x:v>276</x:v>
@@ -14667,10 +14661,10 @@
         <x:v>277</x:v>
       </x:c>
       <x:c r="B460" s="0">
-        <x:v>44.68</x:v>
+        <x:v>43.92</x:v>
       </x:c>
       <x:c r="C460" s="0">
-        <x:v>0.5</x:v>
+        <x:v>-0.76</x:v>
       </x:c>
       <x:c r="D460" s="0" t="s">
         <x:v>278</x:v>
@@ -14696,10 +14690,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B461" s="0">
-        <x:v>5.52</x:v>
+        <x:v>5.49</x:v>
       </x:c>
       <x:c r="C461" s="0">
-        <x:v>-0.15</x:v>
+        <x:v>-0.03</x:v>
       </x:c>
       <x:c r="D461" s="0" t="s">
         <x:v>279</x:v>
@@ -14725,10 +14719,10 @@
         <x:v>167</x:v>
       </x:c>
       <x:c r="B462" s="0">
-        <x:v>1127</x:v>
+        <x:v>1085</x:v>
       </x:c>
       <x:c r="C462" s="0">
-        <x:v>102</x:v>
+        <x:v>-42</x:v>
       </x:c>
       <x:c r="D462" s="0" t="s">
         <x:v>279</x:v>
@@ -14754,10 +14748,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B463" s="0">
-        <x:v>5.52</x:v>
+        <x:v>5.49</x:v>
       </x:c>
       <x:c r="C463" s="0">
-        <x:v>-0.15</x:v>
+        <x:v>-0.03</x:v>
       </x:c>
       <x:c r="D463" s="0" t="s">
         <x:v>280</x:v>
@@ -14783,10 +14777,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B464" s="0">
-        <x:v>34.66</x:v>
+        <x:v>34.62</x:v>
       </x:c>
       <x:c r="C464" s="0">
-        <x:v>-0.92</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D464" s="0" t="s">
         <x:v>280</x:v>
@@ -14812,10 +14806,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B465" s="0">
-        <x:v>232.7</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C465" s="0">
-        <x:v>3.4</x:v>
+        <x:v>-2.7</x:v>
       </x:c>
       <x:c r="D465" s="0" t="s">
         <x:v>280</x:v>
@@ -14841,10 +14835,10 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="B466" s="0">
-        <x:v>239.2</x:v>
+        <x:v>249.4</x:v>
       </x:c>
       <x:c r="C466" s="0">
-        <x:v>-26.55</x:v>
+        <x:v>10.2</x:v>
       </x:c>
       <x:c r="D466" s="0" t="s">
         <x:v>281</x:v>
@@ -14870,10 +14864,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B467" s="0">
-        <x:v>3.51</x:v>
+        <x:v>3.7</x:v>
       </x:c>
       <x:c r="C467" s="0">
-        <x:v>-0.32</x:v>
+        <x:v>0.19</x:v>
       </x:c>
       <x:c r="D467" s="0" t="s">
         <x:v>281</x:v>
@@ -14899,10 +14893,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B468" s="0">
-        <x:v>3.51</x:v>
+        <x:v>3.7</x:v>
       </x:c>
       <x:c r="C468" s="0">
-        <x:v>-0.32</x:v>
+        <x:v>0.19</x:v>
       </x:c>
       <x:c r="D468" s="0" t="s">
         <x:v>281</x:v>
@@ -14928,10 +14922,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B469" s="0">
-        <x:v>114.2</x:v>
+        <x:v>115.2</x:v>
       </x:c>
       <x:c r="C469" s="0">
-        <x:v>-1</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D469" s="0" t="s">
         <x:v>282</x:v>
@@ -14957,10 +14951,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B470" s="0">
-        <x:v>95.95</x:v>
+        <x:v>95.4</x:v>
       </x:c>
       <x:c r="C470" s="0">
-        <x:v>-2.2</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="D470" s="0" t="s">
         <x:v>282</x:v>
@@ -14986,10 +14980,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B471" s="0">
-        <x:v>95.95</x:v>
+        <x:v>95.4</x:v>
       </x:c>
       <x:c r="C471" s="0">
-        <x:v>-2.2</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="D471" s="0" t="s">
         <x:v>282</x:v>
@@ -15015,10 +15009,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B472" s="0">
-        <x:v>3.51</x:v>
+        <x:v>3.7</x:v>
       </x:c>
       <x:c r="C472" s="0">
-        <x:v>-0.32</x:v>
+        <x:v>0.19</x:v>
       </x:c>
       <x:c r="D472" s="0" t="s">
         <x:v>282</x:v>
@@ -15044,10 +15038,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B473" s="0">
-        <x:v>53</x:v>
+        <x:v>53.3</x:v>
       </x:c>
       <x:c r="C473" s="0">
-        <x:v>0.5</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D473" s="0" t="s">
         <x:v>282</x:v>
@@ -15073,10 +15067,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B474" s="0">
-        <x:v>47.7</x:v>
+        <x:v>47.26</x:v>
       </x:c>
       <x:c r="C474" s="0">
-        <x:v>0.14</x:v>
+        <x:v>-0.44</x:v>
       </x:c>
       <x:c r="D474" s="0" t="s">
         <x:v>283</x:v>
@@ -15102,10 +15096,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B475" s="0">
-        <x:v>408</x:v>
+        <x:v>396.5</x:v>
       </x:c>
       <x:c r="C475" s="0">
-        <x:v>-6</x:v>
+        <x:v>-11.5</x:v>
       </x:c>
       <x:c r="D475" s="0" t="s">
         <x:v>284</x:v>
@@ -15131,10 +15125,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B476" s="0">
-        <x:v>232.7</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C476" s="0">
-        <x:v>3.4</x:v>
+        <x:v>-2.7</x:v>
       </x:c>
       <x:c r="D476" s="0" t="s">
         <x:v>284</x:v>
@@ -15160,10 +15154,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B477" s="0">
-        <x:v>15.99</x:v>
+        <x:v>16.38</x:v>
       </x:c>
       <x:c r="C477" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.39</x:v>
       </x:c>
       <x:c r="D477" s="0" t="s">
         <x:v>285</x:v>
@@ -15189,10 +15183,10 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="B478" s="0">
-        <x:v>61.25</x:v>
+        <x:v>61.45</x:v>
       </x:c>
       <x:c r="C478" s="0">
-        <x:v>-1.4</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="D478" s="0" t="s">
         <x:v>286</x:v>
@@ -15218,10 +15212,10 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B479" s="0">
-        <x:v>7.85</x:v>
+        <x:v>7.53</x:v>
       </x:c>
       <x:c r="C479" s="0">
-        <x:v>0.39</x:v>
+        <x:v>-0.32</x:v>
       </x:c>
       <x:c r="D479" s="0" t="s">
         <x:v>286</x:v>
@@ -15247,10 +15241,10 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B480" s="0">
-        <x:v>4.96</x:v>
+        <x:v>4.77</x:v>
       </x:c>
       <x:c r="C480" s="0">
-        <x:v>-0.11</x:v>
+        <x:v>-0.19</x:v>
       </x:c>
       <x:c r="D480" s="0" t="s">
         <x:v>287</x:v>
@@ -15276,10 +15270,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B481" s="0">
-        <x:v>3.51</x:v>
+        <x:v>3.7</x:v>
       </x:c>
       <x:c r="C481" s="0">
-        <x:v>-0.32</x:v>
+        <x:v>0.19</x:v>
       </x:c>
       <x:c r="D481" s="0" t="s">
         <x:v>287</x:v>
@@ -15305,10 +15299,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B482" s="0">
-        <x:v>53</x:v>
+        <x:v>53.3</x:v>
       </x:c>
       <x:c r="C482" s="0">
-        <x:v>0.5</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D482" s="0" t="s">
         <x:v>287</x:v>
@@ -15334,10 +15328,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B483" s="0">
-        <x:v>114.2</x:v>
+        <x:v>115.2</x:v>
       </x:c>
       <x:c r="C483" s="0">
-        <x:v>-1</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D483" s="0" t="s">
         <x:v>288</x:v>
@@ -15363,10 +15357,10 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B484" s="0">
-        <x:v>7.85</x:v>
+        <x:v>7.53</x:v>
       </x:c>
       <x:c r="C484" s="0">
-        <x:v>0.39</x:v>
+        <x:v>-0.32</x:v>
       </x:c>
       <x:c r="D484" s="0" t="s">
         <x:v>288</x:v>
@@ -15392,10 +15386,10 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B485" s="0">
-        <x:v>7.85</x:v>
+        <x:v>7.53</x:v>
       </x:c>
       <x:c r="C485" s="0">
-        <x:v>0.39</x:v>
+        <x:v>-0.32</x:v>
       </x:c>
       <x:c r="D485" s="0" t="s">
         <x:v>289</x:v>
@@ -15421,10 +15415,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B486" s="0">
-        <x:v>42.78</x:v>
+        <x:v>40.48</x:v>
       </x:c>
       <x:c r="C486" s="0">
-        <x:v>0.62</x:v>
+        <x:v>-2.3</x:v>
       </x:c>
       <x:c r="D486" s="0" t="s">
         <x:v>290</x:v>
@@ -15450,10 +15444,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B487" s="0">
-        <x:v>5.52</x:v>
+        <x:v>5.49</x:v>
       </x:c>
       <x:c r="C487" s="0">
-        <x:v>-0.15</x:v>
+        <x:v>-0.03</x:v>
       </x:c>
       <x:c r="D487" s="0" t="s">
         <x:v>290</x:v>
@@ -15479,10 +15473,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B488" s="0">
-        <x:v>34.66</x:v>
+        <x:v>34.62</x:v>
       </x:c>
       <x:c r="C488" s="0">
-        <x:v>-0.92</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D488" s="0" t="s">
         <x:v>290</x:v>
@@ -15508,10 +15502,10 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="B489" s="0">
-        <x:v>239.2</x:v>
+        <x:v>249.4</x:v>
       </x:c>
       <x:c r="C489" s="0">
-        <x:v>-26.55</x:v>
+        <x:v>10.2</x:v>
       </x:c>
       <x:c r="D489" s="0" t="s">
         <x:v>290</x:v>
@@ -15537,10 +15531,10 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="B490" s="0">
-        <x:v>239.2</x:v>
+        <x:v>249.4</x:v>
       </x:c>
       <x:c r="C490" s="0">
-        <x:v>-26.55</x:v>
+        <x:v>10.2</x:v>
       </x:c>
       <x:c r="D490" s="0" t="s">
         <x:v>290</x:v>
@@ -15566,10 +15560,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B491" s="0">
-        <x:v>920</x:v>
+        <x:v>940</x:v>
       </x:c>
       <x:c r="C491" s="0">
-        <x:v>35.5</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D491" s="0" t="s">
         <x:v>291</x:v>
@@ -15595,10 +15589,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B492" s="0">
-        <x:v>35.52</x:v>
+        <x:v>33.74</x:v>
       </x:c>
       <x:c r="C492" s="0">
-        <x:v>-0.88</x:v>
+        <x:v>-1.78</x:v>
       </x:c>
       <x:c r="D492" s="0" t="s">
         <x:v>292</x:v>
@@ -15624,10 +15618,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B493" s="0">
-        <x:v>48.42</x:v>
+        <x:v>47.82</x:v>
       </x:c>
       <x:c r="C493" s="0">
-        <x:v>-0.54</x:v>
+        <x:v>-0.6</x:v>
       </x:c>
       <x:c r="D493" s="0" t="s">
         <x:v>293</x:v>
@@ -15653,10 +15647,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B494" s="0">
-        <x:v>48.42</x:v>
+        <x:v>47.82</x:v>
       </x:c>
       <x:c r="C494" s="0">
-        <x:v>-0.54</x:v>
+        <x:v>-0.6</x:v>
       </x:c>
       <x:c r="D494" s="0" t="s">
         <x:v>293</x:v>
@@ -15682,10 +15676,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B495" s="0">
-        <x:v>408</x:v>
+        <x:v>396.5</x:v>
       </x:c>
       <x:c r="C495" s="0">
-        <x:v>-6</x:v>
+        <x:v>-11.5</x:v>
       </x:c>
       <x:c r="D495" s="0" t="s">
         <x:v>294</x:v>
@@ -15711,10 +15705,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B496" s="0">
-        <x:v>5.94</x:v>
+        <x:v>5.87</x:v>
       </x:c>
       <x:c r="C496" s="0">
-        <x:v>0.07</x:v>
+        <x:v>-0.07</x:v>
       </x:c>
       <x:c r="D496" s="0" t="s">
         <x:v>295</x:v>
@@ -15740,10 +15734,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B497" s="0">
-        <x:v>5.94</x:v>
+        <x:v>5.87</x:v>
       </x:c>
       <x:c r="C497" s="0">
-        <x:v>0.07</x:v>
+        <x:v>-0.07</x:v>
       </x:c>
       <x:c r="D497" s="0" t="s">
         <x:v>295</x:v>
@@ -15769,10 +15763,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B498" s="0">
-        <x:v>42.78</x:v>
+        <x:v>40.48</x:v>
       </x:c>
       <x:c r="C498" s="0">
-        <x:v>0.62</x:v>
+        <x:v>-2.3</x:v>
       </x:c>
       <x:c r="D498" s="0" t="s">
         <x:v>296</x:v>
@@ -15798,10 +15792,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B499" s="0">
-        <x:v>66.75</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C499" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.35</x:v>
       </x:c>
       <x:c r="D499" s="0" t="s">
         <x:v>296</x:v>
@@ -15827,10 +15821,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B500" s="0">
-        <x:v>114.2</x:v>
+        <x:v>115.2</x:v>
       </x:c>
       <x:c r="C500" s="0">
-        <x:v>-1</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D500" s="0" t="s">
         <x:v>296</x:v>
@@ -15856,10 +15850,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B501" s="0">
-        <x:v>62.5</x:v>
+        <x:v>60.9</x:v>
       </x:c>
       <x:c r="C501" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>-1.6</x:v>
       </x:c>
       <x:c r="D501" s="0" t="s">
         <x:v>297</x:v>
@@ -15885,10 +15879,10 @@
         <x:v>298</x:v>
       </x:c>
       <x:c r="B502" s="0">
-        <x:v>316.75</x:v>
+        <x:v>308.5</x:v>
       </x:c>
       <x:c r="C502" s="0">
-        <x:v>-7.25</x:v>
+        <x:v>-8.25</x:v>
       </x:c>
       <x:c r="D502" s="0" t="s">
         <x:v>297</x:v>
@@ -15914,10 +15908,10 @@
         <x:v>299</x:v>
       </x:c>
       <x:c r="B503" s="0">
-        <x:v>30.8</x:v>
+        <x:v>30.7</x:v>
       </x:c>
       <x:c r="C503" s="0">
-        <x:v>0.34</x:v>
+        <x:v>-0.1</x:v>
       </x:c>
       <x:c r="D503" s="0" t="s">
         <x:v>297</x:v>
@@ -15943,10 +15937,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B504" s="0">
-        <x:v>3.51</x:v>
+        <x:v>3.7</x:v>
       </x:c>
       <x:c r="C504" s="0">
-        <x:v>-0.32</x:v>
+        <x:v>0.19</x:v>
       </x:c>
       <x:c r="D504" s="0" t="s">
         <x:v>300</x:v>
@@ -15972,10 +15966,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B505" s="0">
-        <x:v>15.99</x:v>
+        <x:v>16.38</x:v>
       </x:c>
       <x:c r="C505" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.39</x:v>
       </x:c>
       <x:c r="D505" s="0" t="s">
         <x:v>301</x:v>
@@ -16001,10 +15995,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B506" s="0">
-        <x:v>15.99</x:v>
+        <x:v>16.38</x:v>
       </x:c>
       <x:c r="C506" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.39</x:v>
       </x:c>
       <x:c r="D506" s="0" t="s">
         <x:v>301</x:v>
@@ -16030,10 +16024,10 @@
         <x:v>233</x:v>
       </x:c>
       <x:c r="B507" s="0">
-        <x:v>17.04</x:v>
+        <x:v>16.75</x:v>
       </x:c>
       <x:c r="C507" s="0">
-        <x:v>-1.24</x:v>
+        <x:v>-0.29</x:v>
       </x:c>
       <x:c r="D507" s="0" t="s">
         <x:v>302</x:v>
@@ -16059,10 +16053,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B508" s="0">
-        <x:v>5.94</x:v>
+        <x:v>5.87</x:v>
       </x:c>
       <x:c r="C508" s="0">
-        <x:v>0.07</x:v>
+        <x:v>-0.07</x:v>
       </x:c>
       <x:c r="D508" s="0" t="s">
         <x:v>302</x:v>
@@ -16088,10 +16082,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B509" s="0">
-        <x:v>53</x:v>
+        <x:v>53.3</x:v>
       </x:c>
       <x:c r="C509" s="0">
-        <x:v>0.5</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D509" s="0" t="s">
         <x:v>302</x:v>
@@ -16117,10 +16111,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B510" s="0">
-        <x:v>66.75</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C510" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.35</x:v>
       </x:c>
       <x:c r="D510" s="0" t="s">
         <x:v>303</x:v>
@@ -16146,10 +16140,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B511" s="0">
-        <x:v>232.7</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C511" s="0">
-        <x:v>3.4</x:v>
+        <x:v>-2.7</x:v>
       </x:c>
       <x:c r="D511" s="0" t="s">
         <x:v>303</x:v>
@@ -16175,10 +16169,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B512" s="0">
-        <x:v>66.75</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C512" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.35</x:v>
       </x:c>
       <x:c r="D512" s="0" t="s">
         <x:v>304</x:v>
@@ -16204,10 +16198,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B513" s="0">
-        <x:v>283.5</x:v>
+        <x:v>286.25</x:v>
       </x:c>
       <x:c r="C513" s="0">
-        <x:v>2.5</x:v>
+        <x:v>2.75</x:v>
       </x:c>
       <x:c r="D513" s="0" t="s">
         <x:v>305</x:v>
@@ -16233,10 +16227,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B514" s="0">
-        <x:v>79.8</x:v>
+        <x:v>82.15</x:v>
       </x:c>
       <x:c r="C514" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="D514" s="0" t="s">
         <x:v>306</x:v>
@@ -16262,10 +16256,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B515" s="0">
-        <x:v>66.75</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C515" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.35</x:v>
       </x:c>
       <x:c r="D515" s="0" t="s">
         <x:v>307</x:v>
@@ -16291,10 +16285,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B516" s="0">
-        <x:v>408</x:v>
+        <x:v>396.5</x:v>
       </x:c>
       <x:c r="C516" s="0">
-        <x:v>-6</x:v>
+        <x:v>-11.5</x:v>
       </x:c>
       <x:c r="D516" s="0" t="s">
         <x:v>307</x:v>
@@ -16320,10 +16314,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B517" s="0">
-        <x:v>3.51</x:v>
+        <x:v>3.7</x:v>
       </x:c>
       <x:c r="C517" s="0">
-        <x:v>-0.32</x:v>
+        <x:v>0.19</x:v>
       </x:c>
       <x:c r="D517" s="0" t="s">
         <x:v>307</x:v>
@@ -16349,10 +16343,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B518" s="0">
-        <x:v>3.51</x:v>
+        <x:v>3.7</x:v>
       </x:c>
       <x:c r="C518" s="0">
-        <x:v>-0.32</x:v>
+        <x:v>0.19</x:v>
       </x:c>
       <x:c r="D518" s="0" t="s">
         <x:v>307</x:v>
@@ -16378,10 +16372,10 @@
         <x:v>308</x:v>
       </x:c>
       <x:c r="B519" s="0">
-        <x:v>2.99</x:v>
+        <x:v>3.28</x:v>
       </x:c>
       <x:c r="C519" s="0">
-        <x:v>0.27</x:v>
+        <x:v>0.29</x:v>
       </x:c>
       <x:c r="D519" s="0" t="s">
         <x:v>307</x:v>
@@ -16407,10 +16401,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B520" s="0">
-        <x:v>283.5</x:v>
+        <x:v>286.25</x:v>
       </x:c>
       <x:c r="C520" s="0">
-        <x:v>2.5</x:v>
+        <x:v>2.75</x:v>
       </x:c>
       <x:c r="D520" s="0" t="s">
         <x:v>309</x:v>
@@ -16436,10 +16430,10 @@
         <x:v>310</x:v>
       </x:c>
       <x:c r="B521" s="0">
-        <x:v>37.08</x:v>
+        <x:v>35.18</x:v>
       </x:c>
       <x:c r="C521" s="0">
-        <x:v>2.3</x:v>
+        <x:v>-1.9</x:v>
       </x:c>
       <x:c r="D521" s="0" t="s">
         <x:v>309</x:v>
@@ -16465,10 +16459,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B522" s="0">
-        <x:v>232.7</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C522" s="0">
-        <x:v>3.4</x:v>
+        <x:v>-2.7</x:v>
       </x:c>
       <x:c r="D522" s="0" t="s">
         <x:v>311</x:v>
@@ -16494,10 +16488,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B523" s="0">
-        <x:v>34.66</x:v>
+        <x:v>34.62</x:v>
       </x:c>
       <x:c r="C523" s="0">
-        <x:v>-0.92</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D523" s="0" t="s">
         <x:v>312</x:v>
@@ -16523,10 +16517,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B524" s="0">
-        <x:v>42.78</x:v>
+        <x:v>40.48</x:v>
       </x:c>
       <x:c r="C524" s="0">
-        <x:v>0.62</x:v>
+        <x:v>-2.3</x:v>
       </x:c>
       <x:c r="D524" s="0" t="s">
         <x:v>313</x:v>
@@ -16552,10 +16546,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B525" s="0">
-        <x:v>34.66</x:v>
+        <x:v>34.62</x:v>
       </x:c>
       <x:c r="C525" s="0">
-        <x:v>-0.92</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D525" s="0" t="s">
         <x:v>313</x:v>
@@ -16581,10 +16575,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B526" s="0">
-        <x:v>3.51</x:v>
+        <x:v>3.7</x:v>
       </x:c>
       <x:c r="C526" s="0">
-        <x:v>-0.32</x:v>
+        <x:v>0.19</x:v>
       </x:c>
       <x:c r="D526" s="0" t="s">
         <x:v>313</x:v>
@@ -16610,10 +16604,10 @@
         <x:v>314</x:v>
       </x:c>
       <x:c r="B527" s="0">
-        <x:v>83.8</x:v>
+        <x:v>83.85</x:v>
       </x:c>
       <x:c r="C527" s="0">
-        <x:v>-1.2</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D527" s="0" t="s">
         <x:v>315</x:v>
@@ -16639,10 +16633,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B528" s="0">
-        <x:v>12.74</x:v>
+        <x:v>14.01</x:v>
       </x:c>
       <x:c r="C528" s="0">
-        <x:v>1.15</x:v>
+        <x:v>1.27</x:v>
       </x:c>
       <x:c r="D528" s="0" t="s">
         <x:v>315</x:v>
@@ -16668,10 +16662,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B529" s="0">
-        <x:v>15.71</x:v>
+        <x:v>15.12</x:v>
       </x:c>
       <x:c r="C529" s="0">
-        <x:v>-0.09</x:v>
+        <x:v>-0.59</x:v>
       </x:c>
       <x:c r="D529" s="0" t="s">
         <x:v>315</x:v>
@@ -16697,10 +16691,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B530" s="0">
-        <x:v>3.51</x:v>
+        <x:v>3.7</x:v>
       </x:c>
       <x:c r="C530" s="0">
-        <x:v>-0.32</x:v>
+        <x:v>0.19</x:v>
       </x:c>
       <x:c r="D530" s="0" t="s">
         <x:v>315</x:v>
@@ -16726,10 +16720,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B531" s="0">
-        <x:v>5.94</x:v>
+        <x:v>5.87</x:v>
       </x:c>
       <x:c r="C531" s="0">
-        <x:v>0.07</x:v>
+        <x:v>-0.07</x:v>
       </x:c>
       <x:c r="D531" s="0" t="s">
         <x:v>316</x:v>
@@ -16755,10 +16749,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B532" s="0">
-        <x:v>47.7</x:v>
+        <x:v>47.26</x:v>
       </x:c>
       <x:c r="C532" s="0">
-        <x:v>0.14</x:v>
+        <x:v>-0.44</x:v>
       </x:c>
       <x:c r="D532" s="0" t="s">
         <x:v>317</x:v>
@@ -16784,10 +16778,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B533" s="0">
-        <x:v>42.78</x:v>
+        <x:v>40.48</x:v>
       </x:c>
       <x:c r="C533" s="0">
-        <x:v>0.62</x:v>
+        <x:v>-2.3</x:v>
       </x:c>
       <x:c r="D533" s="0" t="s">
         <x:v>318</x:v>
@@ -16813,10 +16807,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B534" s="0">
-        <x:v>15.71</x:v>
+        <x:v>15.12</x:v>
       </x:c>
       <x:c r="C534" s="0">
-        <x:v>-0.09</x:v>
+        <x:v>-0.59</x:v>
       </x:c>
       <x:c r="D534" s="0" t="s">
         <x:v>318</x:v>
@@ -16842,10 +16836,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B535" s="0">
-        <x:v>15.71</x:v>
+        <x:v>15.12</x:v>
       </x:c>
       <x:c r="C535" s="0">
-        <x:v>-0.09</x:v>
+        <x:v>-0.59</x:v>
       </x:c>
       <x:c r="D535" s="0" t="s">
         <x:v>318</x:v>
@@ -16871,10 +16865,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B536" s="0">
-        <x:v>3.51</x:v>
+        <x:v>3.7</x:v>
       </x:c>
       <x:c r="C536" s="0">
-        <x:v>-0.32</x:v>
+        <x:v>0.19</x:v>
       </x:c>
       <x:c r="D536" s="0" t="s">
         <x:v>318</x:v>
@@ -16900,10 +16894,10 @@
         <x:v>319</x:v>
       </x:c>
       <x:c r="B537" s="0">
-        <x:v>22.24</x:v>
+        <x:v>20.02</x:v>
       </x:c>
       <x:c r="C537" s="0">
-        <x:v>-2.46</x:v>
+        <x:v>-2.22</x:v>
       </x:c>
       <x:c r="D537" s="0" t="s">
         <x:v>318</x:v>
@@ -16929,10 +16923,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B538" s="0">
-        <x:v>66.75</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C538" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.35</x:v>
       </x:c>
       <x:c r="D538" s="0" t="s">
         <x:v>320</x:v>
@@ -16958,10 +16952,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B539" s="0">
-        <x:v>3.51</x:v>
+        <x:v>3.7</x:v>
       </x:c>
       <x:c r="C539" s="0">
-        <x:v>-0.32</x:v>
+        <x:v>0.19</x:v>
       </x:c>
       <x:c r="D539" s="0" t="s">
         <x:v>320</x:v>
@@ -16987,10 +16981,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B540" s="0">
-        <x:v>95.95</x:v>
+        <x:v>95.4</x:v>
       </x:c>
       <x:c r="C540" s="0">
-        <x:v>-2.2</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="D540" s="0" t="s">
         <x:v>321</x:v>
@@ -17016,10 +17010,10 @@
         <x:v>237</x:v>
       </x:c>
       <x:c r="B541" s="0">
-        <x:v>23.92</x:v>
+        <x:v>23.28</x:v>
       </x:c>
       <x:c r="C541" s="0">
-        <x:v>-1.64</x:v>
+        <x:v>-0.64</x:v>
       </x:c>
       <x:c r="D541" s="0" t="s">
         <x:v>322</x:v>
@@ -17045,10 +17039,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B542" s="0">
-        <x:v>66.75</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C542" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.35</x:v>
       </x:c>
       <x:c r="D542" s="0" t="s">
         <x:v>323</x:v>
@@ -17074,10 +17068,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B543" s="0">
-        <x:v>3.51</x:v>
+        <x:v>3.7</x:v>
       </x:c>
       <x:c r="C543" s="0">
-        <x:v>-0.32</x:v>
+        <x:v>0.19</x:v>
       </x:c>
       <x:c r="D543" s="0" t="s">
         <x:v>323</x:v>
@@ -17103,10 +17097,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B544" s="0">
-        <x:v>3.51</x:v>
+        <x:v>3.7</x:v>
       </x:c>
       <x:c r="C544" s="0">
-        <x:v>-0.32</x:v>
+        <x:v>0.19</x:v>
       </x:c>
       <x:c r="D544" s="0" t="s">
         <x:v>323</x:v>
@@ -17132,10 +17126,10 @@
         <x:v>164</x:v>
       </x:c>
       <x:c r="B545" s="0">
-        <x:v>40.94</x:v>
+        <x:v>40.9</x:v>
       </x:c>
       <x:c r="C545" s="0">
-        <x:v>-0.72</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D545" s="0" t="s">
         <x:v>324</x:v>
@@ -17161,10 +17155,10 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="B546" s="0">
-        <x:v>14.43</x:v>
+        <x:v>12.99</x:v>
       </x:c>
       <x:c r="C546" s="0">
-        <x:v>1.31</x:v>
+        <x:v>-1.44</x:v>
       </x:c>
       <x:c r="D546" s="0" t="s">
         <x:v>325</x:v>
@@ -17190,10 +17184,10 @@
         <x:v>308</x:v>
       </x:c>
       <x:c r="B547" s="0">
-        <x:v>2.99</x:v>
+        <x:v>3.28</x:v>
       </x:c>
       <x:c r="C547" s="0">
-        <x:v>0.27</x:v>
+        <x:v>0.29</x:v>
       </x:c>
       <x:c r="D547" s="0" t="s">
         <x:v>325</x:v>
@@ -17212,93 +17206,6 @@
       </x:c>
       <x:c r="I547" s="0">
         <x:v>0.0072</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="548" spans="1:9">
-      <x:c r="A548" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="B548" s="0">
-        <x:v>4.5</x:v>
-      </x:c>
-      <x:c r="C548" s="0">
-        <x:v>0.04</x:v>
-      </x:c>
-      <x:c r="D548" s="0" t="s">
-        <x:v>326</x:v>
-      </x:c>
-      <x:c r="E548" s="0">
-        <x:v>975000</x:v>
-      </x:c>
-      <x:c r="F548" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G548" s="0">
-        <x:v>2024.12</x:v>
-      </x:c>
-      <x:c r="H548" s="0">
-        <x:v>2051226610</x:v>
-      </x:c>
-      <x:c r="I548" s="0">
-        <x:v>0.0206</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="549" spans="1:9">
-      <x:c r="A549" s="0" t="s">
-        <x:v>327</x:v>
-      </x:c>
-      <x:c r="B549" s="0">
-        <x:v>118.5</x:v>
-      </x:c>
-      <x:c r="C549" s="0">
-        <x:v>-3.1</x:v>
-      </x:c>
-      <x:c r="D549" s="0" t="s">
-        <x:v>326</x:v>
-      </x:c>
-      <x:c r="E549" s="0">
-        <x:v>750000</x:v>
-      </x:c>
-      <x:c r="F549" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G549" s="0">
-        <x:v>2024.12</x:v>
-      </x:c>
-      <x:c r="H549" s="0">
-        <x:v>636151083</x:v>
-      </x:c>
-      <x:c r="I549" s="0">
-        <x:v>0.0449</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="550" spans="1:9">
-      <x:c r="A550" s="0" t="s">
-        <x:v>319</x:v>
-      </x:c>
-      <x:c r="B550" s="0">
-        <x:v>22.24</x:v>
-      </x:c>
-      <x:c r="C550" s="0">
-        <x:v>-2.46</x:v>
-      </x:c>
-      <x:c r="D550" s="0" t="s">
-        <x:v>326</x:v>
-      </x:c>
-      <x:c r="E550" s="0">
-        <x:v>3432600</x:v>
-      </x:c>
-      <x:c r="F550" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G550" s="0">
-        <x:v>2024.12</x:v>
-      </x:c>
-      <x:c r="H550" s="0">
-        <x:v>1200876303</x:v>
-      </x:c>
-      <x:c r="I550" s="0">
-        <x:v>0.1089</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/yeni-is-anlasmalari/data/yeni-is-anlasmalari.xlsx
+++ b/app/borsa/yeni-is-anlasmalari/data/yeni-is-anlasmalari.xlsx
@@ -43,33 +43,54 @@
     <x:t>Yeni İş İlişkisi / Yıllık Satışlar</x:t>
   </x:si>
   <x:si>
+    <x:t>FONET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-04-28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASTOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>USD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-04-24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BVSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUR</x:t>
+  </x:si>
+  <x:si>
     <x:t>ARDYZ</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-04-24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>USD</x:t>
-  </x:si>
-  <x:si>
     <x:t>KLYPV</x:t>
   </x:si>
   <x:si>
     <x:t>2026-04-22</x:t>
   </x:si>
   <x:si>
-    <x:t>TRY</x:t>
-  </x:si>
-  <x:si>
     <x:t>FORTE</x:t>
   </x:si>
   <x:si>
     <x:t>MEKAG</x:t>
   </x:si>
   <x:si>
-    <x:t>EUR</x:t>
-  </x:si>
-  <x:si>
     <x:t>HRKET</x:t>
   </x:si>
   <x:si>
@@ -121,9 +142,6 @@
     <x:t>GBP</x:t>
   </x:si>
   <x:si>
-    <x:t>BVSAN</x:t>
-  </x:si>
-  <x:si>
     <x:t>2026-04-13</x:t>
   </x:si>
   <x:si>
@@ -148,9 +166,6 @@
     <x:t>GATEG</x:t>
   </x:si>
   <x:si>
-    <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
     <x:t>2026-04-07</x:t>
   </x:si>
   <x:si>
@@ -166,10 +181,250 @@
     <x:t>2026-04-02</x:t>
   </x:si>
   <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
     <x:t>2026-04-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NETAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-03-31</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-03-30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRLSM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PLTUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-03-27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-03-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PENGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-03-24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-03-23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKHAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-03-18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-03-17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASELS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-03-16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-03-13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-03-12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KBORU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-03-11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-03-10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMRTG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-03-06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-03-04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BESTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-03-03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ONRYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-02-27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-02-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UCAYM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-02-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CVKMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LINK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-02-24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-02-23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-02-20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUPWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-02-19</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">EUR </x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEGMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-02-17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-02-16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-02-13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-02-12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCKRC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CGCAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-02-11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-02-05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-02-04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-02-03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRMPL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-02-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-01-30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-01-29</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-01-28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-01-27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-01-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARBL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAFKR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-01-23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-01-22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURKN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-01-21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-01-20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DCTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURCE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-01-19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-01-15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-01-14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-01-13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-01-12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUCLK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-01-09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-01-08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-01-06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-01-05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-01-02</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -520,7 +775,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I43"/>
+  <x:dimension ref="A1:I168"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -557,16 +812,16 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>45.88</x:v>
+        <x:v>5.01</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>2.52</x:v>
+        <x:v>0.15</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>606770</x:v>
+        <x:v>132077304</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
         <x:v>11</x:v>
@@ -575,10 +830,10 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>855070469</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>0.0064</x:v>
+        <x:v>0.1545</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -586,57 +841,57 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>60.3</x:v>
+        <x:v>254.75</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>-0.75</x:v>
+        <x:v>11.15</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>505597002</x:v>
+        <x:v>51531000</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G3" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>8121300519</x:v>
+        <x:v>35290767390</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>0.0623</x:v>
+        <x:v>0.0656</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
       <x:c r="A4" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>45.88</x:v>
+        <x:v>1120</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>2.52</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>948000</x:v>
+        <x:v>950978</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G4" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>1883544167</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>0.0101</x:v>
+        <x:v>0.0227</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -644,57 +899,57 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>95.6</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>0.9</x:v>
+        <x:v>-41.5</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>622000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G5" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>71453576000</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>0.0114</x:v>
+        <x:v>0.0628</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
       <x:c r="A6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B6" s="0">
+        <x:v>82.05</x:v>
+      </x:c>
+      <x:c r="C6" s="0">
+        <x:v>-0.75</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B6" s="0">
-        <x:v>4.27</x:v>
-      </x:c>
-      <x:c r="C6" s="0">
-        <x:v>-0.02</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="E6" s="0">
-        <x:v>983000</x:v>
+        <x:v>286071819</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G6" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>2875634546</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>0.018</x:v>
+        <x:v>0.0818</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -702,28 +957,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>71.2</x:v>
+        <x:v>120.8</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>4.05</x:v>
+        <x:v>3.9</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E7" s="0">
+        <x:v>883793</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="E7" s="0">
-        <x:v>3421818</x:v>
-      </x:c>
-      <x:c r="F7" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="G7" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>5948036961</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>0.0257</x:v>
+        <x:v>0.0148</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -731,28 +986,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>45.3</x:v>
+        <x:v>48.5</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>1.9</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>697435</x:v>
+        <x:v>606770</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G8" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>4728937463</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>0.0066</x:v>
+        <x:v>0.0064</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -760,16 +1015,16 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>52.15</x:v>
+        <x:v>58.35</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>-1.65</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>4587145</x:v>
+        <x:v>505597002</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
         <x:v>11</x:v>
@@ -778,126 +1033,126 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>16733157490</x:v>
+        <x:v>8121300519</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>0.0123</x:v>
+        <x:v>0.0623</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
       <x:c r="A10" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>39.68</x:v>
+        <x:v>48.5</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>0.28</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>43200000</x:v>
+        <x:v>948000</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G10" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>8236540064</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>0.2345</x:v>
+        <x:v>0.0101</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
       <x:c r="A11" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>16.15</x:v>
+        <x:v>92.4</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>0.43</x:v>
+        <x:v>-2.15</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>1200000</x:v>
+        <x:v>622000</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G11" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>3139850323</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>0.0201</x:v>
+        <x:v>0.0114</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
       <x:c r="A12" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>60.3</x:v>
+        <x:v>4.26</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>-0.75</x:v>
+        <x:v>-0.1</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>247902522</x:v>
+        <x:v>983000</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G12" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>8121300519</x:v>
+        <x:v>2875634546</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>0.0305</x:v>
+        <x:v>0.018</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
       <x:c r="A13" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>45.88</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>2.52</x:v>
+        <x:v>-1.8</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>366000</x:v>
+        <x:v>3421818</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G13" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>5948036961</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>0.0039</x:v>
+        <x:v>0.0257</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -905,28 +1160,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>291.25</x:v>
+        <x:v>42.88</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>6.25</x:v>
+        <x:v>-2.7</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>141051834</x:v>
+        <x:v>697435</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G14" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>709077088</x:v>
+        <x:v>4728937463</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>0.1989</x:v>
+        <x:v>0.0066</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -934,103 +1189,103 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>4.94</x:v>
+        <x:v>54.35</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>-0.09</x:v>
+        <x:v>-0.75</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>5096500000</x:v>
+        <x:v>4587145</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>19538660616</x:v>
+        <x:v>16733157490</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>0.2608</x:v>
+        <x:v>0.0123</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
       <x:c r="A16" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>4.94</x:v>
+        <x:v>40.76</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>-0.09</x:v>
+        <x:v>0.44</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>5096500000</x:v>
+        <x:v>43200000</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>19538660616</x:v>
+        <x:v>8236540064</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>0.2608</x:v>
+        <x:v>0.2345</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
       <x:c r="A17" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>35</x:v>
+        <x:v>15.95</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>0.02</x:v>
+        <x:v>-0.02</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>37500000</x:v>
+        <x:v>1200000</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G17" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>16355768622</x:v>
+        <x:v>3139850323</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>0.1024</x:v>
+        <x:v>0.0201</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
       <x:c r="A18" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>222.4</x:v>
+        <x:v>58.35</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>3.9</x:v>
+        <x:v>-1.65</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>2030000</x:v>
+        <x:v>247902522</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
         <x:v>11</x:v>
@@ -1039,404 +1294,404 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>2159813703</x:v>
+        <x:v>8121300519</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>0.042</x:v>
+        <x:v>0.0305</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
       <x:c r="A19" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>52.15</x:v>
+        <x:v>48.5</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>31146246</x:v>
+        <x:v>366000</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G19" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>16733157490</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>0.0832</x:v>
+        <x:v>0.0039</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
       <x:c r="A20" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>11.79</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>0.13</x:v>
+        <x:v>-13.75</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
         <x:v>33</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>1000000</x:v>
+        <x:v>141051834</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G20" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>7221187888</x:v>
+        <x:v>709077088</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>0.0001</x:v>
+        <x:v>0.1989</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
       <x:c r="A21" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>11.79</x:v>
+        <x:v>4.73</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>0.13</x:v>
+        <x:v>-0.2</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
         <x:v>33</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>3150000</x:v>
+        <x:v>5096500000</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>7221187888</x:v>
+        <x:v>19538660616</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>0.0227</x:v>
+        <x:v>0.2608</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
       <x:c r="A22" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>11.79</x:v>
+        <x:v>4.73</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>0.13</x:v>
+        <x:v>-0.2</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
         <x:v>33</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>2690000</x:v>
+        <x:v>5096500000</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>7221187888</x:v>
+        <x:v>19538660616</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>0.0166</x:v>
+        <x:v>0.2608</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
       <x:c r="A23" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>52.15</x:v>
+        <x:v>34.4</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>-1.12</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>4103000</x:v>
+        <x:v>37500000</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G23" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>16733157490</x:v>
+        <x:v>16355768622</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>0.0109</x:v>
+        <x:v>0.1024</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
       <x:c r="A24" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>112.2</x:v>
+        <x:v>222.6</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>0.5</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>500000</x:v>
+        <x:v>2030000</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G24" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>3150489640</x:v>
+        <x:v>2159813703</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>0.0083</x:v>
+        <x:v>0.042</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
       <x:c r="A25" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>45.88</x:v>
+        <x:v>54.35</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>2.52</x:v>
+        <x:v>-0.75</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>872928</x:v>
+        <x:v>31146246</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G25" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>16733157490</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>0.0092</x:v>
+        <x:v>0.0832</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
       <x:c r="A26" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>95.6</x:v>
+        <x:v>11.59</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>0.9</x:v>
+        <x:v>0.07</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>21250000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G26" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>7221187888</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>0.0087</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
       <x:c r="A27" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>60.3</x:v>
+        <x:v>11.59</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>-0.75</x:v>
+        <x:v>0.07</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>67690912</x:v>
+        <x:v>3150000</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G27" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>8121300519</x:v>
+        <x:v>7221187888</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>0.0083</x:v>
+        <x:v>0.0227</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
       <x:c r="A28" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>35</x:v>
+        <x:v>11.59</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0.07</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>65458848</x:v>
+        <x:v>2690000</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G28" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>16355768622</x:v>
+        <x:v>7221187888</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>0.1784</x:v>
+        <x:v>0.0166</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
       <x:c r="A29" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>25.48</x:v>
+        <x:v>54.35</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>0.48</x:v>
+        <x:v>-0.75</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>689500000</x:v>
+        <x:v>4103000</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G29" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>884571536</x:v>
+        <x:v>16733157490</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>0.7795</x:v>
+        <x:v>0.0109</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
       <x:c r="A30" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>5.84</x:v>
+        <x:v>120.8</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>0.11</x:v>
+        <x:v>3.9</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>3024490</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G30" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>2322993973</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>0.0671</x:v>
+        <x:v>0.0083</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
       <x:c r="A31" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>5.84</x:v>
+        <x:v>48.5</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>0.11</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>4510336</x:v>
+        <x:v>872928</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G31" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>2322993973</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>0.0865</x:v>
+        <x:v>0.0092</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
       <x:c r="A32" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>46.28</x:v>
+        <x:v>92.4</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>0.12</x:v>
+        <x:v>-2.15</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>205000000</x:v>
+        <x:v>21250000</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
         <x:v>11</x:v>
@@ -1445,85 +1700,85 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>20597209000</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>0.4434</x:v>
+        <x:v>0.0087</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
       <x:c r="A33" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>350</x:v>
+        <x:v>58.35</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>10</x:v>
+        <x:v>-1.65</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>305000000</x:v>
+        <x:v>67690912</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G33" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>400439646</x:v>
+        <x:v>8121300519</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>0.7617</x:v>
+        <x:v>0.0083</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
       <x:c r="A34" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B34" s="0">
+        <x:v>34.4</x:v>
+      </x:c>
+      <x:c r="C34" s="0">
+        <x:v>-1.12</x:v>
+      </x:c>
+      <x:c r="D34" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="B34" s="0">
-        <x:v>84.7</x:v>
-      </x:c>
-      <x:c r="C34" s="0">
-        <x:v>0.7</x:v>
-      </x:c>
-      <x:c r="D34" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
       <x:c r="E34" s="0">
-        <x:v>11700000</x:v>
+        <x:v>65458848</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G34" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>16355768622</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>0.1718</x:v>
+        <x:v>0.1784</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
       <x:c r="A35" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>222.4</x:v>
+        <x:v>24.16</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>3.9</x:v>
+        <x:v>-0.56</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>1900000</x:v>
+        <x:v>689500000</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
         <x:v>11</x:v>
@@ -1532,114 +1787,114 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>2159813703</x:v>
+        <x:v>884571536</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>0.0391</x:v>
+        <x:v>0.7795</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
       <x:c r="A36" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>4.27</x:v>
+        <x:v>5.82</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>-0.05</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>1670000</x:v>
+        <x:v>3024490</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G36" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>2875634546</x:v>
+        <x:v>2322993973</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>0.0298</x:v>
+        <x:v>0.0671</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
       <x:c r="A37" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>25.48</x:v>
+        <x:v>5.82</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>0.48</x:v>
+        <x:v>-0.05</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>48895800</x:v>
+        <x:v>4510336</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G37" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>884571536</x:v>
+        <x:v>2322993973</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>0.0553</x:v>
+        <x:v>0.0865</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
       <x:c r="A38" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>25.48</x:v>
+        <x:v>49.2</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>0.48</x:v>
+        <x:v>-0.14</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>689500000</x:v>
+        <x:v>205000000</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G38" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>884571536</x:v>
+        <x:v>20597209000</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>0.7795</x:v>
+        <x:v>0.4434</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
       <x:c r="A39" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>46.7</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>-0.1</x:v>
+        <x:v>-9</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>3102911</x:v>
+        <x:v>305000000</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
         <x:v>11</x:v>
@@ -1648,114 +1903,114 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>2907014564</x:v>
+        <x:v>400439646</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>0.0475</x:v>
+        <x:v>0.7617</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
       <x:c r="A40" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>23.8</x:v>
+        <x:v>82.05</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>0</x:v>
+        <x:v>-0.75</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>13000000</x:v>
+        <x:v>11700000</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G40" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>11834942581</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>0.0563</x:v>
+        <x:v>0.1718</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
       <x:c r="A41" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>71.2</x:v>
+        <x:v>222.6</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>4.05</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>6800000</x:v>
+        <x:v>1900000</x:v>
       </x:c>
       <x:c r="F41" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G41" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>5948036961</x:v>
+        <x:v>2159813703</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>0.0583</x:v>
+        <x:v>0.0391</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
       <x:c r="A42" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>46.28</x:v>
+        <x:v>4.26</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>0.12</x:v>
+        <x:v>-0.1</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>36750000</x:v>
+        <x:v>1670000</x:v>
       </x:c>
       <x:c r="F42" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G42" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>20597209000</x:v>
+        <x:v>2875634546</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>0.0793</x:v>
+        <x:v>0.0298</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
       <x:c r="A43" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>995</x:v>
+        <x:v>24.16</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>20</x:v>
+        <x:v>-0.56</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>3867260</x:v>
+        <x:v>48895800</x:v>
       </x:c>
       <x:c r="F43" s="0" t="s">
         <x:v>11</x:v>
@@ -1764,10 +2019,3635 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H43" s="0">
+        <x:v>884571536</x:v>
+      </x:c>
+      <x:c r="I43" s="0">
+        <x:v>0.0553</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:9">
+      <x:c r="A44" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B44" s="0">
+        <x:v>24.16</x:v>
+      </x:c>
+      <x:c r="C44" s="0">
+        <x:v>-0.56</x:v>
+      </x:c>
+      <x:c r="D44" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E44" s="0">
+        <x:v>689500000</x:v>
+      </x:c>
+      <x:c r="F44" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G44" s="0">
+        <x:v>2025.12</x:v>
+      </x:c>
+      <x:c r="H44" s="0">
+        <x:v>884571536</x:v>
+      </x:c>
+      <x:c r="I44" s="0">
+        <x:v>0.7795</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:9">
+      <x:c r="A45" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B45" s="0">
+        <x:v>44.6</x:v>
+      </x:c>
+      <x:c r="C45" s="0">
+        <x:v>-3.18</x:v>
+      </x:c>
+      <x:c r="D45" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E45" s="0">
+        <x:v>3102911</x:v>
+      </x:c>
+      <x:c r="F45" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G45" s="0">
+        <x:v>2025.12</x:v>
+      </x:c>
+      <x:c r="H45" s="0">
+        <x:v>2907014564</x:v>
+      </x:c>
+      <x:c r="I45" s="0">
+        <x:v>0.0475</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:9">
+      <x:c r="A46" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B46" s="0">
+        <x:v>23.58</x:v>
+      </x:c>
+      <x:c r="C46" s="0">
+        <x:v>-0.42</x:v>
+      </x:c>
+      <x:c r="D46" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E46" s="0">
+        <x:v>13000000</x:v>
+      </x:c>
+      <x:c r="F46" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G46" s="0">
+        <x:v>2025.12</x:v>
+      </x:c>
+      <x:c r="H46" s="0">
+        <x:v>11834942581</x:v>
+      </x:c>
+      <x:c r="I46" s="0">
+        <x:v>0.0563</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:9">
+      <x:c r="A47" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B47" s="0">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C47" s="0">
+        <x:v>-1.8</x:v>
+      </x:c>
+      <x:c r="D47" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E47" s="0">
+        <x:v>6800000</x:v>
+      </x:c>
+      <x:c r="F47" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G47" s="0">
+        <x:v>2025.12</x:v>
+      </x:c>
+      <x:c r="H47" s="0">
+        <x:v>5948036961</x:v>
+      </x:c>
+      <x:c r="I47" s="0">
+        <x:v>0.0583</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:9">
+      <x:c r="A48" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B48" s="0">
+        <x:v>49.2</x:v>
+      </x:c>
+      <x:c r="C48" s="0">
+        <x:v>-0.14</x:v>
+      </x:c>
+      <x:c r="D48" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E48" s="0">
+        <x:v>36750000</x:v>
+      </x:c>
+      <x:c r="F48" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G48" s="0">
+        <x:v>2025.12</x:v>
+      </x:c>
+      <x:c r="H48" s="0">
+        <x:v>20597209000</x:v>
+      </x:c>
+      <x:c r="I48" s="0">
+        <x:v>0.0793</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:9">
+      <x:c r="A49" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B49" s="0">
+        <x:v>1120</x:v>
+      </x:c>
+      <x:c r="C49" s="0">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D49" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E49" s="0">
+        <x:v>3867260</x:v>
+      </x:c>
+      <x:c r="F49" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G49" s="0">
+        <x:v>2025.12</x:v>
+      </x:c>
+      <x:c r="H49" s="0">
         <x:v>1883544167</x:v>
       </x:c>
-      <x:c r="I43" s="0">
+      <x:c r="I49" s="0">
         <x:v>0.0912</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:9">
+      <x:c r="A50" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B50" s="0">
+        <x:v>63.1</x:v>
+      </x:c>
+      <x:c r="C50" s="0">
+        <x:v>-2.3</x:v>
+      </x:c>
+      <x:c r="D50" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E50" s="0">
+        <x:v>1498029716</x:v>
+      </x:c>
+      <x:c r="F50" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G50" s="0">
+        <x:v>2025.12</x:v>
+      </x:c>
+      <x:c r="H50" s="0">
+        <x:v>12030341104</x:v>
+      </x:c>
+      <x:c r="I50" s="0">
+        <x:v>0.1245</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:9">
+      <x:c r="A51" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B51" s="0">
+        <x:v>34.4</x:v>
+      </x:c>
+      <x:c r="C51" s="0">
+        <x:v>-1.12</x:v>
+      </x:c>
+      <x:c r="D51" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E51" s="0">
+        <x:v>48000000</x:v>
+      </x:c>
+      <x:c r="F51" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G51" s="0">
+        <x:v>2025.12</x:v>
+      </x:c>
+      <x:c r="H51" s="0">
+        <x:v>16355768622</x:v>
+      </x:c>
+      <x:c r="I51" s="0">
+        <x:v>0.1301</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:9">
+      <x:c r="A52" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B52" s="0">
+        <x:v>82.05</x:v>
+      </x:c>
+      <x:c r="C52" s="0">
+        <x:v>-0.75</x:v>
+      </x:c>
+      <x:c r="D52" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="E52" s="0">
+        <x:v>279699629</x:v>
+      </x:c>
+      <x:c r="F52" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G52" s="0">
+        <x:v>2025.12</x:v>
+      </x:c>
+      <x:c r="H52" s="0">
+        <x:v>3495512127</x:v>
+      </x:c>
+      <x:c r="I52" s="0">
+        <x:v>0.08</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:9">
+      <x:c r="A53" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B53" s="0">
+        <x:v>14.91</x:v>
+      </x:c>
+      <x:c r="C53" s="0">
+        <x:v>-0.25</x:v>
+      </x:c>
+      <x:c r="D53" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="E53" s="0">
+        <x:v>7971822</x:v>
+      </x:c>
+      <x:c r="F53" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G53" s="0">
+        <x:v>2025.12</x:v>
+      </x:c>
+      <x:c r="H53" s="0">
+        <x:v>4675369372</x:v>
+      </x:c>
+      <x:c r="I53" s="0">
+        <x:v>0.0756</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:9">
+      <x:c r="A54" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B54" s="0">
+        <x:v>48.5</x:v>
+      </x:c>
+      <x:c r="C54" s="0">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="D54" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="E54" s="0">
+        <x:v>1104000</x:v>
+      </x:c>
+      <x:c r="F54" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G54" s="0">
+        <x:v>2025.12</x:v>
+      </x:c>
+      <x:c r="H54" s="0">
+        <x:v>4224605448</x:v>
+      </x:c>
+      <x:c r="I54" s="0">
+        <x:v>0.0116</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:9">
+      <x:c r="A55" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B55" s="0">
+        <x:v>24.16</x:v>
+      </x:c>
+      <x:c r="C55" s="0">
+        <x:v>-0.56</x:v>
+      </x:c>
+      <x:c r="D55" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="E55" s="0">
+        <x:v>48895800</x:v>
+      </x:c>
+      <x:c r="F55" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G55" s="0">
+        <x:v>2025.12</x:v>
+      </x:c>
+      <x:c r="H55" s="0">
+        <x:v>884571536</x:v>
+      </x:c>
+      <x:c r="I55" s="0">
+        <x:v>0.0553</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:9">
+      <x:c r="A56" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B56" s="0">
+        <x:v>3.3</x:v>
+      </x:c>
+      <x:c r="C56" s="0">
+        <x:v>-0.1</x:v>
+      </x:c>
+      <x:c r="D56" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="E56" s="0">
+        <x:v>191089413</x:v>
+      </x:c>
+      <x:c r="F56" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G56" s="0">
+        <x:v>2025.12</x:v>
+      </x:c>
+      <x:c r="H56" s="0">
+        <x:v>9665356715</x:v>
+      </x:c>
+      <x:c r="I56" s="0">
+        <x:v>0.0198</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:9">
+      <x:c r="A57" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B57" s="0">
+        <x:v>3.3</x:v>
+      </x:c>
+      <x:c r="C57" s="0">
+        <x:v>-0.1</x:v>
+      </x:c>
+      <x:c r="D57" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="E57" s="0">
+        <x:v>605627160</x:v>
+      </x:c>
+      <x:c r="F57" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G57" s="0">
+        <x:v>2025.12</x:v>
+      </x:c>
+      <x:c r="H57" s="0">
+        <x:v>9665356715</x:v>
+      </x:c>
+      <x:c r="I57" s="0">
+        <x:v>0.0627</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:9">
+      <x:c r="A58" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B58" s="0">
+        <x:v>25.86</x:v>
+      </x:c>
+      <x:c r="C58" s="0">
+        <x:v>-0.68</x:v>
+      </x:c>
+      <x:c r="D58" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="E58" s="0">
+        <x:v>2356546000</x:v>
+      </x:c>
+      <x:c r="F58" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G58" s="0">
+        <x:v>2025.12</x:v>
+      </x:c>
+      <x:c r="H58" s="0">
+        <x:v>7708004248</x:v>
+      </x:c>
+      <x:c r="I58" s="0">
+        <x:v>0.3057</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:9">
+      <x:c r="A59" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B59" s="0">
+        <x:v>15.95</x:v>
+      </x:c>
+      <x:c r="C59" s="0">
+        <x:v>-0.02</x:v>
+      </x:c>
+      <x:c r="D59" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="E59" s="0">
+        <x:v>431250</x:v>
+      </x:c>
+      <x:c r="F59" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G59" s="0">
+        <x:v>2025.12</x:v>
+      </x:c>
+      <x:c r="H59" s="0">
+        <x:v>3139850323</x:v>
+      </x:c>
+      <x:c r="I59" s="0">
+        <x:v>0.0071</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:9">
+      <x:c r="A60" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B60" s="0">
+        <x:v>15.95</x:v>
+      </x:c>
+      <x:c r="C60" s="0">
+        <x:v>-0.02</x:v>
+      </x:c>
+      <x:c r="D60" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="E60" s="0">
+        <x:v>800000</x:v>
+      </x:c>
+      <x:c r="F60" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G60" s="0">
+        <x:v>2025.12</x:v>
+      </x:c>
+      <x:c r="H60" s="0">
+        <x:v>3139850323</x:v>
+      </x:c>
+      <x:c r="I60" s="0">
+        <x:v>0.0131</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:9">
+      <x:c r="A61" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B61" s="0">
+        <x:v>58.35</x:v>
+      </x:c>
+      <x:c r="C61" s="0">
+        <x:v>-1.65</x:v>
+      </x:c>
+      <x:c r="D61" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="E61" s="0">
+        <x:v>127172130</x:v>
+      </x:c>
+      <x:c r="F61" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G61" s="0">
+        <x:v>2025.12</x:v>
+      </x:c>
+      <x:c r="H61" s="0">
+        <x:v>8121300519</x:v>
+      </x:c>
+      <x:c r="I61" s="0">
+        <x:v>0.0157</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:9">
+      <x:c r="A62" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B62" s="0">
+        <x:v>42.88</x:v>
+      </x:c>
+      <x:c r="C62" s="0">
+        <x:v>-2.7</x:v>
+      </x:c>
+      <x:c r="D62" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="E62" s="0">
+        <x:v>42625000</x:v>
+      </x:c>
+      <x:c r="F62" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G62" s="0">
+        <x:v>2025.12</x:v>
+      </x:c>
+      <x:c r="H62" s="0">
+        <x:v>4728937463</x:v>
+      </x:c>
+      <x:c r="I62" s="0">
+        <x:v>0.3994</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:9">
+      <x:c r="A63" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B63" s="0">
+        <x:v>92.4</x:v>
+      </x:c>
+      <x:c r="C63" s="0">
+        <x:v>-2.15</x:v>
+      </x:c>
+      <x:c r="D63" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="E63" s="0">
+        <x:v>1486000</x:v>
+      </x:c>
+      <x:c r="F63" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G63" s="0">
+        <x:v>2025.12</x:v>
+      </x:c>
+      <x:c r="H63" s="0">
+        <x:v>2437633702</x:v>
+      </x:c>
+      <x:c r="I63" s="0">
+        <x:v>0.027</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:9">
+      <x:c r="A64" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B64" s="0">
+        <x:v>254.75</x:v>
+      </x:c>
+      <x:c r="C64" s="0">
+        <x:v>11.15</x:v>
+      </x:c>
+      <x:c r="D64" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="E64" s="0">
+        <x:v>768864700</x:v>
+      </x:c>
+      <x:c r="F64" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G64" s="0">
+        <x:v>2025.12</x:v>
+      </x:c>
+      <x:c r="H64" s="0">
+        <x:v>35290767390</x:v>
+      </x:c>
+      <x:c r="I64" s="0">
+        <x:v>0.9648</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:9">
+      <x:c r="A65" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B65" s="0">
+        <x:v>54.35</x:v>
+      </x:c>
+      <x:c r="C65" s="0">
+        <x:v>-0.75</x:v>
+      </x:c>
+      <x:c r="D65" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="E65" s="0">
+        <x:v>15938617</x:v>
+      </x:c>
+      <x:c r="F65" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G65" s="0">
+        <x:v>2025.12</x:v>
+      </x:c>
+      <x:c r="H65" s="0">
+        <x:v>16733157490</x:v>
+      </x:c>
+      <x:c r="I65" s="0">
+        <x:v>0.0422</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:9">
+      <x:c r="A66" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B66" s="0">
+        <x:v>14.5</x:v>
+      </x:c>
+      <x:c r="C66" s="0">
+        <x:v>-0.3</x:v>
+      </x:c>
+      <x:c r="D66" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E66" s="0">
+        <x:v>30438120</x:v>
+      </x:c>
+      <x:c r="F66" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G66" s="0">
+        <x:v>2025.12</x:v>
+      </x:c>
+      <x:c r="H66" s="0">
+        <x:v>3159124121</x:v>
+      </x:c>
+      <x:c r="I66" s="0">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:9">
+      <x:c r="A67" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B67" s="0">
+        <x:v>222.6</x:v>
+      </x:c>
+      <x:c r="C67" s="0">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="D67" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E67" s="0">
+        <x:v>3900000</x:v>
+      </x:c>
+      <x:c r="F67" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G67" s="0">
+        <x:v>2025.12</x:v>
+      </x:c>
+      <x:c r="H67" s="0">
+        <x:v>2159813703</x:v>
+      </x:c>
+      <x:c r="I67" s="0">
+        <x:v>0.0797</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:9">
+      <x:c r="A68" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B68" s="0">
+        <x:v>222.6</x:v>
+      </x:c>
+      <x:c r="C68" s="0">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="D68" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E68" s="0">
+        <x:v>2104908</x:v>
+      </x:c>
+      <x:c r="F68" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G68" s="0">
+        <x:v>2025.12</x:v>
+      </x:c>
+      <x:c r="H68" s="0">
+        <x:v>2159813703</x:v>
+      </x:c>
+      <x:c r="I68" s="0">
+        <x:v>0.043</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:9">
+      <x:c r="A69" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B69" s="0">
+        <x:v>28.64</x:v>
+      </x:c>
+      <x:c r="C69" s="0">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="D69" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E69" s="0">
+        <x:v>3900000</x:v>
+      </x:c>
+      <x:c r="F69" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G69" s="0">
+        <x:v>2025.12</x:v>
+      </x:c>
+      <x:c r="H69" s="0">
+        <x:v>7297855153</x:v>
+      </x:c>
+      <x:c r="I69" s="0">
+        <x:v>0.0236</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" spans="1:9">
+      <x:c r="A70" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B70" s="0">
+        <x:v>5.01</x:v>
+      </x:c>
+      <x:c r="C70" s="0">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="D70" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="E70" s="0">
+        <x:v>496968445</x:v>
+      </x:c>
+      <x:c r="F70" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G70" s="0">
+        <x:v>2025.12</x:v>
+      </x:c>
+      <x:c r="H70" s="0">
+        <x:v>855070469</x:v>
+      </x:c>
+      <x:c r="I70" s="0">
+        <x:v>0.5812</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" spans="1:9">
+      <x:c r="A71" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B71" s="0">
+        <x:v>12.88</x:v>
+      </x:c>
+      <x:c r="C71" s="0">
+        <x:v>-0.02</x:v>
+      </x:c>
+      <x:c r="D71" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="E71" s="0">
+        <x:v>108750000</x:v>
+      </x:c>
+      <x:c r="F71" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G71" s="0">
+        <x:v>2025.12</x:v>
+      </x:c>
+      <x:c r="H71" s="0">
+        <x:v>1982520183</x:v>
+      </x:c>
+      <x:c r="I71" s="0">
+        <x:v>0.0549</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" spans="1:9">
+      <x:c r="A72" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B72" s="0">
+        <x:v>120.8</x:v>
+      </x:c>
+      <x:c r="C72" s="0">
+        <x:v>3.9</x:v>
+      </x:c>
+      <x:c r="D72" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="E72" s="0">
+        <x:v>1605197</x:v>
+      </x:c>
+      <x:c r="F72" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G72" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H72" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I72" s="0">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" spans="1:9">
+      <x:c r="A73" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B73" s="0">
+        <x:v>414.5</x:v>
+      </x:c>
+      <x:c r="C73" s="0">
+        <x:v>-0.5</x:v>
+      </x:c>
+      <x:c r="D73" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="E73" s="0">
+        <x:v>54600000</x:v>
+      </x:c>
+      <x:c r="F73" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G73" s="0">
+        <x:v>2025.12</x:v>
+      </x:c>
+      <x:c r="H73" s="0">
+        <x:v>180444938000</x:v>
+      </x:c>
+      <x:c r="I73" s="0">
+        <x:v>0.0133</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" spans="1:9">
+      <x:c r="A74" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B74" s="0">
+        <x:v>414.5</x:v>
+      </x:c>
+      <x:c r="C74" s="0">
+        <x:v>-0.5</x:v>
+      </x:c>
+      <x:c r="D74" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="E74" s="0">
+        <x:v>111850000</x:v>
+      </x:c>
+      <x:c r="F74" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G74" s="0">
+        <x:v>2025.12</x:v>
+      </x:c>
+      <x:c r="H74" s="0">
+        <x:v>180444938000</x:v>
+      </x:c>
+      <x:c r="I74" s="0">
+        <x:v>0.0273</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" spans="1:9">
+      <x:c r="A75" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B75" s="0">
+        <x:v>48.5</x:v>
+      </x:c>
+      <x:c r="C75" s="0">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="D75" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="E75" s="0">
+        <x:v>803090</x:v>
+      </x:c>
+      <x:c r="F75" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G75" s="0">
+        <x:v>2025.12</x:v>
+      </x:c>
+      <x:c r="H75" s="0">
+        <x:v>4224605448</x:v>
+      </x:c>
+      <x:c r="I75" s="0">
+        <x:v>0.0084</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" spans="1:9">
+      <x:c r="A76" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B76" s="0">
+        <x:v>25.86</x:v>
+      </x:c>
+      <x:c r="C76" s="0">
+        <x:v>-0.68</x:v>
+      </x:c>
+      <x:c r="D76" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="E76" s="0">
+        <x:v>2356546000</x:v>
+      </x:c>
+      <x:c r="F76" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G76" s="0">
+        <x:v>2025.12</x:v>
+      </x:c>
+      <x:c r="H76" s="0">
+        <x:v>7708004248</x:v>
+      </x:c>
+      <x:c r="I76" s="0">
+        <x:v>0.3057</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" spans="1:9">
+      <x:c r="A77" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B77" s="0">
+        <x:v>1120</x:v>
+      </x:c>
+      <x:c r="C77" s="0">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D77" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="E77" s="0">
+        <x:v>875400</x:v>
+      </x:c>
+      <x:c r="F77" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G77" s="0">
+        <x:v>2025.12</x:v>
+      </x:c>
+      <x:c r="H77" s="0">
+        <x:v>1883544167</x:v>
+      </x:c>
+      <x:c r="I77" s="0">
+        <x:v>0.0205</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" spans="1:9">
+      <x:c r="A78" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B78" s="0">
+        <x:v>24.3</x:v>
+      </x:c>
+      <x:c r="C78" s="0">
+        <x:v>-0.2</x:v>
+      </x:c>
+      <x:c r="D78" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="E78" s="0">
+        <x:v>330000000</x:v>
+      </x:c>
+      <x:c r="F78" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G78" s="0">
+        <x:v>2025.12</x:v>
+      </x:c>
+      <x:c r="H78" s="0">
+        <x:v>5287314404</x:v>
+      </x:c>
+      <x:c r="I78" s="0">
+        <x:v>0.0624</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" spans="1:9">
+      <x:c r="A79" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B79" s="0">
+        <x:v>82.05</x:v>
+      </x:c>
+      <x:c r="C79" s="0">
+        <x:v>-0.75</x:v>
+      </x:c>
+      <x:c r="D79" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="E79" s="0">
+        <x:v>11700000</x:v>
+      </x:c>
+      <x:c r="F79" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G79" s="0">
+        <x:v>2025.12</x:v>
+      </x:c>
+      <x:c r="H79" s="0">
+        <x:v>3495512127</x:v>
+      </x:c>
+      <x:c r="I79" s="0">
+        <x:v>0.1705</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" spans="1:9">
+      <x:c r="A80" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B80" s="0">
+        <x:v>7.32</x:v>
+      </x:c>
+      <x:c r="C80" s="0">
+        <x:v>-0.31</x:v>
+      </x:c>
+      <x:c r="D80" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="E80" s="0">
+        <x:v>4000000000</x:v>
+      </x:c>
+      <x:c r="F80" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G80" s="0">
+        <x:v>2025.12</x:v>
+      </x:c>
+      <x:c r="H80" s="0">
+        <x:v>10581001663</x:v>
+      </x:c>
+      <x:c r="I80" s="0">
+        <x:v>0.378</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" spans="1:9">
+      <x:c r="A81" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B81" s="0">
+        <x:v>15.95</x:v>
+      </x:c>
+      <x:c r="C81" s="0">
+        <x:v>-0.02</x:v>
+      </x:c>
+      <x:c r="D81" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="E81" s="0">
+        <x:v>1086598</x:v>
+      </x:c>
+      <x:c r="F81" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G81" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H81" s="0">
+        <x:v>2020891371</x:v>
+      </x:c>
+      <x:c r="I81" s="0">
+        <x:v>0.0274</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" spans="1:9">
+      <x:c r="A82" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B82" s="0">
+        <x:v>14.91</x:v>
+      </x:c>
+      <x:c r="C82" s="0">
+        <x:v>-0.25</x:v>
+      </x:c>
+      <x:c r="D82" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E82" s="0">
+        <x:v>216000000</x:v>
+      </x:c>
+      <x:c r="F82" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G82" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H82" s="0">
+        <x:v>3025063909</x:v>
+      </x:c>
+      <x:c r="I82" s="0">
+        <x:v>0.0714</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" spans="1:9">
+      <x:c r="A83" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B83" s="0">
+        <x:v>48.5</x:v>
+      </x:c>
+      <x:c r="C83" s="0">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="D83" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E83" s="0">
+        <x:v>7292916</x:v>
+      </x:c>
+      <x:c r="F83" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G83" s="0">
+        <x:v>2025.12</x:v>
+      </x:c>
+      <x:c r="H83" s="0">
+        <x:v>4224605448</x:v>
+      </x:c>
+      <x:c r="I83" s="0">
+        <x:v>0.0758</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" spans="1:9">
+      <x:c r="A84" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B84" s="0">
+        <x:v>25.16</x:v>
+      </x:c>
+      <x:c r="C84" s="0">
+        <x:v>-0.82</x:v>
+      </x:c>
+      <x:c r="D84" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="E84" s="0">
+        <x:v>250000</x:v>
+      </x:c>
+      <x:c r="F84" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G84" s="0">
+        <x:v>2025.12</x:v>
+      </x:c>
+      <x:c r="H84" s="0">
+        <x:v>448686813</x:v>
+      </x:c>
+      <x:c r="I84" s="0">
+        <x:v>0.0006</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" spans="1:9">
+      <x:c r="A85" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B85" s="0">
+        <x:v>54.35</x:v>
+      </x:c>
+      <x:c r="C85" s="0">
+        <x:v>-0.75</x:v>
+      </x:c>
+      <x:c r="D85" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="E85" s="0">
+        <x:v>36900000</x:v>
+      </x:c>
+      <x:c r="F85" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G85" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H85" s="0">
+        <x:v>10597063406</x:v>
+      </x:c>
+      <x:c r="I85" s="0">
+        <x:v>0.1527</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" spans="1:9">
+      <x:c r="A86" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B86" s="0">
+        <x:v>59.85</x:v>
+      </x:c>
+      <x:c r="C86" s="0">
+        <x:v>-1.15</x:v>
+      </x:c>
+      <x:c r="D86" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="E86" s="0">
+        <x:v>3800000</x:v>
+      </x:c>
+      <x:c r="F86" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G86" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H86" s="0">
+        <x:v>832031190</x:v>
+      </x:c>
+      <x:c r="I86" s="0">
+        <x:v>0.2002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" spans="1:9">
+      <x:c r="A87" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B87" s="0">
+        <x:v>5.01</x:v>
+      </x:c>
+      <x:c r="C87" s="0">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="D87" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="E87" s="0">
+        <x:v>2100000</x:v>
+      </x:c>
+      <x:c r="F87" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G87" s="0">
+        <x:v>2025.12</x:v>
+      </x:c>
+      <x:c r="H87" s="0">
+        <x:v>855070469</x:v>
+      </x:c>
+      <x:c r="I87" s="0">
+        <x:v>0.1076</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" spans="1:9">
+      <x:c r="A88" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B88" s="0">
+        <x:v>48.5</x:v>
+      </x:c>
+      <x:c r="C88" s="0">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="D88" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="E88" s="0">
+        <x:v>22928077</x:v>
+      </x:c>
+      <x:c r="F88" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G88" s="0">
+        <x:v>2025.12</x:v>
+      </x:c>
+      <x:c r="H88" s="0">
+        <x:v>4224605448</x:v>
+      </x:c>
+      <x:c r="I88" s="0">
+        <x:v>0.2378</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" spans="1:9">
+      <x:c r="A89" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B89" s="0">
+        <x:v>28.8</x:v>
+      </x:c>
+      <x:c r="C89" s="0">
+        <x:v>-0.04</x:v>
+      </x:c>
+      <x:c r="D89" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="E89" s="0">
+        <x:v>547462013</x:v>
+      </x:c>
+      <x:c r="F89" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G89" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H89" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I89" s="0">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" spans="1:9">
+      <x:c r="A90" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B90" s="0">
+        <x:v>28.8</x:v>
+      </x:c>
+      <x:c r="C90" s="0">
+        <x:v>-0.04</x:v>
+      </x:c>
+      <x:c r="D90" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="E90" s="0">
+        <x:v>10567948</x:v>
+      </x:c>
+      <x:c r="F90" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G90" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H90" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I90" s="0">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" spans="1:9">
+      <x:c r="A91" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B91" s="0">
+        <x:v>82.05</x:v>
+      </x:c>
+      <x:c r="C91" s="0">
+        <x:v>-0.75</x:v>
+      </x:c>
+      <x:c r="D91" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="E91" s="0">
+        <x:v>8300000</x:v>
+      </x:c>
+      <x:c r="F91" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G91" s="0">
+        <x:v>2025.12</x:v>
+      </x:c>
+      <x:c r="H91" s="0">
+        <x:v>3495512127</x:v>
+      </x:c>
+      <x:c r="I91" s="0">
+        <x:v>0.1228</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" spans="1:9">
+      <x:c r="A92" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B92" s="0">
+        <x:v>49.2</x:v>
+      </x:c>
+      <x:c r="C92" s="0">
+        <x:v>-0.14</x:v>
+      </x:c>
+      <x:c r="D92" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="E92" s="0">
+        <x:v>3000000</x:v>
+      </x:c>
+      <x:c r="F92" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G92" s="0">
+        <x:v>2025.12</x:v>
+      </x:c>
+      <x:c r="H92" s="0">
+        <x:v>20597209000</x:v>
+      </x:c>
+      <x:c r="I92" s="0">
+        <x:v>0.0064</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" spans="1:9">
+      <x:c r="A93" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B93" s="0">
+        <x:v>33.34</x:v>
+      </x:c>
+      <x:c r="C93" s="0">
+        <x:v>0.74</x:v>
+      </x:c>
+      <x:c r="D93" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="E93" s="0">
+        <x:v>26640000</x:v>
+      </x:c>
+      <x:c r="F93" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G93" s="0">
+        <x:v>2025.12</x:v>
+      </x:c>
+      <x:c r="H93" s="0">
+        <x:v>3277373640</x:v>
+      </x:c>
+      <x:c r="I93" s="0">
+        <x:v>0.356</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" spans="1:9">
+      <x:c r="A94" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B94" s="0">
+        <x:v>5.35</x:v>
+      </x:c>
+      <x:c r="C94" s="0">
+        <x:v>-0.18</x:v>
+      </x:c>
+      <x:c r="D94" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E94" s="0">
+        <x:v>13107198</x:v>
+      </x:c>
+      <x:c r="F94" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G94" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H94" s="0">
+        <x:v>1627872951</x:v>
+      </x:c>
+      <x:c r="I94" s="0">
+        <x:v>0.0081</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" spans="1:9">
+      <x:c r="A95" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B95" s="0">
+        <x:v>82.05</x:v>
+      </x:c>
+      <x:c r="C95" s="0">
+        <x:v>-0.75</x:v>
+      </x:c>
+      <x:c r="D95" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="E95" s="0">
+        <x:v>237500000</x:v>
+      </x:c>
+      <x:c r="F95" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G95" s="0">
+        <x:v>2025.12</x:v>
+      </x:c>
+      <x:c r="H95" s="0">
+        <x:v>3495512127</x:v>
+      </x:c>
+      <x:c r="I95" s="0">
+        <x:v>0.0679</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" spans="1:9">
+      <x:c r="A96" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B96" s="0">
+        <x:v>58.35</x:v>
+      </x:c>
+      <x:c r="C96" s="0">
+        <x:v>-1.65</x:v>
+      </x:c>
+      <x:c r="D96" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="E96" s="0">
+        <x:v>147892538</x:v>
+      </x:c>
+      <x:c r="F96" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G96" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H96" s="0">
+        <x:v>7257990064</x:v>
+      </x:c>
+      <x:c r="I96" s="0">
+        <x:v>0.0204</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" spans="1:9">
+      <x:c r="A97" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B97" s="0">
+        <x:v>49.08</x:v>
+      </x:c>
+      <x:c r="C97" s="0">
+        <x:v>4.46</x:v>
+      </x:c>
+      <x:c r="D97" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="E97" s="0">
+        <x:v>988848</x:v>
+      </x:c>
+      <x:c r="F97" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G97" s="0">
+        <x:v>2025.12</x:v>
+      </x:c>
+      <x:c r="H97" s="0">
+        <x:v>12999679000</x:v>
+      </x:c>
+      <x:c r="I97" s="0">
+        <x:v>0.0033</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" spans="1:9">
+      <x:c r="A98" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B98" s="0">
+        <x:v>54.35</x:v>
+      </x:c>
+      <x:c r="C98" s="0">
+        <x:v>-0.75</x:v>
+      </x:c>
+      <x:c r="D98" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="E98" s="0">
+        <x:v>47300000</x:v>
+      </x:c>
+      <x:c r="F98" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G98" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H98" s="0">
+        <x:v>10597063406</x:v>
+      </x:c>
+      <x:c r="I98" s="0">
+        <x:v>0.2309</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" spans="1:9">
+      <x:c r="A99" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B99" s="0">
+        <x:v>4.26</x:v>
+      </x:c>
+      <x:c r="C99" s="0">
+        <x:v>-0.1</x:v>
+      </x:c>
+      <x:c r="D99" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="E99" s="0">
+        <x:v>758600</x:v>
+      </x:c>
+      <x:c r="F99" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G99" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H99" s="0">
+        <x:v>1960468575</x:v>
+      </x:c>
+      <x:c r="I99" s="0">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" spans="1:9">
+      <x:c r="A100" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B100" s="0">
+        <x:v>4.26</x:v>
+      </x:c>
+      <x:c r="C100" s="0">
+        <x:v>-0.1</x:v>
+      </x:c>
+      <x:c r="D100" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="E100" s="0">
+        <x:v>758600</x:v>
+      </x:c>
+      <x:c r="F100" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="G100" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H100" s="0">
+        <x:v>1960468575</x:v>
+      </x:c>
+      <x:c r="I100" s="0">
+        <x:v>0.0004</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" spans="1:9">
+      <x:c r="A101" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B101" s="0">
+        <x:v>1120</x:v>
+      </x:c>
+      <x:c r="C101" s="0">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D101" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="E101" s="0">
+        <x:v>576665</x:v>
+      </x:c>
+      <x:c r="F101" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G101" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H101" s="0">
+        <x:v>1586603352</x:v>
+      </x:c>
+      <x:c r="I101" s="0">
+        <x:v>0.0159</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" spans="1:9">
+      <x:c r="A102" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="B102" s="0">
+        <x:v>81.4</x:v>
+      </x:c>
+      <x:c r="C102" s="0">
+        <x:v>-2.15</x:v>
+      </x:c>
+      <x:c r="D102" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="E102" s="0">
+        <x:v>8000000</x:v>
+      </x:c>
+      <x:c r="F102" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G102" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H102" s="0">
+        <x:v>20999579110</x:v>
+      </x:c>
+      <x:c r="I102" s="0">
+        <x:v>0.0166</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" spans="1:9">
+      <x:c r="A103" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B103" s="0">
+        <x:v>92.4</x:v>
+      </x:c>
+      <x:c r="C103" s="0">
+        <x:v>-2.15</x:v>
+      </x:c>
+      <x:c r="D103" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="E103" s="0">
+        <x:v>850000</x:v>
+      </x:c>
+      <x:c r="F103" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G103" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H103" s="0">
+        <x:v>1781510191</x:v>
+      </x:c>
+      <x:c r="I103" s="0">
+        <x:v>0.0208</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" spans="1:9">
+      <x:c r="A104" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B104" s="0">
+        <x:v>15.95</x:v>
+      </x:c>
+      <x:c r="C104" s="0">
+        <x:v>-0.02</x:v>
+      </x:c>
+      <x:c r="D104" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="E104" s="0">
+        <x:v>10149200</x:v>
+      </x:c>
+      <x:c r="F104" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G104" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H104" s="0">
+        <x:v>2020891371</x:v>
+      </x:c>
+      <x:c r="I104" s="0">
+        <x:v>0.2601</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" spans="1:9">
+      <x:c r="A105" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B105" s="0">
+        <x:v>120.8</x:v>
+      </x:c>
+      <x:c r="C105" s="0">
+        <x:v>3.9</x:v>
+      </x:c>
+      <x:c r="D105" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="E105" s="0">
+        <x:v>10500000</x:v>
+      </x:c>
+      <x:c r="F105" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G105" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H105" s="0">
+        <x:v>1742315226</x:v>
+      </x:c>
+      <x:c r="I105" s="0">
+        <x:v>0.3121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" spans="1:9">
+      <x:c r="A106" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B106" s="0">
+        <x:v>92.4</x:v>
+      </x:c>
+      <x:c r="C106" s="0">
+        <x:v>-2.15</x:v>
+      </x:c>
+      <x:c r="D106" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="E106" s="0">
+        <x:v>366956541</x:v>
+      </x:c>
+      <x:c r="F106" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G106" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H106" s="0">
+        <x:v>1781510191</x:v>
+      </x:c>
+      <x:c r="I106" s="0">
+        <x:v>0.206</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" spans="1:9">
+      <x:c r="A107" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B107" s="0">
+        <x:v>58.35</x:v>
+      </x:c>
+      <x:c r="C107" s="0">
+        <x:v>-1.65</x:v>
+      </x:c>
+      <x:c r="D107" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E107" s="0">
+        <x:v>61158155</x:v>
+      </x:c>
+      <x:c r="F107" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G107" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H107" s="0">
+        <x:v>7257990064</x:v>
+      </x:c>
+      <x:c r="I107" s="0">
+        <x:v>0.0084</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" spans="1:9">
+      <x:c r="A108" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="B108" s="0">
+        <x:v>104.8</x:v>
+      </x:c>
+      <x:c r="C108" s="0">
+        <x:v>-1.1</x:v>
+      </x:c>
+      <x:c r="D108" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E108" s="0">
+        <x:v>1000000</x:v>
+      </x:c>
+      <x:c r="F108" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G108" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H108" s="0">
+        <x:v>1688731509</x:v>
+      </x:c>
+      <x:c r="I108" s="0">
+        <x:v>0.0307</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" spans="1:9">
+      <x:c r="A109" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="B109" s="0">
+        <x:v>104.8</x:v>
+      </x:c>
+      <x:c r="C109" s="0">
+        <x:v>-1.1</x:v>
+      </x:c>
+      <x:c r="D109" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E109" s="0">
+        <x:v>1050000</x:v>
+      </x:c>
+      <x:c r="F109" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G109" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H109" s="0">
+        <x:v>1688731509</x:v>
+      </x:c>
+      <x:c r="I109" s="0">
+        <x:v>0.0271</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" spans="1:9">
+      <x:c r="A110" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B110" s="0">
+        <x:v>42.28</x:v>
+      </x:c>
+      <x:c r="C110" s="0">
+        <x:v>-1.36</x:v>
+      </x:c>
+      <x:c r="D110" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="E110" s="0">
+        <x:v>109053804</x:v>
+      </x:c>
+      <x:c r="F110" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G110" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H110" s="0">
+        <x:v>1942491524</x:v>
+      </x:c>
+      <x:c r="I110" s="0">
+        <x:v>0.0561</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" spans="1:9">
+      <x:c r="A111" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="B111" s="0">
+        <x:v>10.3</x:v>
+      </x:c>
+      <x:c r="C111" s="0">
+        <x:v>-0.34</x:v>
+      </x:c>
+      <x:c r="D111" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="E111" s="0">
+        <x:v>62315119</x:v>
+      </x:c>
+      <x:c r="F111" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G111" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H111" s="0">
+        <x:v>12026414029</x:v>
+      </x:c>
+      <x:c r="I111" s="0">
+        <x:v>0.2257</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" spans="1:9">
+      <x:c r="A112" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B112" s="0">
+        <x:v>222.6</x:v>
+      </x:c>
+      <x:c r="C112" s="0">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="D112" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="E112" s="0">
+        <x:v>896400</x:v>
+      </x:c>
+      <x:c r="F112" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G112" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H112" s="0">
+        <x:v>1364716456</x:v>
+      </x:c>
+      <x:c r="I112" s="0">
+        <x:v>0.0285</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" spans="1:9">
+      <x:c r="A113" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="B113" s="0">
+        <x:v>308.75</x:v>
+      </x:c>
+      <x:c r="C113" s="0">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D113" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="E113" s="0">
+        <x:v>3370000</x:v>
+      </x:c>
+      <x:c r="F113" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G113" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H113" s="0">
+        <x:v>1865697176</x:v>
+      </x:c>
+      <x:c r="I113" s="0">
+        <x:v>0.0785</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" spans="1:9">
+      <x:c r="A114" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B114" s="0">
+        <x:v>49.2</x:v>
+      </x:c>
+      <x:c r="C114" s="0">
+        <x:v>-0.14</x:v>
+      </x:c>
+      <x:c r="D114" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="E114" s="0">
+        <x:v>750561215</x:v>
+      </x:c>
+      <x:c r="F114" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G114" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H114" s="0">
+        <x:v>16507905000</x:v>
+      </x:c>
+      <x:c r="I114" s="0">
+        <x:v>0.0455</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" spans="1:9">
+      <x:c r="A115" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="B115" s="0">
+        <x:v>81.4</x:v>
+      </x:c>
+      <x:c r="C115" s="0">
+        <x:v>-2.15</x:v>
+      </x:c>
+      <x:c r="D115" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="E115" s="0">
+        <x:v>20000000</x:v>
+      </x:c>
+      <x:c r="F115" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G115" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H115" s="0">
+        <x:v>20999579110</x:v>
+      </x:c>
+      <x:c r="I115" s="0">
+        <x:v>0.0413</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" spans="1:9">
+      <x:c r="A116" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B116" s="0">
+        <x:v>34.56</x:v>
+      </x:c>
+      <x:c r="C116" s="0">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="D116" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="E116" s="0">
+        <x:v>750000000</x:v>
+      </x:c>
+      <x:c r="F116" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G116" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H116" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I116" s="0">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" spans="1:9">
+      <x:c r="A117" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B117" s="0">
+        <x:v>54.35</x:v>
+      </x:c>
+      <x:c r="C117" s="0">
+        <x:v>-0.75</x:v>
+      </x:c>
+      <x:c r="D117" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="E117" s="0">
+        <x:v>111232418</x:v>
+      </x:c>
+      <x:c r="F117" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G117" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H117" s="0">
+        <x:v>10597063406</x:v>
+      </x:c>
+      <x:c r="I117" s="0">
+        <x:v>0.4554</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" spans="1:9">
+      <x:c r="A118" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B118" s="0">
+        <x:v>34.4</x:v>
+      </x:c>
+      <x:c r="C118" s="0">
+        <x:v>-1.12</x:v>
+      </x:c>
+      <x:c r="D118" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="E118" s="0">
+        <x:v>51384996</x:v>
+      </x:c>
+      <x:c r="F118" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G118" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H118" s="0">
+        <x:v>11899043692</x:v>
+      </x:c>
+      <x:c r="I118" s="0">
+        <x:v>0.1873</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" spans="1:9">
+      <x:c r="A119" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B119" s="0">
+        <x:v>34.4</x:v>
+      </x:c>
+      <x:c r="C119" s="0">
+        <x:v>-1.12</x:v>
+      </x:c>
+      <x:c r="D119" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="E119" s="0">
+        <x:v>3602451</x:v>
+      </x:c>
+      <x:c r="F119" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G119" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H119" s="0">
+        <x:v>11899043692</x:v>
+      </x:c>
+      <x:c r="I119" s="0">
+        <x:v>0.0131</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" spans="1:9">
+      <x:c r="A120" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B120" s="0">
+        <x:v>34.4</x:v>
+      </x:c>
+      <x:c r="C120" s="0">
+        <x:v>-1.12</x:v>
+      </x:c>
+      <x:c r="D120" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="E120" s="0">
+        <x:v>24226465</x:v>
+      </x:c>
+      <x:c r="F120" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G120" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H120" s="0">
+        <x:v>11899043692</x:v>
+      </x:c>
+      <x:c r="I120" s="0">
+        <x:v>0.0883</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" spans="1:9">
+      <x:c r="A121" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B121" s="0">
+        <x:v>48.5</x:v>
+      </x:c>
+      <x:c r="C121" s="0">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="D121" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="E121" s="0">
+        <x:v>12900000</x:v>
+      </x:c>
+      <x:c r="F121" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G121" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H121" s="0">
+        <x:v>2467243928</x:v>
+      </x:c>
+      <x:c r="I121" s="0">
+        <x:v>0.0052</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" spans="1:9">
+      <x:c r="A122" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B122" s="0">
+        <x:v>254.75</x:v>
+      </x:c>
+      <x:c r="C122" s="0">
+        <x:v>11.15</x:v>
+      </x:c>
+      <x:c r="D122" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="E122" s="0">
+        <x:v>53250000</x:v>
+      </x:c>
+      <x:c r="F122" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G122" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H122" s="0">
+        <x:v>24073631758</x:v>
+      </x:c>
+      <x:c r="I122" s="0">
+        <x:v>0.115</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" spans="1:9">
+      <x:c r="A123" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B123" s="0">
+        <x:v>28.8</x:v>
+      </x:c>
+      <x:c r="C123" s="0">
+        <x:v>-0.04</x:v>
+      </x:c>
+      <x:c r="D123" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="E123" s="0">
+        <x:v>6860140</x:v>
+      </x:c>
+      <x:c r="F123" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G123" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H123" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I123" s="0">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" spans="1:9">
+      <x:c r="A124" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B124" s="0">
+        <x:v>82.05</x:v>
+      </x:c>
+      <x:c r="C124" s="0">
+        <x:v>-0.75</x:v>
+      </x:c>
+      <x:c r="D124" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="E124" s="0">
+        <x:v>230000000</x:v>
+      </x:c>
+      <x:c r="F124" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G124" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H124" s="0">
+        <x:v>2941310980</x:v>
+      </x:c>
+      <x:c r="I124" s="0">
+        <x:v>0.0782</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" spans="1:9">
+      <x:c r="A125" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="B125" s="0">
+        <x:v>308.75</x:v>
+      </x:c>
+      <x:c r="C125" s="0">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D125" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="E125" s="0">
+        <x:v>4700000</x:v>
+      </x:c>
+      <x:c r="F125" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G125" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H125" s="0">
+        <x:v>1865697176</x:v>
+      </x:c>
+      <x:c r="I125" s="0">
+        <x:v>0.1092</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" spans="1:9">
+      <x:c r="A126" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B126" s="0">
+        <x:v>28.8</x:v>
+      </x:c>
+      <x:c r="C126" s="0">
+        <x:v>-0.04</x:v>
+      </x:c>
+      <x:c r="D126" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="E126" s="0">
+        <x:v>256000000</x:v>
+      </x:c>
+      <x:c r="F126" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G126" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H126" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I126" s="0">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" spans="1:9">
+      <x:c r="A127" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B127" s="0">
+        <x:v>34.4</x:v>
+      </x:c>
+      <x:c r="C127" s="0">
+        <x:v>-1.12</x:v>
+      </x:c>
+      <x:c r="D127" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="E127" s="0">
+        <x:v>10724896</x:v>
+      </x:c>
+      <x:c r="F127" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G127" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H127" s="0">
+        <x:v>11899043692</x:v>
+      </x:c>
+      <x:c r="I127" s="0">
+        <x:v>0.039</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" spans="1:9">
+      <x:c r="A128" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B128" s="0">
+        <x:v>24.16</x:v>
+      </x:c>
+      <x:c r="C128" s="0">
+        <x:v>-0.56</x:v>
+      </x:c>
+      <x:c r="D128" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="E128" s="0">
+        <x:v>31000000</x:v>
+      </x:c>
+      <x:c r="F128" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G128" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H128" s="0">
+        <x:v>813967617</x:v>
+      </x:c>
+      <x:c r="I128" s="0">
+        <x:v>0.0381</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" spans="1:9">
+      <x:c r="A129" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B129" s="0">
+        <x:v>40.76</x:v>
+      </x:c>
+      <x:c r="C129" s="0">
+        <x:v>0.44</x:v>
+      </x:c>
+      <x:c r="D129" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="E129" s="0">
+        <x:v>13500000</x:v>
+      </x:c>
+      <x:c r="F129" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G129" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H129" s="0">
+        <x:v>6483809984</x:v>
+      </x:c>
+      <x:c r="I129" s="0">
+        <x:v>0.09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" spans="1:9">
+      <x:c r="A130" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B130" s="0">
+        <x:v>42.28</x:v>
+      </x:c>
+      <x:c r="C130" s="0">
+        <x:v>-1.36</x:v>
+      </x:c>
+      <x:c r="D130" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="E130" s="0">
+        <x:v>29886357</x:v>
+      </x:c>
+      <x:c r="F130" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G130" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H130" s="0">
+        <x:v>1942491524</x:v>
+      </x:c>
+      <x:c r="I130" s="0">
+        <x:v>0.0154</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" spans="1:9">
+      <x:c r="A131" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B131" s="0">
+        <x:v>414.5</x:v>
+      </x:c>
+      <x:c r="C131" s="0">
+        <x:v>-0.5</x:v>
+      </x:c>
+      <x:c r="D131" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="E131" s="0">
+        <x:v>171000000</x:v>
+      </x:c>
+      <x:c r="F131" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G131" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H131" s="0">
+        <x:v>130147715000</x:v>
+      </x:c>
+      <x:c r="I131" s="0">
+        <x:v>0.0568</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" spans="1:9">
+      <x:c r="A132" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B132" s="0">
+        <x:v>120.8</x:v>
+      </x:c>
+      <x:c r="C132" s="0">
+        <x:v>3.9</x:v>
+      </x:c>
+      <x:c r="D132" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="E132" s="0">
+        <x:v>1890000</x:v>
+      </x:c>
+      <x:c r="F132" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G132" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H132" s="0">
+        <x:v>1742315226</x:v>
+      </x:c>
+      <x:c r="I132" s="0">
+        <x:v>0.0549</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" spans="1:9">
+      <x:c r="A133" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="B133" s="0">
+        <x:v>13.4</x:v>
+      </x:c>
+      <x:c r="C133" s="0">
+        <x:v>-0.51</x:v>
+      </x:c>
+      <x:c r="D133" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="E133" s="0">
+        <x:v>892825</x:v>
+      </x:c>
+      <x:c r="F133" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G133" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H133" s="0">
+        <x:v>3015442704</x:v>
+      </x:c>
+      <x:c r="I133" s="0">
+        <x:v>0.0128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" spans="1:9">
+      <x:c r="A134" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B134" s="0">
+        <x:v>48.5</x:v>
+      </x:c>
+      <x:c r="C134" s="0">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="D134" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="E134" s="0">
+        <x:v>361176</x:v>
+      </x:c>
+      <x:c r="F134" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G134" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H134" s="0">
+        <x:v>2467243928</x:v>
+      </x:c>
+      <x:c r="I134" s="0">
+        <x:v>0.0063</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" spans="1:9">
+      <x:c r="A135" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="B135" s="0">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C135" s="0">
+        <x:v>-0.34</x:v>
+      </x:c>
+      <x:c r="D135" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="E135" s="0">
+        <x:v>1060000</x:v>
+      </x:c>
+      <x:c r="F135" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G135" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H135" s="0">
+        <x:v>1194839266</x:v>
+      </x:c>
+      <x:c r="I135" s="0">
+        <x:v>0.0384</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" spans="1:9">
+      <x:c r="A136" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="B136" s="0">
+        <x:v>51.75</x:v>
+      </x:c>
+      <x:c r="C136" s="0">
+        <x:v>-0.75</x:v>
+      </x:c>
+      <x:c r="D136" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="E136" s="0">
+        <x:v>259417800</x:v>
+      </x:c>
+      <x:c r="F136" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G136" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H136" s="0">
+        <x:v>2741117556</x:v>
+      </x:c>
+      <x:c r="I136" s="0">
+        <x:v>0.0946</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" spans="1:9">
+      <x:c r="A137" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B137" s="0">
+        <x:v>59.85</x:v>
+      </x:c>
+      <x:c r="C137" s="0">
+        <x:v>-1.15</x:v>
+      </x:c>
+      <x:c r="D137" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="E137" s="0">
+        <x:v>523788</x:v>
+      </x:c>
+      <x:c r="F137" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G137" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H137" s="0">
+        <x:v>832031190</x:v>
+      </x:c>
+      <x:c r="I137" s="0">
+        <x:v>0.0272</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138" spans="1:9">
+      <x:c r="A138" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B138" s="0">
+        <x:v>59.85</x:v>
+      </x:c>
+      <x:c r="C138" s="0">
+        <x:v>-1.15</x:v>
+      </x:c>
+      <x:c r="D138" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="E138" s="0">
+        <x:v>1415270</x:v>
+      </x:c>
+      <x:c r="F138" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G138" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H138" s="0">
+        <x:v>832031190</x:v>
+      </x:c>
+      <x:c r="I138" s="0">
+        <x:v>0.0736</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139" spans="1:9">
+      <x:c r="A139" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="B139" s="0">
+        <x:v>81.4</x:v>
+      </x:c>
+      <x:c r="C139" s="0">
+        <x:v>-2.15</x:v>
+      </x:c>
+      <x:c r="D139" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="E139" s="0">
+        <x:v>25000000</x:v>
+      </x:c>
+      <x:c r="F139" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G139" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H139" s="0">
+        <x:v>20999579110</x:v>
+      </x:c>
+      <x:c r="I139" s="0">
+        <x:v>0.0515</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140" spans="1:9">
+      <x:c r="A140" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B140" s="0">
+        <x:v>5.35</x:v>
+      </x:c>
+      <x:c r="C140" s="0">
+        <x:v>-0.18</x:v>
+      </x:c>
+      <x:c r="D140" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="E140" s="0">
+        <x:v>25000</x:v>
+      </x:c>
+      <x:c r="F140" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G140" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H140" s="0">
+        <x:v>1627872951</x:v>
+      </x:c>
+      <x:c r="I140" s="0">
+        <x:v>0.0007</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141" spans="1:9">
+      <x:c r="A141" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="B141" s="0">
+        <x:v>19.82</x:v>
+      </x:c>
+      <x:c r="C141" s="0">
+        <x:v>-0.38</x:v>
+      </x:c>
+      <x:c r="D141" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="E141" s="0">
+        <x:v>1500000</x:v>
+      </x:c>
+      <x:c r="F141" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G141" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H141" s="0">
+        <x:v>774677961</x:v>
+      </x:c>
+      <x:c r="I141" s="0">
+        <x:v>0.0019</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142" spans="1:9">
+      <x:c r="A142" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B142" s="0">
+        <x:v>7.32</x:v>
+      </x:c>
+      <x:c r="C142" s="0">
+        <x:v>-0.31</x:v>
+      </x:c>
+      <x:c r="D142" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="E142" s="0">
+        <x:v>13833310</x:v>
+      </x:c>
+      <x:c r="F142" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G142" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H142" s="0">
+        <x:v>9028523851</x:v>
+      </x:c>
+      <x:c r="I142" s="0">
+        <x:v>0.0776</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143" spans="1:9">
+      <x:c r="A143" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B143" s="0">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C143" s="0">
+        <x:v>-1.8</x:v>
+      </x:c>
+      <x:c r="D143" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="E143" s="0">
+        <x:v>3419000</x:v>
+      </x:c>
+      <x:c r="F143" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G143" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H143" s="0">
+        <x:v>3895315496</x:v>
+      </x:c>
+      <x:c r="I143" s="0">
+        <x:v>0.0379</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144" spans="1:9">
+      <x:c r="A144" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="B144" s="0">
+        <x:v>308.75</x:v>
+      </x:c>
+      <x:c r="C144" s="0">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D144" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="E144" s="0">
+        <x:v>3700000</x:v>
+      </x:c>
+      <x:c r="F144" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G144" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H144" s="0">
+        <x:v>1865697176</x:v>
+      </x:c>
+      <x:c r="I144" s="0">
+        <x:v>0.0857</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145" spans="1:9">
+      <x:c r="A145" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B145" s="0">
+        <x:v>40.76</x:v>
+      </x:c>
+      <x:c r="C145" s="0">
+        <x:v>0.44</x:v>
+      </x:c>
+      <x:c r="D145" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="E145" s="0">
+        <x:v>16000000</x:v>
+      </x:c>
+      <x:c r="F145" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G145" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H145" s="0">
+        <x:v>6483809984</x:v>
+      </x:c>
+      <x:c r="I145" s="0">
+        <x:v>0.1067</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146" spans="1:9">
+      <x:c r="A146" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B146" s="0">
+        <x:v>48.5</x:v>
+      </x:c>
+      <x:c r="C146" s="0">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="D146" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="E146" s="0">
+        <x:v>906840</x:v>
+      </x:c>
+      <x:c r="F146" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G146" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H146" s="0">
+        <x:v>2467243928</x:v>
+      </x:c>
+      <x:c r="I146" s="0">
+        <x:v>0.0159</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147" spans="1:9">
+      <x:c r="A147" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B147" s="0">
+        <x:v>3.3</x:v>
+      </x:c>
+      <x:c r="C147" s="0">
+        <x:v>-0.1</x:v>
+      </x:c>
+      <x:c r="D147" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="E147" s="0">
+        <x:v>895039950</x:v>
+      </x:c>
+      <x:c r="F147" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G147" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H147" s="0">
+        <x:v>7382591324</x:v>
+      </x:c>
+      <x:c r="I147" s="0">
+        <x:v>0.1212</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148" spans="1:9">
+      <x:c r="A148" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="B148" s="0">
+        <x:v>51.75</x:v>
+      </x:c>
+      <x:c r="C148" s="0">
+        <x:v>-0.75</x:v>
+      </x:c>
+      <x:c r="D148" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="E148" s="0">
+        <x:v>575933040</x:v>
+      </x:c>
+      <x:c r="F148" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G148" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H148" s="0">
+        <x:v>2741117556</x:v>
+      </x:c>
+      <x:c r="I148" s="0">
+        <x:v>0.2101</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149" spans="1:9">
+      <x:c r="A149" s="0" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="B149" s="0">
+        <x:v>12.49</x:v>
+      </x:c>
+      <x:c r="C149" s="0">
+        <x:v>0.24</x:v>
+      </x:c>
+      <x:c r="D149" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="E149" s="0">
+        <x:v>559000</x:v>
+      </x:c>
+      <x:c r="F149" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G149" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H149" s="0">
+        <x:v>2865374550</x:v>
+      </x:c>
+      <x:c r="I149" s="0">
+        <x:v>0.0084</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150" spans="1:9">
+      <x:c r="A150" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B150" s="0">
+        <x:v>49.2</x:v>
+      </x:c>
+      <x:c r="C150" s="0">
+        <x:v>-0.14</x:v>
+      </x:c>
+      <x:c r="D150" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="E150" s="0">
+        <x:v>8900056</x:v>
+      </x:c>
+      <x:c r="F150" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G150" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H150" s="0">
+        <x:v>16507905000</x:v>
+      </x:c>
+      <x:c r="I150" s="0">
+        <x:v>0.0233</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151" spans="1:9">
+      <x:c r="A151" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B151" s="0">
+        <x:v>254.75</x:v>
+      </x:c>
+      <x:c r="C151" s="0">
+        <x:v>11.15</x:v>
+      </x:c>
+      <x:c r="D151" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="E151" s="0">
+        <x:v>164306000</x:v>
+      </x:c>
+      <x:c r="F151" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G151" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H151" s="0">
+        <x:v>24073631758</x:v>
+      </x:c>
+      <x:c r="I151" s="0">
+        <x:v>0.2943</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152" spans="1:9">
+      <x:c r="A152" s="0" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="B152" s="0">
+        <x:v>53.8</x:v>
+      </x:c>
+      <x:c r="C152" s="0">
+        <x:v>-3</x:v>
+      </x:c>
+      <x:c r="D152" s="0" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="E152" s="0">
+        <x:v>275000</x:v>
+      </x:c>
+      <x:c r="F152" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G152" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H152" s="0">
+        <x:v>580678850</x:v>
+      </x:c>
+      <x:c r="I152" s="0">
+        <x:v>0.0204</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153" spans="1:9">
+      <x:c r="A153" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="B153" s="0">
+        <x:v>51.75</x:v>
+      </x:c>
+      <x:c r="C153" s="0">
+        <x:v>-0.75</x:v>
+      </x:c>
+      <x:c r="D153" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="E153" s="0">
+        <x:v>231651480</x:v>
+      </x:c>
+      <x:c r="F153" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G153" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H153" s="0">
+        <x:v>2741117556</x:v>
+      </x:c>
+      <x:c r="I153" s="0">
+        <x:v>0.0845</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154" spans="1:9">
+      <x:c r="A154" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B154" s="0">
+        <x:v>14.91</x:v>
+      </x:c>
+      <x:c r="C154" s="0">
+        <x:v>-0.25</x:v>
+      </x:c>
+      <x:c r="D154" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="E154" s="0">
+        <x:v>31860000</x:v>
+      </x:c>
+      <x:c r="F154" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G154" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H154" s="0">
+        <x:v>3025063909</x:v>
+      </x:c>
+      <x:c r="I154" s="0">
+        <x:v>0.4539</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155" spans="1:9">
+      <x:c r="A155" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B155" s="0">
+        <x:v>92.4</x:v>
+      </x:c>
+      <x:c r="C155" s="0">
+        <x:v>-2.15</x:v>
+      </x:c>
+      <x:c r="D155" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="E155" s="0">
+        <x:v>41650000</x:v>
+      </x:c>
+      <x:c r="F155" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G155" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H155" s="0">
+        <x:v>1781510191</x:v>
+      </x:c>
+      <x:c r="I155" s="0">
+        <x:v>0.0234</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" spans="1:9">
+      <x:c r="A156" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B156" s="0">
+        <x:v>15.95</x:v>
+      </x:c>
+      <x:c r="C156" s="0">
+        <x:v>-0.02</x:v>
+      </x:c>
+      <x:c r="D156" s="0" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="E156" s="0">
+        <x:v>815000</x:v>
+      </x:c>
+      <x:c r="F156" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G156" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H156" s="0">
+        <x:v>2020891371</x:v>
+      </x:c>
+      <x:c r="I156" s="0">
+        <x:v>0.0202</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" spans="1:9">
+      <x:c r="A157" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B157" s="0">
+        <x:v>82.05</x:v>
+      </x:c>
+      <x:c r="C157" s="0">
+        <x:v>-0.75</x:v>
+      </x:c>
+      <x:c r="D157" s="0" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="E157" s="0">
+        <x:v>8300000</x:v>
+      </x:c>
+      <x:c r="F157" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G157" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H157" s="0">
+        <x:v>2941310980</x:v>
+      </x:c>
+      <x:c r="I157" s="0">
+        <x:v>0.1417</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158" spans="1:9">
+      <x:c r="A158" s="0" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="B158" s="0">
+        <x:v>4.22</x:v>
+      </x:c>
+      <x:c r="C158" s="0">
+        <x:v>-0.08</x:v>
+      </x:c>
+      <x:c r="D158" s="0" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="E158" s="0">
+        <x:v>13000000</x:v>
+      </x:c>
+      <x:c r="F158" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G158" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H158" s="0">
+        <x:v>1416740879</x:v>
+      </x:c>
+      <x:c r="I158" s="0">
+        <x:v>0.4613</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" spans="1:9">
+      <x:c r="A159" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B159" s="0">
+        <x:v>120.8</x:v>
+      </x:c>
+      <x:c r="C159" s="0">
+        <x:v>3.9</x:v>
+      </x:c>
+      <x:c r="D159" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="E159" s="0">
+        <x:v>1999793</x:v>
+      </x:c>
+      <x:c r="F159" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G159" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H159" s="0">
+        <x:v>1742315226</x:v>
+      </x:c>
+      <x:c r="I159" s="0">
+        <x:v>0.0494</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" spans="1:9">
+      <x:c r="A160" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B160" s="0">
+        <x:v>48.5</x:v>
+      </x:c>
+      <x:c r="C160" s="0">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="D160" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="E160" s="0">
+        <x:v>1859145</x:v>
+      </x:c>
+      <x:c r="F160" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G160" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H160" s="0">
+        <x:v>2467243928</x:v>
+      </x:c>
+      <x:c r="I160" s="0">
+        <x:v>0.0324</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161" spans="1:9">
+      <x:c r="A161" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B161" s="0">
+        <x:v>3.3</x:v>
+      </x:c>
+      <x:c r="C161" s="0">
+        <x:v>-0.1</x:v>
+      </x:c>
+      <x:c r="D161" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="E161" s="0">
+        <x:v>689661000</x:v>
+      </x:c>
+      <x:c r="F161" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G161" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H161" s="0">
+        <x:v>7382591324</x:v>
+      </x:c>
+      <x:c r="I161" s="0">
+        <x:v>0.0934</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162" spans="1:9">
+      <x:c r="A162" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B162" s="0">
+        <x:v>48.5</x:v>
+      </x:c>
+      <x:c r="C162" s="0">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="D162" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="E162" s="0">
+        <x:v>1902000</x:v>
+      </x:c>
+      <x:c r="F162" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G162" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H162" s="0">
+        <x:v>2467243928</x:v>
+      </x:c>
+      <x:c r="I162" s="0">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163" spans="1:9">
+      <x:c r="A163" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B163" s="0">
+        <x:v>92.4</x:v>
+      </x:c>
+      <x:c r="C163" s="0">
+        <x:v>-2.15</x:v>
+      </x:c>
+      <x:c r="D163" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="E163" s="0">
+        <x:v>56520000</x:v>
+      </x:c>
+      <x:c r="F163" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G163" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H163" s="0">
+        <x:v>1781510191</x:v>
+      </x:c>
+      <x:c r="I163" s="0">
+        <x:v>0.0317</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164" spans="1:9">
+      <x:c r="A164" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B164" s="0">
+        <x:v>92.4</x:v>
+      </x:c>
+      <x:c r="C164" s="0">
+        <x:v>-2.15</x:v>
+      </x:c>
+      <x:c r="D164" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="E164" s="0">
+        <x:v>888325</x:v>
+      </x:c>
+      <x:c r="F164" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G164" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H164" s="0">
+        <x:v>1781510191</x:v>
+      </x:c>
+      <x:c r="I164" s="0">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165" spans="1:9">
+      <x:c r="A165" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B165" s="0">
+        <x:v>7.32</x:v>
+      </x:c>
+      <x:c r="C165" s="0">
+        <x:v>-0.31</x:v>
+      </x:c>
+      <x:c r="D165" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="E165" s="0">
+        <x:v>5581810</x:v>
+      </x:c>
+      <x:c r="F165" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G165" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H165" s="0">
+        <x:v>9028523851</x:v>
+      </x:c>
+      <x:c r="I165" s="0">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166" spans="1:9">
+      <x:c r="A166" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B166" s="0">
+        <x:v>48.5</x:v>
+      </x:c>
+      <x:c r="C166" s="0">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="D166" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="E166" s="0">
+        <x:v>504000000</x:v>
+      </x:c>
+      <x:c r="F166" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G166" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H166" s="0">
+        <x:v>2467243928</x:v>
+      </x:c>
+      <x:c r="I166" s="0">
+        <x:v>0.2043</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167" spans="1:9">
+      <x:c r="A167" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B167" s="0">
+        <x:v>254.75</x:v>
+      </x:c>
+      <x:c r="C167" s="0">
+        <x:v>11.15</x:v>
+      </x:c>
+      <x:c r="D167" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="E167" s="0">
+        <x:v>21500032</x:v>
+      </x:c>
+      <x:c r="F167" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G167" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H167" s="0">
+        <x:v>24073631758</x:v>
+      </x:c>
+      <x:c r="I167" s="0">
+        <x:v>0.0383</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168" spans="1:9">
+      <x:c r="A168" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B168" s="0">
+        <x:v>1120</x:v>
+      </x:c>
+      <x:c r="C168" s="0">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D168" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="E168" s="0">
+        <x:v>6455151</x:v>
+      </x:c>
+      <x:c r="F168" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G168" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H168" s="0">
+        <x:v>1586603352</x:v>
+      </x:c>
+      <x:c r="I168" s="0">
+        <x:v>0.1745</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/yeni-is-anlasmalari/data/yeni-is-anlasmalari.xlsx
+++ b/app/borsa/yeni-is-anlasmalari/data/yeni-is-anlasmalari.xlsx
@@ -43,6 +43,15 @@
     <x:t>Yeni İş İlişkisi / Yıllık Satışlar</x:t>
   </x:si>
   <x:si>
+    <x:t>CWENE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-04-29</x:t>
+  </x:si>
+  <x:si>
+    <x:t>USD</x:t>
+  </x:si>
+  <x:si>
     <x:t>FONET</x:t>
   </x:si>
   <x:si>
@@ -55,9 +64,6 @@
     <x:t>ASTOR</x:t>
   </x:si>
   <x:si>
-    <x:t>USD</x:t>
-  </x:si>
-  <x:si>
     <x:t>ODINE</x:t>
   </x:si>
   <x:si>
@@ -122,9 +128,6 @@
   </x:si>
   <x:si>
     <x:t>KAYSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CWENE</x:t>
   </x:si>
   <x:si>
     <x:t>2026-04-15</x:t>
@@ -775,7 +778,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I168"/>
+  <x:dimension ref="A1:I169"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -812,28 +815,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>5.01</x:v>
+        <x:v>36.44</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>0.15</x:v>
+        <x:v>2.04</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>132077304</x:v>
+        <x:v>2136645</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2026.03</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>855070469</x:v>
+        <x:v>17386730041</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>0.1545</x:v>
+        <x:v>0.0055</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -841,86 +844,86 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>254.75</x:v>
+        <x:v>4.83</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>11.15</x:v>
+        <x:v>-0.18</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>51531000</x:v>
+        <x:v>132077304</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G3" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>35290767390</x:v>
+        <x:v>855070469</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>0.0656</x:v>
+        <x:v>0.1545</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
       <x:c r="A4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>1120</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>57</x:v>
+        <x:v>9.25</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>950978</x:v>
+        <x:v>51531000</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G4" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>1883544167</x:v>
+        <x:v>35290767390</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>0.0227</x:v>
+        <x:v>0.0656</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
       <x:c r="A5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>560</x:v>
+        <x:v>1130</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>-41.5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>100000000</x:v>
+        <x:v>950978</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G5" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>71453576000</x:v>
+        <x:v>1883544167</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>0.0628</x:v>
+        <x:v>0.0227</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -928,16 +931,16 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>82.05</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>-0.75</x:v>
+        <x:v>-4</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>286071819</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
         <x:v>11</x:v>
@@ -946,39 +949,39 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>71453576000</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>0.0818</x:v>
+        <x:v>0.0628</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
       <x:c r="A7" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B7" s="0">
+        <x:v>83.2</x:v>
+      </x:c>
+      <x:c r="C7" s="0">
+        <x:v>1.15</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B7" s="0">
-        <x:v>120.8</x:v>
-      </x:c>
-      <x:c r="C7" s="0">
-        <x:v>3.9</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
       <x:c r="E7" s="0">
-        <x:v>883793</x:v>
+        <x:v>286071819</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G7" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>3150489640</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>0.0148</x:v>
+        <x:v>0.0818</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -986,45 +989,45 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>48.5</x:v>
+        <x:v>117.2</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>-1</x:v>
+        <x:v>-3.6</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>606770</x:v>
+        <x:v>883793</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G8" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>0.0064</x:v>
+        <x:v>0.0148</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
       <x:c r="A9" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>58.35</x:v>
+        <x:v>51.35</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>-1.65</x:v>
+        <x:v>2.85</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>505597002</x:v>
+        <x:v>606770</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
         <x:v>11</x:v>
@@ -1033,126 +1036,126 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>8121300519</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>0.0623</x:v>
+        <x:v>0.0064</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
       <x:c r="A10" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>48.5</x:v>
+        <x:v>58.2</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>-1</x:v>
+        <x:v>-0.15</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>948000</x:v>
+        <x:v>505597002</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G10" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>8121300519</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>0.0101</x:v>
+        <x:v>0.0623</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
       <x:c r="A11" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>92.4</x:v>
+        <x:v>51.35</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>-2.15</x:v>
+        <x:v>2.85</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>622000</x:v>
+        <x:v>948000</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G11" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>0.0114</x:v>
+        <x:v>0.0101</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
       <x:c r="A12" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B12" s="0">
+        <x:v>93.95</x:v>
+      </x:c>
+      <x:c r="C12" s="0">
+        <x:v>1.55</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B12" s="0">
-        <x:v>4.26</x:v>
-      </x:c>
-      <x:c r="C12" s="0">
-        <x:v>-0.1</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="E12" s="0">
-        <x:v>983000</x:v>
+        <x:v>622000</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G12" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>2875634546</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>0.018</x:v>
+        <x:v>0.0114</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
       <x:c r="A13" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>70</x:v>
+        <x:v>4.11</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>-1.8</x:v>
+        <x:v>-0.15</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>3421818</x:v>
+        <x:v>983000</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G13" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>5948036961</x:v>
+        <x:v>2875634546</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>0.0257</x:v>
+        <x:v>0.018</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -1160,57 +1163,57 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>42.88</x:v>
+        <x:v>70.5</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>-2.7</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>697435</x:v>
+        <x:v>3421818</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G14" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>4728937463</x:v>
+        <x:v>5948036961</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>0.0066</x:v>
+        <x:v>0.0257</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
       <x:c r="A15" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B15" s="0">
+        <x:v>45.14</x:v>
+      </x:c>
+      <x:c r="C15" s="0">
+        <x:v>2.26</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="B15" s="0">
-        <x:v>54.35</x:v>
-      </x:c>
-      <x:c r="C15" s="0">
-        <x:v>-0.75</x:v>
-      </x:c>
-      <x:c r="D15" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="E15" s="0">
-        <x:v>4587145</x:v>
+        <x:v>697435</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G15" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>16733157490</x:v>
+        <x:v>4728937463</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>0.0123</x:v>
+        <x:v>0.0066</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -1218,28 +1221,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>40.76</x:v>
+        <x:v>57.2</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>0.44</x:v>
+        <x:v>2.85</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>43200000</x:v>
+        <x:v>4587145</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G16" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>8236540064</x:v>
+        <x:v>16733157490</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>0.2345</x:v>
+        <x:v>0.0123</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1247,103 +1250,103 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>15.95</x:v>
+        <x:v>41.02</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>0.26</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
         <x:v>33</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>1200000</x:v>
+        <x:v>43200000</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G17" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>3139850323</x:v>
+        <x:v>8236540064</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>0.0201</x:v>
+        <x:v>0.2345</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
       <x:c r="A18" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B18" s="0">
+        <x:v>15.85</x:v>
+      </x:c>
+      <x:c r="C18" s="0">
+        <x:v>-0.1</x:v>
+      </x:c>
+      <x:c r="D18" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E18" s="0">
+        <x:v>1200000</x:v>
+      </x:c>
+      <x:c r="F18" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B18" s="0">
-        <x:v>58.35</x:v>
-      </x:c>
-      <x:c r="C18" s="0">
-        <x:v>-1.65</x:v>
-      </x:c>
-      <x:c r="D18" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E18" s="0">
-        <x:v>247902522</x:v>
-      </x:c>
-      <x:c r="F18" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="G18" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>8121300519</x:v>
+        <x:v>3139850323</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>0.0305</x:v>
+        <x:v>0.0201</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
       <x:c r="A19" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>48.5</x:v>
+        <x:v>58.2</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>-1</x:v>
+        <x:v>-0.15</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>366000</x:v>
+        <x:v>247902522</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G19" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>8121300519</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>0.0039</x:v>
+        <x:v>0.0305</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
       <x:c r="A20" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>288</x:v>
+        <x:v>51.35</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>-13.75</x:v>
+        <x:v>2.85</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>141051834</x:v>
+        <x:v>366000</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
         <x:v>11</x:v>
@@ -1352,59 +1355,59 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>709077088</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>0.1989</x:v>
+        <x:v>0.0039</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
       <x:c r="A21" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B21" s="0">
+        <x:v>276.75</x:v>
+      </x:c>
+      <x:c r="C21" s="0">
+        <x:v>-11.25</x:v>
+      </x:c>
+      <x:c r="D21" s="0" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="B21" s="0">
-        <x:v>4.73</x:v>
-      </x:c>
-      <x:c r="C21" s="0">
-        <x:v>-0.2</x:v>
-      </x:c>
-      <x:c r="D21" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
       <x:c r="E21" s="0">
-        <x:v>5096500000</x:v>
+        <x:v>141051834</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>19538660616</x:v>
+        <x:v>709077088</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>0.2608</x:v>
+        <x:v>0.1989</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
       <x:c r="A22" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B22" s="0">
+        <x:v>4.69</x:v>
+      </x:c>
+      <x:c r="C22" s="0">
+        <x:v>-0.04</x:v>
+      </x:c>
+      <x:c r="D22" s="0" t="s">
         <x:v>35</x:v>
-      </x:c>
-      <x:c r="B22" s="0">
-        <x:v>4.73</x:v>
-      </x:c>
-      <x:c r="C22" s="0">
-        <x:v>-0.2</x:v>
-      </x:c>
-      <x:c r="D22" s="0" t="s">
-        <x:v>33</x:v>
       </x:c>
       <x:c r="E22" s="0">
         <x:v>5096500000</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G22" s="0">
         <x:v>2025.09</x:v>
@@ -1418,138 +1421,138 @@
     </x:row>
     <x:row r="23" spans="1:9">
       <x:c r="A23" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>34.4</x:v>
+        <x:v>4.69</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>-1.12</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>37500000</x:v>
+        <x:v>5096500000</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>16355768622</x:v>
+        <x:v>19538660616</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>0.1024</x:v>
+        <x:v>0.2608</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
       <x:c r="A24" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B24" s="0">
+        <x:v>36.44</x:v>
+      </x:c>
+      <x:c r="C24" s="0">
+        <x:v>2.04</x:v>
+      </x:c>
+      <x:c r="D24" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="B24" s="0">
-        <x:v>222.6</x:v>
-      </x:c>
-      <x:c r="C24" s="0">
-        <x:v>0.6</x:v>
-      </x:c>
-      <x:c r="D24" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
       <x:c r="E24" s="0">
-        <x:v>2030000</x:v>
+        <x:v>37500000</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G24" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>2159813703</x:v>
+        <x:v>16355768622</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>0.042</x:v>
+        <x:v>0.1024</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
       <x:c r="A25" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>54.35</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>-0.75</x:v>
+        <x:v>-5.6</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>31146246</x:v>
+        <x:v>2030000</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G25" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>16733157490</x:v>
+        <x:v>2159813703</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>0.0832</x:v>
+        <x:v>0.042</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
       <x:c r="A26" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>11.59</x:v>
+        <x:v>57.2</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>0.07</x:v>
+        <x:v>2.85</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>1000000</x:v>
+        <x:v>31146246</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G26" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>7221187888</x:v>
+        <x:v>16733157490</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>0.0001</x:v>
+        <x:v>0.0832</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
       <x:c r="A27" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>11.59</x:v>
+        <x:v>11.11</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>0.07</x:v>
+        <x:v>-0.48</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>3150000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G27" s="0">
         <x:v>2025.12</x:v>
@@ -1558,27 +1561,27 @@
         <x:v>7221187888</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>0.0227</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
       <x:c r="A28" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>11.59</x:v>
+        <x:v>11.11</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>0.07</x:v>
+        <x:v>-0.48</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>2690000</x:v>
+        <x:v>3150000</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G28" s="0">
         <x:v>2025.12</x:v>
@@ -1587,65 +1590,65 @@
         <x:v>7221187888</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>0.0166</x:v>
+        <x:v>0.0227</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
       <x:c r="A29" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>54.35</x:v>
+        <x:v>11.11</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>-0.75</x:v>
+        <x:v>-0.48</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>4103000</x:v>
+        <x:v>2690000</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G29" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>16733157490</x:v>
+        <x:v>7221187888</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>0.0109</x:v>
+        <x:v>0.0166</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
       <x:c r="A30" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>120.8</x:v>
+        <x:v>57.2</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>3.9</x:v>
+        <x:v>2.85</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>500000</x:v>
+        <x:v>4103000</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G30" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>3150489640</x:v>
+        <x:v>16733157490</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>0.0083</x:v>
+        <x:v>0.0109</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1653,45 +1656,45 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>48.5</x:v>
+        <x:v>117.2</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>-1</x:v>
+        <x:v>-3.6</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>872928</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G31" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>0.0092</x:v>
+        <x:v>0.0083</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
       <x:c r="A32" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>92.4</x:v>
+        <x:v>51.35</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>-2.15</x:v>
+        <x:v>2.85</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>21250000</x:v>
+        <x:v>872928</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
         <x:v>11</x:v>
@@ -1700,85 +1703,85 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>0.0087</x:v>
+        <x:v>0.0092</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
       <x:c r="A33" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>58.35</x:v>
+        <x:v>93.95</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>-1.65</x:v>
+        <x:v>1.55</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>67690912</x:v>
+        <x:v>21250000</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G33" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>8121300519</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>0.0083</x:v>
+        <x:v>0.0087</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
       <x:c r="A34" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>34.4</x:v>
+        <x:v>58.2</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>-1.12</x:v>
+        <x:v>-0.15</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>65458848</x:v>
+        <x:v>67690912</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G34" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>16355768622</x:v>
+        <x:v>8121300519</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>0.1784</x:v>
+        <x:v>0.0083</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
       <x:c r="A35" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B35" s="0">
+        <x:v>36.44</x:v>
+      </x:c>
+      <x:c r="C35" s="0">
+        <x:v>2.04</x:v>
+      </x:c>
+      <x:c r="D35" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="B35" s="0">
-        <x:v>24.16</x:v>
-      </x:c>
-      <x:c r="C35" s="0">
-        <x:v>-0.56</x:v>
-      </x:c>
-      <x:c r="D35" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
       <x:c r="E35" s="0">
-        <x:v>689500000</x:v>
+        <x:v>65458848</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
         <x:v>11</x:v>
@@ -1787,10 +1790,10 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>884571536</x:v>
+        <x:v>16355768622</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>0.7795</x:v>
+        <x:v>0.1784</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1798,48 +1801,48 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>5.82</x:v>
+        <x:v>24.3</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>-0.05</x:v>
+        <x:v>0.14</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>3024490</x:v>
+        <x:v>689500000</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G36" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>2322993973</x:v>
+        <x:v>884571536</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>0.0671</x:v>
+        <x:v>0.7795</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
       <x:c r="A37" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>5.82</x:v>
+        <x:v>5.9</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>-0.05</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>4510336</x:v>
+        <x:v>3024490</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G37" s="0">
         <x:v>2025.12</x:v>
@@ -1848,7 +1851,7 @@
         <x:v>2322993973</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>0.0865</x:v>
+        <x:v>0.0671</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1856,45 +1859,45 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>49.2</x:v>
+        <x:v>5.9</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>-0.14</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>205000000</x:v>
+        <x:v>4510336</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G38" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>20597209000</x:v>
+        <x:v>2322993973</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>0.4434</x:v>
+        <x:v>0.0865</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
       <x:c r="A39" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B39" s="0">
+        <x:v>48.2</x:v>
+      </x:c>
+      <x:c r="C39" s="0">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="D39" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="B39" s="0">
-        <x:v>340</x:v>
-      </x:c>
-      <x:c r="C39" s="0">
-        <x:v>-9</x:v>
-      </x:c>
-      <x:c r="D39" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
       <x:c r="E39" s="0">
-        <x:v>305000000</x:v>
+        <x:v>205000000</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
         <x:v>11</x:v>
@@ -1903,146 +1906,146 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>400439646</x:v>
+        <x:v>20597209000</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>0.7617</x:v>
+        <x:v>0.4434</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
       <x:c r="A40" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>82.05</x:v>
+        <x:v>332.25</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>-0.75</x:v>
+        <x:v>-7.75</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>11700000</x:v>
+        <x:v>305000000</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G40" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>400439646</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>0.1718</x:v>
+        <x:v>0.7617</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
       <x:c r="A41" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>222.6</x:v>
+        <x:v>83.2</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>0.6</x:v>
+        <x:v>1.15</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>1900000</x:v>
+        <x:v>11700000</x:v>
       </x:c>
       <x:c r="F41" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G41" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>2159813703</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>0.0391</x:v>
+        <x:v>0.1718</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
       <x:c r="A42" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>4.26</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>-0.1</x:v>
+        <x:v>-5.6</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>1670000</x:v>
+        <x:v>1900000</x:v>
       </x:c>
       <x:c r="F42" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G42" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>2875634546</x:v>
+        <x:v>2159813703</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>0.0298</x:v>
+        <x:v>0.0391</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
       <x:c r="A43" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>24.16</x:v>
+        <x:v>4.11</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>-0.56</x:v>
+        <x:v>-0.15</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>48895800</x:v>
+        <x:v>1670000</x:v>
       </x:c>
       <x:c r="F43" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G43" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>884571536</x:v>
+        <x:v>2875634546</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>0.0553</x:v>
+        <x:v>0.0298</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
       <x:c r="A44" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>24.16</x:v>
+        <x:v>24.3</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>-0.56</x:v>
+        <x:v>0.14</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>689500000</x:v>
+        <x:v>48895800</x:v>
       </x:c>
       <x:c r="F44" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G44" s="0">
         <x:v>2025.12</x:v>
@@ -2051,36 +2054,36 @@
         <x:v>884571536</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>0.7795</x:v>
+        <x:v>0.0553</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
       <x:c r="A45" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B45" s="0">
+        <x:v>24.3</x:v>
+      </x:c>
+      <x:c r="C45" s="0">
+        <x:v>0.14</x:v>
+      </x:c>
+      <x:c r="D45" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="B45" s="0">
-        <x:v>44.6</x:v>
-      </x:c>
-      <x:c r="C45" s="0">
-        <x:v>-3.18</x:v>
-      </x:c>
-      <x:c r="D45" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="E45" s="0">
-        <x:v>3102911</x:v>
+        <x:v>689500000</x:v>
       </x:c>
       <x:c r="F45" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G45" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>2907014564</x:v>
+        <x:v>884571536</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>0.0475</x:v>
+        <x:v>0.7795</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -2088,132 +2091,132 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>23.58</x:v>
+        <x:v>44.4</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>-0.42</x:v>
+        <x:v>-0.2</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>13000000</x:v>
+        <x:v>3102911</x:v>
       </x:c>
       <x:c r="F46" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G46" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>11834942581</x:v>
+        <x:v>2907014564</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>0.0563</x:v>
+        <x:v>0.0475</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
       <x:c r="A47" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>70</x:v>
+        <x:v>24.26</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>-1.8</x:v>
+        <x:v>0.68</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>6800000</x:v>
+        <x:v>13000000</x:v>
       </x:c>
       <x:c r="F47" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G47" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>5948036961</x:v>
+        <x:v>11834942581</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>0.0583</x:v>
+        <x:v>0.0563</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
       <x:c r="A48" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>49.2</x:v>
+        <x:v>70.5</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>-0.14</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>36750000</x:v>
+        <x:v>6800000</x:v>
       </x:c>
       <x:c r="F48" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G48" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>20597209000</x:v>
+        <x:v>5948036961</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>0.0793</x:v>
+        <x:v>0.0583</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
       <x:c r="A49" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>1120</x:v>
+        <x:v>48.2</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>57</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>3867260</x:v>
+        <x:v>36750000</x:v>
       </x:c>
       <x:c r="F49" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G49" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>1883544167</x:v>
+        <x:v>20597209000</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>0.0912</x:v>
+        <x:v>0.0793</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
       <x:c r="A50" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B50" s="0">
+        <x:v>1130</x:v>
+      </x:c>
+      <x:c r="C50" s="0">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D50" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="B50" s="0">
-        <x:v>63.1</x:v>
-      </x:c>
-      <x:c r="C50" s="0">
-        <x:v>-2.3</x:v>
-      </x:c>
-      <x:c r="D50" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="E50" s="0">
-        <x:v>1498029716</x:v>
+        <x:v>3867260</x:v>
       </x:c>
       <x:c r="F50" s="0" t="s">
         <x:v>11</x:v>
@@ -2222,56 +2225,56 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>12030341104</x:v>
+        <x:v>1883544167</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>0.1245</x:v>
+        <x:v>0.0912</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
       <x:c r="A51" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>34.4</x:v>
+        <x:v>66.05</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>-1.12</x:v>
+        <x:v>2.95</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>48000000</x:v>
+        <x:v>1498029716</x:v>
       </x:c>
       <x:c r="F51" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G51" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>16355768622</x:v>
+        <x:v>12030341104</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>0.1301</x:v>
+        <x:v>0.1245</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
       <x:c r="A52" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>82.05</x:v>
+        <x:v>36.44</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>-0.75</x:v>
+        <x:v>2.04</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>279699629</x:v>
+        <x:v>48000000</x:v>
       </x:c>
       <x:c r="F52" s="0" t="s">
         <x:v>11</x:v>
@@ -2280,85 +2283,85 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>16355768622</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>0.08</x:v>
+        <x:v>0.1301</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:9">
       <x:c r="A53" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B53" s="0">
+        <x:v>83.2</x:v>
+      </x:c>
+      <x:c r="C53" s="0">
+        <x:v>1.15</x:v>
+      </x:c>
+      <x:c r="D53" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="B53" s="0">
-        <x:v>14.91</x:v>
-      </x:c>
-      <x:c r="C53" s="0">
-        <x:v>-0.25</x:v>
-      </x:c>
-      <x:c r="D53" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
       <x:c r="E53" s="0">
-        <x:v>7971822</x:v>
+        <x:v>279699629</x:v>
       </x:c>
       <x:c r="F53" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G53" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H53" s="0">
-        <x:v>4675369372</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>0.0756</x:v>
+        <x:v>0.08</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:9">
       <x:c r="A54" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B54" s="0">
-        <x:v>48.5</x:v>
+        <x:v>14.86</x:v>
       </x:c>
       <x:c r="C54" s="0">
-        <x:v>-1</x:v>
+        <x:v>-0.05</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E54" s="0">
-        <x:v>1104000</x:v>
+        <x:v>7971822</x:v>
       </x:c>
       <x:c r="F54" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G54" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>4675369372</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>0.0116</x:v>
+        <x:v>0.0756</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:9">
       <x:c r="A55" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B55" s="0">
-        <x:v>24.16</x:v>
+        <x:v>51.35</x:v>
       </x:c>
       <x:c r="C55" s="0">
-        <x:v>-0.56</x:v>
+        <x:v>2.85</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E55" s="0">
-        <x:v>48895800</x:v>
+        <x:v>1104000</x:v>
       </x:c>
       <x:c r="F55" s="0" t="s">
         <x:v>11</x:v>
@@ -2367,59 +2370,59 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H55" s="0">
-        <x:v>884571536</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>0.0553</x:v>
+        <x:v>0.0116</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:9">
       <x:c r="A56" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B56" s="0">
-        <x:v>3.3</x:v>
+        <x:v>24.3</x:v>
       </x:c>
       <x:c r="C56" s="0">
-        <x:v>-0.1</x:v>
+        <x:v>0.14</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E56" s="0">
-        <x:v>191089413</x:v>
+        <x:v>48895800</x:v>
       </x:c>
       <x:c r="F56" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G56" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H56" s="0">
-        <x:v>9665356715</x:v>
+        <x:v>884571536</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>0.0198</x:v>
+        <x:v>0.0553</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:9">
       <x:c r="A57" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B57" s="0">
-        <x:v>3.3</x:v>
+        <x:v>3.28</x:v>
       </x:c>
       <x:c r="C57" s="0">
-        <x:v>-0.1</x:v>
+        <x:v>-0.02</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E57" s="0">
-        <x:v>605627160</x:v>
+        <x:v>191089413</x:v>
       </x:c>
       <x:c r="F57" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G57" s="0">
         <x:v>2025.12</x:v>
@@ -2428,7 +2431,7 @@
         <x:v>9665356715</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>0.0627</x:v>
+        <x:v>0.0198</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:9">
@@ -2436,77 +2439,77 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B58" s="0">
-        <x:v>25.86</x:v>
+        <x:v>3.28</x:v>
       </x:c>
       <x:c r="C58" s="0">
-        <x:v>-0.68</x:v>
+        <x:v>-0.02</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E58" s="0">
-        <x:v>2356546000</x:v>
+        <x:v>605627160</x:v>
       </x:c>
       <x:c r="F58" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G58" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H58" s="0">
-        <x:v>7708004248</x:v>
+        <x:v>9665356715</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>0.3057</x:v>
+        <x:v>0.0627</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:9">
       <x:c r="A59" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B59" s="0">
-        <x:v>15.95</x:v>
+        <x:v>26.04</x:v>
       </x:c>
       <x:c r="C59" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E59" s="0">
-        <x:v>431250</x:v>
+        <x:v>2356546000</x:v>
       </x:c>
       <x:c r="F59" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G59" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H59" s="0">
-        <x:v>3139850323</x:v>
+        <x:v>7708004248</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>0.0071</x:v>
+        <x:v>0.3057</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:9">
       <x:c r="A60" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B60" s="0">
-        <x:v>15.95</x:v>
+        <x:v>15.85</x:v>
       </x:c>
       <x:c r="C60" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>-0.1</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E60" s="0">
-        <x:v>800000</x:v>
+        <x:v>431250</x:v>
       </x:c>
       <x:c r="F60" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G60" s="0">
         <x:v>2025.12</x:v>
@@ -2515,230 +2518,230 @@
         <x:v>3139850323</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>0.0131</x:v>
+        <x:v>0.0071</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:9">
       <x:c r="A61" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B61" s="0">
+        <x:v>15.85</x:v>
+      </x:c>
+      <x:c r="C61" s="0">
+        <x:v>-0.1</x:v>
+      </x:c>
+      <x:c r="D61" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="E61" s="0">
+        <x:v>800000</x:v>
+      </x:c>
+      <x:c r="F61" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B61" s="0">
-        <x:v>58.35</x:v>
-      </x:c>
-      <x:c r="C61" s="0">
-        <x:v>-1.65</x:v>
-      </x:c>
-      <x:c r="D61" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="E61" s="0">
-        <x:v>127172130</x:v>
-      </x:c>
-      <x:c r="F61" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="G61" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H61" s="0">
-        <x:v>8121300519</x:v>
+        <x:v>3139850323</x:v>
       </x:c>
       <x:c r="I61" s="0">
-        <x:v>0.0157</x:v>
+        <x:v>0.0131</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:9">
       <x:c r="A62" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B62" s="0">
-        <x:v>42.88</x:v>
+        <x:v>58.2</x:v>
       </x:c>
       <x:c r="C62" s="0">
-        <x:v>-2.7</x:v>
+        <x:v>-0.15</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E62" s="0">
-        <x:v>42625000</x:v>
+        <x:v>127172130</x:v>
       </x:c>
       <x:c r="F62" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G62" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H62" s="0">
-        <x:v>4728937463</x:v>
+        <x:v>8121300519</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>0.3994</x:v>
+        <x:v>0.0157</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:9">
       <x:c r="A63" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B63" s="0">
-        <x:v>92.4</x:v>
+        <x:v>45.14</x:v>
       </x:c>
       <x:c r="C63" s="0">
-        <x:v>-2.15</x:v>
+        <x:v>2.26</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
         <x:v>63</x:v>
       </x:c>
       <x:c r="E63" s="0">
-        <x:v>1486000</x:v>
+        <x:v>42625000</x:v>
       </x:c>
       <x:c r="F63" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G63" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H63" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>4728937463</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>0.027</x:v>
+        <x:v>0.3994</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:9">
       <x:c r="A64" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B64" s="0">
-        <x:v>254.75</x:v>
+        <x:v>93.95</x:v>
       </x:c>
       <x:c r="C64" s="0">
-        <x:v>11.15</x:v>
+        <x:v>1.55</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E64" s="0">
-        <x:v>768864700</x:v>
+        <x:v>1486000</x:v>
       </x:c>
       <x:c r="F64" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G64" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H64" s="0">
-        <x:v>35290767390</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>0.9648</x:v>
+        <x:v>0.027</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:9">
       <x:c r="A65" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B65" s="0">
-        <x:v>54.35</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="C65" s="0">
-        <x:v>-0.75</x:v>
+        <x:v>9.25</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E65" s="0">
-        <x:v>15938617</x:v>
+        <x:v>768864700</x:v>
       </x:c>
       <x:c r="F65" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G65" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H65" s="0">
-        <x:v>16733157490</x:v>
+        <x:v>35290767390</x:v>
       </x:c>
       <x:c r="I65" s="0">
-        <x:v>0.0422</x:v>
+        <x:v>0.9648</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:9">
       <x:c r="A66" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B66" s="0">
+        <x:v>57.2</x:v>
+      </x:c>
+      <x:c r="C66" s="0">
+        <x:v>2.85</x:v>
+      </x:c>
+      <x:c r="D66" s="0" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="B66" s="0">
-        <x:v>14.5</x:v>
-      </x:c>
-      <x:c r="C66" s="0">
-        <x:v>-0.3</x:v>
-      </x:c>
-      <x:c r="D66" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
       <x:c r="E66" s="0">
-        <x:v>30438120</x:v>
+        <x:v>15938617</x:v>
       </x:c>
       <x:c r="F66" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G66" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H66" s="0">
-        <x:v>3159124121</x:v>
+        <x:v>16733157490</x:v>
       </x:c>
       <x:c r="I66" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0422</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:9">
       <x:c r="A67" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B67" s="0">
-        <x:v>222.6</x:v>
+        <x:v>14.58</x:v>
       </x:c>
       <x:c r="C67" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
         <x:v>66</x:v>
       </x:c>
       <x:c r="E67" s="0">
-        <x:v>3900000</x:v>
+        <x:v>30438120</x:v>
       </x:c>
       <x:c r="F67" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G67" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H67" s="0">
-        <x:v>2159813703</x:v>
+        <x:v>3159124121</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>0.0797</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:9">
       <x:c r="A68" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B68" s="0">
-        <x:v>222.6</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="C68" s="0">
-        <x:v>0.6</x:v>
+        <x:v>-5.6</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E68" s="0">
-        <x:v>2104908</x:v>
+        <x:v>3900000</x:v>
       </x:c>
       <x:c r="F68" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G68" s="0">
         <x:v>2025.12</x:v>
@@ -2747,53 +2750,53 @@
         <x:v>2159813703</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>0.043</x:v>
+        <x:v>0.0797</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:9">
       <x:c r="A69" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B69" s="0">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="C69" s="0">
+        <x:v>-5.6</x:v>
+      </x:c>
+      <x:c r="D69" s="0" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="B69" s="0">
-        <x:v>28.64</x:v>
-      </x:c>
-      <x:c r="C69" s="0">
-        <x:v>0.8</x:v>
-      </x:c>
-      <x:c r="D69" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
       <x:c r="E69" s="0">
-        <x:v>3900000</x:v>
+        <x:v>2104908</x:v>
       </x:c>
       <x:c r="F69" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G69" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H69" s="0">
-        <x:v>7297855153</x:v>
+        <x:v>2159813703</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>0.0236</x:v>
+        <x:v>0.043</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:9">
       <x:c r="A70" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B70" s="0">
-        <x:v>5.01</x:v>
+        <x:v>28.38</x:v>
       </x:c>
       <x:c r="C70" s="0">
-        <x:v>0.15</x:v>
+        <x:v>-0.26</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E70" s="0">
-        <x:v>496968445</x:v>
+        <x:v>3900000</x:v>
       </x:c>
       <x:c r="F70" s="0" t="s">
         <x:v>11</x:v>
@@ -2802,117 +2805,117 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H70" s="0">
-        <x:v>855070469</x:v>
+        <x:v>7297855153</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>0.5812</x:v>
+        <x:v>0.0236</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:9">
       <x:c r="A71" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B71" s="0">
+        <x:v>4.83</x:v>
+      </x:c>
+      <x:c r="C71" s="0">
+        <x:v>-0.18</x:v>
+      </x:c>
+      <x:c r="D71" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="B71" s="0">
-        <x:v>12.88</x:v>
-      </x:c>
-      <x:c r="C71" s="0">
-        <x:v>-0.02</x:v>
-      </x:c>
-      <x:c r="D71" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
       <x:c r="E71" s="0">
-        <x:v>108750000</x:v>
+        <x:v>496968445</x:v>
       </x:c>
       <x:c r="F71" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G71" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H71" s="0">
-        <x:v>1982520183</x:v>
+        <x:v>855070469</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>0.0549</x:v>
+        <x:v>0.5812</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:9">
       <x:c r="A72" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B72" s="0">
-        <x:v>120.8</x:v>
+        <x:v>13.58</x:v>
       </x:c>
       <x:c r="C72" s="0">
-        <x:v>3.9</x:v>
+        <x:v>0.7</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E72" s="0">
-        <x:v>1605197</x:v>
+        <x:v>108750000</x:v>
       </x:c>
       <x:c r="F72" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G72" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H72" s="0">
-        <x:v>0</x:v>
+        <x:v>1982520183</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0549</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:9">
       <x:c r="A73" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B73" s="0">
+        <x:v>117.2</x:v>
+      </x:c>
+      <x:c r="C73" s="0">
+        <x:v>-3.6</x:v>
+      </x:c>
+      <x:c r="D73" s="0" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="B73" s="0">
-        <x:v>414.5</x:v>
-      </x:c>
-      <x:c r="C73" s="0">
-        <x:v>-0.5</x:v>
-      </x:c>
-      <x:c r="D73" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
       <x:c r="E73" s="0">
-        <x:v>54600000</x:v>
+        <x:v>1605197</x:v>
       </x:c>
       <x:c r="F73" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G73" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H73" s="0">
-        <x:v>180444938000</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>0.0133</x:v>
+        <x:v>0.0257</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:9">
       <x:c r="A74" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B74" s="0">
-        <x:v>414.5</x:v>
+        <x:v>425.5</x:v>
       </x:c>
       <x:c r="C74" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E74" s="0">
-        <x:v>111850000</x:v>
+        <x:v>54600000</x:v>
       </x:c>
       <x:c r="F74" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G74" s="0">
         <x:v>2025.12</x:v>
@@ -2921,53 +2924,53 @@
         <x:v>180444938000</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>0.0273</x:v>
+        <x:v>0.0133</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:9">
       <x:c r="A75" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B75" s="0">
-        <x:v>48.5</x:v>
+        <x:v>425.5</x:v>
       </x:c>
       <x:c r="C75" s="0">
-        <x:v>-1</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E75" s="0">
-        <x:v>803090</x:v>
+        <x:v>111850000</x:v>
       </x:c>
       <x:c r="F75" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G75" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H75" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>180444938000</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>0.0084</x:v>
+        <x:v>0.0273</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:9">
       <x:c r="A76" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B76" s="0">
-        <x:v>25.86</x:v>
+        <x:v>51.35</x:v>
       </x:c>
       <x:c r="C76" s="0">
-        <x:v>-0.68</x:v>
+        <x:v>2.85</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
         <x:v>73</x:v>
       </x:c>
       <x:c r="E76" s="0">
-        <x:v>2356546000</x:v>
+        <x:v>803090</x:v>
       </x:c>
       <x:c r="F76" s="0" t="s">
         <x:v>11</x:v>
@@ -2976,56 +2979,56 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H76" s="0">
-        <x:v>7708004248</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I76" s="0">
-        <x:v>0.3057</x:v>
+        <x:v>0.0084</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:9">
       <x:c r="A77" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B77" s="0">
-        <x:v>1120</x:v>
+        <x:v>26.04</x:v>
       </x:c>
       <x:c r="C77" s="0">
-        <x:v>57</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
         <x:v>74</x:v>
       </x:c>
       <x:c r="E77" s="0">
-        <x:v>875400</x:v>
+        <x:v>2356546000</x:v>
       </x:c>
       <x:c r="F77" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G77" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H77" s="0">
-        <x:v>1883544167</x:v>
+        <x:v>7708004248</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>0.0205</x:v>
+        <x:v>0.3057</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:9">
       <x:c r="A78" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B78" s="0">
+        <x:v>1130</x:v>
+      </x:c>
+      <x:c r="C78" s="0">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D78" s="0" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="B78" s="0">
-        <x:v>24.3</x:v>
-      </x:c>
-      <x:c r="C78" s="0">
-        <x:v>-0.2</x:v>
-      </x:c>
-      <x:c r="D78" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
       <x:c r="E78" s="0">
-        <x:v>330000000</x:v>
+        <x:v>875400</x:v>
       </x:c>
       <x:c r="F78" s="0" t="s">
         <x:v>11</x:v>
@@ -3034,172 +3037,172 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H78" s="0">
-        <x:v>5287314404</x:v>
+        <x:v>1883544167</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>0.0624</x:v>
+        <x:v>0.0205</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:9">
       <x:c r="A79" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B79" s="0">
-        <x:v>82.05</x:v>
+        <x:v>26.72</x:v>
       </x:c>
       <x:c r="C79" s="0">
-        <x:v>-0.75</x:v>
+        <x:v>2.42</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
         <x:v>77</x:v>
       </x:c>
       <x:c r="E79" s="0">
-        <x:v>11700000</x:v>
+        <x:v>330000000</x:v>
       </x:c>
       <x:c r="F79" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G79" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H79" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>5287314404</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>0.1705</x:v>
+        <x:v>0.0624</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:9">
       <x:c r="A80" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B80" s="0">
+        <x:v>83.2</x:v>
+      </x:c>
+      <x:c r="C80" s="0">
+        <x:v>1.15</x:v>
+      </x:c>
+      <x:c r="D80" s="0" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="B80" s="0">
-        <x:v>7.32</x:v>
-      </x:c>
-      <x:c r="C80" s="0">
-        <x:v>-0.31</x:v>
-      </x:c>
-      <x:c r="D80" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
       <x:c r="E80" s="0">
-        <x:v>4000000000</x:v>
+        <x:v>11700000</x:v>
       </x:c>
       <x:c r="F80" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G80" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H80" s="0">
-        <x:v>10581001663</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>0.378</x:v>
+        <x:v>0.1705</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:9">
       <x:c r="A81" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B81" s="0">
-        <x:v>15.95</x:v>
+        <x:v>7.38</x:v>
       </x:c>
       <x:c r="C81" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E81" s="0">
-        <x:v>1086598</x:v>
+        <x:v>4000000000</x:v>
       </x:c>
       <x:c r="F81" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G81" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H81" s="0">
-        <x:v>2020891371</x:v>
+        <x:v>10581001663</x:v>
       </x:c>
       <x:c r="I81" s="0">
-        <x:v>0.0274</x:v>
+        <x:v>0.378</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:9">
       <x:c r="A82" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B82" s="0">
-        <x:v>14.91</x:v>
+        <x:v>15.85</x:v>
       </x:c>
       <x:c r="C82" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>-0.1</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="E82" s="0">
-        <x:v>216000000</x:v>
+        <x:v>1086598</x:v>
       </x:c>
       <x:c r="F82" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G82" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H82" s="0">
-        <x:v>3025063909</x:v>
+        <x:v>2020891371</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>0.0714</x:v>
+        <x:v>0.0274</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:9">
       <x:c r="A83" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B83" s="0">
-        <x:v>48.5</x:v>
+        <x:v>14.86</x:v>
       </x:c>
       <x:c r="C83" s="0">
-        <x:v>-1</x:v>
+        <x:v>-0.05</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E83" s="0">
-        <x:v>7292916</x:v>
+        <x:v>216000000</x:v>
       </x:c>
       <x:c r="F83" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G83" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H83" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>3025063909</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>0.0758</x:v>
+        <x:v>0.0714</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:9">
       <x:c r="A84" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B84" s="0">
+        <x:v>51.35</x:v>
+      </x:c>
+      <x:c r="C84" s="0">
+        <x:v>2.85</x:v>
+      </x:c>
+      <x:c r="D84" s="0" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="B84" s="0">
-        <x:v>25.16</x:v>
-      </x:c>
-      <x:c r="C84" s="0">
-        <x:v>-0.82</x:v>
-      </x:c>
-      <x:c r="D84" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
       <x:c r="E84" s="0">
-        <x:v>250000</x:v>
+        <x:v>7292916</x:v>
       </x:c>
       <x:c r="F84" s="0" t="s">
         <x:v>11</x:v>
@@ -3208,175 +3211,175 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H84" s="0">
-        <x:v>448686813</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>0.0006</x:v>
+        <x:v>0.0758</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:9">
       <x:c r="A85" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B85" s="0">
-        <x:v>54.35</x:v>
+        <x:v>24.7</x:v>
       </x:c>
       <x:c r="C85" s="0">
-        <x:v>-0.75</x:v>
+        <x:v>-0.46</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E85" s="0">
-        <x:v>36900000</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="F85" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G85" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H85" s="0">
-        <x:v>10597063406</x:v>
+        <x:v>448686813</x:v>
       </x:c>
       <x:c r="I85" s="0">
-        <x:v>0.1527</x:v>
+        <x:v>0.0006</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:9">
       <x:c r="A86" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B86" s="0">
+        <x:v>57.2</x:v>
+      </x:c>
+      <x:c r="C86" s="0">
+        <x:v>2.85</x:v>
+      </x:c>
+      <x:c r="D86" s="0" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="B86" s="0">
-        <x:v>59.85</x:v>
-      </x:c>
-      <x:c r="C86" s="0">
-        <x:v>-1.15</x:v>
-      </x:c>
-      <x:c r="D86" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
       <x:c r="E86" s="0">
-        <x:v>3800000</x:v>
+        <x:v>36900000</x:v>
       </x:c>
       <x:c r="F86" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G86" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H86" s="0">
-        <x:v>832031190</x:v>
+        <x:v>10597063406</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>0.2002</x:v>
+        <x:v>0.1527</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:9">
       <x:c r="A87" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B87" s="0">
-        <x:v>5.01</x:v>
+        <x:v>60.3</x:v>
       </x:c>
       <x:c r="C87" s="0">
-        <x:v>0.15</x:v>
+        <x:v>0.45</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
         <x:v>85</x:v>
       </x:c>
       <x:c r="E87" s="0">
-        <x:v>2100000</x:v>
+        <x:v>3800000</x:v>
       </x:c>
       <x:c r="F87" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G87" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H87" s="0">
-        <x:v>855070469</x:v>
+        <x:v>832031190</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>0.1076</x:v>
+        <x:v>0.2002</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:9">
       <x:c r="A88" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B88" s="0">
-        <x:v>48.5</x:v>
+        <x:v>4.83</x:v>
       </x:c>
       <x:c r="C88" s="0">
-        <x:v>-1</x:v>
+        <x:v>-0.18</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E88" s="0">
-        <x:v>22928077</x:v>
+        <x:v>2100000</x:v>
       </x:c>
       <x:c r="F88" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G88" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H88" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>855070469</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>0.2378</x:v>
+        <x:v>0.1076</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:9">
       <x:c r="A89" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B89" s="0">
+        <x:v>51.35</x:v>
+      </x:c>
+      <x:c r="C89" s="0">
+        <x:v>2.85</x:v>
+      </x:c>
+      <x:c r="D89" s="0" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="B89" s="0">
-        <x:v>28.8</x:v>
-      </x:c>
-      <x:c r="C89" s="0">
-        <x:v>-0.04</x:v>
-      </x:c>
-      <x:c r="D89" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
       <x:c r="E89" s="0">
-        <x:v>547462013</x:v>
+        <x:v>22928077</x:v>
       </x:c>
       <x:c r="F89" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G89" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H89" s="0">
-        <x:v>0</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>0</x:v>
+        <x:v>0.2378</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:9">
       <x:c r="A90" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B90" s="0">
+        <x:v>28.5</x:v>
+      </x:c>
+      <x:c r="C90" s="0">
+        <x:v>-0.3</x:v>
+      </x:c>
+      <x:c r="D90" s="0" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="B90" s="0">
-        <x:v>28.8</x:v>
-      </x:c>
-      <x:c r="C90" s="0">
-        <x:v>-0.04</x:v>
-      </x:c>
-      <x:c r="D90" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
       <x:c r="E90" s="0">
-        <x:v>10567948</x:v>
+        <x:v>547462013</x:v>
       </x:c>
       <x:c r="F90" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G90" s="0">
         <x:v>0</x:v>
@@ -3390,89 +3393,89 @@
     </x:row>
     <x:row r="91" spans="1:9">
       <x:c r="A91" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B91" s="0">
-        <x:v>82.05</x:v>
+        <x:v>28.5</x:v>
       </x:c>
       <x:c r="C91" s="0">
-        <x:v>-0.75</x:v>
+        <x:v>-0.3</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E91" s="0">
-        <x:v>8300000</x:v>
+        <x:v>10567948</x:v>
       </x:c>
       <x:c r="F91" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G91" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H91" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>0.1228</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:9">
       <x:c r="A92" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B92" s="0">
-        <x:v>49.2</x:v>
+        <x:v>83.2</x:v>
       </x:c>
       <x:c r="C92" s="0">
-        <x:v>-0.14</x:v>
+        <x:v>1.15</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E92" s="0">
-        <x:v>3000000</x:v>
+        <x:v>8300000</x:v>
       </x:c>
       <x:c r="F92" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G92" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H92" s="0">
-        <x:v>20597209000</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>0.0064</x:v>
+        <x:v>0.1228</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:9">
       <x:c r="A93" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B93" s="0">
+        <x:v>48.2</x:v>
+      </x:c>
+      <x:c r="C93" s="0">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="D93" s="0" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="B93" s="0">
-        <x:v>33.34</x:v>
-      </x:c>
-      <x:c r="C93" s="0">
-        <x:v>0.74</x:v>
-      </x:c>
-      <x:c r="D93" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
       <x:c r="E93" s="0">
-        <x:v>26640000</x:v>
+        <x:v>3000000</x:v>
       </x:c>
       <x:c r="F93" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G93" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H93" s="0">
-        <x:v>3277373640</x:v>
+        <x:v>20597209000</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>0.356</x:v>
+        <x:v>0.0064</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:9">
@@ -3480,193 +3483,193 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="B94" s="0">
-        <x:v>5.35</x:v>
+        <x:v>34.36</x:v>
       </x:c>
       <x:c r="C94" s="0">
-        <x:v>-0.18</x:v>
+        <x:v>1.02</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E94" s="0">
-        <x:v>13107198</x:v>
+        <x:v>26640000</x:v>
       </x:c>
       <x:c r="F94" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G94" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H94" s="0">
-        <x:v>1627872951</x:v>
+        <x:v>3277373640</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>0.0081</x:v>
+        <x:v>0.356</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:9">
       <x:c r="A95" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B95" s="0">
-        <x:v>82.05</x:v>
+        <x:v>5.34</x:v>
       </x:c>
       <x:c r="C95" s="0">
-        <x:v>-0.75</x:v>
+        <x:v>-0.01</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
         <x:v>91</x:v>
       </x:c>
       <x:c r="E95" s="0">
-        <x:v>237500000</x:v>
+        <x:v>13107198</x:v>
       </x:c>
       <x:c r="F95" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G95" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H95" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>1627872951</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>0.0679</x:v>
+        <x:v>0.0081</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:9">
       <x:c r="A96" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B96" s="0">
-        <x:v>58.35</x:v>
+        <x:v>83.2</x:v>
       </x:c>
       <x:c r="C96" s="0">
-        <x:v>-1.65</x:v>
+        <x:v>1.15</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
         <x:v>92</x:v>
       </x:c>
       <x:c r="E96" s="0">
-        <x:v>147892538</x:v>
+        <x:v>237500000</x:v>
       </x:c>
       <x:c r="F96" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G96" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H96" s="0">
-        <x:v>7257990064</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>0.0204</x:v>
+        <x:v>0.0679</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:9">
       <x:c r="A97" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B97" s="0">
+        <x:v>58.2</x:v>
+      </x:c>
+      <x:c r="C97" s="0">
+        <x:v>-0.15</x:v>
+      </x:c>
+      <x:c r="D97" s="0" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="B97" s="0">
-        <x:v>49.08</x:v>
-      </x:c>
-      <x:c r="C97" s="0">
-        <x:v>4.46</x:v>
-      </x:c>
-      <x:c r="D97" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
       <x:c r="E97" s="0">
-        <x:v>988848</x:v>
+        <x:v>147892538</x:v>
       </x:c>
       <x:c r="F97" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G97" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H97" s="0">
-        <x:v>12999679000</x:v>
+        <x:v>7257990064</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>0.0033</x:v>
+        <x:v>0.0204</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:9">
       <x:c r="A98" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B98" s="0">
-        <x:v>54.35</x:v>
+        <x:v>48.9</x:v>
       </x:c>
       <x:c r="C98" s="0">
-        <x:v>-0.75</x:v>
+        <x:v>-0.18</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E98" s="0">
-        <x:v>47300000</x:v>
+        <x:v>988848</x:v>
       </x:c>
       <x:c r="F98" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G98" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H98" s="0">
-        <x:v>10597063406</x:v>
+        <x:v>12999679000</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>0.2309</x:v>
+        <x:v>0.0033</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:9">
       <x:c r="A99" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B99" s="0">
-        <x:v>4.26</x:v>
+        <x:v>57.2</x:v>
       </x:c>
       <x:c r="C99" s="0">
-        <x:v>-0.1</x:v>
+        <x:v>2.85</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E99" s="0">
-        <x:v>758600</x:v>
+        <x:v>47300000</x:v>
       </x:c>
       <x:c r="F99" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G99" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H99" s="0">
-        <x:v>1960468575</x:v>
+        <x:v>10597063406</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0.2309</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:9">
       <x:c r="A100" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B100" s="0">
-        <x:v>4.26</x:v>
+        <x:v>4.11</x:v>
       </x:c>
       <x:c r="C100" s="0">
-        <x:v>-0.1</x:v>
+        <x:v>-0.15</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E100" s="0">
         <x:v>758600</x:v>
       </x:c>
       <x:c r="F100" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G100" s="0">
         <x:v>2025.09</x:v>
@@ -3675,259 +3678,259 @@
         <x:v>1960468575</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>0.0004</x:v>
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:9">
       <x:c r="A101" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B101" s="0">
-        <x:v>1120</x:v>
+        <x:v>4.11</x:v>
       </x:c>
       <x:c r="C101" s="0">
-        <x:v>57</x:v>
+        <x:v>-0.15</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E101" s="0">
-        <x:v>576665</x:v>
+        <x:v>758600</x:v>
       </x:c>
       <x:c r="F101" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="G101" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H101" s="0">
-        <x:v>1586603352</x:v>
+        <x:v>1960468575</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>0.0159</x:v>
+        <x:v>0.0004</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:9">
       <x:c r="A102" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B102" s="0">
-        <x:v>81.4</x:v>
+        <x:v>1130</x:v>
       </x:c>
       <x:c r="C102" s="0">
-        <x:v>-2.15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E102" s="0">
-        <x:v>8000000</x:v>
+        <x:v>576665</x:v>
       </x:c>
       <x:c r="F102" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G102" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H102" s="0">
-        <x:v>20999579110</x:v>
+        <x:v>1586603352</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>0.0166</x:v>
+        <x:v>0.0159</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:9">
       <x:c r="A103" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B103" s="0">
-        <x:v>92.4</x:v>
+        <x:v>81.8</x:v>
       </x:c>
       <x:c r="C103" s="0">
-        <x:v>-2.15</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E103" s="0">
-        <x:v>850000</x:v>
+        <x:v>8000000</x:v>
       </x:c>
       <x:c r="F103" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G103" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H103" s="0">
-        <x:v>1781510191</x:v>
+        <x:v>20999579110</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>0.0208</x:v>
+        <x:v>0.0166</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:9">
       <x:c r="A104" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B104" s="0">
-        <x:v>15.95</x:v>
+        <x:v>93.95</x:v>
       </x:c>
       <x:c r="C104" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>1.55</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
         <x:v>98</x:v>
       </x:c>
       <x:c r="E104" s="0">
-        <x:v>10149200</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="F104" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G104" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H104" s="0">
-        <x:v>2020891371</x:v>
+        <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I104" s="0">
-        <x:v>0.2601</x:v>
+        <x:v>0.0208</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:9">
       <x:c r="A105" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B105" s="0">
-        <x:v>120.8</x:v>
+        <x:v>15.85</x:v>
       </x:c>
       <x:c r="C105" s="0">
-        <x:v>3.9</x:v>
+        <x:v>-0.1</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E105" s="0">
-        <x:v>10500000</x:v>
+        <x:v>10149200</x:v>
       </x:c>
       <x:c r="F105" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G105" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H105" s="0">
-        <x:v>1742315226</x:v>
+        <x:v>2020891371</x:v>
       </x:c>
       <x:c r="I105" s="0">
-        <x:v>0.3121</x:v>
+        <x:v>0.2601</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:9">
       <x:c r="A106" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B106" s="0">
-        <x:v>92.4</x:v>
+        <x:v>117.2</x:v>
       </x:c>
       <x:c r="C106" s="0">
-        <x:v>-2.15</x:v>
+        <x:v>-3.6</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
         <x:v>99</x:v>
       </x:c>
       <x:c r="E106" s="0">
-        <x:v>366956541</x:v>
+        <x:v>10500000</x:v>
       </x:c>
       <x:c r="F106" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G106" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H106" s="0">
-        <x:v>1781510191</x:v>
+        <x:v>1742315226</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>0.206</x:v>
+        <x:v>0.3121</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:9">
       <x:c r="A107" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B107" s="0">
-        <x:v>58.35</x:v>
+        <x:v>93.95</x:v>
       </x:c>
       <x:c r="C107" s="0">
-        <x:v>-1.65</x:v>
+        <x:v>1.55</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E107" s="0">
-        <x:v>61158155</x:v>
+        <x:v>366956541</x:v>
       </x:c>
       <x:c r="F107" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G107" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H107" s="0">
-        <x:v>7257990064</x:v>
+        <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>0.0084</x:v>
+        <x:v>0.206</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:9">
       <x:c r="A108" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B108" s="0">
+        <x:v>58.2</x:v>
+      </x:c>
+      <x:c r="C108" s="0">
+        <x:v>-0.15</x:v>
+      </x:c>
+      <x:c r="D108" s="0" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="B108" s="0">
-        <x:v>104.8</x:v>
-      </x:c>
-      <x:c r="C108" s="0">
-        <x:v>-1.1</x:v>
-      </x:c>
-      <x:c r="D108" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
       <x:c r="E108" s="0">
-        <x:v>1000000</x:v>
+        <x:v>61158155</x:v>
       </x:c>
       <x:c r="F108" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G108" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H108" s="0">
-        <x:v>1688731509</x:v>
+        <x:v>7257990064</x:v>
       </x:c>
       <x:c r="I108" s="0">
-        <x:v>0.0307</x:v>
+        <x:v>0.0084</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:9">
       <x:c r="A109" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B109" s="0">
+        <x:v>105.2</x:v>
+      </x:c>
+      <x:c r="C109" s="0">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="D109" s="0" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="B109" s="0">
-        <x:v>104.8</x:v>
-      </x:c>
-      <x:c r="C109" s="0">
-        <x:v>-1.1</x:v>
-      </x:c>
-      <x:c r="D109" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
       <x:c r="E109" s="0">
-        <x:v>1050000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="F109" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G109" s="0">
         <x:v>2025.09</x:v>
@@ -3936,7 +3939,7 @@
         <x:v>1688731509</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>0.0271</x:v>
+        <x:v>0.0307</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:9">
@@ -3944,16 +3947,16 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="B110" s="0">
-        <x:v>42.28</x:v>
+        <x:v>105.2</x:v>
       </x:c>
       <x:c r="C110" s="0">
-        <x:v>-1.36</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E110" s="0">
-        <x:v>109053804</x:v>
+        <x:v>1050000</x:v>
       </x:c>
       <x:c r="F110" s="0" t="s">
         <x:v>11</x:v>
@@ -3962,114 +3965,114 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H110" s="0">
-        <x:v>1942491524</x:v>
+        <x:v>1688731509</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>0.0561</x:v>
+        <x:v>0.0271</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:9">
       <x:c r="A111" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B111" s="0">
+        <x:v>41.06</x:v>
+      </x:c>
+      <x:c r="C111" s="0">
+        <x:v>-1.22</x:v>
+      </x:c>
+      <x:c r="D111" s="0" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="B111" s="0">
-        <x:v>10.3</x:v>
-      </x:c>
-      <x:c r="C111" s="0">
-        <x:v>-0.34</x:v>
-      </x:c>
-      <x:c r="D111" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
       <x:c r="E111" s="0">
-        <x:v>62315119</x:v>
+        <x:v>109053804</x:v>
       </x:c>
       <x:c r="F111" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G111" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H111" s="0">
-        <x:v>12026414029</x:v>
+        <x:v>1942491524</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>0.2257</x:v>
+        <x:v>0.0561</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:9">
       <x:c r="A112" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B112" s="0">
-        <x:v>222.6</x:v>
+        <x:v>10.43</x:v>
       </x:c>
       <x:c r="C112" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.13</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E112" s="0">
-        <x:v>896400</x:v>
+        <x:v>62315119</x:v>
       </x:c>
       <x:c r="F112" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G112" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H112" s="0">
-        <x:v>1364716456</x:v>
+        <x:v>12026414029</x:v>
       </x:c>
       <x:c r="I112" s="0">
-        <x:v>0.0285</x:v>
+        <x:v>0.2257</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:9">
       <x:c r="A113" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B113" s="0">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="C113" s="0">
+        <x:v>-5.6</x:v>
+      </x:c>
+      <x:c r="D113" s="0" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="B113" s="0">
-        <x:v>308.75</x:v>
-      </x:c>
-      <x:c r="C113" s="0">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D113" s="0" t="s">
-        <x:v>107</x:v>
-      </x:c>
       <x:c r="E113" s="0">
-        <x:v>3370000</x:v>
+        <x:v>896400</x:v>
       </x:c>
       <x:c r="F113" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G113" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H113" s="0">
-        <x:v>1865697176</x:v>
+        <x:v>1364716456</x:v>
       </x:c>
       <x:c r="I113" s="0">
-        <x:v>0.0785</x:v>
+        <x:v>0.0285</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:9">
       <x:c r="A114" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B114" s="0">
-        <x:v>49.2</x:v>
+        <x:v>339.5</x:v>
       </x:c>
       <x:c r="C114" s="0">
-        <x:v>-0.14</x:v>
+        <x:v>30.75</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
         <x:v>108</x:v>
       </x:c>
       <x:c r="E114" s="0">
-        <x:v>750561215</x:v>
+        <x:v>3370000</x:v>
       </x:c>
       <x:c r="F114" s="0" t="s">
         <x:v>11</x:v>
@@ -4078,146 +4081,146 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H114" s="0">
-        <x:v>16507905000</x:v>
+        <x:v>1865697176</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>0.0455</x:v>
+        <x:v>0.0785</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:9">
       <x:c r="A115" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B115" s="0">
-        <x:v>81.4</x:v>
+        <x:v>48.2</x:v>
       </x:c>
       <x:c r="C115" s="0">
-        <x:v>-2.15</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E115" s="0">
-        <x:v>20000000</x:v>
+        <x:v>750561215</x:v>
       </x:c>
       <x:c r="F115" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G115" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H115" s="0">
-        <x:v>20999579110</x:v>
+        <x:v>16507905000</x:v>
       </x:c>
       <x:c r="I115" s="0">
-        <x:v>0.0413</x:v>
+        <x:v>0.0455</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:9">
       <x:c r="A116" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B116" s="0">
+        <x:v>81.8</x:v>
+      </x:c>
+      <x:c r="C116" s="0">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="D116" s="0" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="B116" s="0">
-        <x:v>34.56</x:v>
-      </x:c>
-      <x:c r="C116" s="0">
-        <x:v>0.18</x:v>
-      </x:c>
-      <x:c r="D116" s="0" t="s">
-        <x:v>110</x:v>
-      </x:c>
       <x:c r="E116" s="0">
-        <x:v>750000000</x:v>
+        <x:v>20000000</x:v>
       </x:c>
       <x:c r="F116" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G116" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H116" s="0">
-        <x:v>0</x:v>
+        <x:v>20999579110</x:v>
       </x:c>
       <x:c r="I116" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0413</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:9">
       <x:c r="A117" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B117" s="0">
-        <x:v>54.35</x:v>
+        <x:v>32.98</x:v>
       </x:c>
       <x:c r="C117" s="0">
-        <x:v>-0.75</x:v>
+        <x:v>-1.58</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E117" s="0">
-        <x:v>111232418</x:v>
+        <x:v>750000000</x:v>
       </x:c>
       <x:c r="F117" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G117" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H117" s="0">
-        <x:v>10597063406</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>0.4554</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:9">
       <x:c r="A118" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B118" s="0">
-        <x:v>34.4</x:v>
+        <x:v>57.2</x:v>
       </x:c>
       <x:c r="C118" s="0">
-        <x:v>-1.12</x:v>
+        <x:v>2.85</x:v>
       </x:c>
       <x:c r="D118" s="0" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="E118" s="0">
-        <x:v>51384996</x:v>
+        <x:v>111232418</x:v>
       </x:c>
       <x:c r="F118" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G118" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H118" s="0">
-        <x:v>11899043692</x:v>
+        <x:v>10597063406</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>0.1873</x:v>
+        <x:v>0.4554</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:9">
       <x:c r="A119" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B119" s="0">
-        <x:v>34.4</x:v>
+        <x:v>36.44</x:v>
       </x:c>
       <x:c r="C119" s="0">
-        <x:v>-1.12</x:v>
+        <x:v>2.04</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E119" s="0">
-        <x:v>3602451</x:v>
+        <x:v>51384996</x:v>
       </x:c>
       <x:c r="F119" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G119" s="0">
         <x:v>2025.09</x:v>
@@ -4226,27 +4229,27 @@
         <x:v>11899043692</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>0.0131</x:v>
+        <x:v>0.1873</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:9">
       <x:c r="A120" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B120" s="0">
-        <x:v>34.4</x:v>
+        <x:v>36.44</x:v>
       </x:c>
       <x:c r="C120" s="0">
-        <x:v>-1.12</x:v>
+        <x:v>2.04</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E120" s="0">
-        <x:v>24226465</x:v>
+        <x:v>3602451</x:v>
       </x:c>
       <x:c r="F120" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G120" s="0">
         <x:v>2025.09</x:v>
@@ -4255,24 +4258,24 @@
         <x:v>11899043692</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>0.0883</x:v>
+        <x:v>0.0131</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:9">
       <x:c r="A121" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B121" s="0">
-        <x:v>48.5</x:v>
+        <x:v>36.44</x:v>
       </x:c>
       <x:c r="C121" s="0">
-        <x:v>-1</x:v>
+        <x:v>2.04</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E121" s="0">
-        <x:v>12900000</x:v>
+        <x:v>24226465</x:v>
       </x:c>
       <x:c r="F121" s="0" t="s">
         <x:v>11</x:v>
@@ -4281,201 +4284,201 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H121" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>11899043692</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>0.0052</x:v>
+        <x:v>0.0883</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:9">
       <x:c r="A122" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B122" s="0">
-        <x:v>254.75</x:v>
+        <x:v>51.35</x:v>
       </x:c>
       <x:c r="C122" s="0">
-        <x:v>11.15</x:v>
+        <x:v>2.85</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E122" s="0">
-        <x:v>53250000</x:v>
+        <x:v>12900000</x:v>
       </x:c>
       <x:c r="F122" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G122" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H122" s="0">
-        <x:v>24073631758</x:v>
+        <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>0.115</x:v>
+        <x:v>0.0052</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:9">
       <x:c r="A123" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B123" s="0">
-        <x:v>28.8</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="C123" s="0">
-        <x:v>-0.04</x:v>
+        <x:v>9.25</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E123" s="0">
-        <x:v>6860140</x:v>
+        <x:v>53250000</x:v>
       </x:c>
       <x:c r="F123" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G123" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H123" s="0">
-        <x:v>0</x:v>
+        <x:v>24073631758</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>0</x:v>
+        <x:v>0.115</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:9">
       <x:c r="A124" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B124" s="0">
-        <x:v>82.05</x:v>
+        <x:v>28.5</x:v>
       </x:c>
       <x:c r="C124" s="0">
-        <x:v>-0.75</x:v>
+        <x:v>-0.3</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
         <x:v>112</x:v>
       </x:c>
       <x:c r="E124" s="0">
-        <x:v>230000000</x:v>
+        <x:v>6860140</x:v>
       </x:c>
       <x:c r="F124" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G124" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H124" s="0">
-        <x:v>2941310980</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>0.0782</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:9">
       <x:c r="A125" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B125" s="0">
-        <x:v>308.75</x:v>
+        <x:v>83.2</x:v>
       </x:c>
       <x:c r="C125" s="0">
-        <x:v>28</x:v>
+        <x:v>1.15</x:v>
       </x:c>
       <x:c r="D125" s="0" t="s">
         <x:v>113</x:v>
       </x:c>
       <x:c r="E125" s="0">
-        <x:v>4700000</x:v>
+        <x:v>230000000</x:v>
       </x:c>
       <x:c r="F125" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G125" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H125" s="0">
-        <x:v>1865697176</x:v>
+        <x:v>2941310980</x:v>
       </x:c>
       <x:c r="I125" s="0">
-        <x:v>0.1092</x:v>
+        <x:v>0.0782</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:9">
       <x:c r="A126" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B126" s="0">
-        <x:v>28.8</x:v>
+        <x:v>339.5</x:v>
       </x:c>
       <x:c r="C126" s="0">
-        <x:v>-0.04</x:v>
+        <x:v>30.75</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="E126" s="0">
-        <x:v>256000000</x:v>
+        <x:v>4700000</x:v>
       </x:c>
       <x:c r="F126" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G126" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H126" s="0">
-        <x:v>0</x:v>
+        <x:v>1865697176</x:v>
       </x:c>
       <x:c r="I126" s="0">
-        <x:v>0</x:v>
+        <x:v>0.1092</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:9">
       <x:c r="A127" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B127" s="0">
-        <x:v>34.4</x:v>
+        <x:v>28.5</x:v>
       </x:c>
       <x:c r="C127" s="0">
-        <x:v>-1.12</x:v>
+        <x:v>-0.3</x:v>
       </x:c>
       <x:c r="D127" s="0" t="s">
         <x:v>114</x:v>
       </x:c>
       <x:c r="E127" s="0">
-        <x:v>10724896</x:v>
+        <x:v>256000000</x:v>
       </x:c>
       <x:c r="F127" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G127" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H127" s="0">
-        <x:v>11899043692</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>0.039</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:9">
       <x:c r="A128" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B128" s="0">
-        <x:v>24.16</x:v>
+        <x:v>36.44</x:v>
       </x:c>
       <x:c r="C128" s="0">
-        <x:v>-0.56</x:v>
+        <x:v>2.04</x:v>
       </x:c>
       <x:c r="D128" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E128" s="0">
-        <x:v>31000000</x:v>
+        <x:v>10724896</x:v>
       </x:c>
       <x:c r="F128" s="0" t="s">
         <x:v>11</x:v>
@@ -4484,56 +4487,56 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H128" s="0">
-        <x:v>813967617</x:v>
+        <x:v>11899043692</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>0.0381</x:v>
+        <x:v>0.039</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:9">
       <x:c r="A129" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B129" s="0">
-        <x:v>40.76</x:v>
+        <x:v>24.3</x:v>
       </x:c>
       <x:c r="C129" s="0">
-        <x:v>0.44</x:v>
+        <x:v>0.14</x:v>
       </x:c>
       <x:c r="D129" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E129" s="0">
-        <x:v>13500000</x:v>
+        <x:v>31000000</x:v>
       </x:c>
       <x:c r="F129" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G129" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H129" s="0">
-        <x:v>6483809984</x:v>
+        <x:v>813967617</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>0.09</x:v>
+        <x:v>0.0381</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:9">
       <x:c r="A130" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B130" s="0">
-        <x:v>42.28</x:v>
+        <x:v>41.02</x:v>
       </x:c>
       <x:c r="C130" s="0">
-        <x:v>-1.36</x:v>
+        <x:v>0.26</x:v>
       </x:c>
       <x:c r="D130" s="0" t="s">
         <x:v>115</x:v>
       </x:c>
       <x:c r="E130" s="0">
-        <x:v>29886357</x:v>
+        <x:v>13500000</x:v>
       </x:c>
       <x:c r="F130" s="0" t="s">
         <x:v>11</x:v>
@@ -4542,172 +4545,172 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H130" s="0">
-        <x:v>1942491524</x:v>
+        <x:v>6483809984</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>0.0154</x:v>
+        <x:v>0.09</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:9">
       <x:c r="A131" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B131" s="0">
-        <x:v>414.5</x:v>
+        <x:v>41.06</x:v>
       </x:c>
       <x:c r="C131" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>-1.22</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E131" s="0">
-        <x:v>171000000</x:v>
+        <x:v>29886357</x:v>
       </x:c>
       <x:c r="F131" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G131" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H131" s="0">
-        <x:v>130147715000</x:v>
+        <x:v>1942491524</x:v>
       </x:c>
       <x:c r="I131" s="0">
-        <x:v>0.0568</x:v>
+        <x:v>0.0154</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:9">
       <x:c r="A132" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B132" s="0">
-        <x:v>120.8</x:v>
+        <x:v>425.5</x:v>
       </x:c>
       <x:c r="C132" s="0">
-        <x:v>3.9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E132" s="0">
-        <x:v>1890000</x:v>
+        <x:v>171000000</x:v>
       </x:c>
       <x:c r="F132" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G132" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H132" s="0">
-        <x:v>1742315226</x:v>
+        <x:v>130147715000</x:v>
       </x:c>
       <x:c r="I132" s="0">
-        <x:v>0.0549</x:v>
+        <x:v>0.0568</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:9">
       <x:c r="A133" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B133" s="0">
+        <x:v>117.2</x:v>
+      </x:c>
+      <x:c r="C133" s="0">
+        <x:v>-3.6</x:v>
+      </x:c>
+      <x:c r="D133" s="0" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="B133" s="0">
-        <x:v>13.4</x:v>
-      </x:c>
-      <x:c r="C133" s="0">
-        <x:v>-0.51</x:v>
-      </x:c>
-      <x:c r="D133" s="0" t="s">
-        <x:v>115</x:v>
-      </x:c>
       <x:c r="E133" s="0">
-        <x:v>892825</x:v>
+        <x:v>1890000</x:v>
       </x:c>
       <x:c r="F133" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G133" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H133" s="0">
-        <x:v>3015442704</x:v>
+        <x:v>1742315226</x:v>
       </x:c>
       <x:c r="I133" s="0">
-        <x:v>0.0128</x:v>
+        <x:v>0.0549</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:9">
       <x:c r="A134" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B134" s="0">
-        <x:v>48.5</x:v>
+        <x:v>13.13</x:v>
       </x:c>
       <x:c r="C134" s="0">
-        <x:v>-1</x:v>
+        <x:v>-0.27</x:v>
       </x:c>
       <x:c r="D134" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E134" s="0">
-        <x:v>361176</x:v>
+        <x:v>892825</x:v>
       </x:c>
       <x:c r="F134" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G134" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H134" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>3015442704</x:v>
       </x:c>
       <x:c r="I134" s="0">
-        <x:v>0.0063</x:v>
+        <x:v>0.0128</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:9">
       <x:c r="A135" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B135" s="0">
-        <x:v>26</x:v>
+        <x:v>51.35</x:v>
       </x:c>
       <x:c r="C135" s="0">
-        <x:v>-0.34</x:v>
+        <x:v>2.85</x:v>
       </x:c>
       <x:c r="D135" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E135" s="0">
-        <x:v>1060000</x:v>
+        <x:v>361176</x:v>
       </x:c>
       <x:c r="F135" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G135" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H135" s="0">
-        <x:v>1194839266</x:v>
+        <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I135" s="0">
-        <x:v>0.0384</x:v>
+        <x:v>0.0063</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:9">
       <x:c r="A136" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="B136" s="0">
+        <x:v>25.56</x:v>
+      </x:c>
+      <x:c r="C136" s="0">
+        <x:v>-0.44</x:v>
+      </x:c>
+      <x:c r="D136" s="0" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="B136" s="0">
-        <x:v>51.75</x:v>
-      </x:c>
-      <x:c r="C136" s="0">
-        <x:v>-0.75</x:v>
-      </x:c>
-      <x:c r="D136" s="0" t="s">
-        <x:v>118</x:v>
-      </x:c>
       <x:c r="E136" s="0">
-        <x:v>259417800</x:v>
+        <x:v>1060000</x:v>
       </x:c>
       <x:c r="F136" s="0" t="s">
         <x:v>11</x:v>
@@ -4716,59 +4719,59 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H136" s="0">
-        <x:v>2741117556</x:v>
+        <x:v>1194839266</x:v>
       </x:c>
       <x:c r="I136" s="0">
-        <x:v>0.0946</x:v>
+        <x:v>0.0384</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:9">
       <x:c r="A137" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B137" s="0">
-        <x:v>59.85</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C137" s="0">
-        <x:v>-1.15</x:v>
+        <x:v>1.25</x:v>
       </x:c>
       <x:c r="D137" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E137" s="0">
-        <x:v>523788</x:v>
+        <x:v>259417800</x:v>
       </x:c>
       <x:c r="F137" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G137" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H137" s="0">
-        <x:v>832031190</x:v>
+        <x:v>2741117556</x:v>
       </x:c>
       <x:c r="I137" s="0">
-        <x:v>0.0272</x:v>
+        <x:v>0.0946</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:9">
       <x:c r="A138" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B138" s="0">
-        <x:v>59.85</x:v>
+        <x:v>60.3</x:v>
       </x:c>
       <x:c r="C138" s="0">
-        <x:v>-1.15</x:v>
+        <x:v>0.45</x:v>
       </x:c>
       <x:c r="D138" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E138" s="0">
-        <x:v>1415270</x:v>
+        <x:v>523788</x:v>
       </x:c>
       <x:c r="F138" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G138" s="0">
         <x:v>2025.09</x:v>
@@ -4777,256 +4780,256 @@
         <x:v>832031190</x:v>
       </x:c>
       <x:c r="I138" s="0">
-        <x:v>0.0736</x:v>
+        <x:v>0.0272</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:9">
       <x:c r="A139" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B139" s="0">
-        <x:v>81.4</x:v>
+        <x:v>60.3</x:v>
       </x:c>
       <x:c r="C139" s="0">
-        <x:v>-2.15</x:v>
+        <x:v>0.45</x:v>
       </x:c>
       <x:c r="D139" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E139" s="0">
-        <x:v>25000000</x:v>
+        <x:v>1415270</x:v>
       </x:c>
       <x:c r="F139" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G139" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H139" s="0">
-        <x:v>20999579110</x:v>
+        <x:v>832031190</x:v>
       </x:c>
       <x:c r="I139" s="0">
-        <x:v>0.0515</x:v>
+        <x:v>0.0736</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:9">
       <x:c r="A140" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B140" s="0">
-        <x:v>5.35</x:v>
+        <x:v>81.8</x:v>
       </x:c>
       <x:c r="C140" s="0">
-        <x:v>-0.18</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="D140" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E140" s="0">
-        <x:v>25000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="F140" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G140" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H140" s="0">
-        <x:v>1627872951</x:v>
+        <x:v>20999579110</x:v>
       </x:c>
       <x:c r="I140" s="0">
-        <x:v>0.0007</x:v>
+        <x:v>0.0515</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:9">
       <x:c r="A141" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B141" s="0">
+        <x:v>5.34</x:v>
+      </x:c>
+      <x:c r="C141" s="0">
+        <x:v>-0.01</x:v>
+      </x:c>
+      <x:c r="D141" s="0" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="B141" s="0">
-        <x:v>19.82</x:v>
-      </x:c>
-      <x:c r="C141" s="0">
-        <x:v>-0.38</x:v>
-      </x:c>
-      <x:c r="D141" s="0" t="s">
-        <x:v>120</x:v>
-      </x:c>
       <x:c r="E141" s="0">
-        <x:v>1500000</x:v>
+        <x:v>25000</x:v>
       </x:c>
       <x:c r="F141" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G141" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H141" s="0">
-        <x:v>774677961</x:v>
+        <x:v>1627872951</x:v>
       </x:c>
       <x:c r="I141" s="0">
-        <x:v>0.0019</x:v>
+        <x:v>0.0007</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:9">
       <x:c r="A142" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B142" s="0">
-        <x:v>7.32</x:v>
+        <x:v>20.02</x:v>
       </x:c>
       <x:c r="C142" s="0">
-        <x:v>-0.31</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="D142" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E142" s="0">
-        <x:v>13833310</x:v>
+        <x:v>1500000</x:v>
       </x:c>
       <x:c r="F142" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G142" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H142" s="0">
-        <x:v>9028523851</x:v>
+        <x:v>774677961</x:v>
       </x:c>
       <x:c r="I142" s="0">
-        <x:v>0.0776</x:v>
+        <x:v>0.0019</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:9">
       <x:c r="A143" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B143" s="0">
-        <x:v>70</x:v>
+        <x:v>7.38</x:v>
       </x:c>
       <x:c r="C143" s="0">
-        <x:v>-1.8</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="D143" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E143" s="0">
-        <x:v>3419000</x:v>
+        <x:v>13833310</x:v>
       </x:c>
       <x:c r="F143" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G143" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H143" s="0">
-        <x:v>3895315496</x:v>
+        <x:v>9028523851</x:v>
       </x:c>
       <x:c r="I143" s="0">
-        <x:v>0.0379</x:v>
+        <x:v>0.0776</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:9">
       <x:c r="A144" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B144" s="0">
-        <x:v>308.75</x:v>
+        <x:v>70.5</x:v>
       </x:c>
       <x:c r="C144" s="0">
-        <x:v>28</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="D144" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="E144" s="0">
-        <x:v>3700000</x:v>
+        <x:v>3419000</x:v>
       </x:c>
       <x:c r="F144" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G144" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H144" s="0">
-        <x:v>1865697176</x:v>
+        <x:v>3895315496</x:v>
       </x:c>
       <x:c r="I144" s="0">
-        <x:v>0.0857</x:v>
+        <x:v>0.0379</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:9">
       <x:c r="A145" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B145" s="0">
-        <x:v>40.76</x:v>
+        <x:v>339.5</x:v>
       </x:c>
       <x:c r="C145" s="0">
-        <x:v>0.44</x:v>
+        <x:v>30.75</x:v>
       </x:c>
       <x:c r="D145" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="E145" s="0">
-        <x:v>16000000</x:v>
+        <x:v>3700000</x:v>
       </x:c>
       <x:c r="F145" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G145" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H145" s="0">
-        <x:v>6483809984</x:v>
+        <x:v>1865697176</x:v>
       </x:c>
       <x:c r="I145" s="0">
-        <x:v>0.1067</x:v>
+        <x:v>0.0857</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:9">
       <x:c r="A146" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B146" s="0">
-        <x:v>48.5</x:v>
+        <x:v>41.02</x:v>
       </x:c>
       <x:c r="C146" s="0">
-        <x:v>-1</x:v>
+        <x:v>0.26</x:v>
       </x:c>
       <x:c r="D146" s="0" t="s">
         <x:v>123</x:v>
       </x:c>
       <x:c r="E146" s="0">
-        <x:v>906840</x:v>
+        <x:v>16000000</x:v>
       </x:c>
       <x:c r="F146" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G146" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H146" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>6483809984</x:v>
       </x:c>
       <x:c r="I146" s="0">
-        <x:v>0.0159</x:v>
+        <x:v>0.1067</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:9">
       <x:c r="A147" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B147" s="0">
-        <x:v>3.3</x:v>
+        <x:v>51.35</x:v>
       </x:c>
       <x:c r="C147" s="0">
-        <x:v>-0.1</x:v>
+        <x:v>2.85</x:v>
       </x:c>
       <x:c r="D147" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E147" s="0">
-        <x:v>895039950</x:v>
+        <x:v>906840</x:v>
       </x:c>
       <x:c r="F147" s="0" t="s">
         <x:v>11</x:v>
@@ -5035,172 +5038,172 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H147" s="0">
-        <x:v>7382591324</x:v>
+        <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I147" s="0">
-        <x:v>0.1212</x:v>
+        <x:v>0.0159</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:9">
       <x:c r="A148" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B148" s="0">
-        <x:v>51.75</x:v>
+        <x:v>3.28</x:v>
       </x:c>
       <x:c r="C148" s="0">
-        <x:v>-0.75</x:v>
+        <x:v>-0.02</x:v>
       </x:c>
       <x:c r="D148" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E148" s="0">
-        <x:v>575933040</x:v>
+        <x:v>895039950</x:v>
       </x:c>
       <x:c r="F148" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G148" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H148" s="0">
-        <x:v>2741117556</x:v>
+        <x:v>7382591324</x:v>
       </x:c>
       <x:c r="I148" s="0">
-        <x:v>0.2101</x:v>
+        <x:v>0.1212</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:9">
       <x:c r="A149" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="B149" s="0">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C149" s="0">
+        <x:v>1.25</x:v>
+      </x:c>
+      <x:c r="D149" s="0" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="B149" s="0">
-        <x:v>12.49</x:v>
-      </x:c>
-      <x:c r="C149" s="0">
-        <x:v>0.24</x:v>
-      </x:c>
-      <x:c r="D149" s="0" t="s">
-        <x:v>123</x:v>
-      </x:c>
       <x:c r="E149" s="0">
-        <x:v>559000</x:v>
+        <x:v>575933040</x:v>
       </x:c>
       <x:c r="F149" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G149" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H149" s="0">
-        <x:v>2865374550</x:v>
+        <x:v>2741117556</x:v>
       </x:c>
       <x:c r="I149" s="0">
-        <x:v>0.0084</x:v>
+        <x:v>0.2101</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:9">
       <x:c r="A150" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B150" s="0">
-        <x:v>49.2</x:v>
+        <x:v>12.19</x:v>
       </x:c>
       <x:c r="C150" s="0">
-        <x:v>-0.14</x:v>
+        <x:v>-0.3</x:v>
       </x:c>
       <x:c r="D150" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E150" s="0">
-        <x:v>8900056</x:v>
+        <x:v>559000</x:v>
       </x:c>
       <x:c r="F150" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G150" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H150" s="0">
-        <x:v>16507905000</x:v>
+        <x:v>2865374550</x:v>
       </x:c>
       <x:c r="I150" s="0">
-        <x:v>0.0233</x:v>
+        <x:v>0.0084</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:9">
       <x:c r="A151" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B151" s="0">
-        <x:v>254.75</x:v>
+        <x:v>48.2</x:v>
       </x:c>
       <x:c r="C151" s="0">
-        <x:v>11.15</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="D151" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E151" s="0">
-        <x:v>164306000</x:v>
+        <x:v>8900056</x:v>
       </x:c>
       <x:c r="F151" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G151" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H151" s="0">
-        <x:v>24073631758</x:v>
+        <x:v>16507905000</x:v>
       </x:c>
       <x:c r="I151" s="0">
-        <x:v>0.2943</x:v>
+        <x:v>0.0233</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:9">
       <x:c r="A152" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B152" s="0">
-        <x:v>53.8</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="C152" s="0">
-        <x:v>-3</x:v>
+        <x:v>9.25</x:v>
       </x:c>
       <x:c r="D152" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E152" s="0">
-        <x:v>275000</x:v>
+        <x:v>164306000</x:v>
       </x:c>
       <x:c r="F152" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G152" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H152" s="0">
-        <x:v>580678850</x:v>
+        <x:v>24073631758</x:v>
       </x:c>
       <x:c r="I152" s="0">
-        <x:v>0.0204</x:v>
+        <x:v>0.2943</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:9">
       <x:c r="A153" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B153" s="0">
-        <x:v>51.75</x:v>
+        <x:v>55.95</x:v>
       </x:c>
       <x:c r="C153" s="0">
-        <x:v>-0.75</x:v>
+        <x:v>2.15</x:v>
       </x:c>
       <x:c r="D153" s="0" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="E153" s="0">
-        <x:v>231651480</x:v>
+        <x:v>275000</x:v>
       </x:c>
       <x:c r="F153" s="0" t="s">
         <x:v>11</x:v>
@@ -5209,56 +5212,56 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H153" s="0">
-        <x:v>2741117556</x:v>
+        <x:v>580678850</x:v>
       </x:c>
       <x:c r="I153" s="0">
-        <x:v>0.0845</x:v>
+        <x:v>0.0204</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:9">
       <x:c r="A154" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B154" s="0">
-        <x:v>14.91</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C154" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>1.25</x:v>
       </x:c>
       <x:c r="D154" s="0" t="s">
         <x:v>128</x:v>
       </x:c>
       <x:c r="E154" s="0">
-        <x:v>31860000</x:v>
+        <x:v>231651480</x:v>
       </x:c>
       <x:c r="F154" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G154" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H154" s="0">
-        <x:v>3025063909</x:v>
+        <x:v>2741117556</x:v>
       </x:c>
       <x:c r="I154" s="0">
-        <x:v>0.4539</x:v>
+        <x:v>0.0845</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:9">
       <x:c r="A155" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B155" s="0">
-        <x:v>92.4</x:v>
+        <x:v>14.86</x:v>
       </x:c>
       <x:c r="C155" s="0">
-        <x:v>-2.15</x:v>
+        <x:v>-0.05</x:v>
       </x:c>
       <x:c r="D155" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="E155" s="0">
-        <x:v>41650000</x:v>
+        <x:v>31860000</x:v>
       </x:c>
       <x:c r="F155" s="0" t="s">
         <x:v>11</x:v>
@@ -5267,126 +5270,126 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H155" s="0">
-        <x:v>1781510191</x:v>
+        <x:v>3025063909</x:v>
       </x:c>
       <x:c r="I155" s="0">
-        <x:v>0.0234</x:v>
+        <x:v>0.4539</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:9">
       <x:c r="A156" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B156" s="0">
-        <x:v>15.95</x:v>
+        <x:v>93.95</x:v>
       </x:c>
       <x:c r="C156" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>1.55</x:v>
       </x:c>
       <x:c r="D156" s="0" t="s">
         <x:v>129</x:v>
       </x:c>
       <x:c r="E156" s="0">
-        <x:v>815000</x:v>
+        <x:v>41650000</x:v>
       </x:c>
       <x:c r="F156" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G156" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H156" s="0">
-        <x:v>2020891371</x:v>
+        <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I156" s="0">
-        <x:v>0.0202</x:v>
+        <x:v>0.0234</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:9">
       <x:c r="A157" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B157" s="0">
-        <x:v>82.05</x:v>
+        <x:v>15.85</x:v>
       </x:c>
       <x:c r="C157" s="0">
-        <x:v>-0.75</x:v>
+        <x:v>-0.1</x:v>
       </x:c>
       <x:c r="D157" s="0" t="s">
         <x:v>130</x:v>
       </x:c>
       <x:c r="E157" s="0">
-        <x:v>8300000</x:v>
+        <x:v>815000</x:v>
       </x:c>
       <x:c r="F157" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G157" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H157" s="0">
-        <x:v>2941310980</x:v>
+        <x:v>2020891371</x:v>
       </x:c>
       <x:c r="I157" s="0">
-        <x:v>0.1417</x:v>
+        <x:v>0.0202</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:9">
       <x:c r="A158" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B158" s="0">
+        <x:v>83.2</x:v>
+      </x:c>
+      <x:c r="C158" s="0">
+        <x:v>1.15</x:v>
+      </x:c>
+      <x:c r="D158" s="0" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="B158" s="0">
-        <x:v>4.22</x:v>
-      </x:c>
-      <x:c r="C158" s="0">
-        <x:v>-0.08</x:v>
-      </x:c>
-      <x:c r="D158" s="0" t="s">
-        <x:v>132</x:v>
-      </x:c>
       <x:c r="E158" s="0">
-        <x:v>13000000</x:v>
+        <x:v>8300000</x:v>
       </x:c>
       <x:c r="F158" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G158" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H158" s="0">
-        <x:v>1416740879</x:v>
+        <x:v>2941310980</x:v>
       </x:c>
       <x:c r="I158" s="0">
-        <x:v>0.4613</x:v>
+        <x:v>0.1417</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:9">
       <x:c r="A159" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B159" s="0">
-        <x:v>120.8</x:v>
+        <x:v>4.16</x:v>
       </x:c>
       <x:c r="C159" s="0">
-        <x:v>3.9</x:v>
+        <x:v>-0.06</x:v>
       </x:c>
       <x:c r="D159" s="0" t="s">
         <x:v>133</x:v>
       </x:c>
       <x:c r="E159" s="0">
-        <x:v>1999793</x:v>
+        <x:v>13000000</x:v>
       </x:c>
       <x:c r="F159" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G159" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H159" s="0">
-        <x:v>1742315226</x:v>
+        <x:v>1416740879</x:v>
       </x:c>
       <x:c r="I159" s="0">
-        <x:v>0.0494</x:v>
+        <x:v>0.4613</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:9">
@@ -5394,45 +5397,45 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B160" s="0">
-        <x:v>48.5</x:v>
+        <x:v>117.2</x:v>
       </x:c>
       <x:c r="C160" s="0">
-        <x:v>-1</x:v>
+        <x:v>-3.6</x:v>
       </x:c>
       <x:c r="D160" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="E160" s="0">
-        <x:v>1859145</x:v>
+        <x:v>1999793</x:v>
       </x:c>
       <x:c r="F160" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G160" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H160" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>1742315226</x:v>
       </x:c>
       <x:c r="I160" s="0">
-        <x:v>0.0324</x:v>
+        <x:v>0.0494</x:v>
       </x:c>
     </x:row>
     <x:row r="161" spans="1:9">
       <x:c r="A161" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B161" s="0">
-        <x:v>3.3</x:v>
+        <x:v>51.35</x:v>
       </x:c>
       <x:c r="C161" s="0">
-        <x:v>-0.1</x:v>
+        <x:v>2.85</x:v>
       </x:c>
       <x:c r="D161" s="0" t="s">
         <x:v>134</x:v>
       </x:c>
       <x:c r="E161" s="0">
-        <x:v>689661000</x:v>
+        <x:v>1859145</x:v>
       </x:c>
       <x:c r="F161" s="0" t="s">
         <x:v>11</x:v>
@@ -5441,56 +5444,56 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H161" s="0">
-        <x:v>7382591324</x:v>
+        <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I161" s="0">
-        <x:v>0.0934</x:v>
+        <x:v>0.0324</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:9">
       <x:c r="A162" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B162" s="0">
-        <x:v>48.5</x:v>
+        <x:v>3.28</x:v>
       </x:c>
       <x:c r="C162" s="0">
-        <x:v>-1</x:v>
+        <x:v>-0.02</x:v>
       </x:c>
       <x:c r="D162" s="0" t="s">
         <x:v>135</x:v>
       </x:c>
       <x:c r="E162" s="0">
-        <x:v>1902000</x:v>
+        <x:v>689661000</x:v>
       </x:c>
       <x:c r="F162" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G162" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H162" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>7382591324</x:v>
       </x:c>
       <x:c r="I162" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0934</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:9">
       <x:c r="A163" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B163" s="0">
-        <x:v>92.4</x:v>
+        <x:v>51.35</x:v>
       </x:c>
       <x:c r="C163" s="0">
-        <x:v>-2.15</x:v>
+        <x:v>2.85</x:v>
       </x:c>
       <x:c r="D163" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="E163" s="0">
-        <x:v>56520000</x:v>
+        <x:v>1902000</x:v>
       </x:c>
       <x:c r="F163" s="0" t="s">
         <x:v>11</x:v>
@@ -5499,30 +5502,30 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H163" s="0">
-        <x:v>1781510191</x:v>
+        <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I163" s="0">
-        <x:v>0.0317</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="164" spans="1:9">
       <x:c r="A164" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B164" s="0">
-        <x:v>92.4</x:v>
+        <x:v>93.95</x:v>
       </x:c>
       <x:c r="C164" s="0">
-        <x:v>-2.15</x:v>
+        <x:v>1.55</x:v>
       </x:c>
       <x:c r="D164" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="E164" s="0">
-        <x:v>888325</x:v>
+        <x:v>56520000</x:v>
       </x:c>
       <x:c r="F164" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G164" s="0">
         <x:v>2025.09</x:v>
@@ -5531,33 +5534,33 @@
         <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I164" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0317</x:v>
       </x:c>
     </x:row>
     <x:row r="165" spans="1:9">
       <x:c r="A165" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B165" s="0">
-        <x:v>7.32</x:v>
+        <x:v>93.95</x:v>
       </x:c>
       <x:c r="C165" s="0">
-        <x:v>-0.31</x:v>
+        <x:v>1.55</x:v>
       </x:c>
       <x:c r="D165" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="E165" s="0">
-        <x:v>5581810</x:v>
+        <x:v>888325</x:v>
       </x:c>
       <x:c r="F165" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G165" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H165" s="0">
-        <x:v>9028523851</x:v>
+        <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I165" s="0">
         <x:v>0</x:v>
@@ -5565,19 +5568,19 @@
     </x:row>
     <x:row r="166" spans="1:9">
       <x:c r="A166" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B166" s="0">
-        <x:v>48.5</x:v>
+        <x:v>7.38</x:v>
       </x:c>
       <x:c r="C166" s="0">
-        <x:v>-1</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="D166" s="0" t="s">
         <x:v>136</x:v>
       </x:c>
       <x:c r="E166" s="0">
-        <x:v>504000000</x:v>
+        <x:v>5581810</x:v>
       </x:c>
       <x:c r="F166" s="0" t="s">
         <x:v>11</x:v>
@@ -5586,67 +5589,96 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H166" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>9028523851</x:v>
       </x:c>
       <x:c r="I166" s="0">
-        <x:v>0.2043</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="167" spans="1:9">
       <x:c r="A167" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B167" s="0">
-        <x:v>254.75</x:v>
+        <x:v>51.35</x:v>
       </x:c>
       <x:c r="C167" s="0">
-        <x:v>11.15</x:v>
+        <x:v>2.85</x:v>
       </x:c>
       <x:c r="D167" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="E167" s="0">
-        <x:v>21500032</x:v>
+        <x:v>504000000</x:v>
       </x:c>
       <x:c r="F167" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G167" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H167" s="0">
-        <x:v>24073631758</x:v>
+        <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I167" s="0">
-        <x:v>0.0383</x:v>
+        <x:v>0.2043</x:v>
       </x:c>
     </x:row>
     <x:row r="168" spans="1:9">
       <x:c r="A168" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B168" s="0">
-        <x:v>1120</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="C168" s="0">
-        <x:v>57</x:v>
+        <x:v>9.25</x:v>
       </x:c>
       <x:c r="D168" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="E168" s="0">
+        <x:v>21500032</x:v>
+      </x:c>
+      <x:c r="F168" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G168" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H168" s="0">
+        <x:v>24073631758</x:v>
+      </x:c>
+      <x:c r="I168" s="0">
+        <x:v>0.0383</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169" spans="1:9">
+      <x:c r="A169" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B169" s="0">
+        <x:v>1130</x:v>
+      </x:c>
+      <x:c r="C169" s="0">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D169" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="E169" s="0">
         <x:v>6455151</x:v>
       </x:c>
-      <x:c r="F168" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G168" s="0">
-        <x:v>2025.09</x:v>
-      </x:c>
-      <x:c r="H168" s="0">
+      <x:c r="F169" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G169" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H169" s="0">
         <x:v>1586603352</x:v>
       </x:c>
-      <x:c r="I168" s="0">
+      <x:c r="I169" s="0">
         <x:v>0.1745</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/yeni-is-anlasmalari/data/yeni-is-anlasmalari.xlsx
+++ b/app/borsa/yeni-is-anlasmalari/data/yeni-is-anlasmalari.xlsx
@@ -43,15 +43,30 @@
     <x:t>Yeni İş İlişkisi / Yıllık Satışlar</x:t>
   </x:si>
   <x:si>
+    <x:t>ASELS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-04-30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>USD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKHAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BVSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-04-29</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUR</x:t>
+  </x:si>
+  <x:si>
     <x:t>CWENE</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-04-29</x:t>
-  </x:si>
-  <x:si>
-    <x:t>USD</x:t>
-  </x:si>
-  <x:si>
     <x:t>FONET</x:t>
   </x:si>
   <x:si>
@@ -76,12 +91,6 @@
     <x:t>ORGE</x:t>
   </x:si>
   <x:si>
-    <x:t>BVSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUR</x:t>
-  </x:si>
-  <x:si>
     <x:t>ARDYZ</x:t>
   </x:si>
   <x:si>
@@ -220,9 +229,6 @@
     <x:t>2026-03-23</x:t>
   </x:si>
   <x:si>
-    <x:t>AKHAN</x:t>
-  </x:si>
-  <x:si>
     <x:t>2026-03-18</x:t>
   </x:si>
   <x:si>
@@ -230,9 +236,6 @@
   </x:si>
   <x:si>
     <x:t>2026-03-17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASELS</x:t>
   </x:si>
   <x:si>
     <x:t>2026-03-16</x:t>
@@ -778,7 +781,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I169"/>
+  <x:dimension ref="A1:I172"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -815,16 +818,16 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>36.44</x:v>
+        <x:v>420.25</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>2.04</x:v>
+        <x:v>-5.25</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>2136645</x:v>
+        <x:v>125100000</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
         <x:v>11</x:v>
@@ -833,10 +836,10 @@
         <x:v>2026.03</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>17386730041</x:v>
+        <x:v>184925592000</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>0.0055</x:v>
+        <x:v>0.0304</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -844,57 +847,57 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>4.83</x:v>
+        <x:v>28.62</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>-0.18</x:v>
+        <x:v>0.24</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>132077304</x:v>
+        <x:v>76650</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G3" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>855070469</x:v>
+        <x:v>7297855153</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>0.1545</x:v>
+        <x:v>0.0005</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
       <x:c r="A4" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B4" s="0">
+        <x:v>118.6</x:v>
+      </x:c>
+      <x:c r="C4" s="0">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E4" s="0">
+        <x:v>915000</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B4" s="0">
-        <x:v>264</x:v>
-      </x:c>
-      <x:c r="C4" s="0">
-        <x:v>9.25</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E4" s="0">
-        <x:v>51531000</x:v>
-      </x:c>
-      <x:c r="F4" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="G4" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>35290767390</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>0.0656</x:v>
+        <x:v>0.0153</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -902,28 +905,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>1130</x:v>
+        <x:v>36.64</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>10</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>950978</x:v>
+        <x:v>2136645</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2026.03</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>1883544167</x:v>
+        <x:v>17386730041</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>0.0227</x:v>
+        <x:v>0.0055</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -931,86 +934,86 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>556</x:v>
+        <x:v>4.91</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>-4</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>100000000</x:v>
+        <x:v>132077304</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G6" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>71453576000</x:v>
+        <x:v>855070469</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>0.0628</x:v>
+        <x:v>0.1545</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
       <x:c r="A7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>83.2</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>1.15</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>286071819</x:v>
+        <x:v>51531000</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G7" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>35290767390</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>0.0818</x:v>
+        <x:v>0.0656</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
       <x:c r="A8" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>117.2</x:v>
+        <x:v>1139</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>-3.6</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>883793</x:v>
+        <x:v>950978</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G8" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>3150489640</x:v>
+        <x:v>1883544167</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>0.0148</x:v>
+        <x:v>0.0227</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -1018,16 +1021,16 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>51.35</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>2.85</x:v>
+        <x:v>-9</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>606770</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
         <x:v>11</x:v>
@@ -1036,68 +1039,68 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>71453576000</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>0.0064</x:v>
+        <x:v>0.0628</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
       <x:c r="A10" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B10" s="0">
+        <x:v>85.5</x:v>
+      </x:c>
+      <x:c r="C10" s="0">
+        <x:v>2.3</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="B10" s="0">
-        <x:v>58.2</x:v>
-      </x:c>
-      <x:c r="C10" s="0">
-        <x:v>-0.15</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
       <x:c r="E10" s="0">
-        <x:v>505597002</x:v>
+        <x:v>286071819</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G10" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>8121300519</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>0.0623</x:v>
+        <x:v>0.0818</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
       <x:c r="A11" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>51.35</x:v>
+        <x:v>118.6</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>2.85</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>948000</x:v>
+        <x:v>883793</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G11" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>0.0101</x:v>
+        <x:v>0.0148</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -1105,16 +1108,16 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>93.95</x:v>
+        <x:v>50.2</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>1.55</x:v>
+        <x:v>-1.15</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>622000</x:v>
+        <x:v>606770</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
         <x:v>11</x:v>
@@ -1123,10 +1126,10 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>0.0114</x:v>
+        <x:v>0.0064</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -1134,45 +1137,45 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>4.11</x:v>
+        <x:v>58.95</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>-0.15</x:v>
+        <x:v>0.75</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>983000</x:v>
+        <x:v>505597002</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G13" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>2875634546</x:v>
+        <x:v>8121300519</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>0.018</x:v>
+        <x:v>0.0623</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
       <x:c r="A14" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B14" s="0">
+        <x:v>50.2</x:v>
+      </x:c>
+      <x:c r="C14" s="0">
+        <x:v>-1.15</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="B14" s="0">
-        <x:v>70.5</x:v>
-      </x:c>
-      <x:c r="C14" s="0">
-        <x:v>0.5</x:v>
-      </x:c>
-      <x:c r="D14" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
       <x:c r="E14" s="0">
-        <x:v>3421818</x:v>
+        <x:v>948000</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
         <x:v>11</x:v>
@@ -1181,27 +1184,27 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>5948036961</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>0.0257</x:v>
+        <x:v>0.0101</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
       <x:c r="A15" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>45.14</x:v>
+        <x:v>94.4</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>2.26</x:v>
+        <x:v>0.45</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>697435</x:v>
+        <x:v>622000</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
         <x:v>11</x:v>
@@ -1210,56 +1213,56 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>4728937463</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>0.0066</x:v>
+        <x:v>0.0114</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
       <x:c r="A16" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>57.2</x:v>
+        <x:v>4.09</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>2.85</x:v>
+        <x:v>-0.02</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>4587145</x:v>
+        <x:v>983000</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G16" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>16733157490</x:v>
+        <x:v>2875634546</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>0.0123</x:v>
+        <x:v>0.018</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
       <x:c r="A17" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>41.02</x:v>
+        <x:v>74.6</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>0.26</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>43200000</x:v>
+        <x:v>3421818</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
         <x:v>11</x:v>
@@ -1268,85 +1271,85 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>8236540064</x:v>
+        <x:v>5948036961</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>0.2345</x:v>
+        <x:v>0.0257</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
       <x:c r="A18" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>15.85</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>-0.1</x:v>
+        <x:v>-1.14</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>1200000</x:v>
+        <x:v>697435</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G18" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>3139850323</x:v>
+        <x:v>4728937463</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>0.0201</x:v>
+        <x:v>0.0066</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
       <x:c r="A19" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>58.2</x:v>
+        <x:v>55.8</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>-0.15</x:v>
+        <x:v>-1.4</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>247902522</x:v>
+        <x:v>4587145</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G19" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>8121300519</x:v>
+        <x:v>16733157490</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>0.0305</x:v>
+        <x:v>0.0123</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
       <x:c r="A20" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>51.35</x:v>
+        <x:v>41.22</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>2.85</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>366000</x:v>
+        <x:v>43200000</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
         <x:v>11</x:v>
@@ -1355,259 +1358,259 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>8236540064</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>0.0039</x:v>
+        <x:v>0.2345</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
       <x:c r="A21" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>276.75</x:v>
+        <x:v>16.01</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>-11.25</x:v>
+        <x:v>0.16</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>141051834</x:v>
+        <x:v>1200000</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G21" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>709077088</x:v>
+        <x:v>3139850323</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>0.1989</x:v>
+        <x:v>0.0201</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
       <x:c r="A22" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>4.69</x:v>
+        <x:v>58.95</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>-0.04</x:v>
+        <x:v>0.75</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>5096500000</x:v>
+        <x:v>247902522</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>19538660616</x:v>
+        <x:v>8121300519</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>0.2608</x:v>
+        <x:v>0.0305</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
       <x:c r="A23" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>4.69</x:v>
+        <x:v>50.2</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>-0.04</x:v>
+        <x:v>-1.15</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>5096500000</x:v>
+        <x:v>366000</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>19538660616</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>0.2608</x:v>
+        <x:v>0.0039</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
       <x:c r="A24" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>36.44</x:v>
+        <x:v>273.5</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>2.04</x:v>
+        <x:v>-3.25</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>37500000</x:v>
+        <x:v>141051834</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G24" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>16355768622</x:v>
+        <x:v>709077088</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>0.1024</x:v>
+        <x:v>0.1989</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
       <x:c r="A25" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>217</x:v>
+        <x:v>4.73</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>-5.6</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>2030000</x:v>
+        <x:v>5096500000</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>2159813703</x:v>
+        <x:v>19538660616</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>0.042</x:v>
+        <x:v>0.2608</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
       <x:c r="A26" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>57.2</x:v>
+        <x:v>4.73</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>2.85</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>31146246</x:v>
+        <x:v>5096500000</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>16733157490</x:v>
+        <x:v>19538660616</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>0.0832</x:v>
+        <x:v>0.2608</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
       <x:c r="A27" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>11.11</x:v>
+        <x:v>36.64</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>-0.48</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>1000000</x:v>
+        <x:v>37500000</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G27" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>7221187888</x:v>
+        <x:v>16355768622</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>0.0001</x:v>
+        <x:v>0.1024</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
       <x:c r="A28" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>11.11</x:v>
+        <x:v>219.8</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>-0.48</x:v>
+        <x:v>2.8</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>3150000</x:v>
+        <x:v>2030000</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G28" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>7221187888</x:v>
+        <x:v>2159813703</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>0.0227</x:v>
+        <x:v>0.042</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
       <x:c r="A29" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>11.11</x:v>
+        <x:v>55.8</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>-0.48</x:v>
+        <x:v>-1.4</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>2690000</x:v>
+        <x:v>31146246</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
         <x:v>11</x:v>
@@ -1616,85 +1619,85 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>7221187888</x:v>
+        <x:v>16733157490</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>0.0166</x:v>
+        <x:v>0.0832</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
       <x:c r="A30" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>57.2</x:v>
+        <x:v>11.25</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>2.85</x:v>
+        <x:v>0.14</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>4103000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G30" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>16733157490</x:v>
+        <x:v>7221187888</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>0.0109</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
       <x:c r="A31" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>117.2</x:v>
+        <x:v>11.25</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>-3.6</x:v>
+        <x:v>0.14</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>500000</x:v>
+        <x:v>3150000</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G31" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>3150489640</x:v>
+        <x:v>7221187888</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>0.0083</x:v>
+        <x:v>0.0227</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
       <x:c r="A32" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>51.35</x:v>
+        <x:v>11.25</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>2.85</x:v>
+        <x:v>0.14</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>872928</x:v>
+        <x:v>2690000</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
         <x:v>11</x:v>
@@ -1703,65 +1706,65 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>7221187888</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>0.0092</x:v>
+        <x:v>0.0166</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
       <x:c r="A33" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>93.95</x:v>
+        <x:v>55.8</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>1.55</x:v>
+        <x:v>-1.4</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>21250000</x:v>
+        <x:v>4103000</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G33" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>16733157490</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>0.0087</x:v>
+        <x:v>0.0109</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
       <x:c r="A34" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>58.2</x:v>
+        <x:v>118.6</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>-0.15</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>67690912</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G34" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>8121300519</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I34" s="0">
         <x:v>0.0083</x:v>
@@ -1769,19 +1772,19 @@
     </x:row>
     <x:row r="35" spans="1:9">
       <x:c r="A35" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>36.44</x:v>
+        <x:v>50.2</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>2.04</x:v>
+        <x:v>-1.15</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>65458848</x:v>
+        <x:v>872928</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
         <x:v>11</x:v>
@@ -1790,85 +1793,85 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>16355768622</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>0.1784</x:v>
+        <x:v>0.0092</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
       <x:c r="A36" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>24.3</x:v>
+        <x:v>94.4</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>0.14</x:v>
+        <x:v>0.45</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>689500000</x:v>
+        <x:v>21250000</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G36" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>884571536</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>0.7795</x:v>
+        <x:v>0.0087</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
       <x:c r="A37" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>5.9</x:v>
+        <x:v>58.95</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>0.08</x:v>
+        <x:v>0.75</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>3024490</x:v>
+        <x:v>67690912</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G37" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>2322993973</x:v>
+        <x:v>8121300519</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>0.0671</x:v>
+        <x:v>0.0083</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
       <x:c r="A38" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>5.9</x:v>
+        <x:v>36.64</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>0.08</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>4510336</x:v>
+        <x:v>65458848</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
         <x:v>11</x:v>
@@ -1877,39 +1880,39 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>2322993973</x:v>
+        <x:v>16355768622</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>0.0865</x:v>
+        <x:v>0.1784</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
       <x:c r="A39" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B39" s="0">
+        <x:v>24.34</x:v>
+      </x:c>
+      <x:c r="C39" s="0">
+        <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="D39" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="B39" s="0">
-        <x:v>48.2</x:v>
-      </x:c>
-      <x:c r="C39" s="0">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="D39" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
       <x:c r="E39" s="0">
-        <x:v>205000000</x:v>
+        <x:v>689500000</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G39" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>20597209000</x:v>
+        <x:v>884571536</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>0.4434</x:v>
+        <x:v>0.7795</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1917,74 +1920,74 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>332.25</x:v>
+        <x:v>6.18</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>-7.75</x:v>
+        <x:v>0.28</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>305000000</x:v>
+        <x:v>3024490</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G40" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>400439646</x:v>
+        <x:v>2322993973</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>0.7617</x:v>
+        <x:v>0.0671</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
       <x:c r="A41" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>83.2</x:v>
+        <x:v>6.18</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>1.15</x:v>
+        <x:v>0.28</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>11700000</x:v>
+        <x:v>4510336</x:v>
       </x:c>
       <x:c r="F41" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G41" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>2322993973</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>0.1718</x:v>
+        <x:v>0.0865</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
       <x:c r="A42" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>217</x:v>
+        <x:v>49.8</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>-5.6</x:v>
+        <x:v>1.6</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>1900000</x:v>
+        <x:v>205000000</x:v>
       </x:c>
       <x:c r="F42" s="0" t="s">
         <x:v>11</x:v>
@@ -1993,201 +1996,201 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>2159813703</x:v>
+        <x:v>20597209000</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>0.0391</x:v>
+        <x:v>0.4434</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
       <x:c r="A43" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>4.11</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>-0.15</x:v>
+        <x:v>-15.25</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>1670000</x:v>
+        <x:v>305000000</x:v>
       </x:c>
       <x:c r="F43" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G43" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>2875634546</x:v>
+        <x:v>400439646</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>0.0298</x:v>
+        <x:v>0.7617</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
       <x:c r="A44" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>24.3</x:v>
+        <x:v>85.5</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>0.14</x:v>
+        <x:v>2.3</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>48895800</x:v>
+        <x:v>11700000</x:v>
       </x:c>
       <x:c r="F44" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G44" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>884571536</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>0.0553</x:v>
+        <x:v>0.1718</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
       <x:c r="A45" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>24.3</x:v>
+        <x:v>219.8</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>0.14</x:v>
+        <x:v>2.8</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>689500000</x:v>
+        <x:v>1900000</x:v>
       </x:c>
       <x:c r="F45" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G45" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>884571536</x:v>
+        <x:v>2159813703</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>0.7795</x:v>
+        <x:v>0.0391</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
       <x:c r="A46" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>44.4</x:v>
+        <x:v>4.09</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>-0.02</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>3102911</x:v>
+        <x:v>1670000</x:v>
       </x:c>
       <x:c r="F46" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G46" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>2907014564</x:v>
+        <x:v>2875634546</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>0.0475</x:v>
+        <x:v>0.0298</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
       <x:c r="A47" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>24.26</x:v>
+        <x:v>24.34</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>0.68</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>13000000</x:v>
+        <x:v>48895800</x:v>
       </x:c>
       <x:c r="F47" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G47" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>11834942581</x:v>
+        <x:v>884571536</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>0.0563</x:v>
+        <x:v>0.0553</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
       <x:c r="A48" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>70.5</x:v>
+        <x:v>24.34</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>0.5</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>6800000</x:v>
+        <x:v>689500000</x:v>
       </x:c>
       <x:c r="F48" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G48" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>5948036961</x:v>
+        <x:v>884571536</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>0.0583</x:v>
+        <x:v>0.7795</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
       <x:c r="A49" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>48.2</x:v>
+        <x:v>45.12</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>-1</x:v>
+        <x:v>0.72</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>36750000</x:v>
+        <x:v>3102911</x:v>
       </x:c>
       <x:c r="F49" s="0" t="s">
         <x:v>11</x:v>
@@ -2196,85 +2199,85 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>20597209000</x:v>
+        <x:v>2907014564</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>0.0793</x:v>
+        <x:v>0.0475</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
       <x:c r="A50" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>1130</x:v>
+        <x:v>24.2</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>10</x:v>
+        <x:v>-0.06</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>3867260</x:v>
+        <x:v>13000000</x:v>
       </x:c>
       <x:c r="F50" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G50" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>1883544167</x:v>
+        <x:v>11834942581</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>0.0912</x:v>
+        <x:v>0.0563</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
       <x:c r="A51" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>66.05</x:v>
+        <x:v>74.6</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>2.95</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>1498029716</x:v>
+        <x:v>6800000</x:v>
       </x:c>
       <x:c r="F51" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G51" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>12030341104</x:v>
+        <x:v>5948036961</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>0.1245</x:v>
+        <x:v>0.0583</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
       <x:c r="A52" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>36.44</x:v>
+        <x:v>49.8</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>2.04</x:v>
+        <x:v>1.6</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>48000000</x:v>
+        <x:v>36750000</x:v>
       </x:c>
       <x:c r="F52" s="0" t="s">
         <x:v>11</x:v>
@@ -2283,39 +2286,39 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>16355768622</x:v>
+        <x:v>20597209000</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>0.1301</x:v>
+        <x:v>0.0793</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:9">
       <x:c r="A53" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B53" s="0">
-        <x:v>83.2</x:v>
+        <x:v>1139</x:v>
       </x:c>
       <x:c r="C53" s="0">
-        <x:v>1.15</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="E53" s="0">
-        <x:v>279699629</x:v>
+        <x:v>3867260</x:v>
       </x:c>
       <x:c r="F53" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G53" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H53" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>1883544167</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>0.08</x:v>
+        <x:v>0.0912</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:9">
@@ -2323,45 +2326,45 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B54" s="0">
-        <x:v>14.86</x:v>
+        <x:v>65.35</x:v>
       </x:c>
       <x:c r="C54" s="0">
-        <x:v>-0.05</x:v>
+        <x:v>-0.7</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E54" s="0">
-        <x:v>7971822</x:v>
+        <x:v>1498029716</x:v>
       </x:c>
       <x:c r="F54" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G54" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>4675369372</x:v>
+        <x:v>12030341104</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>0.0756</x:v>
+        <x:v>0.1245</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:9">
       <x:c r="A55" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B55" s="0">
-        <x:v>51.35</x:v>
+        <x:v>36.64</x:v>
       </x:c>
       <x:c r="C55" s="0">
-        <x:v>2.85</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E55" s="0">
-        <x:v>1104000</x:v>
+        <x:v>48000000</x:v>
       </x:c>
       <x:c r="F55" s="0" t="s">
         <x:v>11</x:v>
@@ -2370,317 +2373,317 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H55" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>16355768622</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>0.0116</x:v>
+        <x:v>0.1301</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:9">
       <x:c r="A56" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B56" s="0">
-        <x:v>24.3</x:v>
+        <x:v>85.5</x:v>
       </x:c>
       <x:c r="C56" s="0">
-        <x:v>0.14</x:v>
+        <x:v>2.3</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E56" s="0">
-        <x:v>48895800</x:v>
+        <x:v>279699629</x:v>
       </x:c>
       <x:c r="F56" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G56" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H56" s="0">
-        <x:v>884571536</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>0.0553</x:v>
+        <x:v>0.08</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:9">
       <x:c r="A57" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B57" s="0">
-        <x:v>3.28</x:v>
+        <x:v>14.94</x:v>
       </x:c>
       <x:c r="C57" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E57" s="0">
-        <x:v>191089413</x:v>
+        <x:v>7971822</x:v>
       </x:c>
       <x:c r="F57" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G57" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H57" s="0">
-        <x:v>9665356715</x:v>
+        <x:v>4675369372</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>0.0198</x:v>
+        <x:v>0.0756</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:9">
       <x:c r="A58" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B58" s="0">
-        <x:v>3.28</x:v>
+        <x:v>50.2</x:v>
       </x:c>
       <x:c r="C58" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>-1.15</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E58" s="0">
-        <x:v>605627160</x:v>
+        <x:v>1104000</x:v>
       </x:c>
       <x:c r="F58" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G58" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H58" s="0">
-        <x:v>9665356715</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>0.0627</x:v>
+        <x:v>0.0116</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:9">
       <x:c r="A59" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B59" s="0">
+        <x:v>24.34</x:v>
+      </x:c>
+      <x:c r="C59" s="0">
+        <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="D59" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="B59" s="0">
-        <x:v>26.04</x:v>
-      </x:c>
-      <x:c r="C59" s="0">
-        <x:v>0.18</x:v>
-      </x:c>
-      <x:c r="D59" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
       <x:c r="E59" s="0">
-        <x:v>2356546000</x:v>
+        <x:v>48895800</x:v>
       </x:c>
       <x:c r="F59" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G59" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H59" s="0">
-        <x:v>7708004248</x:v>
+        <x:v>884571536</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>0.3057</x:v>
+        <x:v>0.0553</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:9">
       <x:c r="A60" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B60" s="0">
-        <x:v>15.85</x:v>
+        <x:v>3.26</x:v>
       </x:c>
       <x:c r="C60" s="0">
-        <x:v>-0.1</x:v>
+        <x:v>-0.02</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E60" s="0">
-        <x:v>431250</x:v>
+        <x:v>191089413</x:v>
       </x:c>
       <x:c r="F60" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G60" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H60" s="0">
-        <x:v>3139850323</x:v>
+        <x:v>9665356715</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>0.0071</x:v>
+        <x:v>0.0198</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:9">
       <x:c r="A61" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B61" s="0">
-        <x:v>15.85</x:v>
+        <x:v>3.26</x:v>
       </x:c>
       <x:c r="C61" s="0">
-        <x:v>-0.1</x:v>
+        <x:v>-0.02</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E61" s="0">
-        <x:v>800000</x:v>
+        <x:v>605627160</x:v>
       </x:c>
       <x:c r="F61" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G61" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H61" s="0">
-        <x:v>3139850323</x:v>
+        <x:v>9665356715</x:v>
       </x:c>
       <x:c r="I61" s="0">
-        <x:v>0.0131</x:v>
+        <x:v>0.0627</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:9">
       <x:c r="A62" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B62" s="0">
-        <x:v>58.2</x:v>
+        <x:v>26.8</x:v>
       </x:c>
       <x:c r="C62" s="0">
-        <x:v>-0.15</x:v>
+        <x:v>0.76</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E62" s="0">
-        <x:v>127172130</x:v>
+        <x:v>2356546000</x:v>
       </x:c>
       <x:c r="F62" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G62" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H62" s="0">
-        <x:v>8121300519</x:v>
+        <x:v>7708004248</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>0.0157</x:v>
+        <x:v>0.3057</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:9">
       <x:c r="A63" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B63" s="0">
-        <x:v>45.14</x:v>
+        <x:v>16.01</x:v>
       </x:c>
       <x:c r="C63" s="0">
-        <x:v>2.26</x:v>
+        <x:v>0.16</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E63" s="0">
-        <x:v>42625000</x:v>
+        <x:v>431250</x:v>
       </x:c>
       <x:c r="F63" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G63" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H63" s="0">
-        <x:v>4728937463</x:v>
+        <x:v>3139850323</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>0.3994</x:v>
+        <x:v>0.0071</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:9">
       <x:c r="A64" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B64" s="0">
-        <x:v>93.95</x:v>
+        <x:v>16.01</x:v>
       </x:c>
       <x:c r="C64" s="0">
-        <x:v>1.55</x:v>
+        <x:v>0.16</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E64" s="0">
-        <x:v>1486000</x:v>
+        <x:v>800000</x:v>
       </x:c>
       <x:c r="F64" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G64" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H64" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>3139850323</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>0.027</x:v>
+        <x:v>0.0131</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:9">
       <x:c r="A65" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B65" s="0">
-        <x:v>264</x:v>
+        <x:v>58.95</x:v>
       </x:c>
       <x:c r="C65" s="0">
-        <x:v>9.25</x:v>
+        <x:v>0.75</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E65" s="0">
-        <x:v>768864700</x:v>
+        <x:v>127172130</x:v>
       </x:c>
       <x:c r="F65" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G65" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H65" s="0">
-        <x:v>35290767390</x:v>
+        <x:v>8121300519</x:v>
       </x:c>
       <x:c r="I65" s="0">
-        <x:v>0.9648</x:v>
+        <x:v>0.0157</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:9">
       <x:c r="A66" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B66" s="0">
-        <x:v>57.2</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C66" s="0">
-        <x:v>2.85</x:v>
+        <x:v>-1.14</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E66" s="0">
-        <x:v>15938617</x:v>
+        <x:v>42625000</x:v>
       </x:c>
       <x:c r="F66" s="0" t="s">
         <x:v>11</x:v>
@@ -2689,56 +2692,56 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H66" s="0">
-        <x:v>16733157490</x:v>
+        <x:v>4728937463</x:v>
       </x:c>
       <x:c r="I66" s="0">
-        <x:v>0.0422</x:v>
+        <x:v>0.3994</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:9">
       <x:c r="A67" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B67" s="0">
-        <x:v>14.58</x:v>
+        <x:v>94.4</x:v>
       </x:c>
       <x:c r="C67" s="0">
-        <x:v>0.08</x:v>
+        <x:v>0.45</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E67" s="0">
-        <x:v>30438120</x:v>
+        <x:v>1486000</x:v>
       </x:c>
       <x:c r="F67" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G67" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H67" s="0">
-        <x:v>3159124121</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>0</x:v>
+        <x:v>0.027</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:9">
       <x:c r="A68" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B68" s="0">
-        <x:v>217</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="C68" s="0">
-        <x:v>-5.6</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
         <x:v>67</x:v>
       </x:c>
       <x:c r="E68" s="0">
-        <x:v>3900000</x:v>
+        <x:v>768864700</x:v>
       </x:c>
       <x:c r="F68" s="0" t="s">
         <x:v>11</x:v>
@@ -2747,27 +2750,27 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H68" s="0">
-        <x:v>2159813703</x:v>
+        <x:v>35290767390</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>0.0797</x:v>
+        <x:v>0.9648</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:9">
       <x:c r="A69" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B69" s="0">
-        <x:v>217</x:v>
+        <x:v>55.8</x:v>
       </x:c>
       <x:c r="C69" s="0">
-        <x:v>-5.6</x:v>
+        <x:v>-1.4</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
         <x:v>67</x:v>
       </x:c>
       <x:c r="E69" s="0">
-        <x:v>2104908</x:v>
+        <x:v>15938617</x:v>
       </x:c>
       <x:c r="F69" s="0" t="s">
         <x:v>11</x:v>
@@ -2776,10 +2779,10 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H69" s="0">
-        <x:v>2159813703</x:v>
+        <x:v>16733157490</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>0.043</x:v>
+        <x:v>0.0422</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:9">
@@ -2787,144 +2790,144 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B70" s="0">
-        <x:v>28.38</x:v>
+        <x:v>13.91</x:v>
       </x:c>
       <x:c r="C70" s="0">
-        <x:v>-0.26</x:v>
+        <x:v>-0.67</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E70" s="0">
-        <x:v>3900000</x:v>
+        <x:v>30438120</x:v>
       </x:c>
       <x:c r="F70" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G70" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H70" s="0">
-        <x:v>7297855153</x:v>
+        <x:v>3159124121</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>0.0236</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:9">
       <x:c r="A71" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B71" s="0">
-        <x:v>4.83</x:v>
+        <x:v>219.8</x:v>
       </x:c>
       <x:c r="C71" s="0">
-        <x:v>-0.18</x:v>
+        <x:v>2.8</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E71" s="0">
-        <x:v>496968445</x:v>
+        <x:v>3900000</x:v>
       </x:c>
       <x:c r="F71" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G71" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H71" s="0">
-        <x:v>855070469</x:v>
+        <x:v>2159813703</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>0.5812</x:v>
+        <x:v>0.0797</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:9">
       <x:c r="A72" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B72" s="0">
+        <x:v>219.8</x:v>
+      </x:c>
+      <x:c r="C72" s="0">
+        <x:v>2.8</x:v>
+      </x:c>
+      <x:c r="D72" s="0" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="B72" s="0">
-        <x:v>13.58</x:v>
-      </x:c>
-      <x:c r="C72" s="0">
-        <x:v>0.7</x:v>
-      </x:c>
-      <x:c r="D72" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
       <x:c r="E72" s="0">
-        <x:v>108750000</x:v>
+        <x:v>2104908</x:v>
       </x:c>
       <x:c r="F72" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G72" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H72" s="0">
-        <x:v>1982520183</x:v>
+        <x:v>2159813703</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>0.0549</x:v>
+        <x:v>0.043</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:9">
       <x:c r="A73" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B73" s="0">
-        <x:v>117.2</x:v>
+        <x:v>28.62</x:v>
       </x:c>
       <x:c r="C73" s="0">
-        <x:v>-3.6</x:v>
+        <x:v>0.24</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E73" s="0">
-        <x:v>1605197</x:v>
+        <x:v>3900000</x:v>
       </x:c>
       <x:c r="F73" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G73" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H73" s="0">
-        <x:v>3150489640</x:v>
+        <x:v>7297855153</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>0.0257</x:v>
+        <x:v>0.0236</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:9">
       <x:c r="A74" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B74" s="0">
-        <x:v>425.5</x:v>
+        <x:v>4.91</x:v>
       </x:c>
       <x:c r="C74" s="0">
-        <x:v>11</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E74" s="0">
-        <x:v>54600000</x:v>
+        <x:v>496968445</x:v>
       </x:c>
       <x:c r="F74" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G74" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H74" s="0">
-        <x:v>180444938000</x:v>
+        <x:v>855070469</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>0.0133</x:v>
+        <x:v>0.5812</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:9">
@@ -2932,103 +2935,103 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="B75" s="0">
-        <x:v>425.5</x:v>
+        <x:v>13.36</x:v>
       </x:c>
       <x:c r="C75" s="0">
-        <x:v>11</x:v>
+        <x:v>-0.22</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E75" s="0">
-        <x:v>111850000</x:v>
+        <x:v>108750000</x:v>
       </x:c>
       <x:c r="F75" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G75" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H75" s="0">
-        <x:v>180444938000</x:v>
+        <x:v>1982520183</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>0.0273</x:v>
+        <x:v>0.0549</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:9">
       <x:c r="A76" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B76" s="0">
-        <x:v>51.35</x:v>
+        <x:v>118.6</x:v>
       </x:c>
       <x:c r="C76" s="0">
-        <x:v>2.85</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
         <x:v>73</x:v>
       </x:c>
       <x:c r="E76" s="0">
-        <x:v>803090</x:v>
+        <x:v>1605197</x:v>
       </x:c>
       <x:c r="F76" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G76" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H76" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I76" s="0">
-        <x:v>0.0084</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:9">
       <x:c r="A77" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B77" s="0">
-        <x:v>26.04</x:v>
+        <x:v>420.25</x:v>
       </x:c>
       <x:c r="C77" s="0">
-        <x:v>0.18</x:v>
+        <x:v>-5.25</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
         <x:v>74</x:v>
       </x:c>
       <x:c r="E77" s="0">
-        <x:v>2356546000</x:v>
+        <x:v>54600000</x:v>
       </x:c>
       <x:c r="F77" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G77" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H77" s="0">
-        <x:v>7708004248</x:v>
+        <x:v>180444938000</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>0.3057</x:v>
+        <x:v>0.0133</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:9">
       <x:c r="A78" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B78" s="0">
-        <x:v>1130</x:v>
+        <x:v>420.25</x:v>
       </x:c>
       <x:c r="C78" s="0">
-        <x:v>10</x:v>
+        <x:v>-5.25</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E78" s="0">
-        <x:v>875400</x:v>
+        <x:v>111850000</x:v>
       </x:c>
       <x:c r="F78" s="0" t="s">
         <x:v>11</x:v>
@@ -3037,619 +3040,619 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H78" s="0">
-        <x:v>1883544167</x:v>
+        <x:v>180444938000</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>0.0205</x:v>
+        <x:v>0.0273</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:9">
       <x:c r="A79" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B79" s="0">
-        <x:v>26.72</x:v>
+        <x:v>50.2</x:v>
       </x:c>
       <x:c r="C79" s="0">
-        <x:v>2.42</x:v>
+        <x:v>-1.15</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E79" s="0">
-        <x:v>330000000</x:v>
+        <x:v>803090</x:v>
       </x:c>
       <x:c r="F79" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G79" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H79" s="0">
-        <x:v>5287314404</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>0.0624</x:v>
+        <x:v>0.0084</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:9">
       <x:c r="A80" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B80" s="0">
+        <x:v>26.8</x:v>
+      </x:c>
+      <x:c r="C80" s="0">
+        <x:v>0.76</x:v>
+      </x:c>
+      <x:c r="D80" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="E80" s="0">
+        <x:v>2356546000</x:v>
+      </x:c>
+      <x:c r="F80" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B80" s="0">
-        <x:v>83.2</x:v>
-      </x:c>
-      <x:c r="C80" s="0">
-        <x:v>1.15</x:v>
-      </x:c>
-      <x:c r="D80" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="E80" s="0">
-        <x:v>11700000</x:v>
-      </x:c>
-      <x:c r="F80" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="G80" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H80" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>7708004248</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>0.1705</x:v>
+        <x:v>0.3057</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:9">
       <x:c r="A81" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B81" s="0">
-        <x:v>7.38</x:v>
+        <x:v>1139</x:v>
       </x:c>
       <x:c r="C81" s="0">
-        <x:v>0.06</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E81" s="0">
-        <x:v>4000000000</x:v>
+        <x:v>875400</x:v>
       </x:c>
       <x:c r="F81" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G81" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H81" s="0">
-        <x:v>10581001663</x:v>
+        <x:v>1883544167</x:v>
       </x:c>
       <x:c r="I81" s="0">
-        <x:v>0.378</x:v>
+        <x:v>0.0205</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:9">
       <x:c r="A82" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B82" s="0">
-        <x:v>15.85</x:v>
+        <x:v>26.8</x:v>
       </x:c>
       <x:c r="C82" s="0">
-        <x:v>-0.1</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E82" s="0">
-        <x:v>1086598</x:v>
+        <x:v>330000000</x:v>
       </x:c>
       <x:c r="F82" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G82" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H82" s="0">
-        <x:v>2020891371</x:v>
+        <x:v>5287314404</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>0.0274</x:v>
+        <x:v>0.0624</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:9">
       <x:c r="A83" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B83" s="0">
-        <x:v>14.86</x:v>
+        <x:v>85.5</x:v>
       </x:c>
       <x:c r="C83" s="0">
-        <x:v>-0.05</x:v>
+        <x:v>2.3</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E83" s="0">
-        <x:v>216000000</x:v>
+        <x:v>11700000</x:v>
       </x:c>
       <x:c r="F83" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G83" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H83" s="0">
-        <x:v>3025063909</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>0.0714</x:v>
+        <x:v>0.1705</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:9">
       <x:c r="A84" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B84" s="0">
-        <x:v>51.35</x:v>
+        <x:v>7.63</x:v>
       </x:c>
       <x:c r="C84" s="0">
-        <x:v>2.85</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E84" s="0">
-        <x:v>7292916</x:v>
+        <x:v>4000000000</x:v>
       </x:c>
       <x:c r="F84" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G84" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H84" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>10581001663</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>0.0758</x:v>
+        <x:v>0.378</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:9">
       <x:c r="A85" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B85" s="0">
-        <x:v>24.7</x:v>
+        <x:v>16.01</x:v>
       </x:c>
       <x:c r="C85" s="0">
-        <x:v>-0.46</x:v>
+        <x:v>0.16</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E85" s="0">
-        <x:v>250000</x:v>
+        <x:v>1086598</x:v>
       </x:c>
       <x:c r="F85" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G85" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H85" s="0">
-        <x:v>448686813</x:v>
+        <x:v>2020891371</x:v>
       </x:c>
       <x:c r="I85" s="0">
-        <x:v>0.0006</x:v>
+        <x:v>0.0274</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:9">
       <x:c r="A86" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B86" s="0">
-        <x:v>57.2</x:v>
+        <x:v>14.94</x:v>
       </x:c>
       <x:c r="C86" s="0">
-        <x:v>2.85</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E86" s="0">
-        <x:v>36900000</x:v>
+        <x:v>216000000</x:v>
       </x:c>
       <x:c r="F86" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G86" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H86" s="0">
-        <x:v>10597063406</x:v>
+        <x:v>3025063909</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>0.1527</x:v>
+        <x:v>0.0714</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:9">
       <x:c r="A87" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B87" s="0">
-        <x:v>60.3</x:v>
+        <x:v>50.2</x:v>
       </x:c>
       <x:c r="C87" s="0">
-        <x:v>0.45</x:v>
+        <x:v>-1.15</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E87" s="0">
-        <x:v>3800000</x:v>
+        <x:v>7292916</x:v>
       </x:c>
       <x:c r="F87" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G87" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H87" s="0">
-        <x:v>832031190</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>0.2002</x:v>
+        <x:v>0.0758</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:9">
       <x:c r="A88" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B88" s="0">
-        <x:v>4.83</x:v>
+        <x:v>27.16</x:v>
       </x:c>
       <x:c r="C88" s="0">
-        <x:v>-0.18</x:v>
+        <x:v>2.46</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E88" s="0">
-        <x:v>2100000</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="F88" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G88" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H88" s="0">
-        <x:v>855070469</x:v>
+        <x:v>448686813</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>0.1076</x:v>
+        <x:v>0.0006</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:9">
       <x:c r="A89" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B89" s="0">
-        <x:v>51.35</x:v>
+        <x:v>55.8</x:v>
       </x:c>
       <x:c r="C89" s="0">
-        <x:v>2.85</x:v>
+        <x:v>-1.4</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E89" s="0">
-        <x:v>22928077</x:v>
+        <x:v>36900000</x:v>
       </x:c>
       <x:c r="F89" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G89" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H89" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>10597063406</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>0.2378</x:v>
+        <x:v>0.1527</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:9">
       <x:c r="A90" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B90" s="0">
-        <x:v>28.5</x:v>
+        <x:v>60.25</x:v>
       </x:c>
       <x:c r="C90" s="0">
-        <x:v>-0.3</x:v>
+        <x:v>-0.05</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
         <x:v>86</x:v>
       </x:c>
       <x:c r="E90" s="0">
-        <x:v>547462013</x:v>
+        <x:v>3800000</x:v>
       </x:c>
       <x:c r="F90" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G90" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H90" s="0">
-        <x:v>0</x:v>
+        <x:v>832031190</x:v>
       </x:c>
       <x:c r="I90" s="0">
-        <x:v>0</x:v>
+        <x:v>0.2002</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:9">
       <x:c r="A91" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B91" s="0">
+        <x:v>4.91</x:v>
+      </x:c>
+      <x:c r="C91" s="0">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="D91" s="0" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="B91" s="0">
-        <x:v>28.5</x:v>
-      </x:c>
-      <x:c r="C91" s="0">
-        <x:v>-0.3</x:v>
-      </x:c>
-      <x:c r="D91" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
       <x:c r="E91" s="0">
-        <x:v>10567948</x:v>
+        <x:v>2100000</x:v>
       </x:c>
       <x:c r="F91" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G91" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H91" s="0">
-        <x:v>0</x:v>
+        <x:v>855070469</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>0</x:v>
+        <x:v>0.1076</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:9">
       <x:c r="A92" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B92" s="0">
-        <x:v>83.2</x:v>
+        <x:v>50.2</x:v>
       </x:c>
       <x:c r="C92" s="0">
-        <x:v>1.15</x:v>
+        <x:v>-1.15</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E92" s="0">
-        <x:v>8300000</x:v>
+        <x:v>22928077</x:v>
       </x:c>
       <x:c r="F92" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G92" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H92" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>0.1228</x:v>
+        <x:v>0.2378</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:9">
       <x:c r="A93" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B93" s="0">
-        <x:v>48.2</x:v>
+        <x:v>28.48</x:v>
       </x:c>
       <x:c r="C93" s="0">
-        <x:v>-1</x:v>
+        <x:v>-0.02</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E93" s="0">
-        <x:v>3000000</x:v>
+        <x:v>547462013</x:v>
       </x:c>
       <x:c r="F93" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G93" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H93" s="0">
-        <x:v>20597209000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>0.0064</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:9">
       <x:c r="A94" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B94" s="0">
-        <x:v>34.36</x:v>
+        <x:v>28.48</x:v>
       </x:c>
       <x:c r="C94" s="0">
-        <x:v>1.02</x:v>
+        <x:v>-0.02</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E94" s="0">
-        <x:v>26640000</x:v>
+        <x:v>10567948</x:v>
       </x:c>
       <x:c r="F94" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G94" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H94" s="0">
-        <x:v>3277373640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>0.356</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:9">
       <x:c r="A95" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B95" s="0">
-        <x:v>5.34</x:v>
+        <x:v>85.5</x:v>
       </x:c>
       <x:c r="C95" s="0">
-        <x:v>-0.01</x:v>
+        <x:v>2.3</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E95" s="0">
-        <x:v>13107198</x:v>
+        <x:v>8300000</x:v>
       </x:c>
       <x:c r="F95" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G95" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H95" s="0">
-        <x:v>1627872951</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>0.0081</x:v>
+        <x:v>0.1228</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:9">
       <x:c r="A96" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B96" s="0">
-        <x:v>83.2</x:v>
+        <x:v>49.8</x:v>
       </x:c>
       <x:c r="C96" s="0">
-        <x:v>1.15</x:v>
+        <x:v>1.6</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E96" s="0">
-        <x:v>237500000</x:v>
+        <x:v>3000000</x:v>
       </x:c>
       <x:c r="F96" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G96" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H96" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>20597209000</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>0.0679</x:v>
+        <x:v>0.0064</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:9">
       <x:c r="A97" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B97" s="0">
-        <x:v>58.2</x:v>
+        <x:v>35.68</x:v>
       </x:c>
       <x:c r="C97" s="0">
-        <x:v>-0.15</x:v>
+        <x:v>1.32</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E97" s="0">
-        <x:v>147892538</x:v>
+        <x:v>26640000</x:v>
       </x:c>
       <x:c r="F97" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G97" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H97" s="0">
-        <x:v>7257990064</x:v>
+        <x:v>3277373640</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>0.0204</x:v>
+        <x:v>0.356</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:9">
       <x:c r="A98" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B98" s="0">
-        <x:v>48.9</x:v>
+        <x:v>5.38</x:v>
       </x:c>
       <x:c r="C98" s="0">
-        <x:v>-0.18</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E98" s="0">
-        <x:v>988848</x:v>
+        <x:v>13107198</x:v>
       </x:c>
       <x:c r="F98" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G98" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H98" s="0">
-        <x:v>12999679000</x:v>
+        <x:v>1627872951</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>0.0033</x:v>
+        <x:v>0.0081</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:9">
       <x:c r="A99" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B99" s="0">
-        <x:v>57.2</x:v>
+        <x:v>85.5</x:v>
       </x:c>
       <x:c r="C99" s="0">
-        <x:v>2.85</x:v>
+        <x:v>2.3</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
         <x:v>93</x:v>
       </x:c>
       <x:c r="E99" s="0">
-        <x:v>47300000</x:v>
+        <x:v>237500000</x:v>
       </x:c>
       <x:c r="F99" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G99" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H99" s="0">
-        <x:v>10597063406</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>0.2309</x:v>
+        <x:v>0.0679</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:9">
@@ -3657,222 +3660,222 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B100" s="0">
-        <x:v>4.11</x:v>
+        <x:v>58.95</x:v>
       </x:c>
       <x:c r="C100" s="0">
-        <x:v>-0.15</x:v>
+        <x:v>0.75</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E100" s="0">
-        <x:v>758600</x:v>
+        <x:v>147892538</x:v>
       </x:c>
       <x:c r="F100" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G100" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H100" s="0">
-        <x:v>1960468575</x:v>
+        <x:v>7257990064</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0.0204</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:9">
       <x:c r="A101" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B101" s="0">
-        <x:v>4.11</x:v>
+        <x:v>52.4</x:v>
       </x:c>
       <x:c r="C101" s="0">
-        <x:v>-0.15</x:v>
+        <x:v>3.5</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E101" s="0">
-        <x:v>758600</x:v>
+        <x:v>988848</x:v>
       </x:c>
       <x:c r="F101" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G101" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H101" s="0">
-        <x:v>1960468575</x:v>
+        <x:v>12999679000</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>0.0004</x:v>
+        <x:v>0.0033</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:9">
       <x:c r="A102" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B102" s="0">
-        <x:v>1130</x:v>
+        <x:v>55.8</x:v>
       </x:c>
       <x:c r="C102" s="0">
-        <x:v>10</x:v>
+        <x:v>-1.4</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E102" s="0">
-        <x:v>576665</x:v>
+        <x:v>47300000</x:v>
       </x:c>
       <x:c r="F102" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G102" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H102" s="0">
-        <x:v>1586603352</x:v>
+        <x:v>10597063406</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>0.0159</x:v>
+        <x:v>0.2309</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:9">
       <x:c r="A103" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B103" s="0">
-        <x:v>81.8</x:v>
+        <x:v>4.09</x:v>
       </x:c>
       <x:c r="C103" s="0">
-        <x:v>0.4</x:v>
+        <x:v>-0.02</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E103" s="0">
-        <x:v>8000000</x:v>
+        <x:v>758600</x:v>
       </x:c>
       <x:c r="F103" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G103" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H103" s="0">
-        <x:v>20999579110</x:v>
+        <x:v>1960468575</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>0.0166</x:v>
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:9">
       <x:c r="A104" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B104" s="0">
-        <x:v>93.95</x:v>
+        <x:v>4.09</x:v>
       </x:c>
       <x:c r="C104" s="0">
-        <x:v>1.55</x:v>
+        <x:v>-0.02</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E104" s="0">
-        <x:v>850000</x:v>
+        <x:v>758600</x:v>
       </x:c>
       <x:c r="F104" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="G104" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H104" s="0">
-        <x:v>1781510191</x:v>
+        <x:v>1960468575</x:v>
       </x:c>
       <x:c r="I104" s="0">
-        <x:v>0.0208</x:v>
+        <x:v>0.0004</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:9">
       <x:c r="A105" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B105" s="0">
-        <x:v>15.85</x:v>
+        <x:v>1139</x:v>
       </x:c>
       <x:c r="C105" s="0">
-        <x:v>-0.1</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E105" s="0">
-        <x:v>10149200</x:v>
+        <x:v>576665</x:v>
       </x:c>
       <x:c r="F105" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G105" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H105" s="0">
-        <x:v>2020891371</x:v>
+        <x:v>1586603352</x:v>
       </x:c>
       <x:c r="I105" s="0">
-        <x:v>0.2601</x:v>
+        <x:v>0.0159</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:9">
       <x:c r="A106" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B106" s="0">
-        <x:v>117.2</x:v>
+        <x:v>81.05</x:v>
       </x:c>
       <x:c r="C106" s="0">
-        <x:v>-3.6</x:v>
+        <x:v>-0.75</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E106" s="0">
-        <x:v>10500000</x:v>
+        <x:v>8000000</x:v>
       </x:c>
       <x:c r="F106" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G106" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H106" s="0">
-        <x:v>1742315226</x:v>
+        <x:v>20999579110</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>0.3121</x:v>
+        <x:v>0.0166</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:9">
       <x:c r="A107" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B107" s="0">
-        <x:v>93.95</x:v>
+        <x:v>94.4</x:v>
       </x:c>
       <x:c r="C107" s="0">
-        <x:v>1.55</x:v>
+        <x:v>0.45</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E107" s="0">
-        <x:v>366956541</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="F107" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G107" s="0">
         <x:v>2025.09</x:v>
@@ -3881,169 +3884,169 @@
         <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>0.206</x:v>
+        <x:v>0.0208</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:9">
       <x:c r="A108" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B108" s="0">
-        <x:v>58.2</x:v>
+        <x:v>16.01</x:v>
       </x:c>
       <x:c r="C108" s="0">
-        <x:v>-0.15</x:v>
+        <x:v>0.16</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E108" s="0">
-        <x:v>61158155</x:v>
+        <x:v>10149200</x:v>
       </x:c>
       <x:c r="F108" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G108" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H108" s="0">
-        <x:v>7257990064</x:v>
+        <x:v>2020891371</x:v>
       </x:c>
       <x:c r="I108" s="0">
-        <x:v>0.0084</x:v>
+        <x:v>0.2601</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:9">
       <x:c r="A109" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B109" s="0">
-        <x:v>105.2</x:v>
+        <x:v>118.6</x:v>
       </x:c>
       <x:c r="C109" s="0">
-        <x:v>0.4</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E109" s="0">
-        <x:v>1000000</x:v>
+        <x:v>10500000</x:v>
       </x:c>
       <x:c r="F109" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G109" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H109" s="0">
-        <x:v>1688731509</x:v>
+        <x:v>1742315226</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>0.0307</x:v>
+        <x:v>0.3121</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:9">
       <x:c r="A110" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B110" s="0">
-        <x:v>105.2</x:v>
+        <x:v>94.4</x:v>
       </x:c>
       <x:c r="C110" s="0">
-        <x:v>0.4</x:v>
+        <x:v>0.45</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
         <x:v>101</x:v>
       </x:c>
       <x:c r="E110" s="0">
-        <x:v>1050000</x:v>
+        <x:v>366956541</x:v>
       </x:c>
       <x:c r="F110" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G110" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H110" s="0">
-        <x:v>1688731509</x:v>
+        <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>0.0271</x:v>
+        <x:v>0.206</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:9">
       <x:c r="A111" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B111" s="0">
-        <x:v>41.06</x:v>
+        <x:v>58.95</x:v>
       </x:c>
       <x:c r="C111" s="0">
-        <x:v>-1.22</x:v>
+        <x:v>0.75</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E111" s="0">
-        <x:v>109053804</x:v>
+        <x:v>61158155</x:v>
       </x:c>
       <x:c r="F111" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G111" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H111" s="0">
-        <x:v>1942491524</x:v>
+        <x:v>7257990064</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>0.0561</x:v>
+        <x:v>0.0084</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:9">
       <x:c r="A112" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B112" s="0">
-        <x:v>10.43</x:v>
+        <x:v>106.3</x:v>
       </x:c>
       <x:c r="C112" s="0">
-        <x:v>0.13</x:v>
+        <x:v>1.1</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E112" s="0">
-        <x:v>62315119</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="F112" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G112" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H112" s="0">
-        <x:v>12026414029</x:v>
+        <x:v>1688731509</x:v>
       </x:c>
       <x:c r="I112" s="0">
-        <x:v>0.2257</x:v>
+        <x:v>0.0307</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:9">
       <x:c r="A113" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B113" s="0">
-        <x:v>217</x:v>
+        <x:v>106.3</x:v>
       </x:c>
       <x:c r="C113" s="0">
-        <x:v>-5.6</x:v>
+        <x:v>1.1</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E113" s="0">
-        <x:v>896400</x:v>
+        <x:v>1050000</x:v>
       </x:c>
       <x:c r="F113" s="0" t="s">
         <x:v>11</x:v>
@@ -4052,85 +4055,85 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H113" s="0">
-        <x:v>1364716456</x:v>
+        <x:v>1688731509</x:v>
       </x:c>
       <x:c r="I113" s="0">
-        <x:v>0.0285</x:v>
+        <x:v>0.0271</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:9">
       <x:c r="A114" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B114" s="0">
-        <x:v>339.5</x:v>
+        <x:v>40.58</x:v>
       </x:c>
       <x:c r="C114" s="0">
-        <x:v>30.75</x:v>
+        <x:v>-0.48</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E114" s="0">
-        <x:v>3370000</x:v>
+        <x:v>109053804</x:v>
       </x:c>
       <x:c r="F114" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G114" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H114" s="0">
-        <x:v>1865697176</x:v>
+        <x:v>1942491524</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>0.0785</x:v>
+        <x:v>0.0561</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:9">
       <x:c r="A115" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B115" s="0">
-        <x:v>48.2</x:v>
+        <x:v>10.41</x:v>
       </x:c>
       <x:c r="C115" s="0">
-        <x:v>-1</x:v>
+        <x:v>-0.02</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E115" s="0">
-        <x:v>750561215</x:v>
+        <x:v>62315119</x:v>
       </x:c>
       <x:c r="F115" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G115" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H115" s="0">
-        <x:v>16507905000</x:v>
+        <x:v>12026414029</x:v>
       </x:c>
       <x:c r="I115" s="0">
-        <x:v>0.0455</x:v>
+        <x:v>0.2257</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:9">
       <x:c r="A116" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B116" s="0">
-        <x:v>81.8</x:v>
+        <x:v>219.8</x:v>
       </x:c>
       <x:c r="C116" s="0">
-        <x:v>0.4</x:v>
+        <x:v>2.8</x:v>
       </x:c>
       <x:c r="D116" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E116" s="0">
-        <x:v>20000000</x:v>
+        <x:v>896400</x:v>
       </x:c>
       <x:c r="F116" s="0" t="s">
         <x:v>11</x:v>
@@ -4139,85 +4142,85 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H116" s="0">
-        <x:v>20999579110</x:v>
+        <x:v>1364716456</x:v>
       </x:c>
       <x:c r="I116" s="0">
-        <x:v>0.0413</x:v>
+        <x:v>0.0285</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:9">
       <x:c r="A117" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B117" s="0">
-        <x:v>32.98</x:v>
+        <x:v>373.25</x:v>
       </x:c>
       <x:c r="C117" s="0">
-        <x:v>-1.58</x:v>
+        <x:v>33.75</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E117" s="0">
-        <x:v>750000000</x:v>
+        <x:v>3370000</x:v>
       </x:c>
       <x:c r="F117" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G117" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H117" s="0">
-        <x:v>0</x:v>
+        <x:v>1865697176</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0785</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:9">
       <x:c r="A118" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B118" s="0">
-        <x:v>57.2</x:v>
+        <x:v>49.8</x:v>
       </x:c>
       <x:c r="C118" s="0">
-        <x:v>2.85</x:v>
+        <x:v>1.6</x:v>
       </x:c>
       <x:c r="D118" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E118" s="0">
-        <x:v>111232418</x:v>
+        <x:v>750561215</x:v>
       </x:c>
       <x:c r="F118" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G118" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H118" s="0">
-        <x:v>10597063406</x:v>
+        <x:v>16507905000</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>0.4554</x:v>
+        <x:v>0.0455</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:9">
       <x:c r="A119" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B119" s="0">
-        <x:v>36.44</x:v>
+        <x:v>81.05</x:v>
       </x:c>
       <x:c r="C119" s="0">
-        <x:v>2.04</x:v>
+        <x:v>-0.75</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E119" s="0">
-        <x:v>51384996</x:v>
+        <x:v>20000000</x:v>
       </x:c>
       <x:c r="F119" s="0" t="s">
         <x:v>11</x:v>
@@ -4226,56 +4229,56 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H119" s="0">
-        <x:v>11899043692</x:v>
+        <x:v>20999579110</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>0.1873</x:v>
+        <x:v>0.0413</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:9">
       <x:c r="A120" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B120" s="0">
-        <x:v>36.44</x:v>
+        <x:v>33.06</x:v>
       </x:c>
       <x:c r="C120" s="0">
-        <x:v>2.04</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
         <x:v>112</x:v>
       </x:c>
       <x:c r="E120" s="0">
-        <x:v>3602451</x:v>
+        <x:v>750000000</x:v>
       </x:c>
       <x:c r="F120" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G120" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H120" s="0">
-        <x:v>11899043692</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>0.0131</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:9">
       <x:c r="A121" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B121" s="0">
-        <x:v>36.44</x:v>
+        <x:v>55.8</x:v>
       </x:c>
       <x:c r="C121" s="0">
-        <x:v>2.04</x:v>
+        <x:v>-1.4</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
         <x:v>112</x:v>
       </x:c>
       <x:c r="E121" s="0">
-        <x:v>24226465</x:v>
+        <x:v>111232418</x:v>
       </x:c>
       <x:c r="F121" s="0" t="s">
         <x:v>11</x:v>
@@ -4284,175 +4287,175 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H121" s="0">
-        <x:v>11899043692</x:v>
+        <x:v>10597063406</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>0.0883</x:v>
+        <x:v>0.4554</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:9">
       <x:c r="A122" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B122" s="0">
-        <x:v>51.35</x:v>
+        <x:v>36.64</x:v>
       </x:c>
       <x:c r="C122" s="0">
-        <x:v>2.85</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E122" s="0">
-        <x:v>12900000</x:v>
+        <x:v>51384996</x:v>
       </x:c>
       <x:c r="F122" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G122" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H122" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>11899043692</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>0.0052</x:v>
+        <x:v>0.1873</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:9">
       <x:c r="A123" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B123" s="0">
-        <x:v>264</x:v>
+        <x:v>36.64</x:v>
       </x:c>
       <x:c r="C123" s="0">
-        <x:v>9.25</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E123" s="0">
-        <x:v>53250000</x:v>
+        <x:v>3602451</x:v>
       </x:c>
       <x:c r="F123" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G123" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H123" s="0">
-        <x:v>24073631758</x:v>
+        <x:v>11899043692</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>0.115</x:v>
+        <x:v>0.0131</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:9">
       <x:c r="A124" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B124" s="0">
-        <x:v>28.5</x:v>
+        <x:v>36.64</x:v>
       </x:c>
       <x:c r="C124" s="0">
-        <x:v>-0.3</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E124" s="0">
-        <x:v>6860140</x:v>
+        <x:v>24226465</x:v>
       </x:c>
       <x:c r="F124" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G124" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H124" s="0">
-        <x:v>0</x:v>
+        <x:v>11899043692</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0883</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:9">
       <x:c r="A125" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B125" s="0">
-        <x:v>83.2</x:v>
+        <x:v>50.2</x:v>
       </x:c>
       <x:c r="C125" s="0">
-        <x:v>1.15</x:v>
+        <x:v>-1.15</x:v>
       </x:c>
       <x:c r="D125" s="0" t="s">
         <x:v>113</x:v>
       </x:c>
       <x:c r="E125" s="0">
-        <x:v>230000000</x:v>
+        <x:v>12900000</x:v>
       </x:c>
       <x:c r="F125" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G125" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H125" s="0">
-        <x:v>2941310980</x:v>
+        <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I125" s="0">
-        <x:v>0.0782</x:v>
+        <x:v>0.0052</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:9">
       <x:c r="A126" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B126" s="0">
-        <x:v>339.5</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="C126" s="0">
-        <x:v>30.75</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E126" s="0">
-        <x:v>4700000</x:v>
+        <x:v>53250000</x:v>
       </x:c>
       <x:c r="F126" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G126" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H126" s="0">
-        <x:v>1865697176</x:v>
+        <x:v>24073631758</x:v>
       </x:c>
       <x:c r="I126" s="0">
-        <x:v>0.1092</x:v>
+        <x:v>0.115</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:9">
       <x:c r="A127" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B127" s="0">
-        <x:v>28.5</x:v>
+        <x:v>28.48</x:v>
       </x:c>
       <x:c r="C127" s="0">
-        <x:v>-0.3</x:v>
+        <x:v>-0.02</x:v>
       </x:c>
       <x:c r="D127" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E127" s="0">
-        <x:v>256000000</x:v>
+        <x:v>6860140</x:v>
       </x:c>
       <x:c r="F127" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G127" s="0">
         <x:v>0</x:v>
@@ -4466,222 +4469,222 @@
     </x:row>
     <x:row r="128" spans="1:9">
       <x:c r="A128" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B128" s="0">
-        <x:v>36.44</x:v>
+        <x:v>85.5</x:v>
       </x:c>
       <x:c r="C128" s="0">
-        <x:v>2.04</x:v>
+        <x:v>2.3</x:v>
       </x:c>
       <x:c r="D128" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="E128" s="0">
-        <x:v>10724896</x:v>
+        <x:v>230000000</x:v>
       </x:c>
       <x:c r="F128" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G128" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H128" s="0">
-        <x:v>11899043692</x:v>
+        <x:v>2941310980</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>0.039</x:v>
+        <x:v>0.0782</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:9">
       <x:c r="A129" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B129" s="0">
-        <x:v>24.3</x:v>
+        <x:v>373.25</x:v>
       </x:c>
       <x:c r="C129" s="0">
-        <x:v>0.14</x:v>
+        <x:v>33.75</x:v>
       </x:c>
       <x:c r="D129" s="0" t="s">
         <x:v>115</x:v>
       </x:c>
       <x:c r="E129" s="0">
-        <x:v>31000000</x:v>
+        <x:v>4700000</x:v>
       </x:c>
       <x:c r="F129" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G129" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H129" s="0">
-        <x:v>813967617</x:v>
+        <x:v>1865697176</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>0.0381</x:v>
+        <x:v>0.1092</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:9">
       <x:c r="A130" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B130" s="0">
-        <x:v>41.02</x:v>
+        <x:v>28.48</x:v>
       </x:c>
       <x:c r="C130" s="0">
-        <x:v>0.26</x:v>
+        <x:v>-0.02</x:v>
       </x:c>
       <x:c r="D130" s="0" t="s">
         <x:v>115</x:v>
       </x:c>
       <x:c r="E130" s="0">
-        <x:v>13500000</x:v>
+        <x:v>256000000</x:v>
       </x:c>
       <x:c r="F130" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G130" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H130" s="0">
-        <x:v>6483809984</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>0.09</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:9">
       <x:c r="A131" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B131" s="0">
-        <x:v>41.06</x:v>
+        <x:v>36.64</x:v>
       </x:c>
       <x:c r="C131" s="0">
-        <x:v>-1.22</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
         <x:v>116</x:v>
       </x:c>
       <x:c r="E131" s="0">
-        <x:v>29886357</x:v>
+        <x:v>10724896</x:v>
       </x:c>
       <x:c r="F131" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G131" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H131" s="0">
-        <x:v>1942491524</x:v>
+        <x:v>11899043692</x:v>
       </x:c>
       <x:c r="I131" s="0">
-        <x:v>0.0154</x:v>
+        <x:v>0.039</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:9">
       <x:c r="A132" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B132" s="0">
-        <x:v>425.5</x:v>
+        <x:v>24.34</x:v>
       </x:c>
       <x:c r="C132" s="0">
-        <x:v>11</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
         <x:v>116</x:v>
       </x:c>
       <x:c r="E132" s="0">
-        <x:v>171000000</x:v>
+        <x:v>31000000</x:v>
       </x:c>
       <x:c r="F132" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G132" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H132" s="0">
-        <x:v>130147715000</x:v>
+        <x:v>813967617</x:v>
       </x:c>
       <x:c r="I132" s="0">
-        <x:v>0.0568</x:v>
+        <x:v>0.0381</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:9">
       <x:c r="A133" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B133" s="0">
-        <x:v>117.2</x:v>
+        <x:v>41.22</x:v>
       </x:c>
       <x:c r="C133" s="0">
-        <x:v>-3.6</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="D133" s="0" t="s">
         <x:v>116</x:v>
       </x:c>
       <x:c r="E133" s="0">
-        <x:v>1890000</x:v>
+        <x:v>13500000</x:v>
       </x:c>
       <x:c r="F133" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G133" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H133" s="0">
-        <x:v>1742315226</x:v>
+        <x:v>6483809984</x:v>
       </x:c>
       <x:c r="I133" s="0">
-        <x:v>0.0549</x:v>
+        <x:v>0.09</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:9">
       <x:c r="A134" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="B134" s="0">
+        <x:v>40.58</x:v>
+      </x:c>
+      <x:c r="C134" s="0">
+        <x:v>-0.48</x:v>
+      </x:c>
+      <x:c r="D134" s="0" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="B134" s="0">
-        <x:v>13.13</x:v>
-      </x:c>
-      <x:c r="C134" s="0">
-        <x:v>-0.27</x:v>
-      </x:c>
-      <x:c r="D134" s="0" t="s">
-        <x:v>116</x:v>
-      </x:c>
       <x:c r="E134" s="0">
-        <x:v>892825</x:v>
+        <x:v>29886357</x:v>
       </x:c>
       <x:c r="F134" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G134" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H134" s="0">
-        <x:v>3015442704</x:v>
+        <x:v>1942491524</x:v>
       </x:c>
       <x:c r="I134" s="0">
-        <x:v>0.0128</x:v>
+        <x:v>0.0154</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:9">
       <x:c r="A135" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B135" s="0">
-        <x:v>51.35</x:v>
+        <x:v>420.25</x:v>
       </x:c>
       <x:c r="C135" s="0">
-        <x:v>2.85</x:v>
+        <x:v>-5.25</x:v>
       </x:c>
       <x:c r="D135" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E135" s="0">
-        <x:v>361176</x:v>
+        <x:v>171000000</x:v>
       </x:c>
       <x:c r="F135" s="0" t="s">
         <x:v>11</x:v>
@@ -4690,85 +4693,85 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H135" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>130147715000</x:v>
       </x:c>
       <x:c r="I135" s="0">
-        <x:v>0.0063</x:v>
+        <x:v>0.0568</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:9">
       <x:c r="A136" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B136" s="0">
-        <x:v>25.56</x:v>
+        <x:v>118.6</x:v>
       </x:c>
       <x:c r="C136" s="0">
-        <x:v>-0.44</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E136" s="0">
-        <x:v>1060000</x:v>
+        <x:v>1890000</x:v>
       </x:c>
       <x:c r="F136" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G136" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H136" s="0">
-        <x:v>1194839266</x:v>
+        <x:v>1742315226</x:v>
       </x:c>
       <x:c r="I136" s="0">
-        <x:v>0.0384</x:v>
+        <x:v>0.0549</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:9">
       <x:c r="A137" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B137" s="0">
-        <x:v>53</x:v>
+        <x:v>13.48</x:v>
       </x:c>
       <x:c r="C137" s="0">
-        <x:v>1.25</x:v>
+        <x:v>0.35</x:v>
       </x:c>
       <x:c r="D137" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E137" s="0">
-        <x:v>259417800</x:v>
+        <x:v>892825</x:v>
       </x:c>
       <x:c r="F137" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G137" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H137" s="0">
-        <x:v>2741117556</x:v>
+        <x:v>3015442704</x:v>
       </x:c>
       <x:c r="I137" s="0">
-        <x:v>0.0946</x:v>
+        <x:v>0.0128</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:9">
       <x:c r="A138" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B138" s="0">
-        <x:v>60.3</x:v>
+        <x:v>50.2</x:v>
       </x:c>
       <x:c r="C138" s="0">
-        <x:v>0.45</x:v>
+        <x:v>-1.15</x:v>
       </x:c>
       <x:c r="D138" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E138" s="0">
-        <x:v>523788</x:v>
+        <x:v>361176</x:v>
       </x:c>
       <x:c r="F138" s="0" t="s">
         <x:v>11</x:v>
@@ -4777,27 +4780,27 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H138" s="0">
-        <x:v>832031190</x:v>
+        <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I138" s="0">
-        <x:v>0.0272</x:v>
+        <x:v>0.0063</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:9">
       <x:c r="A139" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B139" s="0">
-        <x:v>60.3</x:v>
+        <x:v>24.32</x:v>
       </x:c>
       <x:c r="C139" s="0">
-        <x:v>0.45</x:v>
+        <x:v>-1.24</x:v>
       </x:c>
       <x:c r="D139" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E139" s="0">
-        <x:v>1415270</x:v>
+        <x:v>1060000</x:v>
       </x:c>
       <x:c r="F139" s="0" t="s">
         <x:v>11</x:v>
@@ -4806,56 +4809,56 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H139" s="0">
-        <x:v>832031190</x:v>
+        <x:v>1194839266</x:v>
       </x:c>
       <x:c r="I139" s="0">
-        <x:v>0.0736</x:v>
+        <x:v>0.0384</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:9">
       <x:c r="A140" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B140" s="0">
-        <x:v>81.8</x:v>
+        <x:v>52.15</x:v>
       </x:c>
       <x:c r="C140" s="0">
-        <x:v>0.4</x:v>
+        <x:v>-0.85</x:v>
       </x:c>
       <x:c r="D140" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E140" s="0">
-        <x:v>25000000</x:v>
+        <x:v>259417800</x:v>
       </x:c>
       <x:c r="F140" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G140" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H140" s="0">
-        <x:v>20999579110</x:v>
+        <x:v>2741117556</x:v>
       </x:c>
       <x:c r="I140" s="0">
-        <x:v>0.0515</x:v>
+        <x:v>0.0946</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:9">
       <x:c r="A141" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B141" s="0">
-        <x:v>5.34</x:v>
+        <x:v>60.25</x:v>
       </x:c>
       <x:c r="C141" s="0">
-        <x:v>-0.01</x:v>
+        <x:v>-0.05</x:v>
       </x:c>
       <x:c r="D141" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E141" s="0">
-        <x:v>25000</x:v>
+        <x:v>523788</x:v>
       </x:c>
       <x:c r="F141" s="0" t="s">
         <x:v>11</x:v>
@@ -4864,85 +4867,85 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H141" s="0">
-        <x:v>1627872951</x:v>
+        <x:v>832031190</x:v>
       </x:c>
       <x:c r="I141" s="0">
-        <x:v>0.0007</x:v>
+        <x:v>0.0272</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:9">
       <x:c r="A142" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B142" s="0">
-        <x:v>20.02</x:v>
+        <x:v>60.25</x:v>
       </x:c>
       <x:c r="C142" s="0">
-        <x:v>0.2</x:v>
+        <x:v>-0.05</x:v>
       </x:c>
       <x:c r="D142" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E142" s="0">
-        <x:v>1500000</x:v>
+        <x:v>1415270</x:v>
       </x:c>
       <x:c r="F142" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G142" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H142" s="0">
-        <x:v>774677961</x:v>
+        <x:v>832031190</x:v>
       </x:c>
       <x:c r="I142" s="0">
-        <x:v>0.0019</x:v>
+        <x:v>0.0736</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:9">
       <x:c r="A143" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B143" s="0">
-        <x:v>7.38</x:v>
+        <x:v>81.05</x:v>
       </x:c>
       <x:c r="C143" s="0">
-        <x:v>0.06</x:v>
+        <x:v>-0.75</x:v>
       </x:c>
       <x:c r="D143" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E143" s="0">
-        <x:v>13833310</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="F143" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G143" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H143" s="0">
-        <x:v>9028523851</x:v>
+        <x:v>20999579110</x:v>
       </x:c>
       <x:c r="I143" s="0">
-        <x:v>0.0776</x:v>
+        <x:v>0.0515</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:9">
       <x:c r="A144" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B144" s="0">
-        <x:v>70.5</x:v>
+        <x:v>5.38</x:v>
       </x:c>
       <x:c r="C144" s="0">
-        <x:v>0.5</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="D144" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E144" s="0">
-        <x:v>3419000</x:v>
+        <x:v>25000</x:v>
       </x:c>
       <x:c r="F144" s="0" t="s">
         <x:v>11</x:v>
@@ -4951,85 +4954,85 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H144" s="0">
-        <x:v>3895315496</x:v>
+        <x:v>1627872951</x:v>
       </x:c>
       <x:c r="I144" s="0">
-        <x:v>0.0379</x:v>
+        <x:v>0.0007</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:9">
       <x:c r="A145" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B145" s="0">
-        <x:v>339.5</x:v>
+        <x:v>22.02</x:v>
       </x:c>
       <x:c r="C145" s="0">
-        <x:v>30.75</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D145" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E145" s="0">
-        <x:v>3700000</x:v>
+        <x:v>1500000</x:v>
       </x:c>
       <x:c r="F145" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G145" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H145" s="0">
-        <x:v>1865697176</x:v>
+        <x:v>774677961</x:v>
       </x:c>
       <x:c r="I145" s="0">
-        <x:v>0.0857</x:v>
+        <x:v>0.0019</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:9">
       <x:c r="A146" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B146" s="0">
-        <x:v>41.02</x:v>
+        <x:v>7.63</x:v>
       </x:c>
       <x:c r="C146" s="0">
-        <x:v>0.26</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="D146" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E146" s="0">
-        <x:v>16000000</x:v>
+        <x:v>13833310</x:v>
       </x:c>
       <x:c r="F146" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G146" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H146" s="0">
-        <x:v>6483809984</x:v>
+        <x:v>9028523851</x:v>
       </x:c>
       <x:c r="I146" s="0">
-        <x:v>0.1067</x:v>
+        <x:v>0.0776</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:9">
       <x:c r="A147" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B147" s="0">
-        <x:v>51.35</x:v>
+        <x:v>74.6</x:v>
       </x:c>
       <x:c r="C147" s="0">
-        <x:v>2.85</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="D147" s="0" t="s">
         <x:v>124</x:v>
       </x:c>
       <x:c r="E147" s="0">
-        <x:v>906840</x:v>
+        <x:v>3419000</x:v>
       </x:c>
       <x:c r="F147" s="0" t="s">
         <x:v>11</x:v>
@@ -5038,85 +5041,85 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H147" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>3895315496</x:v>
       </x:c>
       <x:c r="I147" s="0">
-        <x:v>0.0159</x:v>
+        <x:v>0.0379</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:9">
       <x:c r="A148" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B148" s="0">
-        <x:v>3.28</x:v>
+        <x:v>373.25</x:v>
       </x:c>
       <x:c r="C148" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>33.75</x:v>
       </x:c>
       <x:c r="D148" s="0" t="s">
         <x:v>124</x:v>
       </x:c>
       <x:c r="E148" s="0">
-        <x:v>895039950</x:v>
+        <x:v>3700000</x:v>
       </x:c>
       <x:c r="F148" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G148" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H148" s="0">
-        <x:v>7382591324</x:v>
+        <x:v>1865697176</x:v>
       </x:c>
       <x:c r="I148" s="0">
-        <x:v>0.1212</x:v>
+        <x:v>0.0857</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:9">
       <x:c r="A149" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B149" s="0">
-        <x:v>53</x:v>
+        <x:v>41.22</x:v>
       </x:c>
       <x:c r="C149" s="0">
-        <x:v>1.25</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="D149" s="0" t="s">
         <x:v>124</x:v>
       </x:c>
       <x:c r="E149" s="0">
-        <x:v>575933040</x:v>
+        <x:v>16000000</x:v>
       </x:c>
       <x:c r="F149" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G149" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H149" s="0">
-        <x:v>2741117556</x:v>
+        <x:v>6483809984</x:v>
       </x:c>
       <x:c r="I149" s="0">
-        <x:v>0.2101</x:v>
+        <x:v>0.1067</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:9">
       <x:c r="A150" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B150" s="0">
+        <x:v>50.2</x:v>
+      </x:c>
+      <x:c r="C150" s="0">
+        <x:v>-1.15</x:v>
+      </x:c>
+      <x:c r="D150" s="0" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="B150" s="0">
-        <x:v>12.19</x:v>
-      </x:c>
-      <x:c r="C150" s="0">
-        <x:v>-0.3</x:v>
-      </x:c>
-      <x:c r="D150" s="0" t="s">
-        <x:v>124</x:v>
-      </x:c>
       <x:c r="E150" s="0">
-        <x:v>559000</x:v>
+        <x:v>906840</x:v>
       </x:c>
       <x:c r="F150" s="0" t="s">
         <x:v>11</x:v>
@@ -5125,68 +5128,68 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H150" s="0">
-        <x:v>2865374550</x:v>
+        <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I150" s="0">
-        <x:v>0.0084</x:v>
+        <x:v>0.0159</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:9">
       <x:c r="A151" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B151" s="0">
-        <x:v>48.2</x:v>
+        <x:v>3.26</x:v>
       </x:c>
       <x:c r="C151" s="0">
-        <x:v>-1</x:v>
+        <x:v>-0.02</x:v>
       </x:c>
       <x:c r="D151" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E151" s="0">
-        <x:v>8900056</x:v>
+        <x:v>895039950</x:v>
       </x:c>
       <x:c r="F151" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G151" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H151" s="0">
-        <x:v>16507905000</x:v>
+        <x:v>7382591324</x:v>
       </x:c>
       <x:c r="I151" s="0">
-        <x:v>0.0233</x:v>
+        <x:v>0.1212</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:9">
       <x:c r="A152" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B152" s="0">
-        <x:v>264</x:v>
+        <x:v>52.15</x:v>
       </x:c>
       <x:c r="C152" s="0">
-        <x:v>9.25</x:v>
+        <x:v>-0.85</x:v>
       </x:c>
       <x:c r="D152" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E152" s="0">
-        <x:v>164306000</x:v>
+        <x:v>575933040</x:v>
       </x:c>
       <x:c r="F152" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G152" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H152" s="0">
-        <x:v>24073631758</x:v>
+        <x:v>2741117556</x:v>
       </x:c>
       <x:c r="I152" s="0">
-        <x:v>0.2943</x:v>
+        <x:v>0.2101</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:9">
@@ -5194,16 +5197,16 @@
         <x:v>126</x:v>
       </x:c>
       <x:c r="B153" s="0">
-        <x:v>55.95</x:v>
+        <x:v>12.34</x:v>
       </x:c>
       <x:c r="C153" s="0">
-        <x:v>2.15</x:v>
+        <x:v>0.15</x:v>
       </x:c>
       <x:c r="D153" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E153" s="0">
-        <x:v>275000</x:v>
+        <x:v>559000</x:v>
       </x:c>
       <x:c r="F153" s="0" t="s">
         <x:v>11</x:v>
@@ -5212,56 +5215,56 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H153" s="0">
-        <x:v>580678850</x:v>
+        <x:v>2865374550</x:v>
       </x:c>
       <x:c r="I153" s="0">
-        <x:v>0.0204</x:v>
+        <x:v>0.0084</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:9">
       <x:c r="A154" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B154" s="0">
-        <x:v>53</x:v>
+        <x:v>49.8</x:v>
       </x:c>
       <x:c r="C154" s="0">
-        <x:v>1.25</x:v>
+        <x:v>1.6</x:v>
       </x:c>
       <x:c r="D154" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E154" s="0">
-        <x:v>231651480</x:v>
+        <x:v>8900056</x:v>
       </x:c>
       <x:c r="F154" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G154" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H154" s="0">
-        <x:v>2741117556</x:v>
+        <x:v>16507905000</x:v>
       </x:c>
       <x:c r="I154" s="0">
-        <x:v>0.0845</x:v>
+        <x:v>0.0233</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:9">
       <x:c r="A155" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B155" s="0">
-        <x:v>14.86</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="C155" s="0">
-        <x:v>-0.05</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D155" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E155" s="0">
-        <x:v>31860000</x:v>
+        <x:v>164306000</x:v>
       </x:c>
       <x:c r="F155" s="0" t="s">
         <x:v>11</x:v>
@@ -5270,230 +5273,230 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H155" s="0">
-        <x:v>3025063909</x:v>
+        <x:v>24073631758</x:v>
       </x:c>
       <x:c r="I155" s="0">
-        <x:v>0.4539</x:v>
+        <x:v>0.2943</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:9">
       <x:c r="A156" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B156" s="0">
-        <x:v>93.95</x:v>
+        <x:v>57.8</x:v>
       </x:c>
       <x:c r="C156" s="0">
-        <x:v>1.55</x:v>
+        <x:v>1.85</x:v>
       </x:c>
       <x:c r="D156" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E156" s="0">
-        <x:v>41650000</x:v>
+        <x:v>275000</x:v>
       </x:c>
       <x:c r="F156" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G156" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H156" s="0">
-        <x:v>1781510191</x:v>
+        <x:v>580678850</x:v>
       </x:c>
       <x:c r="I156" s="0">
-        <x:v>0.0234</x:v>
+        <x:v>0.0204</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:9">
       <x:c r="A157" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B157" s="0">
-        <x:v>15.85</x:v>
+        <x:v>52.15</x:v>
       </x:c>
       <x:c r="C157" s="0">
-        <x:v>-0.1</x:v>
+        <x:v>-0.85</x:v>
       </x:c>
       <x:c r="D157" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="E157" s="0">
-        <x:v>815000</x:v>
+        <x:v>231651480</x:v>
       </x:c>
       <x:c r="F157" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G157" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H157" s="0">
-        <x:v>2020891371</x:v>
+        <x:v>2741117556</x:v>
       </x:c>
       <x:c r="I157" s="0">
-        <x:v>0.0202</x:v>
+        <x:v>0.0845</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:9">
       <x:c r="A158" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B158" s="0">
-        <x:v>83.2</x:v>
+        <x:v>14.94</x:v>
       </x:c>
       <x:c r="C158" s="0">
-        <x:v>1.15</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="D158" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="E158" s="0">
-        <x:v>8300000</x:v>
+        <x:v>31860000</x:v>
       </x:c>
       <x:c r="F158" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G158" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H158" s="0">
-        <x:v>2941310980</x:v>
+        <x:v>3025063909</x:v>
       </x:c>
       <x:c r="I158" s="0">
-        <x:v>0.1417</x:v>
+        <x:v>0.4539</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:9">
       <x:c r="A159" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B159" s="0">
-        <x:v>4.16</x:v>
+        <x:v>94.4</x:v>
       </x:c>
       <x:c r="C159" s="0">
-        <x:v>-0.06</x:v>
+        <x:v>0.45</x:v>
       </x:c>
       <x:c r="D159" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="E159" s="0">
-        <x:v>13000000</x:v>
+        <x:v>41650000</x:v>
       </x:c>
       <x:c r="F159" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G159" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H159" s="0">
-        <x:v>1416740879</x:v>
+        <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I159" s="0">
-        <x:v>0.4613</x:v>
+        <x:v>0.0234</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:9">
       <x:c r="A160" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B160" s="0">
-        <x:v>117.2</x:v>
+        <x:v>16.01</x:v>
       </x:c>
       <x:c r="C160" s="0">
-        <x:v>-3.6</x:v>
+        <x:v>0.16</x:v>
       </x:c>
       <x:c r="D160" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E160" s="0">
-        <x:v>1999793</x:v>
+        <x:v>815000</x:v>
       </x:c>
       <x:c r="F160" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G160" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H160" s="0">
-        <x:v>1742315226</x:v>
+        <x:v>2020891371</x:v>
       </x:c>
       <x:c r="I160" s="0">
-        <x:v>0.0494</x:v>
+        <x:v>0.0202</x:v>
       </x:c>
     </x:row>
     <x:row r="161" spans="1:9">
       <x:c r="A161" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B161" s="0">
-        <x:v>51.35</x:v>
+        <x:v>85.5</x:v>
       </x:c>
       <x:c r="C161" s="0">
-        <x:v>2.85</x:v>
+        <x:v>2.3</x:v>
       </x:c>
       <x:c r="D161" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="E161" s="0">
-        <x:v>1859145</x:v>
+        <x:v>8300000</x:v>
       </x:c>
       <x:c r="F161" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G161" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H161" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>2941310980</x:v>
       </x:c>
       <x:c r="I161" s="0">
-        <x:v>0.0324</x:v>
+        <x:v>0.1417</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:9">
       <x:c r="A162" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B162" s="0">
-        <x:v>3.28</x:v>
+        <x:v>4.18</x:v>
       </x:c>
       <x:c r="C162" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="D162" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="E162" s="0">
-        <x:v>689661000</x:v>
+        <x:v>13000000</x:v>
       </x:c>
       <x:c r="F162" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G162" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H162" s="0">
-        <x:v>7382591324</x:v>
+        <x:v>1416740879</x:v>
       </x:c>
       <x:c r="I162" s="0">
-        <x:v>0.0934</x:v>
+        <x:v>0.4613</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:9">
       <x:c r="A163" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B163" s="0">
-        <x:v>51.35</x:v>
+        <x:v>118.6</x:v>
       </x:c>
       <x:c r="C163" s="0">
-        <x:v>2.85</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="D163" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="E163" s="0">
-        <x:v>1902000</x:v>
+        <x:v>1999793</x:v>
       </x:c>
       <x:c r="F163" s="0" t="s">
         <x:v>11</x:v>
@@ -5502,10 +5505,10 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H163" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>1742315226</x:v>
       </x:c>
       <x:c r="I163" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0494</x:v>
       </x:c>
     </x:row>
     <x:row r="164" spans="1:9">
@@ -5513,74 +5516,74 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B164" s="0">
-        <x:v>93.95</x:v>
+        <x:v>50.2</x:v>
       </x:c>
       <x:c r="C164" s="0">
-        <x:v>1.55</x:v>
+        <x:v>-1.15</x:v>
       </x:c>
       <x:c r="D164" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="E164" s="0">
-        <x:v>56520000</x:v>
+        <x:v>1859145</x:v>
       </x:c>
       <x:c r="F164" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G164" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H164" s="0">
-        <x:v>1781510191</x:v>
+        <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I164" s="0">
-        <x:v>0.0317</x:v>
+        <x:v>0.0324</x:v>
       </x:c>
     </x:row>
     <x:row r="165" spans="1:9">
       <x:c r="A165" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B165" s="0">
-        <x:v>93.95</x:v>
+        <x:v>3.26</x:v>
       </x:c>
       <x:c r="C165" s="0">
-        <x:v>1.55</x:v>
+        <x:v>-0.02</x:v>
       </x:c>
       <x:c r="D165" s="0" t="s">
         <x:v>136</x:v>
       </x:c>
       <x:c r="E165" s="0">
-        <x:v>888325</x:v>
+        <x:v>689661000</x:v>
       </x:c>
       <x:c r="F165" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G165" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H165" s="0">
-        <x:v>1781510191</x:v>
+        <x:v>7382591324</x:v>
       </x:c>
       <x:c r="I165" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0934</x:v>
       </x:c>
     </x:row>
     <x:row r="166" spans="1:9">
       <x:c r="A166" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B166" s="0">
-        <x:v>7.38</x:v>
+        <x:v>50.2</x:v>
       </x:c>
       <x:c r="C166" s="0">
-        <x:v>0.06</x:v>
+        <x:v>-1.15</x:v>
       </x:c>
       <x:c r="D166" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="E166" s="0">
-        <x:v>5581810</x:v>
+        <x:v>1902000</x:v>
       </x:c>
       <x:c r="F166" s="0" t="s">
         <x:v>11</x:v>
@@ -5589,7 +5592,7 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H166" s="0">
-        <x:v>9028523851</x:v>
+        <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I166" s="0">
         <x:v>0</x:v>
@@ -5597,48 +5600,48 @@
     </x:row>
     <x:row r="167" spans="1:9">
       <x:c r="A167" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B167" s="0">
-        <x:v>51.35</x:v>
+        <x:v>94.4</x:v>
       </x:c>
       <x:c r="C167" s="0">
-        <x:v>2.85</x:v>
+        <x:v>0.45</x:v>
       </x:c>
       <x:c r="D167" s="0" t="s">
         <x:v>137</x:v>
       </x:c>
       <x:c r="E167" s="0">
-        <x:v>504000000</x:v>
+        <x:v>56520000</x:v>
       </x:c>
       <x:c r="F167" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G167" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H167" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I167" s="0">
-        <x:v>0.2043</x:v>
+        <x:v>0.0317</x:v>
       </x:c>
     </x:row>
     <x:row r="168" spans="1:9">
       <x:c r="A168" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B168" s="0">
-        <x:v>264</x:v>
+        <x:v>94.4</x:v>
       </x:c>
       <x:c r="C168" s="0">
-        <x:v>9.25</x:v>
+        <x:v>0.45</x:v>
       </x:c>
       <x:c r="D168" s="0" t="s">
         <x:v>137</x:v>
       </x:c>
       <x:c r="E168" s="0">
-        <x:v>21500032</x:v>
+        <x:v>888325</x:v>
       </x:c>
       <x:c r="F168" s="0" t="s">
         <x:v>11</x:v>
@@ -5647,38 +5650,125 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H168" s="0">
-        <x:v>24073631758</x:v>
+        <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I168" s="0">
-        <x:v>0.0383</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="169" spans="1:9">
       <x:c r="A169" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B169" s="0">
-        <x:v>1130</x:v>
+        <x:v>7.63</x:v>
       </x:c>
       <x:c r="C169" s="0">
-        <x:v>10</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="D169" s="0" t="s">
         <x:v>137</x:v>
       </x:c>
       <x:c r="E169" s="0">
+        <x:v>5581810</x:v>
+      </x:c>
+      <x:c r="F169" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G169" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H169" s="0">
+        <x:v>9028523851</x:v>
+      </x:c>
+      <x:c r="I169" s="0">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170" spans="1:9">
+      <x:c r="A170" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B170" s="0">
+        <x:v>50.2</x:v>
+      </x:c>
+      <x:c r="C170" s="0">
+        <x:v>-1.15</x:v>
+      </x:c>
+      <x:c r="D170" s="0" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="E170" s="0">
+        <x:v>504000000</x:v>
+      </x:c>
+      <x:c r="F170" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G170" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H170" s="0">
+        <x:v>2467243928</x:v>
+      </x:c>
+      <x:c r="I170" s="0">
+        <x:v>0.2043</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171" spans="1:9">
+      <x:c r="A171" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B171" s="0">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="C171" s="0">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D171" s="0" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="E171" s="0">
+        <x:v>21500032</x:v>
+      </x:c>
+      <x:c r="F171" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G171" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H171" s="0">
+        <x:v>24073631758</x:v>
+      </x:c>
+      <x:c r="I171" s="0">
+        <x:v>0.0383</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172" spans="1:9">
+      <x:c r="A172" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B172" s="0">
+        <x:v>1139</x:v>
+      </x:c>
+      <x:c r="C172" s="0">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D172" s="0" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="E172" s="0">
         <x:v>6455151</x:v>
       </x:c>
-      <x:c r="F169" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G169" s="0">
-        <x:v>2025.09</x:v>
-      </x:c>
-      <x:c r="H169" s="0">
+      <x:c r="F172" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G172" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H172" s="0">
         <x:v>1586603352</x:v>
       </x:c>
-      <x:c r="I169" s="0">
+      <x:c r="I172" s="0">
         <x:v>0.1745</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/yeni-is-anlasmalari/data/yeni-is-anlasmalari.xlsx
+++ b/app/borsa/yeni-is-anlasmalari/data/yeni-is-anlasmalari.xlsx
@@ -43,6 +43,15 @@
     <x:t>Yeni İş İlişkisi / Yıllık Satışlar</x:t>
   </x:si>
   <x:si>
+    <x:t>FORTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-05-04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRY</x:t>
+  </x:si>
+  <x:si>
     <x:t>ASELS</x:t>
   </x:si>
   <x:si>
@@ -52,6 +61,12 @@
     <x:t>USD</x:t>
   </x:si>
   <x:si>
+    <x:t>SMRTG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUR</x:t>
+  </x:si>
+  <x:si>
     <x:t>AKHAN</x:t>
   </x:si>
   <x:si>
@@ -61,9 +76,6 @@
     <x:t>2026-04-29</x:t>
   </x:si>
   <x:si>
-    <x:t>EUR</x:t>
-  </x:si>
-  <x:si>
     <x:t>CWENE</x:t>
   </x:si>
   <x:si>
@@ -73,9 +85,6 @@
     <x:t>2026-04-28</x:t>
   </x:si>
   <x:si>
-    <x:t>TRY</x:t>
-  </x:si>
-  <x:si>
     <x:t>ASTOR</x:t>
   </x:si>
   <x:si>
@@ -100,9 +109,6 @@
     <x:t>2026-04-22</x:t>
   </x:si>
   <x:si>
-    <x:t>FORTE</x:t>
-  </x:si>
-  <x:si>
     <x:t>MEKAG</x:t>
   </x:si>
   <x:si>
@@ -254,9 +260,6 @@
   </x:si>
   <x:si>
     <x:t>2026-03-10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMRTG</x:t>
   </x:si>
   <x:si>
     <x:t>2026-03-06</x:t>
@@ -781,7 +784,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I172"/>
+  <x:dimension ref="A1:I174"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -818,28 +821,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>420.25</x:v>
+        <x:v>98.2</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>-5.25</x:v>
+        <x:v>3.8</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>125100000</x:v>
+        <x:v>12100000</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>2026.03</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>184925592000</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>0.0304</x:v>
+        <x:v>0.005</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -847,115 +850,115 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>28.62</x:v>
+        <x:v>431.75</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>0.24</x:v>
+        <x:v>11.5</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>76650</x:v>
+        <x:v>125100000</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2026.03</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>7297855153</x:v>
+        <x:v>184925592000</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>0.0005</x:v>
+        <x:v>0.0304</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
       <x:c r="A4" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B4" s="0">
+        <x:v>7.88</x:v>
+      </x:c>
+      <x:c r="C4" s="0">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B4" s="0">
-        <x:v>118.6</x:v>
-      </x:c>
-      <x:c r="C4" s="0">
-        <x:v>1.4</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
       <x:c r="E4" s="0">
-        <x:v>915000</x:v>
+        <x:v>32010000</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G4" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>3150489640</x:v>
+        <x:v>10581001663</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>0.0153</x:v>
+        <x:v>0.1592</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
       <x:c r="A5" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>36.64</x:v>
+        <x:v>28.92</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>0.2</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>2136645</x:v>
+        <x:v>76650</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>2026.03</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>17386730041</x:v>
+        <x:v>7297855153</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>0.0055</x:v>
+        <x:v>0.0005</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
       <x:c r="A6" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>4.91</x:v>
+        <x:v>116.7</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>0.08</x:v>
+        <x:v>-1.9</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>132077304</x:v>
+        <x:v>915000</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G6" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>855070469</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>0.1545</x:v>
+        <x:v>0.0153</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -963,28 +966,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>284</x:v>
+        <x:v>35.8</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>20</x:v>
+        <x:v>-0.84</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>51531000</x:v>
+        <x:v>2136645</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2026.03</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>35290767390</x:v>
+        <x:v>17386730041</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>0.0656</x:v>
+        <x:v>0.0055</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -992,16 +995,16 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>1139</x:v>
+        <x:v>5.4</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>9</x:v>
+        <x:v>0.49</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>950978</x:v>
+        <x:v>132077304</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
         <x:v>11</x:v>
@@ -1010,39 +1013,39 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>1883544167</x:v>
+        <x:v>855070469</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>0.0227</x:v>
+        <x:v>0.1545</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
       <x:c r="A9" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B9" s="0">
+        <x:v>290.25</x:v>
+      </x:c>
+      <x:c r="C9" s="0">
+        <x:v>6.25</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="B9" s="0">
-        <x:v>547</x:v>
-      </x:c>
-      <x:c r="C9" s="0">
-        <x:v>-9</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="E9" s="0">
-        <x:v>100000000</x:v>
+        <x:v>51531000</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G9" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>71453576000</x:v>
+        <x:v>35290767390</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>0.0628</x:v>
+        <x:v>0.0656</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -1050,74 +1053,74 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>85.5</x:v>
+        <x:v>1200</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>2.3</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>286071819</x:v>
+        <x:v>950978</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G10" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>1883544167</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>0.0818</x:v>
+        <x:v>0.0227</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
       <x:c r="A11" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>118.6</x:v>
+        <x:v>567.5</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>1.4</x:v>
+        <x:v>20.5</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>883793</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G11" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>3150489640</x:v>
+        <x:v>71453576000</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>0.0148</x:v>
+        <x:v>0.0628</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
       <x:c r="A12" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>50.2</x:v>
+        <x:v>82.35</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>-1.15</x:v>
+        <x:v>-3.15</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>606770</x:v>
+        <x:v>286071819</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
         <x:v>11</x:v>
@@ -1126,59 +1129,59 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>0.0064</x:v>
+        <x:v>0.0818</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
       <x:c r="A13" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B13" s="0">
+        <x:v>116.7</x:v>
+      </x:c>
+      <x:c r="C13" s="0">
+        <x:v>-1.9</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B13" s="0">
-        <x:v>58.95</x:v>
-      </x:c>
-      <x:c r="C13" s="0">
-        <x:v>0.75</x:v>
-      </x:c>
-      <x:c r="D13" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
       <x:c r="E13" s="0">
-        <x:v>505597002</x:v>
+        <x:v>883793</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G13" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>8121300519</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>0.0623</x:v>
+        <x:v>0.0148</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
       <x:c r="A14" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>50.2</x:v>
+        <x:v>55.2</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>-1.15</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>948000</x:v>
+        <x:v>606770</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G14" s="0">
         <x:v>2025.12</x:v>
@@ -1187,24 +1190,24 @@
         <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>0.0101</x:v>
+        <x:v>0.0064</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
       <x:c r="A15" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>94.4</x:v>
+        <x:v>58.25</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>0.45</x:v>
+        <x:v>-0.7</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>622000</x:v>
+        <x:v>505597002</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
         <x:v>11</x:v>
@@ -1213,358 +1216,358 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>8121300519</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>0.0114</x:v>
+        <x:v>0.0623</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
       <x:c r="A16" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>4.09</x:v>
+        <x:v>55.2</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>983000</x:v>
+        <x:v>948000</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G16" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>2875634546</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>0.018</x:v>
+        <x:v>0.0101</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
       <x:c r="A17" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B17" s="0">
+        <x:v>98.2</x:v>
+      </x:c>
+      <x:c r="C17" s="0">
+        <x:v>3.8</x:v>
+      </x:c>
+      <x:c r="D17" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="B17" s="0">
-        <x:v>74.6</x:v>
-      </x:c>
-      <x:c r="C17" s="0">
-        <x:v>4.1</x:v>
-      </x:c>
-      <x:c r="D17" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="E17" s="0">
-        <x:v>3421818</x:v>
+        <x:v>622000</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G17" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>5948036961</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>0.0257</x:v>
+        <x:v>0.0114</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
       <x:c r="A18" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>44</x:v>
+        <x:v>4.01</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>-1.14</x:v>
+        <x:v>-0.08</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>697435</x:v>
+        <x:v>983000</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G18" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>4728937463</x:v>
+        <x:v>2875634546</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>0.0066</x:v>
+        <x:v>0.018</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
       <x:c r="A19" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B19" s="0">
+        <x:v>77.7</x:v>
+      </x:c>
+      <x:c r="C19" s="0">
+        <x:v>3.1</x:v>
+      </x:c>
+      <x:c r="D19" s="0" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="B19" s="0">
-        <x:v>55.8</x:v>
-      </x:c>
-      <x:c r="C19" s="0">
-        <x:v>-1.4</x:v>
-      </x:c>
-      <x:c r="D19" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
       <x:c r="E19" s="0">
-        <x:v>4587145</x:v>
+        <x:v>3421818</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G19" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>16733157490</x:v>
+        <x:v>5948036961</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>0.0123</x:v>
+        <x:v>0.0257</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
       <x:c r="A20" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>41.22</x:v>
+        <x:v>42.9</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>0.2</x:v>
+        <x:v>-1.1</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>43200000</x:v>
+        <x:v>697435</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G20" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>8236540064</x:v>
+        <x:v>4728937463</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>0.2345</x:v>
+        <x:v>0.0066</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
       <x:c r="A21" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>16.01</x:v>
+        <x:v>61.35</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>0.16</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>1200000</x:v>
+        <x:v>4587145</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G21" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>3139850323</x:v>
+        <x:v>16733157490</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>0.0201</x:v>
+        <x:v>0.0123</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
       <x:c r="A22" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>58.95</x:v>
+        <x:v>40.94</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>0.75</x:v>
+        <x:v>-0.28</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>247902522</x:v>
+        <x:v>43200000</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G22" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>8121300519</x:v>
+        <x:v>8236540064</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>0.0305</x:v>
+        <x:v>0.2345</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
       <x:c r="A23" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>50.2</x:v>
+        <x:v>16.53</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>-1.15</x:v>
+        <x:v>0.52</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>366000</x:v>
+        <x:v>1200000</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G23" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>3139850323</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>0.0039</x:v>
+        <x:v>0.0201</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
       <x:c r="A24" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>273.5</x:v>
+        <x:v>58.25</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>-3.25</x:v>
+        <x:v>-0.7</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>141051834</x:v>
+        <x:v>247902522</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G24" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>709077088</x:v>
+        <x:v>8121300519</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>0.1989</x:v>
+        <x:v>0.0305</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
       <x:c r="A25" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B25" s="0">
+        <x:v>55.2</x:v>
+      </x:c>
+      <x:c r="C25" s="0">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D25" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="B25" s="0">
-        <x:v>4.73</x:v>
-      </x:c>
-      <x:c r="C25" s="0">
-        <x:v>0.04</x:v>
-      </x:c>
-      <x:c r="D25" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
       <x:c r="E25" s="0">
-        <x:v>5096500000</x:v>
+        <x:v>366000</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>19538660616</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>0.2608</x:v>
+        <x:v>0.0039</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
       <x:c r="A26" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B26" s="0">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="C26" s="0">
+        <x:v>-3.5</x:v>
+      </x:c>
+      <x:c r="D26" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="B26" s="0">
-        <x:v>4.73</x:v>
-      </x:c>
-      <x:c r="C26" s="0">
-        <x:v>0.04</x:v>
-      </x:c>
-      <x:c r="D26" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
       <x:c r="E26" s="0">
-        <x:v>5096500000</x:v>
+        <x:v>141051834</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>19538660616</x:v>
+        <x:v>709077088</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>0.2608</x:v>
+        <x:v>0.1989</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
       <x:c r="A27" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>36.64</x:v>
+        <x:v>4.73</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>0.2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>37500000</x:v>
+        <x:v>5096500000</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>16355768622</x:v>
+        <x:v>19538660616</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>0.1024</x:v>
+        <x:v>0.2608</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1572,135 +1575,135 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>219.8</x:v>
+        <x:v>4.73</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>2.8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>2030000</x:v>
+        <x:v>5096500000</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>2159813703</x:v>
+        <x:v>19538660616</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>0.042</x:v>
+        <x:v>0.2608</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
       <x:c r="A29" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>55.8</x:v>
+        <x:v>35.8</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>-1.4</x:v>
+        <x:v>-0.84</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>31146246</x:v>
+        <x:v>37500000</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G29" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>16733157490</x:v>
+        <x:v>16355768622</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>0.0832</x:v>
+        <x:v>0.1024</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
       <x:c r="A30" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B30" s="0">
+        <x:v>232.1</x:v>
+      </x:c>
+      <x:c r="C30" s="0">
+        <x:v>12.3</x:v>
+      </x:c>
+      <x:c r="D30" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="B30" s="0">
-        <x:v>11.25</x:v>
-      </x:c>
-      <x:c r="C30" s="0">
-        <x:v>0.14</x:v>
-      </x:c>
-      <x:c r="D30" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
       <x:c r="E30" s="0">
-        <x:v>1000000</x:v>
+        <x:v>2030000</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G30" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>7221187888</x:v>
+        <x:v>2159813703</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>0.0001</x:v>
+        <x:v>0.042</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
       <x:c r="A31" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B31" s="0">
+        <x:v>61.35</x:v>
+      </x:c>
+      <x:c r="C31" s="0">
+        <x:v>5.55</x:v>
+      </x:c>
+      <x:c r="D31" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="B31" s="0">
-        <x:v>11.25</x:v>
-      </x:c>
-      <x:c r="C31" s="0">
-        <x:v>0.14</x:v>
-      </x:c>
-      <x:c r="D31" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
       <x:c r="E31" s="0">
-        <x:v>3150000</x:v>
+        <x:v>31146246</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G31" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>7221187888</x:v>
+        <x:v>16733157490</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>0.0227</x:v>
+        <x:v>0.0832</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
       <x:c r="A32" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>11.25</x:v>
+        <x:v>11.46</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>0.14</x:v>
+        <x:v>0.21</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>2690000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G32" s="0">
         <x:v>2025.12</x:v>
@@ -1709,169 +1712,169 @@
         <x:v>7221187888</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>0.0166</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
       <x:c r="A33" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>55.8</x:v>
+        <x:v>11.46</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>-1.4</x:v>
+        <x:v>0.21</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>4103000</x:v>
+        <x:v>3150000</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G33" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>16733157490</x:v>
+        <x:v>7221187888</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>0.0109</x:v>
+        <x:v>0.0227</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
       <x:c r="A34" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>118.6</x:v>
+        <x:v>11.46</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>1.4</x:v>
+        <x:v>0.21</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>500000</x:v>
+        <x:v>2690000</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G34" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>3150489640</x:v>
+        <x:v>7221187888</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>0.0083</x:v>
+        <x:v>0.0166</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
       <x:c r="A35" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>50.2</x:v>
+        <x:v>61.35</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>-1.15</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>872928</x:v>
+        <x:v>4103000</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G35" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>16733157490</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>0.0092</x:v>
+        <x:v>0.0109</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
       <x:c r="A36" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>94.4</x:v>
+        <x:v>116.7</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>0.45</x:v>
+        <x:v>-1.9</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>21250000</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G36" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>0.0087</x:v>
+        <x:v>0.0083</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
       <x:c r="A37" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>58.95</x:v>
+        <x:v>55.2</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>0.75</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>67690912</x:v>
+        <x:v>872928</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G37" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>8121300519</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>0.0083</x:v>
+        <x:v>0.0092</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
       <x:c r="A38" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>36.64</x:v>
+        <x:v>98.2</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>0.2</x:v>
+        <x:v>3.8</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>65458848</x:v>
+        <x:v>21250000</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
         <x:v>11</x:v>
@@ -1880,85 +1883,85 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>16355768622</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>0.1784</x:v>
+        <x:v>0.0087</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
       <x:c r="A39" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>24.34</x:v>
+        <x:v>58.25</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>0.04</x:v>
+        <x:v>-0.7</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>689500000</x:v>
+        <x:v>67690912</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G39" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>884571536</x:v>
+        <x:v>8121300519</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>0.7795</x:v>
+        <x:v>0.0083</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
       <x:c r="A40" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B40" s="0">
+        <x:v>35.8</x:v>
+      </x:c>
+      <x:c r="C40" s="0">
+        <x:v>-0.84</x:v>
+      </x:c>
+      <x:c r="D40" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B40" s="0">
-        <x:v>6.18</x:v>
-      </x:c>
-      <x:c r="C40" s="0">
-        <x:v>0.28</x:v>
-      </x:c>
-      <x:c r="D40" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
       <x:c r="E40" s="0">
-        <x:v>3024490</x:v>
+        <x:v>65458848</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G40" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>2322993973</x:v>
+        <x:v>16355768622</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>0.0671</x:v>
+        <x:v>0.1784</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
       <x:c r="A41" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B41" s="0">
+        <x:v>24.7</x:v>
+      </x:c>
+      <x:c r="C41" s="0">
+        <x:v>0.36</x:v>
+      </x:c>
+      <x:c r="D41" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B41" s="0">
-        <x:v>6.18</x:v>
-      </x:c>
-      <x:c r="C41" s="0">
-        <x:v>0.28</x:v>
-      </x:c>
-      <x:c r="D41" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
       <x:c r="E41" s="0">
-        <x:v>4510336</x:v>
+        <x:v>689500000</x:v>
       </x:c>
       <x:c r="F41" s="0" t="s">
         <x:v>11</x:v>
@@ -1967,114 +1970,114 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>2322993973</x:v>
+        <x:v>884571536</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>0.0865</x:v>
+        <x:v>0.7795</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
       <x:c r="A42" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>49.8</x:v>
+        <x:v>6.08</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>1.6</x:v>
+        <x:v>-0.1</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>205000000</x:v>
+        <x:v>3024490</x:v>
       </x:c>
       <x:c r="F42" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G42" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>20597209000</x:v>
+        <x:v>2322993973</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>0.4434</x:v>
+        <x:v>0.0671</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
       <x:c r="A43" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>317</x:v>
+        <x:v>6.08</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>-15.25</x:v>
+        <x:v>-0.1</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>305000000</x:v>
+        <x:v>4510336</x:v>
       </x:c>
       <x:c r="F43" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G43" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>400439646</x:v>
+        <x:v>2322993973</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>0.7617</x:v>
+        <x:v>0.0865</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
       <x:c r="A44" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>85.5</x:v>
+        <x:v>51.05</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>2.3</x:v>
+        <x:v>1.25</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>11700000</x:v>
+        <x:v>205000000</x:v>
       </x:c>
       <x:c r="F44" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G44" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>20597209000</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>0.1718</x:v>
+        <x:v>0.4434</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
       <x:c r="A45" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>219.8</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>2.8</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>1900000</x:v>
+        <x:v>305000000</x:v>
       </x:c>
       <x:c r="F45" s="0" t="s">
         <x:v>11</x:v>
@@ -2083,114 +2086,114 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>2159813703</x:v>
+        <x:v>400439646</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>0.0391</x:v>
+        <x:v>0.7617</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
       <x:c r="A46" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>4.09</x:v>
+        <x:v>82.35</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>-3.15</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>1670000</x:v>
+        <x:v>11700000</x:v>
       </x:c>
       <x:c r="F46" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G46" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>2875634546</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>0.0298</x:v>
+        <x:v>0.1718</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
       <x:c r="A47" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>24.34</x:v>
+        <x:v>232.1</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>0.04</x:v>
+        <x:v>12.3</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>48895800</x:v>
+        <x:v>1900000</x:v>
       </x:c>
       <x:c r="F47" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G47" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>884571536</x:v>
+        <x:v>2159813703</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>0.0553</x:v>
+        <x:v>0.0391</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
       <x:c r="A48" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>24.34</x:v>
+        <x:v>4.01</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>0.04</x:v>
+        <x:v>-0.08</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>689500000</x:v>
+        <x:v>1670000</x:v>
       </x:c>
       <x:c r="F48" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G48" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>884571536</x:v>
+        <x:v>2875634546</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>0.7795</x:v>
+        <x:v>0.0298</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
       <x:c r="A49" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>45.12</x:v>
+        <x:v>24.7</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>0.72</x:v>
+        <x:v>0.36</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>3102911</x:v>
+        <x:v>48895800</x:v>
       </x:c>
       <x:c r="F49" s="0" t="s">
         <x:v>11</x:v>
@@ -2199,259 +2202,259 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>2907014564</x:v>
+        <x:v>884571536</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>0.0475</x:v>
+        <x:v>0.0553</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
       <x:c r="A50" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B50" s="0">
+        <x:v>24.7</x:v>
+      </x:c>
+      <x:c r="C50" s="0">
+        <x:v>0.36</x:v>
+      </x:c>
+      <x:c r="D50" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="B50" s="0">
-        <x:v>24.2</x:v>
-      </x:c>
-      <x:c r="C50" s="0">
-        <x:v>-0.06</x:v>
-      </x:c>
-      <x:c r="D50" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
       <x:c r="E50" s="0">
-        <x:v>13000000</x:v>
+        <x:v>689500000</x:v>
       </x:c>
       <x:c r="F50" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G50" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>11834942581</x:v>
+        <x:v>884571536</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>0.0563</x:v>
+        <x:v>0.7795</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
       <x:c r="A51" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>74.6</x:v>
+        <x:v>45.36</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>4.1</x:v>
+        <x:v>0.24</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>6800000</x:v>
+        <x:v>3102911</x:v>
       </x:c>
       <x:c r="F51" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G51" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>5948036961</x:v>
+        <x:v>2907014564</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>0.0583</x:v>
+        <x:v>0.0475</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
       <x:c r="A52" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>49.8</x:v>
+        <x:v>23.94</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>1.6</x:v>
+        <x:v>-0.26</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>36750000</x:v>
+        <x:v>13000000</x:v>
       </x:c>
       <x:c r="F52" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G52" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>20597209000</x:v>
+        <x:v>11834942581</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>0.0793</x:v>
+        <x:v>0.0563</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:9">
       <x:c r="A53" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B53" s="0">
-        <x:v>1139</x:v>
+        <x:v>77.7</x:v>
       </x:c>
       <x:c r="C53" s="0">
-        <x:v>9</x:v>
+        <x:v>3.1</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E53" s="0">
-        <x:v>3867260</x:v>
+        <x:v>6800000</x:v>
       </x:c>
       <x:c r="F53" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G53" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H53" s="0">
-        <x:v>1883544167</x:v>
+        <x:v>5948036961</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>0.0912</x:v>
+        <x:v>0.0583</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:9">
       <x:c r="A54" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B54" s="0">
+        <x:v>51.05</x:v>
+      </x:c>
+      <x:c r="C54" s="0">
+        <x:v>1.25</x:v>
+      </x:c>
+      <x:c r="D54" s="0" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="B54" s="0">
-        <x:v>65.35</x:v>
-      </x:c>
-      <x:c r="C54" s="0">
-        <x:v>-0.7</x:v>
-      </x:c>
-      <x:c r="D54" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
       <x:c r="E54" s="0">
-        <x:v>1498029716</x:v>
+        <x:v>36750000</x:v>
       </x:c>
       <x:c r="F54" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G54" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>12030341104</x:v>
+        <x:v>20597209000</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>0.1245</x:v>
+        <x:v>0.0793</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:9">
       <x:c r="A55" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B55" s="0">
-        <x:v>36.64</x:v>
+        <x:v>1200</x:v>
       </x:c>
       <x:c r="C55" s="0">
-        <x:v>0.2</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="E55" s="0">
-        <x:v>48000000</x:v>
+        <x:v>3867260</x:v>
       </x:c>
       <x:c r="F55" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G55" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H55" s="0">
-        <x:v>16355768622</x:v>
+        <x:v>1883544167</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>0.1301</x:v>
+        <x:v>0.0912</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:9">
       <x:c r="A56" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B56" s="0">
-        <x:v>85.5</x:v>
+        <x:v>63.5</x:v>
       </x:c>
       <x:c r="C56" s="0">
-        <x:v>2.3</x:v>
+        <x:v>-1.85</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E56" s="0">
-        <x:v>279699629</x:v>
+        <x:v>1498029716</x:v>
       </x:c>
       <x:c r="F56" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G56" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H56" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>12030341104</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>0.08</x:v>
+        <x:v>0.1245</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:9">
       <x:c r="A57" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B57" s="0">
+        <x:v>35.8</x:v>
+      </x:c>
+      <x:c r="C57" s="0">
+        <x:v>-0.84</x:v>
+      </x:c>
+      <x:c r="D57" s="0" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="B57" s="0">
-        <x:v>14.94</x:v>
-      </x:c>
-      <x:c r="C57" s="0">
-        <x:v>0.08</x:v>
-      </x:c>
-      <x:c r="D57" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
       <x:c r="E57" s="0">
-        <x:v>7971822</x:v>
+        <x:v>48000000</x:v>
       </x:c>
       <x:c r="F57" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G57" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H57" s="0">
-        <x:v>4675369372</x:v>
+        <x:v>16355768622</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>0.0756</x:v>
+        <x:v>0.1301</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:9">
       <x:c r="A58" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B58" s="0">
-        <x:v>50.2</x:v>
+        <x:v>82.35</x:v>
       </x:c>
       <x:c r="C58" s="0">
-        <x:v>-1.15</x:v>
+        <x:v>-3.15</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E58" s="0">
-        <x:v>1104000</x:v>
+        <x:v>279699629</x:v>
       </x:c>
       <x:c r="F58" s="0" t="s">
         <x:v>11</x:v>
@@ -2460,259 +2463,259 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H58" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>0.0116</x:v>
+        <x:v>0.08</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:9">
       <x:c r="A59" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B59" s="0">
-        <x:v>24.34</x:v>
+        <x:v>14.9</x:v>
       </x:c>
       <x:c r="C59" s="0">
-        <x:v>0.04</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E59" s="0">
-        <x:v>48895800</x:v>
+        <x:v>7971822</x:v>
       </x:c>
       <x:c r="F59" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G59" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H59" s="0">
-        <x:v>884571536</x:v>
+        <x:v>4675369372</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>0.0553</x:v>
+        <x:v>0.0756</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:9">
       <x:c r="A60" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B60" s="0">
+        <x:v>55.2</x:v>
+      </x:c>
+      <x:c r="C60" s="0">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D60" s="0" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="B60" s="0">
-        <x:v>3.26</x:v>
-      </x:c>
-      <x:c r="C60" s="0">
-        <x:v>-0.02</x:v>
-      </x:c>
-      <x:c r="D60" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
       <x:c r="E60" s="0">
-        <x:v>191089413</x:v>
+        <x:v>1104000</x:v>
       </x:c>
       <x:c r="F60" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G60" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H60" s="0">
-        <x:v>9665356715</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>0.0198</x:v>
+        <x:v>0.0116</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:9">
       <x:c r="A61" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B61" s="0">
+        <x:v>24.7</x:v>
+      </x:c>
+      <x:c r="C61" s="0">
+        <x:v>0.36</x:v>
+      </x:c>
+      <x:c r="D61" s="0" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="B61" s="0">
-        <x:v>3.26</x:v>
-      </x:c>
-      <x:c r="C61" s="0">
-        <x:v>-0.02</x:v>
-      </x:c>
-      <x:c r="D61" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
       <x:c r="E61" s="0">
-        <x:v>605627160</x:v>
+        <x:v>48895800</x:v>
       </x:c>
       <x:c r="F61" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G61" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H61" s="0">
-        <x:v>9665356715</x:v>
+        <x:v>884571536</x:v>
       </x:c>
       <x:c r="I61" s="0">
-        <x:v>0.0627</x:v>
+        <x:v>0.0553</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:9">
       <x:c r="A62" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B62" s="0">
-        <x:v>26.8</x:v>
+        <x:v>3.25</x:v>
       </x:c>
       <x:c r="C62" s="0">
-        <x:v>0.76</x:v>
+        <x:v>-0.01</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E62" s="0">
-        <x:v>2356546000</x:v>
+        <x:v>191089413</x:v>
       </x:c>
       <x:c r="F62" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G62" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H62" s="0">
-        <x:v>7708004248</x:v>
+        <x:v>9665356715</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>0.3057</x:v>
+        <x:v>0.0198</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:9">
       <x:c r="A63" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B63" s="0">
-        <x:v>16.01</x:v>
+        <x:v>3.25</x:v>
       </x:c>
       <x:c r="C63" s="0">
-        <x:v>0.16</x:v>
+        <x:v>-0.01</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E63" s="0">
-        <x:v>431250</x:v>
+        <x:v>605627160</x:v>
       </x:c>
       <x:c r="F63" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G63" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H63" s="0">
-        <x:v>3139850323</x:v>
+        <x:v>9665356715</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>0.0071</x:v>
+        <x:v>0.0627</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:9">
       <x:c r="A64" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B64" s="0">
-        <x:v>16.01</x:v>
+        <x:v>27.26</x:v>
       </x:c>
       <x:c r="C64" s="0">
-        <x:v>0.16</x:v>
+        <x:v>0.46</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E64" s="0">
-        <x:v>800000</x:v>
+        <x:v>2356546000</x:v>
       </x:c>
       <x:c r="F64" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G64" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H64" s="0">
-        <x:v>3139850323</x:v>
+        <x:v>7708004248</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>0.0131</x:v>
+        <x:v>0.3057</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:9">
       <x:c r="A65" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B65" s="0">
-        <x:v>58.95</x:v>
+        <x:v>16.53</x:v>
       </x:c>
       <x:c r="C65" s="0">
-        <x:v>0.75</x:v>
+        <x:v>0.52</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E65" s="0">
-        <x:v>127172130</x:v>
+        <x:v>431250</x:v>
       </x:c>
       <x:c r="F65" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G65" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H65" s="0">
-        <x:v>8121300519</x:v>
+        <x:v>3139850323</x:v>
       </x:c>
       <x:c r="I65" s="0">
-        <x:v>0.0157</x:v>
+        <x:v>0.0071</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:9">
       <x:c r="A66" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B66" s="0">
-        <x:v>44</x:v>
+        <x:v>16.53</x:v>
       </x:c>
       <x:c r="C66" s="0">
-        <x:v>-1.14</x:v>
+        <x:v>0.52</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E66" s="0">
-        <x:v>42625000</x:v>
+        <x:v>800000</x:v>
       </x:c>
       <x:c r="F66" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G66" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H66" s="0">
-        <x:v>4728937463</x:v>
+        <x:v>3139850323</x:v>
       </x:c>
       <x:c r="I66" s="0">
-        <x:v>0.3994</x:v>
+        <x:v>0.0131</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:9">
       <x:c r="A67" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B67" s="0">
-        <x:v>94.4</x:v>
+        <x:v>58.25</x:v>
       </x:c>
       <x:c r="C67" s="0">
-        <x:v>0.45</x:v>
+        <x:v>-0.7</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E67" s="0">
-        <x:v>1486000</x:v>
+        <x:v>127172130</x:v>
       </x:c>
       <x:c r="F67" s="0" t="s">
         <x:v>11</x:v>
@@ -2721,288 +2724,288 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H67" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>8121300519</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>0.027</x:v>
+        <x:v>0.0157</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:9">
       <x:c r="A68" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B68" s="0">
-        <x:v>284</x:v>
+        <x:v>42.9</x:v>
       </x:c>
       <x:c r="C68" s="0">
-        <x:v>20</x:v>
+        <x:v>-1.1</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E68" s="0">
-        <x:v>768864700</x:v>
+        <x:v>42625000</x:v>
       </x:c>
       <x:c r="F68" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G68" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H68" s="0">
-        <x:v>35290767390</x:v>
+        <x:v>4728937463</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>0.9648</x:v>
+        <x:v>0.3994</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:9">
       <x:c r="A69" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B69" s="0">
-        <x:v>55.8</x:v>
+        <x:v>98.2</x:v>
       </x:c>
       <x:c r="C69" s="0">
-        <x:v>-1.4</x:v>
+        <x:v>3.8</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E69" s="0">
-        <x:v>15938617</x:v>
+        <x:v>1486000</x:v>
       </x:c>
       <x:c r="F69" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G69" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H69" s="0">
-        <x:v>16733157490</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>0.0422</x:v>
+        <x:v>0.027</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:9">
       <x:c r="A70" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B70" s="0">
-        <x:v>13.91</x:v>
+        <x:v>290.25</x:v>
       </x:c>
       <x:c r="C70" s="0">
-        <x:v>-0.67</x:v>
+        <x:v>6.25</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="E70" s="0">
-        <x:v>30438120</x:v>
+        <x:v>768864700</x:v>
       </x:c>
       <x:c r="F70" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G70" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H70" s="0">
-        <x:v>3159124121</x:v>
+        <x:v>35290767390</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>0</x:v>
+        <x:v>0.9648</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:9">
       <x:c r="A71" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B71" s="0">
-        <x:v>219.8</x:v>
+        <x:v>61.35</x:v>
       </x:c>
       <x:c r="C71" s="0">
-        <x:v>2.8</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E71" s="0">
-        <x:v>3900000</x:v>
+        <x:v>15938617</x:v>
       </x:c>
       <x:c r="F71" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G71" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H71" s="0">
-        <x:v>2159813703</x:v>
+        <x:v>16733157490</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>0.0797</x:v>
+        <x:v>0.0422</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:9">
       <x:c r="A72" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B72" s="0">
-        <x:v>219.8</x:v>
+        <x:v>14.29</x:v>
       </x:c>
       <x:c r="C72" s="0">
-        <x:v>2.8</x:v>
+        <x:v>0.38</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E72" s="0">
-        <x:v>2104908</x:v>
+        <x:v>30438120</x:v>
       </x:c>
       <x:c r="F72" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G72" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H72" s="0">
-        <x:v>2159813703</x:v>
+        <x:v>3159124121</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>0.043</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:9">
       <x:c r="A73" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B73" s="0">
-        <x:v>28.62</x:v>
+        <x:v>232.1</x:v>
       </x:c>
       <x:c r="C73" s="0">
-        <x:v>0.24</x:v>
+        <x:v>12.3</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E73" s="0">
         <x:v>3900000</x:v>
       </x:c>
       <x:c r="F73" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G73" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H73" s="0">
-        <x:v>7297855153</x:v>
+        <x:v>2159813703</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>0.0236</x:v>
+        <x:v>0.0797</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:9">
       <x:c r="A74" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B74" s="0">
-        <x:v>4.91</x:v>
+        <x:v>232.1</x:v>
       </x:c>
       <x:c r="C74" s="0">
-        <x:v>0.08</x:v>
+        <x:v>12.3</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E74" s="0">
-        <x:v>496968445</x:v>
+        <x:v>2104908</x:v>
       </x:c>
       <x:c r="F74" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G74" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H74" s="0">
-        <x:v>855070469</x:v>
+        <x:v>2159813703</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>0.5812</x:v>
+        <x:v>0.043</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:9">
       <x:c r="A75" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B75" s="0">
+        <x:v>28.92</x:v>
+      </x:c>
+      <x:c r="C75" s="0">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="D75" s="0" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="B75" s="0">
-        <x:v>13.36</x:v>
-      </x:c>
-      <x:c r="C75" s="0">
-        <x:v>-0.22</x:v>
-      </x:c>
-      <x:c r="D75" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
       <x:c r="E75" s="0">
-        <x:v>108750000</x:v>
+        <x:v>3900000</x:v>
       </x:c>
       <x:c r="F75" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G75" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H75" s="0">
-        <x:v>1982520183</x:v>
+        <x:v>7297855153</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>0.0549</x:v>
+        <x:v>0.0236</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:9">
       <x:c r="A76" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B76" s="0">
-        <x:v>118.6</x:v>
+        <x:v>5.4</x:v>
       </x:c>
       <x:c r="C76" s="0">
-        <x:v>1.4</x:v>
+        <x:v>0.49</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
         <x:v>73</x:v>
       </x:c>
       <x:c r="E76" s="0">
-        <x:v>1605197</x:v>
+        <x:v>496968445</x:v>
       </x:c>
       <x:c r="F76" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G76" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H76" s="0">
-        <x:v>0</x:v>
+        <x:v>855070469</x:v>
       </x:c>
       <x:c r="I76" s="0">
-        <x:v>0</x:v>
+        <x:v>0.5812</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:9">
       <x:c r="A77" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B77" s="0">
-        <x:v>420.25</x:v>
+        <x:v>12.66</x:v>
       </x:c>
       <x:c r="C77" s="0">
-        <x:v>-5.25</x:v>
+        <x:v>-0.7</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E77" s="0">
-        <x:v>54600000</x:v>
+        <x:v>108750000</x:v>
       </x:c>
       <x:c r="F77" s="0" t="s">
         <x:v>11</x:v>
@@ -3011,155 +3014,155 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H77" s="0">
-        <x:v>180444938000</x:v>
+        <x:v>1982520183</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>0.0133</x:v>
+        <x:v>0.0549</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:9">
       <x:c r="A78" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B78" s="0">
-        <x:v>420.25</x:v>
+        <x:v>116.7</x:v>
       </x:c>
       <x:c r="C78" s="0">
-        <x:v>-5.25</x:v>
+        <x:v>-1.9</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E78" s="0">
-        <x:v>111850000</x:v>
+        <x:v>1605197</x:v>
       </x:c>
       <x:c r="F78" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G78" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H78" s="0">
-        <x:v>180444938000</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>0.0273</x:v>
+        <x:v>0.0257</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:9">
       <x:c r="A79" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B79" s="0">
-        <x:v>50.2</x:v>
+        <x:v>431.75</x:v>
       </x:c>
       <x:c r="C79" s="0">
-        <x:v>-1.15</x:v>
+        <x:v>11.5</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E79" s="0">
-        <x:v>803090</x:v>
+        <x:v>54600000</x:v>
       </x:c>
       <x:c r="F79" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G79" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H79" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>180444938000</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>0.0084</x:v>
+        <x:v>0.0133</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:9">
       <x:c r="A80" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B80" s="0">
-        <x:v>26.8</x:v>
+        <x:v>431.75</x:v>
       </x:c>
       <x:c r="C80" s="0">
-        <x:v>0.76</x:v>
+        <x:v>11.5</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E80" s="0">
-        <x:v>2356546000</x:v>
+        <x:v>111850000</x:v>
       </x:c>
       <x:c r="F80" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G80" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H80" s="0">
-        <x:v>7708004248</x:v>
+        <x:v>180444938000</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>0.3057</x:v>
+        <x:v>0.0273</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:9">
       <x:c r="A81" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B81" s="0">
-        <x:v>1139</x:v>
+        <x:v>55.2</x:v>
       </x:c>
       <x:c r="C81" s="0">
-        <x:v>9</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
         <x:v>76</x:v>
       </x:c>
       <x:c r="E81" s="0">
-        <x:v>875400</x:v>
+        <x:v>803090</x:v>
       </x:c>
       <x:c r="F81" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G81" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H81" s="0">
-        <x:v>1883544167</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I81" s="0">
-        <x:v>0.0205</x:v>
+        <x:v>0.0084</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:9">
       <x:c r="A82" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B82" s="0">
+        <x:v>27.26</x:v>
+      </x:c>
+      <x:c r="C82" s="0">
+        <x:v>0.46</x:v>
+      </x:c>
+      <x:c r="D82" s="0" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="B82" s="0">
-        <x:v>26.8</x:v>
-      </x:c>
-      <x:c r="C82" s="0">
-        <x:v>0.08</x:v>
-      </x:c>
-      <x:c r="D82" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
       <x:c r="E82" s="0">
-        <x:v>330000000</x:v>
+        <x:v>2356546000</x:v>
       </x:c>
       <x:c r="F82" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G82" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H82" s="0">
-        <x:v>5287314404</x:v>
+        <x:v>7708004248</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>0.0624</x:v>
+        <x:v>0.3057</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:9">
@@ -3167,538 +3170,538 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B83" s="0">
-        <x:v>85.5</x:v>
+        <x:v>1200</x:v>
       </x:c>
       <x:c r="C83" s="0">
-        <x:v>2.3</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E83" s="0">
-        <x:v>11700000</x:v>
+        <x:v>875400</x:v>
       </x:c>
       <x:c r="F83" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G83" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H83" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>1883544167</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>0.1705</x:v>
+        <x:v>0.0205</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:9">
       <x:c r="A84" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B84" s="0">
+        <x:v>26.7</x:v>
+      </x:c>
+      <x:c r="C84" s="0">
+        <x:v>-0.1</x:v>
+      </x:c>
+      <x:c r="D84" s="0" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="B84" s="0">
-        <x:v>7.63</x:v>
-      </x:c>
-      <x:c r="C84" s="0">
-        <x:v>0.25</x:v>
-      </x:c>
-      <x:c r="D84" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
       <x:c r="E84" s="0">
-        <x:v>4000000000</x:v>
+        <x:v>330000000</x:v>
       </x:c>
       <x:c r="F84" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G84" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H84" s="0">
-        <x:v>10581001663</x:v>
+        <x:v>5287314404</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>0.378</x:v>
+        <x:v>0.0624</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:9">
       <x:c r="A85" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B85" s="0">
-        <x:v>16.01</x:v>
+        <x:v>82.35</x:v>
       </x:c>
       <x:c r="C85" s="0">
-        <x:v>0.16</x:v>
+        <x:v>-3.15</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
         <x:v>81</x:v>
       </x:c>
       <x:c r="E85" s="0">
-        <x:v>1086598</x:v>
+        <x:v>11700000</x:v>
       </x:c>
       <x:c r="F85" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G85" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H85" s="0">
-        <x:v>2020891371</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I85" s="0">
-        <x:v>0.0274</x:v>
+        <x:v>0.1705</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:9">
       <x:c r="A86" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B86" s="0">
-        <x:v>14.94</x:v>
+        <x:v>7.88</x:v>
       </x:c>
       <x:c r="C86" s="0">
-        <x:v>0.08</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E86" s="0">
-        <x:v>216000000</x:v>
+        <x:v>4000000000</x:v>
       </x:c>
       <x:c r="F86" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G86" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H86" s="0">
-        <x:v>3025063909</x:v>
+        <x:v>10581001663</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>0.0714</x:v>
+        <x:v>0.378</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:9">
       <x:c r="A87" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B87" s="0">
-        <x:v>50.2</x:v>
+        <x:v>16.53</x:v>
       </x:c>
       <x:c r="C87" s="0">
-        <x:v>-1.15</x:v>
+        <x:v>0.52</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
         <x:v>82</x:v>
       </x:c>
       <x:c r="E87" s="0">
-        <x:v>7292916</x:v>
+        <x:v>1086598</x:v>
       </x:c>
       <x:c r="F87" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G87" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H87" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>2020891371</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>0.0758</x:v>
+        <x:v>0.0274</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:9">
       <x:c r="A88" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B88" s="0">
+        <x:v>14.9</x:v>
+      </x:c>
+      <x:c r="C88" s="0">
+        <x:v>-0.04</x:v>
+      </x:c>
+      <x:c r="D88" s="0" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="B88" s="0">
-        <x:v>27.16</x:v>
-      </x:c>
-      <x:c r="C88" s="0">
-        <x:v>2.46</x:v>
-      </x:c>
-      <x:c r="D88" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
       <x:c r="E88" s="0">
-        <x:v>250000</x:v>
+        <x:v>216000000</x:v>
       </x:c>
       <x:c r="F88" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G88" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H88" s="0">
-        <x:v>448686813</x:v>
+        <x:v>3025063909</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>0.0006</x:v>
+        <x:v>0.0714</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:9">
       <x:c r="A89" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B89" s="0">
-        <x:v>55.8</x:v>
+        <x:v>55.2</x:v>
       </x:c>
       <x:c r="C89" s="0">
-        <x:v>-1.4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E89" s="0">
-        <x:v>36900000</x:v>
+        <x:v>7292916</x:v>
       </x:c>
       <x:c r="F89" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G89" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H89" s="0">
-        <x:v>10597063406</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>0.1527</x:v>
+        <x:v>0.0758</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:9">
       <x:c r="A90" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B90" s="0">
+        <x:v>29.86</x:v>
+      </x:c>
+      <x:c r="C90" s="0">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="D90" s="0" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="B90" s="0">
-        <x:v>60.25</x:v>
-      </x:c>
-      <x:c r="C90" s="0">
-        <x:v>-0.05</x:v>
-      </x:c>
-      <x:c r="D90" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
       <x:c r="E90" s="0">
-        <x:v>3800000</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="F90" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G90" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H90" s="0">
-        <x:v>832031190</x:v>
+        <x:v>448686813</x:v>
       </x:c>
       <x:c r="I90" s="0">
-        <x:v>0.2002</x:v>
+        <x:v>0.0006</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:9">
       <x:c r="A91" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B91" s="0">
-        <x:v>4.91</x:v>
+        <x:v>61.35</x:v>
       </x:c>
       <x:c r="C91" s="0">
-        <x:v>0.08</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E91" s="0">
-        <x:v>2100000</x:v>
+        <x:v>36900000</x:v>
       </x:c>
       <x:c r="F91" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G91" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H91" s="0">
-        <x:v>855070469</x:v>
+        <x:v>10597063406</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>0.1076</x:v>
+        <x:v>0.1527</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:9">
       <x:c r="A92" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B92" s="0">
-        <x:v>50.2</x:v>
+        <x:v>64.25</x:v>
       </x:c>
       <x:c r="C92" s="0">
-        <x:v>-1.15</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
         <x:v>87</x:v>
       </x:c>
       <x:c r="E92" s="0">
-        <x:v>22928077</x:v>
+        <x:v>3800000</x:v>
       </x:c>
       <x:c r="F92" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G92" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H92" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>832031190</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>0.2378</x:v>
+        <x:v>0.2002</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:9">
       <x:c r="A93" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B93" s="0">
+        <x:v>5.4</x:v>
+      </x:c>
+      <x:c r="C93" s="0">
+        <x:v>0.49</x:v>
+      </x:c>
+      <x:c r="D93" s="0" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="B93" s="0">
-        <x:v>28.48</x:v>
-      </x:c>
-      <x:c r="C93" s="0">
-        <x:v>-0.02</x:v>
-      </x:c>
-      <x:c r="D93" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
       <x:c r="E93" s="0">
-        <x:v>547462013</x:v>
+        <x:v>2100000</x:v>
       </x:c>
       <x:c r="F93" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G93" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H93" s="0">
-        <x:v>0</x:v>
+        <x:v>855070469</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>0</x:v>
+        <x:v>0.1076</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:9">
       <x:c r="A94" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B94" s="0">
+        <x:v>55.2</x:v>
+      </x:c>
+      <x:c r="C94" s="0">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D94" s="0" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="B94" s="0">
-        <x:v>28.48</x:v>
-      </x:c>
-      <x:c r="C94" s="0">
-        <x:v>-0.02</x:v>
-      </x:c>
-      <x:c r="D94" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
       <x:c r="E94" s="0">
-        <x:v>10567948</x:v>
+        <x:v>22928077</x:v>
       </x:c>
       <x:c r="F94" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G94" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H94" s="0">
-        <x:v>0</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>0</x:v>
+        <x:v>0.2378</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:9">
       <x:c r="A95" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B95" s="0">
-        <x:v>85.5</x:v>
+        <x:v>30.2</x:v>
       </x:c>
       <x:c r="C95" s="0">
-        <x:v>2.3</x:v>
+        <x:v>1.72</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E95" s="0">
-        <x:v>8300000</x:v>
+        <x:v>547462013</x:v>
       </x:c>
       <x:c r="F95" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G95" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H95" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>0.1228</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:9">
       <x:c r="A96" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B96" s="0">
-        <x:v>49.8</x:v>
+        <x:v>30.2</x:v>
       </x:c>
       <x:c r="C96" s="0">
-        <x:v>1.6</x:v>
+        <x:v>1.72</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E96" s="0">
-        <x:v>3000000</x:v>
+        <x:v>10567948</x:v>
       </x:c>
       <x:c r="F96" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G96" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H96" s="0">
-        <x:v>20597209000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>0.0064</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:9">
       <x:c r="A97" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B97" s="0">
+        <x:v>82.35</x:v>
+      </x:c>
+      <x:c r="C97" s="0">
+        <x:v>-3.15</x:v>
+      </x:c>
+      <x:c r="D97" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="B97" s="0">
-        <x:v>35.68</x:v>
-      </x:c>
-      <x:c r="C97" s="0">
-        <x:v>1.32</x:v>
-      </x:c>
-      <x:c r="D97" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
       <x:c r="E97" s="0">
-        <x:v>26640000</x:v>
+        <x:v>8300000</x:v>
       </x:c>
       <x:c r="F97" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G97" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H97" s="0">
-        <x:v>3277373640</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>0.356</x:v>
+        <x:v>0.1228</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:9">
       <x:c r="A98" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B98" s="0">
-        <x:v>5.38</x:v>
+        <x:v>51.05</x:v>
       </x:c>
       <x:c r="C98" s="0">
-        <x:v>0.04</x:v>
+        <x:v>1.25</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E98" s="0">
-        <x:v>13107198</x:v>
+        <x:v>3000000</x:v>
       </x:c>
       <x:c r="F98" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G98" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H98" s="0">
-        <x:v>1627872951</x:v>
+        <x:v>20597209000</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>0.0081</x:v>
+        <x:v>0.0064</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:9">
       <x:c r="A99" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B99" s="0">
-        <x:v>85.5</x:v>
+        <x:v>35.94</x:v>
       </x:c>
       <x:c r="C99" s="0">
-        <x:v>2.3</x:v>
+        <x:v>0.26</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E99" s="0">
-        <x:v>237500000</x:v>
+        <x:v>26640000</x:v>
       </x:c>
       <x:c r="F99" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G99" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H99" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>3277373640</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>0.0679</x:v>
+        <x:v>0.356</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:9">
       <x:c r="A100" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B100" s="0">
-        <x:v>58.95</x:v>
+        <x:v>5.91</x:v>
       </x:c>
       <x:c r="C100" s="0">
-        <x:v>0.75</x:v>
+        <x:v>0.53</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E100" s="0">
-        <x:v>147892538</x:v>
+        <x:v>13107198</x:v>
       </x:c>
       <x:c r="F100" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G100" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H100" s="0">
-        <x:v>7257990064</x:v>
+        <x:v>1627872951</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>0.0204</x:v>
+        <x:v>0.0081</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:9">
       <x:c r="A101" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B101" s="0">
-        <x:v>52.4</x:v>
+        <x:v>82.35</x:v>
       </x:c>
       <x:c r="C101" s="0">
-        <x:v>3.5</x:v>
+        <x:v>-3.15</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
         <x:v>94</x:v>
       </x:c>
       <x:c r="E101" s="0">
-        <x:v>988848</x:v>
+        <x:v>237500000</x:v>
       </x:c>
       <x:c r="F101" s="0" t="s">
         <x:v>11</x:v>
@@ -3707,346 +3710,346 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H101" s="0">
-        <x:v>12999679000</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>0.0033</x:v>
+        <x:v>0.0679</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:9">
       <x:c r="A102" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B102" s="0">
-        <x:v>55.8</x:v>
+        <x:v>58.25</x:v>
       </x:c>
       <x:c r="C102" s="0">
-        <x:v>-1.4</x:v>
+        <x:v>-0.7</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E102" s="0">
-        <x:v>47300000</x:v>
+        <x:v>147892538</x:v>
       </x:c>
       <x:c r="F102" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G102" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H102" s="0">
-        <x:v>10597063406</x:v>
+        <x:v>7257990064</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>0.2309</x:v>
+        <x:v>0.0204</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:9">
       <x:c r="A103" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B103" s="0">
-        <x:v>4.09</x:v>
+        <x:v>55.45</x:v>
       </x:c>
       <x:c r="C103" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>3.05</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E103" s="0">
-        <x:v>758600</x:v>
+        <x:v>988848</x:v>
       </x:c>
       <x:c r="F103" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G103" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H103" s="0">
-        <x:v>1960468575</x:v>
+        <x:v>12999679000</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0.0033</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:9">
       <x:c r="A104" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B104" s="0">
-        <x:v>4.09</x:v>
+        <x:v>61.35</x:v>
       </x:c>
       <x:c r="C104" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E104" s="0">
-        <x:v>758600</x:v>
+        <x:v>47300000</x:v>
       </x:c>
       <x:c r="F104" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G104" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H104" s="0">
-        <x:v>1960468575</x:v>
+        <x:v>10597063406</x:v>
       </x:c>
       <x:c r="I104" s="0">
-        <x:v>0.0004</x:v>
+        <x:v>0.2309</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:9">
       <x:c r="A105" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B105" s="0">
-        <x:v>1139</x:v>
+        <x:v>4.01</x:v>
       </x:c>
       <x:c r="C105" s="0">
-        <x:v>9</x:v>
+        <x:v>-0.08</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E105" s="0">
-        <x:v>576665</x:v>
+        <x:v>758600</x:v>
       </x:c>
       <x:c r="F105" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G105" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H105" s="0">
-        <x:v>1586603352</x:v>
+        <x:v>1960468575</x:v>
       </x:c>
       <x:c r="I105" s="0">
-        <x:v>0.0159</x:v>
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:9">
       <x:c r="A106" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B106" s="0">
+        <x:v>4.01</x:v>
+      </x:c>
+      <x:c r="C106" s="0">
+        <x:v>-0.08</x:v>
+      </x:c>
+      <x:c r="D106" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="E106" s="0">
+        <x:v>758600</x:v>
+      </x:c>
+      <x:c r="F106" s="0" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="B106" s="0">
-        <x:v>81.05</x:v>
-      </x:c>
-      <x:c r="C106" s="0">
-        <x:v>-0.75</x:v>
-      </x:c>
-      <x:c r="D106" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="E106" s="0">
-        <x:v>8000000</x:v>
-      </x:c>
-      <x:c r="F106" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="G106" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H106" s="0">
-        <x:v>20999579110</x:v>
+        <x:v>1960468575</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>0.0166</x:v>
+        <x:v>0.0004</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:9">
       <x:c r="A107" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B107" s="0">
-        <x:v>94.4</x:v>
+        <x:v>1200</x:v>
       </x:c>
       <x:c r="C107" s="0">
-        <x:v>0.45</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E107" s="0">
-        <x:v>850000</x:v>
+        <x:v>576665</x:v>
       </x:c>
       <x:c r="F107" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G107" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H107" s="0">
-        <x:v>1781510191</x:v>
+        <x:v>1586603352</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>0.0208</x:v>
+        <x:v>0.0159</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:9">
       <x:c r="A108" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B108" s="0">
-        <x:v>16.01</x:v>
+        <x:v>82.7</x:v>
       </x:c>
       <x:c r="C108" s="0">
-        <x:v>0.16</x:v>
+        <x:v>1.65</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E108" s="0">
-        <x:v>10149200</x:v>
+        <x:v>8000000</x:v>
       </x:c>
       <x:c r="F108" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G108" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H108" s="0">
-        <x:v>2020891371</x:v>
+        <x:v>20999579110</x:v>
       </x:c>
       <x:c r="I108" s="0">
-        <x:v>0.2601</x:v>
+        <x:v>0.0166</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:9">
       <x:c r="A109" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B109" s="0">
-        <x:v>118.6</x:v>
+        <x:v>98.2</x:v>
       </x:c>
       <x:c r="C109" s="0">
-        <x:v>1.4</x:v>
+        <x:v>3.8</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E109" s="0">
-        <x:v>10500000</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="F109" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G109" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H109" s="0">
-        <x:v>1742315226</x:v>
+        <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>0.3121</x:v>
+        <x:v>0.0208</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:9">
       <x:c r="A110" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B110" s="0">
-        <x:v>94.4</x:v>
+        <x:v>16.53</x:v>
       </x:c>
       <x:c r="C110" s="0">
-        <x:v>0.45</x:v>
+        <x:v>0.52</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
         <x:v>101</x:v>
       </x:c>
       <x:c r="E110" s="0">
-        <x:v>366956541</x:v>
+        <x:v>10149200</x:v>
       </x:c>
       <x:c r="F110" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G110" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H110" s="0">
-        <x:v>1781510191</x:v>
+        <x:v>2020891371</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>0.206</x:v>
+        <x:v>0.2601</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:9">
       <x:c r="A111" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B111" s="0">
-        <x:v>58.95</x:v>
+        <x:v>116.7</x:v>
       </x:c>
       <x:c r="C111" s="0">
-        <x:v>0.75</x:v>
+        <x:v>-1.9</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E111" s="0">
-        <x:v>61158155</x:v>
+        <x:v>10500000</x:v>
       </x:c>
       <x:c r="F111" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G111" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H111" s="0">
-        <x:v>7257990064</x:v>
+        <x:v>1742315226</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>0.0084</x:v>
+        <x:v>0.3121</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:9">
       <x:c r="A112" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B112" s="0">
-        <x:v>106.3</x:v>
+        <x:v>98.2</x:v>
       </x:c>
       <x:c r="C112" s="0">
-        <x:v>1.1</x:v>
+        <x:v>3.8</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
         <x:v>102</x:v>
       </x:c>
       <x:c r="E112" s="0">
-        <x:v>1000000</x:v>
+        <x:v>366956541</x:v>
       </x:c>
       <x:c r="F112" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G112" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H112" s="0">
-        <x:v>1688731509</x:v>
+        <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I112" s="0">
-        <x:v>0.0307</x:v>
+        <x:v>0.206</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:9">
       <x:c r="A113" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B113" s="0">
+        <x:v>58.25</x:v>
+      </x:c>
+      <x:c r="C113" s="0">
+        <x:v>-0.7</x:v>
+      </x:c>
+      <x:c r="D113" s="0" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="B113" s="0">
-        <x:v>106.3</x:v>
-      </x:c>
-      <x:c r="C113" s="0">
-        <x:v>1.1</x:v>
-      </x:c>
-      <x:c r="D113" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
       <x:c r="E113" s="0">
-        <x:v>1050000</x:v>
+        <x:v>61158155</x:v>
       </x:c>
       <x:c r="F113" s="0" t="s">
         <x:v>11</x:v>
@@ -4055,10 +4058,10 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H113" s="0">
-        <x:v>1688731509</x:v>
+        <x:v>7257990064</x:v>
       </x:c>
       <x:c r="I113" s="0">
-        <x:v>0.0271</x:v>
+        <x:v>0.0084</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:9">
@@ -4066,74 +4069,74 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B114" s="0">
-        <x:v>40.58</x:v>
+        <x:v>111.8</x:v>
       </x:c>
       <x:c r="C114" s="0">
-        <x:v>-0.48</x:v>
+        <x:v>5.5</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E114" s="0">
-        <x:v>109053804</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="F114" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G114" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H114" s="0">
-        <x:v>1942491524</x:v>
+        <x:v>1688731509</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>0.0561</x:v>
+        <x:v>0.0307</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:9">
       <x:c r="A115" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B115" s="0">
-        <x:v>10.41</x:v>
+        <x:v>111.8</x:v>
       </x:c>
       <x:c r="C115" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>5.5</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E115" s="0">
-        <x:v>62315119</x:v>
+        <x:v>1050000</x:v>
       </x:c>
       <x:c r="F115" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G115" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H115" s="0">
-        <x:v>12026414029</x:v>
+        <x:v>1688731509</x:v>
       </x:c>
       <x:c r="I115" s="0">
-        <x:v>0.2257</x:v>
+        <x:v>0.0271</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:9">
       <x:c r="A116" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B116" s="0">
-        <x:v>219.8</x:v>
+        <x:v>40.7</x:v>
       </x:c>
       <x:c r="C116" s="0">
-        <x:v>2.8</x:v>
+        <x:v>0.12</x:v>
       </x:c>
       <x:c r="D116" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E116" s="0">
-        <x:v>896400</x:v>
+        <x:v>109053804</x:v>
       </x:c>
       <x:c r="F116" s="0" t="s">
         <x:v>11</x:v>
@@ -4142,233 +4145,233 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H116" s="0">
-        <x:v>1364716456</x:v>
+        <x:v>1942491524</x:v>
       </x:c>
       <x:c r="I116" s="0">
-        <x:v>0.0285</x:v>
+        <x:v>0.0561</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:9">
       <x:c r="A117" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B117" s="0">
-        <x:v>373.25</x:v>
+        <x:v>9.81</x:v>
       </x:c>
       <x:c r="C117" s="0">
-        <x:v>33.75</x:v>
+        <x:v>-0.6</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E117" s="0">
-        <x:v>3370000</x:v>
+        <x:v>62315119</x:v>
       </x:c>
       <x:c r="F117" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G117" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H117" s="0">
-        <x:v>1865697176</x:v>
+        <x:v>12026414029</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>0.0785</x:v>
+        <x:v>0.2257</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:9">
       <x:c r="A118" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B118" s="0">
-        <x:v>49.8</x:v>
+        <x:v>232.1</x:v>
       </x:c>
       <x:c r="C118" s="0">
-        <x:v>1.6</x:v>
+        <x:v>12.3</x:v>
       </x:c>
       <x:c r="D118" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E118" s="0">
-        <x:v>750561215</x:v>
+        <x:v>896400</x:v>
       </x:c>
       <x:c r="F118" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G118" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H118" s="0">
-        <x:v>16507905000</x:v>
+        <x:v>1364716456</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>0.0455</x:v>
+        <x:v>0.0285</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:9">
       <x:c r="A119" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B119" s="0">
-        <x:v>81.05</x:v>
+        <x:v>410.5</x:v>
       </x:c>
       <x:c r="C119" s="0">
-        <x:v>-0.75</x:v>
+        <x:v>37.25</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
         <x:v>110</x:v>
       </x:c>
       <x:c r="E119" s="0">
-        <x:v>20000000</x:v>
+        <x:v>3370000</x:v>
       </x:c>
       <x:c r="F119" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G119" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H119" s="0">
-        <x:v>20999579110</x:v>
+        <x:v>1865697176</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>0.0413</x:v>
+        <x:v>0.0785</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:9">
       <x:c r="A120" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B120" s="0">
+        <x:v>51.05</x:v>
+      </x:c>
+      <x:c r="C120" s="0">
+        <x:v>1.25</x:v>
+      </x:c>
+      <x:c r="D120" s="0" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="B120" s="0">
-        <x:v>33.06</x:v>
-      </x:c>
-      <x:c r="C120" s="0">
-        <x:v>0.08</x:v>
-      </x:c>
-      <x:c r="D120" s="0" t="s">
-        <x:v>112</x:v>
-      </x:c>
       <x:c r="E120" s="0">
-        <x:v>750000000</x:v>
+        <x:v>750561215</x:v>
       </x:c>
       <x:c r="F120" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G120" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H120" s="0">
-        <x:v>0</x:v>
+        <x:v>16507905000</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0455</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:9">
       <x:c r="A121" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B121" s="0">
-        <x:v>55.8</x:v>
+        <x:v>82.7</x:v>
       </x:c>
       <x:c r="C121" s="0">
-        <x:v>-1.4</x:v>
+        <x:v>1.65</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E121" s="0">
-        <x:v>111232418</x:v>
+        <x:v>20000000</x:v>
       </x:c>
       <x:c r="F121" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G121" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H121" s="0">
-        <x:v>10597063406</x:v>
+        <x:v>20999579110</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>0.4554</x:v>
+        <x:v>0.0413</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:9">
       <x:c r="A122" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B122" s="0">
-        <x:v>36.64</x:v>
+        <x:v>33.14</x:v>
       </x:c>
       <x:c r="C122" s="0">
-        <x:v>0.2</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
         <x:v>113</x:v>
       </x:c>
       <x:c r="E122" s="0">
-        <x:v>51384996</x:v>
+        <x:v>750000000</x:v>
       </x:c>
       <x:c r="F122" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G122" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H122" s="0">
-        <x:v>11899043692</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>0.1873</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:9">
       <x:c r="A123" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B123" s="0">
-        <x:v>36.64</x:v>
+        <x:v>61.35</x:v>
       </x:c>
       <x:c r="C123" s="0">
-        <x:v>0.2</x:v>
+        <x:v>5.55</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
         <x:v>113</x:v>
       </x:c>
       <x:c r="E123" s="0">
-        <x:v>3602451</x:v>
+        <x:v>111232418</x:v>
       </x:c>
       <x:c r="F123" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G123" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H123" s="0">
-        <x:v>11899043692</x:v>
+        <x:v>10597063406</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>0.0131</x:v>
+        <x:v>0.4554</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:9">
       <x:c r="A124" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B124" s="0">
-        <x:v>36.64</x:v>
+        <x:v>35.8</x:v>
       </x:c>
       <x:c r="C124" s="0">
-        <x:v>0.2</x:v>
+        <x:v>-0.84</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="E124" s="0">
-        <x:v>24226465</x:v>
+        <x:v>51384996</x:v>
       </x:c>
       <x:c r="F124" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G124" s="0">
         <x:v>2025.09</x:v>
@@ -4377,36 +4380,36 @@
         <x:v>11899043692</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>0.0883</x:v>
+        <x:v>0.1873</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:9">
       <x:c r="A125" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B125" s="0">
-        <x:v>50.2</x:v>
+        <x:v>35.8</x:v>
       </x:c>
       <x:c r="C125" s="0">
-        <x:v>-1.15</x:v>
+        <x:v>-0.84</x:v>
       </x:c>
       <x:c r="D125" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="E125" s="0">
-        <x:v>12900000</x:v>
+        <x:v>3602451</x:v>
       </x:c>
       <x:c r="F125" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G125" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H125" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>11899043692</x:v>
       </x:c>
       <x:c r="I125" s="0">
-        <x:v>0.0052</x:v>
+        <x:v>0.0131</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:9">
@@ -4414,376 +4417,376 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B126" s="0">
-        <x:v>284</x:v>
+        <x:v>35.8</x:v>
       </x:c>
       <x:c r="C126" s="0">
-        <x:v>20</x:v>
+        <x:v>-0.84</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="E126" s="0">
-        <x:v>53250000</x:v>
+        <x:v>24226465</x:v>
       </x:c>
       <x:c r="F126" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G126" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H126" s="0">
-        <x:v>24073631758</x:v>
+        <x:v>11899043692</x:v>
       </x:c>
       <x:c r="I126" s="0">
-        <x:v>0.115</x:v>
+        <x:v>0.0883</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:9">
       <x:c r="A127" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B127" s="0">
-        <x:v>28.48</x:v>
+        <x:v>55.2</x:v>
       </x:c>
       <x:c r="C127" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D127" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="E127" s="0">
-        <x:v>6860140</x:v>
+        <x:v>12900000</x:v>
       </x:c>
       <x:c r="F127" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G127" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H127" s="0">
-        <x:v>0</x:v>
+        <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0052</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:9">
       <x:c r="A128" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B128" s="0">
-        <x:v>85.5</x:v>
+        <x:v>290.25</x:v>
       </x:c>
       <x:c r="C128" s="0">
-        <x:v>2.3</x:v>
+        <x:v>6.25</x:v>
       </x:c>
       <x:c r="D128" s="0" t="s">
         <x:v>114</x:v>
       </x:c>
       <x:c r="E128" s="0">
-        <x:v>230000000</x:v>
+        <x:v>53250000</x:v>
       </x:c>
       <x:c r="F128" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G128" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H128" s="0">
-        <x:v>2941310980</x:v>
+        <x:v>24073631758</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>0.0782</x:v>
+        <x:v>0.115</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:9">
       <x:c r="A129" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B129" s="0">
-        <x:v>373.25</x:v>
+        <x:v>30.2</x:v>
       </x:c>
       <x:c r="C129" s="0">
-        <x:v>33.75</x:v>
+        <x:v>1.72</x:v>
       </x:c>
       <x:c r="D129" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="E129" s="0">
-        <x:v>4700000</x:v>
+        <x:v>6860140</x:v>
       </x:c>
       <x:c r="F129" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G129" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H129" s="0">
-        <x:v>1865697176</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>0.1092</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:9">
       <x:c r="A130" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B130" s="0">
-        <x:v>28.48</x:v>
+        <x:v>82.35</x:v>
       </x:c>
       <x:c r="C130" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>-3.15</x:v>
       </x:c>
       <x:c r="D130" s="0" t="s">
         <x:v>115</x:v>
       </x:c>
       <x:c r="E130" s="0">
-        <x:v>256000000</x:v>
+        <x:v>230000000</x:v>
       </x:c>
       <x:c r="F130" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G130" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H130" s="0">
-        <x:v>0</x:v>
+        <x:v>2941310980</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0782</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:9">
       <x:c r="A131" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B131" s="0">
-        <x:v>36.64</x:v>
+        <x:v>410.5</x:v>
       </x:c>
       <x:c r="C131" s="0">
-        <x:v>0.2</x:v>
+        <x:v>37.25</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
         <x:v>116</x:v>
       </x:c>
       <x:c r="E131" s="0">
-        <x:v>10724896</x:v>
+        <x:v>4700000</x:v>
       </x:c>
       <x:c r="F131" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G131" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H131" s="0">
-        <x:v>11899043692</x:v>
+        <x:v>1865697176</x:v>
       </x:c>
       <x:c r="I131" s="0">
-        <x:v>0.039</x:v>
+        <x:v>0.1092</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:9">
       <x:c r="A132" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B132" s="0">
-        <x:v>24.34</x:v>
+        <x:v>30.2</x:v>
       </x:c>
       <x:c r="C132" s="0">
-        <x:v>0.04</x:v>
+        <x:v>1.72</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
         <x:v>116</x:v>
       </x:c>
       <x:c r="E132" s="0">
-        <x:v>31000000</x:v>
+        <x:v>256000000</x:v>
       </x:c>
       <x:c r="F132" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G132" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H132" s="0">
-        <x:v>813967617</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I132" s="0">
-        <x:v>0.0381</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:9">
       <x:c r="A133" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B133" s="0">
-        <x:v>41.22</x:v>
+        <x:v>35.8</x:v>
       </x:c>
       <x:c r="C133" s="0">
-        <x:v>0.2</x:v>
+        <x:v>-0.84</x:v>
       </x:c>
       <x:c r="D133" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E133" s="0">
-        <x:v>13500000</x:v>
+        <x:v>10724896</x:v>
       </x:c>
       <x:c r="F133" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G133" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H133" s="0">
-        <x:v>6483809984</x:v>
+        <x:v>11899043692</x:v>
       </x:c>
       <x:c r="I133" s="0">
-        <x:v>0.09</x:v>
+        <x:v>0.039</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:9">
       <x:c r="A134" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B134" s="0">
-        <x:v>40.58</x:v>
+        <x:v>24.7</x:v>
       </x:c>
       <x:c r="C134" s="0">
-        <x:v>-0.48</x:v>
+        <x:v>0.36</x:v>
       </x:c>
       <x:c r="D134" s="0" t="s">
         <x:v>117</x:v>
       </x:c>
       <x:c r="E134" s="0">
-        <x:v>29886357</x:v>
+        <x:v>31000000</x:v>
       </x:c>
       <x:c r="F134" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G134" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H134" s="0">
-        <x:v>1942491524</x:v>
+        <x:v>813967617</x:v>
       </x:c>
       <x:c r="I134" s="0">
-        <x:v>0.0154</x:v>
+        <x:v>0.0381</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:9">
       <x:c r="A135" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B135" s="0">
-        <x:v>420.25</x:v>
+        <x:v>40.94</x:v>
       </x:c>
       <x:c r="C135" s="0">
-        <x:v>-5.25</x:v>
+        <x:v>-0.28</x:v>
       </x:c>
       <x:c r="D135" s="0" t="s">
         <x:v>117</x:v>
       </x:c>
       <x:c r="E135" s="0">
-        <x:v>171000000</x:v>
+        <x:v>13500000</x:v>
       </x:c>
       <x:c r="F135" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G135" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H135" s="0">
-        <x:v>130147715000</x:v>
+        <x:v>6483809984</x:v>
       </x:c>
       <x:c r="I135" s="0">
-        <x:v>0.0568</x:v>
+        <x:v>0.09</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:9">
       <x:c r="A136" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B136" s="0">
-        <x:v>118.6</x:v>
+        <x:v>40.7</x:v>
       </x:c>
       <x:c r="C136" s="0">
-        <x:v>1.4</x:v>
+        <x:v>0.12</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E136" s="0">
-        <x:v>1890000</x:v>
+        <x:v>29886357</x:v>
       </x:c>
       <x:c r="F136" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G136" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H136" s="0">
-        <x:v>1742315226</x:v>
+        <x:v>1942491524</x:v>
       </x:c>
       <x:c r="I136" s="0">
-        <x:v>0.0549</x:v>
+        <x:v>0.0154</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:9">
       <x:c r="A137" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B137" s="0">
+        <x:v>431.75</x:v>
+      </x:c>
+      <x:c r="C137" s="0">
+        <x:v>11.5</x:v>
+      </x:c>
+      <x:c r="D137" s="0" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="B137" s="0">
-        <x:v>13.48</x:v>
-      </x:c>
-      <x:c r="C137" s="0">
-        <x:v>0.35</x:v>
-      </x:c>
-      <x:c r="D137" s="0" t="s">
-        <x:v>117</x:v>
-      </x:c>
       <x:c r="E137" s="0">
-        <x:v>892825</x:v>
+        <x:v>171000000</x:v>
       </x:c>
       <x:c r="F137" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G137" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H137" s="0">
-        <x:v>3015442704</x:v>
+        <x:v>130147715000</x:v>
       </x:c>
       <x:c r="I137" s="0">
-        <x:v>0.0128</x:v>
+        <x:v>0.0568</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:9">
       <x:c r="A138" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B138" s="0">
-        <x:v>50.2</x:v>
+        <x:v>116.7</x:v>
       </x:c>
       <x:c r="C138" s="0">
-        <x:v>-1.15</x:v>
+        <x:v>-1.9</x:v>
       </x:c>
       <x:c r="D138" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E138" s="0">
-        <x:v>361176</x:v>
+        <x:v>1890000</x:v>
       </x:c>
       <x:c r="F138" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G138" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H138" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>1742315226</x:v>
       </x:c>
       <x:c r="I138" s="0">
-        <x:v>0.0063</x:v>
+        <x:v>0.0549</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:9">
@@ -4791,103 +4794,103 @@
         <x:v>119</x:v>
       </x:c>
       <x:c r="B139" s="0">
-        <x:v>24.32</x:v>
+        <x:v>13.5</x:v>
       </x:c>
       <x:c r="C139" s="0">
-        <x:v>-1.24</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="D139" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E139" s="0">
-        <x:v>1060000</x:v>
+        <x:v>892825</x:v>
       </x:c>
       <x:c r="F139" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G139" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H139" s="0">
-        <x:v>1194839266</x:v>
+        <x:v>3015442704</x:v>
       </x:c>
       <x:c r="I139" s="0">
-        <x:v>0.0384</x:v>
+        <x:v>0.0128</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:9">
       <x:c r="A140" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B140" s="0">
-        <x:v>52.15</x:v>
+        <x:v>55.2</x:v>
       </x:c>
       <x:c r="C140" s="0">
-        <x:v>-0.85</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D140" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E140" s="0">
-        <x:v>259417800</x:v>
+        <x:v>361176</x:v>
       </x:c>
       <x:c r="F140" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G140" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H140" s="0">
-        <x:v>2741117556</x:v>
+        <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I140" s="0">
-        <x:v>0.0946</x:v>
+        <x:v>0.0063</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:9">
       <x:c r="A141" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B141" s="0">
-        <x:v>60.25</x:v>
+        <x:v>23.38</x:v>
       </x:c>
       <x:c r="C141" s="0">
-        <x:v>-0.05</x:v>
+        <x:v>-0.94</x:v>
       </x:c>
       <x:c r="D141" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E141" s="0">
-        <x:v>523788</x:v>
+        <x:v>1060000</x:v>
       </x:c>
       <x:c r="F141" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G141" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H141" s="0">
-        <x:v>832031190</x:v>
+        <x:v>1194839266</x:v>
       </x:c>
       <x:c r="I141" s="0">
-        <x:v>0.0272</x:v>
+        <x:v>0.0384</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:9">
       <x:c r="A142" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B142" s="0">
-        <x:v>60.25</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C142" s="0">
-        <x:v>-0.05</x:v>
+        <x:v>-0.15</x:v>
       </x:c>
       <x:c r="D142" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E142" s="0">
-        <x:v>1415270</x:v>
+        <x:v>259417800</x:v>
       </x:c>
       <x:c r="F142" s="0" t="s">
         <x:v>11</x:v>
@@ -4896,317 +4899,317 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H142" s="0">
-        <x:v>832031190</x:v>
+        <x:v>2741117556</x:v>
       </x:c>
       <x:c r="I142" s="0">
-        <x:v>0.0736</x:v>
+        <x:v>0.0946</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:9">
       <x:c r="A143" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B143" s="0">
-        <x:v>81.05</x:v>
+        <x:v>64.25</x:v>
       </x:c>
       <x:c r="C143" s="0">
-        <x:v>-0.75</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D143" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E143" s="0">
-        <x:v>25000000</x:v>
+        <x:v>523788</x:v>
       </x:c>
       <x:c r="F143" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G143" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H143" s="0">
-        <x:v>20999579110</x:v>
+        <x:v>832031190</x:v>
       </x:c>
       <x:c r="I143" s="0">
-        <x:v>0.0515</x:v>
+        <x:v>0.0272</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:9">
       <x:c r="A144" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B144" s="0">
-        <x:v>5.38</x:v>
+        <x:v>64.25</x:v>
       </x:c>
       <x:c r="C144" s="0">
-        <x:v>0.04</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D144" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E144" s="0">
-        <x:v>25000</x:v>
+        <x:v>1415270</x:v>
       </x:c>
       <x:c r="F144" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G144" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H144" s="0">
-        <x:v>1627872951</x:v>
+        <x:v>832031190</x:v>
       </x:c>
       <x:c r="I144" s="0">
-        <x:v>0.0007</x:v>
+        <x:v>0.0736</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:9">
       <x:c r="A145" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B145" s="0">
-        <x:v>22.02</x:v>
+        <x:v>82.7</x:v>
       </x:c>
       <x:c r="C145" s="0">
-        <x:v>2</x:v>
+        <x:v>1.65</x:v>
       </x:c>
       <x:c r="D145" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E145" s="0">
-        <x:v>1500000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="F145" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G145" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H145" s="0">
-        <x:v>774677961</x:v>
+        <x:v>20999579110</x:v>
       </x:c>
       <x:c r="I145" s="0">
-        <x:v>0.0019</x:v>
+        <x:v>0.0515</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:9">
       <x:c r="A146" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B146" s="0">
-        <x:v>7.63</x:v>
+        <x:v>5.91</x:v>
       </x:c>
       <x:c r="C146" s="0">
-        <x:v>0.25</x:v>
+        <x:v>0.53</x:v>
       </x:c>
       <x:c r="D146" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="E146" s="0">
-        <x:v>13833310</x:v>
+        <x:v>25000</x:v>
       </x:c>
       <x:c r="F146" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G146" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H146" s="0">
-        <x:v>9028523851</x:v>
+        <x:v>1627872951</x:v>
       </x:c>
       <x:c r="I146" s="0">
-        <x:v>0.0776</x:v>
+        <x:v>0.0007</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:9">
       <x:c r="A147" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B147" s="0">
-        <x:v>74.6</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C147" s="0">
-        <x:v>4.1</x:v>
+        <x:v>-1.02</x:v>
       </x:c>
       <x:c r="D147" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="E147" s="0">
-        <x:v>3419000</x:v>
+        <x:v>1500000</x:v>
       </x:c>
       <x:c r="F147" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G147" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H147" s="0">
-        <x:v>3895315496</x:v>
+        <x:v>774677961</x:v>
       </x:c>
       <x:c r="I147" s="0">
-        <x:v>0.0379</x:v>
+        <x:v>0.0019</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:9">
       <x:c r="A148" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B148" s="0">
-        <x:v>373.25</x:v>
+        <x:v>7.88</x:v>
       </x:c>
       <x:c r="C148" s="0">
-        <x:v>33.75</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="D148" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="E148" s="0">
-        <x:v>3700000</x:v>
+        <x:v>13833310</x:v>
       </x:c>
       <x:c r="F148" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G148" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H148" s="0">
-        <x:v>1865697176</x:v>
+        <x:v>9028523851</x:v>
       </x:c>
       <x:c r="I148" s="0">
-        <x:v>0.0857</x:v>
+        <x:v>0.0776</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:9">
       <x:c r="A149" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B149" s="0">
-        <x:v>41.22</x:v>
+        <x:v>77.7</x:v>
       </x:c>
       <x:c r="C149" s="0">
-        <x:v>0.2</x:v>
+        <x:v>3.1</x:v>
       </x:c>
       <x:c r="D149" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E149" s="0">
-        <x:v>16000000</x:v>
+        <x:v>3419000</x:v>
       </x:c>
       <x:c r="F149" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G149" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H149" s="0">
-        <x:v>6483809984</x:v>
+        <x:v>3895315496</x:v>
       </x:c>
       <x:c r="I149" s="0">
-        <x:v>0.1067</x:v>
+        <x:v>0.0379</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:9">
       <x:c r="A150" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B150" s="0">
-        <x:v>50.2</x:v>
+        <x:v>410.5</x:v>
       </x:c>
       <x:c r="C150" s="0">
-        <x:v>-1.15</x:v>
+        <x:v>37.25</x:v>
       </x:c>
       <x:c r="D150" s="0" t="s">
         <x:v>125</x:v>
       </x:c>
       <x:c r="E150" s="0">
-        <x:v>906840</x:v>
+        <x:v>3700000</x:v>
       </x:c>
       <x:c r="F150" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G150" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H150" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>1865697176</x:v>
       </x:c>
       <x:c r="I150" s="0">
-        <x:v>0.0159</x:v>
+        <x:v>0.0857</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:9">
       <x:c r="A151" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B151" s="0">
-        <x:v>3.26</x:v>
+        <x:v>40.94</x:v>
       </x:c>
       <x:c r="C151" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>-0.28</x:v>
       </x:c>
       <x:c r="D151" s="0" t="s">
         <x:v>125</x:v>
       </x:c>
       <x:c r="E151" s="0">
-        <x:v>895039950</x:v>
+        <x:v>16000000</x:v>
       </x:c>
       <x:c r="F151" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G151" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H151" s="0">
-        <x:v>7382591324</x:v>
+        <x:v>6483809984</x:v>
       </x:c>
       <x:c r="I151" s="0">
-        <x:v>0.1212</x:v>
+        <x:v>0.1067</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:9">
       <x:c r="A152" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B152" s="0">
-        <x:v>52.15</x:v>
+        <x:v>55.2</x:v>
       </x:c>
       <x:c r="C152" s="0">
-        <x:v>-0.85</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D152" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="E152" s="0">
-        <x:v>575933040</x:v>
+        <x:v>906840</x:v>
       </x:c>
       <x:c r="F152" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G152" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H152" s="0">
-        <x:v>2741117556</x:v>
+        <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I152" s="0">
-        <x:v>0.2101</x:v>
+        <x:v>0.0159</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:9">
       <x:c r="A153" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B153" s="0">
+        <x:v>3.25</x:v>
+      </x:c>
+      <x:c r="C153" s="0">
+        <x:v>-0.01</x:v>
+      </x:c>
+      <x:c r="D153" s="0" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="B153" s="0">
-        <x:v>12.34</x:v>
-      </x:c>
-      <x:c r="C153" s="0">
-        <x:v>0.15</x:v>
-      </x:c>
-      <x:c r="D153" s="0" t="s">
-        <x:v>125</x:v>
-      </x:c>
       <x:c r="E153" s="0">
-        <x:v>559000</x:v>
+        <x:v>895039950</x:v>
       </x:c>
       <x:c r="F153" s="0" t="s">
         <x:v>11</x:v>
@@ -5215,27 +5218,27 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H153" s="0">
-        <x:v>2865374550</x:v>
+        <x:v>7382591324</x:v>
       </x:c>
       <x:c r="I153" s="0">
-        <x:v>0.0084</x:v>
+        <x:v>0.1212</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:9">
       <x:c r="A154" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B154" s="0">
-        <x:v>49.8</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C154" s="0">
-        <x:v>1.6</x:v>
+        <x:v>-0.15</x:v>
       </x:c>
       <x:c r="D154" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="E154" s="0">
-        <x:v>8900056</x:v>
+        <x:v>575933040</x:v>
       </x:c>
       <x:c r="F154" s="0" t="s">
         <x:v>11</x:v>
@@ -5244,349 +5247,349 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H154" s="0">
-        <x:v>16507905000</x:v>
+        <x:v>2741117556</x:v>
       </x:c>
       <x:c r="I154" s="0">
-        <x:v>0.0233</x:v>
+        <x:v>0.2101</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:9">
       <x:c r="A155" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B155" s="0">
-        <x:v>284</x:v>
+        <x:v>11.36</x:v>
       </x:c>
       <x:c r="C155" s="0">
-        <x:v>20</x:v>
+        <x:v>-0.98</x:v>
       </x:c>
       <x:c r="D155" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="E155" s="0">
-        <x:v>164306000</x:v>
+        <x:v>559000</x:v>
       </x:c>
       <x:c r="F155" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G155" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H155" s="0">
-        <x:v>24073631758</x:v>
+        <x:v>2865374550</x:v>
       </x:c>
       <x:c r="I155" s="0">
-        <x:v>0.2943</x:v>
+        <x:v>0.0084</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:9">
       <x:c r="A156" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B156" s="0">
-        <x:v>57.8</x:v>
+        <x:v>51.05</x:v>
       </x:c>
       <x:c r="C156" s="0">
-        <x:v>1.85</x:v>
+        <x:v>1.25</x:v>
       </x:c>
       <x:c r="D156" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="E156" s="0">
-        <x:v>275000</x:v>
+        <x:v>8900056</x:v>
       </x:c>
       <x:c r="F156" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G156" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H156" s="0">
-        <x:v>580678850</x:v>
+        <x:v>16507905000</x:v>
       </x:c>
       <x:c r="I156" s="0">
-        <x:v>0.0204</x:v>
+        <x:v>0.0233</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:9">
       <x:c r="A157" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B157" s="0">
-        <x:v>52.15</x:v>
+        <x:v>290.25</x:v>
       </x:c>
       <x:c r="C157" s="0">
-        <x:v>-0.85</x:v>
+        <x:v>6.25</x:v>
       </x:c>
       <x:c r="D157" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="E157" s="0">
-        <x:v>231651480</x:v>
+        <x:v>164306000</x:v>
       </x:c>
       <x:c r="F157" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G157" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H157" s="0">
-        <x:v>2741117556</x:v>
+        <x:v>24073631758</x:v>
       </x:c>
       <x:c r="I157" s="0">
-        <x:v>0.0845</x:v>
+        <x:v>0.2943</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:9">
       <x:c r="A158" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B158" s="0">
-        <x:v>14.94</x:v>
+        <x:v>55.7</x:v>
       </x:c>
       <x:c r="C158" s="0">
-        <x:v>0.08</x:v>
+        <x:v>-2.1</x:v>
       </x:c>
       <x:c r="D158" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="E158" s="0">
-        <x:v>31860000</x:v>
+        <x:v>275000</x:v>
       </x:c>
       <x:c r="F158" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G158" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H158" s="0">
-        <x:v>3025063909</x:v>
+        <x:v>580678850</x:v>
       </x:c>
       <x:c r="I158" s="0">
-        <x:v>0.4539</x:v>
+        <x:v>0.0204</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:9">
       <x:c r="A159" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B159" s="0">
-        <x:v>94.4</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C159" s="0">
-        <x:v>0.45</x:v>
+        <x:v>-0.15</x:v>
       </x:c>
       <x:c r="D159" s="0" t="s">
         <x:v>130</x:v>
       </x:c>
       <x:c r="E159" s="0">
-        <x:v>41650000</x:v>
+        <x:v>231651480</x:v>
       </x:c>
       <x:c r="F159" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G159" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H159" s="0">
-        <x:v>1781510191</x:v>
+        <x:v>2741117556</x:v>
       </x:c>
       <x:c r="I159" s="0">
-        <x:v>0.0234</x:v>
+        <x:v>0.0845</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:9">
       <x:c r="A160" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B160" s="0">
-        <x:v>16.01</x:v>
+        <x:v>14.9</x:v>
       </x:c>
       <x:c r="C160" s="0">
-        <x:v>0.16</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D160" s="0" t="s">
         <x:v>131</x:v>
       </x:c>
       <x:c r="E160" s="0">
-        <x:v>815000</x:v>
+        <x:v>31860000</x:v>
       </x:c>
       <x:c r="F160" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G160" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H160" s="0">
-        <x:v>2020891371</x:v>
+        <x:v>3025063909</x:v>
       </x:c>
       <x:c r="I160" s="0">
-        <x:v>0.0202</x:v>
+        <x:v>0.4539</x:v>
       </x:c>
     </x:row>
     <x:row r="161" spans="1:9">
       <x:c r="A161" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B161" s="0">
-        <x:v>85.5</x:v>
+        <x:v>98.2</x:v>
       </x:c>
       <x:c r="C161" s="0">
-        <x:v>2.3</x:v>
+        <x:v>3.8</x:v>
       </x:c>
       <x:c r="D161" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E161" s="0">
-        <x:v>8300000</x:v>
+        <x:v>41650000</x:v>
       </x:c>
       <x:c r="F161" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G161" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H161" s="0">
-        <x:v>2941310980</x:v>
+        <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I161" s="0">
-        <x:v>0.1417</x:v>
+        <x:v>0.0234</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:9">
       <x:c r="A162" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B162" s="0">
-        <x:v>4.18</x:v>
+        <x:v>16.53</x:v>
       </x:c>
       <x:c r="C162" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0.52</x:v>
       </x:c>
       <x:c r="D162" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="E162" s="0">
-        <x:v>13000000</x:v>
+        <x:v>815000</x:v>
       </x:c>
       <x:c r="F162" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G162" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H162" s="0">
-        <x:v>1416740879</x:v>
+        <x:v>2020891371</x:v>
       </x:c>
       <x:c r="I162" s="0">
-        <x:v>0.4613</x:v>
+        <x:v>0.0202</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:9">
       <x:c r="A163" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B163" s="0">
-        <x:v>118.6</x:v>
+        <x:v>82.35</x:v>
       </x:c>
       <x:c r="C163" s="0">
-        <x:v>1.4</x:v>
+        <x:v>-3.15</x:v>
       </x:c>
       <x:c r="D163" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="E163" s="0">
-        <x:v>1999793</x:v>
+        <x:v>8300000</x:v>
       </x:c>
       <x:c r="F163" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G163" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H163" s="0">
-        <x:v>1742315226</x:v>
+        <x:v>2941310980</x:v>
       </x:c>
       <x:c r="I163" s="0">
-        <x:v>0.0494</x:v>
+        <x:v>0.1417</x:v>
       </x:c>
     </x:row>
     <x:row r="164" spans="1:9">
       <x:c r="A164" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B164" s="0">
-        <x:v>50.2</x:v>
+        <x:v>4.08</x:v>
       </x:c>
       <x:c r="C164" s="0">
-        <x:v>-1.15</x:v>
+        <x:v>-0.1</x:v>
       </x:c>
       <x:c r="D164" s="0" t="s">
         <x:v>135</x:v>
       </x:c>
       <x:c r="E164" s="0">
-        <x:v>1859145</x:v>
+        <x:v>13000000</x:v>
       </x:c>
       <x:c r="F164" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G164" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H164" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>1416740879</x:v>
       </x:c>
       <x:c r="I164" s="0">
-        <x:v>0.0324</x:v>
+        <x:v>0.4613</x:v>
       </x:c>
     </x:row>
     <x:row r="165" spans="1:9">
       <x:c r="A165" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B165" s="0">
-        <x:v>3.26</x:v>
+        <x:v>116.7</x:v>
       </x:c>
       <x:c r="C165" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>-1.9</x:v>
       </x:c>
       <x:c r="D165" s="0" t="s">
         <x:v>136</x:v>
       </x:c>
       <x:c r="E165" s="0">
-        <x:v>689661000</x:v>
+        <x:v>1999793</x:v>
       </x:c>
       <x:c r="F165" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G165" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H165" s="0">
-        <x:v>7382591324</x:v>
+        <x:v>1742315226</x:v>
       </x:c>
       <x:c r="I165" s="0">
-        <x:v>0.0934</x:v>
+        <x:v>0.0494</x:v>
       </x:c>
     </x:row>
     <x:row r="166" spans="1:9">
       <x:c r="A166" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B166" s="0">
-        <x:v>50.2</x:v>
+        <x:v>55.2</x:v>
       </x:c>
       <x:c r="C166" s="0">
-        <x:v>-1.15</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D166" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="E166" s="0">
-        <x:v>1902000</x:v>
+        <x:v>1859145</x:v>
       </x:c>
       <x:c r="F166" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G166" s="0">
         <x:v>2025.09</x:v>
@@ -5595,36 +5598,36 @@
         <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I166" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0324</x:v>
       </x:c>
     </x:row>
     <x:row r="167" spans="1:9">
       <x:c r="A167" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B167" s="0">
-        <x:v>94.4</x:v>
+        <x:v>3.25</x:v>
       </x:c>
       <x:c r="C167" s="0">
-        <x:v>0.45</x:v>
+        <x:v>-0.01</x:v>
       </x:c>
       <x:c r="D167" s="0" t="s">
         <x:v>137</x:v>
       </x:c>
       <x:c r="E167" s="0">
-        <x:v>56520000</x:v>
+        <x:v>689661000</x:v>
       </x:c>
       <x:c r="F167" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G167" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H167" s="0">
-        <x:v>1781510191</x:v>
+        <x:v>7382591324</x:v>
       </x:c>
       <x:c r="I167" s="0">
-        <x:v>0.0317</x:v>
+        <x:v>0.0934</x:v>
       </x:c>
     </x:row>
     <x:row r="168" spans="1:9">
@@ -5632,25 +5635,25 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B168" s="0">
-        <x:v>94.4</x:v>
+        <x:v>55.2</x:v>
       </x:c>
       <x:c r="C168" s="0">
-        <x:v>0.45</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D168" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="E168" s="0">
-        <x:v>888325</x:v>
+        <x:v>1902000</x:v>
       </x:c>
       <x:c r="F168" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G168" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H168" s="0">
-        <x:v>1781510191</x:v>
+        <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I168" s="0">
         <x:v>0</x:v>
@@ -5658,19 +5661,19 @@
     </x:row>
     <x:row r="169" spans="1:9">
       <x:c r="A169" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B169" s="0">
-        <x:v>7.63</x:v>
+        <x:v>98.2</x:v>
       </x:c>
       <x:c r="C169" s="0">
-        <x:v>0.25</x:v>
+        <x:v>3.8</x:v>
       </x:c>
       <x:c r="D169" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="E169" s="0">
-        <x:v>5581810</x:v>
+        <x:v>56520000</x:v>
       </x:c>
       <x:c r="F169" s="0" t="s">
         <x:v>11</x:v>
@@ -5679,85 +5682,85 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H169" s="0">
-        <x:v>9028523851</x:v>
+        <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I169" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0317</x:v>
       </x:c>
     </x:row>
     <x:row r="170" spans="1:9">
       <x:c r="A170" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B170" s="0">
-        <x:v>50.2</x:v>
+        <x:v>98.2</x:v>
       </x:c>
       <x:c r="C170" s="0">
-        <x:v>-1.15</x:v>
+        <x:v>3.8</x:v>
       </x:c>
       <x:c r="D170" s="0" t="s">
         <x:v>138</x:v>
       </x:c>
       <x:c r="E170" s="0">
-        <x:v>504000000</x:v>
+        <x:v>888325</x:v>
       </x:c>
       <x:c r="F170" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G170" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H170" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I170" s="0">
-        <x:v>0.2043</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="171" spans="1:9">
       <x:c r="A171" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B171" s="0">
-        <x:v>284</x:v>
+        <x:v>7.88</x:v>
       </x:c>
       <x:c r="C171" s="0">
-        <x:v>20</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="D171" s="0" t="s">
         <x:v>138</x:v>
       </x:c>
       <x:c r="E171" s="0">
-        <x:v>21500032</x:v>
+        <x:v>5581810</x:v>
       </x:c>
       <x:c r="F171" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G171" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H171" s="0">
-        <x:v>24073631758</x:v>
+        <x:v>9028523851</x:v>
       </x:c>
       <x:c r="I171" s="0">
-        <x:v>0.0383</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="172" spans="1:9">
       <x:c r="A172" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B172" s="0">
-        <x:v>1139</x:v>
+        <x:v>55.2</x:v>
       </x:c>
       <x:c r="C172" s="0">
-        <x:v>9</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D172" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="E172" s="0">
-        <x:v>6455151</x:v>
+        <x:v>504000000</x:v>
       </x:c>
       <x:c r="F172" s="0" t="s">
         <x:v>11</x:v>
@@ -5766,9 +5769,67 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H172" s="0">
+        <x:v>2467243928</x:v>
+      </x:c>
+      <x:c r="I172" s="0">
+        <x:v>0.2043</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173" spans="1:9">
+      <x:c r="A173" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B173" s="0">
+        <x:v>290.25</x:v>
+      </x:c>
+      <x:c r="C173" s="0">
+        <x:v>6.25</x:v>
+      </x:c>
+      <x:c r="D173" s="0" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="E173" s="0">
+        <x:v>21500032</x:v>
+      </x:c>
+      <x:c r="F173" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G173" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H173" s="0">
+        <x:v>24073631758</x:v>
+      </x:c>
+      <x:c r="I173" s="0">
+        <x:v>0.0383</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174" spans="1:9">
+      <x:c r="A174" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B174" s="0">
+        <x:v>1200</x:v>
+      </x:c>
+      <x:c r="C174" s="0">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D174" s="0" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="E174" s="0">
+        <x:v>6455151</x:v>
+      </x:c>
+      <x:c r="F174" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G174" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H174" s="0">
         <x:v>1586603352</x:v>
       </x:c>
-      <x:c r="I172" s="0">
+      <x:c r="I174" s="0">
         <x:v>0.1745</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/yeni-is-anlasmalari/data/yeni-is-anlasmalari.xlsx
+++ b/app/borsa/yeni-is-anlasmalari/data/yeni-is-anlasmalari.xlsx
@@ -43,12 +43,30 @@
     <x:t>Yeni İş İlişkisi / Yıllık Satışlar</x:t>
   </x:si>
   <x:si>
+    <x:t>CWENE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-05-05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>USD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-05-04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BVSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUR</x:t>
+  </x:si>
+  <x:si>
     <x:t>FORTE</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-05-04</x:t>
-  </x:si>
-  <x:si>
     <x:t>TRY</x:t>
   </x:si>
   <x:si>
@@ -58,27 +76,15 @@
     <x:t>2026-04-30</x:t>
   </x:si>
   <x:si>
-    <x:t>USD</x:t>
-  </x:si>
-  <x:si>
     <x:t>SMRTG</x:t>
   </x:si>
   <x:si>
-    <x:t>EUR</x:t>
-  </x:si>
-  <x:si>
     <x:t>AKHAN</x:t>
   </x:si>
   <x:si>
-    <x:t>BVSAN</x:t>
-  </x:si>
-  <x:si>
     <x:t>2026-04-29</x:t>
   </x:si>
   <x:si>
-    <x:t>CWENE</x:t>
-  </x:si>
-  <x:si>
     <x:t>FONET</x:t>
   </x:si>
   <x:si>
@@ -95,9 +101,6 @@
   </x:si>
   <x:si>
     <x:t>2026-04-24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORGE</x:t>
   </x:si>
   <x:si>
     <x:t>ARDYZ</x:t>
@@ -784,7 +787,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I174"/>
+  <x:dimension ref="A1:I177"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -821,28 +824,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>98.2</x:v>
+        <x:v>36.4</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>3.8</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>12100000</x:v>
+        <x:v>32493961</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2026.03</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>17386730041</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>0.005</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -850,86 +853,86 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>431.75</x:v>
+        <x:v>81.7</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>11.5</x:v>
+        <x:v>-0.65</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>125100000</x:v>
+        <x:v>940002</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>2026.03</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>184925592000</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>0.0304</x:v>
+        <x:v>0.0121</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
       <x:c r="A4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>7.88</x:v>
+        <x:v>118.5</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>0.25</x:v>
+        <x:v>1.8</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>32010000</x:v>
+        <x:v>920000</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G4" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>10581001663</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>0.1592</x:v>
+        <x:v>0.0154</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
       <x:c r="A5" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>28.92</x:v>
+        <x:v>100.7</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>0.3</x:v>
+        <x:v>2.5</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>76650</x:v>
+        <x:v>12100000</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G5" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>7297855153</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>0.0005</x:v>
+        <x:v>0.005</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -937,28 +940,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>116.7</x:v>
+        <x:v>427.25</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>-1.9</x:v>
+        <x:v>-4.5</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>915000</x:v>
+        <x:v>125100000</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2026.03</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>3150489640</x:v>
+        <x:v>184925592000</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>0.0153</x:v>
+        <x:v>0.0304</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -966,28 +969,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>35.8</x:v>
+        <x:v>8.36</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>-0.84</x:v>
+        <x:v>0.48</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>2136645</x:v>
+        <x:v>32010000</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>2026.03</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>17386730041</x:v>
+        <x:v>10581001663</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>0.0055</x:v>
+        <x:v>0.1592</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -995,16 +998,16 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>5.4</x:v>
+        <x:v>29.24</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>0.49</x:v>
+        <x:v>0.32</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>132077304</x:v>
+        <x:v>76650</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
         <x:v>11</x:v>
@@ -1013,114 +1016,114 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>855070469</x:v>
+        <x:v>7297855153</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>0.1545</x:v>
+        <x:v>0.0005</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
       <x:c r="A9" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>290.25</x:v>
+        <x:v>118.5</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>6.25</x:v>
+        <x:v>1.8</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>51531000</x:v>
+        <x:v>915000</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G9" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>35290767390</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>0.0656</x:v>
+        <x:v>0.0153</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
       <x:c r="A10" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>1200</x:v>
+        <x:v>36.4</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>61</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>950978</x:v>
+        <x:v>2136645</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2026.03</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>1883544167</x:v>
+        <x:v>17386730041</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>0.0227</x:v>
+        <x:v>0.0055</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
       <x:c r="A11" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>567.5</x:v>
+        <x:v>5.48</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>20.5</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>100000000</x:v>
+        <x:v>132077304</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G11" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>71453576000</x:v>
+        <x:v>855070469</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>0.0628</x:v>
+        <x:v>0.1545</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
       <x:c r="A12" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>82.35</x:v>
+        <x:v>295.75</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>-3.15</x:v>
+        <x:v>5.5</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>286071819</x:v>
+        <x:v>51531000</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
         <x:v>11</x:v>
@@ -1129,346 +1132,346 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>35290767390</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>0.0818</x:v>
+        <x:v>0.0656</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
       <x:c r="A13" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>116.7</x:v>
+        <x:v>1240</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>-1.9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>883793</x:v>
+        <x:v>950978</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G13" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>3150489640</x:v>
+        <x:v>1883544167</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>0.0148</x:v>
+        <x:v>0.0227</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
       <x:c r="A14" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B14" s="0">
+        <x:v>564</x:v>
+      </x:c>
+      <x:c r="C14" s="0">
+        <x:v>-3.5</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="B14" s="0">
-        <x:v>55.2</x:v>
-      </x:c>
-      <x:c r="C14" s="0">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D14" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="E14" s="0">
-        <x:v>606770</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G14" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>71453576000</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>0.0064</x:v>
+        <x:v>0.0628</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
       <x:c r="A15" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>58.25</x:v>
+        <x:v>81.7</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>-0.7</x:v>
+        <x:v>-0.65</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>505597002</x:v>
+        <x:v>286071819</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G15" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>8121300519</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>0.0623</x:v>
+        <x:v>0.0818</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
       <x:c r="A16" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B16" s="0">
+        <x:v>118.5</x:v>
+      </x:c>
+      <x:c r="C16" s="0">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="D16" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="B16" s="0">
-        <x:v>55.2</x:v>
-      </x:c>
-      <x:c r="C16" s="0">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D16" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="E16" s="0">
-        <x:v>948000</x:v>
+        <x:v>883793</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G16" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>0.0101</x:v>
+        <x:v>0.0148</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
       <x:c r="A17" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>98.2</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>3.8</x:v>
+        <x:v>2.8</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>622000</x:v>
+        <x:v>606770</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G17" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>0.0114</x:v>
+        <x:v>0.0064</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
       <x:c r="A18" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B18" s="0">
+        <x:v>57.75</x:v>
+      </x:c>
+      <x:c r="C18" s="0">
+        <x:v>-0.5</x:v>
+      </x:c>
+      <x:c r="D18" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="B18" s="0">
-        <x:v>4.01</x:v>
-      </x:c>
-      <x:c r="C18" s="0">
-        <x:v>-0.08</x:v>
-      </x:c>
-      <x:c r="D18" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="E18" s="0">
-        <x:v>983000</x:v>
+        <x:v>505597002</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G18" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>2875634546</x:v>
+        <x:v>8121300519</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>0.018</x:v>
+        <x:v>0.0623</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
       <x:c r="A19" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>77.7</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>3.1</x:v>
+        <x:v>2.8</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>3421818</x:v>
+        <x:v>948000</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G19" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>5948036961</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>0.0257</x:v>
+        <x:v>0.0101</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
       <x:c r="A20" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>42.9</x:v>
+        <x:v>100.7</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>-1.1</x:v>
+        <x:v>2.5</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>697435</x:v>
+        <x:v>622000</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G20" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>4728937463</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>0.0066</x:v>
+        <x:v>0.0114</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
       <x:c r="A21" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>61.35</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>5.55</x:v>
+        <x:v>-0.01</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>4587145</x:v>
+        <x:v>983000</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G21" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>16733157490</x:v>
+        <x:v>2875634546</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>0.0123</x:v>
+        <x:v>0.018</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
       <x:c r="A22" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>40.94</x:v>
+        <x:v>80.4</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>-0.28</x:v>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>43200000</x:v>
+        <x:v>3421818</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G22" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>8236540064</x:v>
+        <x:v>5948036961</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>0.2345</x:v>
+        <x:v>0.0257</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
       <x:c r="A23" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>16.53</x:v>
+        <x:v>47.18</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>0.52</x:v>
+        <x:v>4.28</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>1200000</x:v>
+        <x:v>697435</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G23" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>3139850323</x:v>
+        <x:v>4728937463</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>0.0201</x:v>
+        <x:v>0.0066</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
       <x:c r="A24" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>58.25</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>-0.7</x:v>
+        <x:v>4.65</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>247902522</x:v>
+        <x:v>4587145</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
         <x:v>11</x:v>
@@ -1477,242 +1480,242 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>8121300519</x:v>
+        <x:v>16733157490</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>0.0305</x:v>
+        <x:v>0.0123</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
       <x:c r="A25" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>55.2</x:v>
+        <x:v>41.58</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>5</x:v>
+        <x:v>0.64</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>366000</x:v>
+        <x:v>43200000</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G25" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>8236540064</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>0.0039</x:v>
+        <x:v>0.2345</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
       <x:c r="A26" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B26" s="0">
+        <x:v>17.02</x:v>
+      </x:c>
+      <x:c r="C26" s="0">
+        <x:v>0.49</x:v>
+      </x:c>
+      <x:c r="D26" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="B26" s="0">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="C26" s="0">
-        <x:v>-3.5</x:v>
-      </x:c>
-      <x:c r="D26" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
       <x:c r="E26" s="0">
-        <x:v>141051834</x:v>
+        <x:v>1200000</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G26" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>709077088</x:v>
+        <x:v>3139850323</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>0.1989</x:v>
+        <x:v>0.0201</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
       <x:c r="A27" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>4.73</x:v>
+        <x:v>57.75</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>0</x:v>
+        <x:v>-0.5</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>5096500000</x:v>
+        <x:v>247902522</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>19538660616</x:v>
+        <x:v>8121300519</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>0.2608</x:v>
+        <x:v>0.0305</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
       <x:c r="A28" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>4.73</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>0</x:v>
+        <x:v>2.8</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>5096500000</x:v>
+        <x:v>366000</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>19538660616</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>0.2608</x:v>
+        <x:v>0.0039</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
       <x:c r="A29" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>35.8</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>-0.84</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>37500000</x:v>
+        <x:v>141051834</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G29" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>16355768622</x:v>
+        <x:v>709077088</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>0.1024</x:v>
+        <x:v>0.1989</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
       <x:c r="A30" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>232.1</x:v>
+        <x:v>4.76</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>12.3</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>2030000</x:v>
+        <x:v>5096500000</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>2159813703</x:v>
+        <x:v>19538660616</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>0.042</x:v>
+        <x:v>0.2608</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
       <x:c r="A31" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>61.35</x:v>
+        <x:v>4.76</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>5.55</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>31146246</x:v>
+        <x:v>5096500000</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>16733157490</x:v>
+        <x:v>19538660616</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>0.0832</x:v>
+        <x:v>0.2608</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
       <x:c r="A32" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>11.46</x:v>
+        <x:v>36.4</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>0.21</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>1000000</x:v>
+        <x:v>37500000</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G32" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>7221187888</x:v>
+        <x:v>16355768622</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>0.0001</x:v>
+        <x:v>0.1024</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1720,161 +1723,161 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>11.46</x:v>
+        <x:v>241.4</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>0.21</x:v>
+        <x:v>9.3</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>3150000</x:v>
+        <x:v>2030000</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G33" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>7221187888</x:v>
+        <x:v>2159813703</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>0.0227</x:v>
+        <x:v>0.042</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
       <x:c r="A34" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>11.46</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>0.21</x:v>
+        <x:v>4.65</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>2690000</x:v>
+        <x:v>31146246</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G34" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>7221187888</x:v>
+        <x:v>16733157490</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>0.0166</x:v>
+        <x:v>0.0832</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
       <x:c r="A35" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>61.35</x:v>
+        <x:v>11.95</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>5.55</x:v>
+        <x:v>0.49</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>4103000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G35" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>16733157490</x:v>
+        <x:v>7221187888</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>0.0109</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
       <x:c r="A36" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>116.7</x:v>
+        <x:v>11.95</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>-1.9</x:v>
+        <x:v>0.49</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>500000</x:v>
+        <x:v>3150000</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G36" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>3150489640</x:v>
+        <x:v>7221187888</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>0.0083</x:v>
+        <x:v>0.0227</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
       <x:c r="A37" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>55.2</x:v>
+        <x:v>11.95</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>5</x:v>
+        <x:v>0.49</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>872928</x:v>
+        <x:v>2690000</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G37" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>7221187888</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>0.0092</x:v>
+        <x:v>0.0166</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
       <x:c r="A38" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>98.2</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>3.8</x:v>
+        <x:v>4.65</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>21250000</x:v>
+        <x:v>4103000</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
         <x:v>11</x:v>
@@ -1883,36 +1886,36 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>16733157490</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>0.0087</x:v>
+        <x:v>0.0109</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
       <x:c r="A39" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>58.25</x:v>
+        <x:v>118.5</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>-0.7</x:v>
+        <x:v>1.8</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>67690912</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G39" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>8121300519</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I39" s="0">
         <x:v>0.0083</x:v>
@@ -1920,309 +1923,309 @@
     </x:row>
     <x:row r="40" spans="1:9">
       <x:c r="A40" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>35.8</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>-0.84</x:v>
+        <x:v>2.8</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>65458848</x:v>
+        <x:v>872928</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G40" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>16355768622</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>0.1784</x:v>
+        <x:v>0.0092</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
       <x:c r="A41" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>24.7</x:v>
+        <x:v>100.7</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>0.36</x:v>
+        <x:v>2.5</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>689500000</x:v>
+        <x:v>21250000</x:v>
       </x:c>
       <x:c r="F41" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G41" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>884571536</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>0.7795</x:v>
+        <x:v>0.0087</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
       <x:c r="A42" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>6.08</x:v>
+        <x:v>57.75</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>-0.1</x:v>
+        <x:v>-0.5</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>3024490</x:v>
+        <x:v>67690912</x:v>
       </x:c>
       <x:c r="F42" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G42" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>2322993973</x:v>
+        <x:v>8121300519</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>0.0671</x:v>
+        <x:v>0.0083</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
       <x:c r="A43" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>6.08</x:v>
+        <x:v>36.4</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>-0.1</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>4510336</x:v>
+        <x:v>65458848</x:v>
       </x:c>
       <x:c r="F43" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G43" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>2322993973</x:v>
+        <x:v>16355768622</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>0.0865</x:v>
+        <x:v>0.1784</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
       <x:c r="A44" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>51.05</x:v>
+        <x:v>24.76</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>1.25</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>205000000</x:v>
+        <x:v>689500000</x:v>
       </x:c>
       <x:c r="F44" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G44" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>20597209000</x:v>
+        <x:v>884571536</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>0.4434</x:v>
+        <x:v>0.7795</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
       <x:c r="A45" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>330</x:v>
+        <x:v>6.61</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>13</x:v>
+        <x:v>0.53</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>305000000</x:v>
+        <x:v>3024490</x:v>
       </x:c>
       <x:c r="F45" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G45" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>400439646</x:v>
+        <x:v>2322993973</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>0.7617</x:v>
+        <x:v>0.0671</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
       <x:c r="A46" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>82.35</x:v>
+        <x:v>6.61</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>-3.15</x:v>
+        <x:v>0.53</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>11700000</x:v>
+        <x:v>4510336</x:v>
       </x:c>
       <x:c r="F46" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G46" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>2322993973</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>0.1718</x:v>
+        <x:v>0.0865</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
       <x:c r="A47" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>232.1</x:v>
+        <x:v>54.2</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>12.3</x:v>
+        <x:v>3.15</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>1900000</x:v>
+        <x:v>205000000</x:v>
       </x:c>
       <x:c r="F47" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G47" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>2159813703</x:v>
+        <x:v>20597209000</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>0.0391</x:v>
+        <x:v>0.4434</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
       <x:c r="A48" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>4.01</x:v>
+        <x:v>317.5</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>-0.08</x:v>
+        <x:v>-12.5</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>1670000</x:v>
+        <x:v>305000000</x:v>
       </x:c>
       <x:c r="F48" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G48" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>2875634546</x:v>
+        <x:v>400439646</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>0.0298</x:v>
+        <x:v>0.7617</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
       <x:c r="A49" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>24.7</x:v>
+        <x:v>81.7</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>0.36</x:v>
+        <x:v>-0.65</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>48895800</x:v>
+        <x:v>11700000</x:v>
       </x:c>
       <x:c r="F49" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G49" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>884571536</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>0.0553</x:v>
+        <x:v>0.1718</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
       <x:c r="A50" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>24.7</x:v>
+        <x:v>241.4</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>0.36</x:v>
+        <x:v>9.3</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>689500000</x:v>
+        <x:v>1900000</x:v>
       </x:c>
       <x:c r="F50" s="0" t="s">
         <x:v>11</x:v>
@@ -2231,230 +2234,230 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>884571536</x:v>
+        <x:v>2159813703</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>0.7795</x:v>
+        <x:v>0.0391</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
       <x:c r="A51" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>45.36</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>0.24</x:v>
+        <x:v>-0.01</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>3102911</x:v>
+        <x:v>1670000</x:v>
       </x:c>
       <x:c r="F51" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G51" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>2907014564</x:v>
+        <x:v>2875634546</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>0.0475</x:v>
+        <x:v>0.0298</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
       <x:c r="A52" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>23.94</x:v>
+        <x:v>24.76</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>-0.26</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>13000000</x:v>
+        <x:v>48895800</x:v>
       </x:c>
       <x:c r="F52" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G52" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>11834942581</x:v>
+        <x:v>884571536</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>0.0563</x:v>
+        <x:v>0.0553</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:9">
       <x:c r="A53" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B53" s="0">
-        <x:v>77.7</x:v>
+        <x:v>24.76</x:v>
       </x:c>
       <x:c r="C53" s="0">
-        <x:v>3.1</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E53" s="0">
-        <x:v>6800000</x:v>
+        <x:v>689500000</x:v>
       </x:c>
       <x:c r="F53" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G53" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H53" s="0">
-        <x:v>5948036961</x:v>
+        <x:v>884571536</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>0.0583</x:v>
+        <x:v>0.7795</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:9">
       <x:c r="A54" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B54" s="0">
-        <x:v>51.05</x:v>
+        <x:v>45.2</x:v>
       </x:c>
       <x:c r="C54" s="0">
-        <x:v>1.25</x:v>
+        <x:v>-0.16</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E54" s="0">
-        <x:v>36750000</x:v>
+        <x:v>3102911</x:v>
       </x:c>
       <x:c r="F54" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G54" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>20597209000</x:v>
+        <x:v>2907014564</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>0.0793</x:v>
+        <x:v>0.0475</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:9">
       <x:c r="A55" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B55" s="0">
-        <x:v>1200</x:v>
+        <x:v>24.08</x:v>
       </x:c>
       <x:c r="C55" s="0">
-        <x:v>61</x:v>
+        <x:v>0.14</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E55" s="0">
-        <x:v>3867260</x:v>
+        <x:v>13000000</x:v>
       </x:c>
       <x:c r="F55" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G55" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H55" s="0">
-        <x:v>1883544167</x:v>
+        <x:v>11834942581</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>0.0912</x:v>
+        <x:v>0.0563</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:9">
       <x:c r="A56" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B56" s="0">
-        <x:v>63.5</x:v>
+        <x:v>80.4</x:v>
       </x:c>
       <x:c r="C56" s="0">
-        <x:v>-1.85</x:v>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E56" s="0">
-        <x:v>1498029716</x:v>
+        <x:v>6800000</x:v>
       </x:c>
       <x:c r="F56" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G56" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H56" s="0">
-        <x:v>12030341104</x:v>
+        <x:v>5948036961</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>0.1245</x:v>
+        <x:v>0.0583</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:9">
       <x:c r="A57" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B57" s="0">
-        <x:v>35.8</x:v>
+        <x:v>54.2</x:v>
       </x:c>
       <x:c r="C57" s="0">
-        <x:v>-0.84</x:v>
+        <x:v>3.15</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E57" s="0">
-        <x:v>48000000</x:v>
+        <x:v>36750000</x:v>
       </x:c>
       <x:c r="F57" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G57" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H57" s="0">
-        <x:v>16355768622</x:v>
+        <x:v>20597209000</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>0.1301</x:v>
+        <x:v>0.0793</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:9">
       <x:c r="A58" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B58" s="0">
-        <x:v>82.35</x:v>
+        <x:v>1240</x:v>
       </x:c>
       <x:c r="C58" s="0">
-        <x:v>-3.15</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E58" s="0">
-        <x:v>279699629</x:v>
+        <x:v>3867260</x:v>
       </x:c>
       <x:c r="F58" s="0" t="s">
         <x:v>11</x:v>
@@ -2463,97 +2466,97 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H58" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>1883544167</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>0.08</x:v>
+        <x:v>0.0912</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:9">
       <x:c r="A59" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B59" s="0">
-        <x:v>14.9</x:v>
+        <x:v>67.45</x:v>
       </x:c>
       <x:c r="C59" s="0">
-        <x:v>-0.04</x:v>
+        <x:v>3.95</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
         <x:v>64</x:v>
       </x:c>
       <x:c r="E59" s="0">
-        <x:v>7971822</x:v>
+        <x:v>1498029716</x:v>
       </x:c>
       <x:c r="F59" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G59" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H59" s="0">
-        <x:v>4675369372</x:v>
+        <x:v>12030341104</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>0.0756</x:v>
+        <x:v>0.1245</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:9">
       <x:c r="A60" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B60" s="0">
-        <x:v>55.2</x:v>
+        <x:v>36.4</x:v>
       </x:c>
       <x:c r="C60" s="0">
-        <x:v>5</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
         <x:v>64</x:v>
       </x:c>
       <x:c r="E60" s="0">
-        <x:v>1104000</x:v>
+        <x:v>48000000</x:v>
       </x:c>
       <x:c r="F60" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G60" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H60" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>16355768622</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>0.0116</x:v>
+        <x:v>0.1301</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:9">
       <x:c r="A61" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B61" s="0">
-        <x:v>24.7</x:v>
+        <x:v>81.7</x:v>
       </x:c>
       <x:c r="C61" s="0">
-        <x:v>0.36</x:v>
+        <x:v>-0.65</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E61" s="0">
-        <x:v>48895800</x:v>
+        <x:v>279699629</x:v>
       </x:c>
       <x:c r="F61" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G61" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H61" s="0">
-        <x:v>884571536</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I61" s="0">
-        <x:v>0.0553</x:v>
+        <x:v>0.08</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:9">
@@ -2561,16 +2564,16 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B62" s="0">
-        <x:v>3.25</x:v>
+        <x:v>15.9</x:v>
       </x:c>
       <x:c r="C62" s="0">
-        <x:v>-0.01</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E62" s="0">
-        <x:v>191089413</x:v>
+        <x:v>7971822</x:v>
       </x:c>
       <x:c r="F62" s="0" t="s">
         <x:v>11</x:v>
@@ -2579,27 +2582,27 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H62" s="0">
-        <x:v>9665356715</x:v>
+        <x:v>4675369372</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>0.0198</x:v>
+        <x:v>0.0756</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:9">
       <x:c r="A63" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B63" s="0">
-        <x:v>3.25</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C63" s="0">
-        <x:v>-0.01</x:v>
+        <x:v>2.8</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E63" s="0">
-        <x:v>605627160</x:v>
+        <x:v>1104000</x:v>
       </x:c>
       <x:c r="F63" s="0" t="s">
         <x:v>11</x:v>
@@ -2608,213 +2611,213 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H63" s="0">
-        <x:v>9665356715</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>0.0627</x:v>
+        <x:v>0.0116</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:9">
       <x:c r="A64" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B64" s="0">
-        <x:v>27.26</x:v>
+        <x:v>24.76</x:v>
       </x:c>
       <x:c r="C64" s="0">
-        <x:v>0.46</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E64" s="0">
-        <x:v>2356546000</x:v>
+        <x:v>48895800</x:v>
       </x:c>
       <x:c r="F64" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G64" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H64" s="0">
-        <x:v>7708004248</x:v>
+        <x:v>884571536</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>0.3057</x:v>
+        <x:v>0.0553</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:9">
       <x:c r="A65" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B65" s="0">
-        <x:v>16.53</x:v>
+        <x:v>3.29</x:v>
       </x:c>
       <x:c r="C65" s="0">
-        <x:v>0.52</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E65" s="0">
-        <x:v>431250</x:v>
+        <x:v>191089413</x:v>
       </x:c>
       <x:c r="F65" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G65" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H65" s="0">
-        <x:v>3139850323</x:v>
+        <x:v>9665356715</x:v>
       </x:c>
       <x:c r="I65" s="0">
-        <x:v>0.0071</x:v>
+        <x:v>0.0198</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:9">
       <x:c r="A66" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B66" s="0">
-        <x:v>16.53</x:v>
+        <x:v>3.29</x:v>
       </x:c>
       <x:c r="C66" s="0">
-        <x:v>0.52</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E66" s="0">
-        <x:v>800000</x:v>
+        <x:v>605627160</x:v>
       </x:c>
       <x:c r="F66" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G66" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H66" s="0">
-        <x:v>3139850323</x:v>
+        <x:v>9665356715</x:v>
       </x:c>
       <x:c r="I66" s="0">
-        <x:v>0.0131</x:v>
+        <x:v>0.0627</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:9">
       <x:c r="A67" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B67" s="0">
-        <x:v>58.25</x:v>
+        <x:v>27.32</x:v>
       </x:c>
       <x:c r="C67" s="0">
-        <x:v>-0.7</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E67" s="0">
-        <x:v>127172130</x:v>
+        <x:v>2356546000</x:v>
       </x:c>
       <x:c r="F67" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G67" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H67" s="0">
-        <x:v>8121300519</x:v>
+        <x:v>7708004248</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>0.0157</x:v>
+        <x:v>0.3057</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:9">
       <x:c r="A68" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B68" s="0">
-        <x:v>42.9</x:v>
+        <x:v>17.02</x:v>
       </x:c>
       <x:c r="C68" s="0">
-        <x:v>-1.1</x:v>
+        <x:v>0.49</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E68" s="0">
-        <x:v>42625000</x:v>
+        <x:v>431250</x:v>
       </x:c>
       <x:c r="F68" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G68" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H68" s="0">
-        <x:v>4728937463</x:v>
+        <x:v>3139850323</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>0.3994</x:v>
+        <x:v>0.0071</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:9">
       <x:c r="A69" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B69" s="0">
-        <x:v>98.2</x:v>
+        <x:v>17.02</x:v>
       </x:c>
       <x:c r="C69" s="0">
-        <x:v>3.8</x:v>
+        <x:v>0.49</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="E69" s="0">
-        <x:v>1486000</x:v>
+        <x:v>800000</x:v>
       </x:c>
       <x:c r="F69" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G69" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H69" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>3139850323</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>0.027</x:v>
+        <x:v>0.0131</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:9">
       <x:c r="A70" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B70" s="0">
-        <x:v>290.25</x:v>
+        <x:v>57.75</x:v>
       </x:c>
       <x:c r="C70" s="0">
-        <x:v>6.25</x:v>
+        <x:v>-0.5</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="E70" s="0">
-        <x:v>768864700</x:v>
+        <x:v>127172130</x:v>
       </x:c>
       <x:c r="F70" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G70" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H70" s="0">
-        <x:v>35290767390</x:v>
+        <x:v>8121300519</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>0.9648</x:v>
+        <x:v>0.0157</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:9">
@@ -2822,161 +2825,161 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B71" s="0">
-        <x:v>61.35</x:v>
+        <x:v>47.18</x:v>
       </x:c>
       <x:c r="C71" s="0">
-        <x:v>5.55</x:v>
+        <x:v>4.28</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="E71" s="0">
-        <x:v>15938617</x:v>
+        <x:v>42625000</x:v>
       </x:c>
       <x:c r="F71" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G71" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H71" s="0">
-        <x:v>16733157490</x:v>
+        <x:v>4728937463</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>0.0422</x:v>
+        <x:v>0.3994</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:9">
       <x:c r="A72" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B72" s="0">
+        <x:v>100.7</x:v>
+      </x:c>
+      <x:c r="C72" s="0">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="D72" s="0" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="B72" s="0">
-        <x:v>14.29</x:v>
-      </x:c>
-      <x:c r="C72" s="0">
-        <x:v>0.38</x:v>
-      </x:c>
-      <x:c r="D72" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
       <x:c r="E72" s="0">
-        <x:v>30438120</x:v>
+        <x:v>1486000</x:v>
       </x:c>
       <x:c r="F72" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G72" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H72" s="0">
-        <x:v>3159124121</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>0</x:v>
+        <x:v>0.027</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:9">
       <x:c r="A73" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B73" s="0">
-        <x:v>232.1</x:v>
+        <x:v>295.75</x:v>
       </x:c>
       <x:c r="C73" s="0">
-        <x:v>12.3</x:v>
+        <x:v>5.5</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E73" s="0">
-        <x:v>3900000</x:v>
+        <x:v>768864700</x:v>
       </x:c>
       <x:c r="F73" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G73" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H73" s="0">
-        <x:v>2159813703</x:v>
+        <x:v>35290767390</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>0.0797</x:v>
+        <x:v>0.9648</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:9">
       <x:c r="A74" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B74" s="0">
-        <x:v>232.1</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C74" s="0">
-        <x:v>12.3</x:v>
+        <x:v>4.65</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E74" s="0">
-        <x:v>2104908</x:v>
+        <x:v>15938617</x:v>
       </x:c>
       <x:c r="F74" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G74" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H74" s="0">
-        <x:v>2159813703</x:v>
+        <x:v>16733157490</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>0.043</x:v>
+        <x:v>0.0422</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:9">
       <x:c r="A75" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B75" s="0">
-        <x:v>28.92</x:v>
+        <x:v>14.99</x:v>
       </x:c>
       <x:c r="C75" s="0">
-        <x:v>0.3</x:v>
+        <x:v>0.7</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
         <x:v>72</x:v>
       </x:c>
       <x:c r="E75" s="0">
-        <x:v>3900000</x:v>
+        <x:v>30438120</x:v>
       </x:c>
       <x:c r="F75" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G75" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H75" s="0">
-        <x:v>7297855153</x:v>
+        <x:v>3159124121</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>0.0236</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:9">
       <x:c r="A76" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B76" s="0">
-        <x:v>5.4</x:v>
+        <x:v>241.4</x:v>
       </x:c>
       <x:c r="C76" s="0">
-        <x:v>0.49</x:v>
+        <x:v>9.3</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
         <x:v>73</x:v>
       </x:c>
       <x:c r="E76" s="0">
-        <x:v>496968445</x:v>
+        <x:v>3900000</x:v>
       </x:c>
       <x:c r="F76" s="0" t="s">
         <x:v>11</x:v>
@@ -2985,27 +2988,27 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H76" s="0">
-        <x:v>855070469</x:v>
+        <x:v>2159813703</x:v>
       </x:c>
       <x:c r="I76" s="0">
-        <x:v>0.5812</x:v>
+        <x:v>0.0797</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:9">
       <x:c r="A77" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B77" s="0">
-        <x:v>12.66</x:v>
+        <x:v>241.4</x:v>
       </x:c>
       <x:c r="C77" s="0">
-        <x:v>-0.7</x:v>
+        <x:v>9.3</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
         <x:v>73</x:v>
       </x:c>
       <x:c r="E77" s="0">
-        <x:v>108750000</x:v>
+        <x:v>2104908</x:v>
       </x:c>
       <x:c r="F77" s="0" t="s">
         <x:v>11</x:v>
@@ -3014,143 +3017,143 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H77" s="0">
-        <x:v>1982520183</x:v>
+        <x:v>2159813703</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>0.0549</x:v>
+        <x:v>0.043</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:9">
       <x:c r="A78" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B78" s="0">
-        <x:v>116.7</x:v>
+        <x:v>29.24</x:v>
       </x:c>
       <x:c r="C78" s="0">
-        <x:v>-1.9</x:v>
+        <x:v>0.32</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E78" s="0">
-        <x:v>1605197</x:v>
+        <x:v>3900000</x:v>
       </x:c>
       <x:c r="F78" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G78" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H78" s="0">
-        <x:v>3150489640</x:v>
+        <x:v>7297855153</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>0.0257</x:v>
+        <x:v>0.0236</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:9">
       <x:c r="A79" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B79" s="0">
-        <x:v>431.75</x:v>
+        <x:v>5.48</x:v>
       </x:c>
       <x:c r="C79" s="0">
-        <x:v>11.5</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E79" s="0">
-        <x:v>54600000</x:v>
+        <x:v>496968445</x:v>
       </x:c>
       <x:c r="F79" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G79" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H79" s="0">
-        <x:v>180444938000</x:v>
+        <x:v>855070469</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>0.0133</x:v>
+        <x:v>0.5812</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:9">
       <x:c r="A80" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B80" s="0">
-        <x:v>431.75</x:v>
+        <x:v>12.31</x:v>
       </x:c>
       <x:c r="C80" s="0">
-        <x:v>11.5</x:v>
+        <x:v>-0.35</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E80" s="0">
-        <x:v>111850000</x:v>
+        <x:v>108750000</x:v>
       </x:c>
       <x:c r="F80" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G80" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H80" s="0">
-        <x:v>180444938000</x:v>
+        <x:v>1982520183</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>0.0273</x:v>
+        <x:v>0.0549</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:9">
       <x:c r="A81" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B81" s="0">
-        <x:v>55.2</x:v>
+        <x:v>118.5</x:v>
       </x:c>
       <x:c r="C81" s="0">
-        <x:v>5</x:v>
+        <x:v>1.8</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
         <x:v>76</x:v>
       </x:c>
       <x:c r="E81" s="0">
-        <x:v>803090</x:v>
+        <x:v>1605197</x:v>
       </x:c>
       <x:c r="F81" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G81" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H81" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I81" s="0">
-        <x:v>0.0084</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:9">
       <x:c r="A82" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B82" s="0">
-        <x:v>27.26</x:v>
+        <x:v>427.25</x:v>
       </x:c>
       <x:c r="C82" s="0">
-        <x:v>0.46</x:v>
+        <x:v>-4.5</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
         <x:v>77</x:v>
       </x:c>
       <x:c r="E82" s="0">
-        <x:v>2356546000</x:v>
+        <x:v>54600000</x:v>
       </x:c>
       <x:c r="F82" s="0" t="s">
         <x:v>11</x:v>
@@ -3159,56 +3162,56 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H82" s="0">
-        <x:v>7708004248</x:v>
+        <x:v>180444938000</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>0.3057</x:v>
+        <x:v>0.0133</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:9">
       <x:c r="A83" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B83" s="0">
-        <x:v>1200</x:v>
+        <x:v>427.25</x:v>
       </x:c>
       <x:c r="C83" s="0">
-        <x:v>61</x:v>
+        <x:v>-4.5</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E83" s="0">
-        <x:v>875400</x:v>
+        <x:v>111850000</x:v>
       </x:c>
       <x:c r="F83" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G83" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H83" s="0">
-        <x:v>1883544167</x:v>
+        <x:v>180444938000</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>0.0205</x:v>
+        <x:v>0.0273</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:9">
       <x:c r="A84" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B84" s="0">
-        <x:v>26.7</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C84" s="0">
-        <x:v>-0.1</x:v>
+        <x:v>2.8</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E84" s="0">
-        <x:v>330000000</x:v>
+        <x:v>803090</x:v>
       </x:c>
       <x:c r="F84" s="0" t="s">
         <x:v>11</x:v>
@@ -3217,56 +3220,56 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H84" s="0">
-        <x:v>5287314404</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>0.0624</x:v>
+        <x:v>0.0084</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:9">
       <x:c r="A85" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B85" s="0">
-        <x:v>82.35</x:v>
+        <x:v>27.32</x:v>
       </x:c>
       <x:c r="C85" s="0">
-        <x:v>-3.15</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E85" s="0">
-        <x:v>11700000</x:v>
+        <x:v>2356546000</x:v>
       </x:c>
       <x:c r="F85" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G85" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H85" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>7708004248</x:v>
       </x:c>
       <x:c r="I85" s="0">
-        <x:v>0.1705</x:v>
+        <x:v>0.3057</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:9">
       <x:c r="A86" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B86" s="0">
-        <x:v>7.88</x:v>
+        <x:v>1240</x:v>
       </x:c>
       <x:c r="C86" s="0">
-        <x:v>0.25</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E86" s="0">
-        <x:v>4000000000</x:v>
+        <x:v>875400</x:v>
       </x:c>
       <x:c r="F86" s="0" t="s">
         <x:v>11</x:v>
@@ -3275,433 +3278,433 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H86" s="0">
-        <x:v>10581001663</x:v>
+        <x:v>1883544167</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>0.378</x:v>
+        <x:v>0.0205</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:9">
       <x:c r="A87" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B87" s="0">
-        <x:v>16.53</x:v>
+        <x:v>26.82</x:v>
       </x:c>
       <x:c r="C87" s="0">
-        <x:v>0.52</x:v>
+        <x:v>0.12</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E87" s="0">
-        <x:v>1086598</x:v>
+        <x:v>330000000</x:v>
       </x:c>
       <x:c r="F87" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G87" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H87" s="0">
-        <x:v>2020891371</x:v>
+        <x:v>5287314404</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>0.0274</x:v>
+        <x:v>0.0624</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:9">
       <x:c r="A88" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B88" s="0">
-        <x:v>14.9</x:v>
+        <x:v>81.7</x:v>
       </x:c>
       <x:c r="C88" s="0">
-        <x:v>-0.04</x:v>
+        <x:v>-0.65</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E88" s="0">
-        <x:v>216000000</x:v>
+        <x:v>11700000</x:v>
       </x:c>
       <x:c r="F88" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G88" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H88" s="0">
-        <x:v>3025063909</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>0.0714</x:v>
+        <x:v>0.1705</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:9">
       <x:c r="A89" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B89" s="0">
-        <x:v>55.2</x:v>
+        <x:v>8.36</x:v>
       </x:c>
       <x:c r="C89" s="0">
-        <x:v>5</x:v>
+        <x:v>0.48</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E89" s="0">
-        <x:v>7292916</x:v>
+        <x:v>4000000000</x:v>
       </x:c>
       <x:c r="F89" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G89" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H89" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>10581001663</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>0.0758</x:v>
+        <x:v>0.378</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:9">
       <x:c r="A90" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B90" s="0">
-        <x:v>29.86</x:v>
+        <x:v>17.02</x:v>
       </x:c>
       <x:c r="C90" s="0">
-        <x:v>2.7</x:v>
+        <x:v>0.49</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E90" s="0">
-        <x:v>250000</x:v>
+        <x:v>1086598</x:v>
       </x:c>
       <x:c r="F90" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G90" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H90" s="0">
-        <x:v>448686813</x:v>
+        <x:v>2020891371</x:v>
       </x:c>
       <x:c r="I90" s="0">
-        <x:v>0.0006</x:v>
+        <x:v>0.0274</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:9">
       <x:c r="A91" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B91" s="0">
-        <x:v>61.35</x:v>
+        <x:v>15.9</x:v>
       </x:c>
       <x:c r="C91" s="0">
-        <x:v>5.55</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E91" s="0">
-        <x:v>36900000</x:v>
+        <x:v>216000000</x:v>
       </x:c>
       <x:c r="F91" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G91" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H91" s="0">
-        <x:v>10597063406</x:v>
+        <x:v>3025063909</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>0.1527</x:v>
+        <x:v>0.0714</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:9">
       <x:c r="A92" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B92" s="0">
-        <x:v>64.25</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C92" s="0">
-        <x:v>4</x:v>
+        <x:v>2.8</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E92" s="0">
-        <x:v>3800000</x:v>
+        <x:v>7292916</x:v>
       </x:c>
       <x:c r="F92" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G92" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H92" s="0">
-        <x:v>832031190</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>0.2002</x:v>
+        <x:v>0.0758</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:9">
       <x:c r="A93" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B93" s="0">
-        <x:v>5.4</x:v>
+        <x:v>29.22</x:v>
       </x:c>
       <x:c r="C93" s="0">
-        <x:v>0.49</x:v>
+        <x:v>-0.64</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E93" s="0">
-        <x:v>2100000</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="F93" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G93" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H93" s="0">
-        <x:v>855070469</x:v>
+        <x:v>448686813</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>0.1076</x:v>
+        <x:v>0.0006</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:9">
       <x:c r="A94" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B94" s="0">
-        <x:v>55.2</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C94" s="0">
-        <x:v>5</x:v>
+        <x:v>4.65</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E94" s="0">
-        <x:v>22928077</x:v>
+        <x:v>36900000</x:v>
       </x:c>
       <x:c r="F94" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G94" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H94" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>10597063406</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>0.2378</x:v>
+        <x:v>0.1527</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:9">
       <x:c r="A95" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B95" s="0">
-        <x:v>30.2</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C95" s="0">
-        <x:v>1.72</x:v>
+        <x:v>1.75</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
         <x:v>88</x:v>
       </x:c>
       <x:c r="E95" s="0">
-        <x:v>547462013</x:v>
+        <x:v>3800000</x:v>
       </x:c>
       <x:c r="F95" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G95" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H95" s="0">
-        <x:v>0</x:v>
+        <x:v>832031190</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>0</x:v>
+        <x:v>0.2002</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:9">
       <x:c r="A96" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B96" s="0">
+        <x:v>5.48</x:v>
+      </x:c>
+      <x:c r="C96" s="0">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="D96" s="0" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="B96" s="0">
-        <x:v>30.2</x:v>
-      </x:c>
-      <x:c r="C96" s="0">
-        <x:v>1.72</x:v>
-      </x:c>
-      <x:c r="D96" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
       <x:c r="E96" s="0">
-        <x:v>10567948</x:v>
+        <x:v>2100000</x:v>
       </x:c>
       <x:c r="F96" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G96" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H96" s="0">
-        <x:v>0</x:v>
+        <x:v>855070469</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>0</x:v>
+        <x:v>0.1076</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:9">
       <x:c r="A97" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B97" s="0">
-        <x:v>82.35</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C97" s="0">
-        <x:v>-3.15</x:v>
+        <x:v>2.8</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E97" s="0">
-        <x:v>8300000</x:v>
+        <x:v>22928077</x:v>
       </x:c>
       <x:c r="F97" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G97" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H97" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>0.1228</x:v>
+        <x:v>0.2378</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:9">
       <x:c r="A98" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B98" s="0">
-        <x:v>51.05</x:v>
+        <x:v>29.8</x:v>
       </x:c>
       <x:c r="C98" s="0">
-        <x:v>1.25</x:v>
+        <x:v>-0.4</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E98" s="0">
-        <x:v>3000000</x:v>
+        <x:v>547462013</x:v>
       </x:c>
       <x:c r="F98" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G98" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H98" s="0">
-        <x:v>20597209000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>0.0064</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:9">
       <x:c r="A99" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B99" s="0">
-        <x:v>35.94</x:v>
+        <x:v>29.8</x:v>
       </x:c>
       <x:c r="C99" s="0">
-        <x:v>0.26</x:v>
+        <x:v>-0.4</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E99" s="0">
-        <x:v>26640000</x:v>
+        <x:v>10567948</x:v>
       </x:c>
       <x:c r="F99" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G99" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H99" s="0">
-        <x:v>3277373640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>0.356</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:9">
       <x:c r="A100" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B100" s="0">
-        <x:v>5.91</x:v>
+        <x:v>81.7</x:v>
       </x:c>
       <x:c r="C100" s="0">
-        <x:v>0.53</x:v>
+        <x:v>-0.65</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E100" s="0">
-        <x:v>13107198</x:v>
+        <x:v>8300000</x:v>
       </x:c>
       <x:c r="F100" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G100" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H100" s="0">
-        <x:v>1627872951</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>0.0081</x:v>
+        <x:v>0.1228</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:9">
       <x:c r="A101" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B101" s="0">
-        <x:v>82.35</x:v>
+        <x:v>54.2</x:v>
       </x:c>
       <x:c r="C101" s="0">
-        <x:v>-3.15</x:v>
+        <x:v>3.15</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E101" s="0">
-        <x:v>237500000</x:v>
+        <x:v>3000000</x:v>
       </x:c>
       <x:c r="F101" s="0" t="s">
         <x:v>11</x:v>
@@ -3710,317 +3713,317 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H101" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>20597209000</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>0.0679</x:v>
+        <x:v>0.0064</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:9">
       <x:c r="A102" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B102" s="0">
-        <x:v>58.25</x:v>
+        <x:v>35.64</x:v>
       </x:c>
       <x:c r="C102" s="0">
-        <x:v>-0.7</x:v>
+        <x:v>-0.3</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E102" s="0">
-        <x:v>147892538</x:v>
+        <x:v>26640000</x:v>
       </x:c>
       <x:c r="F102" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G102" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H102" s="0">
-        <x:v>7257990064</x:v>
+        <x:v>3277373640</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>0.0204</x:v>
+        <x:v>0.356</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:9">
       <x:c r="A103" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B103" s="0">
-        <x:v>55.45</x:v>
+        <x:v>6.01</x:v>
       </x:c>
       <x:c r="C103" s="0">
-        <x:v>3.05</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E103" s="0">
-        <x:v>988848</x:v>
+        <x:v>13107198</x:v>
       </x:c>
       <x:c r="F103" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G103" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H103" s="0">
-        <x:v>12999679000</x:v>
+        <x:v>1627872951</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>0.0033</x:v>
+        <x:v>0.0081</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:9">
       <x:c r="A104" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B104" s="0">
-        <x:v>61.35</x:v>
+        <x:v>81.7</x:v>
       </x:c>
       <x:c r="C104" s="0">
-        <x:v>5.55</x:v>
+        <x:v>-0.65</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
         <x:v>95</x:v>
       </x:c>
       <x:c r="E104" s="0">
-        <x:v>47300000</x:v>
+        <x:v>237500000</x:v>
       </x:c>
       <x:c r="F104" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G104" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H104" s="0">
-        <x:v>10597063406</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I104" s="0">
-        <x:v>0.2309</x:v>
+        <x:v>0.0679</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:9">
       <x:c r="A105" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B105" s="0">
-        <x:v>4.01</x:v>
+        <x:v>57.75</x:v>
       </x:c>
       <x:c r="C105" s="0">
-        <x:v>-0.08</x:v>
+        <x:v>-0.5</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E105" s="0">
-        <x:v>758600</x:v>
+        <x:v>147892538</x:v>
       </x:c>
       <x:c r="F105" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G105" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H105" s="0">
-        <x:v>1960468575</x:v>
+        <x:v>7257990064</x:v>
       </x:c>
       <x:c r="I105" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0.0204</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:9">
       <x:c r="A106" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B106" s="0">
-        <x:v>4.01</x:v>
+        <x:v>58.8</x:v>
       </x:c>
       <x:c r="C106" s="0">
-        <x:v>-0.08</x:v>
+        <x:v>3.35</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E106" s="0">
-        <x:v>758600</x:v>
+        <x:v>988848</x:v>
       </x:c>
       <x:c r="F106" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G106" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H106" s="0">
-        <x:v>1960468575</x:v>
+        <x:v>12999679000</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>0.0004</x:v>
+        <x:v>0.0033</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:9">
       <x:c r="A107" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B107" s="0">
-        <x:v>1200</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C107" s="0">
-        <x:v>61</x:v>
+        <x:v>4.65</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E107" s="0">
-        <x:v>576665</x:v>
+        <x:v>47300000</x:v>
       </x:c>
       <x:c r="F107" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G107" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H107" s="0">
-        <x:v>1586603352</x:v>
+        <x:v>10597063406</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>0.0159</x:v>
+        <x:v>0.2309</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:9">
       <x:c r="A108" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B108" s="0">
-        <x:v>82.7</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C108" s="0">
-        <x:v>1.65</x:v>
+        <x:v>-0.01</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E108" s="0">
-        <x:v>8000000</x:v>
+        <x:v>758600</x:v>
       </x:c>
       <x:c r="F108" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G108" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H108" s="0">
-        <x:v>20999579110</x:v>
+        <x:v>1960468575</x:v>
       </x:c>
       <x:c r="I108" s="0">
-        <x:v>0.0166</x:v>
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:9">
       <x:c r="A109" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B109" s="0">
-        <x:v>98.2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C109" s="0">
-        <x:v>3.8</x:v>
+        <x:v>-0.01</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E109" s="0">
-        <x:v>850000</x:v>
+        <x:v>758600</x:v>
       </x:c>
       <x:c r="F109" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="G109" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H109" s="0">
-        <x:v>1781510191</x:v>
+        <x:v>1960468575</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>0.0208</x:v>
+        <x:v>0.0004</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:9">
       <x:c r="A110" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B110" s="0">
-        <x:v>16.53</x:v>
+        <x:v>1240</x:v>
       </x:c>
       <x:c r="C110" s="0">
-        <x:v>0.52</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E110" s="0">
-        <x:v>10149200</x:v>
+        <x:v>576665</x:v>
       </x:c>
       <x:c r="F110" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G110" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H110" s="0">
-        <x:v>2020891371</x:v>
+        <x:v>1586603352</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>0.2601</x:v>
+        <x:v>0.0159</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:9">
       <x:c r="A111" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B111" s="0">
-        <x:v>116.7</x:v>
+        <x:v>85.8</x:v>
       </x:c>
       <x:c r="C111" s="0">
-        <x:v>-1.9</x:v>
+        <x:v>3.1</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E111" s="0">
-        <x:v>10500000</x:v>
+        <x:v>8000000</x:v>
       </x:c>
       <x:c r="F111" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G111" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H111" s="0">
-        <x:v>1742315226</x:v>
+        <x:v>20999579110</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>0.3121</x:v>
+        <x:v>0.0166</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:9">
       <x:c r="A112" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B112" s="0">
-        <x:v>98.2</x:v>
+        <x:v>100.7</x:v>
       </x:c>
       <x:c r="C112" s="0">
-        <x:v>3.8</x:v>
+        <x:v>2.5</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E112" s="0">
-        <x:v>366956541</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="F112" s="0" t="s">
         <x:v>11</x:v>
@@ -4032,227 +4035,227 @@
         <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I112" s="0">
-        <x:v>0.206</x:v>
+        <x:v>0.0208</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:9">
       <x:c r="A113" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B113" s="0">
-        <x:v>58.25</x:v>
+        <x:v>17.02</x:v>
       </x:c>
       <x:c r="C113" s="0">
-        <x:v>-0.7</x:v>
+        <x:v>0.49</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E113" s="0">
-        <x:v>61158155</x:v>
+        <x:v>10149200</x:v>
       </x:c>
       <x:c r="F113" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G113" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H113" s="0">
-        <x:v>7257990064</x:v>
+        <x:v>2020891371</x:v>
       </x:c>
       <x:c r="I113" s="0">
-        <x:v>0.0084</x:v>
+        <x:v>0.2601</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:9">
       <x:c r="A114" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B114" s="0">
-        <x:v>111.8</x:v>
+        <x:v>118.5</x:v>
       </x:c>
       <x:c r="C114" s="0">
-        <x:v>5.5</x:v>
+        <x:v>1.8</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E114" s="0">
-        <x:v>1000000</x:v>
+        <x:v>10500000</x:v>
       </x:c>
       <x:c r="F114" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G114" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H114" s="0">
-        <x:v>1688731509</x:v>
+        <x:v>1742315226</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>0.0307</x:v>
+        <x:v>0.3121</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:9">
       <x:c r="A115" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B115" s="0">
-        <x:v>111.8</x:v>
+        <x:v>100.7</x:v>
       </x:c>
       <x:c r="C115" s="0">
-        <x:v>5.5</x:v>
+        <x:v>2.5</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
         <x:v>103</x:v>
       </x:c>
       <x:c r="E115" s="0">
-        <x:v>1050000</x:v>
+        <x:v>366956541</x:v>
       </x:c>
       <x:c r="F115" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G115" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H115" s="0">
-        <x:v>1688731509</x:v>
+        <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I115" s="0">
-        <x:v>0.0271</x:v>
+        <x:v>0.206</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:9">
       <x:c r="A116" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B116" s="0">
-        <x:v>40.7</x:v>
+        <x:v>57.75</x:v>
       </x:c>
       <x:c r="C116" s="0">
-        <x:v>0.12</x:v>
+        <x:v>-0.5</x:v>
       </x:c>
       <x:c r="D116" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E116" s="0">
-        <x:v>109053804</x:v>
+        <x:v>61158155</x:v>
       </x:c>
       <x:c r="F116" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G116" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H116" s="0">
-        <x:v>1942491524</x:v>
+        <x:v>7257990064</x:v>
       </x:c>
       <x:c r="I116" s="0">
-        <x:v>0.0561</x:v>
+        <x:v>0.0084</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:9">
       <x:c r="A117" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B117" s="0">
-        <x:v>9.81</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C117" s="0">
-        <x:v>-0.6</x:v>
+        <x:v>-1.8</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E117" s="0">
-        <x:v>62315119</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="F117" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G117" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H117" s="0">
-        <x:v>12026414029</x:v>
+        <x:v>1688731509</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>0.2257</x:v>
+        <x:v>0.0307</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:9">
       <x:c r="A118" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B118" s="0">
-        <x:v>232.1</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C118" s="0">
-        <x:v>12.3</x:v>
+        <x:v>-1.8</x:v>
       </x:c>
       <x:c r="D118" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E118" s="0">
-        <x:v>896400</x:v>
+        <x:v>1050000</x:v>
       </x:c>
       <x:c r="F118" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G118" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H118" s="0">
-        <x:v>1364716456</x:v>
+        <x:v>1688731509</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>0.0285</x:v>
+        <x:v>0.0271</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:9">
       <x:c r="A119" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B119" s="0">
-        <x:v>410.5</x:v>
+        <x:v>42.14</x:v>
       </x:c>
       <x:c r="C119" s="0">
-        <x:v>37.25</x:v>
+        <x:v>1.44</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E119" s="0">
-        <x:v>3370000</x:v>
+        <x:v>109053804</x:v>
       </x:c>
       <x:c r="F119" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G119" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H119" s="0">
-        <x:v>1865697176</x:v>
+        <x:v>1942491524</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>0.0785</x:v>
+        <x:v>0.0561</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:9">
       <x:c r="A120" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B120" s="0">
-        <x:v>51.05</x:v>
+        <x:v>9.6</x:v>
       </x:c>
       <x:c r="C120" s="0">
-        <x:v>1.25</x:v>
+        <x:v>-0.21</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E120" s="0">
-        <x:v>750561215</x:v>
+        <x:v>62315119</x:v>
       </x:c>
       <x:c r="F120" s="0" t="s">
         <x:v>11</x:v>
@@ -4261,201 +4264,201 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H120" s="0">
-        <x:v>16507905000</x:v>
+        <x:v>12026414029</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>0.0455</x:v>
+        <x:v>0.2257</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:9">
       <x:c r="A121" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B121" s="0">
-        <x:v>82.7</x:v>
+        <x:v>241.4</x:v>
       </x:c>
       <x:c r="C121" s="0">
-        <x:v>1.65</x:v>
+        <x:v>9.3</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E121" s="0">
-        <x:v>20000000</x:v>
+        <x:v>896400</x:v>
       </x:c>
       <x:c r="F121" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G121" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H121" s="0">
-        <x:v>20999579110</x:v>
+        <x:v>1364716456</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>0.0413</x:v>
+        <x:v>0.0285</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:9">
       <x:c r="A122" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B122" s="0">
-        <x:v>33.14</x:v>
+        <x:v>451.5</x:v>
       </x:c>
       <x:c r="C122" s="0">
-        <x:v>0.08</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E122" s="0">
-        <x:v>750000000</x:v>
+        <x:v>3370000</x:v>
       </x:c>
       <x:c r="F122" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G122" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H122" s="0">
-        <x:v>0</x:v>
+        <x:v>1865697176</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0785</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:9">
       <x:c r="A123" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B123" s="0">
-        <x:v>61.35</x:v>
+        <x:v>54.2</x:v>
       </x:c>
       <x:c r="C123" s="0">
-        <x:v>5.55</x:v>
+        <x:v>3.15</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E123" s="0">
-        <x:v>111232418</x:v>
+        <x:v>750561215</x:v>
       </x:c>
       <x:c r="F123" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G123" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H123" s="0">
-        <x:v>10597063406</x:v>
+        <x:v>16507905000</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>0.4554</x:v>
+        <x:v>0.0455</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:9">
       <x:c r="A124" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B124" s="0">
-        <x:v>35.8</x:v>
+        <x:v>85.8</x:v>
       </x:c>
       <x:c r="C124" s="0">
-        <x:v>-0.84</x:v>
+        <x:v>3.1</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E124" s="0">
-        <x:v>51384996</x:v>
+        <x:v>20000000</x:v>
       </x:c>
       <x:c r="F124" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G124" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H124" s="0">
-        <x:v>11899043692</x:v>
+        <x:v>20999579110</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>0.1873</x:v>
+        <x:v>0.0413</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:9">
       <x:c r="A125" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B125" s="0">
-        <x:v>35.8</x:v>
+        <x:v>33.98</x:v>
       </x:c>
       <x:c r="C125" s="0">
-        <x:v>-0.84</x:v>
+        <x:v>0.84</x:v>
       </x:c>
       <x:c r="D125" s="0" t="s">
         <x:v>114</x:v>
       </x:c>
       <x:c r="E125" s="0">
-        <x:v>3602451</x:v>
+        <x:v>750000000</x:v>
       </x:c>
       <x:c r="F125" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G125" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H125" s="0">
-        <x:v>11899043692</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I125" s="0">
-        <x:v>0.0131</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:9">
       <x:c r="A126" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B126" s="0">
-        <x:v>35.8</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C126" s="0">
-        <x:v>-0.84</x:v>
+        <x:v>4.65</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
         <x:v>114</x:v>
       </x:c>
       <x:c r="E126" s="0">
-        <x:v>24226465</x:v>
+        <x:v>111232418</x:v>
       </x:c>
       <x:c r="F126" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G126" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H126" s="0">
-        <x:v>11899043692</x:v>
+        <x:v>10597063406</x:v>
       </x:c>
       <x:c r="I126" s="0">
-        <x:v>0.0883</x:v>
+        <x:v>0.4554</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:9">
       <x:c r="A127" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B127" s="0">
-        <x:v>55.2</x:v>
+        <x:v>36.4</x:v>
       </x:c>
       <x:c r="C127" s="0">
-        <x:v>5</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="D127" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E127" s="0">
-        <x:v>12900000</x:v>
+        <x:v>51384996</x:v>
       </x:c>
       <x:c r="F127" s="0" t="s">
         <x:v>11</x:v>
@@ -4464,143 +4467,143 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H127" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>11899043692</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>0.0052</x:v>
+        <x:v>0.1873</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:9">
       <x:c r="A128" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B128" s="0">
-        <x:v>290.25</x:v>
+        <x:v>36.4</x:v>
       </x:c>
       <x:c r="C128" s="0">
-        <x:v>6.25</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="D128" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E128" s="0">
-        <x:v>53250000</x:v>
+        <x:v>3602451</x:v>
       </x:c>
       <x:c r="F128" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G128" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H128" s="0">
-        <x:v>24073631758</x:v>
+        <x:v>11899043692</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>0.115</x:v>
+        <x:v>0.0131</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:9">
       <x:c r="A129" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B129" s="0">
-        <x:v>30.2</x:v>
+        <x:v>36.4</x:v>
       </x:c>
       <x:c r="C129" s="0">
-        <x:v>1.72</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="D129" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E129" s="0">
-        <x:v>6860140</x:v>
+        <x:v>24226465</x:v>
       </x:c>
       <x:c r="F129" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G129" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H129" s="0">
-        <x:v>0</x:v>
+        <x:v>11899043692</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0883</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:9">
       <x:c r="A130" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B130" s="0">
-        <x:v>82.35</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C130" s="0">
-        <x:v>-3.15</x:v>
+        <x:v>2.8</x:v>
       </x:c>
       <x:c r="D130" s="0" t="s">
         <x:v>115</x:v>
       </x:c>
       <x:c r="E130" s="0">
-        <x:v>230000000</x:v>
+        <x:v>12900000</x:v>
       </x:c>
       <x:c r="F130" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G130" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H130" s="0">
-        <x:v>2941310980</x:v>
+        <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>0.0782</x:v>
+        <x:v>0.0052</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:9">
       <x:c r="A131" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B131" s="0">
-        <x:v>410.5</x:v>
+        <x:v>295.75</x:v>
       </x:c>
       <x:c r="C131" s="0">
-        <x:v>37.25</x:v>
+        <x:v>5.5</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E131" s="0">
-        <x:v>4700000</x:v>
+        <x:v>53250000</x:v>
       </x:c>
       <x:c r="F131" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G131" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H131" s="0">
-        <x:v>1865697176</x:v>
+        <x:v>24073631758</x:v>
       </x:c>
       <x:c r="I131" s="0">
-        <x:v>0.1092</x:v>
+        <x:v>0.115</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:9">
       <x:c r="A132" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B132" s="0">
-        <x:v>30.2</x:v>
+        <x:v>29.8</x:v>
       </x:c>
       <x:c r="C132" s="0">
-        <x:v>1.72</x:v>
+        <x:v>-0.4</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E132" s="0">
-        <x:v>256000000</x:v>
+        <x:v>6860140</x:v>
       </x:c>
       <x:c r="F132" s="0" t="s">
         <x:v>11</x:v>
@@ -4617,48 +4620,48 @@
     </x:row>
     <x:row r="133" spans="1:9">
       <x:c r="A133" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B133" s="0">
-        <x:v>35.8</x:v>
+        <x:v>81.7</x:v>
       </x:c>
       <x:c r="C133" s="0">
-        <x:v>-0.84</x:v>
+        <x:v>-0.65</x:v>
       </x:c>
       <x:c r="D133" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E133" s="0">
-        <x:v>10724896</x:v>
+        <x:v>230000000</x:v>
       </x:c>
       <x:c r="F133" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G133" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H133" s="0">
-        <x:v>11899043692</x:v>
+        <x:v>2941310980</x:v>
       </x:c>
       <x:c r="I133" s="0">
-        <x:v>0.039</x:v>
+        <x:v>0.0782</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:9">
       <x:c r="A134" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B134" s="0">
-        <x:v>24.7</x:v>
+        <x:v>451.5</x:v>
       </x:c>
       <x:c r="C134" s="0">
-        <x:v>0.36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D134" s="0" t="s">
         <x:v>117</x:v>
       </x:c>
       <x:c r="E134" s="0">
-        <x:v>31000000</x:v>
+        <x:v>4700000</x:v>
       </x:c>
       <x:c r="F134" s="0" t="s">
         <x:v>11</x:v>
@@ -4667,56 +4670,56 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H134" s="0">
-        <x:v>813967617</x:v>
+        <x:v>1865697176</x:v>
       </x:c>
       <x:c r="I134" s="0">
-        <x:v>0.0381</x:v>
+        <x:v>0.1092</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:9">
       <x:c r="A135" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B135" s="0">
-        <x:v>40.94</x:v>
+        <x:v>29.8</x:v>
       </x:c>
       <x:c r="C135" s="0">
-        <x:v>-0.28</x:v>
+        <x:v>-0.4</x:v>
       </x:c>
       <x:c r="D135" s="0" t="s">
         <x:v>117</x:v>
       </x:c>
       <x:c r="E135" s="0">
-        <x:v>13500000</x:v>
+        <x:v>256000000</x:v>
       </x:c>
       <x:c r="F135" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G135" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H135" s="0">
-        <x:v>6483809984</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I135" s="0">
-        <x:v>0.09</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:9">
       <x:c r="A136" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B136" s="0">
-        <x:v>40.7</x:v>
+        <x:v>36.4</x:v>
       </x:c>
       <x:c r="C136" s="0">
-        <x:v>0.12</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
         <x:v>118</x:v>
       </x:c>
       <x:c r="E136" s="0">
-        <x:v>29886357</x:v>
+        <x:v>10724896</x:v>
       </x:c>
       <x:c r="F136" s="0" t="s">
         <x:v>11</x:v>
@@ -4725,172 +4728,172 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H136" s="0">
-        <x:v>1942491524</x:v>
+        <x:v>11899043692</x:v>
       </x:c>
       <x:c r="I136" s="0">
-        <x:v>0.0154</x:v>
+        <x:v>0.039</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:9">
       <x:c r="A137" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B137" s="0">
-        <x:v>431.75</x:v>
+        <x:v>24.76</x:v>
       </x:c>
       <x:c r="C137" s="0">
-        <x:v>11.5</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="D137" s="0" t="s">
         <x:v>118</x:v>
       </x:c>
       <x:c r="E137" s="0">
-        <x:v>171000000</x:v>
+        <x:v>31000000</x:v>
       </x:c>
       <x:c r="F137" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G137" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H137" s="0">
-        <x:v>130147715000</x:v>
+        <x:v>813967617</x:v>
       </x:c>
       <x:c r="I137" s="0">
-        <x:v>0.0568</x:v>
+        <x:v>0.0381</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:9">
       <x:c r="A138" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B138" s="0">
-        <x:v>116.7</x:v>
+        <x:v>41.58</x:v>
       </x:c>
       <x:c r="C138" s="0">
-        <x:v>-1.9</x:v>
+        <x:v>0.64</x:v>
       </x:c>
       <x:c r="D138" s="0" t="s">
         <x:v>118</x:v>
       </x:c>
       <x:c r="E138" s="0">
-        <x:v>1890000</x:v>
+        <x:v>13500000</x:v>
       </x:c>
       <x:c r="F138" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G138" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H138" s="0">
-        <x:v>1742315226</x:v>
+        <x:v>6483809984</x:v>
       </x:c>
       <x:c r="I138" s="0">
-        <x:v>0.0549</x:v>
+        <x:v>0.09</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:9">
       <x:c r="A139" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="B139" s="0">
+        <x:v>42.14</x:v>
+      </x:c>
+      <x:c r="C139" s="0">
+        <x:v>1.44</x:v>
+      </x:c>
+      <x:c r="D139" s="0" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="B139" s="0">
-        <x:v>13.5</x:v>
-      </x:c>
-      <x:c r="C139" s="0">
-        <x:v>0.02</x:v>
-      </x:c>
-      <x:c r="D139" s="0" t="s">
-        <x:v>118</x:v>
-      </x:c>
       <x:c r="E139" s="0">
-        <x:v>892825</x:v>
+        <x:v>29886357</x:v>
       </x:c>
       <x:c r="F139" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G139" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H139" s="0">
-        <x:v>3015442704</x:v>
+        <x:v>1942491524</x:v>
       </x:c>
       <x:c r="I139" s="0">
-        <x:v>0.0128</x:v>
+        <x:v>0.0154</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:9">
       <x:c r="A140" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B140" s="0">
-        <x:v>55.2</x:v>
+        <x:v>427.25</x:v>
       </x:c>
       <x:c r="C140" s="0">
-        <x:v>5</x:v>
+        <x:v>-4.5</x:v>
       </x:c>
       <x:c r="D140" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E140" s="0">
-        <x:v>361176</x:v>
+        <x:v>171000000</x:v>
       </x:c>
       <x:c r="F140" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G140" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H140" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>130147715000</x:v>
       </x:c>
       <x:c r="I140" s="0">
-        <x:v>0.0063</x:v>
+        <x:v>0.0568</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:9">
       <x:c r="A141" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B141" s="0">
-        <x:v>23.38</x:v>
+        <x:v>118.5</x:v>
       </x:c>
       <x:c r="C141" s="0">
-        <x:v>-0.94</x:v>
+        <x:v>1.8</x:v>
       </x:c>
       <x:c r="D141" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E141" s="0">
-        <x:v>1060000</x:v>
+        <x:v>1890000</x:v>
       </x:c>
       <x:c r="F141" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G141" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H141" s="0">
-        <x:v>1194839266</x:v>
+        <x:v>1742315226</x:v>
       </x:c>
       <x:c r="I141" s="0">
-        <x:v>0.0384</x:v>
+        <x:v>0.0549</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:9">
       <x:c r="A142" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B142" s="0">
-        <x:v>52</x:v>
+        <x:v>13.9</x:v>
       </x:c>
       <x:c r="C142" s="0">
-        <x:v>-0.15</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="D142" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E142" s="0">
-        <x:v>259417800</x:v>
+        <x:v>892825</x:v>
       </x:c>
       <x:c r="F142" s="0" t="s">
         <x:v>11</x:v>
@@ -4899,317 +4902,317 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H142" s="0">
-        <x:v>2741117556</x:v>
+        <x:v>3015442704</x:v>
       </x:c>
       <x:c r="I142" s="0">
-        <x:v>0.0946</x:v>
+        <x:v>0.0128</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:9">
       <x:c r="A143" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B143" s="0">
-        <x:v>64.25</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C143" s="0">
-        <x:v>4</x:v>
+        <x:v>2.8</x:v>
       </x:c>
       <x:c r="D143" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E143" s="0">
-        <x:v>523788</x:v>
+        <x:v>361176</x:v>
       </x:c>
       <x:c r="F143" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G143" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H143" s="0">
-        <x:v>832031190</x:v>
+        <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I143" s="0">
-        <x:v>0.0272</x:v>
+        <x:v>0.0063</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:9">
       <x:c r="A144" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B144" s="0">
-        <x:v>64.25</x:v>
+        <x:v>24.34</x:v>
       </x:c>
       <x:c r="C144" s="0">
-        <x:v>4</x:v>
+        <x:v>0.96</x:v>
       </x:c>
       <x:c r="D144" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E144" s="0">
-        <x:v>1415270</x:v>
+        <x:v>1060000</x:v>
       </x:c>
       <x:c r="F144" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G144" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H144" s="0">
-        <x:v>832031190</x:v>
+        <x:v>1194839266</x:v>
       </x:c>
       <x:c r="I144" s="0">
-        <x:v>0.0736</x:v>
+        <x:v>0.0384</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:9">
       <x:c r="A145" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B145" s="0">
-        <x:v>82.7</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C145" s="0">
-        <x:v>1.65</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D145" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E145" s="0">
-        <x:v>25000000</x:v>
+        <x:v>259417800</x:v>
       </x:c>
       <x:c r="F145" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G145" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H145" s="0">
-        <x:v>20999579110</x:v>
+        <x:v>2741117556</x:v>
       </x:c>
       <x:c r="I145" s="0">
-        <x:v>0.0515</x:v>
+        <x:v>0.0946</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:9">
       <x:c r="A146" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B146" s="0">
-        <x:v>5.91</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C146" s="0">
-        <x:v>0.53</x:v>
+        <x:v>1.75</x:v>
       </x:c>
       <x:c r="D146" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E146" s="0">
-        <x:v>25000</x:v>
+        <x:v>523788</x:v>
       </x:c>
       <x:c r="F146" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G146" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H146" s="0">
-        <x:v>1627872951</x:v>
+        <x:v>832031190</x:v>
       </x:c>
       <x:c r="I146" s="0">
-        <x:v>0.0007</x:v>
+        <x:v>0.0272</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:9">
       <x:c r="A147" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B147" s="0">
-        <x:v>21</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C147" s="0">
-        <x:v>-1.02</x:v>
+        <x:v>1.75</x:v>
       </x:c>
       <x:c r="D147" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E147" s="0">
-        <x:v>1500000</x:v>
+        <x:v>1415270</x:v>
       </x:c>
       <x:c r="F147" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G147" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H147" s="0">
-        <x:v>774677961</x:v>
+        <x:v>832031190</x:v>
       </x:c>
       <x:c r="I147" s="0">
-        <x:v>0.0019</x:v>
+        <x:v>0.0736</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:9">
       <x:c r="A148" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B148" s="0">
-        <x:v>7.88</x:v>
+        <x:v>85.8</x:v>
       </x:c>
       <x:c r="C148" s="0">
-        <x:v>0.25</x:v>
+        <x:v>3.1</x:v>
       </x:c>
       <x:c r="D148" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E148" s="0">
-        <x:v>13833310</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="F148" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G148" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H148" s="0">
-        <x:v>9028523851</x:v>
+        <x:v>20999579110</x:v>
       </x:c>
       <x:c r="I148" s="0">
-        <x:v>0.0776</x:v>
+        <x:v>0.0515</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:9">
       <x:c r="A149" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B149" s="0">
-        <x:v>77.7</x:v>
+        <x:v>6.01</x:v>
       </x:c>
       <x:c r="C149" s="0">
-        <x:v>3.1</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="D149" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E149" s="0">
-        <x:v>3419000</x:v>
+        <x:v>25000</x:v>
       </x:c>
       <x:c r="F149" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G149" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H149" s="0">
-        <x:v>3895315496</x:v>
+        <x:v>1627872951</x:v>
       </x:c>
       <x:c r="I149" s="0">
-        <x:v>0.0379</x:v>
+        <x:v>0.0007</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:9">
       <x:c r="A150" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B150" s="0">
-        <x:v>410.5</x:v>
+        <x:v>20.98</x:v>
       </x:c>
       <x:c r="C150" s="0">
-        <x:v>37.25</x:v>
+        <x:v>-0.02</x:v>
       </x:c>
       <x:c r="D150" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E150" s="0">
-        <x:v>3700000</x:v>
+        <x:v>1500000</x:v>
       </x:c>
       <x:c r="F150" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G150" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H150" s="0">
-        <x:v>1865697176</x:v>
+        <x:v>774677961</x:v>
       </x:c>
       <x:c r="I150" s="0">
-        <x:v>0.0857</x:v>
+        <x:v>0.0019</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:9">
       <x:c r="A151" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B151" s="0">
-        <x:v>40.94</x:v>
+        <x:v>8.36</x:v>
       </x:c>
       <x:c r="C151" s="0">
-        <x:v>-0.28</x:v>
+        <x:v>0.48</x:v>
       </x:c>
       <x:c r="D151" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E151" s="0">
-        <x:v>16000000</x:v>
+        <x:v>13833310</x:v>
       </x:c>
       <x:c r="F151" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G151" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H151" s="0">
-        <x:v>6483809984</x:v>
+        <x:v>9028523851</x:v>
       </x:c>
       <x:c r="I151" s="0">
-        <x:v>0.1067</x:v>
+        <x:v>0.0776</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:9">
       <x:c r="A152" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B152" s="0">
-        <x:v>55.2</x:v>
+        <x:v>80.4</x:v>
       </x:c>
       <x:c r="C152" s="0">
-        <x:v>5</x:v>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="D152" s="0" t="s">
         <x:v>126</x:v>
       </x:c>
       <x:c r="E152" s="0">
-        <x:v>906840</x:v>
+        <x:v>3419000</x:v>
       </x:c>
       <x:c r="F152" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G152" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H152" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>3895315496</x:v>
       </x:c>
       <x:c r="I152" s="0">
-        <x:v>0.0159</x:v>
+        <x:v>0.0379</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:9">
       <x:c r="A153" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B153" s="0">
-        <x:v>3.25</x:v>
+        <x:v>451.5</x:v>
       </x:c>
       <x:c r="C153" s="0">
-        <x:v>-0.01</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D153" s="0" t="s">
         <x:v>126</x:v>
       </x:c>
       <x:c r="E153" s="0">
-        <x:v>895039950</x:v>
+        <x:v>3700000</x:v>
       </x:c>
       <x:c r="F153" s="0" t="s">
         <x:v>11</x:v>
@@ -5218,27 +5221,27 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H153" s="0">
-        <x:v>7382591324</x:v>
+        <x:v>1865697176</x:v>
       </x:c>
       <x:c r="I153" s="0">
-        <x:v>0.1212</x:v>
+        <x:v>0.0857</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:9">
       <x:c r="A154" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B154" s="0">
-        <x:v>52</x:v>
+        <x:v>41.58</x:v>
       </x:c>
       <x:c r="C154" s="0">
-        <x:v>-0.15</x:v>
+        <x:v>0.64</x:v>
       </x:c>
       <x:c r="D154" s="0" t="s">
         <x:v>126</x:v>
       </x:c>
       <x:c r="E154" s="0">
-        <x:v>575933040</x:v>
+        <x:v>16000000</x:v>
       </x:c>
       <x:c r="F154" s="0" t="s">
         <x:v>11</x:v>
@@ -5247,97 +5250,97 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H154" s="0">
-        <x:v>2741117556</x:v>
+        <x:v>6483809984</x:v>
       </x:c>
       <x:c r="I154" s="0">
-        <x:v>0.2101</x:v>
+        <x:v>0.1067</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:9">
       <x:c r="A155" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B155" s="0">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C155" s="0">
+        <x:v>2.8</x:v>
+      </x:c>
+      <x:c r="D155" s="0" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="B155" s="0">
-        <x:v>11.36</x:v>
-      </x:c>
-      <x:c r="C155" s="0">
-        <x:v>-0.98</x:v>
-      </x:c>
-      <x:c r="D155" s="0" t="s">
-        <x:v>126</x:v>
-      </x:c>
       <x:c r="E155" s="0">
-        <x:v>559000</x:v>
+        <x:v>906840</x:v>
       </x:c>
       <x:c r="F155" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G155" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H155" s="0">
-        <x:v>2865374550</x:v>
+        <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I155" s="0">
-        <x:v>0.0084</x:v>
+        <x:v>0.0159</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:9">
       <x:c r="A156" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B156" s="0">
-        <x:v>51.05</x:v>
+        <x:v>3.29</x:v>
       </x:c>
       <x:c r="C156" s="0">
-        <x:v>1.25</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="D156" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="E156" s="0">
-        <x:v>8900056</x:v>
+        <x:v>895039950</x:v>
       </x:c>
       <x:c r="F156" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G156" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H156" s="0">
-        <x:v>16507905000</x:v>
+        <x:v>7382591324</x:v>
       </x:c>
       <x:c r="I156" s="0">
-        <x:v>0.0233</x:v>
+        <x:v>0.1212</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:9">
       <x:c r="A157" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B157" s="0">
-        <x:v>290.25</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C157" s="0">
-        <x:v>6.25</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D157" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="E157" s="0">
-        <x:v>164306000</x:v>
+        <x:v>575933040</x:v>
       </x:c>
       <x:c r="F157" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G157" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H157" s="0">
-        <x:v>24073631758</x:v>
+        <x:v>2741117556</x:v>
       </x:c>
       <x:c r="I157" s="0">
-        <x:v>0.2943</x:v>
+        <x:v>0.2101</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:9">
@@ -5345,45 +5348,45 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="B158" s="0">
-        <x:v>55.7</x:v>
+        <x:v>12.49</x:v>
       </x:c>
       <x:c r="C158" s="0">
-        <x:v>-2.1</x:v>
+        <x:v>1.13</x:v>
       </x:c>
       <x:c r="D158" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="E158" s="0">
-        <x:v>275000</x:v>
+        <x:v>559000</x:v>
       </x:c>
       <x:c r="F158" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G158" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H158" s="0">
-        <x:v>580678850</x:v>
+        <x:v>2865374550</x:v>
       </x:c>
       <x:c r="I158" s="0">
-        <x:v>0.0204</x:v>
+        <x:v>0.0084</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:9">
       <x:c r="A159" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B159" s="0">
-        <x:v>52</x:v>
+        <x:v>54.2</x:v>
       </x:c>
       <x:c r="C159" s="0">
-        <x:v>-0.15</x:v>
+        <x:v>3.15</x:v>
       </x:c>
       <x:c r="D159" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="E159" s="0">
-        <x:v>231651480</x:v>
+        <x:v>8900056</x:v>
       </x:c>
       <x:c r="F159" s="0" t="s">
         <x:v>11</x:v>
@@ -5392,56 +5395,56 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H159" s="0">
-        <x:v>2741117556</x:v>
+        <x:v>16507905000</x:v>
       </x:c>
       <x:c r="I159" s="0">
-        <x:v>0.0845</x:v>
+        <x:v>0.0233</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:9">
       <x:c r="A160" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B160" s="0">
-        <x:v>14.9</x:v>
+        <x:v>295.75</x:v>
       </x:c>
       <x:c r="C160" s="0">
-        <x:v>-0.04</x:v>
+        <x:v>5.5</x:v>
       </x:c>
       <x:c r="D160" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="E160" s="0">
-        <x:v>31860000</x:v>
+        <x:v>164306000</x:v>
       </x:c>
       <x:c r="F160" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G160" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H160" s="0">
-        <x:v>3025063909</x:v>
+        <x:v>24073631758</x:v>
       </x:c>
       <x:c r="I160" s="0">
-        <x:v>0.4539</x:v>
+        <x:v>0.2943</x:v>
       </x:c>
     </x:row>
     <x:row r="161" spans="1:9">
       <x:c r="A161" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B161" s="0">
-        <x:v>98.2</x:v>
+        <x:v>53.25</x:v>
       </x:c>
       <x:c r="C161" s="0">
-        <x:v>3.8</x:v>
+        <x:v>-2.45</x:v>
       </x:c>
       <x:c r="D161" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="E161" s="0">
-        <x:v>41650000</x:v>
+        <x:v>275000</x:v>
       </x:c>
       <x:c r="F161" s="0" t="s">
         <x:v>11</x:v>
@@ -5450,230 +5453,230 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H161" s="0">
-        <x:v>1781510191</x:v>
+        <x:v>580678850</x:v>
       </x:c>
       <x:c r="I161" s="0">
-        <x:v>0.0234</x:v>
+        <x:v>0.0204</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:9">
       <x:c r="A162" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B162" s="0">
-        <x:v>16.53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C162" s="0">
-        <x:v>0.52</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D162" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E162" s="0">
-        <x:v>815000</x:v>
+        <x:v>231651480</x:v>
       </x:c>
       <x:c r="F162" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G162" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H162" s="0">
-        <x:v>2020891371</x:v>
+        <x:v>2741117556</x:v>
       </x:c>
       <x:c r="I162" s="0">
-        <x:v>0.0202</x:v>
+        <x:v>0.0845</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:9">
       <x:c r="A163" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B163" s="0">
-        <x:v>82.35</x:v>
+        <x:v>15.9</x:v>
       </x:c>
       <x:c r="C163" s="0">
-        <x:v>-3.15</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D163" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="E163" s="0">
-        <x:v>8300000</x:v>
+        <x:v>31860000</x:v>
       </x:c>
       <x:c r="F163" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G163" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H163" s="0">
-        <x:v>2941310980</x:v>
+        <x:v>3025063909</x:v>
       </x:c>
       <x:c r="I163" s="0">
-        <x:v>0.1417</x:v>
+        <x:v>0.4539</x:v>
       </x:c>
     </x:row>
     <x:row r="164" spans="1:9">
       <x:c r="A164" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B164" s="0">
-        <x:v>4.08</x:v>
+        <x:v>100.7</x:v>
       </x:c>
       <x:c r="C164" s="0">
-        <x:v>-0.1</x:v>
+        <x:v>2.5</x:v>
       </x:c>
       <x:c r="D164" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="E164" s="0">
-        <x:v>13000000</x:v>
+        <x:v>41650000</x:v>
       </x:c>
       <x:c r="F164" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G164" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H164" s="0">
-        <x:v>1416740879</x:v>
+        <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I164" s="0">
-        <x:v>0.4613</x:v>
+        <x:v>0.0234</x:v>
       </x:c>
     </x:row>
     <x:row r="165" spans="1:9">
       <x:c r="A165" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B165" s="0">
-        <x:v>116.7</x:v>
+        <x:v>17.02</x:v>
       </x:c>
       <x:c r="C165" s="0">
-        <x:v>-1.9</x:v>
+        <x:v>0.49</x:v>
       </x:c>
       <x:c r="D165" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="E165" s="0">
-        <x:v>1999793</x:v>
+        <x:v>815000</x:v>
       </x:c>
       <x:c r="F165" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G165" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H165" s="0">
-        <x:v>1742315226</x:v>
+        <x:v>2020891371</x:v>
       </x:c>
       <x:c r="I165" s="0">
-        <x:v>0.0494</x:v>
+        <x:v>0.0202</x:v>
       </x:c>
     </x:row>
     <x:row r="166" spans="1:9">
       <x:c r="A166" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B166" s="0">
-        <x:v>55.2</x:v>
+        <x:v>81.7</x:v>
       </x:c>
       <x:c r="C166" s="0">
-        <x:v>5</x:v>
+        <x:v>-0.65</x:v>
       </x:c>
       <x:c r="D166" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="E166" s="0">
-        <x:v>1859145</x:v>
+        <x:v>8300000</x:v>
       </x:c>
       <x:c r="F166" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G166" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H166" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>2941310980</x:v>
       </x:c>
       <x:c r="I166" s="0">
-        <x:v>0.0324</x:v>
+        <x:v>0.1417</x:v>
       </x:c>
     </x:row>
     <x:row r="167" spans="1:9">
       <x:c r="A167" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B167" s="0">
-        <x:v>3.25</x:v>
+        <x:v>4.14</x:v>
       </x:c>
       <x:c r="C167" s="0">
-        <x:v>-0.01</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="D167" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="E167" s="0">
-        <x:v>689661000</x:v>
+        <x:v>13000000</x:v>
       </x:c>
       <x:c r="F167" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G167" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H167" s="0">
-        <x:v>7382591324</x:v>
+        <x:v>1416740879</x:v>
       </x:c>
       <x:c r="I167" s="0">
-        <x:v>0.0934</x:v>
+        <x:v>0.4613</x:v>
       </x:c>
     </x:row>
     <x:row r="168" spans="1:9">
       <x:c r="A168" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B168" s="0">
-        <x:v>55.2</x:v>
+        <x:v>118.5</x:v>
       </x:c>
       <x:c r="C168" s="0">
-        <x:v>5</x:v>
+        <x:v>1.8</x:v>
       </x:c>
       <x:c r="D168" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="E168" s="0">
-        <x:v>1902000</x:v>
+        <x:v>1999793</x:v>
       </x:c>
       <x:c r="F168" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G168" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H168" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>1742315226</x:v>
       </x:c>
       <x:c r="I168" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0494</x:v>
       </x:c>
     </x:row>
     <x:row r="169" spans="1:9">
       <x:c r="A169" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B169" s="0">
-        <x:v>98.2</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C169" s="0">
-        <x:v>3.8</x:v>
+        <x:v>2.8</x:v>
       </x:c>
       <x:c r="D169" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="E169" s="0">
-        <x:v>56520000</x:v>
+        <x:v>1859145</x:v>
       </x:c>
       <x:c r="F169" s="0" t="s">
         <x:v>11</x:v>
@@ -5682,65 +5685,65 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H169" s="0">
-        <x:v>1781510191</x:v>
+        <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I169" s="0">
-        <x:v>0.0317</x:v>
+        <x:v>0.0324</x:v>
       </x:c>
     </x:row>
     <x:row r="170" spans="1:9">
       <x:c r="A170" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B170" s="0">
-        <x:v>98.2</x:v>
+        <x:v>3.29</x:v>
       </x:c>
       <x:c r="C170" s="0">
-        <x:v>3.8</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="D170" s="0" t="s">
         <x:v>138</x:v>
       </x:c>
       <x:c r="E170" s="0">
-        <x:v>888325</x:v>
+        <x:v>689661000</x:v>
       </x:c>
       <x:c r="F170" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G170" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H170" s="0">
-        <x:v>1781510191</x:v>
+        <x:v>7382591324</x:v>
       </x:c>
       <x:c r="I170" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0934</x:v>
       </x:c>
     </x:row>
     <x:row r="171" spans="1:9">
       <x:c r="A171" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B171" s="0">
-        <x:v>7.88</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C171" s="0">
-        <x:v>0.25</x:v>
+        <x:v>2.8</x:v>
       </x:c>
       <x:c r="D171" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="E171" s="0">
-        <x:v>5581810</x:v>
+        <x:v>1902000</x:v>
       </x:c>
       <x:c r="F171" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G171" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H171" s="0">
-        <x:v>9028523851</x:v>
+        <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I171" s="0">
         <x:v>0</x:v>
@@ -5748,88 +5751,175 @@
     </x:row>
     <x:row r="172" spans="1:9">
       <x:c r="A172" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B172" s="0">
-        <x:v>55.2</x:v>
+        <x:v>100.7</x:v>
       </x:c>
       <x:c r="C172" s="0">
-        <x:v>5</x:v>
+        <x:v>2.5</x:v>
       </x:c>
       <x:c r="D172" s="0" t="s">
         <x:v>139</x:v>
       </x:c>
       <x:c r="E172" s="0">
-        <x:v>504000000</x:v>
+        <x:v>56520000</x:v>
       </x:c>
       <x:c r="F172" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G172" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H172" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I172" s="0">
-        <x:v>0.2043</x:v>
+        <x:v>0.0317</x:v>
       </x:c>
     </x:row>
     <x:row r="173" spans="1:9">
       <x:c r="A173" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B173" s="0">
-        <x:v>290.25</x:v>
+        <x:v>100.7</x:v>
       </x:c>
       <x:c r="C173" s="0">
-        <x:v>6.25</x:v>
+        <x:v>2.5</x:v>
       </x:c>
       <x:c r="D173" s="0" t="s">
         <x:v>139</x:v>
       </x:c>
       <x:c r="E173" s="0">
-        <x:v>21500032</x:v>
+        <x:v>888325</x:v>
       </x:c>
       <x:c r="F173" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G173" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H173" s="0">
-        <x:v>24073631758</x:v>
+        <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I173" s="0">
-        <x:v>0.0383</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="174" spans="1:9">
       <x:c r="A174" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B174" s="0">
-        <x:v>1200</x:v>
+        <x:v>8.36</x:v>
       </x:c>
       <x:c r="C174" s="0">
-        <x:v>61</x:v>
+        <x:v>0.48</x:v>
       </x:c>
       <x:c r="D174" s="0" t="s">
         <x:v>139</x:v>
       </x:c>
       <x:c r="E174" s="0">
+        <x:v>5581810</x:v>
+      </x:c>
+      <x:c r="F174" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G174" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H174" s="0">
+        <x:v>9028523851</x:v>
+      </x:c>
+      <x:c r="I174" s="0">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175" spans="1:9">
+      <x:c r="A175" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B175" s="0">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C175" s="0">
+        <x:v>2.8</x:v>
+      </x:c>
+      <x:c r="D175" s="0" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="E175" s="0">
+        <x:v>504000000</x:v>
+      </x:c>
+      <x:c r="F175" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G175" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H175" s="0">
+        <x:v>2467243928</x:v>
+      </x:c>
+      <x:c r="I175" s="0">
+        <x:v>0.2043</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176" spans="1:9">
+      <x:c r="A176" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B176" s="0">
+        <x:v>295.75</x:v>
+      </x:c>
+      <x:c r="C176" s="0">
+        <x:v>5.5</x:v>
+      </x:c>
+      <x:c r="D176" s="0" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="E176" s="0">
+        <x:v>21500032</x:v>
+      </x:c>
+      <x:c r="F176" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G176" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H176" s="0">
+        <x:v>24073631758</x:v>
+      </x:c>
+      <x:c r="I176" s="0">
+        <x:v>0.0383</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177" spans="1:9">
+      <x:c r="A177" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B177" s="0">
+        <x:v>1240</x:v>
+      </x:c>
+      <x:c r="C177" s="0">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D177" s="0" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="E177" s="0">
         <x:v>6455151</x:v>
       </x:c>
-      <x:c r="F174" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G174" s="0">
-        <x:v>2025.09</x:v>
-      </x:c>
-      <x:c r="H174" s="0">
+      <x:c r="F177" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G177" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H177" s="0">
         <x:v>1586603352</x:v>
       </x:c>
-      <x:c r="I174" s="0">
+      <x:c r="I177" s="0">
         <x:v>0.1745</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/yeni-is-anlasmalari/data/yeni-is-anlasmalari.xlsx
+++ b/app/borsa/yeni-is-anlasmalari/data/yeni-is-anlasmalari.xlsx
@@ -43,15 +43,21 @@
     <x:t>Yeni İş İlişkisi / Yıllık Satışlar</x:t>
   </x:si>
   <x:si>
+    <x:t>ARDYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-05-06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>USD</x:t>
+  </x:si>
+  <x:si>
     <x:t>CWENE</x:t>
   </x:si>
   <x:si>
     <x:t>2026-05-05</x:t>
   </x:si>
   <x:si>
-    <x:t>USD</x:t>
-  </x:si>
-  <x:si>
     <x:t>ORGE</x:t>
   </x:si>
   <x:si>
@@ -101,9 +107,6 @@
   </x:si>
   <x:si>
     <x:t>2026-04-24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARDYZ</x:t>
   </x:si>
   <x:si>
     <x:t>KLYPV</x:t>
@@ -787,7 +790,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I177"/>
+  <x:dimension ref="A1:I178"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -824,28 +827,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>36.4</x:v>
+        <x:v>58.5</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>32493961</x:v>
+        <x:v>2517084</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>2026.03</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>17386730041</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0269</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -853,28 +856,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>81.7</x:v>
+        <x:v>38.88</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>-0.65</x:v>
+        <x:v>2.48</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>940002</x:v>
+        <x:v>32493961</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2026.03</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>17386730041</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>0.0121</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -882,28 +885,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>118.5</x:v>
+        <x:v>83.6</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>1.8</x:v>
+        <x:v>1.9</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>920000</x:v>
+        <x:v>940002</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G4" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>3150489640</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>0.0154</x:v>
+        <x:v>0.0121</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -911,16 +914,16 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>100.7</x:v>
+        <x:v>124.5</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>2.5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>12100000</x:v>
+        <x:v>920000</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
         <x:v>17</x:v>
@@ -929,10 +932,10 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>0.005</x:v>
+        <x:v>0.0154</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -940,28 +943,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>427.25</x:v>
+        <x:v>100.7</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>-4.5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E6" s="0">
+        <x:v>12100000</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="E6" s="0">
-        <x:v>125100000</x:v>
-      </x:c>
-      <x:c r="F6" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="G6" s="0">
-        <x:v>2026.03</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>184925592000</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>0.0304</x:v>
+        <x:v>0.005</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -969,144 +972,144 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>8.36</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>0.48</x:v>
+        <x:v>6.75</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>32010000</x:v>
+        <x:v>125100000</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2026.03</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>10581001663</x:v>
+        <x:v>184925592000</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>0.1592</x:v>
+        <x:v>0.0304</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
       <x:c r="A8" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B8" s="0">
+        <x:v>8.41</x:v>
+      </x:c>
+      <x:c r="C8" s="0">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B8" s="0">
-        <x:v>29.24</x:v>
-      </x:c>
-      <x:c r="C8" s="0">
-        <x:v>0.32</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
       <x:c r="E8" s="0">
-        <x:v>76650</x:v>
+        <x:v>32010000</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G8" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>7297855153</x:v>
+        <x:v>10581001663</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>0.0005</x:v>
+        <x:v>0.1592</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
       <x:c r="A9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>118.5</x:v>
+        <x:v>28.84</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>1.8</x:v>
+        <x:v>-0.4</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>915000</x:v>
+        <x:v>76650</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G9" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>3150489640</x:v>
+        <x:v>7297855153</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>0.0153</x:v>
+        <x:v>0.0005</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
       <x:c r="A10" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>36.4</x:v>
+        <x:v>124.5</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>0.6</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>2136645</x:v>
+        <x:v>915000</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>2026.03</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>17386730041</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>0.0055</x:v>
+        <x:v>0.0153</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
       <x:c r="A11" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>5.48</x:v>
+        <x:v>38.88</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>0.08</x:v>
+        <x:v>2.48</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>132077304</x:v>
+        <x:v>2136645</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2026.03</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>855070469</x:v>
+        <x:v>17386730041</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>0.1545</x:v>
+        <x:v>0.0055</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -1114,45 +1117,45 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>295.75</x:v>
+        <x:v>5.42</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>5.5</x:v>
+        <x:v>-0.06</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>51531000</x:v>
+        <x:v>132077304</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G12" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>35290767390</x:v>
+        <x:v>855070469</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>0.0656</x:v>
+        <x:v>0.1545</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
       <x:c r="A13" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B13" s="0">
+        <x:v>317.75</x:v>
+      </x:c>
+      <x:c r="C13" s="0">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B13" s="0">
-        <x:v>1240</x:v>
-      </x:c>
-      <x:c r="C13" s="0">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="D13" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
       <x:c r="E13" s="0">
-        <x:v>950978</x:v>
+        <x:v>51531000</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
         <x:v>11</x:v>
@@ -1161,27 +1164,27 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>1883544167</x:v>
+        <x:v>35290767390</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>0.0227</x:v>
+        <x:v>0.0656</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
       <x:c r="A14" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>564</x:v>
+        <x:v>1188</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>-3.5</x:v>
+        <x:v>-52</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>100000000</x:v>
+        <x:v>950978</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
         <x:v>11</x:v>
@@ -1190,39 +1193,39 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>71453576000</x:v>
+        <x:v>1883544167</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>0.0628</x:v>
+        <x:v>0.0227</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
       <x:c r="A15" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>81.7</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>-0.65</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>286071819</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G15" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>71453576000</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>0.0818</x:v>
+        <x:v>0.0628</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -1230,132 +1233,132 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>118.5</x:v>
+        <x:v>83.6</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>1.8</x:v>
+        <x:v>1.9</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>883793</x:v>
+        <x:v>286071819</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G16" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>3150489640</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>0.0148</x:v>
+        <x:v>0.0818</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
       <x:c r="A17" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>58</x:v>
+        <x:v>124.5</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>2.8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>606770</x:v>
+        <x:v>883793</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G17" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>0.0064</x:v>
+        <x:v>0.0148</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
       <x:c r="A18" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B18" s="0">
+        <x:v>58.5</x:v>
+      </x:c>
+      <x:c r="C18" s="0">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="D18" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="B18" s="0">
-        <x:v>57.75</x:v>
-      </x:c>
-      <x:c r="C18" s="0">
-        <x:v>-0.5</x:v>
-      </x:c>
-      <x:c r="D18" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="E18" s="0">
-        <x:v>505597002</x:v>
+        <x:v>606770</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G18" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>8121300519</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>0.0623</x:v>
+        <x:v>0.0064</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
       <x:c r="A19" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>58</x:v>
+        <x:v>58.9</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>2.8</x:v>
+        <x:v>1.15</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>948000</x:v>
+        <x:v>505597002</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G19" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>8121300519</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>0.0101</x:v>
+        <x:v>0.0623</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
       <x:c r="A20" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>100.7</x:v>
+        <x:v>58.5</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>2.5</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>622000</x:v>
+        <x:v>948000</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
         <x:v>11</x:v>
@@ -1364,39 +1367,39 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>0.0114</x:v>
+        <x:v>0.0101</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
       <x:c r="A21" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B21" s="0">
+        <x:v>100.7</x:v>
+      </x:c>
+      <x:c r="C21" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D21" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="B21" s="0">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C21" s="0">
-        <x:v>-0.01</x:v>
-      </x:c>
-      <x:c r="D21" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="E21" s="0">
-        <x:v>983000</x:v>
+        <x:v>622000</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G21" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>2875634546</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>0.018</x:v>
+        <x:v>0.0114</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1404,45 +1407,45 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>80.4</x:v>
+        <x:v>4.05</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>2.7</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>3421818</x:v>
+        <x:v>983000</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G22" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>5948036961</x:v>
+        <x:v>2875634546</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>0.0257</x:v>
+        <x:v>0.018</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
       <x:c r="A23" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B23" s="0">
+        <x:v>81.7</x:v>
+      </x:c>
+      <x:c r="C23" s="0">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="D23" s="0" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="B23" s="0">
-        <x:v>47.18</x:v>
-      </x:c>
-      <x:c r="C23" s="0">
-        <x:v>4.28</x:v>
-      </x:c>
-      <x:c r="D23" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
       <x:c r="E23" s="0">
-        <x:v>697435</x:v>
+        <x:v>3421818</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
         <x:v>11</x:v>
@@ -1451,10 +1454,10 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>4728937463</x:v>
+        <x:v>5948036961</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>0.0066</x:v>
+        <x:v>0.0257</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1462,16 +1465,16 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>66</x:v>
+        <x:v>49.4</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>4.65</x:v>
+        <x:v>2.22</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>4587145</x:v>
+        <x:v>697435</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
         <x:v>11</x:v>
@@ -1480,27 +1483,27 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>16733157490</x:v>
+        <x:v>4728937463</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>0.0123</x:v>
+        <x:v>0.0066</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
       <x:c r="A25" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B25" s="0">
+        <x:v>66.65</x:v>
+      </x:c>
+      <x:c r="C25" s="0">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="D25" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="B25" s="0">
-        <x:v>41.58</x:v>
-      </x:c>
-      <x:c r="C25" s="0">
-        <x:v>0.64</x:v>
-      </x:c>
-      <x:c r="D25" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
       <x:c r="E25" s="0">
-        <x:v>43200000</x:v>
+        <x:v>4587145</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
         <x:v>11</x:v>
@@ -1509,56 +1512,56 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>8236540064</x:v>
+        <x:v>16733157490</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>0.2345</x:v>
+        <x:v>0.0123</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
       <x:c r="A26" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B26" s="0">
+        <x:v>42.9</x:v>
+      </x:c>
+      <x:c r="C26" s="0">
+        <x:v>1.32</x:v>
+      </x:c>
+      <x:c r="D26" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="B26" s="0">
-        <x:v>17.02</x:v>
-      </x:c>
-      <x:c r="C26" s="0">
-        <x:v>0.49</x:v>
-      </x:c>
-      <x:c r="D26" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
       <x:c r="E26" s="0">
-        <x:v>1200000</x:v>
+        <x:v>43200000</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G26" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>3139850323</x:v>
+        <x:v>8236540064</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>0.0201</x:v>
+        <x:v>0.2345</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
       <x:c r="A27" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>57.75</x:v>
+        <x:v>17.75</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>0.73</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>247902522</x:v>
+        <x:v>1200000</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
         <x:v>17</x:v>
@@ -1567,68 +1570,68 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>8121300519</x:v>
+        <x:v>3139850323</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>0.0305</x:v>
+        <x:v>0.0201</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
       <x:c r="A28" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>58</x:v>
+        <x:v>58.9</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>2.8</x:v>
+        <x:v>1.15</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>366000</x:v>
+        <x:v>247902522</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G28" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>8121300519</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>0.0039</x:v>
+        <x:v>0.0305</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
       <x:c r="A29" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B29" s="0">
+        <x:v>58.5</x:v>
+      </x:c>
+      <x:c r="C29" s="0">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="D29" s="0" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="B29" s="0">
-        <x:v>272</x:v>
-      </x:c>
-      <x:c r="C29" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D29" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
       <x:c r="E29" s="0">
-        <x:v>141051834</x:v>
+        <x:v>366000</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G29" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>709077088</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>0.1989</x:v>
+        <x:v>0.0039</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1636,48 +1639,48 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>4.76</x:v>
+        <x:v>274.25</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>0.03</x:v>
+        <x:v>2.25</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>5096500000</x:v>
+        <x:v>141051834</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>19538660616</x:v>
+        <x:v>709077088</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>0.2608</x:v>
+        <x:v>0.1989</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
       <x:c r="A31" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>4.76</x:v>
+        <x:v>5.12</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.36</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E31" s="0">
         <x:v>5096500000</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G31" s="0">
         <x:v>2025.09</x:v>
@@ -1691,48 +1694,48 @@
     </x:row>
     <x:row r="32" spans="1:9">
       <x:c r="A32" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>36.4</x:v>
+        <x:v>5.12</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.36</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>37500000</x:v>
+        <x:v>5096500000</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>16355768622</x:v>
+        <x:v>19538660616</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>0.1024</x:v>
+        <x:v>0.2608</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
       <x:c r="A33" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B33" s="0">
+        <x:v>38.88</x:v>
+      </x:c>
+      <x:c r="C33" s="0">
+        <x:v>2.48</x:v>
+      </x:c>
+      <x:c r="D33" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="B33" s="0">
-        <x:v>241.4</x:v>
-      </x:c>
-      <x:c r="C33" s="0">
-        <x:v>9.3</x:v>
-      </x:c>
-      <x:c r="D33" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
       <x:c r="E33" s="0">
-        <x:v>2030000</x:v>
+        <x:v>37500000</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
         <x:v>11</x:v>
@@ -1741,27 +1744,27 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>2159813703</x:v>
+        <x:v>16355768622</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>0.042</x:v>
+        <x:v>0.1024</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
       <x:c r="A34" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>66</x:v>
+        <x:v>265.5</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>4.65</x:v>
+        <x:v>24.1</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>31146246</x:v>
+        <x:v>2030000</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
         <x:v>11</x:v>
@@ -1770,59 +1773,59 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>16733157490</x:v>
+        <x:v>2159813703</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>0.0832</x:v>
+        <x:v>0.042</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
       <x:c r="A35" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>11.95</x:v>
+        <x:v>66.65</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>0.49</x:v>
+        <x:v>0.65</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>1000000</x:v>
+        <x:v>31146246</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G35" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>7221187888</x:v>
+        <x:v>16733157490</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>0.0001</x:v>
+        <x:v>0.0832</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
       <x:c r="A36" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>11.95</x:v>
+        <x:v>12.06</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>0.49</x:v>
+        <x:v>0.11</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>3150000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G36" s="0">
         <x:v>2025.12</x:v>
@@ -1831,27 +1834,27 @@
         <x:v>7221187888</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>0.0227</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
       <x:c r="A37" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>11.95</x:v>
+        <x:v>12.06</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>0.49</x:v>
+        <x:v>0.11</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>2690000</x:v>
+        <x:v>3150000</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G37" s="0">
         <x:v>2025.12</x:v>
@@ -1860,24 +1863,24 @@
         <x:v>7221187888</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>0.0166</x:v>
+        <x:v>0.0227</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
       <x:c r="A38" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>66</x:v>
+        <x:v>12.06</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>4.65</x:v>
+        <x:v>0.11</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>4103000</x:v>
+        <x:v>2690000</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
         <x:v>11</x:v>
@@ -1886,184 +1889,184 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>16733157490</x:v>
+        <x:v>7221187888</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>0.0109</x:v>
+        <x:v>0.0166</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
       <x:c r="A39" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>118.5</x:v>
+        <x:v>66.65</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>1.8</x:v>
+        <x:v>0.65</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>500000</x:v>
+        <x:v>4103000</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G39" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>3150489640</x:v>
+        <x:v>16733157490</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>0.0083</x:v>
+        <x:v>0.0109</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
       <x:c r="A40" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>58</x:v>
+        <x:v>124.5</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>2.8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>872928</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G40" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>0.0092</x:v>
+        <x:v>0.0083</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
       <x:c r="A41" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>100.7</x:v>
+        <x:v>58.5</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>2.5</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>21250000</x:v>
+        <x:v>872928</x:v>
       </x:c>
       <x:c r="F41" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G41" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>0.0087</x:v>
+        <x:v>0.0092</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
       <x:c r="A42" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>57.75</x:v>
+        <x:v>100.7</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>67690912</x:v>
+        <x:v>21250000</x:v>
       </x:c>
       <x:c r="F42" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G42" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>8121300519</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>0.0083</x:v>
+        <x:v>0.0087</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
       <x:c r="A43" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>36.4</x:v>
+        <x:v>58.9</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>0.6</x:v>
+        <x:v>1.15</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>65458848</x:v>
+        <x:v>67690912</x:v>
       </x:c>
       <x:c r="F43" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G43" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>16355768622</x:v>
+        <x:v>8121300519</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>0.1784</x:v>
+        <x:v>0.0083</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
       <x:c r="A44" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B44" s="0">
+        <x:v>38.88</x:v>
+      </x:c>
+      <x:c r="C44" s="0">
+        <x:v>2.48</x:v>
+      </x:c>
+      <x:c r="D44" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="B44" s="0">
-        <x:v>24.76</x:v>
-      </x:c>
-      <x:c r="C44" s="0">
-        <x:v>0.06</x:v>
-      </x:c>
-      <x:c r="D44" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="E44" s="0">
-        <x:v>689500000</x:v>
+        <x:v>65458848</x:v>
       </x:c>
       <x:c r="F44" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G44" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>884571536</x:v>
+        <x:v>16355768622</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>0.7795</x:v>
+        <x:v>0.1784</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -2071,48 +2074,48 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>6.61</x:v>
+        <x:v>24.68</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>0.53</x:v>
+        <x:v>-0.08</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>3024490</x:v>
+        <x:v>689500000</x:v>
       </x:c>
       <x:c r="F45" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G45" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>2322993973</x:v>
+        <x:v>884571536</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>0.0671</x:v>
+        <x:v>0.7795</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
       <x:c r="A46" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>6.61</x:v>
+        <x:v>7.18</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>0.53</x:v>
+        <x:v>0.57</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>4510336</x:v>
+        <x:v>3024490</x:v>
       </x:c>
       <x:c r="F46" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G46" s="0">
         <x:v>2025.12</x:v>
@@ -2121,7 +2124,7 @@
         <x:v>2322993973</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>0.0865</x:v>
+        <x:v>0.0671</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -2129,16 +2132,16 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>54.2</x:v>
+        <x:v>7.18</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>3.15</x:v>
+        <x:v>0.57</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>205000000</x:v>
+        <x:v>4510336</x:v>
       </x:c>
       <x:c r="F47" s="0" t="s">
         <x:v>11</x:v>
@@ -2147,143 +2150,143 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>20597209000</x:v>
+        <x:v>2322993973</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>0.4434</x:v>
+        <x:v>0.0865</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
       <x:c r="A48" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B48" s="0">
+        <x:v>56.5</x:v>
+      </x:c>
+      <x:c r="C48" s="0">
+        <x:v>2.3</x:v>
+      </x:c>
+      <x:c r="D48" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="B48" s="0">
-        <x:v>317.5</x:v>
-      </x:c>
-      <x:c r="C48" s="0">
-        <x:v>-12.5</x:v>
-      </x:c>
-      <x:c r="D48" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
       <x:c r="E48" s="0">
-        <x:v>305000000</x:v>
+        <x:v>205000000</x:v>
       </x:c>
       <x:c r="F48" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G48" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>400439646</x:v>
+        <x:v>20597209000</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>0.7617</x:v>
+        <x:v>0.4434</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
       <x:c r="A49" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>81.7</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>-0.65</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>11700000</x:v>
+        <x:v>305000000</x:v>
       </x:c>
       <x:c r="F49" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G49" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>400439646</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>0.1718</x:v>
+        <x:v>0.7617</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
       <x:c r="A50" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>241.4</x:v>
+        <x:v>83.6</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>9.3</x:v>
+        <x:v>1.9</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>1900000</x:v>
+        <x:v>11700000</x:v>
       </x:c>
       <x:c r="F50" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G50" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>2159813703</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>0.0391</x:v>
+        <x:v>0.1718</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
       <x:c r="A51" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>4</x:v>
+        <x:v>265.5</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>-0.01</x:v>
+        <x:v>24.1</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>1670000</x:v>
+        <x:v>1900000</x:v>
       </x:c>
       <x:c r="F51" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G51" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>2875634546</x:v>
+        <x:v>2159813703</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>0.0298</x:v>
+        <x:v>0.0391</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
       <x:c r="A52" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>24.76</x:v>
+        <x:v>4.05</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>48895800</x:v>
+        <x:v>1670000</x:v>
       </x:c>
       <x:c r="F52" s="0" t="s">
         <x:v>17</x:v>
@@ -2292,30 +2295,30 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>884571536</x:v>
+        <x:v>2875634546</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>0.0553</x:v>
+        <x:v>0.0298</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:9">
       <x:c r="A53" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B53" s="0">
-        <x:v>24.76</x:v>
+        <x:v>24.68</x:v>
       </x:c>
       <x:c r="C53" s="0">
-        <x:v>0.06</x:v>
+        <x:v>-0.08</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E53" s="0">
-        <x:v>689500000</x:v>
+        <x:v>48895800</x:v>
       </x:c>
       <x:c r="F53" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G53" s="0">
         <x:v>2025.12</x:v>
@@ -2324,36 +2327,36 @@
         <x:v>884571536</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>0.7795</x:v>
+        <x:v>0.0553</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:9">
       <x:c r="A54" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B54" s="0">
+        <x:v>24.68</x:v>
+      </x:c>
+      <x:c r="C54" s="0">
+        <x:v>-0.08</x:v>
+      </x:c>
+      <x:c r="D54" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="B54" s="0">
-        <x:v>45.2</x:v>
-      </x:c>
-      <x:c r="C54" s="0">
-        <x:v>-0.16</x:v>
-      </x:c>
-      <x:c r="D54" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
       <x:c r="E54" s="0">
-        <x:v>3102911</x:v>
+        <x:v>689500000</x:v>
       </x:c>
       <x:c r="F54" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G54" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>2907014564</x:v>
+        <x:v>884571536</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>0.0475</x:v>
+        <x:v>0.7795</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:9">
@@ -2361,103 +2364,103 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B55" s="0">
-        <x:v>24.08</x:v>
+        <x:v>46.08</x:v>
       </x:c>
       <x:c r="C55" s="0">
-        <x:v>0.14</x:v>
+        <x:v>0.88</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E55" s="0">
-        <x:v>13000000</x:v>
+        <x:v>3102911</x:v>
       </x:c>
       <x:c r="F55" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G55" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H55" s="0">
-        <x:v>11834942581</x:v>
+        <x:v>2907014564</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>0.0563</x:v>
+        <x:v>0.0475</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:9">
       <x:c r="A56" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B56" s="0">
-        <x:v>80.4</x:v>
+        <x:v>24.64</x:v>
       </x:c>
       <x:c r="C56" s="0">
-        <x:v>2.7</x:v>
+        <x:v>0.56</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E56" s="0">
-        <x:v>6800000</x:v>
+        <x:v>13000000</x:v>
       </x:c>
       <x:c r="F56" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G56" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H56" s="0">
-        <x:v>5948036961</x:v>
+        <x:v>11834942581</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>0.0583</x:v>
+        <x:v>0.0563</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:9">
       <x:c r="A57" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B57" s="0">
-        <x:v>54.2</x:v>
+        <x:v>81.7</x:v>
       </x:c>
       <x:c r="C57" s="0">
-        <x:v>3.15</x:v>
+        <x:v>1.3</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E57" s="0">
-        <x:v>36750000</x:v>
+        <x:v>6800000</x:v>
       </x:c>
       <x:c r="F57" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G57" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H57" s="0">
-        <x:v>20597209000</x:v>
+        <x:v>5948036961</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>0.0793</x:v>
+        <x:v>0.0583</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:9">
       <x:c r="A58" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B58" s="0">
-        <x:v>1240</x:v>
+        <x:v>56.5</x:v>
       </x:c>
       <x:c r="C58" s="0">
-        <x:v>40</x:v>
+        <x:v>2.3</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E58" s="0">
-        <x:v>3867260</x:v>
+        <x:v>36750000</x:v>
       </x:c>
       <x:c r="F58" s="0" t="s">
         <x:v>11</x:v>
@@ -2466,68 +2469,68 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H58" s="0">
-        <x:v>1883544167</x:v>
+        <x:v>20597209000</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>0.0912</x:v>
+        <x:v>0.0793</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:9">
       <x:c r="A59" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B59" s="0">
+        <x:v>1188</x:v>
+      </x:c>
+      <x:c r="C59" s="0">
+        <x:v>-52</x:v>
+      </x:c>
+      <x:c r="D59" s="0" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="B59" s="0">
-        <x:v>67.45</x:v>
-      </x:c>
-      <x:c r="C59" s="0">
-        <x:v>3.95</x:v>
-      </x:c>
-      <x:c r="D59" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
       <x:c r="E59" s="0">
-        <x:v>1498029716</x:v>
+        <x:v>3867260</x:v>
       </x:c>
       <x:c r="F59" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G59" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H59" s="0">
-        <x:v>12030341104</x:v>
+        <x:v>1883544167</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>0.1245</x:v>
+        <x:v>0.0912</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:9">
       <x:c r="A60" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B60" s="0">
-        <x:v>36.4</x:v>
+        <x:v>67.25</x:v>
       </x:c>
       <x:c r="C60" s="0">
-        <x:v>0.6</x:v>
+        <x:v>-0.2</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E60" s="0">
-        <x:v>48000000</x:v>
+        <x:v>1498029716</x:v>
       </x:c>
       <x:c r="F60" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G60" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H60" s="0">
-        <x:v>16355768622</x:v>
+        <x:v>12030341104</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>0.1301</x:v>
+        <x:v>0.1245</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:9">
@@ -2535,74 +2538,74 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B61" s="0">
-        <x:v>81.7</x:v>
+        <x:v>38.88</x:v>
       </x:c>
       <x:c r="C61" s="0">
-        <x:v>-0.65</x:v>
+        <x:v>2.48</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
         <x:v>65</x:v>
       </x:c>
       <x:c r="E61" s="0">
-        <x:v>279699629</x:v>
+        <x:v>48000000</x:v>
       </x:c>
       <x:c r="F61" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G61" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H61" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>16355768622</x:v>
       </x:c>
       <x:c r="I61" s="0">
-        <x:v>0.08</x:v>
+        <x:v>0.1301</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:9">
       <x:c r="A62" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B62" s="0">
+        <x:v>83.6</x:v>
+      </x:c>
+      <x:c r="C62" s="0">
+        <x:v>1.9</x:v>
+      </x:c>
+      <x:c r="D62" s="0" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="B62" s="0">
-        <x:v>15.9</x:v>
-      </x:c>
-      <x:c r="C62" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D62" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
       <x:c r="E62" s="0">
-        <x:v>7971822</x:v>
+        <x:v>279699629</x:v>
       </x:c>
       <x:c r="F62" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G62" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H62" s="0">
-        <x:v>4675369372</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>0.0756</x:v>
+        <x:v>0.08</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:9">
       <x:c r="A63" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B63" s="0">
-        <x:v>58</x:v>
+        <x:v>15.68</x:v>
       </x:c>
       <x:c r="C63" s="0">
-        <x:v>2.8</x:v>
+        <x:v>-0.22</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E63" s="0">
-        <x:v>1104000</x:v>
+        <x:v>7971822</x:v>
       </x:c>
       <x:c r="F63" s="0" t="s">
         <x:v>11</x:v>
@@ -2611,88 +2614,88 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H63" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>4675369372</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>0.0116</x:v>
+        <x:v>0.0756</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:9">
       <x:c r="A64" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B64" s="0">
-        <x:v>24.76</x:v>
+        <x:v>58.5</x:v>
       </x:c>
       <x:c r="C64" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E64" s="0">
-        <x:v>48895800</x:v>
+        <x:v>1104000</x:v>
       </x:c>
       <x:c r="F64" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G64" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H64" s="0">
-        <x:v>884571536</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>0.0553</x:v>
+        <x:v>0.0116</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:9">
       <x:c r="A65" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B65" s="0">
-        <x:v>3.29</x:v>
+        <x:v>24.68</x:v>
       </x:c>
       <x:c r="C65" s="0">
-        <x:v>0.04</x:v>
+        <x:v>-0.08</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E65" s="0">
-        <x:v>191089413</x:v>
+        <x:v>48895800</x:v>
       </x:c>
       <x:c r="F65" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G65" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H65" s="0">
-        <x:v>9665356715</x:v>
+        <x:v>884571536</x:v>
       </x:c>
       <x:c r="I65" s="0">
-        <x:v>0.0198</x:v>
+        <x:v>0.0553</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:9">
       <x:c r="A66" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B66" s="0">
-        <x:v>3.29</x:v>
+        <x:v>3.47</x:v>
       </x:c>
       <x:c r="C66" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E66" s="0">
-        <x:v>605627160</x:v>
+        <x:v>191089413</x:v>
       </x:c>
       <x:c r="F66" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G66" s="0">
         <x:v>2025.12</x:v>
@@ -2701,7 +2704,7 @@
         <x:v>9665356715</x:v>
       </x:c>
       <x:c r="I66" s="0">
-        <x:v>0.0627</x:v>
+        <x:v>0.0198</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:9">
@@ -2709,77 +2712,77 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B67" s="0">
-        <x:v>27.32</x:v>
+        <x:v>3.47</x:v>
       </x:c>
       <x:c r="C67" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E67" s="0">
-        <x:v>2356546000</x:v>
+        <x:v>605627160</x:v>
       </x:c>
       <x:c r="F67" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G67" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H67" s="0">
-        <x:v>7708004248</x:v>
+        <x:v>9665356715</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>0.3057</x:v>
+        <x:v>0.0627</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:9">
       <x:c r="A68" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B68" s="0">
-        <x:v>17.02</x:v>
+        <x:v>27.2</x:v>
       </x:c>
       <x:c r="C68" s="0">
-        <x:v>0.49</x:v>
+        <x:v>-0.12</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E68" s="0">
-        <x:v>431250</x:v>
+        <x:v>2356546000</x:v>
       </x:c>
       <x:c r="F68" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G68" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H68" s="0">
-        <x:v>3139850323</x:v>
+        <x:v>7708004248</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>0.0071</x:v>
+        <x:v>0.3057</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:9">
       <x:c r="A69" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B69" s="0">
-        <x:v>17.02</x:v>
+        <x:v>17.75</x:v>
       </x:c>
       <x:c r="C69" s="0">
-        <x:v>0.49</x:v>
+        <x:v>0.73</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E69" s="0">
-        <x:v>800000</x:v>
+        <x:v>431250</x:v>
       </x:c>
       <x:c r="F69" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G69" s="0">
         <x:v>2025.12</x:v>
@@ -2788,24 +2791,24 @@
         <x:v>3139850323</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>0.0131</x:v>
+        <x:v>0.0071</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:9">
       <x:c r="A70" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B70" s="0">
-        <x:v>57.75</x:v>
+        <x:v>17.75</x:v>
       </x:c>
       <x:c r="C70" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>0.73</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E70" s="0">
-        <x:v>127172130</x:v>
+        <x:v>800000</x:v>
       </x:c>
       <x:c r="F70" s="0" t="s">
         <x:v>17</x:v>
@@ -2814,56 +2817,56 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H70" s="0">
-        <x:v>8121300519</x:v>
+        <x:v>3139850323</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>0.0157</x:v>
+        <x:v>0.0131</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:9">
       <x:c r="A71" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B71" s="0">
-        <x:v>47.18</x:v>
+        <x:v>58.9</x:v>
       </x:c>
       <x:c r="C71" s="0">
-        <x:v>4.28</x:v>
+        <x:v>1.15</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E71" s="0">
-        <x:v>42625000</x:v>
+        <x:v>127172130</x:v>
       </x:c>
       <x:c r="F71" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G71" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H71" s="0">
-        <x:v>4728937463</x:v>
+        <x:v>8121300519</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>0.3994</x:v>
+        <x:v>0.0157</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:9">
       <x:c r="A72" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B72" s="0">
-        <x:v>100.7</x:v>
+        <x:v>49.4</x:v>
       </x:c>
       <x:c r="C72" s="0">
-        <x:v>2.5</x:v>
+        <x:v>2.22</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
         <x:v>70</x:v>
       </x:c>
       <x:c r="E72" s="0">
-        <x:v>1486000</x:v>
+        <x:v>42625000</x:v>
       </x:c>
       <x:c r="F72" s="0" t="s">
         <x:v>11</x:v>
@@ -2872,27 +2875,27 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H72" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>4728937463</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>0.027</x:v>
+        <x:v>0.3994</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:9">
       <x:c r="A73" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B73" s="0">
-        <x:v>295.75</x:v>
+        <x:v>100.7</x:v>
       </x:c>
       <x:c r="C73" s="0">
-        <x:v>5.5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E73" s="0">
-        <x:v>768864700</x:v>
+        <x:v>1486000</x:v>
       </x:c>
       <x:c r="F73" s="0" t="s">
         <x:v>11</x:v>
@@ -2901,27 +2904,27 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H73" s="0">
-        <x:v>35290767390</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>0.9648</x:v>
+        <x:v>0.027</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:9">
       <x:c r="A74" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B74" s="0">
-        <x:v>66</x:v>
+        <x:v>317.75</x:v>
       </x:c>
       <x:c r="C74" s="0">
-        <x:v>4.65</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E74" s="0">
-        <x:v>15938617</x:v>
+        <x:v>768864700</x:v>
       </x:c>
       <x:c r="F74" s="0" t="s">
         <x:v>11</x:v>
@@ -2930,85 +2933,85 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H74" s="0">
-        <x:v>16733157490</x:v>
+        <x:v>35290767390</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>0.0422</x:v>
+        <x:v>0.9648</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:9">
       <x:c r="A75" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B75" s="0">
+        <x:v>66.65</x:v>
+      </x:c>
+      <x:c r="C75" s="0">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="D75" s="0" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="B75" s="0">
-        <x:v>14.99</x:v>
-      </x:c>
-      <x:c r="C75" s="0">
-        <x:v>0.7</x:v>
-      </x:c>
-      <x:c r="D75" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
       <x:c r="E75" s="0">
-        <x:v>30438120</x:v>
+        <x:v>15938617</x:v>
       </x:c>
       <x:c r="F75" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G75" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H75" s="0">
-        <x:v>3159124121</x:v>
+        <x:v>16733157490</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0422</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:9">
       <x:c r="A76" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B76" s="0">
-        <x:v>241.4</x:v>
+        <x:v>14.85</x:v>
       </x:c>
       <x:c r="C76" s="0">
-        <x:v>9.3</x:v>
+        <x:v>-0.14</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
         <x:v>73</x:v>
       </x:c>
       <x:c r="E76" s="0">
-        <x:v>3900000</x:v>
+        <x:v>30438120</x:v>
       </x:c>
       <x:c r="F76" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G76" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H76" s="0">
-        <x:v>2159813703</x:v>
+        <x:v>3159124121</x:v>
       </x:c>
       <x:c r="I76" s="0">
-        <x:v>0.0797</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:9">
       <x:c r="A77" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B77" s="0">
-        <x:v>241.4</x:v>
+        <x:v>265.5</x:v>
       </x:c>
       <x:c r="C77" s="0">
-        <x:v>9.3</x:v>
+        <x:v>24.1</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E77" s="0">
-        <x:v>2104908</x:v>
+        <x:v>3900000</x:v>
       </x:c>
       <x:c r="F77" s="0" t="s">
         <x:v>11</x:v>
@@ -3020,24 +3023,24 @@
         <x:v>2159813703</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>0.043</x:v>
+        <x:v>0.0797</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:9">
       <x:c r="A78" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B78" s="0">
-        <x:v>29.24</x:v>
+        <x:v>265.5</x:v>
       </x:c>
       <x:c r="C78" s="0">
-        <x:v>0.32</x:v>
+        <x:v>24.1</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E78" s="0">
-        <x:v>3900000</x:v>
+        <x:v>2104908</x:v>
       </x:c>
       <x:c r="F78" s="0" t="s">
         <x:v>11</x:v>
@@ -3046,10 +3049,10 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H78" s="0">
-        <x:v>7297855153</x:v>
+        <x:v>2159813703</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>0.0236</x:v>
+        <x:v>0.043</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:9">
@@ -3057,132 +3060,132 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B79" s="0">
-        <x:v>5.48</x:v>
+        <x:v>28.84</x:v>
       </x:c>
       <x:c r="C79" s="0">
-        <x:v>0.08</x:v>
+        <x:v>-0.4</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
         <x:v>74</x:v>
       </x:c>
       <x:c r="E79" s="0">
-        <x:v>496968445</x:v>
+        <x:v>3900000</x:v>
       </x:c>
       <x:c r="F79" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G79" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H79" s="0">
-        <x:v>855070469</x:v>
+        <x:v>7297855153</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>0.5812</x:v>
+        <x:v>0.0236</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:9">
       <x:c r="A80" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B80" s="0">
+        <x:v>5.42</x:v>
+      </x:c>
+      <x:c r="C80" s="0">
+        <x:v>-0.06</x:v>
+      </x:c>
+      <x:c r="D80" s="0" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="B80" s="0">
-        <x:v>12.31</x:v>
-      </x:c>
-      <x:c r="C80" s="0">
-        <x:v>-0.35</x:v>
-      </x:c>
-      <x:c r="D80" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
       <x:c r="E80" s="0">
-        <x:v>108750000</x:v>
+        <x:v>496968445</x:v>
       </x:c>
       <x:c r="F80" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G80" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H80" s="0">
-        <x:v>1982520183</x:v>
+        <x:v>855070469</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>0.0549</x:v>
+        <x:v>0.5812</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:9">
       <x:c r="A81" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B81" s="0">
-        <x:v>118.5</x:v>
+        <x:v>12.49</x:v>
       </x:c>
       <x:c r="C81" s="0">
-        <x:v>1.8</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E81" s="0">
-        <x:v>1605197</x:v>
+        <x:v>108750000</x:v>
       </x:c>
       <x:c r="F81" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G81" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H81" s="0">
-        <x:v>0</x:v>
+        <x:v>1982520183</x:v>
       </x:c>
       <x:c r="I81" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0549</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:9">
       <x:c r="A82" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B82" s="0">
-        <x:v>427.25</x:v>
+        <x:v>124.5</x:v>
       </x:c>
       <x:c r="C82" s="0">
-        <x:v>-4.5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
         <x:v>77</x:v>
       </x:c>
       <x:c r="E82" s="0">
-        <x:v>54600000</x:v>
+        <x:v>1605197</x:v>
       </x:c>
       <x:c r="F82" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G82" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H82" s="0">
-        <x:v>180444938000</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>0.0133</x:v>
+        <x:v>0.0257</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:9">
       <x:c r="A83" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B83" s="0">
-        <x:v>427.25</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="C83" s="0">
-        <x:v>-4.5</x:v>
+        <x:v>6.75</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E83" s="0">
-        <x:v>111850000</x:v>
+        <x:v>54600000</x:v>
       </x:c>
       <x:c r="F83" s="0" t="s">
         <x:v>11</x:v>
@@ -3194,24 +3197,24 @@
         <x:v>180444938000</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>0.0273</x:v>
+        <x:v>0.0133</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:9">
       <x:c r="A84" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B84" s="0">
-        <x:v>58</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="C84" s="0">
-        <x:v>2.8</x:v>
+        <x:v>6.75</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E84" s="0">
-        <x:v>803090</x:v>
+        <x:v>111850000</x:v>
       </x:c>
       <x:c r="F84" s="0" t="s">
         <x:v>11</x:v>
@@ -3220,143 +3223,143 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H84" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>180444938000</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>0.0084</x:v>
+        <x:v>0.0273</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:9">
       <x:c r="A85" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B85" s="0">
-        <x:v>27.32</x:v>
+        <x:v>58.5</x:v>
       </x:c>
       <x:c r="C85" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E85" s="0">
-        <x:v>2356546000</x:v>
+        <x:v>803090</x:v>
       </x:c>
       <x:c r="F85" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G85" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H85" s="0">
-        <x:v>7708004248</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I85" s="0">
-        <x:v>0.3057</x:v>
+        <x:v>0.0084</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:9">
       <x:c r="A86" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B86" s="0">
-        <x:v>1240</x:v>
+        <x:v>27.2</x:v>
       </x:c>
       <x:c r="C86" s="0">
-        <x:v>40</x:v>
+        <x:v>-0.12</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
         <x:v>79</x:v>
       </x:c>
       <x:c r="E86" s="0">
-        <x:v>875400</x:v>
+        <x:v>2356546000</x:v>
       </x:c>
       <x:c r="F86" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G86" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H86" s="0">
-        <x:v>1883544167</x:v>
+        <x:v>7708004248</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>0.0205</x:v>
+        <x:v>0.3057</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:9">
       <x:c r="A87" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B87" s="0">
+        <x:v>1188</x:v>
+      </x:c>
+      <x:c r="C87" s="0">
+        <x:v>-52</x:v>
+      </x:c>
+      <x:c r="D87" s="0" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="B87" s="0">
-        <x:v>26.82</x:v>
-      </x:c>
-      <x:c r="C87" s="0">
-        <x:v>0.12</x:v>
-      </x:c>
-      <x:c r="D87" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
       <x:c r="E87" s="0">
-        <x:v>330000000</x:v>
+        <x:v>875400</x:v>
       </x:c>
       <x:c r="F87" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G87" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H87" s="0">
-        <x:v>5287314404</x:v>
+        <x:v>1883544167</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>0.0624</x:v>
+        <x:v>0.0205</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:9">
       <x:c r="A88" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B88" s="0">
-        <x:v>81.7</x:v>
+        <x:v>26.72</x:v>
       </x:c>
       <x:c r="C88" s="0">
-        <x:v>-0.65</x:v>
+        <x:v>-0.1</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
         <x:v>82</x:v>
       </x:c>
       <x:c r="E88" s="0">
-        <x:v>11700000</x:v>
+        <x:v>330000000</x:v>
       </x:c>
       <x:c r="F88" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G88" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H88" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>5287314404</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>0.1705</x:v>
+        <x:v>0.0624</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:9">
       <x:c r="A89" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B89" s="0">
-        <x:v>8.36</x:v>
+        <x:v>83.6</x:v>
       </x:c>
       <x:c r="C89" s="0">
-        <x:v>0.48</x:v>
+        <x:v>1.9</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E89" s="0">
-        <x:v>4000000000</x:v>
+        <x:v>11700000</x:v>
       </x:c>
       <x:c r="F89" s="0" t="s">
         <x:v>17</x:v>
@@ -3365,56 +3368,56 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H89" s="0">
-        <x:v>10581001663</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>0.378</x:v>
+        <x:v>0.1705</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:9">
       <x:c r="A90" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B90" s="0">
-        <x:v>17.02</x:v>
+        <x:v>8.41</x:v>
       </x:c>
       <x:c r="C90" s="0">
-        <x:v>0.49</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
         <x:v>83</x:v>
       </x:c>
       <x:c r="E90" s="0">
-        <x:v>1086598</x:v>
+        <x:v>4000000000</x:v>
       </x:c>
       <x:c r="F90" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G90" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H90" s="0">
-        <x:v>2020891371</x:v>
+        <x:v>10581001663</x:v>
       </x:c>
       <x:c r="I90" s="0">
-        <x:v>0.0274</x:v>
+        <x:v>0.378</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:9">
       <x:c r="A91" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B91" s="0">
-        <x:v>15.9</x:v>
+        <x:v>17.75</x:v>
       </x:c>
       <x:c r="C91" s="0">
-        <x:v>1</x:v>
+        <x:v>0.73</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E91" s="0">
-        <x:v>216000000</x:v>
+        <x:v>1086598</x:v>
       </x:c>
       <x:c r="F91" s="0" t="s">
         <x:v>17</x:v>
@@ -3423,114 +3426,114 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H91" s="0">
-        <x:v>3025063909</x:v>
+        <x:v>2020891371</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>0.0714</x:v>
+        <x:v>0.0274</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:9">
       <x:c r="A92" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B92" s="0">
-        <x:v>58</x:v>
+        <x:v>15.68</x:v>
       </x:c>
       <x:c r="C92" s="0">
-        <x:v>2.8</x:v>
+        <x:v>-0.22</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E92" s="0">
-        <x:v>7292916</x:v>
+        <x:v>216000000</x:v>
       </x:c>
       <x:c r="F92" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G92" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H92" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>3025063909</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>0.0758</x:v>
+        <x:v>0.0714</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:9">
       <x:c r="A93" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B93" s="0">
+        <x:v>58.5</x:v>
+      </x:c>
+      <x:c r="C93" s="0">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="D93" s="0" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="B93" s="0">
-        <x:v>29.22</x:v>
-      </x:c>
-      <x:c r="C93" s="0">
-        <x:v>-0.64</x:v>
-      </x:c>
-      <x:c r="D93" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
       <x:c r="E93" s="0">
-        <x:v>250000</x:v>
+        <x:v>7292916</x:v>
       </x:c>
       <x:c r="F93" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G93" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H93" s="0">
-        <x:v>448686813</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>0.0006</x:v>
+        <x:v>0.0758</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:9">
       <x:c r="A94" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B94" s="0">
-        <x:v>66</x:v>
+        <x:v>28.8</x:v>
       </x:c>
       <x:c r="C94" s="0">
-        <x:v>4.65</x:v>
+        <x:v>-0.42</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E94" s="0">
-        <x:v>36900000</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="F94" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G94" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H94" s="0">
-        <x:v>10597063406</x:v>
+        <x:v>448686813</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>0.1527</x:v>
+        <x:v>0.0006</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:9">
       <x:c r="A95" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B95" s="0">
+        <x:v>66.65</x:v>
+      </x:c>
+      <x:c r="C95" s="0">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="D95" s="0" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="B95" s="0">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="C95" s="0">
-        <x:v>1.75</x:v>
-      </x:c>
-      <x:c r="D95" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
       <x:c r="E95" s="0">
-        <x:v>3800000</x:v>
+        <x:v>36900000</x:v>
       </x:c>
       <x:c r="F95" s="0" t="s">
         <x:v>11</x:v>
@@ -3539,56 +3542,56 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H95" s="0">
-        <x:v>832031190</x:v>
+        <x:v>10597063406</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>0.2002</x:v>
+        <x:v>0.1527</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:9">
       <x:c r="A96" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B96" s="0">
-        <x:v>5.48</x:v>
+        <x:v>68.6</x:v>
       </x:c>
       <x:c r="C96" s="0">
-        <x:v>0.08</x:v>
+        <x:v>2.6</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
         <x:v>89</x:v>
       </x:c>
       <x:c r="E96" s="0">
-        <x:v>2100000</x:v>
+        <x:v>3800000</x:v>
       </x:c>
       <x:c r="F96" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G96" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H96" s="0">
-        <x:v>855070469</x:v>
+        <x:v>832031190</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>0.1076</x:v>
+        <x:v>0.2002</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:9">
       <x:c r="A97" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B97" s="0">
-        <x:v>58</x:v>
+        <x:v>5.42</x:v>
       </x:c>
       <x:c r="C97" s="0">
-        <x:v>2.8</x:v>
+        <x:v>-0.06</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E97" s="0">
-        <x:v>22928077</x:v>
+        <x:v>2100000</x:v>
       </x:c>
       <x:c r="F97" s="0" t="s">
         <x:v>11</x:v>
@@ -3597,59 +3600,59 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H97" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>855070469</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>0.2378</x:v>
+        <x:v>0.1076</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:9">
       <x:c r="A98" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B98" s="0">
+        <x:v>58.5</x:v>
+      </x:c>
+      <x:c r="C98" s="0">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="D98" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="B98" s="0">
-        <x:v>29.8</x:v>
-      </x:c>
-      <x:c r="C98" s="0">
-        <x:v>-0.4</x:v>
-      </x:c>
-      <x:c r="D98" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
       <x:c r="E98" s="0">
-        <x:v>547462013</x:v>
+        <x:v>22928077</x:v>
       </x:c>
       <x:c r="F98" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G98" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H98" s="0">
-        <x:v>0</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>0</x:v>
+        <x:v>0.2378</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:9">
       <x:c r="A99" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B99" s="0">
+        <x:v>29.7</x:v>
+      </x:c>
+      <x:c r="C99" s="0">
+        <x:v>-0.1</x:v>
+      </x:c>
+      <x:c r="D99" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="B99" s="0">
-        <x:v>29.8</x:v>
-      </x:c>
-      <x:c r="C99" s="0">
-        <x:v>-0.4</x:v>
-      </x:c>
-      <x:c r="D99" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
       <x:c r="E99" s="0">
-        <x:v>10567948</x:v>
+        <x:v>547462013</x:v>
       </x:c>
       <x:c r="F99" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G99" s="0">
         <x:v>0</x:v>
@@ -3663,77 +3666,77 @@
     </x:row>
     <x:row r="100" spans="1:9">
       <x:c r="A100" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B100" s="0">
-        <x:v>81.7</x:v>
+        <x:v>29.7</x:v>
       </x:c>
       <x:c r="C100" s="0">
-        <x:v>-0.65</x:v>
+        <x:v>-0.1</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E100" s="0">
-        <x:v>8300000</x:v>
+        <x:v>10567948</x:v>
       </x:c>
       <x:c r="F100" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G100" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H100" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>0.1228</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:9">
       <x:c r="A101" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B101" s="0">
-        <x:v>54.2</x:v>
+        <x:v>83.6</x:v>
       </x:c>
       <x:c r="C101" s="0">
-        <x:v>3.15</x:v>
+        <x:v>1.9</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E101" s="0">
-        <x:v>3000000</x:v>
+        <x:v>8300000</x:v>
       </x:c>
       <x:c r="F101" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G101" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H101" s="0">
-        <x:v>20597209000</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>0.0064</x:v>
+        <x:v>0.1228</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:9">
       <x:c r="A102" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B102" s="0">
+        <x:v>56.5</x:v>
+      </x:c>
+      <x:c r="C102" s="0">
+        <x:v>2.3</x:v>
+      </x:c>
+      <x:c r="D102" s="0" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="B102" s="0">
-        <x:v>35.64</x:v>
-      </x:c>
-      <x:c r="C102" s="0">
-        <x:v>-0.3</x:v>
-      </x:c>
-      <x:c r="D102" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="E102" s="0">
-        <x:v>26640000</x:v>
+        <x:v>3000000</x:v>
       </x:c>
       <x:c r="F102" s="0" t="s">
         <x:v>11</x:v>
@@ -3742,10 +3745,10 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H102" s="0">
-        <x:v>3277373640</x:v>
+        <x:v>20597209000</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>0.356</x:v>
+        <x:v>0.0064</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:9">
@@ -3753,193 +3756,193 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B103" s="0">
-        <x:v>6.01</x:v>
+        <x:v>37.08</x:v>
       </x:c>
       <x:c r="C103" s="0">
-        <x:v>0.1</x:v>
+        <x:v>1.44</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E103" s="0">
-        <x:v>13107198</x:v>
+        <x:v>26640000</x:v>
       </x:c>
       <x:c r="F103" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G103" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H103" s="0">
-        <x:v>1627872951</x:v>
+        <x:v>3277373640</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>0.0081</x:v>
+        <x:v>0.356</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:9">
       <x:c r="A104" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B104" s="0">
-        <x:v>81.7</x:v>
+        <x:v>6.13</x:v>
       </x:c>
       <x:c r="C104" s="0">
-        <x:v>-0.65</x:v>
+        <x:v>0.12</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
         <x:v>95</x:v>
       </x:c>
       <x:c r="E104" s="0">
-        <x:v>237500000</x:v>
+        <x:v>13107198</x:v>
       </x:c>
       <x:c r="F104" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G104" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H104" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>1627872951</x:v>
       </x:c>
       <x:c r="I104" s="0">
-        <x:v>0.0679</x:v>
+        <x:v>0.0081</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:9">
       <x:c r="A105" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B105" s="0">
-        <x:v>57.75</x:v>
+        <x:v>83.6</x:v>
       </x:c>
       <x:c r="C105" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>1.9</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
         <x:v>96</x:v>
       </x:c>
       <x:c r="E105" s="0">
-        <x:v>147892538</x:v>
+        <x:v>237500000</x:v>
       </x:c>
       <x:c r="F105" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G105" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H105" s="0">
-        <x:v>7257990064</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I105" s="0">
-        <x:v>0.0204</x:v>
+        <x:v>0.0679</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:9">
       <x:c r="A106" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B106" s="0">
+        <x:v>58.9</x:v>
+      </x:c>
+      <x:c r="C106" s="0">
+        <x:v>1.15</x:v>
+      </x:c>
+      <x:c r="D106" s="0" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="B106" s="0">
-        <x:v>58.8</x:v>
-      </x:c>
-      <x:c r="C106" s="0">
-        <x:v>3.35</x:v>
-      </x:c>
-      <x:c r="D106" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
       <x:c r="E106" s="0">
-        <x:v>988848</x:v>
+        <x:v>147892538</x:v>
       </x:c>
       <x:c r="F106" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G106" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H106" s="0">
-        <x:v>12999679000</x:v>
+        <x:v>7257990064</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>0.0033</x:v>
+        <x:v>0.0204</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:9">
       <x:c r="A107" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B107" s="0">
-        <x:v>66</x:v>
+        <x:v>61.35</x:v>
       </x:c>
       <x:c r="C107" s="0">
-        <x:v>4.65</x:v>
+        <x:v>2.55</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E107" s="0">
-        <x:v>47300000</x:v>
+        <x:v>988848</x:v>
       </x:c>
       <x:c r="F107" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G107" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H107" s="0">
-        <x:v>10597063406</x:v>
+        <x:v>12999679000</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>0.2309</x:v>
+        <x:v>0.0033</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:9">
       <x:c r="A108" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B108" s="0">
-        <x:v>4</x:v>
+        <x:v>66.65</x:v>
       </x:c>
       <x:c r="C108" s="0">
-        <x:v>-0.01</x:v>
+        <x:v>0.65</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E108" s="0">
-        <x:v>758600</x:v>
+        <x:v>47300000</x:v>
       </x:c>
       <x:c r="F108" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G108" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H108" s="0">
-        <x:v>1960468575</x:v>
+        <x:v>10597063406</x:v>
       </x:c>
       <x:c r="I108" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0.2309</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:9">
       <x:c r="A109" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B109" s="0">
-        <x:v>4</x:v>
+        <x:v>4.05</x:v>
       </x:c>
       <x:c r="C109" s="0">
-        <x:v>-0.01</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E109" s="0">
         <x:v>758600</x:v>
       </x:c>
       <x:c r="F109" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G109" s="0">
         <x:v>2025.09</x:v>
@@ -3948,53 +3951,53 @@
         <x:v>1960468575</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>0.0004</x:v>
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:9">
       <x:c r="A110" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B110" s="0">
-        <x:v>1240</x:v>
+        <x:v>4.05</x:v>
       </x:c>
       <x:c r="C110" s="0">
-        <x:v>40</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E110" s="0">
-        <x:v>576665</x:v>
+        <x:v>758600</x:v>
       </x:c>
       <x:c r="F110" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G110" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H110" s="0">
-        <x:v>1586603352</x:v>
+        <x:v>1960468575</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>0.0159</x:v>
+        <x:v>0.0004</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:9">
       <x:c r="A111" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B111" s="0">
-        <x:v>85.8</x:v>
+        <x:v>1188</x:v>
       </x:c>
       <x:c r="C111" s="0">
-        <x:v>3.1</x:v>
+        <x:v>-52</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E111" s="0">
-        <x:v>8000000</x:v>
+        <x:v>576665</x:v>
       </x:c>
       <x:c r="F111" s="0" t="s">
         <x:v>11</x:v>
@@ -4003,27 +4006,27 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H111" s="0">
-        <x:v>20999579110</x:v>
+        <x:v>1586603352</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>0.0166</x:v>
+        <x:v>0.0159</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:9">
       <x:c r="A112" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B112" s="0">
-        <x:v>100.7</x:v>
+        <x:v>85.2</x:v>
       </x:c>
       <x:c r="C112" s="0">
-        <x:v>2.5</x:v>
+        <x:v>-0.6</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E112" s="0">
-        <x:v>850000</x:v>
+        <x:v>8000000</x:v>
       </x:c>
       <x:c r="F112" s="0" t="s">
         <x:v>11</x:v>
@@ -4032,68 +4035,68 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H112" s="0">
-        <x:v>1781510191</x:v>
+        <x:v>20999579110</x:v>
       </x:c>
       <x:c r="I112" s="0">
-        <x:v>0.0208</x:v>
+        <x:v>0.0166</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:9">
       <x:c r="A113" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B113" s="0">
-        <x:v>17.02</x:v>
+        <x:v>100.7</x:v>
       </x:c>
       <x:c r="C113" s="0">
-        <x:v>0.49</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
         <x:v>102</x:v>
       </x:c>
       <x:c r="E113" s="0">
-        <x:v>10149200</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="F113" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G113" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H113" s="0">
-        <x:v>2020891371</x:v>
+        <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I113" s="0">
-        <x:v>0.2601</x:v>
+        <x:v>0.0208</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:9">
       <x:c r="A114" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B114" s="0">
-        <x:v>118.5</x:v>
+        <x:v>17.75</x:v>
       </x:c>
       <x:c r="C114" s="0">
-        <x:v>1.8</x:v>
+        <x:v>0.73</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E114" s="0">
-        <x:v>10500000</x:v>
+        <x:v>10149200</x:v>
       </x:c>
       <x:c r="F114" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G114" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H114" s="0">
-        <x:v>1742315226</x:v>
+        <x:v>2020891371</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>0.3121</x:v>
+        <x:v>0.2601</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:9">
@@ -4101,16 +4104,16 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B115" s="0">
-        <x:v>100.7</x:v>
+        <x:v>124.5</x:v>
       </x:c>
       <x:c r="C115" s="0">
-        <x:v>2.5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
         <x:v>103</x:v>
       </x:c>
       <x:c r="E115" s="0">
-        <x:v>366956541</x:v>
+        <x:v>10500000</x:v>
       </x:c>
       <x:c r="F115" s="0" t="s">
         <x:v>17</x:v>
@@ -4119,88 +4122,88 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H115" s="0">
-        <x:v>1781510191</x:v>
+        <x:v>1742315226</x:v>
       </x:c>
       <x:c r="I115" s="0">
-        <x:v>0.206</x:v>
+        <x:v>0.3121</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:9">
       <x:c r="A116" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B116" s="0">
-        <x:v>57.75</x:v>
+        <x:v>100.7</x:v>
       </x:c>
       <x:c r="C116" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D116" s="0" t="s">
         <x:v>104</x:v>
       </x:c>
       <x:c r="E116" s="0">
-        <x:v>61158155</x:v>
+        <x:v>366956541</x:v>
       </x:c>
       <x:c r="F116" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G116" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H116" s="0">
-        <x:v>7257990064</x:v>
+        <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I116" s="0">
-        <x:v>0.0084</x:v>
+        <x:v>0.206</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:9">
       <x:c r="A117" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B117" s="0">
+        <x:v>58.9</x:v>
+      </x:c>
+      <x:c r="C117" s="0">
+        <x:v>1.15</x:v>
+      </x:c>
+      <x:c r="D117" s="0" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="B117" s="0">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="C117" s="0">
-        <x:v>-1.8</x:v>
-      </x:c>
-      <x:c r="D117" s="0" t="s">
-        <x:v>104</x:v>
-      </x:c>
       <x:c r="E117" s="0">
-        <x:v>1000000</x:v>
+        <x:v>61158155</x:v>
       </x:c>
       <x:c r="F117" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G117" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H117" s="0">
-        <x:v>1688731509</x:v>
+        <x:v>7257990064</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>0.0307</x:v>
+        <x:v>0.0084</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:9">
       <x:c r="A118" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="B118" s="0">
+        <x:v>108.1</x:v>
+      </x:c>
+      <x:c r="C118" s="0">
+        <x:v>-1.9</x:v>
+      </x:c>
+      <x:c r="D118" s="0" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="B118" s="0">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="C118" s="0">
-        <x:v>-1.8</x:v>
-      </x:c>
-      <x:c r="D118" s="0" t="s">
-        <x:v>104</x:v>
-      </x:c>
       <x:c r="E118" s="0">
-        <x:v>1050000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="F118" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G118" s="0">
         <x:v>2025.09</x:v>
@@ -4209,7 +4212,7 @@
         <x:v>1688731509</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>0.0271</x:v>
+        <x:v>0.0307</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:9">
@@ -4217,74 +4220,74 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="B119" s="0">
-        <x:v>42.14</x:v>
+        <x:v>108.1</x:v>
       </x:c>
       <x:c r="C119" s="0">
-        <x:v>1.44</x:v>
+        <x:v>-1.9</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E119" s="0">
-        <x:v>109053804</x:v>
+        <x:v>1050000</x:v>
       </x:c>
       <x:c r="F119" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G119" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H119" s="0">
-        <x:v>1942491524</x:v>
+        <x:v>1688731509</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>0.0561</x:v>
+        <x:v>0.0271</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:9">
       <x:c r="A120" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="B120" s="0">
+        <x:v>42.6</x:v>
+      </x:c>
+      <x:c r="C120" s="0">
+        <x:v>0.46</x:v>
+      </x:c>
+      <x:c r="D120" s="0" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="B120" s="0">
-        <x:v>9.6</x:v>
-      </x:c>
-      <x:c r="C120" s="0">
-        <x:v>-0.21</x:v>
-      </x:c>
-      <x:c r="D120" s="0" t="s">
-        <x:v>107</x:v>
-      </x:c>
       <x:c r="E120" s="0">
-        <x:v>62315119</x:v>
+        <x:v>109053804</x:v>
       </x:c>
       <x:c r="F120" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G120" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H120" s="0">
-        <x:v>12026414029</x:v>
+        <x:v>1942491524</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>0.2257</x:v>
+        <x:v>0.0561</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:9">
       <x:c r="A121" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B121" s="0">
-        <x:v>241.4</x:v>
+        <x:v>9.75</x:v>
       </x:c>
       <x:c r="C121" s="0">
-        <x:v>9.3</x:v>
+        <x:v>0.15</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E121" s="0">
-        <x:v>896400</x:v>
+        <x:v>62315119</x:v>
       </x:c>
       <x:c r="F121" s="0" t="s">
         <x:v>11</x:v>
@@ -4293,27 +4296,27 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H121" s="0">
-        <x:v>1364716456</x:v>
+        <x:v>12026414029</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>0.0285</x:v>
+        <x:v>0.2257</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:9">
       <x:c r="A122" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B122" s="0">
+        <x:v>265.5</x:v>
+      </x:c>
+      <x:c r="C122" s="0">
+        <x:v>24.1</x:v>
+      </x:c>
+      <x:c r="D122" s="0" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="B122" s="0">
-        <x:v>451.5</x:v>
-      </x:c>
-      <x:c r="C122" s="0">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D122" s="0" t="s">
-        <x:v>111</x:v>
-      </x:c>
       <x:c r="E122" s="0">
-        <x:v>3370000</x:v>
+        <x:v>896400</x:v>
       </x:c>
       <x:c r="F122" s="0" t="s">
         <x:v>11</x:v>
@@ -4322,143 +4325,143 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H122" s="0">
-        <x:v>1865697176</x:v>
+        <x:v>1364716456</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>0.0785</x:v>
+        <x:v>0.0285</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:9">
       <x:c r="A123" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B123" s="0">
-        <x:v>54.2</x:v>
+        <x:v>496.5</x:v>
       </x:c>
       <x:c r="C123" s="0">
-        <x:v>3.15</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
         <x:v>112</x:v>
       </x:c>
       <x:c r="E123" s="0">
-        <x:v>750561215</x:v>
+        <x:v>3370000</x:v>
       </x:c>
       <x:c r="F123" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G123" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H123" s="0">
-        <x:v>16507905000</x:v>
+        <x:v>1865697176</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>0.0455</x:v>
+        <x:v>0.0785</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:9">
       <x:c r="A124" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B124" s="0">
-        <x:v>85.8</x:v>
+        <x:v>56.5</x:v>
       </x:c>
       <x:c r="C124" s="0">
-        <x:v>3.1</x:v>
+        <x:v>2.3</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E124" s="0">
-        <x:v>20000000</x:v>
+        <x:v>750561215</x:v>
       </x:c>
       <x:c r="F124" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G124" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H124" s="0">
-        <x:v>20999579110</x:v>
+        <x:v>16507905000</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>0.0413</x:v>
+        <x:v>0.0455</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:9">
       <x:c r="A125" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="B125" s="0">
+        <x:v>85.2</x:v>
+      </x:c>
+      <x:c r="C125" s="0">
+        <x:v>-0.6</x:v>
+      </x:c>
+      <x:c r="D125" s="0" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="B125" s="0">
-        <x:v>33.98</x:v>
-      </x:c>
-      <x:c r="C125" s="0">
-        <x:v>0.84</x:v>
-      </x:c>
-      <x:c r="D125" s="0" t="s">
-        <x:v>114</x:v>
-      </x:c>
       <x:c r="E125" s="0">
-        <x:v>750000000</x:v>
+        <x:v>20000000</x:v>
       </x:c>
       <x:c r="F125" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G125" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H125" s="0">
-        <x:v>0</x:v>
+        <x:v>20999579110</x:v>
       </x:c>
       <x:c r="I125" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0413</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:9">
       <x:c r="A126" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B126" s="0">
-        <x:v>66</x:v>
+        <x:v>33.64</x:v>
       </x:c>
       <x:c r="C126" s="0">
-        <x:v>4.65</x:v>
+        <x:v>-0.34</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E126" s="0">
-        <x:v>111232418</x:v>
+        <x:v>750000000</x:v>
       </x:c>
       <x:c r="F126" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G126" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H126" s="0">
-        <x:v>10597063406</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I126" s="0">
-        <x:v>0.4554</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:9">
       <x:c r="A127" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B127" s="0">
-        <x:v>36.4</x:v>
+        <x:v>66.65</x:v>
       </x:c>
       <x:c r="C127" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.65</x:v>
       </x:c>
       <x:c r="D127" s="0" t="s">
         <x:v>115</x:v>
       </x:c>
       <x:c r="E127" s="0">
-        <x:v>51384996</x:v>
+        <x:v>111232418</x:v>
       </x:c>
       <x:c r="F127" s="0" t="s">
         <x:v>11</x:v>
@@ -4467,27 +4470,27 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H127" s="0">
-        <x:v>11899043692</x:v>
+        <x:v>10597063406</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>0.1873</x:v>
+        <x:v>0.4554</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:9">
       <x:c r="A128" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B128" s="0">
-        <x:v>36.4</x:v>
+        <x:v>38.88</x:v>
       </x:c>
       <x:c r="C128" s="0">
-        <x:v>0.6</x:v>
+        <x:v>2.48</x:v>
       </x:c>
       <x:c r="D128" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E128" s="0">
-        <x:v>3602451</x:v>
+        <x:v>51384996</x:v>
       </x:c>
       <x:c r="F128" s="0" t="s">
         <x:v>11</x:v>
@@ -4499,24 +4502,24 @@
         <x:v>11899043692</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>0.0131</x:v>
+        <x:v>0.1873</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:9">
       <x:c r="A129" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B129" s="0">
-        <x:v>36.4</x:v>
+        <x:v>38.88</x:v>
       </x:c>
       <x:c r="C129" s="0">
-        <x:v>0.6</x:v>
+        <x:v>2.48</x:v>
       </x:c>
       <x:c r="D129" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E129" s="0">
-        <x:v>24226465</x:v>
+        <x:v>3602451</x:v>
       </x:c>
       <x:c r="F129" s="0" t="s">
         <x:v>11</x:v>
@@ -4528,401 +4531,401 @@
         <x:v>11899043692</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>0.0883</x:v>
+        <x:v>0.0131</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:9">
       <x:c r="A130" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B130" s="0">
-        <x:v>58</x:v>
+        <x:v>38.88</x:v>
       </x:c>
       <x:c r="C130" s="0">
-        <x:v>2.8</x:v>
+        <x:v>2.48</x:v>
       </x:c>
       <x:c r="D130" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E130" s="0">
-        <x:v>12900000</x:v>
+        <x:v>24226465</x:v>
       </x:c>
       <x:c r="F130" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G130" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H130" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>11899043692</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>0.0052</x:v>
+        <x:v>0.0883</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:9">
       <x:c r="A131" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B131" s="0">
-        <x:v>295.75</x:v>
+        <x:v>58.5</x:v>
       </x:c>
       <x:c r="C131" s="0">
-        <x:v>5.5</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E131" s="0">
-        <x:v>53250000</x:v>
+        <x:v>12900000</x:v>
       </x:c>
       <x:c r="F131" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G131" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H131" s="0">
-        <x:v>24073631758</x:v>
+        <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I131" s="0">
-        <x:v>0.115</x:v>
+        <x:v>0.0052</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:9">
       <x:c r="A132" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B132" s="0">
-        <x:v>29.8</x:v>
+        <x:v>317.75</x:v>
       </x:c>
       <x:c r="C132" s="0">
-        <x:v>-0.4</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E132" s="0">
-        <x:v>6860140</x:v>
+        <x:v>53250000</x:v>
       </x:c>
       <x:c r="F132" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G132" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H132" s="0">
-        <x:v>0</x:v>
+        <x:v>24073631758</x:v>
       </x:c>
       <x:c r="I132" s="0">
-        <x:v>0</x:v>
+        <x:v>0.115</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:9">
       <x:c r="A133" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B133" s="0">
-        <x:v>81.7</x:v>
+        <x:v>29.7</x:v>
       </x:c>
       <x:c r="C133" s="0">
-        <x:v>-0.65</x:v>
+        <x:v>-0.1</x:v>
       </x:c>
       <x:c r="D133" s="0" t="s">
         <x:v>116</x:v>
       </x:c>
       <x:c r="E133" s="0">
-        <x:v>230000000</x:v>
+        <x:v>6860140</x:v>
       </x:c>
       <x:c r="F133" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G133" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H133" s="0">
-        <x:v>2941310980</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I133" s="0">
-        <x:v>0.0782</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:9">
       <x:c r="A134" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B134" s="0">
-        <x:v>451.5</x:v>
+        <x:v>83.6</x:v>
       </x:c>
       <x:c r="C134" s="0">
-        <x:v>41</x:v>
+        <x:v>1.9</x:v>
       </x:c>
       <x:c r="D134" s="0" t="s">
         <x:v>117</x:v>
       </x:c>
       <x:c r="E134" s="0">
-        <x:v>4700000</x:v>
+        <x:v>230000000</x:v>
       </x:c>
       <x:c r="F134" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G134" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H134" s="0">
-        <x:v>1865697176</x:v>
+        <x:v>2941310980</x:v>
       </x:c>
       <x:c r="I134" s="0">
-        <x:v>0.1092</x:v>
+        <x:v>0.0782</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:9">
       <x:c r="A135" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B135" s="0">
-        <x:v>29.8</x:v>
+        <x:v>496.5</x:v>
       </x:c>
       <x:c r="C135" s="0">
-        <x:v>-0.4</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D135" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E135" s="0">
-        <x:v>256000000</x:v>
+        <x:v>4700000</x:v>
       </x:c>
       <x:c r="F135" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G135" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H135" s="0">
-        <x:v>0</x:v>
+        <x:v>1865697176</x:v>
       </x:c>
       <x:c r="I135" s="0">
-        <x:v>0</x:v>
+        <x:v>0.1092</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:9">
       <x:c r="A136" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B136" s="0">
-        <x:v>36.4</x:v>
+        <x:v>29.7</x:v>
       </x:c>
       <x:c r="C136" s="0">
-        <x:v>0.6</x:v>
+        <x:v>-0.1</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
         <x:v>118</x:v>
       </x:c>
       <x:c r="E136" s="0">
-        <x:v>10724896</x:v>
+        <x:v>256000000</x:v>
       </x:c>
       <x:c r="F136" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G136" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H136" s="0">
-        <x:v>11899043692</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I136" s="0">
-        <x:v>0.039</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:9">
       <x:c r="A137" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B137" s="0">
-        <x:v>24.76</x:v>
+        <x:v>38.88</x:v>
       </x:c>
       <x:c r="C137" s="0">
-        <x:v>0.06</x:v>
+        <x:v>2.48</x:v>
       </x:c>
       <x:c r="D137" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E137" s="0">
-        <x:v>31000000</x:v>
+        <x:v>10724896</x:v>
       </x:c>
       <x:c r="F137" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G137" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H137" s="0">
-        <x:v>813967617</x:v>
+        <x:v>11899043692</x:v>
       </x:c>
       <x:c r="I137" s="0">
-        <x:v>0.0381</x:v>
+        <x:v>0.039</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:9">
       <x:c r="A138" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B138" s="0">
-        <x:v>41.58</x:v>
+        <x:v>24.68</x:v>
       </x:c>
       <x:c r="C138" s="0">
-        <x:v>0.64</x:v>
+        <x:v>-0.08</x:v>
       </x:c>
       <x:c r="D138" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E138" s="0">
-        <x:v>13500000</x:v>
+        <x:v>31000000</x:v>
       </x:c>
       <x:c r="F138" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G138" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H138" s="0">
-        <x:v>6483809984</x:v>
+        <x:v>813967617</x:v>
       </x:c>
       <x:c r="I138" s="0">
-        <x:v>0.09</x:v>
+        <x:v>0.0381</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:9">
       <x:c r="A139" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B139" s="0">
-        <x:v>42.14</x:v>
+        <x:v>42.9</x:v>
       </x:c>
       <x:c r="C139" s="0">
-        <x:v>1.44</x:v>
+        <x:v>1.32</x:v>
       </x:c>
       <x:c r="D139" s="0" t="s">
         <x:v>119</x:v>
       </x:c>
       <x:c r="E139" s="0">
-        <x:v>29886357</x:v>
+        <x:v>13500000</x:v>
       </x:c>
       <x:c r="F139" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G139" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H139" s="0">
-        <x:v>1942491524</x:v>
+        <x:v>6483809984</x:v>
       </x:c>
       <x:c r="I139" s="0">
-        <x:v>0.0154</x:v>
+        <x:v>0.09</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:9">
       <x:c r="A140" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B140" s="0">
-        <x:v>427.25</x:v>
+        <x:v>42.6</x:v>
       </x:c>
       <x:c r="C140" s="0">
-        <x:v>-4.5</x:v>
+        <x:v>0.46</x:v>
       </x:c>
       <x:c r="D140" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E140" s="0">
-        <x:v>171000000</x:v>
+        <x:v>29886357</x:v>
       </x:c>
       <x:c r="F140" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G140" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H140" s="0">
-        <x:v>130147715000</x:v>
+        <x:v>1942491524</x:v>
       </x:c>
       <x:c r="I140" s="0">
-        <x:v>0.0568</x:v>
+        <x:v>0.0154</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:9">
       <x:c r="A141" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B141" s="0">
-        <x:v>118.5</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="C141" s="0">
-        <x:v>1.8</x:v>
+        <x:v>6.75</x:v>
       </x:c>
       <x:c r="D141" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E141" s="0">
-        <x:v>1890000</x:v>
+        <x:v>171000000</x:v>
       </x:c>
       <x:c r="F141" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G141" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H141" s="0">
-        <x:v>1742315226</x:v>
+        <x:v>130147715000</x:v>
       </x:c>
       <x:c r="I141" s="0">
-        <x:v>0.0549</x:v>
+        <x:v>0.0568</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:9">
       <x:c r="A142" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B142" s="0">
+        <x:v>124.5</x:v>
+      </x:c>
+      <x:c r="C142" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D142" s="0" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="B142" s="0">
-        <x:v>13.9</x:v>
-      </x:c>
-      <x:c r="C142" s="0">
-        <x:v>0.4</x:v>
-      </x:c>
-      <x:c r="D142" s="0" t="s">
-        <x:v>119</x:v>
-      </x:c>
       <x:c r="E142" s="0">
-        <x:v>892825</x:v>
+        <x:v>1890000</x:v>
       </x:c>
       <x:c r="F142" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G142" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H142" s="0">
-        <x:v>3015442704</x:v>
+        <x:v>1742315226</x:v>
       </x:c>
       <x:c r="I142" s="0">
-        <x:v>0.0128</x:v>
+        <x:v>0.0549</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:9">
       <x:c r="A143" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B143" s="0">
-        <x:v>58</x:v>
+        <x:v>14.02</x:v>
       </x:c>
       <x:c r="C143" s="0">
-        <x:v>2.8</x:v>
+        <x:v>0.12</x:v>
       </x:c>
       <x:c r="D143" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E143" s="0">
-        <x:v>361176</x:v>
+        <x:v>892825</x:v>
       </x:c>
       <x:c r="F143" s="0" t="s">
         <x:v>11</x:v>
@@ -4931,27 +4934,27 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H143" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>3015442704</x:v>
       </x:c>
       <x:c r="I143" s="0">
-        <x:v>0.0063</x:v>
+        <x:v>0.0128</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:9">
       <x:c r="A144" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B144" s="0">
-        <x:v>24.34</x:v>
+        <x:v>58.5</x:v>
       </x:c>
       <x:c r="C144" s="0">
-        <x:v>0.96</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="D144" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E144" s="0">
-        <x:v>1060000</x:v>
+        <x:v>361176</x:v>
       </x:c>
       <x:c r="F144" s="0" t="s">
         <x:v>11</x:v>
@@ -4960,85 +4963,85 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H144" s="0">
-        <x:v>1194839266</x:v>
+        <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I144" s="0">
-        <x:v>0.0384</x:v>
+        <x:v>0.0063</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:9">
       <x:c r="A145" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="B145" s="0">
+        <x:v>24.92</x:v>
+      </x:c>
+      <x:c r="C145" s="0">
+        <x:v>0.58</x:v>
+      </x:c>
+      <x:c r="D145" s="0" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="B145" s="0">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C145" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D145" s="0" t="s">
-        <x:v>122</x:v>
-      </x:c>
       <x:c r="E145" s="0">
-        <x:v>259417800</x:v>
+        <x:v>1060000</x:v>
       </x:c>
       <x:c r="F145" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G145" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H145" s="0">
-        <x:v>2741117556</x:v>
+        <x:v>1194839266</x:v>
       </x:c>
       <x:c r="I145" s="0">
-        <x:v>0.0946</x:v>
+        <x:v>0.0384</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:9">
       <x:c r="A146" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B146" s="0">
-        <x:v>66</x:v>
+        <x:v>55.7</x:v>
       </x:c>
       <x:c r="C146" s="0">
-        <x:v>1.75</x:v>
+        <x:v>1.7</x:v>
       </x:c>
       <x:c r="D146" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="E146" s="0">
-        <x:v>523788</x:v>
+        <x:v>259417800</x:v>
       </x:c>
       <x:c r="F146" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G146" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H146" s="0">
-        <x:v>832031190</x:v>
+        <x:v>2741117556</x:v>
       </x:c>
       <x:c r="I146" s="0">
-        <x:v>0.0272</x:v>
+        <x:v>0.0946</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:9">
       <x:c r="A147" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B147" s="0">
-        <x:v>66</x:v>
+        <x:v>68.6</x:v>
       </x:c>
       <x:c r="C147" s="0">
-        <x:v>1.75</x:v>
+        <x:v>2.6</x:v>
       </x:c>
       <x:c r="D147" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="E147" s="0">
-        <x:v>1415270</x:v>
+        <x:v>523788</x:v>
       </x:c>
       <x:c r="F147" s="0" t="s">
         <x:v>11</x:v>
@@ -5050,24 +5053,24 @@
         <x:v>832031190</x:v>
       </x:c>
       <x:c r="I147" s="0">
-        <x:v>0.0736</x:v>
+        <x:v>0.0272</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:9">
       <x:c r="A148" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B148" s="0">
-        <x:v>85.8</x:v>
+        <x:v>68.6</x:v>
       </x:c>
       <x:c r="C148" s="0">
-        <x:v>3.1</x:v>
+        <x:v>2.6</x:v>
       </x:c>
       <x:c r="D148" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="E148" s="0">
-        <x:v>25000000</x:v>
+        <x:v>1415270</x:v>
       </x:c>
       <x:c r="F148" s="0" t="s">
         <x:v>11</x:v>
@@ -5076,27 +5079,27 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H148" s="0">
-        <x:v>20999579110</x:v>
+        <x:v>832031190</x:v>
       </x:c>
       <x:c r="I148" s="0">
-        <x:v>0.0515</x:v>
+        <x:v>0.0736</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:9">
       <x:c r="A149" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B149" s="0">
-        <x:v>6.01</x:v>
+        <x:v>85.2</x:v>
       </x:c>
       <x:c r="C149" s="0">
-        <x:v>0.1</x:v>
+        <x:v>-0.6</x:v>
       </x:c>
       <x:c r="D149" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="E149" s="0">
-        <x:v>25000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="F149" s="0" t="s">
         <x:v>11</x:v>
@@ -5105,114 +5108,114 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H149" s="0">
-        <x:v>1627872951</x:v>
+        <x:v>20999579110</x:v>
       </x:c>
       <x:c r="I149" s="0">
-        <x:v>0.0007</x:v>
+        <x:v>0.0515</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:9">
       <x:c r="A150" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B150" s="0">
+        <x:v>6.13</x:v>
+      </x:c>
+      <x:c r="C150" s="0">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="D150" s="0" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="B150" s="0">
-        <x:v>20.98</x:v>
-      </x:c>
-      <x:c r="C150" s="0">
-        <x:v>-0.02</x:v>
-      </x:c>
-      <x:c r="D150" s="0" t="s">
-        <x:v>124</x:v>
-      </x:c>
       <x:c r="E150" s="0">
-        <x:v>1500000</x:v>
+        <x:v>25000</x:v>
       </x:c>
       <x:c r="F150" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G150" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H150" s="0">
-        <x:v>774677961</x:v>
+        <x:v>1627872951</x:v>
       </x:c>
       <x:c r="I150" s="0">
-        <x:v>0.0019</x:v>
+        <x:v>0.0007</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:9">
       <x:c r="A151" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B151" s="0">
-        <x:v>8.36</x:v>
+        <x:v>21.2</x:v>
       </x:c>
       <x:c r="C151" s="0">
-        <x:v>0.48</x:v>
+        <x:v>0.22</x:v>
       </x:c>
       <x:c r="D151" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E151" s="0">
-        <x:v>13833310</x:v>
+        <x:v>1500000</x:v>
       </x:c>
       <x:c r="F151" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G151" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H151" s="0">
-        <x:v>9028523851</x:v>
+        <x:v>774677961</x:v>
       </x:c>
       <x:c r="I151" s="0">
-        <x:v>0.0776</x:v>
+        <x:v>0.0019</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:9">
       <x:c r="A152" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B152" s="0">
-        <x:v>80.4</x:v>
+        <x:v>8.41</x:v>
       </x:c>
       <x:c r="C152" s="0">
-        <x:v>2.7</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D152" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E152" s="0">
-        <x:v>3419000</x:v>
+        <x:v>13833310</x:v>
       </x:c>
       <x:c r="F152" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G152" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H152" s="0">
-        <x:v>3895315496</x:v>
+        <x:v>9028523851</x:v>
       </x:c>
       <x:c r="I152" s="0">
-        <x:v>0.0379</x:v>
+        <x:v>0.0776</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:9">
       <x:c r="A153" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B153" s="0">
-        <x:v>451.5</x:v>
+        <x:v>81.7</x:v>
       </x:c>
       <x:c r="C153" s="0">
-        <x:v>41</x:v>
+        <x:v>1.3</x:v>
       </x:c>
       <x:c r="D153" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="E153" s="0">
-        <x:v>3700000</x:v>
+        <x:v>3419000</x:v>
       </x:c>
       <x:c r="F153" s="0" t="s">
         <x:v>11</x:v>
@@ -5221,27 +5224,27 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H153" s="0">
-        <x:v>1865697176</x:v>
+        <x:v>3895315496</x:v>
       </x:c>
       <x:c r="I153" s="0">
-        <x:v>0.0857</x:v>
+        <x:v>0.0379</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:9">
       <x:c r="A154" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B154" s="0">
-        <x:v>41.58</x:v>
+        <x:v>496.5</x:v>
       </x:c>
       <x:c r="C154" s="0">
-        <x:v>0.64</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D154" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="E154" s="0">
-        <x:v>16000000</x:v>
+        <x:v>3700000</x:v>
       </x:c>
       <x:c r="F154" s="0" t="s">
         <x:v>11</x:v>
@@ -5250,27 +5253,27 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H154" s="0">
-        <x:v>6483809984</x:v>
+        <x:v>1865697176</x:v>
       </x:c>
       <x:c r="I154" s="0">
-        <x:v>0.1067</x:v>
+        <x:v>0.0857</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:9">
       <x:c r="A155" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B155" s="0">
-        <x:v>58</x:v>
+        <x:v>42.9</x:v>
       </x:c>
       <x:c r="C155" s="0">
-        <x:v>2.8</x:v>
+        <x:v>1.32</x:v>
       </x:c>
       <x:c r="D155" s="0" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="E155" s="0">
-        <x:v>906840</x:v>
+        <x:v>16000000</x:v>
       </x:c>
       <x:c r="F155" s="0" t="s">
         <x:v>11</x:v>
@@ -5279,114 +5282,114 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H155" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>6483809984</x:v>
       </x:c>
       <x:c r="I155" s="0">
-        <x:v>0.0159</x:v>
+        <x:v>0.1067</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:9">
       <x:c r="A156" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B156" s="0">
-        <x:v>3.29</x:v>
+        <x:v>58.5</x:v>
       </x:c>
       <x:c r="C156" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="D156" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E156" s="0">
-        <x:v>895039950</x:v>
+        <x:v>906840</x:v>
       </x:c>
       <x:c r="F156" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G156" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H156" s="0">
-        <x:v>7382591324</x:v>
+        <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I156" s="0">
-        <x:v>0.1212</x:v>
+        <x:v>0.0159</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:9">
       <x:c r="A157" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B157" s="0">
-        <x:v>54</x:v>
+        <x:v>3.47</x:v>
       </x:c>
       <x:c r="C157" s="0">
-        <x:v>2</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="D157" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E157" s="0">
-        <x:v>575933040</x:v>
+        <x:v>895039950</x:v>
       </x:c>
       <x:c r="F157" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G157" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H157" s="0">
-        <x:v>2741117556</x:v>
+        <x:v>7382591324</x:v>
       </x:c>
       <x:c r="I157" s="0">
-        <x:v>0.2101</x:v>
+        <x:v>0.1212</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:9">
       <x:c r="A158" s="0" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="B158" s="0">
+        <x:v>55.7</x:v>
+      </x:c>
+      <x:c r="C158" s="0">
+        <x:v>1.7</x:v>
+      </x:c>
+      <x:c r="D158" s="0" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="B158" s="0">
-        <x:v>12.49</x:v>
-      </x:c>
-      <x:c r="C158" s="0">
-        <x:v>1.13</x:v>
-      </x:c>
-      <x:c r="D158" s="0" t="s">
-        <x:v>127</x:v>
-      </x:c>
       <x:c r="E158" s="0">
-        <x:v>559000</x:v>
+        <x:v>575933040</x:v>
       </x:c>
       <x:c r="F158" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G158" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H158" s="0">
-        <x:v>2865374550</x:v>
+        <x:v>2741117556</x:v>
       </x:c>
       <x:c r="I158" s="0">
-        <x:v>0.0084</x:v>
+        <x:v>0.2101</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:9">
       <x:c r="A159" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B159" s="0">
-        <x:v>54.2</x:v>
+        <x:v>12.6</x:v>
       </x:c>
       <x:c r="C159" s="0">
-        <x:v>3.15</x:v>
+        <x:v>0.11</x:v>
       </x:c>
       <x:c r="D159" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E159" s="0">
-        <x:v>8900056</x:v>
+        <x:v>559000</x:v>
       </x:c>
       <x:c r="F159" s="0" t="s">
         <x:v>11</x:v>
@@ -5395,27 +5398,27 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H159" s="0">
-        <x:v>16507905000</x:v>
+        <x:v>2865374550</x:v>
       </x:c>
       <x:c r="I159" s="0">
-        <x:v>0.0233</x:v>
+        <x:v>0.0084</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:9">
       <x:c r="A160" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B160" s="0">
-        <x:v>295.75</x:v>
+        <x:v>56.5</x:v>
       </x:c>
       <x:c r="C160" s="0">
-        <x:v>5.5</x:v>
+        <x:v>2.3</x:v>
       </x:c>
       <x:c r="D160" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E160" s="0">
-        <x:v>164306000</x:v>
+        <x:v>8900056</x:v>
       </x:c>
       <x:c r="F160" s="0" t="s">
         <x:v>11</x:v>
@@ -5424,27 +5427,27 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H160" s="0">
-        <x:v>24073631758</x:v>
+        <x:v>16507905000</x:v>
       </x:c>
       <x:c r="I160" s="0">
-        <x:v>0.2943</x:v>
+        <x:v>0.0233</x:v>
       </x:c>
     </x:row>
     <x:row r="161" spans="1:9">
       <x:c r="A161" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B161" s="0">
-        <x:v>53.25</x:v>
+        <x:v>317.75</x:v>
       </x:c>
       <x:c r="C161" s="0">
-        <x:v>-2.45</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D161" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E161" s="0">
-        <x:v>275000</x:v>
+        <x:v>164306000</x:v>
       </x:c>
       <x:c r="F161" s="0" t="s">
         <x:v>11</x:v>
@@ -5453,230 +5456,230 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H161" s="0">
-        <x:v>580678850</x:v>
+        <x:v>24073631758</x:v>
       </x:c>
       <x:c r="I161" s="0">
-        <x:v>0.0204</x:v>
+        <x:v>0.2943</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:9">
       <x:c r="A162" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B162" s="0">
-        <x:v>54</x:v>
+        <x:v>54.85</x:v>
       </x:c>
       <x:c r="C162" s="0">
-        <x:v>2</x:v>
+        <x:v>1.6</x:v>
       </x:c>
       <x:c r="D162" s="0" t="s">
         <x:v>131</x:v>
       </x:c>
       <x:c r="E162" s="0">
-        <x:v>231651480</x:v>
+        <x:v>275000</x:v>
       </x:c>
       <x:c r="F162" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G162" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H162" s="0">
-        <x:v>2741117556</x:v>
+        <x:v>580678850</x:v>
       </x:c>
       <x:c r="I162" s="0">
-        <x:v>0.0845</x:v>
+        <x:v>0.0204</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:9">
       <x:c r="A163" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B163" s="0">
-        <x:v>15.9</x:v>
+        <x:v>55.7</x:v>
       </x:c>
       <x:c r="C163" s="0">
-        <x:v>1</x:v>
+        <x:v>1.7</x:v>
       </x:c>
       <x:c r="D163" s="0" t="s">
         <x:v>132</x:v>
       </x:c>
       <x:c r="E163" s="0">
-        <x:v>31860000</x:v>
+        <x:v>231651480</x:v>
       </x:c>
       <x:c r="F163" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G163" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H163" s="0">
-        <x:v>3025063909</x:v>
+        <x:v>2741117556</x:v>
       </x:c>
       <x:c r="I163" s="0">
-        <x:v>0.4539</x:v>
+        <x:v>0.0845</x:v>
       </x:c>
     </x:row>
     <x:row r="164" spans="1:9">
       <x:c r="A164" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B164" s="0">
-        <x:v>100.7</x:v>
+        <x:v>15.68</x:v>
       </x:c>
       <x:c r="C164" s="0">
-        <x:v>2.5</x:v>
+        <x:v>-0.22</x:v>
       </x:c>
       <x:c r="D164" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="E164" s="0">
-        <x:v>41650000</x:v>
+        <x:v>31860000</x:v>
       </x:c>
       <x:c r="F164" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G164" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H164" s="0">
-        <x:v>1781510191</x:v>
+        <x:v>3025063909</x:v>
       </x:c>
       <x:c r="I164" s="0">
-        <x:v>0.0234</x:v>
+        <x:v>0.4539</x:v>
       </x:c>
     </x:row>
     <x:row r="165" spans="1:9">
       <x:c r="A165" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B165" s="0">
-        <x:v>17.02</x:v>
+        <x:v>100.7</x:v>
       </x:c>
       <x:c r="C165" s="0">
-        <x:v>0.49</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D165" s="0" t="s">
         <x:v>133</x:v>
       </x:c>
       <x:c r="E165" s="0">
-        <x:v>815000</x:v>
+        <x:v>41650000</x:v>
       </x:c>
       <x:c r="F165" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G165" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H165" s="0">
-        <x:v>2020891371</x:v>
+        <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I165" s="0">
-        <x:v>0.0202</x:v>
+        <x:v>0.0234</x:v>
       </x:c>
     </x:row>
     <x:row r="166" spans="1:9">
       <x:c r="A166" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B166" s="0">
-        <x:v>81.7</x:v>
+        <x:v>17.75</x:v>
       </x:c>
       <x:c r="C166" s="0">
-        <x:v>-0.65</x:v>
+        <x:v>0.73</x:v>
       </x:c>
       <x:c r="D166" s="0" t="s">
         <x:v>134</x:v>
       </x:c>
       <x:c r="E166" s="0">
-        <x:v>8300000</x:v>
+        <x:v>815000</x:v>
       </x:c>
       <x:c r="F166" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G166" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H166" s="0">
-        <x:v>2941310980</x:v>
+        <x:v>2020891371</x:v>
       </x:c>
       <x:c r="I166" s="0">
-        <x:v>0.1417</x:v>
+        <x:v>0.0202</x:v>
       </x:c>
     </x:row>
     <x:row r="167" spans="1:9">
       <x:c r="A167" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B167" s="0">
+        <x:v>83.6</x:v>
+      </x:c>
+      <x:c r="C167" s="0">
+        <x:v>1.9</x:v>
+      </x:c>
+      <x:c r="D167" s="0" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="B167" s="0">
-        <x:v>4.14</x:v>
-      </x:c>
-      <x:c r="C167" s="0">
-        <x:v>0.06</x:v>
-      </x:c>
-      <x:c r="D167" s="0" t="s">
-        <x:v>136</x:v>
-      </x:c>
       <x:c r="E167" s="0">
-        <x:v>13000000</x:v>
+        <x:v>8300000</x:v>
       </x:c>
       <x:c r="F167" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G167" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H167" s="0">
-        <x:v>1416740879</x:v>
+        <x:v>2941310980</x:v>
       </x:c>
       <x:c r="I167" s="0">
-        <x:v>0.4613</x:v>
+        <x:v>0.1417</x:v>
       </x:c>
     </x:row>
     <x:row r="168" spans="1:9">
       <x:c r="A168" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B168" s="0">
-        <x:v>118.5</x:v>
+        <x:v>4.25</x:v>
       </x:c>
       <x:c r="C168" s="0">
-        <x:v>1.8</x:v>
+        <x:v>0.11</x:v>
       </x:c>
       <x:c r="D168" s="0" t="s">
         <x:v>137</x:v>
       </x:c>
       <x:c r="E168" s="0">
-        <x:v>1999793</x:v>
+        <x:v>13000000</x:v>
       </x:c>
       <x:c r="F168" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G168" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H168" s="0">
-        <x:v>1742315226</x:v>
+        <x:v>1416740879</x:v>
       </x:c>
       <x:c r="I168" s="0">
-        <x:v>0.0494</x:v>
+        <x:v>0.4613</x:v>
       </x:c>
     </x:row>
     <x:row r="169" spans="1:9">
       <x:c r="A169" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B169" s="0">
-        <x:v>58</x:v>
+        <x:v>124.5</x:v>
       </x:c>
       <x:c r="C169" s="0">
-        <x:v>2.8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D169" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="E169" s="0">
-        <x:v>1859145</x:v>
+        <x:v>1999793</x:v>
       </x:c>
       <x:c r="F169" s="0" t="s">
         <x:v>11</x:v>
@@ -5685,117 +5688,117 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H169" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>1742315226</x:v>
       </x:c>
       <x:c r="I169" s="0">
-        <x:v>0.0324</x:v>
+        <x:v>0.0494</x:v>
       </x:c>
     </x:row>
     <x:row r="170" spans="1:9">
       <x:c r="A170" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B170" s="0">
-        <x:v>3.29</x:v>
+        <x:v>58.5</x:v>
       </x:c>
       <x:c r="C170" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="D170" s="0" t="s">
         <x:v>138</x:v>
       </x:c>
       <x:c r="E170" s="0">
-        <x:v>689661000</x:v>
+        <x:v>1859145</x:v>
       </x:c>
       <x:c r="F170" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G170" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H170" s="0">
-        <x:v>7382591324</x:v>
+        <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I170" s="0">
-        <x:v>0.0934</x:v>
+        <x:v>0.0324</x:v>
       </x:c>
     </x:row>
     <x:row r="171" spans="1:9">
       <x:c r="A171" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B171" s="0">
-        <x:v>58</x:v>
+        <x:v>3.47</x:v>
       </x:c>
       <x:c r="C171" s="0">
-        <x:v>2.8</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="D171" s="0" t="s">
         <x:v>139</x:v>
       </x:c>
       <x:c r="E171" s="0">
-        <x:v>1902000</x:v>
+        <x:v>689661000</x:v>
       </x:c>
       <x:c r="F171" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G171" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H171" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>7382591324</x:v>
       </x:c>
       <x:c r="I171" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0934</x:v>
       </x:c>
     </x:row>
     <x:row r="172" spans="1:9">
       <x:c r="A172" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B172" s="0">
-        <x:v>100.7</x:v>
+        <x:v>58.5</x:v>
       </x:c>
       <x:c r="C172" s="0">
-        <x:v>2.5</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="D172" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="E172" s="0">
-        <x:v>56520000</x:v>
+        <x:v>1902000</x:v>
       </x:c>
       <x:c r="F172" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G172" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H172" s="0">
-        <x:v>1781510191</x:v>
+        <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I172" s="0">
-        <x:v>0.0317</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="173" spans="1:9">
       <x:c r="A173" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B173" s="0">
         <x:v>100.7</x:v>
       </x:c>
       <x:c r="C173" s="0">
-        <x:v>2.5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D173" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="E173" s="0">
-        <x:v>888325</x:v>
+        <x:v>56520000</x:v>
       </x:c>
       <x:c r="F173" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G173" s="0">
         <x:v>2025.09</x:v>
@@ -5804,24 +5807,24 @@
         <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I173" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0317</x:v>
       </x:c>
     </x:row>
     <x:row r="174" spans="1:9">
       <x:c r="A174" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B174" s="0">
-        <x:v>8.36</x:v>
+        <x:v>100.7</x:v>
       </x:c>
       <x:c r="C174" s="0">
-        <x:v>0.48</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D174" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="E174" s="0">
-        <x:v>5581810</x:v>
+        <x:v>888325</x:v>
       </x:c>
       <x:c r="F174" s="0" t="s">
         <x:v>11</x:v>
@@ -5830,7 +5833,7 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H174" s="0">
-        <x:v>9028523851</x:v>
+        <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I174" s="0">
         <x:v>0</x:v>
@@ -5838,88 +5841,117 @@
     </x:row>
     <x:row r="175" spans="1:9">
       <x:c r="A175" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B175" s="0">
-        <x:v>58</x:v>
+        <x:v>8.41</x:v>
       </x:c>
       <x:c r="C175" s="0">
-        <x:v>2.8</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D175" s="0" t="s">
         <x:v>140</x:v>
       </x:c>
       <x:c r="E175" s="0">
-        <x:v>504000000</x:v>
+        <x:v>5581810</x:v>
       </x:c>
       <x:c r="F175" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G175" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H175" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>9028523851</x:v>
       </x:c>
       <x:c r="I175" s="0">
-        <x:v>0.2043</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="176" spans="1:9">
       <x:c r="A176" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B176" s="0">
-        <x:v>295.75</x:v>
+        <x:v>58.5</x:v>
       </x:c>
       <x:c r="C176" s="0">
-        <x:v>5.5</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="D176" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="E176" s="0">
-        <x:v>21500032</x:v>
+        <x:v>504000000</x:v>
       </x:c>
       <x:c r="F176" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G176" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H176" s="0">
-        <x:v>24073631758</x:v>
+        <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I176" s="0">
-        <x:v>0.0383</x:v>
+        <x:v>0.2043</x:v>
       </x:c>
     </x:row>
     <x:row r="177" spans="1:9">
       <x:c r="A177" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B177" s="0">
-        <x:v>1240</x:v>
+        <x:v>317.75</x:v>
       </x:c>
       <x:c r="C177" s="0">
-        <x:v>40</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D177" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="E177" s="0">
+        <x:v>21500032</x:v>
+      </x:c>
+      <x:c r="F177" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G177" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H177" s="0">
+        <x:v>24073631758</x:v>
+      </x:c>
+      <x:c r="I177" s="0">
+        <x:v>0.0383</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178" spans="1:9">
+      <x:c r="A178" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B178" s="0">
+        <x:v>1188</x:v>
+      </x:c>
+      <x:c r="C178" s="0">
+        <x:v>-52</x:v>
+      </x:c>
+      <x:c r="D178" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="E178" s="0">
         <x:v>6455151</x:v>
       </x:c>
-      <x:c r="F177" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G177" s="0">
-        <x:v>2025.09</x:v>
-      </x:c>
-      <x:c r="H177" s="0">
+      <x:c r="F178" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G178" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H178" s="0">
         <x:v>1586603352</x:v>
       </x:c>
-      <x:c r="I177" s="0">
+      <x:c r="I178" s="0">
         <x:v>0.1745</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/yeni-is-anlasmalari/data/yeni-is-anlasmalari.xlsx
+++ b/app/borsa/yeni-is-anlasmalari/data/yeni-is-anlasmalari.xlsx
@@ -43,13 +43,40 @@
     <x:t>Yeni İş İlişkisi / Yıllık Satışlar</x:t>
   </x:si>
   <x:si>
+    <x:t>FORTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-05-07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>USD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKAG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKHAN</x:t>
+  </x:si>
+  <x:si>
     <x:t>ARDYZ</x:t>
   </x:si>
   <x:si>
     <x:t>2026-05-06</x:t>
   </x:si>
   <x:si>
-    <x:t>USD</x:t>
+    <x:t>VBTYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ONCSM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRY</x:t>
   </x:si>
   <x:si>
     <x:t>CWENE</x:t>
@@ -67,15 +94,6 @@
     <x:t>BVSAN</x:t>
   </x:si>
   <x:si>
-    <x:t>EUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRY</x:t>
-  </x:si>
-  <x:si>
     <x:t>ASELS</x:t>
   </x:si>
   <x:si>
@@ -85,9 +103,6 @@
     <x:t>SMRTG</x:t>
   </x:si>
   <x:si>
-    <x:t>AKHAN</x:t>
-  </x:si>
-  <x:si>
     <x:t>2026-04-29</x:t>
   </x:si>
   <x:si>
@@ -115,9 +130,6 @@
     <x:t>2026-04-22</x:t>
   </x:si>
   <x:si>
-    <x:t>MEKAG</x:t>
-  </x:si>
-  <x:si>
     <x:t>HRKET</x:t>
   </x:si>
   <x:si>
@@ -145,9 +157,6 @@
     <x:t>2026-04-16</x:t>
   </x:si>
   <x:si>
-    <x:t>ONCSM</x:t>
-  </x:si>
-  <x:si>
     <x:t>KAYSE</x:t>
   </x:si>
   <x:si>
@@ -176,9 +185,6 @@
   </x:si>
   <x:si>
     <x:t>CEOEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKOS</x:t>
   </x:si>
   <x:si>
     <x:t>GESAN</x:t>
@@ -790,7 +796,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I178"/>
+  <x:dimension ref="A1:I184"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -827,16 +833,16 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>58.5</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>0.5</x:v>
+        <x:v>-0.7</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>2517084</x:v>
+        <x:v>3384000</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
         <x:v>11</x:v>
@@ -845,10 +851,10 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>0.0269</x:v>
+        <x:v>0.0627</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -856,318 +862,318 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>38.88</x:v>
+        <x:v>4.16</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>2.48</x:v>
+        <x:v>0.11</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>32493961</x:v>
+        <x:v>1178000</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>2026.03</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>17386730041</x:v>
+        <x:v>2875634546</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0185</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
       <x:c r="A4" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B4" s="0">
+        <x:v>7.89</x:v>
+      </x:c>
+      <x:c r="C4" s="0">
+        <x:v>0.71</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E4" s="0">
+        <x:v>1180000</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B4" s="0">
-        <x:v>83.6</x:v>
-      </x:c>
-      <x:c r="C4" s="0">
-        <x:v>1.9</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E4" s="0">
-        <x:v>940002</x:v>
-      </x:c>
-      <x:c r="F4" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="G4" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>2322993973</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>0.0121</x:v>
+        <x:v>0.0268</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
       <x:c r="A5" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>124.5</x:v>
+        <x:v>29.16</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>6</x:v>
+        <x:v>0.32</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>920000</x:v>
+        <x:v>26910</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G5" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>3150489640</x:v>
+        <x:v>7297855153</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>0.0154</x:v>
+        <x:v>0.0002</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
       <x:c r="A6" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>100.7</x:v>
+        <x:v>57.05</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>0</x:v>
+        <x:v>-1.45</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>12100000</x:v>
+        <x:v>2517084</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G6" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>0.005</x:v>
+        <x:v>0.0269</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
       <x:c r="A7" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>434</x:v>
+        <x:v>24.76</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>6.75</x:v>
+        <x:v>2.24</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>125100000</x:v>
+        <x:v>9600000</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>2026.03</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>184925592000</x:v>
+        <x:v>2427624044</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>0.0304</x:v>
+        <x:v>0.1785</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
       <x:c r="A8" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>8.41</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>0.05</x:v>
+        <x:v>8.75</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>32010000</x:v>
+        <x:v>9172451</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G8" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>10581001663</x:v>
+        <x:v>709077088</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>0.1592</x:v>
+        <x:v>0.0129</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
       <x:c r="A9" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>28.84</x:v>
+        <x:v>37.8</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>-0.4</x:v>
+        <x:v>-1.08</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>76650</x:v>
+        <x:v>32493961</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2026.03</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>7297855153</x:v>
+        <x:v>17386730041</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>0.0005</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
       <x:c r="A10" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>124.5</x:v>
+        <x:v>84.2</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>6</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>915000</x:v>
+        <x:v>940002</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G10" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>3150489640</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>0.0153</x:v>
+        <x:v>0.0121</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
       <x:c r="A11" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>38.88</x:v>
+        <x:v>136.9</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>2.48</x:v>
+        <x:v>12.4</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>2136645</x:v>
+        <x:v>920000</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>2026.03</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>17386730041</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>0.0055</x:v>
+        <x:v>0.0154</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
       <x:c r="A12" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>5.42</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>-0.06</x:v>
+        <x:v>-0.7</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>132077304</x:v>
+        <x:v>12100000</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G12" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>855070469</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>0.1545</x:v>
+        <x:v>0.005</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
       <x:c r="A13" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B13" s="0">
+        <x:v>428</x:v>
+      </x:c>
+      <x:c r="C13" s="0">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="B13" s="0">
-        <x:v>317.75</x:v>
-      </x:c>
-      <x:c r="C13" s="0">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D13" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="E13" s="0">
-        <x:v>51531000</x:v>
+        <x:v>125100000</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2026.03</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>35290767390</x:v>
+        <x:v>184925592000</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>0.0656</x:v>
+        <x:v>0.0304</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -1175,45 +1181,45 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>1188</x:v>
+        <x:v>8.8</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>-52</x:v>
+        <x:v>0.39</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>950978</x:v>
+        <x:v>32010000</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G14" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>1883544167</x:v>
+        <x:v>10581001663</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>0.0227</x:v>
+        <x:v>0.1592</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
       <x:c r="A15" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>620</x:v>
+        <x:v>29.16</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>56</x:v>
+        <x:v>0.32</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>100000000</x:v>
+        <x:v>76650</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
         <x:v>11</x:v>
@@ -1222,143 +1228,143 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>71453576000</x:v>
+        <x:v>7297855153</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>0.0628</x:v>
+        <x:v>0.0005</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
       <x:c r="A16" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B16" s="0">
+        <x:v>136.9</x:v>
+      </x:c>
+      <x:c r="C16" s="0">
+        <x:v>12.4</x:v>
+      </x:c>
+      <x:c r="D16" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E16" s="0">
+        <x:v>915000</x:v>
+      </x:c>
+      <x:c r="F16" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B16" s="0">
-        <x:v>83.6</x:v>
-      </x:c>
-      <x:c r="C16" s="0">
-        <x:v>1.9</x:v>
-      </x:c>
-      <x:c r="D16" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E16" s="0">
-        <x:v>286071819</x:v>
-      </x:c>
-      <x:c r="F16" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
       <x:c r="G16" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>0.0818</x:v>
+        <x:v>0.0153</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
       <x:c r="A17" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>124.5</x:v>
+        <x:v>37.8</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>6</x:v>
+        <x:v>-1.08</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>883793</x:v>
+        <x:v>2136645</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2026.03</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>3150489640</x:v>
+        <x:v>17386730041</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>0.0148</x:v>
+        <x:v>0.0055</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
       <x:c r="A18" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>58.5</x:v>
+        <x:v>5.84</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>0.5</x:v>
+        <x:v>0.42</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>606770</x:v>
+        <x:v>132077304</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G18" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>855070469</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>0.0064</x:v>
+        <x:v>0.1545</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
       <x:c r="A19" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B19" s="0">
+        <x:v>320.75</x:v>
+      </x:c>
+      <x:c r="C19" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D19" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="B19" s="0">
-        <x:v>58.9</x:v>
-      </x:c>
-      <x:c r="C19" s="0">
-        <x:v>1.15</x:v>
-      </x:c>
-      <x:c r="D19" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
       <x:c r="E19" s="0">
-        <x:v>505597002</x:v>
+        <x:v>51531000</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G19" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>8121300519</x:v>
+        <x:v>35290767390</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>0.0623</x:v>
+        <x:v>0.0656</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
       <x:c r="A20" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>58.5</x:v>
+        <x:v>1190</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>0.5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>948000</x:v>
+        <x:v>950978</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
         <x:v>11</x:v>
@@ -1367,27 +1373,27 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>1883544167</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>0.0101</x:v>
+        <x:v>0.0227</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
       <x:c r="A21" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>100.7</x:v>
+        <x:v>620.5</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>0</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>622000</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
         <x:v>11</x:v>
@@ -1396,85 +1402,85 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>71453576000</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>0.0114</x:v>
+        <x:v>0.0628</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
       <x:c r="A22" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>4.05</x:v>
+        <x:v>84.2</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>0.05</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>983000</x:v>
+        <x:v>286071819</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G22" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>2875634546</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>0.018</x:v>
+        <x:v>0.0818</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
       <x:c r="A23" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>81.7</x:v>
+        <x:v>136.9</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>1.3</x:v>
+        <x:v>12.4</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
         <x:v>35</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>3421818</x:v>
+        <x:v>883793</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G23" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>5948036961</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>0.0257</x:v>
+        <x:v>0.0148</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
       <x:c r="A24" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>49.4</x:v>
+        <x:v>57.05</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>2.22</x:v>
+        <x:v>-1.45</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
         <x:v>35</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>697435</x:v>
+        <x:v>606770</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
         <x:v>11</x:v>
@@ -1483,56 +1489,56 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>4728937463</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>0.0066</x:v>
+        <x:v>0.0064</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
       <x:c r="A25" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B25" s="0">
+        <x:v>60.5</x:v>
+      </x:c>
+      <x:c r="C25" s="0">
+        <x:v>1.6</x:v>
+      </x:c>
+      <x:c r="D25" s="0" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="B25" s="0">
-        <x:v>66.65</x:v>
-      </x:c>
-      <x:c r="C25" s="0">
-        <x:v>0.65</x:v>
-      </x:c>
-      <x:c r="D25" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
       <x:c r="E25" s="0">
-        <x:v>4587145</x:v>
+        <x:v>505597002</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G25" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>16733157490</x:v>
+        <x:v>8121300519</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>0.0123</x:v>
+        <x:v>0.0623</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
       <x:c r="A26" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>42.9</x:v>
+        <x:v>57.05</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>1.32</x:v>
+        <x:v>-1.45</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>43200000</x:v>
+        <x:v>948000</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
         <x:v>11</x:v>
@@ -1541,85 +1547,85 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>8236540064</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>0.2345</x:v>
+        <x:v>0.0101</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
       <x:c r="A27" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>17.75</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>0.73</x:v>
+        <x:v>-0.7</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>1200000</x:v>
+        <x:v>622000</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G27" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>3139850323</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>0.0201</x:v>
+        <x:v>0.0114</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
       <x:c r="A28" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>58.9</x:v>
+        <x:v>4.16</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>1.15</x:v>
+        <x:v>0.11</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>247902522</x:v>
+        <x:v>983000</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G28" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>8121300519</x:v>
+        <x:v>2875634546</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>0.0305</x:v>
+        <x:v>0.018</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
       <x:c r="A29" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>58.5</x:v>
+        <x:v>80.25</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>0.5</x:v>
+        <x:v>-1.45</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>366000</x:v>
+        <x:v>3421818</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
         <x:v>11</x:v>
@@ -1628,172 +1634,172 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>5948036961</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>0.0039</x:v>
+        <x:v>0.0257</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
       <x:c r="A30" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>274.25</x:v>
+        <x:v>48.8</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>2.25</x:v>
+        <x:v>-0.6</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>141051834</x:v>
+        <x:v>697435</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G30" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>709077088</x:v>
+        <x:v>4728937463</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>0.1989</x:v>
+        <x:v>0.0066</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
       <x:c r="A31" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>5.12</x:v>
+        <x:v>73.3</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>0.36</x:v>
+        <x:v>6.65</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>5096500000</x:v>
+        <x:v>4587145</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>19538660616</x:v>
+        <x:v>16733157490</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>0.2608</x:v>
+        <x:v>0.0123</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
       <x:c r="A32" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B32" s="0">
+        <x:v>43.74</x:v>
+      </x:c>
+      <x:c r="C32" s="0">
+        <x:v>0.84</x:v>
+      </x:c>
+      <x:c r="D32" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="B32" s="0">
-        <x:v>5.12</x:v>
-      </x:c>
-      <x:c r="C32" s="0">
-        <x:v>0.36</x:v>
-      </x:c>
-      <x:c r="D32" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="E32" s="0">
-        <x:v>5096500000</x:v>
+        <x:v>43200000</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>19538660616</x:v>
+        <x:v>8236540064</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>0.2608</x:v>
+        <x:v>0.2345</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
       <x:c r="A33" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>38.88</x:v>
+        <x:v>17.71</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>2.48</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>37500000</x:v>
+        <x:v>1200000</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G33" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>16355768622</x:v>
+        <x:v>3139850323</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>0.1024</x:v>
+        <x:v>0.0201</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
       <x:c r="A34" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B34" s="0">
+        <x:v>60.5</x:v>
+      </x:c>
+      <x:c r="C34" s="0">
+        <x:v>1.6</x:v>
+      </x:c>
+      <x:c r="D34" s="0" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="B34" s="0">
-        <x:v>265.5</x:v>
-      </x:c>
-      <x:c r="C34" s="0">
-        <x:v>24.1</x:v>
-      </x:c>
-      <x:c r="D34" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
       <x:c r="E34" s="0">
-        <x:v>2030000</x:v>
+        <x:v>247902522</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G34" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>2159813703</x:v>
+        <x:v>8121300519</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>0.042</x:v>
+        <x:v>0.0305</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
       <x:c r="A35" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>66.65</x:v>
+        <x:v>57.05</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>0.65</x:v>
+        <x:v>-1.45</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>31146246</x:v>
+        <x:v>366000</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
         <x:v>11</x:v>
@@ -1802,39 +1808,39 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>16733157490</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>0.0832</x:v>
+        <x:v>0.0039</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
       <x:c r="A36" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>12.06</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>0.11</x:v>
+        <x:v>8.75</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>1000000</x:v>
+        <x:v>141051834</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G36" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>7221187888</x:v>
+        <x:v>709077088</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>0.0001</x:v>
+        <x:v>0.1989</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1842,28 +1848,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>12.06</x:v>
+        <x:v>4.99</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>0.11</x:v>
+        <x:v>-0.13</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>3150000</x:v>
+        <x:v>5096500000</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>7221187888</x:v>
+        <x:v>19538660616</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>0.0227</x:v>
+        <x:v>0.2608</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1871,45 +1877,45 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>12.06</x:v>
+        <x:v>4.99</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>0.11</x:v>
+        <x:v>-0.13</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>2690000</x:v>
+        <x:v>5096500000</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>7221187888</x:v>
+        <x:v>19538660616</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>0.0166</x:v>
+        <x:v>0.2608</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
       <x:c r="A39" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>66.65</x:v>
+        <x:v>37.8</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>0.65</x:v>
+        <x:v>-1.08</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>4103000</x:v>
+        <x:v>37500000</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
         <x:v>11</x:v>
@@ -1918,56 +1924,56 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>16733157490</x:v>
+        <x:v>16355768622</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>0.0109</x:v>
+        <x:v>0.1024</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
       <x:c r="A40" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>124.5</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>6</x:v>
+        <x:v>-0.5</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>500000</x:v>
+        <x:v>2030000</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G40" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>3150489640</x:v>
+        <x:v>2159813703</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>0.0083</x:v>
+        <x:v>0.042</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
       <x:c r="A41" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>58.5</x:v>
+        <x:v>73.3</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>0.5</x:v>
+        <x:v>6.65</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>872928</x:v>
+        <x:v>31146246</x:v>
       </x:c>
       <x:c r="F41" s="0" t="s">
         <x:v>11</x:v>
@@ -1976,85 +1982,85 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>16733157490</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>0.0092</x:v>
+        <x:v>0.0832</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
       <x:c r="A42" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>100.7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>0</x:v>
+        <x:v>0.94</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>21250000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="F42" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G42" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>7221187888</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>0.0087</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
       <x:c r="A43" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>58.9</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>1.15</x:v>
+        <x:v>0.94</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>67690912</x:v>
+        <x:v>3150000</x:v>
       </x:c>
       <x:c r="F43" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G43" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>8121300519</x:v>
+        <x:v>7221187888</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>0.0083</x:v>
+        <x:v>0.0227</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
       <x:c r="A44" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>38.88</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>2.48</x:v>
+        <x:v>0.94</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>65458848</x:v>
+        <x:v>2690000</x:v>
       </x:c>
       <x:c r="F44" s="0" t="s">
         <x:v>11</x:v>
@@ -2063,85 +2069,85 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>16355768622</x:v>
+        <x:v>7221187888</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>0.1784</x:v>
+        <x:v>0.0166</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
       <x:c r="A45" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>24.68</x:v>
+        <x:v>73.3</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>-0.08</x:v>
+        <x:v>6.65</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>689500000</x:v>
+        <x:v>4103000</x:v>
       </x:c>
       <x:c r="F45" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G45" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>884571536</x:v>
+        <x:v>16733157490</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>0.7795</x:v>
+        <x:v>0.0109</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
       <x:c r="A46" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>7.18</x:v>
+        <x:v>136.9</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>0.57</x:v>
+        <x:v>12.4</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>3024490</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="F46" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G46" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>2322993973</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>0.0671</x:v>
+        <x:v>0.0083</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
       <x:c r="A47" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>7.18</x:v>
+        <x:v>57.05</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>0.57</x:v>
+        <x:v>-1.45</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>4510336</x:v>
+        <x:v>872928</x:v>
       </x:c>
       <x:c r="F47" s="0" t="s">
         <x:v>11</x:v>
@@ -2150,404 +2156,404 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>2322993973</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>0.0865</x:v>
+        <x:v>0.0092</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
       <x:c r="A48" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>56.5</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>2.3</x:v>
+        <x:v>-0.7</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>205000000</x:v>
+        <x:v>21250000</x:v>
       </x:c>
       <x:c r="F48" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G48" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>20597209000</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>0.4434</x:v>
+        <x:v>0.0087</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
       <x:c r="A49" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>318</x:v>
+        <x:v>60.5</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>0.5</x:v>
+        <x:v>1.6</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>305000000</x:v>
+        <x:v>67690912</x:v>
       </x:c>
       <x:c r="F49" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G49" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>400439646</x:v>
+        <x:v>8121300519</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>0.7617</x:v>
+        <x:v>0.0083</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
       <x:c r="A50" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>83.6</x:v>
+        <x:v>37.8</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>1.9</x:v>
+        <x:v>-1.08</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>11700000</x:v>
+        <x:v>65458848</x:v>
       </x:c>
       <x:c r="F50" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G50" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>16355768622</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>0.1718</x:v>
+        <x:v>0.1784</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
       <x:c r="A51" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>265.5</x:v>
+        <x:v>24.84</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>24.1</x:v>
+        <x:v>0.16</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>1900000</x:v>
+        <x:v>689500000</x:v>
       </x:c>
       <x:c r="F51" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G51" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>2159813703</x:v>
+        <x:v>884571536</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>0.0391</x:v>
+        <x:v>0.7795</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
       <x:c r="A52" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>4.05</x:v>
+        <x:v>7.89</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>0.05</x:v>
+        <x:v>0.71</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>1670000</x:v>
+        <x:v>3024490</x:v>
       </x:c>
       <x:c r="F52" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G52" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>2875634546</x:v>
+        <x:v>2322993973</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>0.0298</x:v>
+        <x:v>0.0671</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:9">
       <x:c r="A53" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B53" s="0">
-        <x:v>24.68</x:v>
+        <x:v>7.89</x:v>
       </x:c>
       <x:c r="C53" s="0">
-        <x:v>-0.08</x:v>
+        <x:v>0.71</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E53" s="0">
-        <x:v>48895800</x:v>
+        <x:v>4510336</x:v>
       </x:c>
       <x:c r="F53" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G53" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H53" s="0">
-        <x:v>884571536</x:v>
+        <x:v>2322993973</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>0.0553</x:v>
+        <x:v>0.0865</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:9">
       <x:c r="A54" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B54" s="0">
-        <x:v>24.68</x:v>
+        <x:v>58.4</x:v>
       </x:c>
       <x:c r="C54" s="0">
-        <x:v>-0.08</x:v>
+        <x:v>1.9</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E54" s="0">
-        <x:v>689500000</x:v>
+        <x:v>205000000</x:v>
       </x:c>
       <x:c r="F54" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G54" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>884571536</x:v>
+        <x:v>20597209000</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>0.7795</x:v>
+        <x:v>0.4434</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:9">
       <x:c r="A55" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B55" s="0">
-        <x:v>46.08</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="C55" s="0">
-        <x:v>0.88</x:v>
+        <x:v>-12</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E55" s="0">
-        <x:v>3102911</x:v>
+        <x:v>305000000</x:v>
       </x:c>
       <x:c r="F55" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G55" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H55" s="0">
-        <x:v>2907014564</x:v>
+        <x:v>400439646</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>0.0475</x:v>
+        <x:v>0.7617</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:9">
       <x:c r="A56" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B56" s="0">
-        <x:v>24.64</x:v>
+        <x:v>84.2</x:v>
       </x:c>
       <x:c r="C56" s="0">
-        <x:v>0.56</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E56" s="0">
-        <x:v>13000000</x:v>
+        <x:v>11700000</x:v>
       </x:c>
       <x:c r="F56" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G56" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H56" s="0">
-        <x:v>11834942581</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>0.0563</x:v>
+        <x:v>0.1718</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:9">
       <x:c r="A57" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B57" s="0">
-        <x:v>81.7</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="C57" s="0">
-        <x:v>1.3</x:v>
+        <x:v>-0.5</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E57" s="0">
-        <x:v>6800000</x:v>
+        <x:v>1900000</x:v>
       </x:c>
       <x:c r="F57" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G57" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H57" s="0">
-        <x:v>5948036961</x:v>
+        <x:v>2159813703</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>0.0583</x:v>
+        <x:v>0.0391</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:9">
       <x:c r="A58" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B58" s="0">
-        <x:v>56.5</x:v>
+        <x:v>4.16</x:v>
       </x:c>
       <x:c r="C58" s="0">
-        <x:v>2.3</x:v>
+        <x:v>0.11</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E58" s="0">
-        <x:v>36750000</x:v>
+        <x:v>1670000</x:v>
       </x:c>
       <x:c r="F58" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G58" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H58" s="0">
-        <x:v>20597209000</x:v>
+        <x:v>2875634546</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>0.0793</x:v>
+        <x:v>0.0298</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:9">
       <x:c r="A59" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B59" s="0">
-        <x:v>1188</x:v>
+        <x:v>24.84</x:v>
       </x:c>
       <x:c r="C59" s="0">
-        <x:v>-52</x:v>
+        <x:v>0.16</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E59" s="0">
-        <x:v>3867260</x:v>
+        <x:v>48895800</x:v>
       </x:c>
       <x:c r="F59" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G59" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H59" s="0">
-        <x:v>1883544167</x:v>
+        <x:v>884571536</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>0.0912</x:v>
+        <x:v>0.0553</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:9">
       <x:c r="A60" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B60" s="0">
-        <x:v>67.25</x:v>
+        <x:v>24.84</x:v>
       </x:c>
       <x:c r="C60" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>0.16</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E60" s="0">
-        <x:v>1498029716</x:v>
+        <x:v>689500000</x:v>
       </x:c>
       <x:c r="F60" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G60" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H60" s="0">
-        <x:v>12030341104</x:v>
+        <x:v>884571536</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>0.1245</x:v>
+        <x:v>0.7795</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:9">
       <x:c r="A61" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B61" s="0">
-        <x:v>38.88</x:v>
+        <x:v>48.8</x:v>
       </x:c>
       <x:c r="C61" s="0">
-        <x:v>2.48</x:v>
+        <x:v>2.72</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E61" s="0">
-        <x:v>48000000</x:v>
+        <x:v>3102911</x:v>
       </x:c>
       <x:c r="F61" s="0" t="s">
         <x:v>11</x:v>
@@ -2556,85 +2562,85 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H61" s="0">
-        <x:v>16355768622</x:v>
+        <x:v>2907014564</x:v>
       </x:c>
       <x:c r="I61" s="0">
-        <x:v>0.1301</x:v>
+        <x:v>0.0475</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:9">
       <x:c r="A62" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B62" s="0">
+        <x:v>25.94</x:v>
+      </x:c>
+      <x:c r="C62" s="0">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="D62" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E62" s="0">
+        <x:v>13000000</x:v>
+      </x:c>
+      <x:c r="F62" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B62" s="0">
-        <x:v>83.6</x:v>
-      </x:c>
-      <x:c r="C62" s="0">
-        <x:v>1.9</x:v>
-      </x:c>
-      <x:c r="D62" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E62" s="0">
-        <x:v>279699629</x:v>
-      </x:c>
-      <x:c r="F62" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
       <x:c r="G62" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H62" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>11834942581</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>0.08</x:v>
+        <x:v>0.0563</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:9">
       <x:c r="A63" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B63" s="0">
-        <x:v>15.68</x:v>
+        <x:v>80.25</x:v>
       </x:c>
       <x:c r="C63" s="0">
-        <x:v>-0.22</x:v>
+        <x:v>-1.45</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E63" s="0">
-        <x:v>7971822</x:v>
+        <x:v>6800000</x:v>
       </x:c>
       <x:c r="F63" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G63" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H63" s="0">
-        <x:v>4675369372</x:v>
+        <x:v>5948036961</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>0.0756</x:v>
+        <x:v>0.0583</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:9">
       <x:c r="A64" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B64" s="0">
-        <x:v>58.5</x:v>
+        <x:v>58.4</x:v>
       </x:c>
       <x:c r="C64" s="0">
-        <x:v>0.5</x:v>
+        <x:v>1.9</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E64" s="0">
-        <x:v>1104000</x:v>
+        <x:v>36750000</x:v>
       </x:c>
       <x:c r="F64" s="0" t="s">
         <x:v>11</x:v>
@@ -2643,404 +2649,404 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H64" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>20597209000</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>0.0116</x:v>
+        <x:v>0.0793</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:9">
       <x:c r="A65" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B65" s="0">
-        <x:v>24.68</x:v>
+        <x:v>1190</x:v>
       </x:c>
       <x:c r="C65" s="0">
-        <x:v>-0.08</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E65" s="0">
-        <x:v>48895800</x:v>
+        <x:v>3867260</x:v>
       </x:c>
       <x:c r="F65" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G65" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H65" s="0">
-        <x:v>884571536</x:v>
+        <x:v>1883544167</x:v>
       </x:c>
       <x:c r="I65" s="0">
-        <x:v>0.0553</x:v>
+        <x:v>0.0912</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:9">
       <x:c r="A66" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B66" s="0">
-        <x:v>3.47</x:v>
+        <x:v>68.75</x:v>
       </x:c>
       <x:c r="C66" s="0">
-        <x:v>0.18</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E66" s="0">
-        <x:v>191089413</x:v>
+        <x:v>1498029716</x:v>
       </x:c>
       <x:c r="F66" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G66" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H66" s="0">
-        <x:v>9665356715</x:v>
+        <x:v>12030341104</x:v>
       </x:c>
       <x:c r="I66" s="0">
-        <x:v>0.0198</x:v>
+        <x:v>0.1245</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:9">
       <x:c r="A67" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B67" s="0">
-        <x:v>3.47</x:v>
+        <x:v>37.8</x:v>
       </x:c>
       <x:c r="C67" s="0">
-        <x:v>0.18</x:v>
+        <x:v>-1.08</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E67" s="0">
-        <x:v>605627160</x:v>
+        <x:v>48000000</x:v>
       </x:c>
       <x:c r="F67" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G67" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H67" s="0">
-        <x:v>9665356715</x:v>
+        <x:v>16355768622</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>0.0627</x:v>
+        <x:v>0.1301</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:9">
       <x:c r="A68" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B68" s="0">
-        <x:v>27.2</x:v>
+        <x:v>84.2</x:v>
       </x:c>
       <x:c r="C68" s="0">
-        <x:v>-0.12</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E68" s="0">
-        <x:v>2356546000</x:v>
+        <x:v>279699629</x:v>
       </x:c>
       <x:c r="F68" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G68" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H68" s="0">
-        <x:v>7708004248</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>0.3057</x:v>
+        <x:v>0.08</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:9">
       <x:c r="A69" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B69" s="0">
-        <x:v>17.75</x:v>
+        <x:v>16.44</x:v>
       </x:c>
       <x:c r="C69" s="0">
-        <x:v>0.73</x:v>
+        <x:v>0.76</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E69" s="0">
-        <x:v>431250</x:v>
+        <x:v>7971822</x:v>
       </x:c>
       <x:c r="F69" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G69" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H69" s="0">
-        <x:v>3139850323</x:v>
+        <x:v>4675369372</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>0.0071</x:v>
+        <x:v>0.0756</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:9">
       <x:c r="A70" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B70" s="0">
-        <x:v>17.75</x:v>
+        <x:v>57.05</x:v>
       </x:c>
       <x:c r="C70" s="0">
-        <x:v>0.73</x:v>
+        <x:v>-1.45</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E70" s="0">
-        <x:v>800000</x:v>
+        <x:v>1104000</x:v>
       </x:c>
       <x:c r="F70" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G70" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H70" s="0">
-        <x:v>3139850323</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>0.0131</x:v>
+        <x:v>0.0116</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:9">
       <x:c r="A71" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B71" s="0">
-        <x:v>58.9</x:v>
+        <x:v>24.84</x:v>
       </x:c>
       <x:c r="C71" s="0">
-        <x:v>1.15</x:v>
+        <x:v>0.16</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E71" s="0">
-        <x:v>127172130</x:v>
+        <x:v>48895800</x:v>
       </x:c>
       <x:c r="F71" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G71" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H71" s="0">
-        <x:v>8121300519</x:v>
+        <x:v>884571536</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>0.0157</x:v>
+        <x:v>0.0553</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:9">
       <x:c r="A72" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B72" s="0">
-        <x:v>49.4</x:v>
+        <x:v>3.46</x:v>
       </x:c>
       <x:c r="C72" s="0">
-        <x:v>2.22</x:v>
+        <x:v>-0.01</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E72" s="0">
-        <x:v>42625000</x:v>
+        <x:v>191089413</x:v>
       </x:c>
       <x:c r="F72" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G72" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H72" s="0">
-        <x:v>4728937463</x:v>
+        <x:v>9665356715</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>0.3994</x:v>
+        <x:v>0.0198</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:9">
       <x:c r="A73" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B73" s="0">
-        <x:v>100.7</x:v>
+        <x:v>3.46</x:v>
       </x:c>
       <x:c r="C73" s="0">
-        <x:v>0</x:v>
+        <x:v>-0.01</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E73" s="0">
-        <x:v>1486000</x:v>
+        <x:v>605627160</x:v>
       </x:c>
       <x:c r="F73" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G73" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H73" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>9665356715</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>0.027</x:v>
+        <x:v>0.0627</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:9">
       <x:c r="A74" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B74" s="0">
-        <x:v>317.75</x:v>
+        <x:v>27.46</x:v>
       </x:c>
       <x:c r="C74" s="0">
-        <x:v>22</x:v>
+        <x:v>0.26</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E74" s="0">
-        <x:v>768864700</x:v>
+        <x:v>2356546000</x:v>
       </x:c>
       <x:c r="F74" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G74" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H74" s="0">
-        <x:v>35290767390</x:v>
+        <x:v>7708004248</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>0.9648</x:v>
+        <x:v>0.3057</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:9">
       <x:c r="A75" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B75" s="0">
-        <x:v>66.65</x:v>
+        <x:v>17.71</x:v>
       </x:c>
       <x:c r="C75" s="0">
-        <x:v>0.65</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E75" s="0">
-        <x:v>15938617</x:v>
+        <x:v>431250</x:v>
       </x:c>
       <x:c r="F75" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G75" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H75" s="0">
-        <x:v>16733157490</x:v>
+        <x:v>3139850323</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>0.0422</x:v>
+        <x:v>0.0071</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:9">
       <x:c r="A76" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B76" s="0">
+        <x:v>17.71</x:v>
+      </x:c>
+      <x:c r="C76" s="0">
+        <x:v>-0.04</x:v>
+      </x:c>
+      <x:c r="D76" s="0" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="B76" s="0">
-        <x:v>14.85</x:v>
-      </x:c>
-      <x:c r="C76" s="0">
-        <x:v>-0.14</x:v>
-      </x:c>
-      <x:c r="D76" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
       <x:c r="E76" s="0">
-        <x:v>30438120</x:v>
+        <x:v>800000</x:v>
       </x:c>
       <x:c r="F76" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G76" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H76" s="0">
-        <x:v>3159124121</x:v>
+        <x:v>3139850323</x:v>
       </x:c>
       <x:c r="I76" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0131</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:9">
       <x:c r="A77" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B77" s="0">
-        <x:v>265.5</x:v>
+        <x:v>60.5</x:v>
       </x:c>
       <x:c r="C77" s="0">
-        <x:v>24.1</x:v>
+        <x:v>1.6</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E77" s="0">
-        <x:v>3900000</x:v>
+        <x:v>127172130</x:v>
       </x:c>
       <x:c r="F77" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G77" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H77" s="0">
-        <x:v>2159813703</x:v>
+        <x:v>8121300519</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>0.0797</x:v>
+        <x:v>0.0157</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:9">
       <x:c r="A78" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B78" s="0">
-        <x:v>265.5</x:v>
+        <x:v>48.8</x:v>
       </x:c>
       <x:c r="C78" s="0">
-        <x:v>24.1</x:v>
+        <x:v>-0.6</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E78" s="0">
-        <x:v>2104908</x:v>
+        <x:v>42625000</x:v>
       </x:c>
       <x:c r="F78" s="0" t="s">
         <x:v>11</x:v>
@@ -3049,27 +3055,27 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H78" s="0">
-        <x:v>2159813703</x:v>
+        <x:v>4728937463</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>0.043</x:v>
+        <x:v>0.3994</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:9">
       <x:c r="A79" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B79" s="0">
-        <x:v>28.84</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C79" s="0">
-        <x:v>-0.4</x:v>
+        <x:v>-0.7</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E79" s="0">
-        <x:v>3900000</x:v>
+        <x:v>1486000</x:v>
       </x:c>
       <x:c r="F79" s="0" t="s">
         <x:v>11</x:v>
@@ -3078,114 +3084,114 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H79" s="0">
-        <x:v>7297855153</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>0.0236</x:v>
+        <x:v>0.027</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:9">
       <x:c r="A80" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B80" s="0">
-        <x:v>5.42</x:v>
+        <x:v>320.75</x:v>
       </x:c>
       <x:c r="C80" s="0">
-        <x:v>-0.06</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E80" s="0">
-        <x:v>496968445</x:v>
+        <x:v>768864700</x:v>
       </x:c>
       <x:c r="F80" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G80" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H80" s="0">
-        <x:v>855070469</x:v>
+        <x:v>35290767390</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>0.5812</x:v>
+        <x:v>0.9648</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:9">
       <x:c r="A81" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B81" s="0">
-        <x:v>12.49</x:v>
+        <x:v>73.3</x:v>
       </x:c>
       <x:c r="C81" s="0">
-        <x:v>0.18</x:v>
+        <x:v>6.65</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E81" s="0">
-        <x:v>108750000</x:v>
+        <x:v>15938617</x:v>
       </x:c>
       <x:c r="F81" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G81" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H81" s="0">
-        <x:v>1982520183</x:v>
+        <x:v>16733157490</x:v>
       </x:c>
       <x:c r="I81" s="0">
-        <x:v>0.0549</x:v>
+        <x:v>0.0422</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:9">
       <x:c r="A82" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B82" s="0">
-        <x:v>124.5</x:v>
+        <x:v>14.85</x:v>
       </x:c>
       <x:c r="C82" s="0">
-        <x:v>6</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E82" s="0">
-        <x:v>1605197</x:v>
+        <x:v>30438120</x:v>
       </x:c>
       <x:c r="F82" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G82" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H82" s="0">
-        <x:v>3150489640</x:v>
+        <x:v>3159124121</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>0.0257</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:9">
       <x:c r="A83" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B83" s="0">
-        <x:v>434</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="C83" s="0">
-        <x:v>6.75</x:v>
+        <x:v>-0.5</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E83" s="0">
-        <x:v>54600000</x:v>
+        <x:v>3900000</x:v>
       </x:c>
       <x:c r="F83" s="0" t="s">
         <x:v>11</x:v>
@@ -3194,27 +3200,27 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H83" s="0">
-        <x:v>180444938000</x:v>
+        <x:v>2159813703</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>0.0133</x:v>
+        <x:v>0.0797</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:9">
       <x:c r="A84" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B84" s="0">
-        <x:v>434</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="C84" s="0">
-        <x:v>6.75</x:v>
+        <x:v>-0.5</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E84" s="0">
-        <x:v>111850000</x:v>
+        <x:v>2104908</x:v>
       </x:c>
       <x:c r="F84" s="0" t="s">
         <x:v>11</x:v>
@@ -3223,27 +3229,27 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H84" s="0">
-        <x:v>180444938000</x:v>
+        <x:v>2159813703</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>0.0273</x:v>
+        <x:v>0.043</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:9">
       <x:c r="A85" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B85" s="0">
-        <x:v>58.5</x:v>
+        <x:v>29.16</x:v>
       </x:c>
       <x:c r="C85" s="0">
-        <x:v>0.5</x:v>
+        <x:v>0.32</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E85" s="0">
-        <x:v>803090</x:v>
+        <x:v>3900000</x:v>
       </x:c>
       <x:c r="F85" s="0" t="s">
         <x:v>11</x:v>
@@ -3252,230 +3258,230 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H85" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>7297855153</x:v>
       </x:c>
       <x:c r="I85" s="0">
-        <x:v>0.0084</x:v>
+        <x:v>0.0236</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:9">
       <x:c r="A86" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B86" s="0">
-        <x:v>27.2</x:v>
+        <x:v>5.84</x:v>
       </x:c>
       <x:c r="C86" s="0">
-        <x:v>-0.12</x:v>
+        <x:v>0.42</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E86" s="0">
-        <x:v>2356546000</x:v>
+        <x:v>496968445</x:v>
       </x:c>
       <x:c r="F86" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G86" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H86" s="0">
-        <x:v>7708004248</x:v>
+        <x:v>855070469</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>0.3057</x:v>
+        <x:v>0.5812</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:9">
       <x:c r="A87" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B87" s="0">
-        <x:v>1188</x:v>
+        <x:v>12.57</x:v>
       </x:c>
       <x:c r="C87" s="0">
-        <x:v>-52</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E87" s="0">
-        <x:v>875400</x:v>
+        <x:v>108750000</x:v>
       </x:c>
       <x:c r="F87" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G87" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H87" s="0">
-        <x:v>1883544167</x:v>
+        <x:v>1982520183</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>0.0205</x:v>
+        <x:v>0.0549</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:9">
       <x:c r="A88" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B88" s="0">
-        <x:v>26.72</x:v>
+        <x:v>136.9</x:v>
       </x:c>
       <x:c r="C88" s="0">
-        <x:v>-0.1</x:v>
+        <x:v>12.4</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E88" s="0">
-        <x:v>330000000</x:v>
+        <x:v>1605197</x:v>
       </x:c>
       <x:c r="F88" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G88" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H88" s="0">
-        <x:v>5287314404</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>0.0624</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:9">
       <x:c r="A89" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B89" s="0">
-        <x:v>83.6</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="C89" s="0">
-        <x:v>1.9</x:v>
+        <x:v>-6</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E89" s="0">
-        <x:v>11700000</x:v>
+        <x:v>54600000</x:v>
       </x:c>
       <x:c r="F89" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G89" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H89" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>180444938000</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>0.1705</x:v>
+        <x:v>0.0133</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:9">
       <x:c r="A90" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B90" s="0">
-        <x:v>8.41</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="C90" s="0">
-        <x:v>0.05</x:v>
+        <x:v>-6</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E90" s="0">
-        <x:v>4000000000</x:v>
+        <x:v>111850000</x:v>
       </x:c>
       <x:c r="F90" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G90" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H90" s="0">
-        <x:v>10581001663</x:v>
+        <x:v>180444938000</x:v>
       </x:c>
       <x:c r="I90" s="0">
-        <x:v>0.378</x:v>
+        <x:v>0.0273</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:9">
       <x:c r="A91" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B91" s="0">
-        <x:v>17.75</x:v>
+        <x:v>57.05</x:v>
       </x:c>
       <x:c r="C91" s="0">
-        <x:v>0.73</x:v>
+        <x:v>-1.45</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E91" s="0">
-        <x:v>1086598</x:v>
+        <x:v>803090</x:v>
       </x:c>
       <x:c r="F91" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G91" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H91" s="0">
-        <x:v>2020891371</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>0.0274</x:v>
+        <x:v>0.0084</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:9">
       <x:c r="A92" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B92" s="0">
-        <x:v>15.68</x:v>
+        <x:v>27.46</x:v>
       </x:c>
       <x:c r="C92" s="0">
-        <x:v>-0.22</x:v>
+        <x:v>0.26</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E92" s="0">
-        <x:v>216000000</x:v>
+        <x:v>2356546000</x:v>
       </x:c>
       <x:c r="F92" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G92" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H92" s="0">
-        <x:v>3025063909</x:v>
+        <x:v>7708004248</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>0.0714</x:v>
+        <x:v>0.3057</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:9">
       <x:c r="A93" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B93" s="0">
-        <x:v>58.5</x:v>
+        <x:v>1190</x:v>
       </x:c>
       <x:c r="C93" s="0">
-        <x:v>0.5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E93" s="0">
-        <x:v>7292916</x:v>
+        <x:v>875400</x:v>
       </x:c>
       <x:c r="F93" s="0" t="s">
         <x:v>11</x:v>
@@ -3484,288 +3490,288 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H93" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>1883544167</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>0.0758</x:v>
+        <x:v>0.0205</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:9">
       <x:c r="A94" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B94" s="0">
-        <x:v>28.8</x:v>
+        <x:v>27.76</x:v>
       </x:c>
       <x:c r="C94" s="0">
-        <x:v>-0.42</x:v>
+        <x:v>1.04</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E94" s="0">
-        <x:v>250000</x:v>
+        <x:v>330000000</x:v>
       </x:c>
       <x:c r="F94" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G94" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H94" s="0">
-        <x:v>448686813</x:v>
+        <x:v>5287314404</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>0.0006</x:v>
+        <x:v>0.0624</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:9">
       <x:c r="A95" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B95" s="0">
-        <x:v>66.65</x:v>
+        <x:v>84.2</x:v>
       </x:c>
       <x:c r="C95" s="0">
-        <x:v>0.65</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E95" s="0">
-        <x:v>36900000</x:v>
+        <x:v>11700000</x:v>
       </x:c>
       <x:c r="F95" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G95" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H95" s="0">
-        <x:v>10597063406</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>0.1527</x:v>
+        <x:v>0.1705</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:9">
       <x:c r="A96" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B96" s="0">
-        <x:v>68.6</x:v>
+        <x:v>8.8</x:v>
       </x:c>
       <x:c r="C96" s="0">
-        <x:v>2.6</x:v>
+        <x:v>0.39</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E96" s="0">
-        <x:v>3800000</x:v>
+        <x:v>4000000000</x:v>
       </x:c>
       <x:c r="F96" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G96" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H96" s="0">
-        <x:v>832031190</x:v>
+        <x:v>10581001663</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>0.2002</x:v>
+        <x:v>0.378</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:9">
       <x:c r="A97" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B97" s="0">
-        <x:v>5.42</x:v>
+        <x:v>17.71</x:v>
       </x:c>
       <x:c r="C97" s="0">
-        <x:v>-0.06</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E97" s="0">
-        <x:v>2100000</x:v>
+        <x:v>1086598</x:v>
       </x:c>
       <x:c r="F97" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G97" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H97" s="0">
-        <x:v>855070469</x:v>
+        <x:v>2020891371</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>0.1076</x:v>
+        <x:v>0.0274</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:9">
       <x:c r="A98" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B98" s="0">
-        <x:v>58.5</x:v>
+        <x:v>16.44</x:v>
       </x:c>
       <x:c r="C98" s="0">
-        <x:v>0.5</x:v>
+        <x:v>0.76</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E98" s="0">
-        <x:v>22928077</x:v>
+        <x:v>216000000</x:v>
       </x:c>
       <x:c r="F98" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G98" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H98" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>3025063909</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>0.2378</x:v>
+        <x:v>0.0714</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:9">
       <x:c r="A99" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B99" s="0">
-        <x:v>29.7</x:v>
+        <x:v>57.05</x:v>
       </x:c>
       <x:c r="C99" s="0">
-        <x:v>-0.1</x:v>
+        <x:v>-1.45</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E99" s="0">
-        <x:v>547462013</x:v>
+        <x:v>7292916</x:v>
       </x:c>
       <x:c r="F99" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G99" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H99" s="0">
-        <x:v>0</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0758</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:9">
       <x:c r="A100" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B100" s="0">
-        <x:v>29.7</x:v>
+        <x:v>30.06</x:v>
       </x:c>
       <x:c r="C100" s="0">
-        <x:v>-0.1</x:v>
+        <x:v>1.26</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E100" s="0">
-        <x:v>10567948</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="F100" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G100" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H100" s="0">
-        <x:v>0</x:v>
+        <x:v>448686813</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0006</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:9">
       <x:c r="A101" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B101" s="0">
-        <x:v>83.6</x:v>
+        <x:v>73.3</x:v>
       </x:c>
       <x:c r="C101" s="0">
-        <x:v>1.9</x:v>
+        <x:v>6.65</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E101" s="0">
-        <x:v>8300000</x:v>
+        <x:v>36900000</x:v>
       </x:c>
       <x:c r="F101" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G101" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H101" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>10597063406</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>0.1228</x:v>
+        <x:v>0.1527</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:9">
       <x:c r="A102" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B102" s="0">
-        <x:v>56.5</x:v>
+        <x:v>71.15</x:v>
       </x:c>
       <x:c r="C102" s="0">
-        <x:v>2.3</x:v>
+        <x:v>2.55</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E102" s="0">
-        <x:v>3000000</x:v>
+        <x:v>3800000</x:v>
       </x:c>
       <x:c r="F102" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G102" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H102" s="0">
-        <x:v>20597209000</x:v>
+        <x:v>832031190</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>0.0064</x:v>
+        <x:v>0.2002</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:9">
       <x:c r="A103" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B103" s="0">
-        <x:v>37.08</x:v>
+        <x:v>5.84</x:v>
       </x:c>
       <x:c r="C103" s="0">
-        <x:v>1.44</x:v>
+        <x:v>0.42</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
         <x:v>92</x:v>
       </x:c>
       <x:c r="E103" s="0">
-        <x:v>26640000</x:v>
+        <x:v>2100000</x:v>
       </x:c>
       <x:c r="F103" s="0" t="s">
         <x:v>11</x:v>
@@ -3774,300 +3780,300 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H103" s="0">
-        <x:v>3277373640</x:v>
+        <x:v>855070469</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>0.356</x:v>
+        <x:v>0.1076</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:9">
       <x:c r="A104" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B104" s="0">
-        <x:v>6.13</x:v>
+        <x:v>57.05</x:v>
       </x:c>
       <x:c r="C104" s="0">
-        <x:v>0.12</x:v>
+        <x:v>-1.45</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E104" s="0">
-        <x:v>13107198</x:v>
+        <x:v>22928077</x:v>
       </x:c>
       <x:c r="F104" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G104" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H104" s="0">
-        <x:v>1627872951</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I104" s="0">
-        <x:v>0.0081</x:v>
+        <x:v>0.2378</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:9">
       <x:c r="A105" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B105" s="0">
-        <x:v>83.6</x:v>
+        <x:v>30.42</x:v>
       </x:c>
       <x:c r="C105" s="0">
-        <x:v>1.9</x:v>
+        <x:v>0.72</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E105" s="0">
-        <x:v>237500000</x:v>
+        <x:v>547462013</x:v>
       </x:c>
       <x:c r="F105" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G105" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H105" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I105" s="0">
-        <x:v>0.0679</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:9">
       <x:c r="A106" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B106" s="0">
-        <x:v>58.9</x:v>
+        <x:v>30.42</x:v>
       </x:c>
       <x:c r="C106" s="0">
-        <x:v>1.15</x:v>
+        <x:v>0.72</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E106" s="0">
-        <x:v>147892538</x:v>
+        <x:v>10567948</x:v>
       </x:c>
       <x:c r="F106" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G106" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H106" s="0">
-        <x:v>7257990064</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>0.0204</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:9">
       <x:c r="A107" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B107" s="0">
-        <x:v>61.35</x:v>
+        <x:v>84.2</x:v>
       </x:c>
       <x:c r="C107" s="0">
-        <x:v>2.55</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E107" s="0">
-        <x:v>988848</x:v>
+        <x:v>8300000</x:v>
       </x:c>
       <x:c r="F107" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G107" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H107" s="0">
-        <x:v>12999679000</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>0.0033</x:v>
+        <x:v>0.1228</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:9">
       <x:c r="A108" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B108" s="0">
-        <x:v>66.65</x:v>
+        <x:v>58.4</x:v>
       </x:c>
       <x:c r="C108" s="0">
-        <x:v>0.65</x:v>
+        <x:v>1.9</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E108" s="0">
-        <x:v>47300000</x:v>
+        <x:v>3000000</x:v>
       </x:c>
       <x:c r="F108" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G108" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H108" s="0">
-        <x:v>10597063406</x:v>
+        <x:v>20597209000</x:v>
       </x:c>
       <x:c r="I108" s="0">
-        <x:v>0.2309</x:v>
+        <x:v>0.0064</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:9">
       <x:c r="A109" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B109" s="0">
-        <x:v>4.05</x:v>
+        <x:v>37.22</x:v>
       </x:c>
       <x:c r="C109" s="0">
-        <x:v>0.05</x:v>
+        <x:v>0.14</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E109" s="0">
-        <x:v>758600</x:v>
+        <x:v>26640000</x:v>
       </x:c>
       <x:c r="F109" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G109" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H109" s="0">
-        <x:v>1960468575</x:v>
+        <x:v>3277373640</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0.356</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:9">
       <x:c r="A110" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B110" s="0">
-        <x:v>4.05</x:v>
+        <x:v>6.32</x:v>
       </x:c>
       <x:c r="C110" s="0">
-        <x:v>0.05</x:v>
+        <x:v>0.19</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E110" s="0">
-        <x:v>758600</x:v>
+        <x:v>13107198</x:v>
       </x:c>
       <x:c r="F110" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G110" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H110" s="0">
-        <x:v>1960468575</x:v>
+        <x:v>1627872951</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>0.0004</x:v>
+        <x:v>0.0081</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:9">
       <x:c r="A111" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B111" s="0">
-        <x:v>1188</x:v>
+        <x:v>84.2</x:v>
       </x:c>
       <x:c r="C111" s="0">
-        <x:v>-52</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E111" s="0">
-        <x:v>576665</x:v>
+        <x:v>237500000</x:v>
       </x:c>
       <x:c r="F111" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G111" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H111" s="0">
-        <x:v>1586603352</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>0.0159</x:v>
+        <x:v>0.0679</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:9">
       <x:c r="A112" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B112" s="0">
-        <x:v>85.2</x:v>
+        <x:v>60.5</x:v>
       </x:c>
       <x:c r="C112" s="0">
-        <x:v>-0.6</x:v>
+        <x:v>1.6</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
         <x:v>99</x:v>
       </x:c>
       <x:c r="E112" s="0">
-        <x:v>8000000</x:v>
+        <x:v>147892538</x:v>
       </x:c>
       <x:c r="F112" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G112" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H112" s="0">
-        <x:v>20999579110</x:v>
+        <x:v>7257990064</x:v>
       </x:c>
       <x:c r="I112" s="0">
-        <x:v>0.0166</x:v>
+        <x:v>0.0204</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:9">
       <x:c r="A113" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B113" s="0">
-        <x:v>100.7</x:v>
+        <x:v>59.5</x:v>
       </x:c>
       <x:c r="C113" s="0">
-        <x:v>0</x:v>
+        <x:v>-1.85</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E113" s="0">
-        <x:v>850000</x:v>
+        <x:v>988848</x:v>
       </x:c>
       <x:c r="F113" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G113" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H113" s="0">
-        <x:v>1781510191</x:v>
+        <x:v>12999679000</x:v>
       </x:c>
       <x:c r="I113" s="0">
-        <x:v>0.0208</x:v>
+        <x:v>0.0033</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:9">
@@ -4075,161 +4081,161 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B114" s="0">
-        <x:v>17.75</x:v>
+        <x:v>73.3</x:v>
       </x:c>
       <x:c r="C114" s="0">
-        <x:v>0.73</x:v>
+        <x:v>6.65</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E114" s="0">
-        <x:v>10149200</x:v>
+        <x:v>47300000</x:v>
       </x:c>
       <x:c r="F114" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G114" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H114" s="0">
-        <x:v>2020891371</x:v>
+        <x:v>10597063406</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>0.2601</x:v>
+        <x:v>0.2309</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:9">
       <x:c r="A115" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B115" s="0">
-        <x:v>124.5</x:v>
+        <x:v>4.16</x:v>
       </x:c>
       <x:c r="C115" s="0">
-        <x:v>6</x:v>
+        <x:v>0.11</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E115" s="0">
-        <x:v>10500000</x:v>
+        <x:v>758600</x:v>
       </x:c>
       <x:c r="F115" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G115" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H115" s="0">
-        <x:v>1742315226</x:v>
+        <x:v>1960468575</x:v>
       </x:c>
       <x:c r="I115" s="0">
-        <x:v>0.3121</x:v>
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:9">
       <x:c r="A116" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B116" s="0">
-        <x:v>100.7</x:v>
+        <x:v>4.16</x:v>
       </x:c>
       <x:c r="C116" s="0">
-        <x:v>0</x:v>
+        <x:v>0.11</x:v>
       </x:c>
       <x:c r="D116" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E116" s="0">
-        <x:v>366956541</x:v>
+        <x:v>758600</x:v>
       </x:c>
       <x:c r="F116" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="G116" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H116" s="0">
-        <x:v>1781510191</x:v>
+        <x:v>1960468575</x:v>
       </x:c>
       <x:c r="I116" s="0">
-        <x:v>0.206</x:v>
+        <x:v>0.0004</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:9">
       <x:c r="A117" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B117" s="0">
-        <x:v>58.9</x:v>
+        <x:v>1190</x:v>
       </x:c>
       <x:c r="C117" s="0">
-        <x:v>1.15</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E117" s="0">
-        <x:v>61158155</x:v>
+        <x:v>576665</x:v>
       </x:c>
       <x:c r="F117" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G117" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H117" s="0">
-        <x:v>7257990064</x:v>
+        <x:v>1586603352</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>0.0084</x:v>
+        <x:v>0.0159</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:9">
       <x:c r="A118" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B118" s="0">
-        <x:v>108.1</x:v>
+        <x:v>86.05</x:v>
       </x:c>
       <x:c r="C118" s="0">
-        <x:v>-1.9</x:v>
+        <x:v>0.85</x:v>
       </x:c>
       <x:c r="D118" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E118" s="0">
-        <x:v>1000000</x:v>
+        <x:v>8000000</x:v>
       </x:c>
       <x:c r="F118" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G118" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H118" s="0">
-        <x:v>1688731509</x:v>
+        <x:v>20999579110</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>0.0307</x:v>
+        <x:v>0.0166</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:9">
       <x:c r="A119" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B119" s="0">
-        <x:v>108.1</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C119" s="0">
-        <x:v>-1.9</x:v>
+        <x:v>-0.7</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E119" s="0">
-        <x:v>1050000</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="F119" s="0" t="s">
         <x:v>11</x:v>
@@ -4238,172 +4244,172 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H119" s="0">
-        <x:v>1688731509</x:v>
+        <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>0.0271</x:v>
+        <x:v>0.0208</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:9">
       <x:c r="A120" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B120" s="0">
-        <x:v>42.6</x:v>
+        <x:v>17.71</x:v>
       </x:c>
       <x:c r="C120" s="0">
-        <x:v>0.46</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E120" s="0">
-        <x:v>109053804</x:v>
+        <x:v>10149200</x:v>
       </x:c>
       <x:c r="F120" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G120" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H120" s="0">
-        <x:v>1942491524</x:v>
+        <x:v>2020891371</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>0.0561</x:v>
+        <x:v>0.2601</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:9">
       <x:c r="A121" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B121" s="0">
-        <x:v>9.75</x:v>
+        <x:v>136.9</x:v>
       </x:c>
       <x:c r="C121" s="0">
-        <x:v>0.15</x:v>
+        <x:v>12.4</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E121" s="0">
-        <x:v>62315119</x:v>
+        <x:v>10500000</x:v>
       </x:c>
       <x:c r="F121" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G121" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H121" s="0">
-        <x:v>12026414029</x:v>
+        <x:v>1742315226</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>0.2257</x:v>
+        <x:v>0.3121</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:9">
       <x:c r="A122" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B122" s="0">
-        <x:v>265.5</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C122" s="0">
-        <x:v>24.1</x:v>
+        <x:v>-0.7</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E122" s="0">
-        <x:v>896400</x:v>
+        <x:v>366956541</x:v>
       </x:c>
       <x:c r="F122" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G122" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H122" s="0">
-        <x:v>1364716456</x:v>
+        <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>0.0285</x:v>
+        <x:v>0.206</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:9">
       <x:c r="A123" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B123" s="0">
-        <x:v>496.5</x:v>
+        <x:v>60.5</x:v>
       </x:c>
       <x:c r="C123" s="0">
-        <x:v>45</x:v>
+        <x:v>1.6</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E123" s="0">
-        <x:v>3370000</x:v>
+        <x:v>61158155</x:v>
       </x:c>
       <x:c r="F123" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G123" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H123" s="0">
-        <x:v>1865697176</x:v>
+        <x:v>7257990064</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>0.0785</x:v>
+        <x:v>0.0084</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:9">
       <x:c r="A124" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B124" s="0">
-        <x:v>56.5</x:v>
+        <x:v>111.8</x:v>
       </x:c>
       <x:c r="C124" s="0">
-        <x:v>2.3</x:v>
+        <x:v>3.7</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E124" s="0">
-        <x:v>750561215</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="F124" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G124" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H124" s="0">
-        <x:v>16507905000</x:v>
+        <x:v>1688731509</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>0.0455</x:v>
+        <x:v>0.0307</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:9">
       <x:c r="A125" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B125" s="0">
-        <x:v>85.2</x:v>
+        <x:v>111.8</x:v>
       </x:c>
       <x:c r="C125" s="0">
-        <x:v>-0.6</x:v>
+        <x:v>3.7</x:v>
       </x:c>
       <x:c r="D125" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E125" s="0">
-        <x:v>20000000</x:v>
+        <x:v>1050000</x:v>
       </x:c>
       <x:c r="F125" s="0" t="s">
         <x:v>11</x:v>
@@ -4412,56 +4418,56 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H125" s="0">
-        <x:v>20999579110</x:v>
+        <x:v>1688731509</x:v>
       </x:c>
       <x:c r="I125" s="0">
-        <x:v>0.0413</x:v>
+        <x:v>0.0271</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:9">
       <x:c r="A126" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B126" s="0">
-        <x:v>33.64</x:v>
+        <x:v>42.28</x:v>
       </x:c>
       <x:c r="C126" s="0">
-        <x:v>-0.34</x:v>
+        <x:v>-0.32</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E126" s="0">
-        <x:v>750000000</x:v>
+        <x:v>109053804</x:v>
       </x:c>
       <x:c r="F126" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G126" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H126" s="0">
-        <x:v>0</x:v>
+        <x:v>1942491524</x:v>
       </x:c>
       <x:c r="I126" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0561</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:9">
       <x:c r="A127" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B127" s="0">
-        <x:v>66.65</x:v>
+        <x:v>10.22</x:v>
       </x:c>
       <x:c r="C127" s="0">
-        <x:v>0.65</x:v>
+        <x:v>0.47</x:v>
       </x:c>
       <x:c r="D127" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E127" s="0">
-        <x:v>111232418</x:v>
+        <x:v>62315119</x:v>
       </x:c>
       <x:c r="F127" s="0" t="s">
         <x:v>11</x:v>
@@ -4470,27 +4476,27 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H127" s="0">
-        <x:v>10597063406</x:v>
+        <x:v>12026414029</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>0.4554</x:v>
+        <x:v>0.2257</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:9">
       <x:c r="A128" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B128" s="0">
-        <x:v>38.88</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="C128" s="0">
-        <x:v>2.48</x:v>
+        <x:v>-0.5</x:v>
       </x:c>
       <x:c r="D128" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E128" s="0">
-        <x:v>51384996</x:v>
+        <x:v>896400</x:v>
       </x:c>
       <x:c r="F128" s="0" t="s">
         <x:v>11</x:v>
@@ -4499,27 +4505,27 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H128" s="0">
-        <x:v>11899043692</x:v>
+        <x:v>1364716456</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>0.1873</x:v>
+        <x:v>0.0285</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:9">
       <x:c r="A129" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B129" s="0">
-        <x:v>38.88</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="C129" s="0">
-        <x:v>2.48</x:v>
+        <x:v>49.5</x:v>
       </x:c>
       <x:c r="D129" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="E129" s="0">
-        <x:v>3602451</x:v>
+        <x:v>3370000</x:v>
       </x:c>
       <x:c r="F129" s="0" t="s">
         <x:v>11</x:v>
@@ -4528,172 +4534,172 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H129" s="0">
-        <x:v>11899043692</x:v>
+        <x:v>1865697176</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>0.0131</x:v>
+        <x:v>0.0785</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:9">
       <x:c r="A130" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B130" s="0">
-        <x:v>38.88</x:v>
+        <x:v>58.4</x:v>
       </x:c>
       <x:c r="C130" s="0">
-        <x:v>2.48</x:v>
+        <x:v>1.9</x:v>
       </x:c>
       <x:c r="D130" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E130" s="0">
-        <x:v>24226465</x:v>
+        <x:v>750561215</x:v>
       </x:c>
       <x:c r="F130" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G130" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H130" s="0">
-        <x:v>11899043692</x:v>
+        <x:v>16507905000</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>0.0883</x:v>
+        <x:v>0.0455</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:9">
       <x:c r="A131" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B131" s="0">
-        <x:v>58.5</x:v>
+        <x:v>86.05</x:v>
       </x:c>
       <x:c r="C131" s="0">
-        <x:v>0.5</x:v>
+        <x:v>0.85</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E131" s="0">
-        <x:v>12900000</x:v>
+        <x:v>20000000</x:v>
       </x:c>
       <x:c r="F131" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G131" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H131" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>20999579110</x:v>
       </x:c>
       <x:c r="I131" s="0">
-        <x:v>0.0052</x:v>
+        <x:v>0.0413</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:9">
       <x:c r="A132" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B132" s="0">
-        <x:v>317.75</x:v>
+        <x:v>35.5</x:v>
       </x:c>
       <x:c r="C132" s="0">
-        <x:v>22</x:v>
+        <x:v>1.86</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E132" s="0">
-        <x:v>53250000</x:v>
+        <x:v>750000000</x:v>
       </x:c>
       <x:c r="F132" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G132" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H132" s="0">
-        <x:v>24073631758</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I132" s="0">
-        <x:v>0.115</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:9">
       <x:c r="A133" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B133" s="0">
-        <x:v>29.7</x:v>
+        <x:v>73.3</x:v>
       </x:c>
       <x:c r="C133" s="0">
-        <x:v>-0.1</x:v>
+        <x:v>6.65</x:v>
       </x:c>
       <x:c r="D133" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E133" s="0">
-        <x:v>6860140</x:v>
+        <x:v>111232418</x:v>
       </x:c>
       <x:c r="F133" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G133" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H133" s="0">
-        <x:v>0</x:v>
+        <x:v>10597063406</x:v>
       </x:c>
       <x:c r="I133" s="0">
-        <x:v>0</x:v>
+        <x:v>0.4554</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:9">
       <x:c r="A134" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B134" s="0">
-        <x:v>83.6</x:v>
+        <x:v>37.8</x:v>
       </x:c>
       <x:c r="C134" s="0">
-        <x:v>1.9</x:v>
+        <x:v>-1.08</x:v>
       </x:c>
       <x:c r="D134" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E134" s="0">
-        <x:v>230000000</x:v>
+        <x:v>51384996</x:v>
       </x:c>
       <x:c r="F134" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G134" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H134" s="0">
-        <x:v>2941310980</x:v>
+        <x:v>11899043692</x:v>
       </x:c>
       <x:c r="I134" s="0">
-        <x:v>0.0782</x:v>
+        <x:v>0.1873</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:9">
       <x:c r="A135" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B135" s="0">
-        <x:v>496.5</x:v>
+        <x:v>37.8</x:v>
       </x:c>
       <x:c r="C135" s="0">
-        <x:v>45</x:v>
+        <x:v>-1.08</x:v>
       </x:c>
       <x:c r="D135" s="0" t="s">
         <x:v>118</x:v>
       </x:c>
       <x:c r="E135" s="0">
-        <x:v>4700000</x:v>
+        <x:v>3602451</x:v>
       </x:c>
       <x:c r="F135" s="0" t="s">
         <x:v>11</x:v>
@@ -4702,172 +4708,172 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H135" s="0">
-        <x:v>1865697176</x:v>
+        <x:v>11899043692</x:v>
       </x:c>
       <x:c r="I135" s="0">
-        <x:v>0.1092</x:v>
+        <x:v>0.0131</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:9">
       <x:c r="A136" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B136" s="0">
-        <x:v>29.7</x:v>
+        <x:v>37.8</x:v>
       </x:c>
       <x:c r="C136" s="0">
-        <x:v>-0.1</x:v>
+        <x:v>-1.08</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
         <x:v>118</x:v>
       </x:c>
       <x:c r="E136" s="0">
-        <x:v>256000000</x:v>
+        <x:v>24226465</x:v>
       </x:c>
       <x:c r="F136" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G136" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H136" s="0">
-        <x:v>0</x:v>
+        <x:v>11899043692</x:v>
       </x:c>
       <x:c r="I136" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0883</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:9">
       <x:c r="A137" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B137" s="0">
-        <x:v>38.88</x:v>
+        <x:v>57.05</x:v>
       </x:c>
       <x:c r="C137" s="0">
-        <x:v>2.48</x:v>
+        <x:v>-1.45</x:v>
       </x:c>
       <x:c r="D137" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E137" s="0">
-        <x:v>10724896</x:v>
+        <x:v>12900000</x:v>
       </x:c>
       <x:c r="F137" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G137" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H137" s="0">
-        <x:v>11899043692</x:v>
+        <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I137" s="0">
-        <x:v>0.039</x:v>
+        <x:v>0.0052</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:9">
       <x:c r="A138" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B138" s="0">
-        <x:v>24.68</x:v>
+        <x:v>320.75</x:v>
       </x:c>
       <x:c r="C138" s="0">
-        <x:v>-0.08</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D138" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E138" s="0">
-        <x:v>31000000</x:v>
+        <x:v>53250000</x:v>
       </x:c>
       <x:c r="F138" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G138" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H138" s="0">
-        <x:v>813967617</x:v>
+        <x:v>24073631758</x:v>
       </x:c>
       <x:c r="I138" s="0">
-        <x:v>0.0381</x:v>
+        <x:v>0.115</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:9">
       <x:c r="A139" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B139" s="0">
-        <x:v>42.9</x:v>
+        <x:v>30.42</x:v>
       </x:c>
       <x:c r="C139" s="0">
-        <x:v>1.32</x:v>
+        <x:v>0.72</x:v>
       </x:c>
       <x:c r="D139" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E139" s="0">
-        <x:v>13500000</x:v>
+        <x:v>6860140</x:v>
       </x:c>
       <x:c r="F139" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G139" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H139" s="0">
-        <x:v>6483809984</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I139" s="0">
-        <x:v>0.09</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:9">
       <x:c r="A140" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B140" s="0">
-        <x:v>42.6</x:v>
+        <x:v>84.2</x:v>
       </x:c>
       <x:c r="C140" s="0">
-        <x:v>0.46</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="D140" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E140" s="0">
-        <x:v>29886357</x:v>
+        <x:v>230000000</x:v>
       </x:c>
       <x:c r="F140" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G140" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H140" s="0">
-        <x:v>1942491524</x:v>
+        <x:v>2941310980</x:v>
       </x:c>
       <x:c r="I140" s="0">
-        <x:v>0.0154</x:v>
+        <x:v>0.0782</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:9">
       <x:c r="A141" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B141" s="0">
-        <x:v>434</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="C141" s="0">
-        <x:v>6.75</x:v>
+        <x:v>49.5</x:v>
       </x:c>
       <x:c r="D141" s="0" t="s">
         <x:v>120</x:v>
       </x:c>
       <x:c r="E141" s="0">
-        <x:v>171000000</x:v>
+        <x:v>4700000</x:v>
       </x:c>
       <x:c r="F141" s="0" t="s">
         <x:v>11</x:v>
@@ -4876,56 +4882,56 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H141" s="0">
-        <x:v>130147715000</x:v>
+        <x:v>1865697176</x:v>
       </x:c>
       <x:c r="I141" s="0">
-        <x:v>0.0568</x:v>
+        <x:v>0.1092</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:9">
       <x:c r="A142" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B142" s="0">
-        <x:v>124.5</x:v>
+        <x:v>30.42</x:v>
       </x:c>
       <x:c r="C142" s="0">
-        <x:v>6</x:v>
+        <x:v>0.72</x:v>
       </x:c>
       <x:c r="D142" s="0" t="s">
         <x:v>120</x:v>
       </x:c>
       <x:c r="E142" s="0">
-        <x:v>1890000</x:v>
+        <x:v>256000000</x:v>
       </x:c>
       <x:c r="F142" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G142" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H142" s="0">
-        <x:v>1742315226</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I142" s="0">
-        <x:v>0.0549</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:9">
       <x:c r="A143" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B143" s="0">
+        <x:v>37.8</x:v>
+      </x:c>
+      <x:c r="C143" s="0">
+        <x:v>-1.08</x:v>
+      </x:c>
+      <x:c r="D143" s="0" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="B143" s="0">
-        <x:v>14.02</x:v>
-      </x:c>
-      <x:c r="C143" s="0">
-        <x:v>0.12</x:v>
-      </x:c>
-      <x:c r="D143" s="0" t="s">
-        <x:v>120</x:v>
-      </x:c>
       <x:c r="E143" s="0">
-        <x:v>892825</x:v>
+        <x:v>10724896</x:v>
       </x:c>
       <x:c r="F143" s="0" t="s">
         <x:v>11</x:v>
@@ -4934,56 +4940,56 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H143" s="0">
-        <x:v>3015442704</x:v>
+        <x:v>11899043692</x:v>
       </x:c>
       <x:c r="I143" s="0">
-        <x:v>0.0128</x:v>
+        <x:v>0.039</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:9">
       <x:c r="A144" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B144" s="0">
-        <x:v>58.5</x:v>
+        <x:v>24.84</x:v>
       </x:c>
       <x:c r="C144" s="0">
-        <x:v>0.5</x:v>
+        <x:v>0.16</x:v>
       </x:c>
       <x:c r="D144" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E144" s="0">
-        <x:v>361176</x:v>
+        <x:v>31000000</x:v>
       </x:c>
       <x:c r="F144" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G144" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H144" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>813967617</x:v>
       </x:c>
       <x:c r="I144" s="0">
-        <x:v>0.0063</x:v>
+        <x:v>0.0381</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:9">
       <x:c r="A145" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B145" s="0">
-        <x:v>24.92</x:v>
+        <x:v>43.74</x:v>
       </x:c>
       <x:c r="C145" s="0">
-        <x:v>0.58</x:v>
+        <x:v>0.84</x:v>
       </x:c>
       <x:c r="D145" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E145" s="0">
-        <x:v>1060000</x:v>
+        <x:v>13500000</x:v>
       </x:c>
       <x:c r="F145" s="0" t="s">
         <x:v>11</x:v>
@@ -4992,56 +4998,56 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H145" s="0">
-        <x:v>1194839266</x:v>
+        <x:v>6483809984</x:v>
       </x:c>
       <x:c r="I145" s="0">
-        <x:v>0.0384</x:v>
+        <x:v>0.09</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:9">
       <x:c r="A146" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B146" s="0">
-        <x:v>55.7</x:v>
+        <x:v>42.28</x:v>
       </x:c>
       <x:c r="C146" s="0">
-        <x:v>1.7</x:v>
+        <x:v>-0.32</x:v>
       </x:c>
       <x:c r="D146" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E146" s="0">
-        <x:v>259417800</x:v>
+        <x:v>29886357</x:v>
       </x:c>
       <x:c r="F146" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G146" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H146" s="0">
-        <x:v>2741117556</x:v>
+        <x:v>1942491524</x:v>
       </x:c>
       <x:c r="I146" s="0">
-        <x:v>0.0946</x:v>
+        <x:v>0.0154</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:9">
       <x:c r="A147" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B147" s="0">
-        <x:v>68.6</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="C147" s="0">
-        <x:v>2.6</x:v>
+        <x:v>-6</x:v>
       </x:c>
       <x:c r="D147" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E147" s="0">
-        <x:v>523788</x:v>
+        <x:v>171000000</x:v>
       </x:c>
       <x:c r="F147" s="0" t="s">
         <x:v>11</x:v>
@@ -5050,56 +5056,56 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H147" s="0">
-        <x:v>832031190</x:v>
+        <x:v>130147715000</x:v>
       </x:c>
       <x:c r="I147" s="0">
-        <x:v>0.0272</x:v>
+        <x:v>0.0568</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:9">
       <x:c r="A148" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B148" s="0">
-        <x:v>68.6</x:v>
+        <x:v>136.9</x:v>
       </x:c>
       <x:c r="C148" s="0">
-        <x:v>2.6</x:v>
+        <x:v>12.4</x:v>
       </x:c>
       <x:c r="D148" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E148" s="0">
-        <x:v>1415270</x:v>
+        <x:v>1890000</x:v>
       </x:c>
       <x:c r="F148" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G148" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H148" s="0">
-        <x:v>832031190</x:v>
+        <x:v>1742315226</x:v>
       </x:c>
       <x:c r="I148" s="0">
-        <x:v>0.0736</x:v>
+        <x:v>0.0549</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:9">
       <x:c r="A149" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B149" s="0">
-        <x:v>85.2</x:v>
+        <x:v>14.16</x:v>
       </x:c>
       <x:c r="C149" s="0">
-        <x:v>-0.6</x:v>
+        <x:v>0.14</x:v>
       </x:c>
       <x:c r="D149" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E149" s="0">
-        <x:v>25000000</x:v>
+        <x:v>892825</x:v>
       </x:c>
       <x:c r="F149" s="0" t="s">
         <x:v>11</x:v>
@@ -5108,27 +5114,27 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H149" s="0">
-        <x:v>20999579110</x:v>
+        <x:v>3015442704</x:v>
       </x:c>
       <x:c r="I149" s="0">
-        <x:v>0.0515</x:v>
+        <x:v>0.0128</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:9">
       <x:c r="A150" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B150" s="0">
-        <x:v>6.13</x:v>
+        <x:v>57.05</x:v>
       </x:c>
       <x:c r="C150" s="0">
-        <x:v>0.12</x:v>
+        <x:v>-1.45</x:v>
       </x:c>
       <x:c r="D150" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E150" s="0">
-        <x:v>25000</x:v>
+        <x:v>361176</x:v>
       </x:c>
       <x:c r="F150" s="0" t="s">
         <x:v>11</x:v>
@@ -5137,85 +5143,85 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H150" s="0">
-        <x:v>1627872951</x:v>
+        <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I150" s="0">
-        <x:v>0.0007</x:v>
+        <x:v>0.0063</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:9">
       <x:c r="A151" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B151" s="0">
-        <x:v>21.2</x:v>
+        <x:v>25.74</x:v>
       </x:c>
       <x:c r="C151" s="0">
-        <x:v>0.22</x:v>
+        <x:v>0.82</x:v>
       </x:c>
       <x:c r="D151" s="0" t="s">
         <x:v>125</x:v>
       </x:c>
       <x:c r="E151" s="0">
-        <x:v>1500000</x:v>
+        <x:v>1060000</x:v>
       </x:c>
       <x:c r="F151" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G151" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H151" s="0">
-        <x:v>774677961</x:v>
+        <x:v>1194839266</x:v>
       </x:c>
       <x:c r="I151" s="0">
-        <x:v>0.0019</x:v>
+        <x:v>0.0384</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:9">
       <x:c r="A152" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B152" s="0">
-        <x:v>8.41</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C152" s="0">
-        <x:v>0.05</x:v>
+        <x:v>-0.7</x:v>
       </x:c>
       <x:c r="D152" s="0" t="s">
         <x:v>125</x:v>
       </x:c>
       <x:c r="E152" s="0">
-        <x:v>13833310</x:v>
+        <x:v>259417800</x:v>
       </x:c>
       <x:c r="F152" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G152" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H152" s="0">
-        <x:v>9028523851</x:v>
+        <x:v>2741117556</x:v>
       </x:c>
       <x:c r="I152" s="0">
-        <x:v>0.0776</x:v>
+        <x:v>0.0946</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:9">
       <x:c r="A153" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B153" s="0">
-        <x:v>81.7</x:v>
+        <x:v>71.15</x:v>
       </x:c>
       <x:c r="C153" s="0">
-        <x:v>1.3</x:v>
+        <x:v>2.55</x:v>
       </x:c>
       <x:c r="D153" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E153" s="0">
-        <x:v>3419000</x:v>
+        <x:v>523788</x:v>
       </x:c>
       <x:c r="F153" s="0" t="s">
         <x:v>11</x:v>
@@ -5224,27 +5230,27 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H153" s="0">
-        <x:v>3895315496</x:v>
+        <x:v>832031190</x:v>
       </x:c>
       <x:c r="I153" s="0">
-        <x:v>0.0379</x:v>
+        <x:v>0.0272</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:9">
       <x:c r="A154" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B154" s="0">
-        <x:v>496.5</x:v>
+        <x:v>71.15</x:v>
       </x:c>
       <x:c r="C154" s="0">
-        <x:v>45</x:v>
+        <x:v>2.55</x:v>
       </x:c>
       <x:c r="D154" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E154" s="0">
-        <x:v>3700000</x:v>
+        <x:v>1415270</x:v>
       </x:c>
       <x:c r="F154" s="0" t="s">
         <x:v>11</x:v>
@@ -5253,27 +5259,27 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H154" s="0">
-        <x:v>1865697176</x:v>
+        <x:v>832031190</x:v>
       </x:c>
       <x:c r="I154" s="0">
-        <x:v>0.0857</x:v>
+        <x:v>0.0736</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:9">
       <x:c r="A155" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B155" s="0">
-        <x:v>42.9</x:v>
+        <x:v>86.05</x:v>
       </x:c>
       <x:c r="C155" s="0">
-        <x:v>1.32</x:v>
+        <x:v>0.85</x:v>
       </x:c>
       <x:c r="D155" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E155" s="0">
-        <x:v>16000000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="F155" s="0" t="s">
         <x:v>11</x:v>
@@ -5282,27 +5288,27 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H155" s="0">
-        <x:v>6483809984</x:v>
+        <x:v>20999579110</x:v>
       </x:c>
       <x:c r="I155" s="0">
-        <x:v>0.1067</x:v>
+        <x:v>0.0515</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:9">
       <x:c r="A156" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B156" s="0">
-        <x:v>58.5</x:v>
+        <x:v>6.32</x:v>
       </x:c>
       <x:c r="C156" s="0">
-        <x:v>0.5</x:v>
+        <x:v>0.19</x:v>
       </x:c>
       <x:c r="D156" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="E156" s="0">
-        <x:v>906840</x:v>
+        <x:v>25000</x:v>
       </x:c>
       <x:c r="F156" s="0" t="s">
         <x:v>11</x:v>
@@ -5311,85 +5317,85 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H156" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>1627872951</x:v>
       </x:c>
       <x:c r="I156" s="0">
-        <x:v>0.0159</x:v>
+        <x:v>0.0007</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:9">
       <x:c r="A157" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B157" s="0">
-        <x:v>3.47</x:v>
+        <x:v>21.32</x:v>
       </x:c>
       <x:c r="C157" s="0">
-        <x:v>0.18</x:v>
+        <x:v>0.12</x:v>
       </x:c>
       <x:c r="D157" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="E157" s="0">
-        <x:v>895039950</x:v>
+        <x:v>1500000</x:v>
       </x:c>
       <x:c r="F157" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G157" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H157" s="0">
-        <x:v>7382591324</x:v>
+        <x:v>774677961</x:v>
       </x:c>
       <x:c r="I157" s="0">
-        <x:v>0.1212</x:v>
+        <x:v>0.0019</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:9">
       <x:c r="A158" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B158" s="0">
-        <x:v>55.7</x:v>
+        <x:v>8.8</x:v>
       </x:c>
       <x:c r="C158" s="0">
-        <x:v>1.7</x:v>
+        <x:v>0.39</x:v>
       </x:c>
       <x:c r="D158" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="E158" s="0">
-        <x:v>575933040</x:v>
+        <x:v>13833310</x:v>
       </x:c>
       <x:c r="F158" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G158" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H158" s="0">
-        <x:v>2741117556</x:v>
+        <x:v>9028523851</x:v>
       </x:c>
       <x:c r="I158" s="0">
-        <x:v>0.2101</x:v>
+        <x:v>0.0776</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:9">
       <x:c r="A159" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B159" s="0">
+        <x:v>80.25</x:v>
+      </x:c>
+      <x:c r="C159" s="0">
+        <x:v>-1.45</x:v>
+      </x:c>
+      <x:c r="D159" s="0" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="B159" s="0">
-        <x:v>12.6</x:v>
-      </x:c>
-      <x:c r="C159" s="0">
-        <x:v>0.11</x:v>
-      </x:c>
-      <x:c r="D159" s="0" t="s">
-        <x:v>128</x:v>
-      </x:c>
       <x:c r="E159" s="0">
-        <x:v>559000</x:v>
+        <x:v>3419000</x:v>
       </x:c>
       <x:c r="F159" s="0" t="s">
         <x:v>11</x:v>
@@ -5398,27 +5404,27 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H159" s="0">
-        <x:v>2865374550</x:v>
+        <x:v>3895315496</x:v>
       </x:c>
       <x:c r="I159" s="0">
-        <x:v>0.0084</x:v>
+        <x:v>0.0379</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:9">
       <x:c r="A160" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B160" s="0">
-        <x:v>56.5</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="C160" s="0">
-        <x:v>2.3</x:v>
+        <x:v>49.5</x:v>
       </x:c>
       <x:c r="D160" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="E160" s="0">
-        <x:v>8900056</x:v>
+        <x:v>3700000</x:v>
       </x:c>
       <x:c r="F160" s="0" t="s">
         <x:v>11</x:v>
@@ -5427,27 +5433,27 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H160" s="0">
-        <x:v>16507905000</x:v>
+        <x:v>1865697176</x:v>
       </x:c>
       <x:c r="I160" s="0">
-        <x:v>0.0233</x:v>
+        <x:v>0.0857</x:v>
       </x:c>
     </x:row>
     <x:row r="161" spans="1:9">
       <x:c r="A161" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B161" s="0">
-        <x:v>317.75</x:v>
+        <x:v>43.74</x:v>
       </x:c>
       <x:c r="C161" s="0">
-        <x:v>22</x:v>
+        <x:v>0.84</x:v>
       </x:c>
       <x:c r="D161" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="E161" s="0">
-        <x:v>164306000</x:v>
+        <x:v>16000000</x:v>
       </x:c>
       <x:c r="F161" s="0" t="s">
         <x:v>11</x:v>
@@ -5456,27 +5462,27 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H161" s="0">
-        <x:v>24073631758</x:v>
+        <x:v>6483809984</x:v>
       </x:c>
       <x:c r="I161" s="0">
-        <x:v>0.2943</x:v>
+        <x:v>0.1067</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:9">
       <x:c r="A162" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B162" s="0">
+        <x:v>57.05</x:v>
+      </x:c>
+      <x:c r="C162" s="0">
+        <x:v>-1.45</x:v>
+      </x:c>
+      <x:c r="D162" s="0" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="B162" s="0">
-        <x:v>54.85</x:v>
-      </x:c>
-      <x:c r="C162" s="0">
-        <x:v>1.6</x:v>
-      </x:c>
-      <x:c r="D162" s="0" t="s">
-        <x:v>131</x:v>
-      </x:c>
       <x:c r="E162" s="0">
-        <x:v>275000</x:v>
+        <x:v>906840</x:v>
       </x:c>
       <x:c r="F162" s="0" t="s">
         <x:v>11</x:v>
@@ -5485,230 +5491,230 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H162" s="0">
-        <x:v>580678850</x:v>
+        <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I162" s="0">
-        <x:v>0.0204</x:v>
+        <x:v>0.0159</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:9">
       <x:c r="A163" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B163" s="0">
-        <x:v>55.7</x:v>
+        <x:v>3.46</x:v>
       </x:c>
       <x:c r="C163" s="0">
-        <x:v>1.7</x:v>
+        <x:v>-0.01</x:v>
       </x:c>
       <x:c r="D163" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="E163" s="0">
-        <x:v>231651480</x:v>
+        <x:v>895039950</x:v>
       </x:c>
       <x:c r="F163" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G163" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H163" s="0">
-        <x:v>2741117556</x:v>
+        <x:v>7382591324</x:v>
       </x:c>
       <x:c r="I163" s="0">
-        <x:v>0.0845</x:v>
+        <x:v>0.1212</x:v>
       </x:c>
     </x:row>
     <x:row r="164" spans="1:9">
       <x:c r="A164" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B164" s="0">
-        <x:v>15.68</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C164" s="0">
-        <x:v>-0.22</x:v>
+        <x:v>-0.7</x:v>
       </x:c>
       <x:c r="D164" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="E164" s="0">
-        <x:v>31860000</x:v>
+        <x:v>575933040</x:v>
       </x:c>
       <x:c r="F164" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G164" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H164" s="0">
-        <x:v>3025063909</x:v>
+        <x:v>2741117556</x:v>
       </x:c>
       <x:c r="I164" s="0">
-        <x:v>0.4539</x:v>
+        <x:v>0.2101</x:v>
       </x:c>
     </x:row>
     <x:row r="165" spans="1:9">
       <x:c r="A165" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B165" s="0">
-        <x:v>100.7</x:v>
+        <x:v>12.68</x:v>
       </x:c>
       <x:c r="C165" s="0">
-        <x:v>0</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="D165" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="E165" s="0">
-        <x:v>41650000</x:v>
+        <x:v>559000</x:v>
       </x:c>
       <x:c r="F165" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G165" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H165" s="0">
-        <x:v>1781510191</x:v>
+        <x:v>2865374550</x:v>
       </x:c>
       <x:c r="I165" s="0">
-        <x:v>0.0234</x:v>
+        <x:v>0.0084</x:v>
       </x:c>
     </x:row>
     <x:row r="166" spans="1:9">
       <x:c r="A166" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B166" s="0">
-        <x:v>17.75</x:v>
+        <x:v>58.4</x:v>
       </x:c>
       <x:c r="C166" s="0">
-        <x:v>0.73</x:v>
+        <x:v>1.9</x:v>
       </x:c>
       <x:c r="D166" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="E166" s="0">
-        <x:v>815000</x:v>
+        <x:v>8900056</x:v>
       </x:c>
       <x:c r="F166" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G166" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H166" s="0">
-        <x:v>2020891371</x:v>
+        <x:v>16507905000</x:v>
       </x:c>
       <x:c r="I166" s="0">
-        <x:v>0.0202</x:v>
+        <x:v>0.0233</x:v>
       </x:c>
     </x:row>
     <x:row r="167" spans="1:9">
       <x:c r="A167" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B167" s="0">
-        <x:v>83.6</x:v>
+        <x:v>320.75</x:v>
       </x:c>
       <x:c r="C167" s="0">
-        <x:v>1.9</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D167" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="E167" s="0">
-        <x:v>8300000</x:v>
+        <x:v>164306000</x:v>
       </x:c>
       <x:c r="F167" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G167" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H167" s="0">
-        <x:v>2941310980</x:v>
+        <x:v>24073631758</x:v>
       </x:c>
       <x:c r="I167" s="0">
-        <x:v>0.1417</x:v>
+        <x:v>0.2943</x:v>
       </x:c>
     </x:row>
     <x:row r="168" spans="1:9">
       <x:c r="A168" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B168" s="0">
-        <x:v>4.25</x:v>
+        <x:v>55.3</x:v>
       </x:c>
       <x:c r="C168" s="0">
-        <x:v>0.11</x:v>
+        <x:v>0.45</x:v>
       </x:c>
       <x:c r="D168" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="E168" s="0">
-        <x:v>13000000</x:v>
+        <x:v>275000</x:v>
       </x:c>
       <x:c r="F168" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G168" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H168" s="0">
-        <x:v>1416740879</x:v>
+        <x:v>580678850</x:v>
       </x:c>
       <x:c r="I168" s="0">
-        <x:v>0.4613</x:v>
+        <x:v>0.0204</x:v>
       </x:c>
     </x:row>
     <x:row r="169" spans="1:9">
       <x:c r="A169" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B169" s="0">
-        <x:v>124.5</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C169" s="0">
-        <x:v>6</x:v>
+        <x:v>-0.7</x:v>
       </x:c>
       <x:c r="D169" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="E169" s="0">
-        <x:v>1999793</x:v>
+        <x:v>231651480</x:v>
       </x:c>
       <x:c r="F169" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G169" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H169" s="0">
-        <x:v>1742315226</x:v>
+        <x:v>2741117556</x:v>
       </x:c>
       <x:c r="I169" s="0">
-        <x:v>0.0494</x:v>
+        <x:v>0.0845</x:v>
       </x:c>
     </x:row>
     <x:row r="170" spans="1:9">
       <x:c r="A170" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B170" s="0">
-        <x:v>58.5</x:v>
+        <x:v>16.44</x:v>
       </x:c>
       <x:c r="C170" s="0">
-        <x:v>0.5</x:v>
+        <x:v>0.76</x:v>
       </x:c>
       <x:c r="D170" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="E170" s="0">
-        <x:v>1859145</x:v>
+        <x:v>31860000</x:v>
       </x:c>
       <x:c r="F170" s="0" t="s">
         <x:v>11</x:v>
@@ -5717,143 +5723,143 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H170" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>3025063909</x:v>
       </x:c>
       <x:c r="I170" s="0">
-        <x:v>0.0324</x:v>
+        <x:v>0.4539</x:v>
       </x:c>
     </x:row>
     <x:row r="171" spans="1:9">
       <x:c r="A171" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B171" s="0">
-        <x:v>3.47</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C171" s="0">
-        <x:v>0.18</x:v>
+        <x:v>-0.7</x:v>
       </x:c>
       <x:c r="D171" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="E171" s="0">
-        <x:v>689661000</x:v>
+        <x:v>41650000</x:v>
       </x:c>
       <x:c r="F171" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G171" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H171" s="0">
-        <x:v>7382591324</x:v>
+        <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I171" s="0">
-        <x:v>0.0934</x:v>
+        <x:v>0.0234</x:v>
       </x:c>
     </x:row>
     <x:row r="172" spans="1:9">
       <x:c r="A172" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B172" s="0">
-        <x:v>58.5</x:v>
+        <x:v>17.71</x:v>
       </x:c>
       <x:c r="C172" s="0">
-        <x:v>0.5</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D172" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="E172" s="0">
-        <x:v>1902000</x:v>
+        <x:v>815000</x:v>
       </x:c>
       <x:c r="F172" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G172" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H172" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>2020891371</x:v>
       </x:c>
       <x:c r="I172" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0202</x:v>
       </x:c>
     </x:row>
     <x:row r="173" spans="1:9">
       <x:c r="A173" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B173" s="0">
-        <x:v>100.7</x:v>
+        <x:v>84.2</x:v>
       </x:c>
       <x:c r="C173" s="0">
-        <x:v>0</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="D173" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="E173" s="0">
-        <x:v>56520000</x:v>
+        <x:v>8300000</x:v>
       </x:c>
       <x:c r="F173" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G173" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H173" s="0">
-        <x:v>1781510191</x:v>
+        <x:v>2941310980</x:v>
       </x:c>
       <x:c r="I173" s="0">
-        <x:v>0.0317</x:v>
+        <x:v>0.1417</x:v>
       </x:c>
     </x:row>
     <x:row r="174" spans="1:9">
       <x:c r="A174" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B174" s="0">
-        <x:v>100.7</x:v>
+        <x:v>4.3</x:v>
       </x:c>
       <x:c r="C174" s="0">
-        <x:v>0</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D174" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="E174" s="0">
-        <x:v>888325</x:v>
+        <x:v>13000000</x:v>
       </x:c>
       <x:c r="F174" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G174" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H174" s="0">
-        <x:v>1781510191</x:v>
+        <x:v>1416740879</x:v>
       </x:c>
       <x:c r="I174" s="0">
-        <x:v>0</x:v>
+        <x:v>0.4613</x:v>
       </x:c>
     </x:row>
     <x:row r="175" spans="1:9">
       <x:c r="A175" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B175" s="0">
-        <x:v>8.41</x:v>
+        <x:v>136.9</x:v>
       </x:c>
       <x:c r="C175" s="0">
-        <x:v>0.05</x:v>
+        <x:v>12.4</x:v>
       </x:c>
       <x:c r="D175" s="0" t="s">
         <x:v>140</x:v>
       </x:c>
       <x:c r="E175" s="0">
-        <x:v>5581810</x:v>
+        <x:v>1999793</x:v>
       </x:c>
       <x:c r="F175" s="0" t="s">
         <x:v>11</x:v>
@@ -5862,30 +5868,30 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H175" s="0">
-        <x:v>9028523851</x:v>
+        <x:v>1742315226</x:v>
       </x:c>
       <x:c r="I175" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0494</x:v>
       </x:c>
     </x:row>
     <x:row r="176" spans="1:9">
       <x:c r="A176" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B176" s="0">
-        <x:v>58.5</x:v>
+        <x:v>57.05</x:v>
       </x:c>
       <x:c r="C176" s="0">
-        <x:v>0.5</x:v>
+        <x:v>-1.45</x:v>
       </x:c>
       <x:c r="D176" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="E176" s="0">
-        <x:v>504000000</x:v>
+        <x:v>1859145</x:v>
       </x:c>
       <x:c r="F176" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G176" s="0">
         <x:v>2025.09</x:v>
@@ -5894,64 +5900,238 @@
         <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I176" s="0">
-        <x:v>0.2043</x:v>
+        <x:v>0.0324</x:v>
       </x:c>
     </x:row>
     <x:row r="177" spans="1:9">
       <x:c r="A177" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B177" s="0">
-        <x:v>317.75</x:v>
+        <x:v>3.46</x:v>
       </x:c>
       <x:c r="C177" s="0">
-        <x:v>22</x:v>
+        <x:v>-0.01</x:v>
       </x:c>
       <x:c r="D177" s="0" t="s">
         <x:v>141</x:v>
       </x:c>
       <x:c r="E177" s="0">
-        <x:v>21500032</x:v>
+        <x:v>689661000</x:v>
       </x:c>
       <x:c r="F177" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G177" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H177" s="0">
-        <x:v>24073631758</x:v>
+        <x:v>7382591324</x:v>
       </x:c>
       <x:c r="I177" s="0">
-        <x:v>0.0383</x:v>
+        <x:v>0.0934</x:v>
       </x:c>
     </x:row>
     <x:row r="178" spans="1:9">
       <x:c r="A178" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B178" s="0">
+        <x:v>57.05</x:v>
+      </x:c>
+      <x:c r="C178" s="0">
+        <x:v>-1.45</x:v>
+      </x:c>
+      <x:c r="D178" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="E178" s="0">
+        <x:v>1902000</x:v>
+      </x:c>
+      <x:c r="F178" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G178" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H178" s="0">
+        <x:v>2467243928</x:v>
+      </x:c>
+      <x:c r="I178" s="0">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179" spans="1:9">
+      <x:c r="A179" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B179" s="0">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C179" s="0">
+        <x:v>-0.7</x:v>
+      </x:c>
+      <x:c r="D179" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="E179" s="0">
+        <x:v>56520000</x:v>
+      </x:c>
+      <x:c r="F179" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G179" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H179" s="0">
+        <x:v>1781510191</x:v>
+      </x:c>
+      <x:c r="I179" s="0">
+        <x:v>0.0317</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180" spans="1:9">
+      <x:c r="A180" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B180" s="0">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C180" s="0">
+        <x:v>-0.7</x:v>
+      </x:c>
+      <x:c r="D180" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="E180" s="0">
+        <x:v>888325</x:v>
+      </x:c>
+      <x:c r="F180" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G180" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H180" s="0">
+        <x:v>1781510191</x:v>
+      </x:c>
+      <x:c r="I180" s="0">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181" spans="1:9">
+      <x:c r="A181" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="B178" s="0">
-        <x:v>1188</x:v>
-      </x:c>
-      <x:c r="C178" s="0">
-        <x:v>-52</x:v>
-      </x:c>
-      <x:c r="D178" s="0" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="E178" s="0">
+      <x:c r="B181" s="0">
+        <x:v>8.8</x:v>
+      </x:c>
+      <x:c r="C181" s="0">
+        <x:v>0.39</x:v>
+      </x:c>
+      <x:c r="D181" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="E181" s="0">
+        <x:v>5581810</x:v>
+      </x:c>
+      <x:c r="F181" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G181" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H181" s="0">
+        <x:v>9028523851</x:v>
+      </x:c>
+      <x:c r="I181" s="0">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182" spans="1:9">
+      <x:c r="A182" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B182" s="0">
+        <x:v>57.05</x:v>
+      </x:c>
+      <x:c r="C182" s="0">
+        <x:v>-1.45</x:v>
+      </x:c>
+      <x:c r="D182" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="E182" s="0">
+        <x:v>504000000</x:v>
+      </x:c>
+      <x:c r="F182" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G182" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H182" s="0">
+        <x:v>2467243928</x:v>
+      </x:c>
+      <x:c r="I182" s="0">
+        <x:v>0.2043</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183" spans="1:9">
+      <x:c r="A183" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B183" s="0">
+        <x:v>320.75</x:v>
+      </x:c>
+      <x:c r="C183" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D183" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="E183" s="0">
+        <x:v>21500032</x:v>
+      </x:c>
+      <x:c r="F183" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G183" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H183" s="0">
+        <x:v>24073631758</x:v>
+      </x:c>
+      <x:c r="I183" s="0">
+        <x:v>0.0383</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184" spans="1:9">
+      <x:c r="A184" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B184" s="0">
+        <x:v>1190</x:v>
+      </x:c>
+      <x:c r="C184" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D184" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="E184" s="0">
         <x:v>6455151</x:v>
       </x:c>
-      <x:c r="F178" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G178" s="0">
-        <x:v>2025.09</x:v>
-      </x:c>
-      <x:c r="H178" s="0">
+      <x:c r="F184" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G184" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H184" s="0">
         <x:v>1586603352</x:v>
       </x:c>
-      <x:c r="I178" s="0">
+      <x:c r="I184" s="0">
         <x:v>0.1745</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/yeni-is-anlasmalari/data/yeni-is-anlasmalari.xlsx
+++ b/app/borsa/yeni-is-anlasmalari/data/yeni-is-anlasmalari.xlsx
@@ -43,15 +43,18 @@
     <x:t>Yeni İş İlişkisi / Yıllık Satışlar</x:t>
   </x:si>
   <x:si>
+    <x:t>VBTYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-05-07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>USD</x:t>
+  </x:si>
+  <x:si>
     <x:t>FORTE</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-05-07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>USD</x:t>
-  </x:si>
-  <x:si>
     <x:t>MEKAG</x:t>
   </x:si>
   <x:si>
@@ -61,6 +64,9 @@
     <x:t>EUR</x:t>
   </x:si>
   <x:si>
+    <x:t>TCKRC</x:t>
+  </x:si>
+  <x:si>
     <x:t>AKHAN</x:t>
   </x:si>
   <x:si>
@@ -70,9 +76,6 @@
     <x:t>2026-05-06</x:t>
   </x:si>
   <x:si>
-    <x:t>VBTYZ</x:t>
-  </x:si>
-  <x:si>
     <x:t>ONCSM</x:t>
   </x:si>
   <x:si>
@@ -338,9 +341,6 @@
   </x:si>
   <x:si>
     <x:t>2026-02-12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCKRC</x:t>
   </x:si>
   <x:si>
     <x:t>CGCAM</x:t>
@@ -796,7 +796,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I184"/>
+  <x:dimension ref="A1:I186"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -833,16 +833,16 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>100</x:v>
+        <x:v>24.38</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>-0.7</x:v>
+        <x:v>-0.38</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>3384000</x:v>
+        <x:v>1816317</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
         <x:v>11</x:v>
@@ -851,10 +851,10 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>2427624044</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>0.0627</x:v>
+        <x:v>0.0338</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -862,16 +862,16 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>4.16</x:v>
+        <x:v>98.2</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>0.11</x:v>
+        <x:v>-1.8</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>1178000</x:v>
+        <x:v>3384000</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
         <x:v>11</x:v>
@@ -880,10 +880,10 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>2875634546</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>0.0185</x:v>
+        <x:v>0.0627</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -891,57 +891,57 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>7.89</x:v>
+        <x:v>4.16</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>0.71</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>1180000</x:v>
+        <x:v>1178000</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G4" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>2322993973</x:v>
+        <x:v>2875634546</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>0.0268</x:v>
+        <x:v>0.0185</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
       <x:c r="A5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>29.16</x:v>
+        <x:v>7.69</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>0.32</x:v>
+        <x:v>-0.2</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>26910</x:v>
+        <x:v>1180000</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G5" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>7297855153</x:v>
+        <x:v>2322993973</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>0.0002</x:v>
+        <x:v>0.0268</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -949,16 +949,16 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>57.05</x:v>
+        <x:v>111.7</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>-1.45</x:v>
+        <x:v>-0.1</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>2517084</x:v>
+        <x:v>1220000</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
         <x:v>11</x:v>
@@ -967,27 +967,27 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>2988208362</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>0.0269</x:v>
+        <x:v>0.0184</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
       <x:c r="A7" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>24.76</x:v>
+        <x:v>28.78</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>2.24</x:v>
+        <x:v>-0.38</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>9600000</x:v>
+        <x:v>26910</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
         <x:v>11</x:v>
@@ -996,155 +996,155 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>2427624044</x:v>
+        <x:v>7297855153</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>0.1785</x:v>
+        <x:v>0.0002</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
       <x:c r="A8" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B8" s="0">
+        <x:v>57.25</x:v>
+      </x:c>
+      <x:c r="C8" s="0">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B8" s="0">
-        <x:v>283</x:v>
-      </x:c>
-      <x:c r="C8" s="0">
-        <x:v>8.75</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="E8" s="0">
-        <x:v>9172451</x:v>
+        <x:v>2517084</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G8" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>709077088</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>0.0129</x:v>
+        <x:v>0.0269</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
       <x:c r="A9" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>37.8</x:v>
+        <x:v>24.38</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>-1.08</x:v>
+        <x:v>-0.38</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>32493961</x:v>
+        <x:v>9600000</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>2026.03</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>17386730041</x:v>
+        <x:v>2427624044</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>0</x:v>
+        <x:v>0.1785</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
       <x:c r="A10" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>84.2</x:v>
+        <x:v>296.75</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>0.6</x:v>
+        <x:v>13.75</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>940002</x:v>
+        <x:v>9172451</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G10" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>709077088</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>0.0121</x:v>
+        <x:v>0.0129</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
       <x:c r="A11" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>136.9</x:v>
+        <x:v>37.6</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>12.4</x:v>
+        <x:v>-0.2</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>920000</x:v>
+        <x:v>32493961</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2026.03</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>3150489640</x:v>
+        <x:v>17386730041</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>0.0154</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
       <x:c r="A12" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>100</x:v>
+        <x:v>86.5</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>-0.7</x:v>
+        <x:v>2.3</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>12100000</x:v>
+        <x:v>940002</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G12" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>0.005</x:v>
+        <x:v>0.0121</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -1152,248 +1152,248 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>428</x:v>
+        <x:v>150.5</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>-6</x:v>
+        <x:v>13.6</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>125100000</x:v>
+        <x:v>920000</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>2026.03</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>184925592000</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>0.0304</x:v>
+        <x:v>0.0154</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
       <x:c r="A14" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>8.8</x:v>
+        <x:v>98.2</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>0.39</x:v>
+        <x:v>-1.8</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>32010000</x:v>
+        <x:v>12100000</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G14" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>10581001663</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>0.1592</x:v>
+        <x:v>0.005</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
       <x:c r="A15" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>29.16</x:v>
+        <x:v>428.5</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>0.32</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>76650</x:v>
+        <x:v>125100000</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2026.03</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>7297855153</x:v>
+        <x:v>184925592000</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>0.0005</x:v>
+        <x:v>0.0304</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
       <x:c r="A16" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>136.9</x:v>
+        <x:v>9.68</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>12.4</x:v>
+        <x:v>0.88</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>915000</x:v>
+        <x:v>32010000</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G16" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>3150489640</x:v>
+        <x:v>10581001663</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>0.0153</x:v>
+        <x:v>0.1592</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
       <x:c r="A17" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>37.8</x:v>
+        <x:v>28.78</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>-1.08</x:v>
+        <x:v>-0.38</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>2136645</x:v>
+        <x:v>76650</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>2026.03</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>17386730041</x:v>
+        <x:v>7297855153</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>0.0055</x:v>
+        <x:v>0.0005</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
       <x:c r="A18" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B18" s="0">
+        <x:v>150.5</x:v>
+      </x:c>
+      <x:c r="C18" s="0">
+        <x:v>13.6</x:v>
+      </x:c>
+      <x:c r="D18" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="B18" s="0">
-        <x:v>5.84</x:v>
-      </x:c>
-      <x:c r="C18" s="0">
-        <x:v>0.42</x:v>
-      </x:c>
-      <x:c r="D18" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="E18" s="0">
-        <x:v>132077304</x:v>
+        <x:v>915000</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G18" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>855070469</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>0.1545</x:v>
+        <x:v>0.0153</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
       <x:c r="A19" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>320.75</x:v>
+        <x:v>37.6</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>3</x:v>
+        <x:v>-0.2</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>51531000</x:v>
+        <x:v>2136645</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2026.03</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>35290767390</x:v>
+        <x:v>17386730041</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>0.0656</x:v>
+        <x:v>0.0055</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
       <x:c r="A20" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>1190</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>2</x:v>
+        <x:v>0.16</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>950978</x:v>
+        <x:v>132077304</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G20" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>1883544167</x:v>
+        <x:v>855070469</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>0.0227</x:v>
+        <x:v>0.1545</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
       <x:c r="A21" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>620.5</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>0.5</x:v>
+        <x:v>5.25</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>100000000</x:v>
+        <x:v>51531000</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
         <x:v>11</x:v>
@@ -1402,143 +1402,143 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>71453576000</x:v>
+        <x:v>35290767390</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>0.0628</x:v>
+        <x:v>0.0656</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
       <x:c r="A22" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>84.2</x:v>
+        <x:v>1200</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>0.6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>286071819</x:v>
+        <x:v>950978</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G22" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>1883544167</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>0.0818</x:v>
+        <x:v>0.0227</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
       <x:c r="A23" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>136.9</x:v>
+        <x:v>601.5</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>12.4</x:v>
+        <x:v>-19</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>883793</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G23" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>3150489640</x:v>
+        <x:v>71453576000</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>0.0148</x:v>
+        <x:v>0.0628</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
       <x:c r="A24" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>57.05</x:v>
+        <x:v>86.5</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>-1.45</x:v>
+        <x:v>2.3</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>606770</x:v>
+        <x:v>286071819</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G24" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>0.0064</x:v>
+        <x:v>0.0818</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
       <x:c r="A25" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B25" s="0">
+        <x:v>150.5</x:v>
+      </x:c>
+      <x:c r="C25" s="0">
+        <x:v>13.6</x:v>
+      </x:c>
+      <x:c r="D25" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="B25" s="0">
-        <x:v>60.5</x:v>
-      </x:c>
-      <x:c r="C25" s="0">
-        <x:v>1.6</x:v>
-      </x:c>
-      <x:c r="D25" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
       <x:c r="E25" s="0">
-        <x:v>505597002</x:v>
+        <x:v>883793</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G25" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>8121300519</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>0.0623</x:v>
+        <x:v>0.0148</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
       <x:c r="A26" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>57.05</x:v>
+        <x:v>57.25</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>-1.45</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>948000</x:v>
+        <x:v>606770</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
         <x:v>11</x:v>
@@ -1550,82 +1550,82 @@
         <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>0.0101</x:v>
+        <x:v>0.0064</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
       <x:c r="A27" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>100</x:v>
+        <x:v>63.15</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>-0.7</x:v>
+        <x:v>2.65</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>622000</x:v>
+        <x:v>505597002</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G27" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>8121300519</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>0.0114</x:v>
+        <x:v>0.0623</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
       <x:c r="A28" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>4.16</x:v>
+        <x:v>57.25</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>0.11</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>983000</x:v>
+        <x:v>948000</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G28" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>2875634546</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>0.018</x:v>
+        <x:v>0.0101</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
       <x:c r="A29" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B29" s="0">
+        <x:v>98.2</x:v>
+      </x:c>
+      <x:c r="C29" s="0">
+        <x:v>-1.8</x:v>
+      </x:c>
+      <x:c r="D29" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="B29" s="0">
-        <x:v>80.25</x:v>
-      </x:c>
-      <x:c r="C29" s="0">
-        <x:v>-1.45</x:v>
-      </x:c>
-      <x:c r="D29" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
       <x:c r="E29" s="0">
-        <x:v>3421818</x:v>
+        <x:v>622000</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
         <x:v>11</x:v>
@@ -1634,56 +1634,56 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>5948036961</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>0.0257</x:v>
+        <x:v>0.0114</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
       <x:c r="A30" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>48.8</x:v>
+        <x:v>4.16</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>-0.6</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>697435</x:v>
+        <x:v>983000</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G30" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>4728937463</x:v>
+        <x:v>2875634546</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>0.0066</x:v>
+        <x:v>0.018</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
       <x:c r="A31" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>73.3</x:v>
+        <x:v>76.85</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>6.65</x:v>
+        <x:v>-3.4</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>4587145</x:v>
+        <x:v>3421818</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
         <x:v>11</x:v>
@@ -1692,27 +1692,27 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>16733157490</x:v>
+        <x:v>5948036961</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>0.0123</x:v>
+        <x:v>0.0257</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
       <x:c r="A32" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>43.74</x:v>
+        <x:v>49.6</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>0.84</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>43200000</x:v>
+        <x:v>697435</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
         <x:v>11</x:v>
@@ -1721,259 +1721,259 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>8236540064</x:v>
+        <x:v>4728937463</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>0.2345</x:v>
+        <x:v>0.0066</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
       <x:c r="A33" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>17.71</x:v>
+        <x:v>80.6</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>-0.04</x:v>
+        <x:v>7.3</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>1200000</x:v>
+        <x:v>4587145</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G33" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>3139850323</x:v>
+        <x:v>16733157490</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>0.0201</x:v>
+        <x:v>0.0123</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
       <x:c r="A34" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>60.5</x:v>
+        <x:v>46.44</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>1.6</x:v>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>247902522</x:v>
+        <x:v>43200000</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G34" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>8121300519</x:v>
+        <x:v>8236540064</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>0.0305</x:v>
+        <x:v>0.2345</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
       <x:c r="A35" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>57.05</x:v>
+        <x:v>19.48</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>-1.45</x:v>
+        <x:v>1.77</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>366000</x:v>
+        <x:v>1200000</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G35" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>3139850323</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>0.0039</x:v>
+        <x:v>0.0201</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
       <x:c r="A36" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>283</x:v>
+        <x:v>63.15</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>8.75</x:v>
+        <x:v>2.65</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>141051834</x:v>
+        <x:v>247902522</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G36" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>709077088</x:v>
+        <x:v>8121300519</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>0.1989</x:v>
+        <x:v>0.0305</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
       <x:c r="A37" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B37" s="0">
+        <x:v>57.25</x:v>
+      </x:c>
+      <x:c r="C37" s="0">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="D37" s="0" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="B37" s="0">
-        <x:v>4.99</x:v>
-      </x:c>
-      <x:c r="C37" s="0">
-        <x:v>-0.13</x:v>
-      </x:c>
-      <x:c r="D37" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
       <x:c r="E37" s="0">
-        <x:v>5096500000</x:v>
+        <x:v>366000</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>19538660616</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>0.2608</x:v>
+        <x:v>0.0039</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
       <x:c r="A38" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B38" s="0">
+        <x:v>296.75</x:v>
+      </x:c>
+      <x:c r="C38" s="0">
+        <x:v>13.75</x:v>
+      </x:c>
+      <x:c r="D38" s="0" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="B38" s="0">
-        <x:v>4.99</x:v>
-      </x:c>
-      <x:c r="C38" s="0">
-        <x:v>-0.13</x:v>
-      </x:c>
-      <x:c r="D38" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
       <x:c r="E38" s="0">
-        <x:v>5096500000</x:v>
+        <x:v>141051834</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>19538660616</x:v>
+        <x:v>709077088</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>0.2608</x:v>
+        <x:v>0.1989</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
       <x:c r="A39" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B39" s="0">
+        <x:v>4.94</x:v>
+      </x:c>
+      <x:c r="C39" s="0">
+        <x:v>-0.05</x:v>
+      </x:c>
+      <x:c r="D39" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E39" s="0">
+        <x:v>5096500000</x:v>
+      </x:c>
+      <x:c r="F39" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B39" s="0">
-        <x:v>37.8</x:v>
-      </x:c>
-      <x:c r="C39" s="0">
-        <x:v>-1.08</x:v>
-      </x:c>
-      <x:c r="D39" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E39" s="0">
-        <x:v>37500000</x:v>
-      </x:c>
-      <x:c r="F39" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="G39" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>16355768622</x:v>
+        <x:v>19538660616</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>0.1024</x:v>
+        <x:v>0.2608</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
       <x:c r="A40" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>265</x:v>
+        <x:v>4.94</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>-0.05</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>2030000</x:v>
+        <x:v>5096500000</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>2159813703</x:v>
+        <x:v>19538660616</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>0.042</x:v>
+        <x:v>0.2608</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
       <x:c r="A41" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>73.3</x:v>
+        <x:v>37.6</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>6.65</x:v>
+        <x:v>-0.2</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>31146246</x:v>
+        <x:v>37500000</x:v>
       </x:c>
       <x:c r="F41" s="0" t="s">
         <x:v>11</x:v>
@@ -1982,10 +1982,10 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>16733157490</x:v>
+        <x:v>16355768622</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>0.0832</x:v>
+        <x:v>0.1024</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1993,77 +1993,77 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>13</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>0.94</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>1000000</x:v>
+        <x:v>2030000</x:v>
       </x:c>
       <x:c r="F42" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G42" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>7221187888</x:v>
+        <x:v>2159813703</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>0.0001</x:v>
+        <x:v>0.042</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
       <x:c r="A43" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>13</x:v>
+        <x:v>80.6</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>0.94</x:v>
+        <x:v>7.3</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>3150000</x:v>
+        <x:v>31146246</x:v>
       </x:c>
       <x:c r="F43" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G43" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>7221187888</x:v>
+        <x:v>16733157490</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>0.0227</x:v>
+        <x:v>0.0832</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
       <x:c r="A44" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>13</x:v>
+        <x:v>12.86</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>0.94</x:v>
+        <x:v>-0.14</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>2690000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="F44" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G44" s="0">
         <x:v>2025.12</x:v>
@@ -2072,82 +2072,82 @@
         <x:v>7221187888</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>0.0166</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
       <x:c r="A45" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>73.3</x:v>
+        <x:v>12.86</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>6.65</x:v>
+        <x:v>-0.14</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>4103000</x:v>
+        <x:v>3150000</x:v>
       </x:c>
       <x:c r="F45" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G45" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>16733157490</x:v>
+        <x:v>7221187888</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>0.0109</x:v>
+        <x:v>0.0227</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
       <x:c r="A46" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>136.9</x:v>
+        <x:v>12.86</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>12.4</x:v>
+        <x:v>-0.14</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>500000</x:v>
+        <x:v>2690000</x:v>
       </x:c>
       <x:c r="F46" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G46" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>3150489640</x:v>
+        <x:v>7221187888</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>0.0083</x:v>
+        <x:v>0.0166</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
       <x:c r="A47" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>57.05</x:v>
+        <x:v>80.6</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>-1.45</x:v>
+        <x:v>7.3</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>872928</x:v>
+        <x:v>4103000</x:v>
       </x:c>
       <x:c r="F47" s="0" t="s">
         <x:v>11</x:v>
@@ -2156,578 +2156,578 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>16733157490</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>0.0092</x:v>
+        <x:v>0.0109</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
       <x:c r="A48" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>100</x:v>
+        <x:v>150.5</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>-0.7</x:v>
+        <x:v>13.6</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>21250000</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="F48" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G48" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>0.0087</x:v>
+        <x:v>0.0083</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
       <x:c r="A49" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>60.5</x:v>
+        <x:v>57.25</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>1.6</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>67690912</x:v>
+        <x:v>872928</x:v>
       </x:c>
       <x:c r="F49" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G49" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>8121300519</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>0.0083</x:v>
+        <x:v>0.0092</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
       <x:c r="A50" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>37.8</x:v>
+        <x:v>98.2</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>-1.08</x:v>
+        <x:v>-1.8</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>65458848</x:v>
+        <x:v>21250000</x:v>
       </x:c>
       <x:c r="F50" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G50" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>16355768622</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>0.1784</x:v>
+        <x:v>0.0087</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
       <x:c r="A51" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B51" s="0">
+        <x:v>63.15</x:v>
+      </x:c>
+      <x:c r="C51" s="0">
+        <x:v>2.65</x:v>
+      </x:c>
+      <x:c r="D51" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="B51" s="0">
-        <x:v>24.84</x:v>
-      </x:c>
-      <x:c r="C51" s="0">
-        <x:v>0.16</x:v>
-      </x:c>
-      <x:c r="D51" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
       <x:c r="E51" s="0">
-        <x:v>689500000</x:v>
+        <x:v>67690912</x:v>
       </x:c>
       <x:c r="F51" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G51" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>884571536</x:v>
+        <x:v>8121300519</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>0.7795</x:v>
+        <x:v>0.0083</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
       <x:c r="A52" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>7.89</x:v>
+        <x:v>37.6</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>0.71</x:v>
+        <x:v>-0.2</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>3024490</x:v>
+        <x:v>65458848</x:v>
       </x:c>
       <x:c r="F52" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G52" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>2322993973</x:v>
+        <x:v>16355768622</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>0.0671</x:v>
+        <x:v>0.1784</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:9">
       <x:c r="A53" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B53" s="0">
-        <x:v>7.89</x:v>
+        <x:v>24.9</x:v>
       </x:c>
       <x:c r="C53" s="0">
-        <x:v>0.71</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E53" s="0">
-        <x:v>4510336</x:v>
+        <x:v>689500000</x:v>
       </x:c>
       <x:c r="F53" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G53" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H53" s="0">
-        <x:v>2322993973</x:v>
+        <x:v>884571536</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>0.0865</x:v>
+        <x:v>0.7795</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:9">
       <x:c r="A54" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B54" s="0">
-        <x:v>58.4</x:v>
+        <x:v>7.69</x:v>
       </x:c>
       <x:c r="C54" s="0">
-        <x:v>1.9</x:v>
+        <x:v>-0.2</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E54" s="0">
-        <x:v>205000000</x:v>
+        <x:v>3024490</x:v>
       </x:c>
       <x:c r="F54" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G54" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>20597209000</x:v>
+        <x:v>2322993973</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>0.4434</x:v>
+        <x:v>0.0671</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:9">
       <x:c r="A55" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B55" s="0">
-        <x:v>306</x:v>
+        <x:v>7.69</x:v>
       </x:c>
       <x:c r="C55" s="0">
-        <x:v>-12</x:v>
+        <x:v>-0.2</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E55" s="0">
-        <x:v>305000000</x:v>
+        <x:v>4510336</x:v>
       </x:c>
       <x:c r="F55" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G55" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H55" s="0">
-        <x:v>400439646</x:v>
+        <x:v>2322993973</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>0.7617</x:v>
+        <x:v>0.0865</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:9">
       <x:c r="A56" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B56" s="0">
-        <x:v>84.2</x:v>
+        <x:v>61.4</x:v>
       </x:c>
       <x:c r="C56" s="0">
-        <x:v>0.6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E56" s="0">
-        <x:v>11700000</x:v>
+        <x:v>205000000</x:v>
       </x:c>
       <x:c r="F56" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G56" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H56" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>20597209000</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>0.1718</x:v>
+        <x:v>0.4434</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:9">
       <x:c r="A57" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B57" s="0">
-        <x:v>265</x:v>
+        <x:v>310.25</x:v>
       </x:c>
       <x:c r="C57" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>4.25</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E57" s="0">
-        <x:v>1900000</x:v>
+        <x:v>305000000</x:v>
       </x:c>
       <x:c r="F57" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G57" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H57" s="0">
-        <x:v>2159813703</x:v>
+        <x:v>400439646</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>0.0391</x:v>
+        <x:v>0.7617</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:9">
       <x:c r="A58" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B58" s="0">
-        <x:v>4.16</x:v>
+        <x:v>86.5</x:v>
       </x:c>
       <x:c r="C58" s="0">
-        <x:v>0.11</x:v>
+        <x:v>2.3</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E58" s="0">
-        <x:v>1670000</x:v>
+        <x:v>11700000</x:v>
       </x:c>
       <x:c r="F58" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G58" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H58" s="0">
-        <x:v>2875634546</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>0.0298</x:v>
+        <x:v>0.1718</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:9">
       <x:c r="A59" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B59" s="0">
-        <x:v>24.84</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="C59" s="0">
-        <x:v>0.16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="E59" s="0">
-        <x:v>48895800</x:v>
+        <x:v>1900000</x:v>
       </x:c>
       <x:c r="F59" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G59" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H59" s="0">
-        <x:v>884571536</x:v>
+        <x:v>2159813703</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>0.0553</x:v>
+        <x:v>0.0391</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:9">
       <x:c r="A60" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B60" s="0">
-        <x:v>24.84</x:v>
+        <x:v>4.16</x:v>
       </x:c>
       <x:c r="C60" s="0">
-        <x:v>0.16</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="E60" s="0">
-        <x:v>689500000</x:v>
+        <x:v>1670000</x:v>
       </x:c>
       <x:c r="F60" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G60" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H60" s="0">
-        <x:v>884571536</x:v>
+        <x:v>2875634546</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>0.7795</x:v>
+        <x:v>0.0298</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:9">
       <x:c r="A61" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B61" s="0">
+        <x:v>24.9</x:v>
+      </x:c>
+      <x:c r="C61" s="0">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="D61" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="B61" s="0">
-        <x:v>48.8</x:v>
-      </x:c>
-      <x:c r="C61" s="0">
-        <x:v>2.72</x:v>
-      </x:c>
-      <x:c r="D61" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
       <x:c r="E61" s="0">
-        <x:v>3102911</x:v>
+        <x:v>48895800</x:v>
       </x:c>
       <x:c r="F61" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G61" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H61" s="0">
-        <x:v>2907014564</x:v>
+        <x:v>884571536</x:v>
       </x:c>
       <x:c r="I61" s="0">
-        <x:v>0.0475</x:v>
+        <x:v>0.0553</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:9">
       <x:c r="A62" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B62" s="0">
-        <x:v>25.94</x:v>
+        <x:v>24.9</x:v>
       </x:c>
       <x:c r="C62" s="0">
-        <x:v>1.3</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E62" s="0">
-        <x:v>13000000</x:v>
+        <x:v>689500000</x:v>
       </x:c>
       <x:c r="F62" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G62" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H62" s="0">
-        <x:v>11834942581</x:v>
+        <x:v>884571536</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>0.0563</x:v>
+        <x:v>0.7795</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:9">
       <x:c r="A63" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B63" s="0">
-        <x:v>80.25</x:v>
+        <x:v>48.28</x:v>
       </x:c>
       <x:c r="C63" s="0">
-        <x:v>-1.45</x:v>
+        <x:v>-0.52</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E63" s="0">
-        <x:v>6800000</x:v>
+        <x:v>3102911</x:v>
       </x:c>
       <x:c r="F63" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G63" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H63" s="0">
-        <x:v>5948036961</x:v>
+        <x:v>2907014564</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>0.0583</x:v>
+        <x:v>0.0475</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:9">
       <x:c r="A64" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B64" s="0">
-        <x:v>58.4</x:v>
+        <x:v>25.78</x:v>
       </x:c>
       <x:c r="C64" s="0">
-        <x:v>1.9</x:v>
+        <x:v>-0.16</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E64" s="0">
-        <x:v>36750000</x:v>
+        <x:v>13000000</x:v>
       </x:c>
       <x:c r="F64" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G64" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H64" s="0">
-        <x:v>20597209000</x:v>
+        <x:v>11834942581</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>0.0793</x:v>
+        <x:v>0.0563</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:9">
       <x:c r="A65" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B65" s="0">
-        <x:v>1190</x:v>
+        <x:v>76.85</x:v>
       </x:c>
       <x:c r="C65" s="0">
-        <x:v>2</x:v>
+        <x:v>-3.4</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
         <x:v>65</x:v>
       </x:c>
       <x:c r="E65" s="0">
-        <x:v>3867260</x:v>
+        <x:v>6800000</x:v>
       </x:c>
       <x:c r="F65" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G65" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H65" s="0">
-        <x:v>1883544167</x:v>
+        <x:v>5948036961</x:v>
       </x:c>
       <x:c r="I65" s="0">
-        <x:v>0.0912</x:v>
+        <x:v>0.0583</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:9">
       <x:c r="A66" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B66" s="0">
-        <x:v>68.75</x:v>
+        <x:v>61.4</x:v>
       </x:c>
       <x:c r="C66" s="0">
-        <x:v>1.5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E66" s="0">
-        <x:v>1498029716</x:v>
+        <x:v>36750000</x:v>
       </x:c>
       <x:c r="F66" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G66" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H66" s="0">
-        <x:v>12030341104</x:v>
+        <x:v>20597209000</x:v>
       </x:c>
       <x:c r="I66" s="0">
-        <x:v>0.1245</x:v>
+        <x:v>0.0793</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:9">
       <x:c r="A67" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B67" s="0">
-        <x:v>37.8</x:v>
+        <x:v>1200</x:v>
       </x:c>
       <x:c r="C67" s="0">
-        <x:v>-1.08</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E67" s="0">
-        <x:v>48000000</x:v>
+        <x:v>3867260</x:v>
       </x:c>
       <x:c r="F67" s="0" t="s">
         <x:v>11</x:v>
@@ -2736,56 +2736,56 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H67" s="0">
-        <x:v>16355768622</x:v>
+        <x:v>1883544167</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>0.1301</x:v>
+        <x:v>0.0912</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:9">
       <x:c r="A68" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B68" s="0">
-        <x:v>84.2</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C68" s="0">
-        <x:v>0.6</x:v>
+        <x:v>-0.75</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
         <x:v>68</x:v>
       </x:c>
       <x:c r="E68" s="0">
-        <x:v>279699629</x:v>
+        <x:v>1498029716</x:v>
       </x:c>
       <x:c r="F68" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G68" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H68" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>12030341104</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>0.08</x:v>
+        <x:v>0.1245</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:9">
       <x:c r="A69" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B69" s="0">
-        <x:v>16.44</x:v>
+        <x:v>37.6</x:v>
       </x:c>
       <x:c r="C69" s="0">
-        <x:v>0.76</x:v>
+        <x:v>-0.2</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
         <x:v>68</x:v>
       </x:c>
       <x:c r="E69" s="0">
-        <x:v>7971822</x:v>
+        <x:v>48000000</x:v>
       </x:c>
       <x:c r="F69" s="0" t="s">
         <x:v>11</x:v>
@@ -2794,126 +2794,126 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H69" s="0">
-        <x:v>4675369372</x:v>
+        <x:v>16355768622</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>0.0756</x:v>
+        <x:v>0.1301</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:9">
       <x:c r="A70" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B70" s="0">
-        <x:v>57.05</x:v>
+        <x:v>86.5</x:v>
       </x:c>
       <x:c r="C70" s="0">
-        <x:v>-1.45</x:v>
+        <x:v>2.3</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E70" s="0">
-        <x:v>1104000</x:v>
+        <x:v>279699629</x:v>
       </x:c>
       <x:c r="F70" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G70" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H70" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>0.0116</x:v>
+        <x:v>0.08</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:9">
       <x:c r="A71" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B71" s="0">
-        <x:v>24.84</x:v>
+        <x:v>16.8</x:v>
       </x:c>
       <x:c r="C71" s="0">
-        <x:v>0.16</x:v>
+        <x:v>0.36</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E71" s="0">
-        <x:v>48895800</x:v>
+        <x:v>7971822</x:v>
       </x:c>
       <x:c r="F71" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G71" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H71" s="0">
-        <x:v>884571536</x:v>
+        <x:v>4675369372</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>0.0553</x:v>
+        <x:v>0.0756</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:9">
       <x:c r="A72" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B72" s="0">
-        <x:v>3.46</x:v>
+        <x:v>57.25</x:v>
       </x:c>
       <x:c r="C72" s="0">
-        <x:v>-0.01</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E72" s="0">
-        <x:v>191089413</x:v>
+        <x:v>1104000</x:v>
       </x:c>
       <x:c r="F72" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G72" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H72" s="0">
-        <x:v>9665356715</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>0.0198</x:v>
+        <x:v>0.0116</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:9">
       <x:c r="A73" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B73" s="0">
-        <x:v>3.46</x:v>
+        <x:v>24.9</x:v>
       </x:c>
       <x:c r="C73" s="0">
-        <x:v>-0.01</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E73" s="0">
-        <x:v>605627160</x:v>
+        <x:v>48895800</x:v>
       </x:c>
       <x:c r="F73" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G73" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H73" s="0">
-        <x:v>9665356715</x:v>
+        <x:v>884571536</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>0.0627</x:v>
+        <x:v>0.0553</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:9">
@@ -2921,190 +2921,190 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="B74" s="0">
-        <x:v>27.46</x:v>
+        <x:v>3.41</x:v>
       </x:c>
       <x:c r="C74" s="0">
-        <x:v>0.26</x:v>
+        <x:v>-0.05</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E74" s="0">
-        <x:v>2356546000</x:v>
+        <x:v>191089413</x:v>
       </x:c>
       <x:c r="F74" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G74" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H74" s="0">
-        <x:v>7708004248</x:v>
+        <x:v>9665356715</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>0.3057</x:v>
+        <x:v>0.0198</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:9">
       <x:c r="A75" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B75" s="0">
-        <x:v>17.71</x:v>
+        <x:v>3.41</x:v>
       </x:c>
       <x:c r="C75" s="0">
-        <x:v>-0.04</x:v>
+        <x:v>-0.05</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E75" s="0">
-        <x:v>431250</x:v>
+        <x:v>605627160</x:v>
       </x:c>
       <x:c r="F75" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G75" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H75" s="0">
-        <x:v>3139850323</x:v>
+        <x:v>9665356715</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>0.0071</x:v>
+        <x:v>0.0627</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:9">
       <x:c r="A76" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B76" s="0">
-        <x:v>17.71</x:v>
+        <x:v>27.9</x:v>
       </x:c>
       <x:c r="C76" s="0">
-        <x:v>-0.04</x:v>
+        <x:v>0.44</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E76" s="0">
-        <x:v>800000</x:v>
+        <x:v>2356546000</x:v>
       </x:c>
       <x:c r="F76" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G76" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H76" s="0">
-        <x:v>3139850323</x:v>
+        <x:v>7708004248</x:v>
       </x:c>
       <x:c r="I76" s="0">
-        <x:v>0.0131</x:v>
+        <x:v>0.3057</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:9">
       <x:c r="A77" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B77" s="0">
-        <x:v>60.5</x:v>
+        <x:v>19.48</x:v>
       </x:c>
       <x:c r="C77" s="0">
-        <x:v>1.6</x:v>
+        <x:v>1.77</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E77" s="0">
-        <x:v>127172130</x:v>
+        <x:v>431250</x:v>
       </x:c>
       <x:c r="F77" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G77" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H77" s="0">
-        <x:v>8121300519</x:v>
+        <x:v>3139850323</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>0.0157</x:v>
+        <x:v>0.0071</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:9">
       <x:c r="A78" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B78" s="0">
-        <x:v>48.8</x:v>
+        <x:v>19.48</x:v>
       </x:c>
       <x:c r="C78" s="0">
-        <x:v>-0.6</x:v>
+        <x:v>1.77</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E78" s="0">
-        <x:v>42625000</x:v>
+        <x:v>800000</x:v>
       </x:c>
       <x:c r="F78" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G78" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H78" s="0">
-        <x:v>4728937463</x:v>
+        <x:v>3139850323</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>0.3994</x:v>
+        <x:v>0.0131</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:9">
       <x:c r="A79" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B79" s="0">
-        <x:v>100</x:v>
+        <x:v>63.15</x:v>
       </x:c>
       <x:c r="C79" s="0">
-        <x:v>-0.7</x:v>
+        <x:v>2.65</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
         <x:v>73</x:v>
       </x:c>
       <x:c r="E79" s="0">
-        <x:v>1486000</x:v>
+        <x:v>127172130</x:v>
       </x:c>
       <x:c r="F79" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G79" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H79" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>8121300519</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>0.027</x:v>
+        <x:v>0.0157</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:9">
       <x:c r="A80" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B80" s="0">
-        <x:v>320.75</x:v>
+        <x:v>49.6</x:v>
       </x:c>
       <x:c r="C80" s="0">
-        <x:v>3</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
         <x:v>73</x:v>
       </x:c>
       <x:c r="E80" s="0">
-        <x:v>768864700</x:v>
+        <x:v>42625000</x:v>
       </x:c>
       <x:c r="F80" s="0" t="s">
         <x:v>11</x:v>
@@ -3113,27 +3113,27 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H80" s="0">
-        <x:v>35290767390</x:v>
+        <x:v>4728937463</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>0.9648</x:v>
+        <x:v>0.3994</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:9">
       <x:c r="A81" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B81" s="0">
-        <x:v>73.3</x:v>
+        <x:v>98.2</x:v>
       </x:c>
       <x:c r="C81" s="0">
-        <x:v>6.65</x:v>
+        <x:v>-1.8</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E81" s="0">
-        <x:v>15938617</x:v>
+        <x:v>1486000</x:v>
       </x:c>
       <x:c r="F81" s="0" t="s">
         <x:v>11</x:v>
@@ -3142,56 +3142,56 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H81" s="0">
-        <x:v>16733157490</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I81" s="0">
-        <x:v>0.0422</x:v>
+        <x:v>0.027</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:9">
       <x:c r="A82" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B82" s="0">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c r="C82" s="0">
+        <x:v>5.25</x:v>
+      </x:c>
+      <x:c r="D82" s="0" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="B82" s="0">
-        <x:v>14.85</x:v>
-      </x:c>
-      <x:c r="C82" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D82" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
       <x:c r="E82" s="0">
-        <x:v>30438120</x:v>
+        <x:v>768864700</x:v>
       </x:c>
       <x:c r="F82" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G82" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H82" s="0">
-        <x:v>3159124121</x:v>
+        <x:v>35290767390</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>0</x:v>
+        <x:v>0.9648</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:9">
       <x:c r="A83" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B83" s="0">
-        <x:v>265</x:v>
+        <x:v>80.6</x:v>
       </x:c>
       <x:c r="C83" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>7.3</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E83" s="0">
-        <x:v>3900000</x:v>
+        <x:v>15938617</x:v>
       </x:c>
       <x:c r="F83" s="0" t="s">
         <x:v>11</x:v>
@@ -3200,53 +3200,53 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H83" s="0">
-        <x:v>2159813703</x:v>
+        <x:v>16733157490</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>0.0797</x:v>
+        <x:v>0.0422</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:9">
       <x:c r="A84" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B84" s="0">
-        <x:v>265</x:v>
+        <x:v>14.99</x:v>
       </x:c>
       <x:c r="C84" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>0.14</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
         <x:v>76</x:v>
       </x:c>
       <x:c r="E84" s="0">
-        <x:v>2104908</x:v>
+        <x:v>30438120</x:v>
       </x:c>
       <x:c r="F84" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G84" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H84" s="0">
-        <x:v>2159813703</x:v>
+        <x:v>3159124121</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>0.043</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:9">
       <x:c r="A85" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B85" s="0">
-        <x:v>29.16</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="C85" s="0">
-        <x:v>0.32</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E85" s="0">
         <x:v>3900000</x:v>
@@ -3258,126 +3258,126 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H85" s="0">
-        <x:v>7297855153</x:v>
+        <x:v>2159813703</x:v>
       </x:c>
       <x:c r="I85" s="0">
-        <x:v>0.0236</x:v>
+        <x:v>0.0797</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:9">
       <x:c r="A86" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B86" s="0">
-        <x:v>5.84</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="C86" s="0">
-        <x:v>0.42</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
         <x:v>77</x:v>
       </x:c>
       <x:c r="E86" s="0">
-        <x:v>496968445</x:v>
+        <x:v>2104908</x:v>
       </x:c>
       <x:c r="F86" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G86" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H86" s="0">
-        <x:v>855070469</x:v>
+        <x:v>2159813703</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>0.5812</x:v>
+        <x:v>0.043</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:9">
       <x:c r="A87" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B87" s="0">
-        <x:v>12.57</x:v>
+        <x:v>28.78</x:v>
       </x:c>
       <x:c r="C87" s="0">
-        <x:v>0.08</x:v>
+        <x:v>-0.38</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
         <x:v>77</x:v>
       </x:c>
       <x:c r="E87" s="0">
-        <x:v>108750000</x:v>
+        <x:v>3900000</x:v>
       </x:c>
       <x:c r="F87" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G87" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H87" s="0">
-        <x:v>1982520183</x:v>
+        <x:v>7297855153</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>0.0549</x:v>
+        <x:v>0.0236</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:9">
       <x:c r="A88" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B88" s="0">
-        <x:v>136.9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C88" s="0">
-        <x:v>12.4</x:v>
+        <x:v>0.16</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E88" s="0">
-        <x:v>1605197</x:v>
+        <x:v>496968445</x:v>
       </x:c>
       <x:c r="F88" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G88" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H88" s="0">
-        <x:v>0</x:v>
+        <x:v>855070469</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>0</x:v>
+        <x:v>0.5812</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:9">
       <x:c r="A89" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B89" s="0">
-        <x:v>428</x:v>
+        <x:v>12.53</x:v>
       </x:c>
       <x:c r="C89" s="0">
-        <x:v>-6</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E89" s="0">
-        <x:v>54600000</x:v>
+        <x:v>108750000</x:v>
       </x:c>
       <x:c r="F89" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G89" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H89" s="0">
-        <x:v>180444938000</x:v>
+        <x:v>1982520183</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>0.0133</x:v>
+        <x:v>0.0549</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:9">
@@ -3385,45 +3385,45 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B90" s="0">
-        <x:v>428</x:v>
+        <x:v>150.5</x:v>
       </x:c>
       <x:c r="C90" s="0">
-        <x:v>-6</x:v>
+        <x:v>13.6</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="E90" s="0">
-        <x:v>111850000</x:v>
+        <x:v>1605197</x:v>
       </x:c>
       <x:c r="F90" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G90" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H90" s="0">
-        <x:v>180444938000</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I90" s="0">
-        <x:v>0.0273</x:v>
+        <x:v>0.0257</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:9">
       <x:c r="A91" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B91" s="0">
-        <x:v>57.05</x:v>
+        <x:v>428.5</x:v>
       </x:c>
       <x:c r="C91" s="0">
-        <x:v>-1.45</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E91" s="0">
-        <x:v>803090</x:v>
+        <x:v>54600000</x:v>
       </x:c>
       <x:c r="F91" s="0" t="s">
         <x:v>11</x:v>
@@ -3432,56 +3432,56 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H91" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>180444938000</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>0.0084</x:v>
+        <x:v>0.0133</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:9">
       <x:c r="A92" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B92" s="0">
-        <x:v>27.46</x:v>
+        <x:v>428.5</x:v>
       </x:c>
       <x:c r="C92" s="0">
-        <x:v>0.26</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
         <x:v>81</x:v>
       </x:c>
       <x:c r="E92" s="0">
-        <x:v>2356546000</x:v>
+        <x:v>111850000</x:v>
       </x:c>
       <x:c r="F92" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G92" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H92" s="0">
-        <x:v>7708004248</x:v>
+        <x:v>180444938000</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>0.3057</x:v>
+        <x:v>0.0273</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:9">
       <x:c r="A93" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B93" s="0">
-        <x:v>1190</x:v>
+        <x:v>57.25</x:v>
       </x:c>
       <x:c r="C93" s="0">
-        <x:v>2</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E93" s="0">
-        <x:v>875400</x:v>
+        <x:v>803090</x:v>
       </x:c>
       <x:c r="F93" s="0" t="s">
         <x:v>11</x:v>
@@ -3490,752 +3490,752 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H93" s="0">
-        <x:v>1883544167</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>0.0205</x:v>
+        <x:v>0.0084</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:9">
       <x:c r="A94" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B94" s="0">
-        <x:v>27.76</x:v>
+        <x:v>27.9</x:v>
       </x:c>
       <x:c r="C94" s="0">
-        <x:v>1.04</x:v>
+        <x:v>0.44</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E94" s="0">
-        <x:v>330000000</x:v>
+        <x:v>2356546000</x:v>
       </x:c>
       <x:c r="F94" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G94" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H94" s="0">
-        <x:v>5287314404</x:v>
+        <x:v>7708004248</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>0.0624</x:v>
+        <x:v>0.3057</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:9">
       <x:c r="A95" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B95" s="0">
-        <x:v>84.2</x:v>
+        <x:v>1200</x:v>
       </x:c>
       <x:c r="C95" s="0">
-        <x:v>0.6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E95" s="0">
-        <x:v>11700000</x:v>
+        <x:v>875400</x:v>
       </x:c>
       <x:c r="F95" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G95" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H95" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>1883544167</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>0.1705</x:v>
+        <x:v>0.0205</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:9">
       <x:c r="A96" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B96" s="0">
-        <x:v>8.8</x:v>
+        <x:v>27.5</x:v>
       </x:c>
       <x:c r="C96" s="0">
-        <x:v>0.39</x:v>
+        <x:v>-0.26</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
         <x:v>85</x:v>
       </x:c>
       <x:c r="E96" s="0">
-        <x:v>4000000000</x:v>
+        <x:v>330000000</x:v>
       </x:c>
       <x:c r="F96" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G96" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H96" s="0">
-        <x:v>10581001663</x:v>
+        <x:v>5287314404</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>0.378</x:v>
+        <x:v>0.0624</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:9">
       <x:c r="A97" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B97" s="0">
-        <x:v>17.71</x:v>
+        <x:v>86.5</x:v>
       </x:c>
       <x:c r="C97" s="0">
-        <x:v>-0.04</x:v>
+        <x:v>2.3</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
         <x:v>86</x:v>
       </x:c>
       <x:c r="E97" s="0">
-        <x:v>1086598</x:v>
+        <x:v>11700000</x:v>
       </x:c>
       <x:c r="F97" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G97" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H97" s="0">
-        <x:v>2020891371</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>0.0274</x:v>
+        <x:v>0.1705</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:9">
       <x:c r="A98" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B98" s="0">
-        <x:v>16.44</x:v>
+        <x:v>9.68</x:v>
       </x:c>
       <x:c r="C98" s="0">
-        <x:v>0.76</x:v>
+        <x:v>0.88</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E98" s="0">
-        <x:v>216000000</x:v>
+        <x:v>4000000000</x:v>
       </x:c>
       <x:c r="F98" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G98" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H98" s="0">
-        <x:v>3025063909</x:v>
+        <x:v>10581001663</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>0.0714</x:v>
+        <x:v>0.378</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:9">
       <x:c r="A99" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B99" s="0">
-        <x:v>57.05</x:v>
+        <x:v>19.48</x:v>
       </x:c>
       <x:c r="C99" s="0">
-        <x:v>-1.45</x:v>
+        <x:v>1.77</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
         <x:v>87</x:v>
       </x:c>
       <x:c r="E99" s="0">
-        <x:v>7292916</x:v>
+        <x:v>1086598</x:v>
       </x:c>
       <x:c r="F99" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G99" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H99" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>2020891371</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>0.0758</x:v>
+        <x:v>0.0274</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:9">
       <x:c r="A100" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B100" s="0">
+        <x:v>16.8</x:v>
+      </x:c>
+      <x:c r="C100" s="0">
+        <x:v>0.36</x:v>
+      </x:c>
+      <x:c r="D100" s="0" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="B100" s="0">
-        <x:v>30.06</x:v>
-      </x:c>
-      <x:c r="C100" s="0">
-        <x:v>1.26</x:v>
-      </x:c>
-      <x:c r="D100" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
       <x:c r="E100" s="0">
-        <x:v>250000</x:v>
+        <x:v>216000000</x:v>
       </x:c>
       <x:c r="F100" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G100" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H100" s="0">
-        <x:v>448686813</x:v>
+        <x:v>3025063909</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>0.0006</x:v>
+        <x:v>0.0714</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:9">
       <x:c r="A101" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B101" s="0">
-        <x:v>73.3</x:v>
+        <x:v>57.25</x:v>
       </x:c>
       <x:c r="C101" s="0">
-        <x:v>6.65</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E101" s="0">
-        <x:v>36900000</x:v>
+        <x:v>7292916</x:v>
       </x:c>
       <x:c r="F101" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G101" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H101" s="0">
-        <x:v>10597063406</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>0.1527</x:v>
+        <x:v>0.0758</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:9">
       <x:c r="A102" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B102" s="0">
+        <x:v>31.12</x:v>
+      </x:c>
+      <x:c r="C102" s="0">
+        <x:v>1.06</x:v>
+      </x:c>
+      <x:c r="D102" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="B102" s="0">
-        <x:v>71.15</x:v>
-      </x:c>
-      <x:c r="C102" s="0">
-        <x:v>2.55</x:v>
-      </x:c>
-      <x:c r="D102" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="E102" s="0">
-        <x:v>3800000</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="F102" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G102" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H102" s="0">
-        <x:v>832031190</x:v>
+        <x:v>448686813</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>0.2002</x:v>
+        <x:v>0.0006</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:9">
       <x:c r="A103" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B103" s="0">
-        <x:v>5.84</x:v>
+        <x:v>80.6</x:v>
       </x:c>
       <x:c r="C103" s="0">
-        <x:v>0.42</x:v>
+        <x:v>7.3</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E103" s="0">
-        <x:v>2100000</x:v>
+        <x:v>36900000</x:v>
       </x:c>
       <x:c r="F103" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G103" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H103" s="0">
-        <x:v>855070469</x:v>
+        <x:v>10597063406</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>0.1076</x:v>
+        <x:v>0.1527</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:9">
       <x:c r="A104" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B104" s="0">
-        <x:v>57.05</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C104" s="0">
-        <x:v>-1.45</x:v>
+        <x:v>0.85</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
         <x:v>92</x:v>
       </x:c>
       <x:c r="E104" s="0">
-        <x:v>22928077</x:v>
+        <x:v>3800000</x:v>
       </x:c>
       <x:c r="F104" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G104" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H104" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>832031190</x:v>
       </x:c>
       <x:c r="I104" s="0">
-        <x:v>0.2378</x:v>
+        <x:v>0.2002</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:9">
       <x:c r="A105" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B105" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C105" s="0">
+        <x:v>0.16</x:v>
+      </x:c>
+      <x:c r="D105" s="0" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="B105" s="0">
-        <x:v>30.42</x:v>
-      </x:c>
-      <x:c r="C105" s="0">
-        <x:v>0.72</x:v>
-      </x:c>
-      <x:c r="D105" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
       <x:c r="E105" s="0">
-        <x:v>547462013</x:v>
+        <x:v>2100000</x:v>
       </x:c>
       <x:c r="F105" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G105" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H105" s="0">
-        <x:v>0</x:v>
+        <x:v>855070469</x:v>
       </x:c>
       <x:c r="I105" s="0">
-        <x:v>0</x:v>
+        <x:v>0.1076</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:9">
       <x:c r="A106" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B106" s="0">
+        <x:v>57.25</x:v>
+      </x:c>
+      <x:c r="C106" s="0">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="D106" s="0" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="B106" s="0">
-        <x:v>30.42</x:v>
-      </x:c>
-      <x:c r="C106" s="0">
-        <x:v>0.72</x:v>
-      </x:c>
-      <x:c r="D106" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
       <x:c r="E106" s="0">
-        <x:v>10567948</x:v>
+        <x:v>22928077</x:v>
       </x:c>
       <x:c r="F106" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G106" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H106" s="0">
-        <x:v>0</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>0</x:v>
+        <x:v>0.2378</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:9">
       <x:c r="A107" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B107" s="0">
-        <x:v>84.2</x:v>
+        <x:v>31.08</x:v>
       </x:c>
       <x:c r="C107" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.66</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E107" s="0">
-        <x:v>8300000</x:v>
+        <x:v>547462013</x:v>
       </x:c>
       <x:c r="F107" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G107" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H107" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>0.1228</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:9">
       <x:c r="A108" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B108" s="0">
-        <x:v>58.4</x:v>
+        <x:v>31.08</x:v>
       </x:c>
       <x:c r="C108" s="0">
-        <x:v>1.9</x:v>
+        <x:v>0.66</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E108" s="0">
-        <x:v>3000000</x:v>
+        <x:v>10567948</x:v>
       </x:c>
       <x:c r="F108" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G108" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H108" s="0">
-        <x:v>20597209000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I108" s="0">
-        <x:v>0.0064</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:9">
       <x:c r="A109" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B109" s="0">
+        <x:v>86.5</x:v>
+      </x:c>
+      <x:c r="C109" s="0">
+        <x:v>2.3</x:v>
+      </x:c>
+      <x:c r="D109" s="0" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="B109" s="0">
-        <x:v>37.22</x:v>
-      </x:c>
-      <x:c r="C109" s="0">
-        <x:v>0.14</x:v>
-      </x:c>
-      <x:c r="D109" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
       <x:c r="E109" s="0">
-        <x:v>26640000</x:v>
+        <x:v>8300000</x:v>
       </x:c>
       <x:c r="F109" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G109" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H109" s="0">
-        <x:v>3277373640</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>0.356</x:v>
+        <x:v>0.1228</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:9">
       <x:c r="A110" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B110" s="0">
-        <x:v>6.32</x:v>
+        <x:v>61.4</x:v>
       </x:c>
       <x:c r="C110" s="0">
-        <x:v>0.19</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E110" s="0">
-        <x:v>13107198</x:v>
+        <x:v>3000000</x:v>
       </x:c>
       <x:c r="F110" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G110" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H110" s="0">
-        <x:v>1627872951</x:v>
+        <x:v>20597209000</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>0.0081</x:v>
+        <x:v>0.0064</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:9">
       <x:c r="A111" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B111" s="0">
-        <x:v>84.2</x:v>
+        <x:v>40.4</x:v>
       </x:c>
       <x:c r="C111" s="0">
-        <x:v>0.6</x:v>
+        <x:v>3.18</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E111" s="0">
-        <x:v>237500000</x:v>
+        <x:v>26640000</x:v>
       </x:c>
       <x:c r="F111" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G111" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H111" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>3277373640</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>0.0679</x:v>
+        <x:v>0.356</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:9">
       <x:c r="A112" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B112" s="0">
-        <x:v>60.5</x:v>
+        <x:v>6.3</x:v>
       </x:c>
       <x:c r="C112" s="0">
-        <x:v>1.6</x:v>
+        <x:v>-0.02</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E112" s="0">
-        <x:v>147892538</x:v>
+        <x:v>13107198</x:v>
       </x:c>
       <x:c r="F112" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G112" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H112" s="0">
-        <x:v>7257990064</x:v>
+        <x:v>1627872951</x:v>
       </x:c>
       <x:c r="I112" s="0">
-        <x:v>0.0204</x:v>
+        <x:v>0.0081</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:9">
       <x:c r="A113" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B113" s="0">
-        <x:v>59.5</x:v>
+        <x:v>86.5</x:v>
       </x:c>
       <x:c r="C113" s="0">
-        <x:v>-1.85</x:v>
+        <x:v>2.3</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
         <x:v>99</x:v>
       </x:c>
       <x:c r="E113" s="0">
-        <x:v>988848</x:v>
+        <x:v>237500000</x:v>
       </x:c>
       <x:c r="F113" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G113" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H113" s="0">
-        <x:v>12999679000</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I113" s="0">
-        <x:v>0.0033</x:v>
+        <x:v>0.0679</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:9">
       <x:c r="A114" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B114" s="0">
-        <x:v>73.3</x:v>
+        <x:v>63.15</x:v>
       </x:c>
       <x:c r="C114" s="0">
-        <x:v>6.65</x:v>
+        <x:v>2.65</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E114" s="0">
-        <x:v>47300000</x:v>
+        <x:v>147892538</x:v>
       </x:c>
       <x:c r="F114" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G114" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H114" s="0">
-        <x:v>10597063406</x:v>
+        <x:v>7257990064</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>0.2309</x:v>
+        <x:v>0.0204</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:9">
       <x:c r="A115" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B115" s="0">
-        <x:v>4.16</x:v>
+        <x:v>59.1</x:v>
       </x:c>
       <x:c r="C115" s="0">
-        <x:v>0.11</x:v>
+        <x:v>-0.4</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E115" s="0">
-        <x:v>758600</x:v>
+        <x:v>988848</x:v>
       </x:c>
       <x:c r="F115" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G115" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H115" s="0">
-        <x:v>1960468575</x:v>
+        <x:v>12999679000</x:v>
       </x:c>
       <x:c r="I115" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0.0033</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:9">
       <x:c r="A116" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B116" s="0">
-        <x:v>4.16</x:v>
+        <x:v>80.6</x:v>
       </x:c>
       <x:c r="C116" s="0">
-        <x:v>0.11</x:v>
+        <x:v>7.3</x:v>
       </x:c>
       <x:c r="D116" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E116" s="0">
-        <x:v>758600</x:v>
+        <x:v>47300000</x:v>
       </x:c>
       <x:c r="F116" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G116" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H116" s="0">
-        <x:v>1960468575</x:v>
+        <x:v>10597063406</x:v>
       </x:c>
       <x:c r="I116" s="0">
-        <x:v>0.0004</x:v>
+        <x:v>0.2309</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:9">
       <x:c r="A117" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B117" s="0">
-        <x:v>1190</x:v>
+        <x:v>4.16</x:v>
       </x:c>
       <x:c r="C117" s="0">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E117" s="0">
-        <x:v>576665</x:v>
+        <x:v>758600</x:v>
       </x:c>
       <x:c r="F117" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G117" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H117" s="0">
-        <x:v>1586603352</x:v>
+        <x:v>1960468575</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>0.0159</x:v>
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:9">
       <x:c r="A118" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B118" s="0">
+        <x:v>4.16</x:v>
+      </x:c>
+      <x:c r="C118" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D118" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="E118" s="0">
+        <x:v>758600</x:v>
+      </x:c>
+      <x:c r="F118" s="0" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="B118" s="0">
-        <x:v>86.05</x:v>
-      </x:c>
-      <x:c r="C118" s="0">
-        <x:v>0.85</x:v>
-      </x:c>
-      <x:c r="D118" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="E118" s="0">
-        <x:v>8000000</x:v>
-      </x:c>
-      <x:c r="F118" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="G118" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H118" s="0">
-        <x:v>20999579110</x:v>
+        <x:v>1960468575</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>0.0166</x:v>
+        <x:v>0.0004</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:9">
       <x:c r="A119" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B119" s="0">
-        <x:v>100</x:v>
+        <x:v>1200</x:v>
       </x:c>
       <x:c r="C119" s="0">
-        <x:v>-0.7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E119" s="0">
-        <x:v>850000</x:v>
+        <x:v>576665</x:v>
       </x:c>
       <x:c r="F119" s="0" t="s">
         <x:v>11</x:v>
@@ -4244,230 +4244,230 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H119" s="0">
-        <x:v>1781510191</x:v>
+        <x:v>1586603352</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>0.0208</x:v>
+        <x:v>0.0159</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:9">
       <x:c r="A120" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B120" s="0">
-        <x:v>17.71</x:v>
+        <x:v>86.8</x:v>
       </x:c>
       <x:c r="C120" s="0">
-        <x:v>-0.04</x:v>
+        <x:v>0.75</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E120" s="0">
-        <x:v>10149200</x:v>
+        <x:v>8000000</x:v>
       </x:c>
       <x:c r="F120" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G120" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H120" s="0">
-        <x:v>2020891371</x:v>
+        <x:v>20999579110</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>0.2601</x:v>
+        <x:v>0.0166</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:9">
       <x:c r="A121" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B121" s="0">
-        <x:v>136.9</x:v>
+        <x:v>98.2</x:v>
       </x:c>
       <x:c r="C121" s="0">
-        <x:v>12.4</x:v>
+        <x:v>-1.8</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
         <x:v>105</x:v>
       </x:c>
       <x:c r="E121" s="0">
-        <x:v>10500000</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="F121" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G121" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H121" s="0">
-        <x:v>1742315226</x:v>
+        <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>0.3121</x:v>
+        <x:v>0.0208</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:9">
       <x:c r="A122" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B122" s="0">
-        <x:v>100</x:v>
+        <x:v>19.48</x:v>
       </x:c>
       <x:c r="C122" s="0">
-        <x:v>-0.7</x:v>
+        <x:v>1.77</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
         <x:v>106</x:v>
       </x:c>
       <x:c r="E122" s="0">
-        <x:v>366956541</x:v>
+        <x:v>10149200</x:v>
       </x:c>
       <x:c r="F122" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G122" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H122" s="0">
-        <x:v>1781510191</x:v>
+        <x:v>2020891371</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>0.206</x:v>
+        <x:v>0.2601</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:9">
       <x:c r="A123" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B123" s="0">
-        <x:v>60.5</x:v>
+        <x:v>150.5</x:v>
       </x:c>
       <x:c r="C123" s="0">
-        <x:v>1.6</x:v>
+        <x:v>13.6</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E123" s="0">
-        <x:v>61158155</x:v>
+        <x:v>10500000</x:v>
       </x:c>
       <x:c r="F123" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G123" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H123" s="0">
-        <x:v>7257990064</x:v>
+        <x:v>1742315226</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>0.0084</x:v>
+        <x:v>0.3121</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:9">
       <x:c r="A124" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B124" s="0">
-        <x:v>111.8</x:v>
+        <x:v>98.2</x:v>
       </x:c>
       <x:c r="C124" s="0">
-        <x:v>3.7</x:v>
+        <x:v>-1.8</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
         <x:v>107</x:v>
       </x:c>
       <x:c r="E124" s="0">
-        <x:v>1000000</x:v>
+        <x:v>366956541</x:v>
       </x:c>
       <x:c r="F124" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G124" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H124" s="0">
-        <x:v>1688731509</x:v>
+        <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>0.0307</x:v>
+        <x:v>0.206</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:9">
       <x:c r="A125" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B125" s="0">
+        <x:v>63.15</x:v>
+      </x:c>
+      <x:c r="C125" s="0">
+        <x:v>2.65</x:v>
+      </x:c>
+      <x:c r="D125" s="0" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="B125" s="0">
-        <x:v>111.8</x:v>
-      </x:c>
-      <x:c r="C125" s="0">
-        <x:v>3.7</x:v>
-      </x:c>
-      <x:c r="D125" s="0" t="s">
-        <x:v>107</x:v>
-      </x:c>
       <x:c r="E125" s="0">
-        <x:v>1050000</x:v>
+        <x:v>61158155</x:v>
       </x:c>
       <x:c r="F125" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G125" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H125" s="0">
-        <x:v>1688731509</x:v>
+        <x:v>7257990064</x:v>
       </x:c>
       <x:c r="I125" s="0">
-        <x:v>0.0271</x:v>
+        <x:v>0.0084</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:9">
       <x:c r="A126" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B126" s="0">
-        <x:v>42.28</x:v>
+        <x:v>111.7</x:v>
       </x:c>
       <x:c r="C126" s="0">
-        <x:v>-0.32</x:v>
+        <x:v>-0.1</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E126" s="0">
-        <x:v>109053804</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="F126" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G126" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H126" s="0">
-        <x:v>1942491524</x:v>
+        <x:v>1688731509</x:v>
       </x:c>
       <x:c r="I126" s="0">
-        <x:v>0.0561</x:v>
+        <x:v>0.0307</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:9">
       <x:c r="A127" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B127" s="0">
-        <x:v>10.22</x:v>
+        <x:v>111.7</x:v>
       </x:c>
       <x:c r="C127" s="0">
-        <x:v>0.47</x:v>
+        <x:v>-0.1</x:v>
       </x:c>
       <x:c r="D127" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E127" s="0">
-        <x:v>62315119</x:v>
+        <x:v>1050000</x:v>
       </x:c>
       <x:c r="F127" s="0" t="s">
         <x:v>11</x:v>
@@ -4476,56 +4476,56 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H127" s="0">
-        <x:v>12026414029</x:v>
+        <x:v>1688731509</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>0.2257</x:v>
+        <x:v>0.0271</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:9">
       <x:c r="A128" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B128" s="0">
-        <x:v>265</x:v>
+        <x:v>44.8</x:v>
       </x:c>
       <x:c r="C128" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>2.52</x:v>
       </x:c>
       <x:c r="D128" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E128" s="0">
-        <x:v>896400</x:v>
+        <x:v>109053804</x:v>
       </x:c>
       <x:c r="F128" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G128" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H128" s="0">
-        <x:v>1364716456</x:v>
+        <x:v>1942491524</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>0.0285</x:v>
+        <x:v>0.0561</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:9">
       <x:c r="A129" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B129" s="0">
-        <x:v>546</x:v>
+        <x:v>10.39</x:v>
       </x:c>
       <x:c r="C129" s="0">
-        <x:v>49.5</x:v>
+        <x:v>0.17</x:v>
       </x:c>
       <x:c r="D129" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E129" s="0">
-        <x:v>3370000</x:v>
+        <x:v>62315119</x:v>
       </x:c>
       <x:c r="F129" s="0" t="s">
         <x:v>11</x:v>
@@ -4534,56 +4534,56 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H129" s="0">
-        <x:v>1865697176</x:v>
+        <x:v>12026414029</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>0.0785</x:v>
+        <x:v>0.2257</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:9">
       <x:c r="A130" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B130" s="0">
-        <x:v>58.4</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="C130" s="0">
-        <x:v>1.9</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D130" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E130" s="0">
-        <x:v>750561215</x:v>
+        <x:v>896400</x:v>
       </x:c>
       <x:c r="F130" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G130" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H130" s="0">
-        <x:v>16507905000</x:v>
+        <x:v>1364716456</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>0.0455</x:v>
+        <x:v>0.0285</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:9">
       <x:c r="A131" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B131" s="0">
-        <x:v>86.05</x:v>
+        <x:v>600.5</x:v>
       </x:c>
       <x:c r="C131" s="0">
-        <x:v>0.85</x:v>
+        <x:v>54.5</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="E131" s="0">
-        <x:v>20000000</x:v>
+        <x:v>3370000</x:v>
       </x:c>
       <x:c r="F131" s="0" t="s">
         <x:v>11</x:v>
@@ -4592,56 +4592,56 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H131" s="0">
-        <x:v>20999579110</x:v>
+        <x:v>1865697176</x:v>
       </x:c>
       <x:c r="I131" s="0">
-        <x:v>0.0413</x:v>
+        <x:v>0.0785</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:9">
       <x:c r="A132" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B132" s="0">
-        <x:v>35.5</x:v>
+        <x:v>61.4</x:v>
       </x:c>
       <x:c r="C132" s="0">
-        <x:v>1.86</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E132" s="0">
-        <x:v>750000000</x:v>
+        <x:v>750561215</x:v>
       </x:c>
       <x:c r="F132" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G132" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H132" s="0">
-        <x:v>0</x:v>
+        <x:v>16507905000</x:v>
       </x:c>
       <x:c r="I132" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0455</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:9">
       <x:c r="A133" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B133" s="0">
-        <x:v>73.3</x:v>
+        <x:v>86.8</x:v>
       </x:c>
       <x:c r="C133" s="0">
-        <x:v>6.65</x:v>
+        <x:v>0.75</x:v>
       </x:c>
       <x:c r="D133" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E133" s="0">
-        <x:v>111232418</x:v>
+        <x:v>20000000</x:v>
       </x:c>
       <x:c r="F133" s="0" t="s">
         <x:v>11</x:v>
@@ -4650,56 +4650,56 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H133" s="0">
-        <x:v>10597063406</x:v>
+        <x:v>20999579110</x:v>
       </x:c>
       <x:c r="I133" s="0">
-        <x:v>0.4554</x:v>
+        <x:v>0.0413</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:9">
       <x:c r="A134" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="B134" s="0">
+        <x:v>36.82</x:v>
+      </x:c>
+      <x:c r="C134" s="0">
+        <x:v>1.32</x:v>
+      </x:c>
+      <x:c r="D134" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="E134" s="0">
+        <x:v>750000000</x:v>
+      </x:c>
+      <x:c r="F134" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B134" s="0">
-        <x:v>37.8</x:v>
-      </x:c>
-      <x:c r="C134" s="0">
-        <x:v>-1.08</x:v>
-      </x:c>
-      <x:c r="D134" s="0" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="E134" s="0">
-        <x:v>51384996</x:v>
-      </x:c>
-      <x:c r="F134" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="G134" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H134" s="0">
-        <x:v>11899043692</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I134" s="0">
-        <x:v>0.1873</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:9">
       <x:c r="A135" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B135" s="0">
-        <x:v>37.8</x:v>
+        <x:v>80.6</x:v>
       </x:c>
       <x:c r="C135" s="0">
-        <x:v>-1.08</x:v>
+        <x:v>7.3</x:v>
       </x:c>
       <x:c r="D135" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E135" s="0">
-        <x:v>3602451</x:v>
+        <x:v>111232418</x:v>
       </x:c>
       <x:c r="F135" s="0" t="s">
         <x:v>11</x:v>
@@ -4708,27 +4708,27 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H135" s="0">
-        <x:v>11899043692</x:v>
+        <x:v>10597063406</x:v>
       </x:c>
       <x:c r="I135" s="0">
-        <x:v>0.0131</x:v>
+        <x:v>0.4554</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:9">
       <x:c r="A136" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B136" s="0">
-        <x:v>37.8</x:v>
+        <x:v>37.6</x:v>
       </x:c>
       <x:c r="C136" s="0">
-        <x:v>-1.08</x:v>
+        <x:v>-0.2</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
         <x:v>118</x:v>
       </x:c>
       <x:c r="E136" s="0">
-        <x:v>24226465</x:v>
+        <x:v>51384996</x:v>
       </x:c>
       <x:c r="F136" s="0" t="s">
         <x:v>11</x:v>
@@ -4740,198 +4740,198 @@
         <x:v>11899043692</x:v>
       </x:c>
       <x:c r="I136" s="0">
-        <x:v>0.0883</x:v>
+        <x:v>0.1873</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:9">
       <x:c r="A137" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B137" s="0">
-        <x:v>57.05</x:v>
+        <x:v>37.6</x:v>
       </x:c>
       <x:c r="C137" s="0">
-        <x:v>-1.45</x:v>
+        <x:v>-0.2</x:v>
       </x:c>
       <x:c r="D137" s="0" t="s">
         <x:v>118</x:v>
       </x:c>
       <x:c r="E137" s="0">
-        <x:v>12900000</x:v>
+        <x:v>3602451</x:v>
       </x:c>
       <x:c r="F137" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G137" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H137" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>11899043692</x:v>
       </x:c>
       <x:c r="I137" s="0">
-        <x:v>0.0052</x:v>
+        <x:v>0.0131</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:9">
       <x:c r="A138" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B138" s="0">
-        <x:v>320.75</x:v>
+        <x:v>37.6</x:v>
       </x:c>
       <x:c r="C138" s="0">
-        <x:v>3</x:v>
+        <x:v>-0.2</x:v>
       </x:c>
       <x:c r="D138" s="0" t="s">
         <x:v>118</x:v>
       </x:c>
       <x:c r="E138" s="0">
-        <x:v>53250000</x:v>
+        <x:v>24226465</x:v>
       </x:c>
       <x:c r="F138" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G138" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H138" s="0">
-        <x:v>24073631758</x:v>
+        <x:v>11899043692</x:v>
       </x:c>
       <x:c r="I138" s="0">
-        <x:v>0.115</x:v>
+        <x:v>0.0883</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:9">
       <x:c r="A139" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B139" s="0">
-        <x:v>30.42</x:v>
+        <x:v>57.25</x:v>
       </x:c>
       <x:c r="C139" s="0">
-        <x:v>0.72</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="D139" s="0" t="s">
         <x:v>118</x:v>
       </x:c>
       <x:c r="E139" s="0">
-        <x:v>6860140</x:v>
+        <x:v>12900000</x:v>
       </x:c>
       <x:c r="F139" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G139" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H139" s="0">
-        <x:v>0</x:v>
+        <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I139" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0052</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:9">
       <x:c r="A140" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B140" s="0">
-        <x:v>84.2</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="C140" s="0">
-        <x:v>0.6</x:v>
+        <x:v>5.25</x:v>
       </x:c>
       <x:c r="D140" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E140" s="0">
-        <x:v>230000000</x:v>
+        <x:v>53250000</x:v>
       </x:c>
       <x:c r="F140" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G140" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H140" s="0">
-        <x:v>2941310980</x:v>
+        <x:v>24073631758</x:v>
       </x:c>
       <x:c r="I140" s="0">
-        <x:v>0.0782</x:v>
+        <x:v>0.115</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:9">
       <x:c r="A141" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B141" s="0">
-        <x:v>546</x:v>
+        <x:v>31.08</x:v>
       </x:c>
       <x:c r="C141" s="0">
-        <x:v>49.5</x:v>
+        <x:v>0.66</x:v>
       </x:c>
       <x:c r="D141" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E141" s="0">
-        <x:v>4700000</x:v>
+        <x:v>6860140</x:v>
       </x:c>
       <x:c r="F141" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G141" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H141" s="0">
-        <x:v>1865697176</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I141" s="0">
-        <x:v>0.1092</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:9">
       <x:c r="A142" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B142" s="0">
-        <x:v>30.42</x:v>
+        <x:v>86.5</x:v>
       </x:c>
       <x:c r="C142" s="0">
-        <x:v>0.72</x:v>
+        <x:v>2.3</x:v>
       </x:c>
       <x:c r="D142" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E142" s="0">
-        <x:v>256000000</x:v>
+        <x:v>230000000</x:v>
       </x:c>
       <x:c r="F142" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G142" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H142" s="0">
-        <x:v>0</x:v>
+        <x:v>2941310980</x:v>
       </x:c>
       <x:c r="I142" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0782</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:9">
       <x:c r="A143" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B143" s="0">
-        <x:v>37.8</x:v>
+        <x:v>600.5</x:v>
       </x:c>
       <x:c r="C143" s="0">
-        <x:v>-1.08</x:v>
+        <x:v>54.5</x:v>
       </x:c>
       <x:c r="D143" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E143" s="0">
-        <x:v>10724896</x:v>
+        <x:v>4700000</x:v>
       </x:c>
       <x:c r="F143" s="0" t="s">
         <x:v>11</x:v>
@@ -4940,56 +4940,56 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H143" s="0">
-        <x:v>11899043692</x:v>
+        <x:v>1865697176</x:v>
       </x:c>
       <x:c r="I143" s="0">
-        <x:v>0.039</x:v>
+        <x:v>0.1092</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:9">
       <x:c r="A144" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B144" s="0">
-        <x:v>24.84</x:v>
+        <x:v>31.08</x:v>
       </x:c>
       <x:c r="C144" s="0">
-        <x:v>0.16</x:v>
+        <x:v>0.66</x:v>
       </x:c>
       <x:c r="D144" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E144" s="0">
-        <x:v>31000000</x:v>
+        <x:v>256000000</x:v>
       </x:c>
       <x:c r="F144" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G144" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H144" s="0">
-        <x:v>813967617</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I144" s="0">
-        <x:v>0.0381</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:9">
       <x:c r="A145" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B145" s="0">
-        <x:v>43.74</x:v>
+        <x:v>37.6</x:v>
       </x:c>
       <x:c r="C145" s="0">
-        <x:v>0.84</x:v>
+        <x:v>-0.2</x:v>
       </x:c>
       <x:c r="D145" s="0" t="s">
         <x:v>121</x:v>
       </x:c>
       <x:c r="E145" s="0">
-        <x:v>13500000</x:v>
+        <x:v>10724896</x:v>
       </x:c>
       <x:c r="F145" s="0" t="s">
         <x:v>11</x:v>
@@ -4998,56 +4998,56 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H145" s="0">
-        <x:v>6483809984</x:v>
+        <x:v>11899043692</x:v>
       </x:c>
       <x:c r="I145" s="0">
-        <x:v>0.09</x:v>
+        <x:v>0.039</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:9">
       <x:c r="A146" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B146" s="0">
-        <x:v>42.28</x:v>
+        <x:v>24.9</x:v>
       </x:c>
       <x:c r="C146" s="0">
-        <x:v>-0.32</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="D146" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E146" s="0">
-        <x:v>29886357</x:v>
+        <x:v>31000000</x:v>
       </x:c>
       <x:c r="F146" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G146" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H146" s="0">
-        <x:v>1942491524</x:v>
+        <x:v>813967617</x:v>
       </x:c>
       <x:c r="I146" s="0">
-        <x:v>0.0154</x:v>
+        <x:v>0.0381</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:9">
       <x:c r="A147" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B147" s="0">
-        <x:v>428</x:v>
+        <x:v>46.44</x:v>
       </x:c>
       <x:c r="C147" s="0">
-        <x:v>-6</x:v>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="D147" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E147" s="0">
-        <x:v>171000000</x:v>
+        <x:v>13500000</x:v>
       </x:c>
       <x:c r="F147" s="0" t="s">
         <x:v>11</x:v>
@@ -5056,56 +5056,56 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H147" s="0">
-        <x:v>130147715000</x:v>
+        <x:v>6483809984</x:v>
       </x:c>
       <x:c r="I147" s="0">
-        <x:v>0.0568</x:v>
+        <x:v>0.09</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:9">
       <x:c r="A148" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B148" s="0">
-        <x:v>136.9</x:v>
+        <x:v>44.8</x:v>
       </x:c>
       <x:c r="C148" s="0">
-        <x:v>12.4</x:v>
+        <x:v>2.52</x:v>
       </x:c>
       <x:c r="D148" s="0" t="s">
         <x:v>122</x:v>
       </x:c>
       <x:c r="E148" s="0">
-        <x:v>1890000</x:v>
+        <x:v>29886357</x:v>
       </x:c>
       <x:c r="F148" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G148" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H148" s="0">
-        <x:v>1742315226</x:v>
+        <x:v>1942491524</x:v>
       </x:c>
       <x:c r="I148" s="0">
-        <x:v>0.0549</x:v>
+        <x:v>0.0154</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:9">
       <x:c r="A149" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B149" s="0">
-        <x:v>14.16</x:v>
+        <x:v>428.5</x:v>
       </x:c>
       <x:c r="C149" s="0">
-        <x:v>0.14</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="D149" s="0" t="s">
         <x:v>122</x:v>
       </x:c>
       <x:c r="E149" s="0">
-        <x:v>892825</x:v>
+        <x:v>171000000</x:v>
       </x:c>
       <x:c r="F149" s="0" t="s">
         <x:v>11</x:v>
@@ -5114,56 +5114,56 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H149" s="0">
-        <x:v>3015442704</x:v>
+        <x:v>130147715000</x:v>
       </x:c>
       <x:c r="I149" s="0">
-        <x:v>0.0128</x:v>
+        <x:v>0.0568</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:9">
       <x:c r="A150" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B150" s="0">
-        <x:v>57.05</x:v>
+        <x:v>150.5</x:v>
       </x:c>
       <x:c r="C150" s="0">
-        <x:v>-1.45</x:v>
+        <x:v>13.6</x:v>
       </x:c>
       <x:c r="D150" s="0" t="s">
         <x:v>122</x:v>
       </x:c>
       <x:c r="E150" s="0">
-        <x:v>361176</x:v>
+        <x:v>1890000</x:v>
       </x:c>
       <x:c r="F150" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G150" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H150" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>1742315226</x:v>
       </x:c>
       <x:c r="I150" s="0">
-        <x:v>0.0063</x:v>
+        <x:v>0.0549</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:9">
       <x:c r="A151" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B151" s="0">
-        <x:v>25.74</x:v>
+        <x:v>14.1</x:v>
       </x:c>
       <x:c r="C151" s="0">
-        <x:v>0.82</x:v>
+        <x:v>-0.06</x:v>
       </x:c>
       <x:c r="D151" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E151" s="0">
-        <x:v>1060000</x:v>
+        <x:v>892825</x:v>
       </x:c>
       <x:c r="F151" s="0" t="s">
         <x:v>11</x:v>
@@ -5172,56 +5172,56 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H151" s="0">
-        <x:v>1194839266</x:v>
+        <x:v>3015442704</x:v>
       </x:c>
       <x:c r="I151" s="0">
-        <x:v>0.0384</x:v>
+        <x:v>0.0128</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:9">
       <x:c r="A152" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B152" s="0">
-        <x:v>55</x:v>
+        <x:v>57.25</x:v>
       </x:c>
       <x:c r="C152" s="0">
-        <x:v>-0.7</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="D152" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E152" s="0">
-        <x:v>259417800</x:v>
+        <x:v>361176</x:v>
       </x:c>
       <x:c r="F152" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G152" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H152" s="0">
-        <x:v>2741117556</x:v>
+        <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I152" s="0">
-        <x:v>0.0946</x:v>
+        <x:v>0.0063</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:9">
       <x:c r="A153" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B153" s="0">
-        <x:v>71.15</x:v>
+        <x:v>25.92</x:v>
       </x:c>
       <x:c r="C153" s="0">
-        <x:v>2.55</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="D153" s="0" t="s">
         <x:v>125</x:v>
       </x:c>
       <x:c r="E153" s="0">
-        <x:v>523788</x:v>
+        <x:v>1060000</x:v>
       </x:c>
       <x:c r="F153" s="0" t="s">
         <x:v>11</x:v>
@@ -5230,47 +5230,47 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H153" s="0">
-        <x:v>832031190</x:v>
+        <x:v>1194839266</x:v>
       </x:c>
       <x:c r="I153" s="0">
-        <x:v>0.0272</x:v>
+        <x:v>0.0384</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:9">
       <x:c r="A154" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B154" s="0">
-        <x:v>71.15</x:v>
+        <x:v>54.05</x:v>
       </x:c>
       <x:c r="C154" s="0">
-        <x:v>2.55</x:v>
+        <x:v>-0.95</x:v>
       </x:c>
       <x:c r="D154" s="0" t="s">
         <x:v>125</x:v>
       </x:c>
       <x:c r="E154" s="0">
-        <x:v>1415270</x:v>
+        <x:v>259417800</x:v>
       </x:c>
       <x:c r="F154" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G154" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H154" s="0">
-        <x:v>832031190</x:v>
+        <x:v>2741117556</x:v>
       </x:c>
       <x:c r="I154" s="0">
-        <x:v>0.0736</x:v>
+        <x:v>0.0946</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:9">
       <x:c r="A155" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B155" s="0">
-        <x:v>86.05</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C155" s="0">
         <x:v>0.85</x:v>
@@ -5279,7 +5279,7 @@
         <x:v>125</x:v>
       </x:c>
       <x:c r="E155" s="0">
-        <x:v>25000000</x:v>
+        <x:v>523788</x:v>
       </x:c>
       <x:c r="F155" s="0" t="s">
         <x:v>11</x:v>
@@ -5288,27 +5288,27 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H155" s="0">
-        <x:v>20999579110</x:v>
+        <x:v>832031190</x:v>
       </x:c>
       <x:c r="I155" s="0">
-        <x:v>0.0515</x:v>
+        <x:v>0.0272</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:9">
       <x:c r="A156" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B156" s="0">
-        <x:v>6.32</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C156" s="0">
-        <x:v>0.19</x:v>
+        <x:v>0.85</x:v>
       </x:c>
       <x:c r="D156" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E156" s="0">
-        <x:v>25000</x:v>
+        <x:v>1415270</x:v>
       </x:c>
       <x:c r="F156" s="0" t="s">
         <x:v>11</x:v>
@@ -5317,143 +5317,143 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H156" s="0">
-        <x:v>1627872951</x:v>
+        <x:v>832031190</x:v>
       </x:c>
       <x:c r="I156" s="0">
-        <x:v>0.0007</x:v>
+        <x:v>0.0736</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:9">
       <x:c r="A157" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B157" s="0">
-        <x:v>21.32</x:v>
+        <x:v>86.8</x:v>
       </x:c>
       <x:c r="C157" s="0">
-        <x:v>0.12</x:v>
+        <x:v>0.75</x:v>
       </x:c>
       <x:c r="D157" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E157" s="0">
-        <x:v>1500000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="F157" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G157" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H157" s="0">
-        <x:v>774677961</x:v>
+        <x:v>20999579110</x:v>
       </x:c>
       <x:c r="I157" s="0">
-        <x:v>0.0019</x:v>
+        <x:v>0.0515</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:9">
       <x:c r="A158" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B158" s="0">
-        <x:v>8.8</x:v>
+        <x:v>6.3</x:v>
       </x:c>
       <x:c r="C158" s="0">
-        <x:v>0.39</x:v>
+        <x:v>-0.02</x:v>
       </x:c>
       <x:c r="D158" s="0" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="E158" s="0">
-        <x:v>13833310</x:v>
+        <x:v>25000</x:v>
       </x:c>
       <x:c r="F158" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G158" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H158" s="0">
-        <x:v>9028523851</x:v>
+        <x:v>1627872951</x:v>
       </x:c>
       <x:c r="I158" s="0">
-        <x:v>0.0776</x:v>
+        <x:v>0.0007</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:9">
       <x:c r="A159" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B159" s="0">
-        <x:v>80.25</x:v>
+        <x:v>21.72</x:v>
       </x:c>
       <x:c r="C159" s="0">
-        <x:v>-1.45</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="D159" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="E159" s="0">
-        <x:v>3419000</x:v>
+        <x:v>1500000</x:v>
       </x:c>
       <x:c r="F159" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G159" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H159" s="0">
-        <x:v>3895315496</x:v>
+        <x:v>774677961</x:v>
       </x:c>
       <x:c r="I159" s="0">
-        <x:v>0.0379</x:v>
+        <x:v>0.0019</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:9">
       <x:c r="A160" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B160" s="0">
-        <x:v>546</x:v>
+        <x:v>9.68</x:v>
       </x:c>
       <x:c r="C160" s="0">
-        <x:v>49.5</x:v>
+        <x:v>0.88</x:v>
       </x:c>
       <x:c r="D160" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="E160" s="0">
-        <x:v>3700000</x:v>
+        <x:v>13833310</x:v>
       </x:c>
       <x:c r="F160" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G160" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H160" s="0">
-        <x:v>1865697176</x:v>
+        <x:v>9028523851</x:v>
       </x:c>
       <x:c r="I160" s="0">
-        <x:v>0.0857</x:v>
+        <x:v>0.0776</x:v>
       </x:c>
     </x:row>
     <x:row r="161" spans="1:9">
       <x:c r="A161" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B161" s="0">
-        <x:v>43.74</x:v>
+        <x:v>76.85</x:v>
       </x:c>
       <x:c r="C161" s="0">
-        <x:v>0.84</x:v>
+        <x:v>-3.4</x:v>
       </x:c>
       <x:c r="D161" s="0" t="s">
         <x:v>129</x:v>
       </x:c>
       <x:c r="E161" s="0">
-        <x:v>16000000</x:v>
+        <x:v>3419000</x:v>
       </x:c>
       <x:c r="F161" s="0" t="s">
         <x:v>11</x:v>
@@ -5462,27 +5462,27 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H161" s="0">
-        <x:v>6483809984</x:v>
+        <x:v>3895315496</x:v>
       </x:c>
       <x:c r="I161" s="0">
-        <x:v>0.1067</x:v>
+        <x:v>0.0379</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:9">
       <x:c r="A162" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B162" s="0">
-        <x:v>57.05</x:v>
+        <x:v>600.5</x:v>
       </x:c>
       <x:c r="C162" s="0">
-        <x:v>-1.45</x:v>
+        <x:v>54.5</x:v>
       </x:c>
       <x:c r="D162" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="E162" s="0">
-        <x:v>906840</x:v>
+        <x:v>3700000</x:v>
       </x:c>
       <x:c r="F162" s="0" t="s">
         <x:v>11</x:v>
@@ -5491,143 +5491,143 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H162" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>1865697176</x:v>
       </x:c>
       <x:c r="I162" s="0">
-        <x:v>0.0159</x:v>
+        <x:v>0.0857</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:9">
       <x:c r="A163" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B163" s="0">
-        <x:v>3.46</x:v>
+        <x:v>46.44</x:v>
       </x:c>
       <x:c r="C163" s="0">
-        <x:v>-0.01</x:v>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="D163" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="E163" s="0">
-        <x:v>895039950</x:v>
+        <x:v>16000000</x:v>
       </x:c>
       <x:c r="F163" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G163" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H163" s="0">
-        <x:v>7382591324</x:v>
+        <x:v>6483809984</x:v>
       </x:c>
       <x:c r="I163" s="0">
-        <x:v>0.1212</x:v>
+        <x:v>0.1067</x:v>
       </x:c>
     </x:row>
     <x:row r="164" spans="1:9">
       <x:c r="A164" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B164" s="0">
-        <x:v>55</x:v>
+        <x:v>57.25</x:v>
       </x:c>
       <x:c r="C164" s="0">
-        <x:v>-0.7</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="D164" s="0" t="s">
         <x:v>130</x:v>
       </x:c>
       <x:c r="E164" s="0">
-        <x:v>575933040</x:v>
+        <x:v>906840</x:v>
       </x:c>
       <x:c r="F164" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G164" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H164" s="0">
-        <x:v>2741117556</x:v>
+        <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I164" s="0">
-        <x:v>0.2101</x:v>
+        <x:v>0.0159</x:v>
       </x:c>
     </x:row>
     <x:row r="165" spans="1:9">
       <x:c r="A165" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B165" s="0">
-        <x:v>12.68</x:v>
+        <x:v>3.41</x:v>
       </x:c>
       <x:c r="C165" s="0">
-        <x:v>0.08</x:v>
+        <x:v>-0.05</x:v>
       </x:c>
       <x:c r="D165" s="0" t="s">
         <x:v>130</x:v>
       </x:c>
       <x:c r="E165" s="0">
-        <x:v>559000</x:v>
+        <x:v>895039950</x:v>
       </x:c>
       <x:c r="F165" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G165" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H165" s="0">
-        <x:v>2865374550</x:v>
+        <x:v>7382591324</x:v>
       </x:c>
       <x:c r="I165" s="0">
-        <x:v>0.0084</x:v>
+        <x:v>0.1212</x:v>
       </x:c>
     </x:row>
     <x:row r="166" spans="1:9">
       <x:c r="A166" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B166" s="0">
-        <x:v>58.4</x:v>
+        <x:v>54.05</x:v>
       </x:c>
       <x:c r="C166" s="0">
-        <x:v>1.9</x:v>
+        <x:v>-0.95</x:v>
       </x:c>
       <x:c r="D166" s="0" t="s">
         <x:v>130</x:v>
       </x:c>
       <x:c r="E166" s="0">
-        <x:v>8900056</x:v>
+        <x:v>575933040</x:v>
       </x:c>
       <x:c r="F166" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G166" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H166" s="0">
-        <x:v>16507905000</x:v>
+        <x:v>2741117556</x:v>
       </x:c>
       <x:c r="I166" s="0">
-        <x:v>0.0233</x:v>
+        <x:v>0.2101</x:v>
       </x:c>
     </x:row>
     <x:row r="167" spans="1:9">
       <x:c r="A167" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B167" s="0">
-        <x:v>320.75</x:v>
+        <x:v>12.95</x:v>
       </x:c>
       <x:c r="C167" s="0">
-        <x:v>3</x:v>
+        <x:v>0.27</x:v>
       </x:c>
       <x:c r="D167" s="0" t="s">
         <x:v>130</x:v>
       </x:c>
       <x:c r="E167" s="0">
-        <x:v>164306000</x:v>
+        <x:v>559000</x:v>
       </x:c>
       <x:c r="F167" s="0" t="s">
         <x:v>11</x:v>
@@ -5636,27 +5636,27 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H167" s="0">
-        <x:v>24073631758</x:v>
+        <x:v>2865374550</x:v>
       </x:c>
       <x:c r="I167" s="0">
-        <x:v>0.2943</x:v>
+        <x:v>0.0084</x:v>
       </x:c>
     </x:row>
     <x:row r="168" spans="1:9">
       <x:c r="A168" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B168" s="0">
-        <x:v>55.3</x:v>
+        <x:v>61.4</x:v>
       </x:c>
       <x:c r="C168" s="0">
-        <x:v>0.45</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D168" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="E168" s="0">
-        <x:v>275000</x:v>
+        <x:v>8900056</x:v>
       </x:c>
       <x:c r="F168" s="0" t="s">
         <x:v>11</x:v>
@@ -5665,56 +5665,56 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H168" s="0">
-        <x:v>580678850</x:v>
+        <x:v>16507905000</x:v>
       </x:c>
       <x:c r="I168" s="0">
-        <x:v>0.0204</x:v>
+        <x:v>0.0233</x:v>
       </x:c>
     </x:row>
     <x:row r="169" spans="1:9">
       <x:c r="A169" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B169" s="0">
-        <x:v>55</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="C169" s="0">
-        <x:v>-0.7</x:v>
+        <x:v>5.25</x:v>
       </x:c>
       <x:c r="D169" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="E169" s="0">
-        <x:v>231651480</x:v>
+        <x:v>164306000</x:v>
       </x:c>
       <x:c r="F169" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G169" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H169" s="0">
-        <x:v>2741117556</x:v>
+        <x:v>24073631758</x:v>
       </x:c>
       <x:c r="I169" s="0">
-        <x:v>0.0845</x:v>
+        <x:v>0.2943</x:v>
       </x:c>
     </x:row>
     <x:row r="170" spans="1:9">
       <x:c r="A170" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B170" s="0">
-        <x:v>16.44</x:v>
+        <x:v>54.75</x:v>
       </x:c>
       <x:c r="C170" s="0">
-        <x:v>0.76</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="D170" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="E170" s="0">
-        <x:v>31860000</x:v>
+        <x:v>275000</x:v>
       </x:c>
       <x:c r="F170" s="0" t="s">
         <x:v>11</x:v>
@@ -5723,230 +5723,230 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H170" s="0">
-        <x:v>3025063909</x:v>
+        <x:v>580678850</x:v>
       </x:c>
       <x:c r="I170" s="0">
-        <x:v>0.4539</x:v>
+        <x:v>0.0204</x:v>
       </x:c>
     </x:row>
     <x:row r="171" spans="1:9">
       <x:c r="A171" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B171" s="0">
-        <x:v>100</x:v>
+        <x:v>54.05</x:v>
       </x:c>
       <x:c r="C171" s="0">
-        <x:v>-0.7</x:v>
+        <x:v>-0.95</x:v>
       </x:c>
       <x:c r="D171" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="E171" s="0">
-        <x:v>41650000</x:v>
+        <x:v>231651480</x:v>
       </x:c>
       <x:c r="F171" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G171" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H171" s="0">
-        <x:v>1781510191</x:v>
+        <x:v>2741117556</x:v>
       </x:c>
       <x:c r="I171" s="0">
-        <x:v>0.0234</x:v>
+        <x:v>0.0845</x:v>
       </x:c>
     </x:row>
     <x:row r="172" spans="1:9">
       <x:c r="A172" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B172" s="0">
-        <x:v>17.71</x:v>
+        <x:v>16.8</x:v>
       </x:c>
       <x:c r="C172" s="0">
-        <x:v>-0.04</x:v>
+        <x:v>0.36</x:v>
       </x:c>
       <x:c r="D172" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="E172" s="0">
-        <x:v>815000</x:v>
+        <x:v>31860000</x:v>
       </x:c>
       <x:c r="F172" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G172" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H172" s="0">
-        <x:v>2020891371</x:v>
+        <x:v>3025063909</x:v>
       </x:c>
       <x:c r="I172" s="0">
-        <x:v>0.0202</x:v>
+        <x:v>0.4539</x:v>
       </x:c>
     </x:row>
     <x:row r="173" spans="1:9">
       <x:c r="A173" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B173" s="0">
-        <x:v>84.2</x:v>
+        <x:v>98.2</x:v>
       </x:c>
       <x:c r="C173" s="0">
-        <x:v>0.6</x:v>
+        <x:v>-1.8</x:v>
       </x:c>
       <x:c r="D173" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="E173" s="0">
-        <x:v>8300000</x:v>
+        <x:v>41650000</x:v>
       </x:c>
       <x:c r="F173" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G173" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H173" s="0">
-        <x:v>2941310980</x:v>
+        <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I173" s="0">
-        <x:v>0.1417</x:v>
+        <x:v>0.0234</x:v>
       </x:c>
     </x:row>
     <x:row r="174" spans="1:9">
       <x:c r="A174" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B174" s="0">
-        <x:v>4.3</x:v>
+        <x:v>19.48</x:v>
       </x:c>
       <x:c r="C174" s="0">
-        <x:v>0.05</x:v>
+        <x:v>1.77</x:v>
       </x:c>
       <x:c r="D174" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="E174" s="0">
-        <x:v>13000000</x:v>
+        <x:v>815000</x:v>
       </x:c>
       <x:c r="F174" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G174" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H174" s="0">
-        <x:v>1416740879</x:v>
+        <x:v>2020891371</x:v>
       </x:c>
       <x:c r="I174" s="0">
-        <x:v>0.4613</x:v>
+        <x:v>0.0202</x:v>
       </x:c>
     </x:row>
     <x:row r="175" spans="1:9">
       <x:c r="A175" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B175" s="0">
-        <x:v>136.9</x:v>
+        <x:v>86.5</x:v>
       </x:c>
       <x:c r="C175" s="0">
-        <x:v>12.4</x:v>
+        <x:v>2.3</x:v>
       </x:c>
       <x:c r="D175" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="E175" s="0">
-        <x:v>1999793</x:v>
+        <x:v>8300000</x:v>
       </x:c>
       <x:c r="F175" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G175" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H175" s="0">
-        <x:v>1742315226</x:v>
+        <x:v>2941310980</x:v>
       </x:c>
       <x:c r="I175" s="0">
-        <x:v>0.0494</x:v>
+        <x:v>0.1417</x:v>
       </x:c>
     </x:row>
     <x:row r="176" spans="1:9">
       <x:c r="A176" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B176" s="0">
-        <x:v>57.05</x:v>
+        <x:v>4.4</x:v>
       </x:c>
       <x:c r="C176" s="0">
-        <x:v>-1.45</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="D176" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="E176" s="0">
-        <x:v>1859145</x:v>
+        <x:v>13000000</x:v>
       </x:c>
       <x:c r="F176" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G176" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H176" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>1416740879</x:v>
       </x:c>
       <x:c r="I176" s="0">
-        <x:v>0.0324</x:v>
+        <x:v>0.4613</x:v>
       </x:c>
     </x:row>
     <x:row r="177" spans="1:9">
       <x:c r="A177" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B177" s="0">
-        <x:v>3.46</x:v>
+        <x:v>150.5</x:v>
       </x:c>
       <x:c r="C177" s="0">
-        <x:v>-0.01</x:v>
+        <x:v>13.6</x:v>
       </x:c>
       <x:c r="D177" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="E177" s="0">
-        <x:v>689661000</x:v>
+        <x:v>1999793</x:v>
       </x:c>
       <x:c r="F177" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G177" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H177" s="0">
-        <x:v>7382591324</x:v>
+        <x:v>1742315226</x:v>
       </x:c>
       <x:c r="I177" s="0">
-        <x:v>0.0934</x:v>
+        <x:v>0.0494</x:v>
       </x:c>
     </x:row>
     <x:row r="178" spans="1:9">
       <x:c r="A178" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B178" s="0">
-        <x:v>57.05</x:v>
+        <x:v>57.25</x:v>
       </x:c>
       <x:c r="C178" s="0">
-        <x:v>-1.45</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="D178" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="E178" s="0">
-        <x:v>1902000</x:v>
+        <x:v>1859145</x:v>
       </x:c>
       <x:c r="F178" s="0" t="s">
         <x:v>11</x:v>
@@ -5958,53 +5958,53 @@
         <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I178" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0324</x:v>
       </x:c>
     </x:row>
     <x:row r="179" spans="1:9">
       <x:c r="A179" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B179" s="0">
-        <x:v>100</x:v>
+        <x:v>3.41</x:v>
       </x:c>
       <x:c r="C179" s="0">
-        <x:v>-0.7</x:v>
+        <x:v>-0.05</x:v>
       </x:c>
       <x:c r="D179" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="E179" s="0">
-        <x:v>56520000</x:v>
+        <x:v>689661000</x:v>
       </x:c>
       <x:c r="F179" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G179" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H179" s="0">
-        <x:v>1781510191</x:v>
+        <x:v>7382591324</x:v>
       </x:c>
       <x:c r="I179" s="0">
-        <x:v>0.0317</x:v>
+        <x:v>0.0934</x:v>
       </x:c>
     </x:row>
     <x:row r="180" spans="1:9">
       <x:c r="A180" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B180" s="0">
-        <x:v>100</x:v>
+        <x:v>57.25</x:v>
       </x:c>
       <x:c r="C180" s="0">
-        <x:v>-0.7</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="D180" s="0" t="s">
         <x:v>142</x:v>
       </x:c>
       <x:c r="E180" s="0">
-        <x:v>888325</x:v>
+        <x:v>1902000</x:v>
       </x:c>
       <x:c r="F180" s="0" t="s">
         <x:v>11</x:v>
@@ -6013,7 +6013,7 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H180" s="0">
-        <x:v>1781510191</x:v>
+        <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I180" s="0">
         <x:v>0</x:v>
@@ -6021,77 +6021,77 @@
     </x:row>
     <x:row r="181" spans="1:9">
       <x:c r="A181" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B181" s="0">
-        <x:v>8.8</x:v>
+        <x:v>98.2</x:v>
       </x:c>
       <x:c r="C181" s="0">
-        <x:v>0.39</x:v>
+        <x:v>-1.8</x:v>
       </x:c>
       <x:c r="D181" s="0" t="s">
         <x:v>142</x:v>
       </x:c>
       <x:c r="E181" s="0">
-        <x:v>5581810</x:v>
+        <x:v>56520000</x:v>
       </x:c>
       <x:c r="F181" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G181" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H181" s="0">
-        <x:v>9028523851</x:v>
+        <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I181" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0317</x:v>
       </x:c>
     </x:row>
     <x:row r="182" spans="1:9">
       <x:c r="A182" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B182" s="0">
-        <x:v>57.05</x:v>
+        <x:v>98.2</x:v>
       </x:c>
       <x:c r="C182" s="0">
-        <x:v>-1.45</x:v>
+        <x:v>-1.8</x:v>
       </x:c>
       <x:c r="D182" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="E182" s="0">
-        <x:v>504000000</x:v>
+        <x:v>888325</x:v>
       </x:c>
       <x:c r="F182" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G182" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H182" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I182" s="0">
-        <x:v>0.2043</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="183" spans="1:9">
       <x:c r="A183" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B183" s="0">
-        <x:v>320.75</x:v>
+        <x:v>9.68</x:v>
       </x:c>
       <x:c r="C183" s="0">
-        <x:v>3</x:v>
+        <x:v>0.88</x:v>
       </x:c>
       <x:c r="D183" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="E183" s="0">
-        <x:v>21500032</x:v>
+        <x:v>5581810</x:v>
       </x:c>
       <x:c r="F183" s="0" t="s">
         <x:v>11</x:v>
@@ -6100,38 +6100,96 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H183" s="0">
-        <x:v>24073631758</x:v>
+        <x:v>9028523851</x:v>
       </x:c>
       <x:c r="I183" s="0">
-        <x:v>0.0383</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="184" spans="1:9">
       <x:c r="A184" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B184" s="0">
-        <x:v>1190</x:v>
+        <x:v>57.25</x:v>
       </x:c>
       <x:c r="C184" s="0">
-        <x:v>2</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="D184" s="0" t="s">
         <x:v>143</x:v>
       </x:c>
       <x:c r="E184" s="0">
+        <x:v>504000000</x:v>
+      </x:c>
+      <x:c r="F184" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="G184" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H184" s="0">
+        <x:v>2467243928</x:v>
+      </x:c>
+      <x:c r="I184" s="0">
+        <x:v>0.2043</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185" spans="1:9">
+      <x:c r="A185" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B185" s="0">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c r="C185" s="0">
+        <x:v>5.25</x:v>
+      </x:c>
+      <x:c r="D185" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="E185" s="0">
+        <x:v>21500032</x:v>
+      </x:c>
+      <x:c r="F185" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G185" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H185" s="0">
+        <x:v>24073631758</x:v>
+      </x:c>
+      <x:c r="I185" s="0">
+        <x:v>0.0383</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186" spans="1:9">
+      <x:c r="A186" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B186" s="0">
+        <x:v>1200</x:v>
+      </x:c>
+      <x:c r="C186" s="0">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D186" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="E186" s="0">
         <x:v>6455151</x:v>
       </x:c>
-      <x:c r="F184" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G184" s="0">
-        <x:v>2025.09</x:v>
-      </x:c>
-      <x:c r="H184" s="0">
+      <x:c r="F186" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G186" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H186" s="0">
         <x:v>1586603352</x:v>
       </x:c>
-      <x:c r="I184" s="0">
+      <x:c r="I186" s="0">
         <x:v>0.1745</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/yeni-is-anlasmalari/data/yeni-is-anlasmalari.xlsx
+++ b/app/borsa/yeni-is-anlasmalari/data/yeni-is-anlasmalari.xlsx
@@ -43,15 +43,21 @@
     <x:t>Yeni İş İlişkisi / Yıllık Satışlar</x:t>
   </x:si>
   <x:si>
+    <x:t>SMRTG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-05-11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>USD</x:t>
+  </x:si>
+  <x:si>
     <x:t>VBTYZ</x:t>
   </x:si>
   <x:si>
     <x:t>2026-05-07</x:t>
   </x:si>
   <x:si>
-    <x:t>USD</x:t>
-  </x:si>
-  <x:si>
     <x:t>FORTE</x:t>
   </x:si>
   <x:si>
@@ -101,9 +107,6 @@
   </x:si>
   <x:si>
     <x:t>2026-04-30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMRTG</x:t>
   </x:si>
   <x:si>
     <x:t>2026-04-29</x:t>
@@ -796,7 +799,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I186"/>
+  <x:dimension ref="A1:I187"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -833,16 +836,16 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>24.38</x:v>
+        <x:v>10.64</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>-0.38</x:v>
+        <x:v>0.96</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>1816317</x:v>
+        <x:v>10201876</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
         <x:v>11</x:v>
@@ -851,10 +854,10 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>2427624044</x:v>
+        <x:v>10581001663</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>0.0338</x:v>
+        <x:v>0.0436</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -862,16 +865,16 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>98.2</x:v>
+        <x:v>24.68</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>-1.8</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>3384000</x:v>
+        <x:v>1816317</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
         <x:v>11</x:v>
@@ -880,27 +883,27 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>2427624044</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>0.0627</x:v>
+        <x:v>0.0338</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
       <x:c r="A4" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B4" s="0">
+        <x:v>99.5</x:v>
+      </x:c>
+      <x:c r="C4" s="0">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B4" s="0">
-        <x:v>4.16</x:v>
-      </x:c>
-      <x:c r="C4" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
       <x:c r="E4" s="0">
-        <x:v>1178000</x:v>
+        <x:v>3384000</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
         <x:v>11</x:v>
@@ -909,39 +912,39 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>2875634546</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>0.0185</x:v>
+        <x:v>0.0627</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
       <x:c r="A5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>7.69</x:v>
+        <x:v>4.28</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>0.12</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>1180000</x:v>
+        <x:v>1178000</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G5" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>2322993973</x:v>
+        <x:v>2875634546</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>0.0268</x:v>
+        <x:v>0.0185</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -949,45 +952,45 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>111.7</x:v>
+        <x:v>8.45</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>-0.1</x:v>
+        <x:v>0.76</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>1220000</x:v>
+        <x:v>1180000</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G6" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>2988208362</x:v>
+        <x:v>2322993973</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>0.0184</x:v>
+        <x:v>0.0268</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
       <x:c r="A7" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>28.78</x:v>
+        <x:v>117.3</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>-0.38</x:v>
+        <x:v>5.6</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>26910</x:v>
+        <x:v>1220000</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
         <x:v>11</x:v>
@@ -996,27 +999,27 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>7297855153</x:v>
+        <x:v>2988208362</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>0.0002</x:v>
+        <x:v>0.0184</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
       <x:c r="A8" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>57.25</x:v>
+        <x:v>29.36</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>0.2</x:v>
+        <x:v>0.58</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>2517084</x:v>
+        <x:v>26910</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
         <x:v>11</x:v>
@@ -1025,27 +1028,27 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>7297855153</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>0.0269</x:v>
+        <x:v>0.0002</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
       <x:c r="A9" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>24.38</x:v>
+        <x:v>58.7</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>-0.38</x:v>
+        <x:v>1.45</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>9600000</x:v>
+        <x:v>2517084</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
         <x:v>11</x:v>
@@ -1054,39 +1057,39 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>2427624044</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>0.1785</x:v>
+        <x:v>0.0269</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
       <x:c r="A10" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>296.75</x:v>
+        <x:v>24.68</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>13.75</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>9172451</x:v>
+        <x:v>9600000</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G10" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>709077088</x:v>
+        <x:v>2427624044</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>0.0129</x:v>
+        <x:v>0.1785</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -1094,28 +1097,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>37.6</x:v>
+        <x:v>311.25</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>14.5</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E11" s="0">
+        <x:v>9172451</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="E11" s="0">
-        <x:v>32493961</x:v>
-      </x:c>
-      <x:c r="F11" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="G11" s="0">
-        <x:v>2026.03</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>17386730041</x:v>
+        <x:v>709077088</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0129</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -1123,28 +1126,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>86.5</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>2.3</x:v>
+        <x:v>2.4</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>940002</x:v>
+        <x:v>32493961</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2026.03</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>17386730041</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>0.0121</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -1152,86 +1155,86 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>150.5</x:v>
+        <x:v>86.55</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>13.6</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>920000</x:v>
+        <x:v>940002</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G13" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>3150489640</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>0.0154</x:v>
+        <x:v>0.0121</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
       <x:c r="A14" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>98.2</x:v>
+        <x:v>146.5</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>-1.8</x:v>
+        <x:v>-4</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>12100000</x:v>
+        <x:v>920000</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G14" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>0.005</x:v>
+        <x:v>0.0154</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
       <x:c r="A15" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B15" s="0">
+        <x:v>99.5</x:v>
+      </x:c>
+      <x:c r="C15" s="0">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="B15" s="0">
-        <x:v>428.5</x:v>
-      </x:c>
-      <x:c r="C15" s="0">
-        <x:v>0.5</x:v>
-      </x:c>
-      <x:c r="D15" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
       <x:c r="E15" s="0">
-        <x:v>125100000</x:v>
+        <x:v>12100000</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>2026.03</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>184925592000</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>0.0304</x:v>
+        <x:v>0.005</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -1239,173 +1242,173 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>9.68</x:v>
+        <x:v>431.75</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>0.88</x:v>
+        <x:v>3.25</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>32010000</x:v>
+        <x:v>125100000</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2026.03</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>10581001663</x:v>
+        <x:v>184925592000</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>0.1592</x:v>
+        <x:v>0.0304</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
       <x:c r="A17" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B17" s="0">
+        <x:v>10.64</x:v>
+      </x:c>
+      <x:c r="C17" s="0">
+        <x:v>0.96</x:v>
+      </x:c>
+      <x:c r="D17" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E17" s="0">
+        <x:v>32010000</x:v>
+      </x:c>
+      <x:c r="F17" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B17" s="0">
-        <x:v>28.78</x:v>
-      </x:c>
-      <x:c r="C17" s="0">
-        <x:v>-0.38</x:v>
-      </x:c>
-      <x:c r="D17" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E17" s="0">
-        <x:v>76650</x:v>
-      </x:c>
-      <x:c r="F17" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="G17" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>7297855153</x:v>
+        <x:v>10581001663</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>0.0005</x:v>
+        <x:v>0.1592</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
       <x:c r="A18" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>150.5</x:v>
+        <x:v>29.36</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>13.6</x:v>
+        <x:v>0.58</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>915000</x:v>
+        <x:v>76650</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G18" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>3150489640</x:v>
+        <x:v>7297855153</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>0.0153</x:v>
+        <x:v>0.0005</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
       <x:c r="A19" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>37.6</x:v>
+        <x:v>146.5</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>-4</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>2136645</x:v>
+        <x:v>915000</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>2026.03</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>17386730041</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>0.0055</x:v>
+        <x:v>0.0153</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
       <x:c r="A20" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B20" s="0">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C20" s="0">
+        <x:v>2.4</x:v>
+      </x:c>
+      <x:c r="D20" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="B20" s="0">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C20" s="0">
-        <x:v>0.16</x:v>
-      </x:c>
-      <x:c r="D20" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
       <x:c r="E20" s="0">
-        <x:v>132077304</x:v>
+        <x:v>2136645</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2026.03</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>855070469</x:v>
+        <x:v>17386730041</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>0.1545</x:v>
+        <x:v>0.0055</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
       <x:c r="A21" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B21" s="0">
+        <x:v>6.12</x:v>
+      </x:c>
+      <x:c r="C21" s="0">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="D21" s="0" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="B21" s="0">
-        <x:v>326</x:v>
-      </x:c>
-      <x:c r="C21" s="0">
-        <x:v>5.25</x:v>
-      </x:c>
-      <x:c r="D21" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
       <x:c r="E21" s="0">
-        <x:v>51531000</x:v>
+        <x:v>132077304</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G21" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>35290767390</x:v>
+        <x:v>855070469</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>0.0656</x:v>
+        <x:v>0.1545</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1413,16 +1416,16 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>1200</x:v>
+        <x:v>339.5</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>10</x:v>
+        <x:v>13.5</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>950978</x:v>
+        <x:v>51531000</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
         <x:v>11</x:v>
@@ -1431,10 +1434,10 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>1883544167</x:v>
+        <x:v>35290767390</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>0.0227</x:v>
+        <x:v>0.0656</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1442,16 +1445,16 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>601.5</x:v>
+        <x:v>1131</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>-19</x:v>
+        <x:v>-69</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>100000000</x:v>
+        <x:v>950978</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
         <x:v>11</x:v>
@@ -1460,39 +1463,39 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>71453576000</x:v>
+        <x:v>1883544167</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>0.0628</x:v>
+        <x:v>0.0227</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
       <x:c r="A24" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>86.5</x:v>
+        <x:v>596.5</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>2.3</x:v>
+        <x:v>-5</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>286071819</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G24" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>71453576000</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>0.0818</x:v>
+        <x:v>0.0628</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1500,132 +1503,132 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>150.5</x:v>
+        <x:v>86.55</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>13.6</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>883793</x:v>
+        <x:v>286071819</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G25" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>3150489640</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>0.0148</x:v>
+        <x:v>0.0818</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
       <x:c r="A26" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>57.25</x:v>
+        <x:v>146.5</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>0.2</x:v>
+        <x:v>-4</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>606770</x:v>
+        <x:v>883793</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G26" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>0.0064</x:v>
+        <x:v>0.0148</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
       <x:c r="A27" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B27" s="0">
+        <x:v>58.7</x:v>
+      </x:c>
+      <x:c r="C27" s="0">
+        <x:v>1.45</x:v>
+      </x:c>
+      <x:c r="D27" s="0" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="B27" s="0">
-        <x:v>63.15</x:v>
-      </x:c>
-      <x:c r="C27" s="0">
-        <x:v>2.65</x:v>
-      </x:c>
-      <x:c r="D27" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
       <x:c r="E27" s="0">
-        <x:v>505597002</x:v>
+        <x:v>606770</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G27" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>8121300519</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>0.0623</x:v>
+        <x:v>0.0064</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
       <x:c r="A28" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>57.25</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>0.2</x:v>
+        <x:v>2.85</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>948000</x:v>
+        <x:v>505597002</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G28" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>8121300519</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>0.0101</x:v>
+        <x:v>0.0623</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
       <x:c r="A29" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>98.2</x:v>
+        <x:v>58.7</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>-1.8</x:v>
+        <x:v>1.45</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>622000</x:v>
+        <x:v>948000</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
         <x:v>11</x:v>
@@ -1634,85 +1637,85 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>0.0114</x:v>
+        <x:v>0.0101</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
       <x:c r="A30" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>4.16</x:v>
+        <x:v>99.5</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>0</x:v>
+        <x:v>1.3</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>983000</x:v>
+        <x:v>622000</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G30" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>2875634546</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>0.018</x:v>
+        <x:v>0.0114</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
       <x:c r="A31" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B31" s="0">
+        <x:v>4.28</x:v>
+      </x:c>
+      <x:c r="C31" s="0">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="D31" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="B31" s="0">
-        <x:v>76.85</x:v>
-      </x:c>
-      <x:c r="C31" s="0">
-        <x:v>-3.4</x:v>
-      </x:c>
-      <x:c r="D31" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
       <x:c r="E31" s="0">
-        <x:v>3421818</x:v>
+        <x:v>983000</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G31" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>5948036961</x:v>
+        <x:v>2875634546</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>0.0257</x:v>
+        <x:v>0.018</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
       <x:c r="A32" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B32" s="0">
+        <x:v>76.5</x:v>
+      </x:c>
+      <x:c r="C32" s="0">
+        <x:v>-0.35</x:v>
+      </x:c>
+      <x:c r="D32" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="B32" s="0">
-        <x:v>49.6</x:v>
-      </x:c>
-      <x:c r="C32" s="0">
-        <x:v>0.8</x:v>
-      </x:c>
-      <x:c r="D32" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
       <x:c r="E32" s="0">
-        <x:v>697435</x:v>
+        <x:v>3421818</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
         <x:v>11</x:v>
@@ -1721,10 +1724,10 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>4728937463</x:v>
+        <x:v>5948036961</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>0.0066</x:v>
+        <x:v>0.0257</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1732,16 +1735,16 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>80.6</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>7.3</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>4587145</x:v>
+        <x:v>697435</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
         <x:v>11</x:v>
@@ -1750,27 +1753,27 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>16733157490</x:v>
+        <x:v>4728937463</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>0.0123</x:v>
+        <x:v>0.0066</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
       <x:c r="A34" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B34" s="0">
+        <x:v>86.25</x:v>
+      </x:c>
+      <x:c r="C34" s="0">
+        <x:v>5.65</x:v>
+      </x:c>
+      <x:c r="D34" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="B34" s="0">
-        <x:v>46.44</x:v>
-      </x:c>
-      <x:c r="C34" s="0">
-        <x:v>2.7</x:v>
-      </x:c>
-      <x:c r="D34" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
       <x:c r="E34" s="0">
-        <x:v>43200000</x:v>
+        <x:v>4587145</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
         <x:v>11</x:v>
@@ -1779,97 +1782,97 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>8236540064</x:v>
+        <x:v>16733157490</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>0.2345</x:v>
+        <x:v>0.0123</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
       <x:c r="A35" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B35" s="0">
+        <x:v>51.05</x:v>
+      </x:c>
+      <x:c r="C35" s="0">
+        <x:v>4.61</x:v>
+      </x:c>
+      <x:c r="D35" s="0" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="B35" s="0">
-        <x:v>19.48</x:v>
-      </x:c>
-      <x:c r="C35" s="0">
-        <x:v>1.77</x:v>
-      </x:c>
-      <x:c r="D35" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
       <x:c r="E35" s="0">
-        <x:v>1200000</x:v>
+        <x:v>43200000</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G35" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>3139850323</x:v>
+        <x:v>8236540064</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>0.0201</x:v>
+        <x:v>0.2345</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
       <x:c r="A36" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>63.15</x:v>
+        <x:v>19.37</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>2.65</x:v>
+        <x:v>-0.11</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>247902522</x:v>
+        <x:v>1200000</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G36" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>8121300519</x:v>
+        <x:v>3139850323</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>0.0305</x:v>
+        <x:v>0.0201</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
       <x:c r="A37" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>57.25</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>0.2</x:v>
+        <x:v>2.85</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>366000</x:v>
+        <x:v>247902522</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G37" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>8121300519</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>0.0039</x:v>
+        <x:v>0.0305</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1877,77 +1880,77 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>296.75</x:v>
+        <x:v>58.7</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>13.75</x:v>
+        <x:v>1.45</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>141051834</x:v>
+        <x:v>366000</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G38" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>709077088</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>0.1989</x:v>
+        <x:v>0.0039</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
       <x:c r="A39" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B39" s="0">
+        <x:v>311.25</x:v>
+      </x:c>
+      <x:c r="C39" s="0">
+        <x:v>14.5</x:v>
+      </x:c>
+      <x:c r="D39" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="B39" s="0">
-        <x:v>4.94</x:v>
-      </x:c>
-      <x:c r="C39" s="0">
-        <x:v>-0.05</x:v>
-      </x:c>
-      <x:c r="D39" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
       <x:c r="E39" s="0">
-        <x:v>5096500000</x:v>
+        <x:v>141051834</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>19538660616</x:v>
+        <x:v>709077088</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>0.2608</x:v>
+        <x:v>0.1989</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
       <x:c r="A40" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B40" s="0">
+        <x:v>5.03</x:v>
+      </x:c>
+      <x:c r="C40" s="0">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="D40" s="0" t="s">
         <x:v>48</x:v>
-      </x:c>
-      <x:c r="B40" s="0">
-        <x:v>4.94</x:v>
-      </x:c>
-      <x:c r="C40" s="0">
-        <x:v>-0.05</x:v>
-      </x:c>
-      <x:c r="D40" s="0" t="s">
-        <x:v>47</x:v>
       </x:c>
       <x:c r="E40" s="0">
         <x:v>5096500000</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G40" s="0">
         <x:v>2025.09</x:v>
@@ -1961,48 +1964,48 @@
     </x:row>
     <x:row r="41" spans="1:9">
       <x:c r="A41" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>37.6</x:v>
+        <x:v>5.03</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>0.09</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>37500000</x:v>
+        <x:v>5096500000</x:v>
       </x:c>
       <x:c r="F41" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>16355768622</x:v>
+        <x:v>19538660616</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>0.1024</x:v>
+        <x:v>0.2608</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
       <x:c r="A42" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B42" s="0">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C42" s="0">
+        <x:v>2.4</x:v>
+      </x:c>
+      <x:c r="D42" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B42" s="0">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="C42" s="0">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D42" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
       <x:c r="E42" s="0">
-        <x:v>2030000</x:v>
+        <x:v>37500000</x:v>
       </x:c>
       <x:c r="F42" s="0" t="s">
         <x:v>11</x:v>
@@ -2011,27 +2014,27 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>2159813703</x:v>
+        <x:v>16355768622</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>0.042</x:v>
+        <x:v>0.1024</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
       <x:c r="A43" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>80.6</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>7.3</x:v>
+        <x:v>-13</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>31146246</x:v>
+        <x:v>2030000</x:v>
       </x:c>
       <x:c r="F43" s="0" t="s">
         <x:v>11</x:v>
@@ -2040,59 +2043,59 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>16733157490</x:v>
+        <x:v>2159813703</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>0.0832</x:v>
+        <x:v>0.042</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
       <x:c r="A44" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>12.86</x:v>
+        <x:v>86.25</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>-0.14</x:v>
+        <x:v>5.65</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>1000000</x:v>
+        <x:v>31146246</x:v>
       </x:c>
       <x:c r="F44" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G44" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>7221187888</x:v>
+        <x:v>16733157490</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>0.0001</x:v>
+        <x:v>0.0832</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
       <x:c r="A45" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>12.86</x:v>
+        <x:v>13.24</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>-0.14</x:v>
+        <x:v>0.38</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>3150000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="F45" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G45" s="0">
         <x:v>2025.12</x:v>
@@ -2101,27 +2104,27 @@
         <x:v>7221187888</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>0.0227</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
       <x:c r="A46" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>12.86</x:v>
+        <x:v>13.24</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>-0.14</x:v>
+        <x:v>0.38</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>2690000</x:v>
+        <x:v>3150000</x:v>
       </x:c>
       <x:c r="F46" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G46" s="0">
         <x:v>2025.12</x:v>
@@ -2130,24 +2133,24 @@
         <x:v>7221187888</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>0.0166</x:v>
+        <x:v>0.0227</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
       <x:c r="A47" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>80.6</x:v>
+        <x:v>13.24</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>7.3</x:v>
+        <x:v>0.38</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>4103000</x:v>
+        <x:v>2690000</x:v>
       </x:c>
       <x:c r="F47" s="0" t="s">
         <x:v>11</x:v>
@@ -2156,233 +2159,233 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>16733157490</x:v>
+        <x:v>7221187888</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>0.0109</x:v>
+        <x:v>0.0166</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
       <x:c r="A48" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>150.5</x:v>
+        <x:v>86.25</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>13.6</x:v>
+        <x:v>5.65</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>500000</x:v>
+        <x:v>4103000</x:v>
       </x:c>
       <x:c r="F48" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G48" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>3150489640</x:v>
+        <x:v>16733157490</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>0.0083</x:v>
+        <x:v>0.0109</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
       <x:c r="A49" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>57.25</x:v>
+        <x:v>146.5</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>0.2</x:v>
+        <x:v>-4</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>872928</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="F49" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G49" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>0.0092</x:v>
+        <x:v>0.0083</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
       <x:c r="A50" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>98.2</x:v>
+        <x:v>58.7</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>-1.8</x:v>
+        <x:v>1.45</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>21250000</x:v>
+        <x:v>872928</x:v>
       </x:c>
       <x:c r="F50" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G50" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>0.0087</x:v>
+        <x:v>0.0092</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
       <x:c r="A51" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>63.15</x:v>
+        <x:v>99.5</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>2.65</x:v>
+        <x:v>1.3</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>67690912</x:v>
+        <x:v>21250000</x:v>
       </x:c>
       <x:c r="F51" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G51" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>8121300519</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>0.0083</x:v>
+        <x:v>0.0087</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
       <x:c r="A52" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>37.6</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>2.85</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>65458848</x:v>
+        <x:v>67690912</x:v>
       </x:c>
       <x:c r="F52" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G52" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>16355768622</x:v>
+        <x:v>8121300519</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>0.1784</x:v>
+        <x:v>0.0083</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:9">
       <x:c r="A53" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B53" s="0">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C53" s="0">
+        <x:v>2.4</x:v>
+      </x:c>
+      <x:c r="D53" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="B53" s="0">
-        <x:v>24.9</x:v>
-      </x:c>
-      <x:c r="C53" s="0">
-        <x:v>0.06</x:v>
-      </x:c>
-      <x:c r="D53" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
       <x:c r="E53" s="0">
-        <x:v>689500000</x:v>
+        <x:v>65458848</x:v>
       </x:c>
       <x:c r="F53" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G53" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H53" s="0">
-        <x:v>884571536</x:v>
+        <x:v>16355768622</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>0.7795</x:v>
+        <x:v>0.1784</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:9">
       <x:c r="A54" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B54" s="0">
-        <x:v>7.69</x:v>
+        <x:v>25.08</x:v>
       </x:c>
       <x:c r="C54" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E54" s="0">
-        <x:v>3024490</x:v>
+        <x:v>689500000</x:v>
       </x:c>
       <x:c r="F54" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G54" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>2322993973</x:v>
+        <x:v>884571536</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>0.0671</x:v>
+        <x:v>0.7795</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:9">
       <x:c r="A55" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B55" s="0">
-        <x:v>7.69</x:v>
+        <x:v>8.45</x:v>
       </x:c>
       <x:c r="C55" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>0.76</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E55" s="0">
-        <x:v>4510336</x:v>
+        <x:v>3024490</x:v>
       </x:c>
       <x:c r="F55" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G55" s="0">
         <x:v>2025.12</x:v>
@@ -2391,24 +2394,24 @@
         <x:v>2322993973</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>0.0865</x:v>
+        <x:v>0.0671</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:9">
       <x:c r="A56" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B56" s="0">
-        <x:v>61.4</x:v>
+        <x:v>8.45</x:v>
       </x:c>
       <x:c r="C56" s="0">
-        <x:v>3</x:v>
+        <x:v>0.76</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E56" s="0">
-        <x:v>205000000</x:v>
+        <x:v>4510336</x:v>
       </x:c>
       <x:c r="F56" s="0" t="s">
         <x:v>11</x:v>
@@ -2417,175 +2420,175 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H56" s="0">
-        <x:v>20597209000</x:v>
+        <x:v>2322993973</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>0.4434</x:v>
+        <x:v>0.0865</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:9">
       <x:c r="A57" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B57" s="0">
+        <x:v>61.35</x:v>
+      </x:c>
+      <x:c r="C57" s="0">
+        <x:v>-0.05</x:v>
+      </x:c>
+      <x:c r="D57" s="0" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="B57" s="0">
-        <x:v>310.25</x:v>
-      </x:c>
-      <x:c r="C57" s="0">
-        <x:v>4.25</x:v>
-      </x:c>
-      <x:c r="D57" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
       <x:c r="E57" s="0">
-        <x:v>305000000</x:v>
+        <x:v>205000000</x:v>
       </x:c>
       <x:c r="F57" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G57" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H57" s="0">
-        <x:v>400439646</x:v>
+        <x:v>20597209000</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>0.7617</x:v>
+        <x:v>0.4434</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:9">
       <x:c r="A58" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B58" s="0">
-        <x:v>86.5</x:v>
+        <x:v>315.5</x:v>
       </x:c>
       <x:c r="C58" s="0">
-        <x:v>2.3</x:v>
+        <x:v>5.25</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E58" s="0">
-        <x:v>11700000</x:v>
+        <x:v>305000000</x:v>
       </x:c>
       <x:c r="F58" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G58" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H58" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>400439646</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>0.1718</x:v>
+        <x:v>0.7617</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:9">
       <x:c r="A59" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B59" s="0">
-        <x:v>288</x:v>
+        <x:v>86.55</x:v>
       </x:c>
       <x:c r="C59" s="0">
-        <x:v>23</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E59" s="0">
-        <x:v>1900000</x:v>
+        <x:v>11700000</x:v>
       </x:c>
       <x:c r="F59" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G59" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H59" s="0">
-        <x:v>2159813703</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>0.0391</x:v>
+        <x:v>0.1718</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:9">
       <x:c r="A60" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B60" s="0">
-        <x:v>4.16</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="C60" s="0">
-        <x:v>0</x:v>
+        <x:v>-13</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E60" s="0">
-        <x:v>1670000</x:v>
+        <x:v>1900000</x:v>
       </x:c>
       <x:c r="F60" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G60" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H60" s="0">
-        <x:v>2875634546</x:v>
+        <x:v>2159813703</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>0.0298</x:v>
+        <x:v>0.0391</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:9">
       <x:c r="A61" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B61" s="0">
-        <x:v>24.9</x:v>
+        <x:v>4.28</x:v>
       </x:c>
       <x:c r="C61" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0.12</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E61" s="0">
-        <x:v>48895800</x:v>
+        <x:v>1670000</x:v>
       </x:c>
       <x:c r="F61" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G61" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H61" s="0">
-        <x:v>884571536</x:v>
+        <x:v>2875634546</x:v>
       </x:c>
       <x:c r="I61" s="0">
-        <x:v>0.0553</x:v>
+        <x:v>0.0298</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:9">
       <x:c r="A62" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B62" s="0">
-        <x:v>24.9</x:v>
+        <x:v>25.08</x:v>
       </x:c>
       <x:c r="C62" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E62" s="0">
-        <x:v>689500000</x:v>
+        <x:v>48895800</x:v>
       </x:c>
       <x:c r="F62" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G62" s="0">
         <x:v>2025.12</x:v>
@@ -2594,36 +2597,36 @@
         <x:v>884571536</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>0.7795</x:v>
+        <x:v>0.0553</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:9">
       <x:c r="A63" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B63" s="0">
+        <x:v>25.08</x:v>
+      </x:c>
+      <x:c r="C63" s="0">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="D63" s="0" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="B63" s="0">
-        <x:v>48.28</x:v>
-      </x:c>
-      <x:c r="C63" s="0">
-        <x:v>-0.52</x:v>
-      </x:c>
-      <x:c r="D63" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
       <x:c r="E63" s="0">
-        <x:v>3102911</x:v>
+        <x:v>689500000</x:v>
       </x:c>
       <x:c r="F63" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G63" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H63" s="0">
-        <x:v>2907014564</x:v>
+        <x:v>884571536</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>0.0475</x:v>
+        <x:v>0.7795</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:9">
@@ -2631,103 +2634,103 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="B64" s="0">
-        <x:v>25.78</x:v>
+        <x:v>49.6</x:v>
       </x:c>
       <x:c r="C64" s="0">
-        <x:v>-0.16</x:v>
+        <x:v>1.32</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E64" s="0">
-        <x:v>13000000</x:v>
+        <x:v>3102911</x:v>
       </x:c>
       <x:c r="F64" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G64" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H64" s="0">
-        <x:v>11834942581</x:v>
+        <x:v>2907014564</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>0.0563</x:v>
+        <x:v>0.0475</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:9">
       <x:c r="A65" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B65" s="0">
-        <x:v>76.85</x:v>
+        <x:v>26.38</x:v>
       </x:c>
       <x:c r="C65" s="0">
-        <x:v>-3.4</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E65" s="0">
-        <x:v>6800000</x:v>
+        <x:v>13000000</x:v>
       </x:c>
       <x:c r="F65" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G65" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H65" s="0">
-        <x:v>5948036961</x:v>
+        <x:v>11834942581</x:v>
       </x:c>
       <x:c r="I65" s="0">
-        <x:v>0.0583</x:v>
+        <x:v>0.0563</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:9">
       <x:c r="A66" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B66" s="0">
-        <x:v>61.4</x:v>
+        <x:v>76.5</x:v>
       </x:c>
       <x:c r="C66" s="0">
-        <x:v>3</x:v>
+        <x:v>-0.35</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E66" s="0">
-        <x:v>36750000</x:v>
+        <x:v>6800000</x:v>
       </x:c>
       <x:c r="F66" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G66" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H66" s="0">
-        <x:v>20597209000</x:v>
+        <x:v>5948036961</x:v>
       </x:c>
       <x:c r="I66" s="0">
-        <x:v>0.0793</x:v>
+        <x:v>0.0583</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:9">
       <x:c r="A67" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B67" s="0">
-        <x:v>1200</x:v>
+        <x:v>61.35</x:v>
       </x:c>
       <x:c r="C67" s="0">
-        <x:v>10</x:v>
+        <x:v>-0.05</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
         <x:v>66</x:v>
       </x:c>
       <x:c r="E67" s="0">
-        <x:v>3867260</x:v>
+        <x:v>36750000</x:v>
       </x:c>
       <x:c r="F67" s="0" t="s">
         <x:v>11</x:v>
@@ -2736,68 +2739,68 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H67" s="0">
-        <x:v>1883544167</x:v>
+        <x:v>20597209000</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>0.0912</x:v>
+        <x:v>0.0793</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:9">
       <x:c r="A68" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B68" s="0">
+        <x:v>1131</x:v>
+      </x:c>
+      <x:c r="C68" s="0">
+        <x:v>-69</x:v>
+      </x:c>
+      <x:c r="D68" s="0" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="B68" s="0">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="C68" s="0">
-        <x:v>-0.75</x:v>
-      </x:c>
-      <x:c r="D68" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
       <x:c r="E68" s="0">
-        <x:v>1498029716</x:v>
+        <x:v>3867260</x:v>
       </x:c>
       <x:c r="F68" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G68" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H68" s="0">
-        <x:v>12030341104</x:v>
+        <x:v>1883544167</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>0.1245</x:v>
+        <x:v>0.0912</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:9">
       <x:c r="A69" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B69" s="0">
-        <x:v>37.6</x:v>
+        <x:v>71.1</x:v>
       </x:c>
       <x:c r="C69" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>3.1</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E69" s="0">
-        <x:v>48000000</x:v>
+        <x:v>1498029716</x:v>
       </x:c>
       <x:c r="F69" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G69" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H69" s="0">
-        <x:v>16355768622</x:v>
+        <x:v>12030341104</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>0.1301</x:v>
+        <x:v>0.1245</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:9">
@@ -2805,74 +2808,74 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B70" s="0">
-        <x:v>86.5</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C70" s="0">
-        <x:v>2.3</x:v>
+        <x:v>2.4</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="E70" s="0">
-        <x:v>279699629</x:v>
+        <x:v>48000000</x:v>
       </x:c>
       <x:c r="F70" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G70" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H70" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>16355768622</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>0.08</x:v>
+        <x:v>0.1301</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:9">
       <x:c r="A71" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B71" s="0">
+        <x:v>86.55</x:v>
+      </x:c>
+      <x:c r="C71" s="0">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="D71" s="0" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="B71" s="0">
-        <x:v>16.8</x:v>
-      </x:c>
-      <x:c r="C71" s="0">
-        <x:v>0.36</x:v>
-      </x:c>
-      <x:c r="D71" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
       <x:c r="E71" s="0">
-        <x:v>7971822</x:v>
+        <x:v>279699629</x:v>
       </x:c>
       <x:c r="F71" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G71" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H71" s="0">
-        <x:v>4675369372</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>0.0756</x:v>
+        <x:v>0.08</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:9">
       <x:c r="A72" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B72" s="0">
-        <x:v>57.25</x:v>
+        <x:v>16.98</x:v>
       </x:c>
       <x:c r="C72" s="0">
-        <x:v>0.2</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E72" s="0">
-        <x:v>1104000</x:v>
+        <x:v>7971822</x:v>
       </x:c>
       <x:c r="F72" s="0" t="s">
         <x:v>11</x:v>
@@ -2881,88 +2884,88 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H72" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>4675369372</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>0.0116</x:v>
+        <x:v>0.0756</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:9">
       <x:c r="A73" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B73" s="0">
-        <x:v>24.9</x:v>
+        <x:v>58.7</x:v>
       </x:c>
       <x:c r="C73" s="0">
-        <x:v>0.06</x:v>
+        <x:v>1.45</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E73" s="0">
-        <x:v>48895800</x:v>
+        <x:v>1104000</x:v>
       </x:c>
       <x:c r="F73" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G73" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H73" s="0">
-        <x:v>884571536</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>0.0553</x:v>
+        <x:v>0.0116</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:9">
       <x:c r="A74" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B74" s="0">
-        <x:v>3.41</x:v>
+        <x:v>25.08</x:v>
       </x:c>
       <x:c r="C74" s="0">
-        <x:v>-0.05</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E74" s="0">
-        <x:v>191089413</x:v>
+        <x:v>48895800</x:v>
       </x:c>
       <x:c r="F74" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G74" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H74" s="0">
-        <x:v>9665356715</x:v>
+        <x:v>884571536</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>0.0198</x:v>
+        <x:v>0.0553</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:9">
       <x:c r="A75" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B75" s="0">
-        <x:v>3.41</x:v>
+        <x:v>3.51</x:v>
       </x:c>
       <x:c r="C75" s="0">
-        <x:v>-0.05</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E75" s="0">
-        <x:v>605627160</x:v>
+        <x:v>191089413</x:v>
       </x:c>
       <x:c r="F75" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G75" s="0">
         <x:v>2025.12</x:v>
@@ -2971,7 +2974,7 @@
         <x:v>9665356715</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>0.0627</x:v>
+        <x:v>0.0198</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:9">
@@ -2979,77 +2982,77 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="B76" s="0">
-        <x:v>27.9</x:v>
+        <x:v>3.51</x:v>
       </x:c>
       <x:c r="C76" s="0">
-        <x:v>0.44</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E76" s="0">
-        <x:v>2356546000</x:v>
+        <x:v>605627160</x:v>
       </x:c>
       <x:c r="F76" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G76" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H76" s="0">
-        <x:v>7708004248</x:v>
+        <x:v>9665356715</x:v>
       </x:c>
       <x:c r="I76" s="0">
-        <x:v>0.3057</x:v>
+        <x:v>0.0627</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:9">
       <x:c r="A77" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B77" s="0">
-        <x:v>19.48</x:v>
+        <x:v>25.98</x:v>
       </x:c>
       <x:c r="C77" s="0">
-        <x:v>1.77</x:v>
+        <x:v>-1.92</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E77" s="0">
-        <x:v>431250</x:v>
+        <x:v>2356546000</x:v>
       </x:c>
       <x:c r="F77" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G77" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H77" s="0">
-        <x:v>3139850323</x:v>
+        <x:v>7708004248</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>0.0071</x:v>
+        <x:v>0.3057</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:9">
       <x:c r="A78" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B78" s="0">
-        <x:v>19.48</x:v>
+        <x:v>19.37</x:v>
       </x:c>
       <x:c r="C78" s="0">
-        <x:v>1.77</x:v>
+        <x:v>-0.11</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E78" s="0">
-        <x:v>800000</x:v>
+        <x:v>431250</x:v>
       </x:c>
       <x:c r="F78" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G78" s="0">
         <x:v>2025.12</x:v>
@@ -3058,82 +3061,82 @@
         <x:v>3139850323</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>0.0131</x:v>
+        <x:v>0.0071</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:9">
       <x:c r="A79" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B79" s="0">
-        <x:v>63.15</x:v>
+        <x:v>19.37</x:v>
       </x:c>
       <x:c r="C79" s="0">
-        <x:v>2.65</x:v>
+        <x:v>-0.11</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E79" s="0">
-        <x:v>127172130</x:v>
+        <x:v>800000</x:v>
       </x:c>
       <x:c r="F79" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G79" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H79" s="0">
-        <x:v>8121300519</x:v>
+        <x:v>3139850323</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>0.0157</x:v>
+        <x:v>0.0131</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:9">
       <x:c r="A80" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B80" s="0">
-        <x:v>49.6</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C80" s="0">
-        <x:v>0.8</x:v>
+        <x:v>2.85</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E80" s="0">
-        <x:v>42625000</x:v>
+        <x:v>127172130</x:v>
       </x:c>
       <x:c r="F80" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G80" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H80" s="0">
-        <x:v>4728937463</x:v>
+        <x:v>8121300519</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>0.3994</x:v>
+        <x:v>0.0157</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:9">
       <x:c r="A81" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B81" s="0">
-        <x:v>98.2</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C81" s="0">
-        <x:v>-1.8</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
         <x:v>74</x:v>
       </x:c>
       <x:c r="E81" s="0">
-        <x:v>1486000</x:v>
+        <x:v>42625000</x:v>
       </x:c>
       <x:c r="F81" s="0" t="s">
         <x:v>11</x:v>
@@ -3142,27 +3145,27 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H81" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>4728937463</x:v>
       </x:c>
       <x:c r="I81" s="0">
-        <x:v>0.027</x:v>
+        <x:v>0.3994</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:9">
       <x:c r="A82" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B82" s="0">
-        <x:v>326</x:v>
+        <x:v>99.5</x:v>
       </x:c>
       <x:c r="C82" s="0">
-        <x:v>5.25</x:v>
+        <x:v>1.3</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E82" s="0">
-        <x:v>768864700</x:v>
+        <x:v>1486000</x:v>
       </x:c>
       <x:c r="F82" s="0" t="s">
         <x:v>11</x:v>
@@ -3171,27 +3174,27 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H82" s="0">
-        <x:v>35290767390</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>0.9648</x:v>
+        <x:v>0.027</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:9">
       <x:c r="A83" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B83" s="0">
-        <x:v>80.6</x:v>
+        <x:v>339.5</x:v>
       </x:c>
       <x:c r="C83" s="0">
-        <x:v>7.3</x:v>
+        <x:v>13.5</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E83" s="0">
-        <x:v>15938617</x:v>
+        <x:v>768864700</x:v>
       </x:c>
       <x:c r="F83" s="0" t="s">
         <x:v>11</x:v>
@@ -3200,85 +3203,85 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H83" s="0">
-        <x:v>16733157490</x:v>
+        <x:v>35290767390</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>0.0422</x:v>
+        <x:v>0.9648</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:9">
       <x:c r="A84" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B84" s="0">
+        <x:v>86.25</x:v>
+      </x:c>
+      <x:c r="C84" s="0">
+        <x:v>5.65</x:v>
+      </x:c>
+      <x:c r="D84" s="0" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="B84" s="0">
-        <x:v>14.99</x:v>
-      </x:c>
-      <x:c r="C84" s="0">
-        <x:v>0.14</x:v>
-      </x:c>
-      <x:c r="D84" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
       <x:c r="E84" s="0">
-        <x:v>30438120</x:v>
+        <x:v>15938617</x:v>
       </x:c>
       <x:c r="F84" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G84" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H84" s="0">
-        <x:v>3159124121</x:v>
+        <x:v>16733157490</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0422</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:9">
       <x:c r="A85" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B85" s="0">
-        <x:v>288</x:v>
+        <x:v>14.84</x:v>
       </x:c>
       <x:c r="C85" s="0">
-        <x:v>23</x:v>
+        <x:v>-0.15</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
         <x:v>77</x:v>
       </x:c>
       <x:c r="E85" s="0">
-        <x:v>3900000</x:v>
+        <x:v>30438120</x:v>
       </x:c>
       <x:c r="F85" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G85" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H85" s="0">
-        <x:v>2159813703</x:v>
+        <x:v>3159124121</x:v>
       </x:c>
       <x:c r="I85" s="0">
-        <x:v>0.0797</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:9">
       <x:c r="A86" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B86" s="0">
-        <x:v>288</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="C86" s="0">
-        <x:v>23</x:v>
+        <x:v>-13</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E86" s="0">
-        <x:v>2104908</x:v>
+        <x:v>3900000</x:v>
       </x:c>
       <x:c r="F86" s="0" t="s">
         <x:v>11</x:v>
@@ -3290,24 +3293,24 @@
         <x:v>2159813703</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>0.043</x:v>
+        <x:v>0.0797</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:9">
       <x:c r="A87" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B87" s="0">
-        <x:v>28.78</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="C87" s="0">
-        <x:v>-0.38</x:v>
+        <x:v>-13</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E87" s="0">
-        <x:v>3900000</x:v>
+        <x:v>2104908</x:v>
       </x:c>
       <x:c r="F87" s="0" t="s">
         <x:v>11</x:v>
@@ -3316,143 +3319,143 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H87" s="0">
-        <x:v>7297855153</x:v>
+        <x:v>2159813703</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>0.0236</x:v>
+        <x:v>0.043</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:9">
       <x:c r="A88" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B88" s="0">
-        <x:v>6</x:v>
+        <x:v>29.36</x:v>
       </x:c>
       <x:c r="C88" s="0">
-        <x:v>0.16</x:v>
+        <x:v>0.58</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E88" s="0">
-        <x:v>496968445</x:v>
+        <x:v>3900000</x:v>
       </x:c>
       <x:c r="F88" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G88" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H88" s="0">
-        <x:v>855070469</x:v>
+        <x:v>7297855153</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>0.5812</x:v>
+        <x:v>0.0236</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:9">
       <x:c r="A89" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B89" s="0">
+        <x:v>6.12</x:v>
+      </x:c>
+      <x:c r="C89" s="0">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="D89" s="0" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="B89" s="0">
-        <x:v>12.53</x:v>
-      </x:c>
-      <x:c r="C89" s="0">
-        <x:v>-0.04</x:v>
-      </x:c>
-      <x:c r="D89" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
       <x:c r="E89" s="0">
-        <x:v>108750000</x:v>
+        <x:v>496968445</x:v>
       </x:c>
       <x:c r="F89" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G89" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H89" s="0">
-        <x:v>1982520183</x:v>
+        <x:v>855070469</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>0.0549</x:v>
+        <x:v>0.5812</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:9">
       <x:c r="A90" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B90" s="0">
-        <x:v>150.5</x:v>
+        <x:v>11.63</x:v>
       </x:c>
       <x:c r="C90" s="0">
-        <x:v>13.6</x:v>
+        <x:v>-0.9</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E90" s="0">
-        <x:v>1605197</x:v>
+        <x:v>108750000</x:v>
       </x:c>
       <x:c r="F90" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G90" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H90" s="0">
-        <x:v>3150489640</x:v>
+        <x:v>1982520183</x:v>
       </x:c>
       <x:c r="I90" s="0">
-        <x:v>0.0257</x:v>
+        <x:v>0.0549</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:9">
       <x:c r="A91" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B91" s="0">
-        <x:v>428.5</x:v>
+        <x:v>146.5</x:v>
       </x:c>
       <x:c r="C91" s="0">
-        <x:v>0.5</x:v>
+        <x:v>-4</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
         <x:v>81</x:v>
       </x:c>
       <x:c r="E91" s="0">
-        <x:v>54600000</x:v>
+        <x:v>1605197</x:v>
       </x:c>
       <x:c r="F91" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G91" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H91" s="0">
-        <x:v>180444938000</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>0.0133</x:v>
+        <x:v>0.0257</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:9">
       <x:c r="A92" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B92" s="0">
-        <x:v>428.5</x:v>
+        <x:v>431.75</x:v>
       </x:c>
       <x:c r="C92" s="0">
-        <x:v>0.5</x:v>
+        <x:v>3.25</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E92" s="0">
-        <x:v>111850000</x:v>
+        <x:v>54600000</x:v>
       </x:c>
       <x:c r="F92" s="0" t="s">
         <x:v>11</x:v>
@@ -3464,24 +3467,24 @@
         <x:v>180444938000</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>0.0273</x:v>
+        <x:v>0.0133</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:9">
       <x:c r="A93" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B93" s="0">
-        <x:v>57.25</x:v>
+        <x:v>431.75</x:v>
       </x:c>
       <x:c r="C93" s="0">
-        <x:v>0.2</x:v>
+        <x:v>3.25</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E93" s="0">
-        <x:v>803090</x:v>
+        <x:v>111850000</x:v>
       </x:c>
       <x:c r="F93" s="0" t="s">
         <x:v>11</x:v>
@@ -3490,317 +3493,317 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H93" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>180444938000</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>0.0084</x:v>
+        <x:v>0.0273</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:9">
       <x:c r="A94" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B94" s="0">
-        <x:v>27.9</x:v>
+        <x:v>58.7</x:v>
       </x:c>
       <x:c r="C94" s="0">
-        <x:v>0.44</x:v>
+        <x:v>1.45</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
         <x:v>82</x:v>
       </x:c>
       <x:c r="E94" s="0">
-        <x:v>2356546000</x:v>
+        <x:v>803090</x:v>
       </x:c>
       <x:c r="F94" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G94" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H94" s="0">
-        <x:v>7708004248</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>0.3057</x:v>
+        <x:v>0.0084</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:9">
       <x:c r="A95" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B95" s="0">
-        <x:v>1200</x:v>
+        <x:v>25.98</x:v>
       </x:c>
       <x:c r="C95" s="0">
-        <x:v>10</x:v>
+        <x:v>-1.92</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
         <x:v>83</x:v>
       </x:c>
       <x:c r="E95" s="0">
-        <x:v>875400</x:v>
+        <x:v>2356546000</x:v>
       </x:c>
       <x:c r="F95" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G95" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H95" s="0">
-        <x:v>1883544167</x:v>
+        <x:v>7708004248</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>0.0205</x:v>
+        <x:v>0.3057</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:9">
       <x:c r="A96" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B96" s="0">
+        <x:v>1131</x:v>
+      </x:c>
+      <x:c r="C96" s="0">
+        <x:v>-69</x:v>
+      </x:c>
+      <x:c r="D96" s="0" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="B96" s="0">
-        <x:v>27.5</x:v>
-      </x:c>
-      <x:c r="C96" s="0">
-        <x:v>-0.26</x:v>
-      </x:c>
-      <x:c r="D96" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
       <x:c r="E96" s="0">
-        <x:v>330000000</x:v>
+        <x:v>875400</x:v>
       </x:c>
       <x:c r="F96" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G96" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H96" s="0">
-        <x:v>5287314404</x:v>
+        <x:v>1883544167</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>0.0624</x:v>
+        <x:v>0.0205</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:9">
       <x:c r="A97" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B97" s="0">
-        <x:v>86.5</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C97" s="0">
-        <x:v>2.3</x:v>
+        <x:v>-0.5</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
         <x:v>86</x:v>
       </x:c>
       <x:c r="E97" s="0">
-        <x:v>11700000</x:v>
+        <x:v>330000000</x:v>
       </x:c>
       <x:c r="F97" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G97" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H97" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>5287314404</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>0.1705</x:v>
+        <x:v>0.0624</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:9">
       <x:c r="A98" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B98" s="0">
-        <x:v>9.68</x:v>
+        <x:v>86.55</x:v>
       </x:c>
       <x:c r="C98" s="0">
-        <x:v>0.88</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E98" s="0">
-        <x:v>4000000000</x:v>
+        <x:v>11700000</x:v>
       </x:c>
       <x:c r="F98" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G98" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H98" s="0">
-        <x:v>10581001663</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>0.378</x:v>
+        <x:v>0.1705</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:9">
       <x:c r="A99" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B99" s="0">
-        <x:v>19.48</x:v>
+        <x:v>10.64</x:v>
       </x:c>
       <x:c r="C99" s="0">
-        <x:v>1.77</x:v>
+        <x:v>0.96</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
         <x:v>87</x:v>
       </x:c>
       <x:c r="E99" s="0">
-        <x:v>1086598</x:v>
+        <x:v>4000000000</x:v>
       </x:c>
       <x:c r="F99" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G99" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H99" s="0">
-        <x:v>2020891371</x:v>
+        <x:v>10581001663</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>0.0274</x:v>
+        <x:v>0.378</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:9">
       <x:c r="A100" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B100" s="0">
-        <x:v>16.8</x:v>
+        <x:v>19.37</x:v>
       </x:c>
       <x:c r="C100" s="0">
-        <x:v>0.36</x:v>
+        <x:v>-0.11</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
         <x:v>88</x:v>
       </x:c>
       <x:c r="E100" s="0">
-        <x:v>216000000</x:v>
+        <x:v>1086598</x:v>
       </x:c>
       <x:c r="F100" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G100" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H100" s="0">
-        <x:v>3025063909</x:v>
+        <x:v>2020891371</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>0.0714</x:v>
+        <x:v>0.0274</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:9">
       <x:c r="A101" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B101" s="0">
-        <x:v>57.25</x:v>
+        <x:v>16.98</x:v>
       </x:c>
       <x:c r="C101" s="0">
-        <x:v>0.2</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E101" s="0">
-        <x:v>7292916</x:v>
+        <x:v>216000000</x:v>
       </x:c>
       <x:c r="F101" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G101" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H101" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>3025063909</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>0.0758</x:v>
+        <x:v>0.0714</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:9">
       <x:c r="A102" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B102" s="0">
+        <x:v>58.7</x:v>
+      </x:c>
+      <x:c r="C102" s="0">
+        <x:v>1.45</x:v>
+      </x:c>
+      <x:c r="D102" s="0" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="B102" s="0">
-        <x:v>31.12</x:v>
-      </x:c>
-      <x:c r="C102" s="0">
-        <x:v>1.06</x:v>
-      </x:c>
-      <x:c r="D102" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
       <x:c r="E102" s="0">
-        <x:v>250000</x:v>
+        <x:v>7292916</x:v>
       </x:c>
       <x:c r="F102" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G102" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H102" s="0">
-        <x:v>448686813</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>0.0006</x:v>
+        <x:v>0.0758</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:9">
       <x:c r="A103" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B103" s="0">
-        <x:v>80.6</x:v>
+        <x:v>30.72</x:v>
       </x:c>
       <x:c r="C103" s="0">
-        <x:v>7.3</x:v>
+        <x:v>-0.4</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E103" s="0">
-        <x:v>36900000</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="F103" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G103" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H103" s="0">
-        <x:v>10597063406</x:v>
+        <x:v>448686813</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>0.1527</x:v>
+        <x:v>0.0006</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:9">
       <x:c r="A104" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B104" s="0">
+        <x:v>86.25</x:v>
+      </x:c>
+      <x:c r="C104" s="0">
+        <x:v>5.65</x:v>
+      </x:c>
+      <x:c r="D104" s="0" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="B104" s="0">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="C104" s="0">
-        <x:v>0.85</x:v>
-      </x:c>
-      <x:c r="D104" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
       <x:c r="E104" s="0">
-        <x:v>3800000</x:v>
+        <x:v>36900000</x:v>
       </x:c>
       <x:c r="F104" s="0" t="s">
         <x:v>11</x:v>
@@ -3809,56 +3812,56 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H104" s="0">
-        <x:v>832031190</x:v>
+        <x:v>10597063406</x:v>
       </x:c>
       <x:c r="I104" s="0">
-        <x:v>0.2002</x:v>
+        <x:v>0.1527</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:9">
       <x:c r="A105" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B105" s="0">
-        <x:v>6</x:v>
+        <x:v>71.75</x:v>
       </x:c>
       <x:c r="C105" s="0">
-        <x:v>0.16</x:v>
+        <x:v>-0.25</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
         <x:v>93</x:v>
       </x:c>
       <x:c r="E105" s="0">
-        <x:v>2100000</x:v>
+        <x:v>3800000</x:v>
       </x:c>
       <x:c r="F105" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G105" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H105" s="0">
-        <x:v>855070469</x:v>
+        <x:v>832031190</x:v>
       </x:c>
       <x:c r="I105" s="0">
-        <x:v>0.1076</x:v>
+        <x:v>0.2002</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:9">
       <x:c r="A106" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B106" s="0">
-        <x:v>57.25</x:v>
+        <x:v>6.12</x:v>
       </x:c>
       <x:c r="C106" s="0">
-        <x:v>0.2</x:v>
+        <x:v>0.12</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E106" s="0">
-        <x:v>22928077</x:v>
+        <x:v>2100000</x:v>
       </x:c>
       <x:c r="F106" s="0" t="s">
         <x:v>11</x:v>
@@ -3867,59 +3870,59 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H106" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>855070469</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>0.2378</x:v>
+        <x:v>0.1076</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:9">
       <x:c r="A107" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B107" s="0">
+        <x:v>58.7</x:v>
+      </x:c>
+      <x:c r="C107" s="0">
+        <x:v>1.45</x:v>
+      </x:c>
+      <x:c r="D107" s="0" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="B107" s="0">
-        <x:v>31.08</x:v>
-      </x:c>
-      <x:c r="C107" s="0">
-        <x:v>0.66</x:v>
-      </x:c>
-      <x:c r="D107" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
       <x:c r="E107" s="0">
-        <x:v>547462013</x:v>
+        <x:v>22928077</x:v>
       </x:c>
       <x:c r="F107" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G107" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H107" s="0">
-        <x:v>0</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>0</x:v>
+        <x:v>0.2378</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:9">
       <x:c r="A108" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B108" s="0">
+        <x:v>31.18</x:v>
+      </x:c>
+      <x:c r="C108" s="0">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="D108" s="0" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="B108" s="0">
-        <x:v>31.08</x:v>
-      </x:c>
-      <x:c r="C108" s="0">
-        <x:v>0.66</x:v>
-      </x:c>
-      <x:c r="D108" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
       <x:c r="E108" s="0">
-        <x:v>10567948</x:v>
+        <x:v>547462013</x:v>
       </x:c>
       <x:c r="F108" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G108" s="0">
         <x:v>0</x:v>
@@ -3933,77 +3936,77 @@
     </x:row>
     <x:row r="109" spans="1:9">
       <x:c r="A109" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B109" s="0">
-        <x:v>86.5</x:v>
+        <x:v>31.18</x:v>
       </x:c>
       <x:c r="C109" s="0">
-        <x:v>2.3</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E109" s="0">
-        <x:v>8300000</x:v>
+        <x:v>10567948</x:v>
       </x:c>
       <x:c r="F109" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G109" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H109" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>0.1228</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:9">
       <x:c r="A110" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B110" s="0">
-        <x:v>61.4</x:v>
+        <x:v>86.55</x:v>
       </x:c>
       <x:c r="C110" s="0">
-        <x:v>3</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E110" s="0">
-        <x:v>3000000</x:v>
+        <x:v>8300000</x:v>
       </x:c>
       <x:c r="F110" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G110" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H110" s="0">
-        <x:v>20597209000</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>0.0064</x:v>
+        <x:v>0.1228</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:9">
       <x:c r="A111" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B111" s="0">
+        <x:v>61.35</x:v>
+      </x:c>
+      <x:c r="C111" s="0">
+        <x:v>-0.05</x:v>
+      </x:c>
+      <x:c r="D111" s="0" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="B111" s="0">
-        <x:v>40.4</x:v>
-      </x:c>
-      <x:c r="C111" s="0">
-        <x:v>3.18</x:v>
-      </x:c>
-      <x:c r="D111" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
       <x:c r="E111" s="0">
-        <x:v>26640000</x:v>
+        <x:v>3000000</x:v>
       </x:c>
       <x:c r="F111" s="0" t="s">
         <x:v>11</x:v>
@@ -4012,10 +4015,10 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H111" s="0">
-        <x:v>3277373640</x:v>
+        <x:v>20597209000</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>0.356</x:v>
+        <x:v>0.0064</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:9">
@@ -4023,193 +4026,193 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B112" s="0">
-        <x:v>6.3</x:v>
+        <x:v>40.5</x:v>
       </x:c>
       <x:c r="C112" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E112" s="0">
-        <x:v>13107198</x:v>
+        <x:v>26640000</x:v>
       </x:c>
       <x:c r="F112" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G112" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H112" s="0">
-        <x:v>1627872951</x:v>
+        <x:v>3277373640</x:v>
       </x:c>
       <x:c r="I112" s="0">
-        <x:v>0.0081</x:v>
+        <x:v>0.356</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:9">
       <x:c r="A113" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B113" s="0">
-        <x:v>86.5</x:v>
+        <x:v>6.62</x:v>
       </x:c>
       <x:c r="C113" s="0">
-        <x:v>2.3</x:v>
+        <x:v>0.32</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
         <x:v>99</x:v>
       </x:c>
       <x:c r="E113" s="0">
-        <x:v>237500000</x:v>
+        <x:v>13107198</x:v>
       </x:c>
       <x:c r="F113" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G113" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H113" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>1627872951</x:v>
       </x:c>
       <x:c r="I113" s="0">
-        <x:v>0.0679</x:v>
+        <x:v>0.0081</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:9">
       <x:c r="A114" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B114" s="0">
-        <x:v>63.15</x:v>
+        <x:v>86.55</x:v>
       </x:c>
       <x:c r="C114" s="0">
-        <x:v>2.65</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E114" s="0">
-        <x:v>147892538</x:v>
+        <x:v>237500000</x:v>
       </x:c>
       <x:c r="F114" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G114" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H114" s="0">
-        <x:v>7257990064</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>0.0204</x:v>
+        <x:v>0.0679</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:9">
       <x:c r="A115" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B115" s="0">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C115" s="0">
+        <x:v>2.85</x:v>
+      </x:c>
+      <x:c r="D115" s="0" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="B115" s="0">
-        <x:v>59.1</x:v>
-      </x:c>
-      <x:c r="C115" s="0">
-        <x:v>-0.4</x:v>
-      </x:c>
-      <x:c r="D115" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
       <x:c r="E115" s="0">
-        <x:v>988848</x:v>
+        <x:v>147892538</x:v>
       </x:c>
       <x:c r="F115" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G115" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H115" s="0">
-        <x:v>12999679000</x:v>
+        <x:v>7257990064</x:v>
       </x:c>
       <x:c r="I115" s="0">
-        <x:v>0.0033</x:v>
+        <x:v>0.0204</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:9">
       <x:c r="A116" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B116" s="0">
-        <x:v>80.6</x:v>
+        <x:v>57.65</x:v>
       </x:c>
       <x:c r="C116" s="0">
-        <x:v>7.3</x:v>
+        <x:v>-1.45</x:v>
       </x:c>
       <x:c r="D116" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E116" s="0">
-        <x:v>47300000</x:v>
+        <x:v>988848</x:v>
       </x:c>
       <x:c r="F116" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G116" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H116" s="0">
-        <x:v>10597063406</x:v>
+        <x:v>12999679000</x:v>
       </x:c>
       <x:c r="I116" s="0">
-        <x:v>0.2309</x:v>
+        <x:v>0.0033</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:9">
       <x:c r="A117" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B117" s="0">
-        <x:v>4.16</x:v>
+        <x:v>86.25</x:v>
       </x:c>
       <x:c r="C117" s="0">
-        <x:v>0</x:v>
+        <x:v>5.65</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E117" s="0">
-        <x:v>758600</x:v>
+        <x:v>47300000</x:v>
       </x:c>
       <x:c r="F117" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G117" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H117" s="0">
-        <x:v>1960468575</x:v>
+        <x:v>10597063406</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0.2309</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:9">
       <x:c r="A118" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B118" s="0">
-        <x:v>4.16</x:v>
+        <x:v>4.28</x:v>
       </x:c>
       <x:c r="C118" s="0">
-        <x:v>0</x:v>
+        <x:v>0.12</x:v>
       </x:c>
       <x:c r="D118" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E118" s="0">
         <x:v>758600</x:v>
       </x:c>
       <x:c r="F118" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G118" s="0">
         <x:v>2025.09</x:v>
@@ -4218,53 +4221,53 @@
         <x:v>1960468575</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>0.0004</x:v>
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:9">
       <x:c r="A119" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B119" s="0">
-        <x:v>1200</x:v>
+        <x:v>4.28</x:v>
       </x:c>
       <x:c r="C119" s="0">
-        <x:v>10</x:v>
+        <x:v>0.12</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E119" s="0">
-        <x:v>576665</x:v>
+        <x:v>758600</x:v>
       </x:c>
       <x:c r="F119" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="G119" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H119" s="0">
-        <x:v>1586603352</x:v>
+        <x:v>1960468575</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>0.0159</x:v>
+        <x:v>0.0004</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:9">
       <x:c r="A120" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B120" s="0">
-        <x:v>86.8</x:v>
+        <x:v>1131</x:v>
       </x:c>
       <x:c r="C120" s="0">
-        <x:v>0.75</x:v>
+        <x:v>-69</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E120" s="0">
-        <x:v>8000000</x:v>
+        <x:v>576665</x:v>
       </x:c>
       <x:c r="F120" s="0" t="s">
         <x:v>11</x:v>
@@ -4273,27 +4276,27 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H120" s="0">
-        <x:v>20999579110</x:v>
+        <x:v>1586603352</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>0.0166</x:v>
+        <x:v>0.0159</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:9">
       <x:c r="A121" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B121" s="0">
-        <x:v>98.2</x:v>
+        <x:v>93.25</x:v>
       </x:c>
       <x:c r="C121" s="0">
-        <x:v>-1.8</x:v>
+        <x:v>6.45</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E121" s="0">
-        <x:v>850000</x:v>
+        <x:v>8000000</x:v>
       </x:c>
       <x:c r="F121" s="0" t="s">
         <x:v>11</x:v>
@@ -4302,175 +4305,175 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H121" s="0">
-        <x:v>1781510191</x:v>
+        <x:v>20999579110</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>0.0208</x:v>
+        <x:v>0.0166</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:9">
       <x:c r="A122" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B122" s="0">
-        <x:v>19.48</x:v>
+        <x:v>99.5</x:v>
       </x:c>
       <x:c r="C122" s="0">
-        <x:v>1.77</x:v>
+        <x:v>1.3</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
         <x:v>106</x:v>
       </x:c>
       <x:c r="E122" s="0">
-        <x:v>10149200</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="F122" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G122" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H122" s="0">
-        <x:v>2020891371</x:v>
+        <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>0.2601</x:v>
+        <x:v>0.0208</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:9">
       <x:c r="A123" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B123" s="0">
-        <x:v>150.5</x:v>
+        <x:v>19.37</x:v>
       </x:c>
       <x:c r="C123" s="0">
-        <x:v>13.6</x:v>
+        <x:v>-0.11</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E123" s="0">
-        <x:v>10500000</x:v>
+        <x:v>10149200</x:v>
       </x:c>
       <x:c r="F123" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G123" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H123" s="0">
-        <x:v>1742315226</x:v>
+        <x:v>2020891371</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>0.3121</x:v>
+        <x:v>0.2601</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:9">
       <x:c r="A124" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B124" s="0">
-        <x:v>98.2</x:v>
+        <x:v>146.5</x:v>
       </x:c>
       <x:c r="C124" s="0">
-        <x:v>-1.8</x:v>
+        <x:v>-4</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
         <x:v>107</x:v>
       </x:c>
       <x:c r="E124" s="0">
-        <x:v>366956541</x:v>
+        <x:v>10500000</x:v>
       </x:c>
       <x:c r="F124" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G124" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H124" s="0">
-        <x:v>1781510191</x:v>
+        <x:v>1742315226</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>0.206</x:v>
+        <x:v>0.3121</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:9">
       <x:c r="A125" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B125" s="0">
-        <x:v>63.15</x:v>
+        <x:v>99.5</x:v>
       </x:c>
       <x:c r="C125" s="0">
-        <x:v>2.65</x:v>
+        <x:v>1.3</x:v>
       </x:c>
       <x:c r="D125" s="0" t="s">
         <x:v>108</x:v>
       </x:c>
       <x:c r="E125" s="0">
-        <x:v>61158155</x:v>
+        <x:v>366956541</x:v>
       </x:c>
       <x:c r="F125" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G125" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H125" s="0">
-        <x:v>7257990064</x:v>
+        <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I125" s="0">
-        <x:v>0.0084</x:v>
+        <x:v>0.206</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:9">
       <x:c r="A126" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B126" s="0">
-        <x:v>111.7</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C126" s="0">
-        <x:v>-0.1</x:v>
+        <x:v>2.85</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E126" s="0">
-        <x:v>1000000</x:v>
+        <x:v>61158155</x:v>
       </x:c>
       <x:c r="F126" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G126" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H126" s="0">
-        <x:v>1688731509</x:v>
+        <x:v>7257990064</x:v>
       </x:c>
       <x:c r="I126" s="0">
-        <x:v>0.0307</x:v>
+        <x:v>0.0084</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:9">
       <x:c r="A127" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B127" s="0">
-        <x:v>111.7</x:v>
+        <x:v>117.3</x:v>
       </x:c>
       <x:c r="C127" s="0">
-        <x:v>-0.1</x:v>
+        <x:v>5.6</x:v>
       </x:c>
       <x:c r="D127" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E127" s="0">
-        <x:v>1050000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="F127" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G127" s="0">
         <x:v>2025.09</x:v>
@@ -4479,82 +4482,82 @@
         <x:v>1688731509</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>0.0271</x:v>
+        <x:v>0.0307</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:9">
       <x:c r="A128" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B128" s="0">
+        <x:v>117.3</x:v>
+      </x:c>
+      <x:c r="C128" s="0">
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="D128" s="0" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="B128" s="0">
-        <x:v>44.8</x:v>
-      </x:c>
-      <x:c r="C128" s="0">
-        <x:v>2.52</x:v>
-      </x:c>
-      <x:c r="D128" s="0" t="s">
-        <x:v>110</x:v>
-      </x:c>
       <x:c r="E128" s="0">
-        <x:v>109053804</x:v>
+        <x:v>1050000</x:v>
       </x:c>
       <x:c r="F128" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G128" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H128" s="0">
-        <x:v>1942491524</x:v>
+        <x:v>1688731509</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>0.0561</x:v>
+        <x:v>0.0271</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:9">
       <x:c r="A129" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="B129" s="0">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C129" s="0">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="D129" s="0" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="B129" s="0">
-        <x:v>10.39</x:v>
-      </x:c>
-      <x:c r="C129" s="0">
-        <x:v>0.17</x:v>
-      </x:c>
-      <x:c r="D129" s="0" t="s">
-        <x:v>110</x:v>
-      </x:c>
       <x:c r="E129" s="0">
-        <x:v>62315119</x:v>
+        <x:v>109053804</x:v>
       </x:c>
       <x:c r="F129" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G129" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H129" s="0">
-        <x:v>12026414029</x:v>
+        <x:v>1942491524</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>0.2257</x:v>
+        <x:v>0.0561</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:9">
       <x:c r="A130" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B130" s="0">
-        <x:v>288</x:v>
+        <x:v>10.39</x:v>
       </x:c>
       <x:c r="C130" s="0">
-        <x:v>23</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D130" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E130" s="0">
-        <x:v>896400</x:v>
+        <x:v>62315119</x:v>
       </x:c>
       <x:c r="F130" s="0" t="s">
         <x:v>11</x:v>
@@ -4563,27 +4566,27 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H130" s="0">
-        <x:v>1364716456</x:v>
+        <x:v>12026414029</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>0.0285</x:v>
+        <x:v>0.2257</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:9">
       <x:c r="A131" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B131" s="0">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="C131" s="0">
+        <x:v>-13</x:v>
+      </x:c>
+      <x:c r="D131" s="0" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="B131" s="0">
-        <x:v>600.5</x:v>
-      </x:c>
-      <x:c r="C131" s="0">
-        <x:v>54.5</x:v>
-      </x:c>
-      <x:c r="D131" s="0" t="s">
-        <x:v>114</x:v>
-      </x:c>
       <x:c r="E131" s="0">
-        <x:v>3370000</x:v>
+        <x:v>896400</x:v>
       </x:c>
       <x:c r="F131" s="0" t="s">
         <x:v>11</x:v>
@@ -4592,143 +4595,143 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H131" s="0">
-        <x:v>1865697176</x:v>
+        <x:v>1364716456</x:v>
       </x:c>
       <x:c r="I131" s="0">
-        <x:v>0.0785</x:v>
+        <x:v>0.0285</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:9">
       <x:c r="A132" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B132" s="0">
-        <x:v>61.4</x:v>
+        <x:v>660.5</x:v>
       </x:c>
       <x:c r="C132" s="0">
-        <x:v>3</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
         <x:v>115</x:v>
       </x:c>
       <x:c r="E132" s="0">
-        <x:v>750561215</x:v>
+        <x:v>3370000</x:v>
       </x:c>
       <x:c r="F132" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G132" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H132" s="0">
-        <x:v>16507905000</x:v>
+        <x:v>1865697176</x:v>
       </x:c>
       <x:c r="I132" s="0">
-        <x:v>0.0455</x:v>
+        <x:v>0.0785</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:9">
       <x:c r="A133" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B133" s="0">
-        <x:v>86.8</x:v>
+        <x:v>61.35</x:v>
       </x:c>
       <x:c r="C133" s="0">
-        <x:v>0.75</x:v>
+        <x:v>-0.05</x:v>
       </x:c>
       <x:c r="D133" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E133" s="0">
-        <x:v>20000000</x:v>
+        <x:v>750561215</x:v>
       </x:c>
       <x:c r="F133" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G133" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H133" s="0">
-        <x:v>20999579110</x:v>
+        <x:v>16507905000</x:v>
       </x:c>
       <x:c r="I133" s="0">
-        <x:v>0.0413</x:v>
+        <x:v>0.0455</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:9">
       <x:c r="A134" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="B134" s="0">
+        <x:v>93.25</x:v>
+      </x:c>
+      <x:c r="C134" s="0">
+        <x:v>6.45</x:v>
+      </x:c>
+      <x:c r="D134" s="0" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="B134" s="0">
-        <x:v>36.82</x:v>
-      </x:c>
-      <x:c r="C134" s="0">
-        <x:v>1.32</x:v>
-      </x:c>
-      <x:c r="D134" s="0" t="s">
-        <x:v>117</x:v>
-      </x:c>
       <x:c r="E134" s="0">
-        <x:v>750000000</x:v>
+        <x:v>20000000</x:v>
       </x:c>
       <x:c r="F134" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G134" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H134" s="0">
-        <x:v>0</x:v>
+        <x:v>20999579110</x:v>
       </x:c>
       <x:c r="I134" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0413</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:9">
       <x:c r="A135" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B135" s="0">
-        <x:v>80.6</x:v>
+        <x:v>36.66</x:v>
       </x:c>
       <x:c r="C135" s="0">
-        <x:v>7.3</x:v>
+        <x:v>-0.16</x:v>
       </x:c>
       <x:c r="D135" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E135" s="0">
-        <x:v>111232418</x:v>
+        <x:v>750000000</x:v>
       </x:c>
       <x:c r="F135" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G135" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H135" s="0">
-        <x:v>10597063406</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I135" s="0">
-        <x:v>0.4554</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:9">
       <x:c r="A136" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B136" s="0">
-        <x:v>37.6</x:v>
+        <x:v>86.25</x:v>
       </x:c>
       <x:c r="C136" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>5.65</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
         <x:v>118</x:v>
       </x:c>
       <x:c r="E136" s="0">
-        <x:v>51384996</x:v>
+        <x:v>111232418</x:v>
       </x:c>
       <x:c r="F136" s="0" t="s">
         <x:v>11</x:v>
@@ -4737,27 +4740,27 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H136" s="0">
-        <x:v>11899043692</x:v>
+        <x:v>10597063406</x:v>
       </x:c>
       <x:c r="I136" s="0">
-        <x:v>0.1873</x:v>
+        <x:v>0.4554</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:9">
       <x:c r="A137" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B137" s="0">
-        <x:v>37.6</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C137" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>2.4</x:v>
       </x:c>
       <x:c r="D137" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E137" s="0">
-        <x:v>3602451</x:v>
+        <x:v>51384996</x:v>
       </x:c>
       <x:c r="F137" s="0" t="s">
         <x:v>11</x:v>
@@ -4769,24 +4772,24 @@
         <x:v>11899043692</x:v>
       </x:c>
       <x:c r="I137" s="0">
-        <x:v>0.0131</x:v>
+        <x:v>0.1873</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:9">
       <x:c r="A138" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B138" s="0">
-        <x:v>37.6</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C138" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>2.4</x:v>
       </x:c>
       <x:c r="D138" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E138" s="0">
-        <x:v>24226465</x:v>
+        <x:v>3602451</x:v>
       </x:c>
       <x:c r="F138" s="0" t="s">
         <x:v>11</x:v>
@@ -4798,401 +4801,401 @@
         <x:v>11899043692</x:v>
       </x:c>
       <x:c r="I138" s="0">
-        <x:v>0.0883</x:v>
+        <x:v>0.0131</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:9">
       <x:c r="A139" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B139" s="0">
-        <x:v>57.25</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C139" s="0">
-        <x:v>0.2</x:v>
+        <x:v>2.4</x:v>
       </x:c>
       <x:c r="D139" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E139" s="0">
-        <x:v>12900000</x:v>
+        <x:v>24226465</x:v>
       </x:c>
       <x:c r="F139" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G139" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H139" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>11899043692</x:v>
       </x:c>
       <x:c r="I139" s="0">
-        <x:v>0.0052</x:v>
+        <x:v>0.0883</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:9">
       <x:c r="A140" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B140" s="0">
-        <x:v>326</x:v>
+        <x:v>58.7</x:v>
       </x:c>
       <x:c r="C140" s="0">
-        <x:v>5.25</x:v>
+        <x:v>1.45</x:v>
       </x:c>
       <x:c r="D140" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E140" s="0">
-        <x:v>53250000</x:v>
+        <x:v>12900000</x:v>
       </x:c>
       <x:c r="F140" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G140" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H140" s="0">
-        <x:v>24073631758</x:v>
+        <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I140" s="0">
-        <x:v>0.115</x:v>
+        <x:v>0.0052</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:9">
       <x:c r="A141" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B141" s="0">
-        <x:v>31.08</x:v>
+        <x:v>339.5</x:v>
       </x:c>
       <x:c r="C141" s="0">
-        <x:v>0.66</x:v>
+        <x:v>13.5</x:v>
       </x:c>
       <x:c r="D141" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E141" s="0">
-        <x:v>6860140</x:v>
+        <x:v>53250000</x:v>
       </x:c>
       <x:c r="F141" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G141" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H141" s="0">
-        <x:v>0</x:v>
+        <x:v>24073631758</x:v>
       </x:c>
       <x:c r="I141" s="0">
-        <x:v>0</x:v>
+        <x:v>0.115</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:9">
       <x:c r="A142" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B142" s="0">
-        <x:v>86.5</x:v>
+        <x:v>31.18</x:v>
       </x:c>
       <x:c r="C142" s="0">
-        <x:v>2.3</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="D142" s="0" t="s">
         <x:v>119</x:v>
       </x:c>
       <x:c r="E142" s="0">
-        <x:v>230000000</x:v>
+        <x:v>6860140</x:v>
       </x:c>
       <x:c r="F142" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G142" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H142" s="0">
-        <x:v>2941310980</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I142" s="0">
-        <x:v>0.0782</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:9">
       <x:c r="A143" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B143" s="0">
-        <x:v>600.5</x:v>
+        <x:v>86.55</x:v>
       </x:c>
       <x:c r="C143" s="0">
-        <x:v>54.5</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D143" s="0" t="s">
         <x:v>120</x:v>
       </x:c>
       <x:c r="E143" s="0">
-        <x:v>4700000</x:v>
+        <x:v>230000000</x:v>
       </x:c>
       <x:c r="F143" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G143" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H143" s="0">
-        <x:v>1865697176</x:v>
+        <x:v>2941310980</x:v>
       </x:c>
       <x:c r="I143" s="0">
-        <x:v>0.1092</x:v>
+        <x:v>0.0782</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:9">
       <x:c r="A144" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B144" s="0">
-        <x:v>31.08</x:v>
+        <x:v>660.5</x:v>
       </x:c>
       <x:c r="C144" s="0">
-        <x:v>0.66</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D144" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E144" s="0">
-        <x:v>256000000</x:v>
+        <x:v>4700000</x:v>
       </x:c>
       <x:c r="F144" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G144" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H144" s="0">
-        <x:v>0</x:v>
+        <x:v>1865697176</x:v>
       </x:c>
       <x:c r="I144" s="0">
-        <x:v>0</x:v>
+        <x:v>0.1092</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:9">
       <x:c r="A145" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B145" s="0">
-        <x:v>37.6</x:v>
+        <x:v>31.18</x:v>
       </x:c>
       <x:c r="C145" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="D145" s="0" t="s">
         <x:v>121</x:v>
       </x:c>
       <x:c r="E145" s="0">
-        <x:v>10724896</x:v>
+        <x:v>256000000</x:v>
       </x:c>
       <x:c r="F145" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G145" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H145" s="0">
-        <x:v>11899043692</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I145" s="0">
-        <x:v>0.039</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:9">
       <x:c r="A146" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B146" s="0">
-        <x:v>24.9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C146" s="0">
-        <x:v>0.06</x:v>
+        <x:v>2.4</x:v>
       </x:c>
       <x:c r="D146" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E146" s="0">
-        <x:v>31000000</x:v>
+        <x:v>10724896</x:v>
       </x:c>
       <x:c r="F146" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G146" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H146" s="0">
-        <x:v>813967617</x:v>
+        <x:v>11899043692</x:v>
       </x:c>
       <x:c r="I146" s="0">
-        <x:v>0.0381</x:v>
+        <x:v>0.039</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:9">
       <x:c r="A147" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B147" s="0">
-        <x:v>46.44</x:v>
+        <x:v>25.08</x:v>
       </x:c>
       <x:c r="C147" s="0">
-        <x:v>2.7</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="D147" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E147" s="0">
-        <x:v>13500000</x:v>
+        <x:v>31000000</x:v>
       </x:c>
       <x:c r="F147" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G147" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H147" s="0">
-        <x:v>6483809984</x:v>
+        <x:v>813967617</x:v>
       </x:c>
       <x:c r="I147" s="0">
-        <x:v>0.09</x:v>
+        <x:v>0.0381</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:9">
       <x:c r="A148" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B148" s="0">
-        <x:v>44.8</x:v>
+        <x:v>51.05</x:v>
       </x:c>
       <x:c r="C148" s="0">
-        <x:v>2.52</x:v>
+        <x:v>4.61</x:v>
       </x:c>
       <x:c r="D148" s="0" t="s">
         <x:v>122</x:v>
       </x:c>
       <x:c r="E148" s="0">
-        <x:v>29886357</x:v>
+        <x:v>13500000</x:v>
       </x:c>
       <x:c r="F148" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G148" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H148" s="0">
-        <x:v>1942491524</x:v>
+        <x:v>6483809984</x:v>
       </x:c>
       <x:c r="I148" s="0">
-        <x:v>0.0154</x:v>
+        <x:v>0.09</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:9">
       <x:c r="A149" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B149" s="0">
-        <x:v>428.5</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C149" s="0">
-        <x:v>0.5</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="D149" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="E149" s="0">
-        <x:v>171000000</x:v>
+        <x:v>29886357</x:v>
       </x:c>
       <x:c r="F149" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G149" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H149" s="0">
-        <x:v>130147715000</x:v>
+        <x:v>1942491524</x:v>
       </x:c>
       <x:c r="I149" s="0">
-        <x:v>0.0568</x:v>
+        <x:v>0.0154</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:9">
       <x:c r="A150" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B150" s="0">
-        <x:v>150.5</x:v>
+        <x:v>431.75</x:v>
       </x:c>
       <x:c r="C150" s="0">
-        <x:v>13.6</x:v>
+        <x:v>3.25</x:v>
       </x:c>
       <x:c r="D150" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="E150" s="0">
-        <x:v>1890000</x:v>
+        <x:v>171000000</x:v>
       </x:c>
       <x:c r="F150" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G150" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H150" s="0">
-        <x:v>1742315226</x:v>
+        <x:v>130147715000</x:v>
       </x:c>
       <x:c r="I150" s="0">
-        <x:v>0.0549</x:v>
+        <x:v>0.0568</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:9">
       <x:c r="A151" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B151" s="0">
+        <x:v>146.5</x:v>
+      </x:c>
+      <x:c r="C151" s="0">
+        <x:v>-4</x:v>
+      </x:c>
+      <x:c r="D151" s="0" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="B151" s="0">
-        <x:v>14.1</x:v>
-      </x:c>
-      <x:c r="C151" s="0">
-        <x:v>-0.06</x:v>
-      </x:c>
-      <x:c r="D151" s="0" t="s">
-        <x:v>122</x:v>
-      </x:c>
       <x:c r="E151" s="0">
-        <x:v>892825</x:v>
+        <x:v>1890000</x:v>
       </x:c>
       <x:c r="F151" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G151" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H151" s="0">
-        <x:v>3015442704</x:v>
+        <x:v>1742315226</x:v>
       </x:c>
       <x:c r="I151" s="0">
-        <x:v>0.0128</x:v>
+        <x:v>0.0549</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:9">
       <x:c r="A152" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B152" s="0">
-        <x:v>57.25</x:v>
+        <x:v>13.94</x:v>
       </x:c>
       <x:c r="C152" s="0">
-        <x:v>0.2</x:v>
+        <x:v>-0.16</x:v>
       </x:c>
       <x:c r="D152" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="E152" s="0">
-        <x:v>361176</x:v>
+        <x:v>892825</x:v>
       </x:c>
       <x:c r="F152" s="0" t="s">
         <x:v>11</x:v>
@@ -5201,27 +5204,27 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H152" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>3015442704</x:v>
       </x:c>
       <x:c r="I152" s="0">
-        <x:v>0.0063</x:v>
+        <x:v>0.0128</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:9">
       <x:c r="A153" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B153" s="0">
-        <x:v>25.92</x:v>
+        <x:v>58.7</x:v>
       </x:c>
       <x:c r="C153" s="0">
-        <x:v>0.18</x:v>
+        <x:v>1.45</x:v>
       </x:c>
       <x:c r="D153" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="E153" s="0">
-        <x:v>1060000</x:v>
+        <x:v>361176</x:v>
       </x:c>
       <x:c r="F153" s="0" t="s">
         <x:v>11</x:v>
@@ -5230,85 +5233,85 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H153" s="0">
-        <x:v>1194839266</x:v>
+        <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I153" s="0">
-        <x:v>0.0384</x:v>
+        <x:v>0.0063</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:9">
       <x:c r="A154" s="0" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="B154" s="0">
+        <x:v>26.04</x:v>
+      </x:c>
+      <x:c r="C154" s="0">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="D154" s="0" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="B154" s="0">
-        <x:v>54.05</x:v>
-      </x:c>
-      <x:c r="C154" s="0">
-        <x:v>-0.95</x:v>
-      </x:c>
-      <x:c r="D154" s="0" t="s">
-        <x:v>125</x:v>
-      </x:c>
       <x:c r="E154" s="0">
-        <x:v>259417800</x:v>
+        <x:v>1060000</x:v>
       </x:c>
       <x:c r="F154" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G154" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H154" s="0">
-        <x:v>2741117556</x:v>
+        <x:v>1194839266</x:v>
       </x:c>
       <x:c r="I154" s="0">
-        <x:v>0.0946</x:v>
+        <x:v>0.0384</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:9">
       <x:c r="A155" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B155" s="0">
-        <x:v>72</x:v>
+        <x:v>53.1</x:v>
       </x:c>
       <x:c r="C155" s="0">
-        <x:v>0.85</x:v>
+        <x:v>-0.95</x:v>
       </x:c>
       <x:c r="D155" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="E155" s="0">
-        <x:v>523788</x:v>
+        <x:v>259417800</x:v>
       </x:c>
       <x:c r="F155" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G155" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H155" s="0">
-        <x:v>832031190</x:v>
+        <x:v>2741117556</x:v>
       </x:c>
       <x:c r="I155" s="0">
-        <x:v>0.0272</x:v>
+        <x:v>0.0946</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:9">
       <x:c r="A156" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B156" s="0">
-        <x:v>72</x:v>
+        <x:v>71.75</x:v>
       </x:c>
       <x:c r="C156" s="0">
-        <x:v>0.85</x:v>
+        <x:v>-0.25</x:v>
       </x:c>
       <x:c r="D156" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="E156" s="0">
-        <x:v>1415270</x:v>
+        <x:v>523788</x:v>
       </x:c>
       <x:c r="F156" s="0" t="s">
         <x:v>11</x:v>
@@ -5320,24 +5323,24 @@
         <x:v>832031190</x:v>
       </x:c>
       <x:c r="I156" s="0">
-        <x:v>0.0736</x:v>
+        <x:v>0.0272</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:9">
       <x:c r="A157" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B157" s="0">
-        <x:v>86.8</x:v>
+        <x:v>71.75</x:v>
       </x:c>
       <x:c r="C157" s="0">
-        <x:v>0.75</x:v>
+        <x:v>-0.25</x:v>
       </x:c>
       <x:c r="D157" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="E157" s="0">
-        <x:v>25000000</x:v>
+        <x:v>1415270</x:v>
       </x:c>
       <x:c r="F157" s="0" t="s">
         <x:v>11</x:v>
@@ -5346,27 +5349,27 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H157" s="0">
-        <x:v>20999579110</x:v>
+        <x:v>832031190</x:v>
       </x:c>
       <x:c r="I157" s="0">
-        <x:v>0.0515</x:v>
+        <x:v>0.0736</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:9">
       <x:c r="A158" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B158" s="0">
-        <x:v>6.3</x:v>
+        <x:v>93.25</x:v>
       </x:c>
       <x:c r="C158" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>6.45</x:v>
       </x:c>
       <x:c r="D158" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="E158" s="0">
-        <x:v>25000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="F158" s="0" t="s">
         <x:v>11</x:v>
@@ -5375,114 +5378,114 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H158" s="0">
-        <x:v>1627872951</x:v>
+        <x:v>20999579110</x:v>
       </x:c>
       <x:c r="I158" s="0">
-        <x:v>0.0007</x:v>
+        <x:v>0.0515</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:9">
       <x:c r="A159" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B159" s="0">
+        <x:v>6.62</x:v>
+      </x:c>
+      <x:c r="C159" s="0">
+        <x:v>0.32</x:v>
+      </x:c>
+      <x:c r="D159" s="0" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="B159" s="0">
-        <x:v>21.72</x:v>
-      </x:c>
-      <x:c r="C159" s="0">
-        <x:v>0.4</x:v>
-      </x:c>
-      <x:c r="D159" s="0" t="s">
-        <x:v>127</x:v>
-      </x:c>
       <x:c r="E159" s="0">
-        <x:v>1500000</x:v>
+        <x:v>25000</x:v>
       </x:c>
       <x:c r="F159" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G159" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H159" s="0">
-        <x:v>774677961</x:v>
+        <x:v>1627872951</x:v>
       </x:c>
       <x:c r="I159" s="0">
-        <x:v>0.0019</x:v>
+        <x:v>0.0007</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:9">
       <x:c r="A160" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B160" s="0">
-        <x:v>9.68</x:v>
+        <x:v>21.62</x:v>
       </x:c>
       <x:c r="C160" s="0">
-        <x:v>0.88</x:v>
+        <x:v>-0.1</x:v>
       </x:c>
       <x:c r="D160" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E160" s="0">
-        <x:v>13833310</x:v>
+        <x:v>1500000</x:v>
       </x:c>
       <x:c r="F160" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G160" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H160" s="0">
-        <x:v>9028523851</x:v>
+        <x:v>774677961</x:v>
       </x:c>
       <x:c r="I160" s="0">
-        <x:v>0.0776</x:v>
+        <x:v>0.0019</x:v>
       </x:c>
     </x:row>
     <x:row r="161" spans="1:9">
       <x:c r="A161" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B161" s="0">
-        <x:v>76.85</x:v>
+        <x:v>10.64</x:v>
       </x:c>
       <x:c r="C161" s="0">
-        <x:v>-3.4</x:v>
+        <x:v>0.96</x:v>
       </x:c>
       <x:c r="D161" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E161" s="0">
-        <x:v>3419000</x:v>
+        <x:v>13833310</x:v>
       </x:c>
       <x:c r="F161" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G161" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H161" s="0">
-        <x:v>3895315496</x:v>
+        <x:v>9028523851</x:v>
       </x:c>
       <x:c r="I161" s="0">
-        <x:v>0.0379</x:v>
+        <x:v>0.0776</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:9">
       <x:c r="A162" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B162" s="0">
-        <x:v>600.5</x:v>
+        <x:v>76.5</x:v>
       </x:c>
       <x:c r="C162" s="0">
-        <x:v>54.5</x:v>
+        <x:v>-0.35</x:v>
       </x:c>
       <x:c r="D162" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="E162" s="0">
-        <x:v>3700000</x:v>
+        <x:v>3419000</x:v>
       </x:c>
       <x:c r="F162" s="0" t="s">
         <x:v>11</x:v>
@@ -5491,27 +5494,27 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H162" s="0">
-        <x:v>1865697176</x:v>
+        <x:v>3895315496</x:v>
       </x:c>
       <x:c r="I162" s="0">
-        <x:v>0.0857</x:v>
+        <x:v>0.0379</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:9">
       <x:c r="A163" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B163" s="0">
-        <x:v>46.44</x:v>
+        <x:v>660.5</x:v>
       </x:c>
       <x:c r="C163" s="0">
-        <x:v>2.7</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D163" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="E163" s="0">
-        <x:v>16000000</x:v>
+        <x:v>3700000</x:v>
       </x:c>
       <x:c r="F163" s="0" t="s">
         <x:v>11</x:v>
@@ -5520,27 +5523,27 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H163" s="0">
-        <x:v>6483809984</x:v>
+        <x:v>1865697176</x:v>
       </x:c>
       <x:c r="I163" s="0">
-        <x:v>0.1067</x:v>
+        <x:v>0.0857</x:v>
       </x:c>
     </x:row>
     <x:row r="164" spans="1:9">
       <x:c r="A164" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B164" s="0">
-        <x:v>57.25</x:v>
+        <x:v>51.05</x:v>
       </x:c>
       <x:c r="C164" s="0">
-        <x:v>0.2</x:v>
+        <x:v>4.61</x:v>
       </x:c>
       <x:c r="D164" s="0" t="s">
         <x:v>130</x:v>
       </x:c>
       <x:c r="E164" s="0">
-        <x:v>906840</x:v>
+        <x:v>16000000</x:v>
       </x:c>
       <x:c r="F164" s="0" t="s">
         <x:v>11</x:v>
@@ -5549,114 +5552,114 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H164" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>6483809984</x:v>
       </x:c>
       <x:c r="I164" s="0">
-        <x:v>0.0159</x:v>
+        <x:v>0.1067</x:v>
       </x:c>
     </x:row>
     <x:row r="165" spans="1:9">
       <x:c r="A165" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B165" s="0">
-        <x:v>3.41</x:v>
+        <x:v>58.7</x:v>
       </x:c>
       <x:c r="C165" s="0">
-        <x:v>-0.05</x:v>
+        <x:v>1.45</x:v>
       </x:c>
       <x:c r="D165" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E165" s="0">
-        <x:v>895039950</x:v>
+        <x:v>906840</x:v>
       </x:c>
       <x:c r="F165" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G165" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H165" s="0">
-        <x:v>7382591324</x:v>
+        <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I165" s="0">
-        <x:v>0.1212</x:v>
+        <x:v>0.0159</x:v>
       </x:c>
     </x:row>
     <x:row r="166" spans="1:9">
       <x:c r="A166" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B166" s="0">
-        <x:v>54.05</x:v>
+        <x:v>3.51</x:v>
       </x:c>
       <x:c r="C166" s="0">
-        <x:v>-0.95</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="D166" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E166" s="0">
-        <x:v>575933040</x:v>
+        <x:v>895039950</x:v>
       </x:c>
       <x:c r="F166" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G166" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H166" s="0">
-        <x:v>2741117556</x:v>
+        <x:v>7382591324</x:v>
       </x:c>
       <x:c r="I166" s="0">
-        <x:v>0.2101</x:v>
+        <x:v>0.1212</x:v>
       </x:c>
     </x:row>
     <x:row r="167" spans="1:9">
       <x:c r="A167" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="B167" s="0">
+        <x:v>53.1</x:v>
+      </x:c>
+      <x:c r="C167" s="0">
+        <x:v>-0.95</x:v>
+      </x:c>
+      <x:c r="D167" s="0" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="B167" s="0">
-        <x:v>12.95</x:v>
-      </x:c>
-      <x:c r="C167" s="0">
-        <x:v>0.27</x:v>
-      </x:c>
-      <x:c r="D167" s="0" t="s">
-        <x:v>130</x:v>
-      </x:c>
       <x:c r="E167" s="0">
-        <x:v>559000</x:v>
+        <x:v>575933040</x:v>
       </x:c>
       <x:c r="F167" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G167" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H167" s="0">
-        <x:v>2865374550</x:v>
+        <x:v>2741117556</x:v>
       </x:c>
       <x:c r="I167" s="0">
-        <x:v>0.0084</x:v>
+        <x:v>0.2101</x:v>
       </x:c>
     </x:row>
     <x:row r="168" spans="1:9">
       <x:c r="A168" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B168" s="0">
-        <x:v>61.4</x:v>
+        <x:v>13.01</x:v>
       </x:c>
       <x:c r="C168" s="0">
-        <x:v>3</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="D168" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E168" s="0">
-        <x:v>8900056</x:v>
+        <x:v>559000</x:v>
       </x:c>
       <x:c r="F168" s="0" t="s">
         <x:v>11</x:v>
@@ -5665,27 +5668,27 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H168" s="0">
-        <x:v>16507905000</x:v>
+        <x:v>2865374550</x:v>
       </x:c>
       <x:c r="I168" s="0">
-        <x:v>0.0233</x:v>
+        <x:v>0.0084</x:v>
       </x:c>
     </x:row>
     <x:row r="169" spans="1:9">
       <x:c r="A169" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B169" s="0">
-        <x:v>326</x:v>
+        <x:v>61.35</x:v>
       </x:c>
       <x:c r="C169" s="0">
-        <x:v>5.25</x:v>
+        <x:v>-0.05</x:v>
       </x:c>
       <x:c r="D169" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E169" s="0">
-        <x:v>164306000</x:v>
+        <x:v>8900056</x:v>
       </x:c>
       <x:c r="F169" s="0" t="s">
         <x:v>11</x:v>
@@ -5694,27 +5697,27 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H169" s="0">
-        <x:v>24073631758</x:v>
+        <x:v>16507905000</x:v>
       </x:c>
       <x:c r="I169" s="0">
-        <x:v>0.2943</x:v>
+        <x:v>0.0233</x:v>
       </x:c>
     </x:row>
     <x:row r="170" spans="1:9">
       <x:c r="A170" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B170" s="0">
-        <x:v>54.75</x:v>
+        <x:v>339.5</x:v>
       </x:c>
       <x:c r="C170" s="0">
-        <x:v>-0.55</x:v>
+        <x:v>13.5</x:v>
       </x:c>
       <x:c r="D170" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E170" s="0">
-        <x:v>275000</x:v>
+        <x:v>164306000</x:v>
       </x:c>
       <x:c r="F170" s="0" t="s">
         <x:v>11</x:v>
@@ -5723,230 +5726,230 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H170" s="0">
-        <x:v>580678850</x:v>
+        <x:v>24073631758</x:v>
       </x:c>
       <x:c r="I170" s="0">
-        <x:v>0.0204</x:v>
+        <x:v>0.2943</x:v>
       </x:c>
     </x:row>
     <x:row r="171" spans="1:9">
       <x:c r="A171" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B171" s="0">
-        <x:v>54.05</x:v>
+        <x:v>54.3</x:v>
       </x:c>
       <x:c r="C171" s="0">
-        <x:v>-0.95</x:v>
+        <x:v>-0.45</x:v>
       </x:c>
       <x:c r="D171" s="0" t="s">
         <x:v>134</x:v>
       </x:c>
       <x:c r="E171" s="0">
-        <x:v>231651480</x:v>
+        <x:v>275000</x:v>
       </x:c>
       <x:c r="F171" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G171" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H171" s="0">
-        <x:v>2741117556</x:v>
+        <x:v>580678850</x:v>
       </x:c>
       <x:c r="I171" s="0">
-        <x:v>0.0845</x:v>
+        <x:v>0.0204</x:v>
       </x:c>
     </x:row>
     <x:row r="172" spans="1:9">
       <x:c r="A172" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B172" s="0">
-        <x:v>16.8</x:v>
+        <x:v>53.1</x:v>
       </x:c>
       <x:c r="C172" s="0">
-        <x:v>0.36</x:v>
+        <x:v>-0.95</x:v>
       </x:c>
       <x:c r="D172" s="0" t="s">
         <x:v>135</x:v>
       </x:c>
       <x:c r="E172" s="0">
-        <x:v>31860000</x:v>
+        <x:v>231651480</x:v>
       </x:c>
       <x:c r="F172" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G172" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H172" s="0">
-        <x:v>3025063909</x:v>
+        <x:v>2741117556</x:v>
       </x:c>
       <x:c r="I172" s="0">
-        <x:v>0.4539</x:v>
+        <x:v>0.0845</x:v>
       </x:c>
     </x:row>
     <x:row r="173" spans="1:9">
       <x:c r="A173" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B173" s="0">
-        <x:v>98.2</x:v>
+        <x:v>16.98</x:v>
       </x:c>
       <x:c r="C173" s="0">
-        <x:v>-1.8</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="D173" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="E173" s="0">
-        <x:v>41650000</x:v>
+        <x:v>31860000</x:v>
       </x:c>
       <x:c r="F173" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G173" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H173" s="0">
-        <x:v>1781510191</x:v>
+        <x:v>3025063909</x:v>
       </x:c>
       <x:c r="I173" s="0">
-        <x:v>0.0234</x:v>
+        <x:v>0.4539</x:v>
       </x:c>
     </x:row>
     <x:row r="174" spans="1:9">
       <x:c r="A174" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B174" s="0">
-        <x:v>19.48</x:v>
+        <x:v>99.5</x:v>
       </x:c>
       <x:c r="C174" s="0">
-        <x:v>1.77</x:v>
+        <x:v>1.3</x:v>
       </x:c>
       <x:c r="D174" s="0" t="s">
         <x:v>136</x:v>
       </x:c>
       <x:c r="E174" s="0">
-        <x:v>815000</x:v>
+        <x:v>41650000</x:v>
       </x:c>
       <x:c r="F174" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G174" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H174" s="0">
-        <x:v>2020891371</x:v>
+        <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I174" s="0">
-        <x:v>0.0202</x:v>
+        <x:v>0.0234</x:v>
       </x:c>
     </x:row>
     <x:row r="175" spans="1:9">
       <x:c r="A175" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B175" s="0">
-        <x:v>86.5</x:v>
+        <x:v>19.37</x:v>
       </x:c>
       <x:c r="C175" s="0">
-        <x:v>2.3</x:v>
+        <x:v>-0.11</x:v>
       </x:c>
       <x:c r="D175" s="0" t="s">
         <x:v>137</x:v>
       </x:c>
       <x:c r="E175" s="0">
-        <x:v>8300000</x:v>
+        <x:v>815000</x:v>
       </x:c>
       <x:c r="F175" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G175" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H175" s="0">
-        <x:v>2941310980</x:v>
+        <x:v>2020891371</x:v>
       </x:c>
       <x:c r="I175" s="0">
-        <x:v>0.1417</x:v>
+        <x:v>0.0202</x:v>
       </x:c>
     </x:row>
     <x:row r="176" spans="1:9">
       <x:c r="A176" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B176" s="0">
+        <x:v>86.55</x:v>
+      </x:c>
+      <x:c r="C176" s="0">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="D176" s="0" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="B176" s="0">
-        <x:v>4.4</x:v>
-      </x:c>
-      <x:c r="C176" s="0">
-        <x:v>0.1</x:v>
-      </x:c>
-      <x:c r="D176" s="0" t="s">
-        <x:v>139</x:v>
-      </x:c>
       <x:c r="E176" s="0">
-        <x:v>13000000</x:v>
+        <x:v>8300000</x:v>
       </x:c>
       <x:c r="F176" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G176" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H176" s="0">
-        <x:v>1416740879</x:v>
+        <x:v>2941310980</x:v>
       </x:c>
       <x:c r="I176" s="0">
-        <x:v>0.4613</x:v>
+        <x:v>0.1417</x:v>
       </x:c>
     </x:row>
     <x:row r="177" spans="1:9">
       <x:c r="A177" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B177" s="0">
-        <x:v>150.5</x:v>
+        <x:v>4.45</x:v>
       </x:c>
       <x:c r="C177" s="0">
-        <x:v>13.6</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D177" s="0" t="s">
         <x:v>140</x:v>
       </x:c>
       <x:c r="E177" s="0">
-        <x:v>1999793</x:v>
+        <x:v>13000000</x:v>
       </x:c>
       <x:c r="F177" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G177" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H177" s="0">
-        <x:v>1742315226</x:v>
+        <x:v>1416740879</x:v>
       </x:c>
       <x:c r="I177" s="0">
-        <x:v>0.0494</x:v>
+        <x:v>0.4613</x:v>
       </x:c>
     </x:row>
     <x:row r="178" spans="1:9">
       <x:c r="A178" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B178" s="0">
-        <x:v>57.25</x:v>
+        <x:v>146.5</x:v>
       </x:c>
       <x:c r="C178" s="0">
-        <x:v>0.2</x:v>
+        <x:v>-4</x:v>
       </x:c>
       <x:c r="D178" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="E178" s="0">
-        <x:v>1859145</x:v>
+        <x:v>1999793</x:v>
       </x:c>
       <x:c r="F178" s="0" t="s">
         <x:v>11</x:v>
@@ -5955,117 +5958,117 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H178" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>1742315226</x:v>
       </x:c>
       <x:c r="I178" s="0">
-        <x:v>0.0324</x:v>
+        <x:v>0.0494</x:v>
       </x:c>
     </x:row>
     <x:row r="179" spans="1:9">
       <x:c r="A179" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B179" s="0">
-        <x:v>3.41</x:v>
+        <x:v>58.7</x:v>
       </x:c>
       <x:c r="C179" s="0">
-        <x:v>-0.05</x:v>
+        <x:v>1.45</x:v>
       </x:c>
       <x:c r="D179" s="0" t="s">
         <x:v>141</x:v>
       </x:c>
       <x:c r="E179" s="0">
-        <x:v>689661000</x:v>
+        <x:v>1859145</x:v>
       </x:c>
       <x:c r="F179" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G179" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H179" s="0">
-        <x:v>7382591324</x:v>
+        <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I179" s="0">
-        <x:v>0.0934</x:v>
+        <x:v>0.0324</x:v>
       </x:c>
     </x:row>
     <x:row r="180" spans="1:9">
       <x:c r="A180" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B180" s="0">
-        <x:v>57.25</x:v>
+        <x:v>3.51</x:v>
       </x:c>
       <x:c r="C180" s="0">
-        <x:v>0.2</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="D180" s="0" t="s">
         <x:v>142</x:v>
       </x:c>
       <x:c r="E180" s="0">
-        <x:v>1902000</x:v>
+        <x:v>689661000</x:v>
       </x:c>
       <x:c r="F180" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G180" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H180" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>7382591324</x:v>
       </x:c>
       <x:c r="I180" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0934</x:v>
       </x:c>
     </x:row>
     <x:row r="181" spans="1:9">
       <x:c r="A181" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B181" s="0">
-        <x:v>98.2</x:v>
+        <x:v>58.7</x:v>
       </x:c>
       <x:c r="C181" s="0">
-        <x:v>-1.8</x:v>
+        <x:v>1.45</x:v>
       </x:c>
       <x:c r="D181" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="E181" s="0">
-        <x:v>56520000</x:v>
+        <x:v>1902000</x:v>
       </x:c>
       <x:c r="F181" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G181" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H181" s="0">
-        <x:v>1781510191</x:v>
+        <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I181" s="0">
-        <x:v>0.0317</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="182" spans="1:9">
       <x:c r="A182" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B182" s="0">
-        <x:v>98.2</x:v>
+        <x:v>99.5</x:v>
       </x:c>
       <x:c r="C182" s="0">
-        <x:v>-1.8</x:v>
+        <x:v>1.3</x:v>
       </x:c>
       <x:c r="D182" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="E182" s="0">
-        <x:v>888325</x:v>
+        <x:v>56520000</x:v>
       </x:c>
       <x:c r="F182" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G182" s="0">
         <x:v>2025.09</x:v>
@@ -6074,24 +6077,24 @@
         <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I182" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0317</x:v>
       </x:c>
     </x:row>
     <x:row r="183" spans="1:9">
       <x:c r="A183" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B183" s="0">
-        <x:v>9.68</x:v>
+        <x:v>99.5</x:v>
       </x:c>
       <x:c r="C183" s="0">
-        <x:v>0.88</x:v>
+        <x:v>1.3</x:v>
       </x:c>
       <x:c r="D183" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="E183" s="0">
-        <x:v>5581810</x:v>
+        <x:v>888325</x:v>
       </x:c>
       <x:c r="F183" s="0" t="s">
         <x:v>11</x:v>
@@ -6100,7 +6103,7 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H183" s="0">
-        <x:v>9028523851</x:v>
+        <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I183" s="0">
         <x:v>0</x:v>
@@ -6108,60 +6111,60 @@
     </x:row>
     <x:row r="184" spans="1:9">
       <x:c r="A184" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B184" s="0">
-        <x:v>57.25</x:v>
+        <x:v>10.64</x:v>
       </x:c>
       <x:c r="C184" s="0">
-        <x:v>0.2</x:v>
+        <x:v>0.96</x:v>
       </x:c>
       <x:c r="D184" s="0" t="s">
         <x:v>143</x:v>
       </x:c>
       <x:c r="E184" s="0">
-        <x:v>504000000</x:v>
+        <x:v>5581810</x:v>
       </x:c>
       <x:c r="F184" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G184" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H184" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>9028523851</x:v>
       </x:c>
       <x:c r="I184" s="0">
-        <x:v>0.2043</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="185" spans="1:9">
       <x:c r="A185" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B185" s="0">
-        <x:v>326</x:v>
+        <x:v>58.7</x:v>
       </x:c>
       <x:c r="C185" s="0">
-        <x:v>5.25</x:v>
+        <x:v>1.45</x:v>
       </x:c>
       <x:c r="D185" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="E185" s="0">
-        <x:v>21500032</x:v>
+        <x:v>504000000</x:v>
       </x:c>
       <x:c r="F185" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G185" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H185" s="0">
-        <x:v>24073631758</x:v>
+        <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I185" s="0">
-        <x:v>0.0383</x:v>
+        <x:v>0.2043</x:v>
       </x:c>
     </x:row>
     <x:row r="186" spans="1:9">
@@ -6169,27 +6172,56 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B186" s="0">
-        <x:v>1200</x:v>
+        <x:v>339.5</x:v>
       </x:c>
       <x:c r="C186" s="0">
-        <x:v>10</x:v>
+        <x:v>13.5</x:v>
       </x:c>
       <x:c r="D186" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="E186" s="0">
+        <x:v>21500032</x:v>
+      </x:c>
+      <x:c r="F186" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G186" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H186" s="0">
+        <x:v>24073631758</x:v>
+      </x:c>
+      <x:c r="I186" s="0">
+        <x:v>0.0383</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187" spans="1:9">
+      <x:c r="A187" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B187" s="0">
+        <x:v>1131</x:v>
+      </x:c>
+      <x:c r="C187" s="0">
+        <x:v>-69</x:v>
+      </x:c>
+      <x:c r="D187" s="0" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="E187" s="0">
         <x:v>6455151</x:v>
       </x:c>
-      <x:c r="F186" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G186" s="0">
-        <x:v>2025.09</x:v>
-      </x:c>
-      <x:c r="H186" s="0">
+      <x:c r="F187" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G187" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H187" s="0">
         <x:v>1586603352</x:v>
       </x:c>
-      <x:c r="I186" s="0">
+      <x:c r="I187" s="0">
         <x:v>0.1745</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/yeni-is-anlasmalari/data/yeni-is-anlasmalari.xlsx
+++ b/app/borsa/yeni-is-anlasmalari/data/yeni-is-anlasmalari.xlsx
@@ -43,13 +43,28 @@
     <x:t>Yeni İş İlişkisi / Yıllık Satışlar</x:t>
   </x:si>
   <x:si>
+    <x:t>SDTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-05-12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>USD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YEOTK</x:t>
+  </x:si>
+  <x:si>
     <x:t>SMRTG</x:t>
   </x:si>
   <x:si>
     <x:t>2026-05-11</x:t>
   </x:si>
   <x:si>
-    <x:t>USD</x:t>
+    <x:t>AKHAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BESTE</x:t>
   </x:si>
   <x:si>
     <x:t>VBTYZ</x:t>
@@ -73,9 +88,6 @@
     <x:t>TCKRC</x:t>
   </x:si>
   <x:si>
-    <x:t>AKHAN</x:t>
-  </x:si>
-  <x:si>
     <x:t>ARDYZ</x:t>
   </x:si>
   <x:si>
@@ -145,9 +157,6 @@
     <x:t>HATSN</x:t>
   </x:si>
   <x:si>
-    <x:t>YEOTK</x:t>
-  </x:si>
-  <x:si>
     <x:t>2026-04-20</x:t>
   </x:si>
   <x:si>
@@ -169,9 +178,6 @@
     <x:t>2026-04-15</x:t>
   </x:si>
   <x:si>
-    <x:t>SDTTR</x:t>
-  </x:si>
-  <x:si>
     <x:t>OZYSR</x:t>
   </x:si>
   <x:si>
@@ -284,9 +290,6 @@
   </x:si>
   <x:si>
     <x:t>2026-03-04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BESTE</x:t>
   </x:si>
   <x:si>
     <x:t>2026-03-03</x:t>
@@ -799,7 +802,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I187"/>
+  <x:dimension ref="A1:I191"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -836,28 +839,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>10.64</x:v>
+        <x:v>269.5</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>0.96</x:v>
+        <x:v>-5.5</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>10201876</x:v>
+        <x:v>4950000</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2026.03</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>10581001663</x:v>
+        <x:v>2443327017</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>0.0436</x:v>
+        <x:v>0.0916</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -865,57 +868,57 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>24.68</x:v>
+        <x:v>94.85</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>0.3</x:v>
+        <x:v>8.6</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>1816317</x:v>
+        <x:v>1950000</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2026.03</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>2427624044</x:v>
+        <x:v>18658831210</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>0.0338</x:v>
+        <x:v>0.0047</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
       <x:c r="A4" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B4" s="0">
+        <x:v>11.41</x:v>
+      </x:c>
+      <x:c r="C4" s="0">
+        <x:v>0.77</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B4" s="0">
-        <x:v>99.5</x:v>
-      </x:c>
-      <x:c r="C4" s="0">
-        <x:v>1.3</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="E4" s="0">
-        <x:v>3384000</x:v>
+        <x:v>10201876</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2026.03</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>9721975029</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>0.0627</x:v>
+        <x:v>0.0474</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -923,28 +926,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>4.28</x:v>
+        <x:v>28.78</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>0.12</x:v>
+        <x:v>-0.58</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>1178000</x:v>
+        <x:v>459000</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2026.03</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>2875634546</x:v>
+        <x:v>7727514294</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>0.0185</x:v>
+        <x:v>0.0027</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -952,45 +955,45 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>8.45</x:v>
+        <x:v>30.7</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>0.76</x:v>
+        <x:v>-0.02</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>1180000</x:v>
+        <x:v>17776799</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2026.03</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>2322993973</x:v>
+        <x:v>433239437</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>0.0268</x:v>
+        <x:v>1.8545</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
       <x:c r="A7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B7" s="0">
+        <x:v>23.5</x:v>
+      </x:c>
+      <x:c r="C7" s="0">
+        <x:v>-1.18</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B7" s="0">
-        <x:v>117.3</x:v>
-      </x:c>
-      <x:c r="C7" s="0">
-        <x:v>5.6</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="E7" s="0">
-        <x:v>1220000</x:v>
+        <x:v>1816317</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
         <x:v>11</x:v>
@@ -999,10 +1002,10 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>2988208362</x:v>
+        <x:v>2427624044</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>0.0184</x:v>
+        <x:v>0.0338</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -1010,16 +1013,16 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>29.36</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>0.58</x:v>
+        <x:v>-5.5</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>26910</x:v>
+        <x:v>3384000</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
         <x:v>11</x:v>
@@ -1028,10 +1031,10 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>7297855153</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>0.0002</x:v>
+        <x:v>0.0627</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -1039,16 +1042,16 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>58.7</x:v>
+        <x:v>4.11</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>1.45</x:v>
+        <x:v>-0.17</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>2517084</x:v>
+        <x:v>1178000</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
         <x:v>11</x:v>
@@ -1057,114 +1060,114 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>2875634546</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>0.0269</x:v>
+        <x:v>0.0185</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
       <x:c r="A10" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>24.68</x:v>
+        <x:v>8.1</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>0.3</x:v>
+        <x:v>-0.35</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>9600000</x:v>
+        <x:v>1180000</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G10" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>2427624044</x:v>
+        <x:v>2322993973</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>0.1785</x:v>
+        <x:v>0.0268</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
       <x:c r="A11" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>311.25</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>14.5</x:v>
+        <x:v>7.7</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>9172451</x:v>
+        <x:v>1220000</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G11" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>709077088</x:v>
+        <x:v>2988208362</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>0.0129</x:v>
+        <x:v>0.0184</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
       <x:c r="A12" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>40</x:v>
+        <x:v>28.78</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>2.4</x:v>
+        <x:v>-0.58</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>32493961</x:v>
+        <x:v>26910</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>2026.03</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>17386730041</x:v>
+        <x:v>7297855153</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0002</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
       <x:c r="A13" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>86.55</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>0.05</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>940002</x:v>
+        <x:v>2517084</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
         <x:v>11</x:v>
@@ -1173,85 +1176,85 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>0.0121</x:v>
+        <x:v>0.0269</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
       <x:c r="A14" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>146.5</x:v>
+        <x:v>23.5</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>-4</x:v>
+        <x:v>-1.18</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>920000</x:v>
+        <x:v>9600000</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G14" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>3150489640</x:v>
+        <x:v>2427624044</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>0.0154</x:v>
+        <x:v>0.1785</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
       <x:c r="A15" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>99.5</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>1.3</x:v>
+        <x:v>13.75</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E15" s="0">
+        <x:v>9172451</x:v>
+      </x:c>
+      <x:c r="F15" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="E15" s="0">
-        <x:v>12100000</x:v>
-      </x:c>
-      <x:c r="F15" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="G15" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>709077088</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>0.005</x:v>
+        <x:v>0.0129</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
       <x:c r="A16" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B16" s="0">
+        <x:v>40.2</x:v>
+      </x:c>
+      <x:c r="C16" s="0">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="D16" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="B16" s="0">
-        <x:v>431.75</x:v>
-      </x:c>
-      <x:c r="C16" s="0">
-        <x:v>3.25</x:v>
-      </x:c>
-      <x:c r="D16" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="E16" s="0">
-        <x:v>125100000</x:v>
+        <x:v>32493961</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
         <x:v>11</x:v>
@@ -1260,114 +1263,114 @@
         <x:v>2026.03</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>184925592000</x:v>
+        <x:v>17386730041</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>0.0304</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
       <x:c r="A17" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>10.64</x:v>
+        <x:v>95.2</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>0.96</x:v>
+        <x:v>8.65</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>32010000</x:v>
+        <x:v>940002</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G17" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>10581001663</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>0.1592</x:v>
+        <x:v>0.0121</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
       <x:c r="A18" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>29.36</x:v>
+        <x:v>135.4</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>0.58</x:v>
+        <x:v>-11.1</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>76650</x:v>
+        <x:v>920000</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G18" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>7297855153</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>0.0005</x:v>
+        <x:v>0.0154</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
       <x:c r="A19" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>146.5</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>-4</x:v>
+        <x:v>-5.5</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>915000</x:v>
+        <x:v>12100000</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G19" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>3150489640</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>0.0153</x:v>
+        <x:v>0.005</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
       <x:c r="A20" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>40</x:v>
+        <x:v>419.25</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>2.4</x:v>
+        <x:v>-12.5</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>2136645</x:v>
+        <x:v>125100000</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
         <x:v>11</x:v>
@@ -1376,56 +1379,56 @@
         <x:v>2026.03</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>17386730041</x:v>
+        <x:v>184925592000</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>0.0055</x:v>
+        <x:v>0.0304</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
       <x:c r="A21" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>6.12</x:v>
+        <x:v>11.41</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>0.12</x:v>
+        <x:v>0.77</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>132077304</x:v>
+        <x:v>32010000</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G21" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>855070469</x:v>
+        <x:v>10581001663</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>0.1545</x:v>
+        <x:v>0.1592</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
       <x:c r="A22" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B22" s="0">
+        <x:v>28.78</x:v>
+      </x:c>
+      <x:c r="C22" s="0">
+        <x:v>-0.58</x:v>
+      </x:c>
+      <x:c r="D22" s="0" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="B22" s="0">
-        <x:v>339.5</x:v>
-      </x:c>
-      <x:c r="C22" s="0">
-        <x:v>13.5</x:v>
-      </x:c>
-      <x:c r="D22" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
       <x:c r="E22" s="0">
-        <x:v>51531000</x:v>
+        <x:v>76650</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
         <x:v>11</x:v>
@@ -1434,143 +1437,143 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>35290767390</x:v>
+        <x:v>7297855153</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>0.0656</x:v>
+        <x:v>0.0005</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
       <x:c r="A23" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B23" s="0">
+        <x:v>135.4</x:v>
+      </x:c>
+      <x:c r="C23" s="0">
+        <x:v>-11.1</x:v>
+      </x:c>
+      <x:c r="D23" s="0" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="B23" s="0">
-        <x:v>1131</x:v>
-      </x:c>
-      <x:c r="C23" s="0">
-        <x:v>-69</x:v>
-      </x:c>
-      <x:c r="D23" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
       <x:c r="E23" s="0">
-        <x:v>950978</x:v>
+        <x:v>915000</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G23" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>1883544167</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>0.0227</x:v>
+        <x:v>0.0153</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
       <x:c r="A24" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>596.5</x:v>
+        <x:v>40.2</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>-5</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>100000000</x:v>
+        <x:v>2136645</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2026.03</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>71453576000</x:v>
+        <x:v>17386730041</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>0.0628</x:v>
+        <x:v>0.0055</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
       <x:c r="A25" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>86.55</x:v>
+        <x:v>5.6</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>0.05</x:v>
+        <x:v>-0.52</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>286071819</x:v>
+        <x:v>132077304</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G25" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>855070469</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>0.0818</x:v>
+        <x:v>0.1545</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
       <x:c r="A26" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>146.5</x:v>
+        <x:v>333.25</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>-4</x:v>
+        <x:v>-6.25</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>883793</x:v>
+        <x:v>51531000</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G26" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>3150489640</x:v>
+        <x:v>35290767390</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>0.0148</x:v>
+        <x:v>0.0656</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
       <x:c r="A27" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>58.7</x:v>
+        <x:v>1172</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>1.45</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>606770</x:v>
+        <x:v>950978</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
         <x:v>11</x:v>
@@ -1579,172 +1582,172 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>1883544167</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>0.0064</x:v>
+        <x:v>0.0227</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
       <x:c r="A28" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>66</x:v>
+        <x:v>539.5</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>2.85</x:v>
+        <x:v>-57</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>505597002</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G28" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>8121300519</x:v>
+        <x:v>71453576000</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>0.0623</x:v>
+        <x:v>0.0628</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
       <x:c r="A29" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>58.7</x:v>
+        <x:v>95.2</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>1.45</x:v>
+        <x:v>8.65</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>948000</x:v>
+        <x:v>286071819</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G29" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>0.0101</x:v>
+        <x:v>0.0818</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
       <x:c r="A30" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>99.5</x:v>
+        <x:v>135.4</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>1.3</x:v>
+        <x:v>-11.1</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>622000</x:v>
+        <x:v>883793</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G30" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>0.0114</x:v>
+        <x:v>0.0148</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
       <x:c r="A31" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>4.28</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>0.12</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>983000</x:v>
+        <x:v>606770</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G31" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>2875634546</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>0.018</x:v>
+        <x:v>0.0064</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
       <x:c r="A32" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>76.5</x:v>
+        <x:v>63.3</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>-0.35</x:v>
+        <x:v>-2.7</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>3421818</x:v>
+        <x:v>505597002</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G32" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>5948036961</x:v>
+        <x:v>8121300519</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>0.0257</x:v>
+        <x:v>0.0623</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
       <x:c r="A33" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>51</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>1.4</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>697435</x:v>
+        <x:v>948000</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
         <x:v>11</x:v>
@@ -1753,27 +1756,27 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>4728937463</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>0.0066</x:v>
+        <x:v>0.0101</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
       <x:c r="A34" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B34" s="0">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="C34" s="0">
+        <x:v>-5.5</x:v>
+      </x:c>
+      <x:c r="D34" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="B34" s="0">
-        <x:v>86.25</x:v>
-      </x:c>
-      <x:c r="C34" s="0">
-        <x:v>5.65</x:v>
-      </x:c>
-      <x:c r="D34" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
       <x:c r="E34" s="0">
-        <x:v>4587145</x:v>
+        <x:v>622000</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
         <x:v>11</x:v>
@@ -1782,114 +1785,114 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>16733157490</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>0.0123</x:v>
+        <x:v>0.0114</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
       <x:c r="A35" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>51.05</x:v>
+        <x:v>4.11</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>4.61</x:v>
+        <x:v>-0.17</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>43200000</x:v>
+        <x:v>983000</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G35" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>8236540064</x:v>
+        <x:v>2875634546</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>0.2345</x:v>
+        <x:v>0.018</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
       <x:c r="A36" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>19.37</x:v>
+        <x:v>76.8</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>-0.11</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>1200000</x:v>
+        <x:v>3421818</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G36" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>3139850323</x:v>
+        <x:v>5948036961</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>0.0201</x:v>
+        <x:v>0.0257</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
       <x:c r="A37" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>66</x:v>
+        <x:v>49.6</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>2.85</x:v>
+        <x:v>-1.4</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>247902522</x:v>
+        <x:v>697435</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G37" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>8121300519</x:v>
+        <x:v>4728937463</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>0.0305</x:v>
+        <x:v>0.0066</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
       <x:c r="A38" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>58.7</x:v>
+        <x:v>94.85</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>1.45</x:v>
+        <x:v>8.6</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>366000</x:v>
+        <x:v>4587145</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
         <x:v>11</x:v>
@@ -1898,97 +1901,97 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>16733157490</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>0.0039</x:v>
+        <x:v>0.0123</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
       <x:c r="A39" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>311.25</x:v>
+        <x:v>50.25</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>14.5</x:v>
+        <x:v>-0.8</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>141051834</x:v>
+        <x:v>43200000</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G39" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>709077088</x:v>
+        <x:v>8236540064</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>0.1989</x:v>
+        <x:v>0.2345</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
       <x:c r="A40" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>5.03</x:v>
+        <x:v>18.5</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>0.09</x:v>
+        <x:v>-0.87</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>5096500000</x:v>
+        <x:v>1200000</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>19538660616</x:v>
+        <x:v>3139850323</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>0.2608</x:v>
+        <x:v>0.0201</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
       <x:c r="A41" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>5.03</x:v>
+        <x:v>63.3</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>0.09</x:v>
+        <x:v>-2.7</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>5096500000</x:v>
+        <x:v>247902522</x:v>
       </x:c>
       <x:c r="F41" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>19538660616</x:v>
+        <x:v>8121300519</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>0.2608</x:v>
+        <x:v>0.0305</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1996,16 +1999,16 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>40</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>2.4</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>37500000</x:v>
+        <x:v>366000</x:v>
       </x:c>
       <x:c r="F42" s="0" t="s">
         <x:v>11</x:v>
@@ -2014,68 +2017,68 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>16355768622</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>0.1024</x:v>
+        <x:v>0.0039</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
       <x:c r="A43" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B43" s="0">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="C43" s="0">
+        <x:v>13.75</x:v>
+      </x:c>
+      <x:c r="D43" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="B43" s="0">
-        <x:v>275</x:v>
-      </x:c>
-      <x:c r="C43" s="0">
-        <x:v>-13</x:v>
-      </x:c>
-      <x:c r="D43" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
       <x:c r="E43" s="0">
-        <x:v>2030000</x:v>
+        <x:v>141051834</x:v>
       </x:c>
       <x:c r="F43" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G43" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>2159813703</x:v>
+        <x:v>709077088</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>0.042</x:v>
+        <x:v>0.1989</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
       <x:c r="A44" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>86.25</x:v>
+        <x:v>4.94</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>5.65</x:v>
+        <x:v>-0.09</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>31146246</x:v>
+        <x:v>5096500000</x:v>
       </x:c>
       <x:c r="F44" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>16733157490</x:v>
+        <x:v>19538660616</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>0.0832</x:v>
+        <x:v>0.2608</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -2083,74 +2086,74 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>13.24</x:v>
+        <x:v>4.94</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>0.38</x:v>
+        <x:v>-0.09</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>1000000</x:v>
+        <x:v>5096500000</x:v>
       </x:c>
       <x:c r="F45" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>7221187888</x:v>
+        <x:v>19538660616</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>0.0001</x:v>
+        <x:v>0.2608</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
       <x:c r="A46" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>13.24</x:v>
+        <x:v>40.2</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>0.38</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>3150000</x:v>
+        <x:v>37500000</x:v>
       </x:c>
       <x:c r="F46" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G46" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>7221187888</x:v>
+        <x:v>16355768622</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>0.0227</x:v>
+        <x:v>0.1024</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
       <x:c r="A47" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>13.24</x:v>
+        <x:v>269.5</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>0.38</x:v>
+        <x:v>-5.5</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>2690000</x:v>
+        <x:v>2030000</x:v>
       </x:c>
       <x:c r="F47" s="0" t="s">
         <x:v>11</x:v>
@@ -2159,27 +2162,27 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>7221187888</x:v>
+        <x:v>2159813703</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>0.0166</x:v>
+        <x:v>0.042</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
       <x:c r="A48" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>86.25</x:v>
+        <x:v>94.85</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>5.65</x:v>
+        <x:v>8.6</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>4103000</x:v>
+        <x:v>31146246</x:v>
       </x:c>
       <x:c r="F48" s="0" t="s">
         <x:v>11</x:v>
@@ -2191,256 +2194,256 @@
         <x:v>16733157490</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>0.0109</x:v>
+        <x:v>0.0832</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
       <x:c r="A49" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>146.5</x:v>
+        <x:v>12.72</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>-4</x:v>
+        <x:v>-0.52</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>500000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="F49" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G49" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>3150489640</x:v>
+        <x:v>7221187888</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>0.0083</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
       <x:c r="A50" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>58.7</x:v>
+        <x:v>12.72</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>1.45</x:v>
+        <x:v>-0.52</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>872928</x:v>
+        <x:v>3150000</x:v>
       </x:c>
       <x:c r="F50" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G50" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>7221187888</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>0.0092</x:v>
+        <x:v>0.0227</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
       <x:c r="A51" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>99.5</x:v>
+        <x:v>12.72</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>1.3</x:v>
+        <x:v>-0.52</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>21250000</x:v>
+        <x:v>2690000</x:v>
       </x:c>
       <x:c r="F51" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G51" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>7221187888</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>0.0087</x:v>
+        <x:v>0.0166</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
       <x:c r="A52" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>66</x:v>
+        <x:v>94.85</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>2.85</x:v>
+        <x:v>8.6</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>67690912</x:v>
+        <x:v>4103000</x:v>
       </x:c>
       <x:c r="F52" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G52" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>8121300519</x:v>
+        <x:v>16733157490</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>0.0083</x:v>
+        <x:v>0.0109</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:9">
       <x:c r="A53" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B53" s="0">
-        <x:v>40</x:v>
+        <x:v>135.4</x:v>
       </x:c>
       <x:c r="C53" s="0">
-        <x:v>2.4</x:v>
+        <x:v>-11.1</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
       <x:c r="E53" s="0">
-        <x:v>65458848</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="F53" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G53" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H53" s="0">
-        <x:v>16355768622</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>0.1784</x:v>
+        <x:v>0.0083</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:9">
       <x:c r="A54" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B54" s="0">
-        <x:v>25.08</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C54" s="0">
-        <x:v>0.18</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
       <x:c r="E54" s="0">
-        <x:v>689500000</x:v>
+        <x:v>872928</x:v>
       </x:c>
       <x:c r="F54" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G54" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>884571536</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>0.7795</x:v>
+        <x:v>0.0092</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:9">
       <x:c r="A55" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B55" s="0">
-        <x:v>8.45</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C55" s="0">
-        <x:v>0.76</x:v>
+        <x:v>-5.5</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E55" s="0">
-        <x:v>3024490</x:v>
+        <x:v>21250000</x:v>
       </x:c>
       <x:c r="F55" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G55" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H55" s="0">
-        <x:v>2322993973</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>0.0671</x:v>
+        <x:v>0.0087</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:9">
       <x:c r="A56" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B56" s="0">
-        <x:v>8.45</x:v>
+        <x:v>63.3</x:v>
       </x:c>
       <x:c r="C56" s="0">
-        <x:v>0.76</x:v>
+        <x:v>-2.7</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E56" s="0">
-        <x:v>4510336</x:v>
+        <x:v>67690912</x:v>
       </x:c>
       <x:c r="F56" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G56" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H56" s="0">
-        <x:v>2322993973</x:v>
+        <x:v>8121300519</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>0.0865</x:v>
+        <x:v>0.0083</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:9">
       <x:c r="A57" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B57" s="0">
+        <x:v>40.2</x:v>
+      </x:c>
+      <x:c r="C57" s="0">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="D57" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="B57" s="0">
-        <x:v>61.35</x:v>
-      </x:c>
-      <x:c r="C57" s="0">
-        <x:v>-0.05</x:v>
-      </x:c>
-      <x:c r="D57" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
       <x:c r="E57" s="0">
-        <x:v>205000000</x:v>
+        <x:v>65458848</x:v>
       </x:c>
       <x:c r="F57" s="0" t="s">
         <x:v>11</x:v>
@@ -2449,85 +2452,85 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H57" s="0">
-        <x:v>20597209000</x:v>
+        <x:v>16355768622</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>0.4434</x:v>
+        <x:v>0.1784</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:9">
       <x:c r="A58" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B58" s="0">
-        <x:v>315.5</x:v>
+        <x:v>25.32</x:v>
       </x:c>
       <x:c r="C58" s="0">
-        <x:v>5.25</x:v>
+        <x:v>0.24</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E58" s="0">
-        <x:v>305000000</x:v>
+        <x:v>689500000</x:v>
       </x:c>
       <x:c r="F58" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G58" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H58" s="0">
-        <x:v>400439646</x:v>
+        <x:v>884571536</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>0.7617</x:v>
+        <x:v>0.7795</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:9">
       <x:c r="A59" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B59" s="0">
-        <x:v>86.55</x:v>
+        <x:v>8.1</x:v>
       </x:c>
       <x:c r="C59" s="0">
-        <x:v>0.05</x:v>
+        <x:v>-0.35</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E59" s="0">
-        <x:v>11700000</x:v>
+        <x:v>3024490</x:v>
       </x:c>
       <x:c r="F59" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G59" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H59" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>2322993973</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>0.1718</x:v>
+        <x:v>0.0671</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:9">
       <x:c r="A60" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B60" s="0">
-        <x:v>275</x:v>
+        <x:v>8.1</x:v>
       </x:c>
       <x:c r="C60" s="0">
-        <x:v>-13</x:v>
+        <x:v>-0.35</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E60" s="0">
-        <x:v>1900000</x:v>
+        <x:v>4510336</x:v>
       </x:c>
       <x:c r="F60" s="0" t="s">
         <x:v>11</x:v>
@@ -2536,114 +2539,114 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H60" s="0">
-        <x:v>2159813703</x:v>
+        <x:v>2322993973</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>0.0391</x:v>
+        <x:v>0.0865</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:9">
       <x:c r="A61" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B61" s="0">
-        <x:v>4.28</x:v>
+        <x:v>61.35</x:v>
       </x:c>
       <x:c r="C61" s="0">
-        <x:v>0.12</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="E61" s="0">
-        <x:v>1670000</x:v>
+        <x:v>205000000</x:v>
       </x:c>
       <x:c r="F61" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G61" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H61" s="0">
-        <x:v>2875634546</x:v>
+        <x:v>20597209000</x:v>
       </x:c>
       <x:c r="I61" s="0">
-        <x:v>0.0298</x:v>
+        <x:v>0.4434</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:9">
       <x:c r="A62" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B62" s="0">
-        <x:v>25.08</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="C62" s="0">
-        <x:v>0.18</x:v>
+        <x:v>4.5</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E62" s="0">
-        <x:v>48895800</x:v>
+        <x:v>305000000</x:v>
       </x:c>
       <x:c r="F62" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G62" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H62" s="0">
-        <x:v>884571536</x:v>
+        <x:v>400439646</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>0.0553</x:v>
+        <x:v>0.7617</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:9">
       <x:c r="A63" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B63" s="0">
-        <x:v>25.08</x:v>
+        <x:v>95.2</x:v>
       </x:c>
       <x:c r="C63" s="0">
-        <x:v>0.18</x:v>
+        <x:v>8.65</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E63" s="0">
-        <x:v>689500000</x:v>
+        <x:v>11700000</x:v>
       </x:c>
       <x:c r="F63" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G63" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H63" s="0">
-        <x:v>884571536</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>0.7795</x:v>
+        <x:v>0.1718</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:9">
       <x:c r="A64" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B64" s="0">
+        <x:v>269.5</x:v>
+      </x:c>
+      <x:c r="C64" s="0">
+        <x:v>-5.5</x:v>
+      </x:c>
+      <x:c r="D64" s="0" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="B64" s="0">
-        <x:v>49.6</x:v>
-      </x:c>
-      <x:c r="C64" s="0">
-        <x:v>1.32</x:v>
-      </x:c>
-      <x:c r="D64" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
       <x:c r="E64" s="0">
-        <x:v>3102911</x:v>
+        <x:v>1900000</x:v>
       </x:c>
       <x:c r="F64" s="0" t="s">
         <x:v>11</x:v>
@@ -2652,114 +2655,114 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H64" s="0">
-        <x:v>2907014564</x:v>
+        <x:v>2159813703</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>0.0475</x:v>
+        <x:v>0.0391</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:9">
       <x:c r="A65" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B65" s="0">
-        <x:v>26.38</x:v>
+        <x:v>4.11</x:v>
       </x:c>
       <x:c r="C65" s="0">
-        <x:v>0.6</x:v>
+        <x:v>-0.17</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E65" s="0">
-        <x:v>13000000</x:v>
+        <x:v>1670000</x:v>
       </x:c>
       <x:c r="F65" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G65" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H65" s="0">
-        <x:v>11834942581</x:v>
+        <x:v>2875634546</x:v>
       </x:c>
       <x:c r="I65" s="0">
-        <x:v>0.0563</x:v>
+        <x:v>0.0298</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:9">
       <x:c r="A66" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B66" s="0">
-        <x:v>76.5</x:v>
+        <x:v>25.32</x:v>
       </x:c>
       <x:c r="C66" s="0">
-        <x:v>-0.35</x:v>
+        <x:v>0.24</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E66" s="0">
-        <x:v>6800000</x:v>
+        <x:v>48895800</x:v>
       </x:c>
       <x:c r="F66" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G66" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H66" s="0">
-        <x:v>5948036961</x:v>
+        <x:v>884571536</x:v>
       </x:c>
       <x:c r="I66" s="0">
-        <x:v>0.0583</x:v>
+        <x:v>0.0553</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:9">
       <x:c r="A67" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B67" s="0">
-        <x:v>61.35</x:v>
+        <x:v>25.32</x:v>
       </x:c>
       <x:c r="C67" s="0">
-        <x:v>-0.05</x:v>
+        <x:v>0.24</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E67" s="0">
-        <x:v>36750000</x:v>
+        <x:v>689500000</x:v>
       </x:c>
       <x:c r="F67" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G67" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H67" s="0">
-        <x:v>20597209000</x:v>
+        <x:v>884571536</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>0.0793</x:v>
+        <x:v>0.7795</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:9">
       <x:c r="A68" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B68" s="0">
-        <x:v>1131</x:v>
+        <x:v>48.58</x:v>
       </x:c>
       <x:c r="C68" s="0">
-        <x:v>-69</x:v>
+        <x:v>-1.02</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E68" s="0">
-        <x:v>3867260</x:v>
+        <x:v>3102911</x:v>
       </x:c>
       <x:c r="F68" s="0" t="s">
         <x:v>11</x:v>
@@ -2768,114 +2771,114 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H68" s="0">
-        <x:v>1883544167</x:v>
+        <x:v>2907014564</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>0.0912</x:v>
+        <x:v>0.0475</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:9">
       <x:c r="A69" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B69" s="0">
-        <x:v>71.1</x:v>
+        <x:v>24.7</x:v>
       </x:c>
       <x:c r="C69" s="0">
-        <x:v>3.1</x:v>
+        <x:v>-1.68</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E69" s="0">
-        <x:v>1498029716</x:v>
+        <x:v>13000000</x:v>
       </x:c>
       <x:c r="F69" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G69" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H69" s="0">
-        <x:v>12030341104</x:v>
+        <x:v>11834942581</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>0.1245</x:v>
+        <x:v>0.0563</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:9">
       <x:c r="A70" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B70" s="0">
-        <x:v>40</x:v>
+        <x:v>76.8</x:v>
       </x:c>
       <x:c r="C70" s="0">
-        <x:v>2.4</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E70" s="0">
-        <x:v>48000000</x:v>
+        <x:v>6800000</x:v>
       </x:c>
       <x:c r="F70" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G70" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H70" s="0">
-        <x:v>16355768622</x:v>
+        <x:v>5948036961</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>0.1301</x:v>
+        <x:v>0.0583</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:9">
       <x:c r="A71" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B71" s="0">
-        <x:v>86.55</x:v>
+        <x:v>61.35</x:v>
       </x:c>
       <x:c r="C71" s="0">
-        <x:v>0.05</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E71" s="0">
-        <x:v>279699629</x:v>
+        <x:v>36750000</x:v>
       </x:c>
       <x:c r="F71" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G71" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H71" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>20597209000</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>0.08</x:v>
+        <x:v>0.0793</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:9">
       <x:c r="A72" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B72" s="0">
-        <x:v>16.98</x:v>
+        <x:v>1172</x:v>
       </x:c>
       <x:c r="C72" s="0">
-        <x:v>0.18</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E72" s="0">
-        <x:v>7971822</x:v>
+        <x:v>3867260</x:v>
       </x:c>
       <x:c r="F72" s="0" t="s">
         <x:v>11</x:v>
@@ -2884,404 +2887,404 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H72" s="0">
-        <x:v>4675369372</x:v>
+        <x:v>1883544167</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>0.0756</x:v>
+        <x:v>0.0912</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:9">
       <x:c r="A73" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B73" s="0">
-        <x:v>58.7</x:v>
+        <x:v>70.15</x:v>
       </x:c>
       <x:c r="C73" s="0">
-        <x:v>1.45</x:v>
+        <x:v>-0.95</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E73" s="0">
-        <x:v>1104000</x:v>
+        <x:v>1498029716</x:v>
       </x:c>
       <x:c r="F73" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G73" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H73" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>12030341104</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>0.0116</x:v>
+        <x:v>0.1245</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:9">
       <x:c r="A74" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B74" s="0">
-        <x:v>25.08</x:v>
+        <x:v>40.2</x:v>
       </x:c>
       <x:c r="C74" s="0">
-        <x:v>0.18</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E74" s="0">
-        <x:v>48895800</x:v>
+        <x:v>48000000</x:v>
       </x:c>
       <x:c r="F74" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G74" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H74" s="0">
-        <x:v>884571536</x:v>
+        <x:v>16355768622</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>0.0553</x:v>
+        <x:v>0.1301</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:9">
       <x:c r="A75" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B75" s="0">
+        <x:v>95.2</x:v>
+      </x:c>
+      <x:c r="C75" s="0">
+        <x:v>8.65</x:v>
+      </x:c>
+      <x:c r="D75" s="0" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="B75" s="0">
-        <x:v>3.51</x:v>
-      </x:c>
-      <x:c r="C75" s="0">
-        <x:v>0.1</x:v>
-      </x:c>
-      <x:c r="D75" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
       <x:c r="E75" s="0">
-        <x:v>191089413</x:v>
+        <x:v>279699629</x:v>
       </x:c>
       <x:c r="F75" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G75" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H75" s="0">
-        <x:v>9665356715</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>0.0198</x:v>
+        <x:v>0.08</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:9">
       <x:c r="A76" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B76" s="0">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C76" s="0">
+        <x:v>-0.98</x:v>
+      </x:c>
+      <x:c r="D76" s="0" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="B76" s="0">
-        <x:v>3.51</x:v>
-      </x:c>
-      <x:c r="C76" s="0">
-        <x:v>0.1</x:v>
-      </x:c>
-      <x:c r="D76" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
       <x:c r="E76" s="0">
-        <x:v>605627160</x:v>
+        <x:v>7971822</x:v>
       </x:c>
       <x:c r="F76" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G76" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H76" s="0">
-        <x:v>9665356715</x:v>
+        <x:v>4675369372</x:v>
       </x:c>
       <x:c r="I76" s="0">
-        <x:v>0.0627</x:v>
+        <x:v>0.0756</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:9">
       <x:c r="A77" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B77" s="0">
-        <x:v>25.98</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C77" s="0">
-        <x:v>-1.92</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E77" s="0">
-        <x:v>2356546000</x:v>
+        <x:v>1104000</x:v>
       </x:c>
       <x:c r="F77" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G77" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H77" s="0">
-        <x:v>7708004248</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>0.3057</x:v>
+        <x:v>0.0116</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:9">
       <x:c r="A78" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B78" s="0">
-        <x:v>19.37</x:v>
+        <x:v>25.32</x:v>
       </x:c>
       <x:c r="C78" s="0">
-        <x:v>-0.11</x:v>
+        <x:v>0.24</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E78" s="0">
-        <x:v>431250</x:v>
+        <x:v>48895800</x:v>
       </x:c>
       <x:c r="F78" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G78" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H78" s="0">
-        <x:v>3139850323</x:v>
+        <x:v>884571536</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>0.0071</x:v>
+        <x:v>0.0553</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:9">
       <x:c r="A79" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B79" s="0">
-        <x:v>19.37</x:v>
+        <x:v>3.56</x:v>
       </x:c>
       <x:c r="C79" s="0">
-        <x:v>-0.11</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E79" s="0">
-        <x:v>800000</x:v>
+        <x:v>191089413</x:v>
       </x:c>
       <x:c r="F79" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G79" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H79" s="0">
-        <x:v>3139850323</x:v>
+        <x:v>9665356715</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>0.0131</x:v>
+        <x:v>0.0198</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:9">
       <x:c r="A80" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B80" s="0">
-        <x:v>66</x:v>
+        <x:v>3.56</x:v>
       </x:c>
       <x:c r="C80" s="0">
-        <x:v>2.85</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E80" s="0">
-        <x:v>127172130</x:v>
+        <x:v>605627160</x:v>
       </x:c>
       <x:c r="F80" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G80" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H80" s="0">
-        <x:v>8121300519</x:v>
+        <x:v>9665356715</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>0.0157</x:v>
+        <x:v>0.0627</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:9">
       <x:c r="A81" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B81" s="0">
-        <x:v>51</x:v>
+        <x:v>25.76</x:v>
       </x:c>
       <x:c r="C81" s="0">
-        <x:v>1.4</x:v>
+        <x:v>-0.22</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E81" s="0">
-        <x:v>42625000</x:v>
+        <x:v>2356546000</x:v>
       </x:c>
       <x:c r="F81" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G81" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H81" s="0">
-        <x:v>4728937463</x:v>
+        <x:v>7708004248</x:v>
       </x:c>
       <x:c r="I81" s="0">
-        <x:v>0.3994</x:v>
+        <x:v>0.3057</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:9">
       <x:c r="A82" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B82" s="0">
-        <x:v>99.5</x:v>
+        <x:v>18.5</x:v>
       </x:c>
       <x:c r="C82" s="0">
-        <x:v>1.3</x:v>
+        <x:v>-0.87</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E82" s="0">
-        <x:v>1486000</x:v>
+        <x:v>431250</x:v>
       </x:c>
       <x:c r="F82" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G82" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H82" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>3139850323</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>0.027</x:v>
+        <x:v>0.0071</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:9">
       <x:c r="A83" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B83" s="0">
-        <x:v>339.5</x:v>
+        <x:v>18.5</x:v>
       </x:c>
       <x:c r="C83" s="0">
-        <x:v>13.5</x:v>
+        <x:v>-0.87</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E83" s="0">
-        <x:v>768864700</x:v>
+        <x:v>800000</x:v>
       </x:c>
       <x:c r="F83" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G83" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H83" s="0">
-        <x:v>35290767390</x:v>
+        <x:v>3139850323</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>0.9648</x:v>
+        <x:v>0.0131</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:9">
       <x:c r="A84" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B84" s="0">
-        <x:v>86.25</x:v>
+        <x:v>63.3</x:v>
       </x:c>
       <x:c r="C84" s="0">
-        <x:v>5.65</x:v>
+        <x:v>-2.7</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E84" s="0">
-        <x:v>15938617</x:v>
+        <x:v>127172130</x:v>
       </x:c>
       <x:c r="F84" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G84" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H84" s="0">
-        <x:v>16733157490</x:v>
+        <x:v>8121300519</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>0.0422</x:v>
+        <x:v>0.0157</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:9">
       <x:c r="A85" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B85" s="0">
+        <x:v>49.6</x:v>
+      </x:c>
+      <x:c r="C85" s="0">
+        <x:v>-1.4</x:v>
+      </x:c>
+      <x:c r="D85" s="0" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="B85" s="0">
-        <x:v>14.84</x:v>
-      </x:c>
-      <x:c r="C85" s="0">
-        <x:v>-0.15</x:v>
-      </x:c>
-      <x:c r="D85" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
       <x:c r="E85" s="0">
-        <x:v>30438120</x:v>
+        <x:v>42625000</x:v>
       </x:c>
       <x:c r="F85" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G85" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H85" s="0">
-        <x:v>3159124121</x:v>
+        <x:v>4728937463</x:v>
       </x:c>
       <x:c r="I85" s="0">
-        <x:v>0</x:v>
+        <x:v>0.3994</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:9">
       <x:c r="A86" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B86" s="0">
-        <x:v>275</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C86" s="0">
-        <x:v>-13</x:v>
+        <x:v>-5.5</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E86" s="0">
-        <x:v>3900000</x:v>
+        <x:v>1486000</x:v>
       </x:c>
       <x:c r="F86" s="0" t="s">
         <x:v>11</x:v>
@@ -3290,27 +3293,27 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H86" s="0">
-        <x:v>2159813703</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>0.0797</x:v>
+        <x:v>0.027</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:9">
       <x:c r="A87" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B87" s="0">
-        <x:v>275</x:v>
+        <x:v>333.25</x:v>
       </x:c>
       <x:c r="C87" s="0">
-        <x:v>-13</x:v>
+        <x:v>-6.25</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E87" s="0">
-        <x:v>2104908</x:v>
+        <x:v>768864700</x:v>
       </x:c>
       <x:c r="F87" s="0" t="s">
         <x:v>11</x:v>
@@ -3319,27 +3322,27 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H87" s="0">
-        <x:v>2159813703</x:v>
+        <x:v>35290767390</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>0.043</x:v>
+        <x:v>0.9648</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:9">
       <x:c r="A88" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B88" s="0">
-        <x:v>29.36</x:v>
+        <x:v>94.85</x:v>
       </x:c>
       <x:c r="C88" s="0">
-        <x:v>0.58</x:v>
+        <x:v>8.6</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E88" s="0">
-        <x:v>3900000</x:v>
+        <x:v>15938617</x:v>
       </x:c>
       <x:c r="F88" s="0" t="s">
         <x:v>11</x:v>
@@ -3348,114 +3351,114 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H88" s="0">
-        <x:v>7297855153</x:v>
+        <x:v>16733157490</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>0.0236</x:v>
+        <x:v>0.0422</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:9">
       <x:c r="A89" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B89" s="0">
-        <x:v>6.12</x:v>
+        <x:v>14.86</x:v>
       </x:c>
       <x:c r="C89" s="0">
-        <x:v>0.12</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
         <x:v>79</x:v>
       </x:c>
       <x:c r="E89" s="0">
-        <x:v>496968445</x:v>
+        <x:v>30438120</x:v>
       </x:c>
       <x:c r="F89" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G89" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H89" s="0">
-        <x:v>855070469</x:v>
+        <x:v>3159124121</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>0.5812</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:9">
       <x:c r="A90" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B90" s="0">
+        <x:v>269.5</x:v>
+      </x:c>
+      <x:c r="C90" s="0">
+        <x:v>-5.5</x:v>
+      </x:c>
+      <x:c r="D90" s="0" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="B90" s="0">
-        <x:v>11.63</x:v>
-      </x:c>
-      <x:c r="C90" s="0">
-        <x:v>-0.9</x:v>
-      </x:c>
-      <x:c r="D90" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
       <x:c r="E90" s="0">
-        <x:v>108750000</x:v>
+        <x:v>3900000</x:v>
       </x:c>
       <x:c r="F90" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G90" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H90" s="0">
-        <x:v>1982520183</x:v>
+        <x:v>2159813703</x:v>
       </x:c>
       <x:c r="I90" s="0">
-        <x:v>0.0549</x:v>
+        <x:v>0.0797</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:9">
       <x:c r="A91" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B91" s="0">
-        <x:v>146.5</x:v>
+        <x:v>269.5</x:v>
       </x:c>
       <x:c r="C91" s="0">
-        <x:v>-4</x:v>
+        <x:v>-5.5</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E91" s="0">
-        <x:v>1605197</x:v>
+        <x:v>2104908</x:v>
       </x:c>
       <x:c r="F91" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G91" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H91" s="0">
-        <x:v>3150489640</x:v>
+        <x:v>2159813703</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>0.0257</x:v>
+        <x:v>0.043</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:9">
       <x:c r="A92" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B92" s="0">
-        <x:v>431.75</x:v>
+        <x:v>28.78</x:v>
       </x:c>
       <x:c r="C92" s="0">
-        <x:v>3.25</x:v>
+        <x:v>-0.58</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E92" s="0">
-        <x:v>54600000</x:v>
+        <x:v>3900000</x:v>
       </x:c>
       <x:c r="F92" s="0" t="s">
         <x:v>11</x:v>
@@ -3464,114 +3467,114 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H92" s="0">
-        <x:v>180444938000</x:v>
+        <x:v>7297855153</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>0.0133</x:v>
+        <x:v>0.0236</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:9">
       <x:c r="A93" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B93" s="0">
-        <x:v>431.75</x:v>
+        <x:v>5.6</x:v>
       </x:c>
       <x:c r="C93" s="0">
-        <x:v>3.25</x:v>
+        <x:v>-0.52</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E93" s="0">
-        <x:v>111850000</x:v>
+        <x:v>496968445</x:v>
       </x:c>
       <x:c r="F93" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G93" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H93" s="0">
-        <x:v>180444938000</x:v>
+        <x:v>855070469</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>0.0273</x:v>
+        <x:v>0.5812</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:9">
       <x:c r="A94" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B94" s="0">
-        <x:v>58.7</x:v>
+        <x:v>11.31</x:v>
       </x:c>
       <x:c r="C94" s="0">
-        <x:v>1.45</x:v>
+        <x:v>-0.32</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E94" s="0">
-        <x:v>803090</x:v>
+        <x:v>108750000</x:v>
       </x:c>
       <x:c r="F94" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G94" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H94" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>1982520183</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>0.0084</x:v>
+        <x:v>0.0549</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:9">
       <x:c r="A95" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B95" s="0">
-        <x:v>25.98</x:v>
+        <x:v>135.4</x:v>
       </x:c>
       <x:c r="C95" s="0">
-        <x:v>-1.92</x:v>
+        <x:v>-11.1</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
         <x:v>83</x:v>
       </x:c>
       <x:c r="E95" s="0">
-        <x:v>2356546000</x:v>
+        <x:v>1605197</x:v>
       </x:c>
       <x:c r="F95" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G95" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H95" s="0">
-        <x:v>7708004248</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>0.3057</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:9">
       <x:c r="A96" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B96" s="0">
-        <x:v>1131</x:v>
+        <x:v>419.25</x:v>
       </x:c>
       <x:c r="C96" s="0">
-        <x:v>-69</x:v>
+        <x:v>-12.5</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E96" s="0">
-        <x:v>875400</x:v>
+        <x:v>54600000</x:v>
       </x:c>
       <x:c r="F96" s="0" t="s">
         <x:v>11</x:v>
@@ -3580,288 +3583,288 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H96" s="0">
-        <x:v>1883544167</x:v>
+        <x:v>180444938000</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>0.0205</x:v>
+        <x:v>0.0133</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:9">
       <x:c r="A97" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B97" s="0">
-        <x:v>27</x:v>
+        <x:v>419.25</x:v>
       </x:c>
       <x:c r="C97" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>-12.5</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E97" s="0">
-        <x:v>330000000</x:v>
+        <x:v>111850000</x:v>
       </x:c>
       <x:c r="F97" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G97" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H97" s="0">
-        <x:v>5287314404</x:v>
+        <x:v>180444938000</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>0.0624</x:v>
+        <x:v>0.0273</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:9">
       <x:c r="A98" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B98" s="0">
-        <x:v>86.55</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C98" s="0">
-        <x:v>0.05</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E98" s="0">
-        <x:v>11700000</x:v>
+        <x:v>803090</x:v>
       </x:c>
       <x:c r="F98" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G98" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H98" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>0.1705</x:v>
+        <x:v>0.0084</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:9">
       <x:c r="A99" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B99" s="0">
-        <x:v>10.64</x:v>
+        <x:v>25.76</x:v>
       </x:c>
       <x:c r="C99" s="0">
-        <x:v>0.96</x:v>
+        <x:v>-0.22</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E99" s="0">
-        <x:v>4000000000</x:v>
+        <x:v>2356546000</x:v>
       </x:c>
       <x:c r="F99" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G99" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H99" s="0">
-        <x:v>10581001663</x:v>
+        <x:v>7708004248</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>0.378</x:v>
+        <x:v>0.3057</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:9">
       <x:c r="A100" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B100" s="0">
-        <x:v>19.37</x:v>
+        <x:v>1172</x:v>
       </x:c>
       <x:c r="C100" s="0">
-        <x:v>-0.11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E100" s="0">
-        <x:v>1086598</x:v>
+        <x:v>875400</x:v>
       </x:c>
       <x:c r="F100" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G100" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H100" s="0">
-        <x:v>2020891371</x:v>
+        <x:v>1883544167</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>0.0274</x:v>
+        <x:v>0.0205</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:9">
       <x:c r="A101" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B101" s="0">
-        <x:v>16.98</x:v>
+        <x:v>26.34</x:v>
       </x:c>
       <x:c r="C101" s="0">
-        <x:v>0.18</x:v>
+        <x:v>-0.66</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E101" s="0">
-        <x:v>216000000</x:v>
+        <x:v>330000000</x:v>
       </x:c>
       <x:c r="F101" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G101" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H101" s="0">
-        <x:v>3025063909</x:v>
+        <x:v>5287314404</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>0.0714</x:v>
+        <x:v>0.0624</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:9">
       <x:c r="A102" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B102" s="0">
-        <x:v>58.7</x:v>
+        <x:v>95.2</x:v>
       </x:c>
       <x:c r="C102" s="0">
-        <x:v>1.45</x:v>
+        <x:v>8.65</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
         <x:v>89</x:v>
       </x:c>
       <x:c r="E102" s="0">
-        <x:v>7292916</x:v>
+        <x:v>11700000</x:v>
       </x:c>
       <x:c r="F102" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G102" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H102" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>0.0758</x:v>
+        <x:v>0.1705</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:9">
       <x:c r="A103" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B103" s="0">
-        <x:v>30.72</x:v>
+        <x:v>11.41</x:v>
       </x:c>
       <x:c r="C103" s="0">
-        <x:v>-0.4</x:v>
+        <x:v>0.77</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E103" s="0">
-        <x:v>250000</x:v>
+        <x:v>4000000000</x:v>
       </x:c>
       <x:c r="F103" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G103" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H103" s="0">
-        <x:v>448686813</x:v>
+        <x:v>10581001663</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>0.0006</x:v>
+        <x:v>0.378</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:9">
       <x:c r="A104" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B104" s="0">
-        <x:v>86.25</x:v>
+        <x:v>18.5</x:v>
       </x:c>
       <x:c r="C104" s="0">
-        <x:v>5.65</x:v>
+        <x:v>-0.87</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E104" s="0">
-        <x:v>36900000</x:v>
+        <x:v>1086598</x:v>
       </x:c>
       <x:c r="F104" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G104" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H104" s="0">
-        <x:v>10597063406</x:v>
+        <x:v>2020891371</x:v>
       </x:c>
       <x:c r="I104" s="0">
-        <x:v>0.1527</x:v>
+        <x:v>0.0274</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:9">
       <x:c r="A105" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B105" s="0">
-        <x:v>71.75</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C105" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>-0.98</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E105" s="0">
-        <x:v>3800000</x:v>
+        <x:v>216000000</x:v>
       </x:c>
       <x:c r="F105" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G105" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H105" s="0">
-        <x:v>832031190</x:v>
+        <x:v>3025063909</x:v>
       </x:c>
       <x:c r="I105" s="0">
-        <x:v>0.2002</x:v>
+        <x:v>0.0714</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:9">
       <x:c r="A106" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B106" s="0">
-        <x:v>6.12</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C106" s="0">
-        <x:v>0.12</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E106" s="0">
-        <x:v>2100000</x:v>
+        <x:v>7292916</x:v>
       </x:c>
       <x:c r="F106" s="0" t="s">
         <x:v>11</x:v>
@@ -3870,143 +3873,143 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H106" s="0">
-        <x:v>855070469</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>0.1076</x:v>
+        <x:v>0.0758</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:9">
       <x:c r="A107" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B107" s="0">
-        <x:v>58.7</x:v>
+        <x:v>30.7</x:v>
       </x:c>
       <x:c r="C107" s="0">
-        <x:v>1.45</x:v>
+        <x:v>-0.02</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E107" s="0">
-        <x:v>22928077</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="F107" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G107" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H107" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>448686813</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>0.2378</x:v>
+        <x:v>0.0006</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:9">
       <x:c r="A108" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B108" s="0">
-        <x:v>31.18</x:v>
+        <x:v>94.85</x:v>
       </x:c>
       <x:c r="C108" s="0">
-        <x:v>0.1</x:v>
+        <x:v>8.6</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E108" s="0">
-        <x:v>547462013</x:v>
+        <x:v>36900000</x:v>
       </x:c>
       <x:c r="F108" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G108" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H108" s="0">
-        <x:v>0</x:v>
+        <x:v>10597063406</x:v>
       </x:c>
       <x:c r="I108" s="0">
-        <x:v>0</x:v>
+        <x:v>0.1527</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:9">
       <x:c r="A109" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B109" s="0">
-        <x:v>31.18</x:v>
+        <x:v>66.5</x:v>
       </x:c>
       <x:c r="C109" s="0">
-        <x:v>0.1</x:v>
+        <x:v>-5.25</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
         <x:v>94</x:v>
       </x:c>
       <x:c r="E109" s="0">
-        <x:v>10567948</x:v>
+        <x:v>3800000</x:v>
       </x:c>
       <x:c r="F109" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G109" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H109" s="0">
-        <x:v>0</x:v>
+        <x:v>832031190</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>0</x:v>
+        <x:v>0.2002</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:9">
       <x:c r="A110" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B110" s="0">
-        <x:v>86.55</x:v>
+        <x:v>5.6</x:v>
       </x:c>
       <x:c r="C110" s="0">
-        <x:v>0.05</x:v>
+        <x:v>-0.52</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E110" s="0">
-        <x:v>8300000</x:v>
+        <x:v>2100000</x:v>
       </x:c>
       <x:c r="F110" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G110" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H110" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>855070469</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>0.1228</x:v>
+        <x:v>0.1076</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:9">
       <x:c r="A111" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B111" s="0">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="B111" s="0">
-        <x:v>61.35</x:v>
-      </x:c>
       <x:c r="C111" s="0">
-        <x:v>-0.05</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E111" s="0">
-        <x:v>3000000</x:v>
+        <x:v>22928077</x:v>
       </x:c>
       <x:c r="F111" s="0" t="s">
         <x:v>11</x:v>
@@ -4015,88 +4018,88 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H111" s="0">
-        <x:v>20597209000</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>0.0064</x:v>
+        <x:v>0.2378</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:9">
       <x:c r="A112" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B112" s="0">
-        <x:v>40.5</x:v>
+        <x:v>31.36</x:v>
       </x:c>
       <x:c r="C112" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E112" s="0">
-        <x:v>26640000</x:v>
+        <x:v>547462013</x:v>
       </x:c>
       <x:c r="F112" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G112" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H112" s="0">
-        <x:v>3277373640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I112" s="0">
-        <x:v>0.356</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:9">
       <x:c r="A113" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B113" s="0">
-        <x:v>6.62</x:v>
+        <x:v>31.36</x:v>
       </x:c>
       <x:c r="C113" s="0">
-        <x:v>0.32</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E113" s="0">
-        <x:v>13107198</x:v>
+        <x:v>10567948</x:v>
       </x:c>
       <x:c r="F113" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G113" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H113" s="0">
-        <x:v>1627872951</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I113" s="0">
-        <x:v>0.0081</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:9">
       <x:c r="A114" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B114" s="0">
-        <x:v>86.55</x:v>
+        <x:v>95.2</x:v>
       </x:c>
       <x:c r="C114" s="0">
-        <x:v>0.05</x:v>
+        <x:v>8.65</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E114" s="0">
-        <x:v>237500000</x:v>
+        <x:v>8300000</x:v>
       </x:c>
       <x:c r="F114" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G114" s="0">
         <x:v>2025.12</x:v>
@@ -4105,53 +4108,53 @@
         <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>0.0679</x:v>
+        <x:v>0.1228</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:9">
       <x:c r="A115" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B115" s="0">
-        <x:v>66</x:v>
+        <x:v>61.35</x:v>
       </x:c>
       <x:c r="C115" s="0">
-        <x:v>2.85</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E115" s="0">
-        <x:v>147892538</x:v>
+        <x:v>3000000</x:v>
       </x:c>
       <x:c r="F115" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G115" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H115" s="0">
-        <x:v>7257990064</x:v>
+        <x:v>20597209000</x:v>
       </x:c>
       <x:c r="I115" s="0">
-        <x:v>0.0204</x:v>
+        <x:v>0.0064</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:9">
       <x:c r="A116" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B116" s="0">
-        <x:v>57.65</x:v>
+        <x:v>38.66</x:v>
       </x:c>
       <x:c r="C116" s="0">
-        <x:v>-1.45</x:v>
+        <x:v>-1.84</x:v>
       </x:c>
       <x:c r="D116" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E116" s="0">
-        <x:v>988848</x:v>
+        <x:v>26640000</x:v>
       </x:c>
       <x:c r="F116" s="0" t="s">
         <x:v>11</x:v>
@@ -4160,462 +4163,462 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H116" s="0">
-        <x:v>12999679000</x:v>
+        <x:v>3277373640</x:v>
       </x:c>
       <x:c r="I116" s="0">
-        <x:v>0.0033</x:v>
+        <x:v>0.356</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:9">
       <x:c r="A117" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B117" s="0">
-        <x:v>86.25</x:v>
+        <x:v>6.55</x:v>
       </x:c>
       <x:c r="C117" s="0">
-        <x:v>5.65</x:v>
+        <x:v>-0.07</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E117" s="0">
-        <x:v>47300000</x:v>
+        <x:v>13107198</x:v>
       </x:c>
       <x:c r="F117" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G117" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H117" s="0">
-        <x:v>10597063406</x:v>
+        <x:v>1627872951</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>0.2309</x:v>
+        <x:v>0.0081</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:9">
       <x:c r="A118" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B118" s="0">
-        <x:v>4.28</x:v>
+        <x:v>95.2</x:v>
       </x:c>
       <x:c r="C118" s="0">
-        <x:v>0.12</x:v>
+        <x:v>8.65</x:v>
       </x:c>
       <x:c r="D118" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E118" s="0">
-        <x:v>758600</x:v>
+        <x:v>237500000</x:v>
       </x:c>
       <x:c r="F118" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G118" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H118" s="0">
-        <x:v>1960468575</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0.0679</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:9">
       <x:c r="A119" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B119" s="0">
-        <x:v>4.28</x:v>
+        <x:v>63.3</x:v>
       </x:c>
       <x:c r="C119" s="0">
-        <x:v>0.12</x:v>
+        <x:v>-2.7</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E119" s="0">
-        <x:v>758600</x:v>
+        <x:v>147892538</x:v>
       </x:c>
       <x:c r="F119" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G119" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H119" s="0">
-        <x:v>1960468575</x:v>
+        <x:v>7257990064</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>0.0004</x:v>
+        <x:v>0.0204</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:9">
       <x:c r="A120" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B120" s="0">
-        <x:v>1131</x:v>
+        <x:v>58.8</x:v>
       </x:c>
       <x:c r="C120" s="0">
-        <x:v>-69</x:v>
+        <x:v>1.15</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E120" s="0">
-        <x:v>576665</x:v>
+        <x:v>988848</x:v>
       </x:c>
       <x:c r="F120" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G120" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H120" s="0">
-        <x:v>1586603352</x:v>
+        <x:v>12999679000</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>0.0159</x:v>
+        <x:v>0.0033</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:9">
       <x:c r="A121" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B121" s="0">
-        <x:v>93.25</x:v>
+        <x:v>94.85</x:v>
       </x:c>
       <x:c r="C121" s="0">
-        <x:v>6.45</x:v>
+        <x:v>8.6</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E121" s="0">
-        <x:v>8000000</x:v>
+        <x:v>47300000</x:v>
       </x:c>
       <x:c r="F121" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G121" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H121" s="0">
-        <x:v>20999579110</x:v>
+        <x:v>10597063406</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>0.0166</x:v>
+        <x:v>0.2309</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:9">
       <x:c r="A122" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B122" s="0">
-        <x:v>99.5</x:v>
+        <x:v>4.11</x:v>
       </x:c>
       <x:c r="C122" s="0">
-        <x:v>1.3</x:v>
+        <x:v>-0.17</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E122" s="0">
-        <x:v>850000</x:v>
+        <x:v>758600</x:v>
       </x:c>
       <x:c r="F122" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G122" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H122" s="0">
-        <x:v>1781510191</x:v>
+        <x:v>1960468575</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>0.0208</x:v>
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:9">
       <x:c r="A123" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B123" s="0">
-        <x:v>19.37</x:v>
+        <x:v>4.11</x:v>
       </x:c>
       <x:c r="C123" s="0">
-        <x:v>-0.11</x:v>
+        <x:v>-0.17</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E123" s="0">
-        <x:v>10149200</x:v>
+        <x:v>758600</x:v>
       </x:c>
       <x:c r="F123" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G123" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H123" s="0">
-        <x:v>2020891371</x:v>
+        <x:v>1960468575</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>0.2601</x:v>
+        <x:v>0.0004</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:9">
       <x:c r="A124" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B124" s="0">
-        <x:v>146.5</x:v>
+        <x:v>1172</x:v>
       </x:c>
       <x:c r="C124" s="0">
-        <x:v>-4</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E124" s="0">
-        <x:v>10500000</x:v>
+        <x:v>576665</x:v>
       </x:c>
       <x:c r="F124" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G124" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H124" s="0">
-        <x:v>1742315226</x:v>
+        <x:v>1586603352</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>0.3121</x:v>
+        <x:v>0.0159</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:9">
       <x:c r="A125" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B125" s="0">
-        <x:v>99.5</x:v>
+        <x:v>88.15</x:v>
       </x:c>
       <x:c r="C125" s="0">
-        <x:v>1.3</x:v>
+        <x:v>-5.1</x:v>
       </x:c>
       <x:c r="D125" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E125" s="0">
-        <x:v>366956541</x:v>
+        <x:v>8000000</x:v>
       </x:c>
       <x:c r="F125" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G125" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H125" s="0">
-        <x:v>1781510191</x:v>
+        <x:v>20999579110</x:v>
       </x:c>
       <x:c r="I125" s="0">
-        <x:v>0.206</x:v>
+        <x:v>0.0166</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:9">
       <x:c r="A126" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B126" s="0">
-        <x:v>66</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C126" s="0">
-        <x:v>2.85</x:v>
+        <x:v>-5.5</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E126" s="0">
-        <x:v>61158155</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="F126" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G126" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H126" s="0">
-        <x:v>7257990064</x:v>
+        <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I126" s="0">
-        <x:v>0.0084</x:v>
+        <x:v>0.0208</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:9">
       <x:c r="A127" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B127" s="0">
-        <x:v>117.3</x:v>
+        <x:v>18.5</x:v>
       </x:c>
       <x:c r="C127" s="0">
-        <x:v>5.6</x:v>
+        <x:v>-0.87</x:v>
       </x:c>
       <x:c r="D127" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E127" s="0">
-        <x:v>1000000</x:v>
+        <x:v>10149200</x:v>
       </x:c>
       <x:c r="F127" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G127" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H127" s="0">
-        <x:v>1688731509</x:v>
+        <x:v>2020891371</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>0.0307</x:v>
+        <x:v>0.2601</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:9">
       <x:c r="A128" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B128" s="0">
-        <x:v>117.3</x:v>
+        <x:v>135.4</x:v>
       </x:c>
       <x:c r="C128" s="0">
-        <x:v>5.6</x:v>
+        <x:v>-11.1</x:v>
       </x:c>
       <x:c r="D128" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E128" s="0">
-        <x:v>1050000</x:v>
+        <x:v>10500000</x:v>
       </x:c>
       <x:c r="F128" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G128" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H128" s="0">
-        <x:v>1688731509</x:v>
+        <x:v>1742315226</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>0.0271</x:v>
+        <x:v>0.3121</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:9">
       <x:c r="A129" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B129" s="0">
-        <x:v>45</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C129" s="0">
-        <x:v>0.2</x:v>
+        <x:v>-5.5</x:v>
       </x:c>
       <x:c r="D129" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E129" s="0">
-        <x:v>109053804</x:v>
+        <x:v>366956541</x:v>
       </x:c>
       <x:c r="F129" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G129" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H129" s="0">
-        <x:v>1942491524</x:v>
+        <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>0.0561</x:v>
+        <x:v>0.206</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:9">
       <x:c r="A130" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B130" s="0">
-        <x:v>10.39</x:v>
+        <x:v>63.3</x:v>
       </x:c>
       <x:c r="C130" s="0">
-        <x:v>0</x:v>
+        <x:v>-2.7</x:v>
       </x:c>
       <x:c r="D130" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E130" s="0">
-        <x:v>62315119</x:v>
+        <x:v>61158155</x:v>
       </x:c>
       <x:c r="F130" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G130" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H130" s="0">
-        <x:v>12026414029</x:v>
+        <x:v>7257990064</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>0.2257</x:v>
+        <x:v>0.0084</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:9">
       <x:c r="A131" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B131" s="0">
-        <x:v>275</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C131" s="0">
-        <x:v>-13</x:v>
+        <x:v>7.7</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E131" s="0">
-        <x:v>896400</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="F131" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G131" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H131" s="0">
-        <x:v>1364716456</x:v>
+        <x:v>1688731509</x:v>
       </x:c>
       <x:c r="I131" s="0">
-        <x:v>0.0285</x:v>
+        <x:v>0.0307</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:9">
       <x:c r="A132" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B132" s="0">
-        <x:v>660.5</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C132" s="0">
-        <x:v>60</x:v>
+        <x:v>7.7</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E132" s="0">
-        <x:v>3370000</x:v>
+        <x:v>1050000</x:v>
       </x:c>
       <x:c r="F132" s="0" t="s">
         <x:v>11</x:v>
@@ -4624,56 +4627,56 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H132" s="0">
-        <x:v>1865697176</x:v>
+        <x:v>1688731509</x:v>
       </x:c>
       <x:c r="I132" s="0">
-        <x:v>0.0785</x:v>
+        <x:v>0.0271</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:9">
       <x:c r="A133" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B133" s="0">
-        <x:v>61.35</x:v>
+        <x:v>45.46</x:v>
       </x:c>
       <x:c r="C133" s="0">
-        <x:v>-0.05</x:v>
+        <x:v>0.46</x:v>
       </x:c>
       <x:c r="D133" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E133" s="0">
-        <x:v>750561215</x:v>
+        <x:v>109053804</x:v>
       </x:c>
       <x:c r="F133" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G133" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H133" s="0">
-        <x:v>16507905000</x:v>
+        <x:v>1942491524</x:v>
       </x:c>
       <x:c r="I133" s="0">
-        <x:v>0.0455</x:v>
+        <x:v>0.0561</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:9">
       <x:c r="A134" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B134" s="0">
-        <x:v>93.25</x:v>
+        <x:v>10.02</x:v>
       </x:c>
       <x:c r="C134" s="0">
-        <x:v>6.45</x:v>
+        <x:v>-0.37</x:v>
       </x:c>
       <x:c r="D134" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E134" s="0">
-        <x:v>20000000</x:v>
+        <x:v>62315119</x:v>
       </x:c>
       <x:c r="F134" s="0" t="s">
         <x:v>11</x:v>
@@ -4682,56 +4685,56 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H134" s="0">
-        <x:v>20999579110</x:v>
+        <x:v>12026414029</x:v>
       </x:c>
       <x:c r="I134" s="0">
-        <x:v>0.0413</x:v>
+        <x:v>0.2257</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:9">
       <x:c r="A135" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B135" s="0">
-        <x:v>36.66</x:v>
+        <x:v>269.5</x:v>
       </x:c>
       <x:c r="C135" s="0">
-        <x:v>-0.16</x:v>
+        <x:v>-5.5</x:v>
       </x:c>
       <x:c r="D135" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="E135" s="0">
-        <x:v>750000000</x:v>
+        <x:v>896400</x:v>
       </x:c>
       <x:c r="F135" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G135" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H135" s="0">
-        <x:v>0</x:v>
+        <x:v>1364716456</x:v>
       </x:c>
       <x:c r="I135" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0285</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:9">
       <x:c r="A136" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B136" s="0">
-        <x:v>86.25</x:v>
+        <x:v>726.5</x:v>
       </x:c>
       <x:c r="C136" s="0">
-        <x:v>5.65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E136" s="0">
-        <x:v>111232418</x:v>
+        <x:v>3370000</x:v>
       </x:c>
       <x:c r="F136" s="0" t="s">
         <x:v>11</x:v>
@@ -4740,56 +4743,56 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H136" s="0">
-        <x:v>10597063406</x:v>
+        <x:v>1865697176</x:v>
       </x:c>
       <x:c r="I136" s="0">
-        <x:v>0.4554</x:v>
+        <x:v>0.0785</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:9">
       <x:c r="A137" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B137" s="0">
-        <x:v>40</x:v>
+        <x:v>61.35</x:v>
       </x:c>
       <x:c r="C137" s="0">
-        <x:v>2.4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D137" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E137" s="0">
-        <x:v>51384996</x:v>
+        <x:v>750561215</x:v>
       </x:c>
       <x:c r="F137" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G137" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H137" s="0">
-        <x:v>11899043692</x:v>
+        <x:v>16507905000</x:v>
       </x:c>
       <x:c r="I137" s="0">
-        <x:v>0.1873</x:v>
+        <x:v>0.0455</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:9">
       <x:c r="A138" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B138" s="0">
-        <x:v>40</x:v>
+        <x:v>88.15</x:v>
       </x:c>
       <x:c r="C138" s="0">
-        <x:v>2.4</x:v>
+        <x:v>-5.1</x:v>
       </x:c>
       <x:c r="D138" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E138" s="0">
-        <x:v>3602451</x:v>
+        <x:v>20000000</x:v>
       </x:c>
       <x:c r="F138" s="0" t="s">
         <x:v>11</x:v>
@@ -4798,288 +4801,288 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H138" s="0">
-        <x:v>11899043692</x:v>
+        <x:v>20999579110</x:v>
       </x:c>
       <x:c r="I138" s="0">
-        <x:v>0.0131</x:v>
+        <x:v>0.0413</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:9">
       <x:c r="A139" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B139" s="0">
-        <x:v>40</x:v>
+        <x:v>35.76</x:v>
       </x:c>
       <x:c r="C139" s="0">
-        <x:v>2.4</x:v>
+        <x:v>-0.9</x:v>
       </x:c>
       <x:c r="D139" s="0" t="s">
         <x:v>119</x:v>
       </x:c>
       <x:c r="E139" s="0">
-        <x:v>24226465</x:v>
+        <x:v>750000000</x:v>
       </x:c>
       <x:c r="F139" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G139" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H139" s="0">
-        <x:v>11899043692</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I139" s="0">
-        <x:v>0.0883</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:9">
       <x:c r="A140" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B140" s="0">
-        <x:v>58.7</x:v>
+        <x:v>94.85</x:v>
       </x:c>
       <x:c r="C140" s="0">
-        <x:v>1.45</x:v>
+        <x:v>8.6</x:v>
       </x:c>
       <x:c r="D140" s="0" t="s">
         <x:v>119</x:v>
       </x:c>
       <x:c r="E140" s="0">
-        <x:v>12900000</x:v>
+        <x:v>111232418</x:v>
       </x:c>
       <x:c r="F140" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G140" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H140" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>10597063406</x:v>
       </x:c>
       <x:c r="I140" s="0">
-        <x:v>0.0052</x:v>
+        <x:v>0.4554</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:9">
       <x:c r="A141" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B141" s="0">
-        <x:v>339.5</x:v>
+        <x:v>40.2</x:v>
       </x:c>
       <x:c r="C141" s="0">
-        <x:v>13.5</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="D141" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E141" s="0">
-        <x:v>53250000</x:v>
+        <x:v>51384996</x:v>
       </x:c>
       <x:c r="F141" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G141" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H141" s="0">
-        <x:v>24073631758</x:v>
+        <x:v>11899043692</x:v>
       </x:c>
       <x:c r="I141" s="0">
-        <x:v>0.115</x:v>
+        <x:v>0.1873</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:9">
       <x:c r="A142" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B142" s="0">
-        <x:v>31.18</x:v>
+        <x:v>40.2</x:v>
       </x:c>
       <x:c r="C142" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="D142" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E142" s="0">
-        <x:v>6860140</x:v>
+        <x:v>3602451</x:v>
       </x:c>
       <x:c r="F142" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G142" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H142" s="0">
-        <x:v>0</x:v>
+        <x:v>11899043692</x:v>
       </x:c>
       <x:c r="I142" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0131</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:9">
       <x:c r="A143" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B143" s="0">
-        <x:v>86.55</x:v>
+        <x:v>40.2</x:v>
       </x:c>
       <x:c r="C143" s="0">
-        <x:v>0.05</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="D143" s="0" t="s">
         <x:v>120</x:v>
       </x:c>
       <x:c r="E143" s="0">
-        <x:v>230000000</x:v>
+        <x:v>24226465</x:v>
       </x:c>
       <x:c r="F143" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G143" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H143" s="0">
-        <x:v>2941310980</x:v>
+        <x:v>11899043692</x:v>
       </x:c>
       <x:c r="I143" s="0">
-        <x:v>0.0782</x:v>
+        <x:v>0.0883</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:9">
       <x:c r="A144" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B144" s="0">
-        <x:v>660.5</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C144" s="0">
-        <x:v>60</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D144" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E144" s="0">
-        <x:v>4700000</x:v>
+        <x:v>12900000</x:v>
       </x:c>
       <x:c r="F144" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G144" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H144" s="0">
-        <x:v>1865697176</x:v>
+        <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I144" s="0">
-        <x:v>0.1092</x:v>
+        <x:v>0.0052</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:9">
       <x:c r="A145" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B145" s="0">
-        <x:v>31.18</x:v>
+        <x:v>333.25</x:v>
       </x:c>
       <x:c r="C145" s="0">
-        <x:v>0.1</x:v>
+        <x:v>-6.25</x:v>
       </x:c>
       <x:c r="D145" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E145" s="0">
-        <x:v>256000000</x:v>
+        <x:v>53250000</x:v>
       </x:c>
       <x:c r="F145" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G145" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H145" s="0">
-        <x:v>0</x:v>
+        <x:v>24073631758</x:v>
       </x:c>
       <x:c r="I145" s="0">
-        <x:v>0</x:v>
+        <x:v>0.115</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:9">
       <x:c r="A146" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B146" s="0">
-        <x:v>40</x:v>
+        <x:v>31.36</x:v>
       </x:c>
       <x:c r="C146" s="0">
-        <x:v>2.4</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="D146" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E146" s="0">
-        <x:v>10724896</x:v>
+        <x:v>6860140</x:v>
       </x:c>
       <x:c r="F146" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G146" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H146" s="0">
-        <x:v>11899043692</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I146" s="0">
-        <x:v>0.039</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:9">
       <x:c r="A147" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B147" s="0">
-        <x:v>25.08</x:v>
+        <x:v>95.2</x:v>
       </x:c>
       <x:c r="C147" s="0">
-        <x:v>0.18</x:v>
+        <x:v>8.65</x:v>
       </x:c>
       <x:c r="D147" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E147" s="0">
-        <x:v>31000000</x:v>
+        <x:v>230000000</x:v>
       </x:c>
       <x:c r="F147" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G147" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H147" s="0">
-        <x:v>813967617</x:v>
+        <x:v>2941310980</x:v>
       </x:c>
       <x:c r="I147" s="0">
-        <x:v>0.0381</x:v>
+        <x:v>0.0782</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:9">
       <x:c r="A148" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B148" s="0">
-        <x:v>51.05</x:v>
+        <x:v>726.5</x:v>
       </x:c>
       <x:c r="C148" s="0">
-        <x:v>4.61</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D148" s="0" t="s">
         <x:v>122</x:v>
       </x:c>
       <x:c r="E148" s="0">
-        <x:v>13500000</x:v>
+        <x:v>4700000</x:v>
       </x:c>
       <x:c r="F148" s="0" t="s">
         <x:v>11</x:v>
@@ -5088,56 +5091,56 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H148" s="0">
-        <x:v>6483809984</x:v>
+        <x:v>1865697176</x:v>
       </x:c>
       <x:c r="I148" s="0">
-        <x:v>0.09</x:v>
+        <x:v>0.1092</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:9">
       <x:c r="A149" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B149" s="0">
-        <x:v>45</x:v>
+        <x:v>31.36</x:v>
       </x:c>
       <x:c r="C149" s="0">
-        <x:v>0.2</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="D149" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E149" s="0">
-        <x:v>29886357</x:v>
+        <x:v>256000000</x:v>
       </x:c>
       <x:c r="F149" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G149" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H149" s="0">
-        <x:v>1942491524</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I149" s="0">
-        <x:v>0.0154</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:9">
       <x:c r="A150" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B150" s="0">
-        <x:v>431.75</x:v>
+        <x:v>40.2</x:v>
       </x:c>
       <x:c r="C150" s="0">
-        <x:v>3.25</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="D150" s="0" t="s">
         <x:v>123</x:v>
       </x:c>
       <x:c r="E150" s="0">
-        <x:v>171000000</x:v>
+        <x:v>10724896</x:v>
       </x:c>
       <x:c r="F150" s="0" t="s">
         <x:v>11</x:v>
@@ -5146,56 +5149,56 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H150" s="0">
-        <x:v>130147715000</x:v>
+        <x:v>11899043692</x:v>
       </x:c>
       <x:c r="I150" s="0">
-        <x:v>0.0568</x:v>
+        <x:v>0.039</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:9">
       <x:c r="A151" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B151" s="0">
-        <x:v>146.5</x:v>
+        <x:v>25.32</x:v>
       </x:c>
       <x:c r="C151" s="0">
-        <x:v>-4</x:v>
+        <x:v>0.24</x:v>
       </x:c>
       <x:c r="D151" s="0" t="s">
         <x:v>123</x:v>
       </x:c>
       <x:c r="E151" s="0">
-        <x:v>1890000</x:v>
+        <x:v>31000000</x:v>
       </x:c>
       <x:c r="F151" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G151" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H151" s="0">
-        <x:v>1742315226</x:v>
+        <x:v>813967617</x:v>
       </x:c>
       <x:c r="I151" s="0">
-        <x:v>0.0549</x:v>
+        <x:v>0.0381</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:9">
       <x:c r="A152" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B152" s="0">
-        <x:v>13.94</x:v>
+        <x:v>50.25</x:v>
       </x:c>
       <x:c r="C152" s="0">
-        <x:v>-0.16</x:v>
+        <x:v>-0.8</x:v>
       </x:c>
       <x:c r="D152" s="0" t="s">
         <x:v>123</x:v>
       </x:c>
       <x:c r="E152" s="0">
-        <x:v>892825</x:v>
+        <x:v>13500000</x:v>
       </x:c>
       <x:c r="F152" s="0" t="s">
         <x:v>11</x:v>
@@ -5204,56 +5207,56 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H152" s="0">
-        <x:v>3015442704</x:v>
+        <x:v>6483809984</x:v>
       </x:c>
       <x:c r="I152" s="0">
-        <x:v>0.0128</x:v>
+        <x:v>0.09</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:9">
       <x:c r="A153" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B153" s="0">
-        <x:v>58.7</x:v>
+        <x:v>45.46</x:v>
       </x:c>
       <x:c r="C153" s="0">
-        <x:v>1.45</x:v>
+        <x:v>0.46</x:v>
       </x:c>
       <x:c r="D153" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E153" s="0">
-        <x:v>361176</x:v>
+        <x:v>29886357</x:v>
       </x:c>
       <x:c r="F153" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G153" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H153" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>1942491524</x:v>
       </x:c>
       <x:c r="I153" s="0">
-        <x:v>0.0063</x:v>
+        <x:v>0.0154</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:9">
       <x:c r="A154" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B154" s="0">
-        <x:v>26.04</x:v>
+        <x:v>419.25</x:v>
       </x:c>
       <x:c r="C154" s="0">
-        <x:v>0.12</x:v>
+        <x:v>-12.5</x:v>
       </x:c>
       <x:c r="D154" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E154" s="0">
-        <x:v>1060000</x:v>
+        <x:v>171000000</x:v>
       </x:c>
       <x:c r="F154" s="0" t="s">
         <x:v>11</x:v>
@@ -5262,56 +5265,56 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H154" s="0">
-        <x:v>1194839266</x:v>
+        <x:v>130147715000</x:v>
       </x:c>
       <x:c r="I154" s="0">
-        <x:v>0.0384</x:v>
+        <x:v>0.0568</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:9">
       <x:c r="A155" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B155" s="0">
-        <x:v>53.1</x:v>
+        <x:v>135.4</x:v>
       </x:c>
       <x:c r="C155" s="0">
-        <x:v>-0.95</x:v>
+        <x:v>-11.1</x:v>
       </x:c>
       <x:c r="D155" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E155" s="0">
-        <x:v>259417800</x:v>
+        <x:v>1890000</x:v>
       </x:c>
       <x:c r="F155" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G155" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H155" s="0">
-        <x:v>2741117556</x:v>
+        <x:v>1742315226</x:v>
       </x:c>
       <x:c r="I155" s="0">
-        <x:v>0.0946</x:v>
+        <x:v>0.0549</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:9">
       <x:c r="A156" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B156" s="0">
-        <x:v>71.75</x:v>
+        <x:v>13.59</x:v>
       </x:c>
       <x:c r="C156" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>-0.35</x:v>
       </x:c>
       <x:c r="D156" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E156" s="0">
-        <x:v>523788</x:v>
+        <x:v>892825</x:v>
       </x:c>
       <x:c r="F156" s="0" t="s">
         <x:v>11</x:v>
@@ -5320,27 +5323,27 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H156" s="0">
-        <x:v>832031190</x:v>
+        <x:v>3015442704</x:v>
       </x:c>
       <x:c r="I156" s="0">
-        <x:v>0.0272</x:v>
+        <x:v>0.0128</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:9">
       <x:c r="A157" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B157" s="0">
-        <x:v>71.75</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C157" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D157" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E157" s="0">
-        <x:v>1415270</x:v>
+        <x:v>361176</x:v>
       </x:c>
       <x:c r="F157" s="0" t="s">
         <x:v>11</x:v>
@@ -5349,27 +5352,27 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H157" s="0">
-        <x:v>832031190</x:v>
+        <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I157" s="0">
-        <x:v>0.0736</x:v>
+        <x:v>0.0063</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:9">
       <x:c r="A158" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B158" s="0">
-        <x:v>93.25</x:v>
+        <x:v>24.8</x:v>
       </x:c>
       <x:c r="C158" s="0">
-        <x:v>6.45</x:v>
+        <x:v>-1.24</x:v>
       </x:c>
       <x:c r="D158" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="E158" s="0">
-        <x:v>25000000</x:v>
+        <x:v>1060000</x:v>
       </x:c>
       <x:c r="F158" s="0" t="s">
         <x:v>11</x:v>
@@ -5378,114 +5381,114 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H158" s="0">
-        <x:v>20999579110</x:v>
+        <x:v>1194839266</x:v>
       </x:c>
       <x:c r="I158" s="0">
-        <x:v>0.0515</x:v>
+        <x:v>0.0384</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:9">
       <x:c r="A159" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B159" s="0">
-        <x:v>6.62</x:v>
+        <x:v>52.35</x:v>
       </x:c>
       <x:c r="C159" s="0">
-        <x:v>0.32</x:v>
+        <x:v>-0.75</x:v>
       </x:c>
       <x:c r="D159" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="E159" s="0">
-        <x:v>25000</x:v>
+        <x:v>259417800</x:v>
       </x:c>
       <x:c r="F159" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G159" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H159" s="0">
-        <x:v>1627872951</x:v>
+        <x:v>2741117556</x:v>
       </x:c>
       <x:c r="I159" s="0">
-        <x:v>0.0007</x:v>
+        <x:v>0.0946</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:9">
       <x:c r="A160" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B160" s="0">
-        <x:v>21.62</x:v>
+        <x:v>66.5</x:v>
       </x:c>
       <x:c r="C160" s="0">
-        <x:v>-0.1</x:v>
+        <x:v>-5.25</x:v>
       </x:c>
       <x:c r="D160" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="E160" s="0">
-        <x:v>1500000</x:v>
+        <x:v>523788</x:v>
       </x:c>
       <x:c r="F160" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G160" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H160" s="0">
-        <x:v>774677961</x:v>
+        <x:v>832031190</x:v>
       </x:c>
       <x:c r="I160" s="0">
-        <x:v>0.0019</x:v>
+        <x:v>0.0272</x:v>
       </x:c>
     </x:row>
     <x:row r="161" spans="1:9">
       <x:c r="A161" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B161" s="0">
-        <x:v>10.64</x:v>
+        <x:v>66.5</x:v>
       </x:c>
       <x:c r="C161" s="0">
-        <x:v>0.96</x:v>
+        <x:v>-5.25</x:v>
       </x:c>
       <x:c r="D161" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="E161" s="0">
-        <x:v>13833310</x:v>
+        <x:v>1415270</x:v>
       </x:c>
       <x:c r="F161" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G161" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H161" s="0">
-        <x:v>9028523851</x:v>
+        <x:v>832031190</x:v>
       </x:c>
       <x:c r="I161" s="0">
-        <x:v>0.0776</x:v>
+        <x:v>0.0736</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:9">
       <x:c r="A162" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B162" s="0">
-        <x:v>76.5</x:v>
+        <x:v>88.15</x:v>
       </x:c>
       <x:c r="C162" s="0">
-        <x:v>-0.35</x:v>
+        <x:v>-5.1</x:v>
       </x:c>
       <x:c r="D162" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="E162" s="0">
-        <x:v>3419000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="F162" s="0" t="s">
         <x:v>11</x:v>
@@ -5494,27 +5497,27 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H162" s="0">
-        <x:v>3895315496</x:v>
+        <x:v>20999579110</x:v>
       </x:c>
       <x:c r="I162" s="0">
-        <x:v>0.0379</x:v>
+        <x:v>0.0515</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:9">
       <x:c r="A163" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B163" s="0">
-        <x:v>660.5</x:v>
+        <x:v>6.55</x:v>
       </x:c>
       <x:c r="C163" s="0">
-        <x:v>60</x:v>
+        <x:v>-0.07</x:v>
       </x:c>
       <x:c r="D163" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="E163" s="0">
-        <x:v>3700000</x:v>
+        <x:v>25000</x:v>
       </x:c>
       <x:c r="F163" s="0" t="s">
         <x:v>11</x:v>
@@ -5523,143 +5526,143 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H163" s="0">
-        <x:v>1865697176</x:v>
+        <x:v>1627872951</x:v>
       </x:c>
       <x:c r="I163" s="0">
-        <x:v>0.0857</x:v>
+        <x:v>0.0007</x:v>
       </x:c>
     </x:row>
     <x:row r="164" spans="1:9">
       <x:c r="A164" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B164" s="0">
-        <x:v>51.05</x:v>
+        <x:v>23.26</x:v>
       </x:c>
       <x:c r="C164" s="0">
-        <x:v>4.61</x:v>
+        <x:v>1.64</x:v>
       </x:c>
       <x:c r="D164" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="E164" s="0">
-        <x:v>16000000</x:v>
+        <x:v>1500000</x:v>
       </x:c>
       <x:c r="F164" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G164" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H164" s="0">
-        <x:v>6483809984</x:v>
+        <x:v>774677961</x:v>
       </x:c>
       <x:c r="I164" s="0">
-        <x:v>0.1067</x:v>
+        <x:v>0.0019</x:v>
       </x:c>
     </x:row>
     <x:row r="165" spans="1:9">
       <x:c r="A165" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B165" s="0">
-        <x:v>58.7</x:v>
+        <x:v>11.41</x:v>
       </x:c>
       <x:c r="C165" s="0">
-        <x:v>1.45</x:v>
+        <x:v>0.77</x:v>
       </x:c>
       <x:c r="D165" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="E165" s="0">
-        <x:v>906840</x:v>
+        <x:v>13833310</x:v>
       </x:c>
       <x:c r="F165" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G165" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H165" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>9028523851</x:v>
       </x:c>
       <x:c r="I165" s="0">
-        <x:v>0.0159</x:v>
+        <x:v>0.0776</x:v>
       </x:c>
     </x:row>
     <x:row r="166" spans="1:9">
       <x:c r="A166" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B166" s="0">
-        <x:v>3.51</x:v>
+        <x:v>76.8</x:v>
       </x:c>
       <x:c r="C166" s="0">
-        <x:v>0.1</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D166" s="0" t="s">
         <x:v>131</x:v>
       </x:c>
       <x:c r="E166" s="0">
-        <x:v>895039950</x:v>
+        <x:v>3419000</x:v>
       </x:c>
       <x:c r="F166" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G166" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H166" s="0">
-        <x:v>7382591324</x:v>
+        <x:v>3895315496</x:v>
       </x:c>
       <x:c r="I166" s="0">
-        <x:v>0.1212</x:v>
+        <x:v>0.0379</x:v>
       </x:c>
     </x:row>
     <x:row r="167" spans="1:9">
       <x:c r="A167" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B167" s="0">
-        <x:v>53.1</x:v>
+        <x:v>726.5</x:v>
       </x:c>
       <x:c r="C167" s="0">
-        <x:v>-0.95</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D167" s="0" t="s">
         <x:v>131</x:v>
       </x:c>
       <x:c r="E167" s="0">
-        <x:v>575933040</x:v>
+        <x:v>3700000</x:v>
       </x:c>
       <x:c r="F167" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G167" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H167" s="0">
-        <x:v>2741117556</x:v>
+        <x:v>1865697176</x:v>
       </x:c>
       <x:c r="I167" s="0">
-        <x:v>0.2101</x:v>
+        <x:v>0.0857</x:v>
       </x:c>
     </x:row>
     <x:row r="168" spans="1:9">
       <x:c r="A168" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B168" s="0">
-        <x:v>13.01</x:v>
+        <x:v>50.25</x:v>
       </x:c>
       <x:c r="C168" s="0">
-        <x:v>0.06</x:v>
+        <x:v>-0.8</x:v>
       </x:c>
       <x:c r="D168" s="0" t="s">
         <x:v>131</x:v>
       </x:c>
       <x:c r="E168" s="0">
-        <x:v>559000</x:v>
+        <x:v>16000000</x:v>
       </x:c>
       <x:c r="F168" s="0" t="s">
         <x:v>11</x:v>
@@ -5668,27 +5671,27 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H168" s="0">
-        <x:v>2865374550</x:v>
+        <x:v>6483809984</x:v>
       </x:c>
       <x:c r="I168" s="0">
-        <x:v>0.0084</x:v>
+        <x:v>0.1067</x:v>
       </x:c>
     </x:row>
     <x:row r="169" spans="1:9">
       <x:c r="A169" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B169" s="0">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="B169" s="0">
-        <x:v>61.35</x:v>
-      </x:c>
       <x:c r="C169" s="0">
-        <x:v>-0.05</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D169" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="E169" s="0">
-        <x:v>8900056</x:v>
+        <x:v>906840</x:v>
       </x:c>
       <x:c r="F169" s="0" t="s">
         <x:v>11</x:v>
@@ -5697,114 +5700,114 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H169" s="0">
-        <x:v>16507905000</x:v>
+        <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I169" s="0">
-        <x:v>0.0233</x:v>
+        <x:v>0.0159</x:v>
       </x:c>
     </x:row>
     <x:row r="170" spans="1:9">
       <x:c r="A170" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B170" s="0">
-        <x:v>339.5</x:v>
+        <x:v>3.56</x:v>
       </x:c>
       <x:c r="C170" s="0">
-        <x:v>13.5</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D170" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="E170" s="0">
-        <x:v>164306000</x:v>
+        <x:v>895039950</x:v>
       </x:c>
       <x:c r="F170" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G170" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H170" s="0">
-        <x:v>24073631758</x:v>
+        <x:v>7382591324</x:v>
       </x:c>
       <x:c r="I170" s="0">
-        <x:v>0.2943</x:v>
+        <x:v>0.1212</x:v>
       </x:c>
     </x:row>
     <x:row r="171" spans="1:9">
       <x:c r="A171" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B171" s="0">
-        <x:v>54.3</x:v>
+        <x:v>52.35</x:v>
       </x:c>
       <x:c r="C171" s="0">
-        <x:v>-0.45</x:v>
+        <x:v>-0.75</x:v>
       </x:c>
       <x:c r="D171" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="E171" s="0">
-        <x:v>275000</x:v>
+        <x:v>575933040</x:v>
       </x:c>
       <x:c r="F171" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G171" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H171" s="0">
-        <x:v>580678850</x:v>
+        <x:v>2741117556</x:v>
       </x:c>
       <x:c r="I171" s="0">
-        <x:v>0.0204</x:v>
+        <x:v>0.2101</x:v>
       </x:c>
     </x:row>
     <x:row r="172" spans="1:9">
       <x:c r="A172" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B172" s="0">
-        <x:v>53.1</x:v>
+        <x:v>12.77</x:v>
       </x:c>
       <x:c r="C172" s="0">
-        <x:v>-0.95</x:v>
+        <x:v>-0.24</x:v>
       </x:c>
       <x:c r="D172" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="E172" s="0">
-        <x:v>231651480</x:v>
+        <x:v>559000</x:v>
       </x:c>
       <x:c r="F172" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G172" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H172" s="0">
-        <x:v>2741117556</x:v>
+        <x:v>2865374550</x:v>
       </x:c>
       <x:c r="I172" s="0">
-        <x:v>0.0845</x:v>
+        <x:v>0.0084</x:v>
       </x:c>
     </x:row>
     <x:row r="173" spans="1:9">
       <x:c r="A173" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B173" s="0">
-        <x:v>16.98</x:v>
+        <x:v>61.35</x:v>
       </x:c>
       <x:c r="C173" s="0">
-        <x:v>0.18</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D173" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="E173" s="0">
-        <x:v>31860000</x:v>
+        <x:v>8900056</x:v>
       </x:c>
       <x:c r="F173" s="0" t="s">
         <x:v>11</x:v>
@@ -5813,288 +5816,288 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H173" s="0">
-        <x:v>3025063909</x:v>
+        <x:v>16507905000</x:v>
       </x:c>
       <x:c r="I173" s="0">
-        <x:v>0.4539</x:v>
+        <x:v>0.0233</x:v>
       </x:c>
     </x:row>
     <x:row r="174" spans="1:9">
       <x:c r="A174" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B174" s="0">
-        <x:v>99.5</x:v>
+        <x:v>333.25</x:v>
       </x:c>
       <x:c r="C174" s="0">
-        <x:v>1.3</x:v>
+        <x:v>-6.25</x:v>
       </x:c>
       <x:c r="D174" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="E174" s="0">
-        <x:v>41650000</x:v>
+        <x:v>164306000</x:v>
       </x:c>
       <x:c r="F174" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G174" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H174" s="0">
-        <x:v>1781510191</x:v>
+        <x:v>24073631758</x:v>
       </x:c>
       <x:c r="I174" s="0">
-        <x:v>0.0234</x:v>
+        <x:v>0.2943</x:v>
       </x:c>
     </x:row>
     <x:row r="175" spans="1:9">
       <x:c r="A175" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B175" s="0">
-        <x:v>19.37</x:v>
+        <x:v>52.5</x:v>
       </x:c>
       <x:c r="C175" s="0">
-        <x:v>-0.11</x:v>
+        <x:v>-1.8</x:v>
       </x:c>
       <x:c r="D175" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="E175" s="0">
-        <x:v>815000</x:v>
+        <x:v>275000</x:v>
       </x:c>
       <x:c r="F175" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G175" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H175" s="0">
-        <x:v>2020891371</x:v>
+        <x:v>580678850</x:v>
       </x:c>
       <x:c r="I175" s="0">
-        <x:v>0.0202</x:v>
+        <x:v>0.0204</x:v>
       </x:c>
     </x:row>
     <x:row r="176" spans="1:9">
       <x:c r="A176" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B176" s="0">
-        <x:v>86.55</x:v>
+        <x:v>52.35</x:v>
       </x:c>
       <x:c r="C176" s="0">
-        <x:v>0.05</x:v>
+        <x:v>-0.75</x:v>
       </x:c>
       <x:c r="D176" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="E176" s="0">
-        <x:v>8300000</x:v>
+        <x:v>231651480</x:v>
       </x:c>
       <x:c r="F176" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G176" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H176" s="0">
-        <x:v>2941310980</x:v>
+        <x:v>2741117556</x:v>
       </x:c>
       <x:c r="I176" s="0">
-        <x:v>0.1417</x:v>
+        <x:v>0.0845</x:v>
       </x:c>
     </x:row>
     <x:row r="177" spans="1:9">
       <x:c r="A177" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B177" s="0">
-        <x:v>4.45</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C177" s="0">
-        <x:v>0.05</x:v>
+        <x:v>-0.98</x:v>
       </x:c>
       <x:c r="D177" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="E177" s="0">
-        <x:v>13000000</x:v>
+        <x:v>31860000</x:v>
       </x:c>
       <x:c r="F177" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G177" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H177" s="0">
-        <x:v>1416740879</x:v>
+        <x:v>3025063909</x:v>
       </x:c>
       <x:c r="I177" s="0">
-        <x:v>0.4613</x:v>
+        <x:v>0.4539</x:v>
       </x:c>
     </x:row>
     <x:row r="178" spans="1:9">
       <x:c r="A178" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B178" s="0">
-        <x:v>146.5</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C178" s="0">
-        <x:v>-4</x:v>
+        <x:v>-5.5</x:v>
       </x:c>
       <x:c r="D178" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="E178" s="0">
-        <x:v>1999793</x:v>
+        <x:v>41650000</x:v>
       </x:c>
       <x:c r="F178" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G178" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H178" s="0">
-        <x:v>1742315226</x:v>
+        <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I178" s="0">
-        <x:v>0.0494</x:v>
+        <x:v>0.0234</x:v>
       </x:c>
     </x:row>
     <x:row r="179" spans="1:9">
       <x:c r="A179" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B179" s="0">
-        <x:v>58.7</x:v>
+        <x:v>18.5</x:v>
       </x:c>
       <x:c r="C179" s="0">
-        <x:v>1.45</x:v>
+        <x:v>-0.87</x:v>
       </x:c>
       <x:c r="D179" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="E179" s="0">
-        <x:v>1859145</x:v>
+        <x:v>815000</x:v>
       </x:c>
       <x:c r="F179" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G179" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H179" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>2020891371</x:v>
       </x:c>
       <x:c r="I179" s="0">
-        <x:v>0.0324</x:v>
+        <x:v>0.0202</x:v>
       </x:c>
     </x:row>
     <x:row r="180" spans="1:9">
       <x:c r="A180" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B180" s="0">
-        <x:v>3.51</x:v>
+        <x:v>95.2</x:v>
       </x:c>
       <x:c r="C180" s="0">
-        <x:v>0.1</x:v>
+        <x:v>8.65</x:v>
       </x:c>
       <x:c r="D180" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="E180" s="0">
-        <x:v>689661000</x:v>
+        <x:v>8300000</x:v>
       </x:c>
       <x:c r="F180" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G180" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H180" s="0">
-        <x:v>7382591324</x:v>
+        <x:v>2941310980</x:v>
       </x:c>
       <x:c r="I180" s="0">
-        <x:v>0.0934</x:v>
+        <x:v>0.1417</x:v>
       </x:c>
     </x:row>
     <x:row r="181" spans="1:9">
       <x:c r="A181" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B181" s="0">
-        <x:v>58.7</x:v>
+        <x:v>4.39</x:v>
       </x:c>
       <x:c r="C181" s="0">
-        <x:v>1.45</x:v>
+        <x:v>-0.06</x:v>
       </x:c>
       <x:c r="D181" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="E181" s="0">
-        <x:v>1902000</x:v>
+        <x:v>13000000</x:v>
       </x:c>
       <x:c r="F181" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G181" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H181" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>1416740879</x:v>
       </x:c>
       <x:c r="I181" s="0">
-        <x:v>0</x:v>
+        <x:v>0.4613</x:v>
       </x:c>
     </x:row>
     <x:row r="182" spans="1:9">
       <x:c r="A182" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B182" s="0">
-        <x:v>99.5</x:v>
+        <x:v>135.4</x:v>
       </x:c>
       <x:c r="C182" s="0">
-        <x:v>1.3</x:v>
+        <x:v>-11.1</x:v>
       </x:c>
       <x:c r="D182" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="E182" s="0">
-        <x:v>56520000</x:v>
+        <x:v>1999793</x:v>
       </x:c>
       <x:c r="F182" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G182" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H182" s="0">
-        <x:v>1781510191</x:v>
+        <x:v>1742315226</x:v>
       </x:c>
       <x:c r="I182" s="0">
-        <x:v>0.0317</x:v>
+        <x:v>0.0494</x:v>
       </x:c>
     </x:row>
     <x:row r="183" spans="1:9">
       <x:c r="A183" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B183" s="0">
-        <x:v>99.5</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C183" s="0">
-        <x:v>1.3</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D183" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="E183" s="0">
-        <x:v>888325</x:v>
+        <x:v>1859145</x:v>
       </x:c>
       <x:c r="F183" s="0" t="s">
         <x:v>11</x:v>
@@ -6103,59 +6106,59 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H183" s="0">
-        <x:v>1781510191</x:v>
+        <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I183" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0324</x:v>
       </x:c>
     </x:row>
     <x:row r="184" spans="1:9">
       <x:c r="A184" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B184" s="0">
-        <x:v>10.64</x:v>
+        <x:v>3.56</x:v>
       </x:c>
       <x:c r="C184" s="0">
-        <x:v>0.96</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D184" s="0" t="s">
         <x:v>143</x:v>
       </x:c>
       <x:c r="E184" s="0">
-        <x:v>5581810</x:v>
+        <x:v>689661000</x:v>
       </x:c>
       <x:c r="F184" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G184" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H184" s="0">
-        <x:v>9028523851</x:v>
+        <x:v>7382591324</x:v>
       </x:c>
       <x:c r="I184" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0934</x:v>
       </x:c>
     </x:row>
     <x:row r="185" spans="1:9">
       <x:c r="A185" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B185" s="0">
-        <x:v>58.7</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C185" s="0">
-        <x:v>1.45</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D185" s="0" t="s">
         <x:v>144</x:v>
       </x:c>
       <x:c r="E185" s="0">
-        <x:v>504000000</x:v>
+        <x:v>1902000</x:v>
       </x:c>
       <x:c r="F185" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G185" s="0">
         <x:v>2025.09</x:v>
@@ -6164,64 +6167,180 @@
         <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I185" s="0">
-        <x:v>0.2043</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="186" spans="1:9">
       <x:c r="A186" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B186" s="0">
-        <x:v>339.5</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C186" s="0">
-        <x:v>13.5</x:v>
+        <x:v>-5.5</x:v>
       </x:c>
       <x:c r="D186" s="0" t="s">
         <x:v>144</x:v>
       </x:c>
       <x:c r="E186" s="0">
-        <x:v>21500032</x:v>
+        <x:v>56520000</x:v>
       </x:c>
       <x:c r="F186" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G186" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H186" s="0">
-        <x:v>24073631758</x:v>
+        <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I186" s="0">
-        <x:v>0.0383</x:v>
+        <x:v>0.0317</x:v>
       </x:c>
     </x:row>
     <x:row r="187" spans="1:9">
       <x:c r="A187" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B187" s="0">
-        <x:v>1131</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C187" s="0">
-        <x:v>-69</x:v>
+        <x:v>-5.5</x:v>
       </x:c>
       <x:c r="D187" s="0" t="s">
         <x:v>144</x:v>
       </x:c>
       <x:c r="E187" s="0">
+        <x:v>888325</x:v>
+      </x:c>
+      <x:c r="F187" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G187" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H187" s="0">
+        <x:v>1781510191</x:v>
+      </x:c>
+      <x:c r="I187" s="0">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188" spans="1:9">
+      <x:c r="A188" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B188" s="0">
+        <x:v>11.41</x:v>
+      </x:c>
+      <x:c r="C188" s="0">
+        <x:v>0.77</x:v>
+      </x:c>
+      <x:c r="D188" s="0" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="E188" s="0">
+        <x:v>5581810</x:v>
+      </x:c>
+      <x:c r="F188" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G188" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H188" s="0">
+        <x:v>9028523851</x:v>
+      </x:c>
+      <x:c r="I188" s="0">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189" spans="1:9">
+      <x:c r="A189" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B189" s="0">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C189" s="0">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="D189" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E189" s="0">
+        <x:v>504000000</x:v>
+      </x:c>
+      <x:c r="F189" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G189" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H189" s="0">
+        <x:v>2467243928</x:v>
+      </x:c>
+      <x:c r="I189" s="0">
+        <x:v>0.2043</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190" spans="1:9">
+      <x:c r="A190" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B190" s="0">
+        <x:v>333.25</x:v>
+      </x:c>
+      <x:c r="C190" s="0">
+        <x:v>-6.25</x:v>
+      </x:c>
+      <x:c r="D190" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E190" s="0">
+        <x:v>21500032</x:v>
+      </x:c>
+      <x:c r="F190" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G190" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H190" s="0">
+        <x:v>24073631758</x:v>
+      </x:c>
+      <x:c r="I190" s="0">
+        <x:v>0.0383</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191" spans="1:9">
+      <x:c r="A191" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B191" s="0">
+        <x:v>1172</x:v>
+      </x:c>
+      <x:c r="C191" s="0">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D191" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="E191" s="0">
         <x:v>6455151</x:v>
       </x:c>
-      <x:c r="F187" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G187" s="0">
-        <x:v>2025.09</x:v>
-      </x:c>
-      <x:c r="H187" s="0">
+      <x:c r="F191" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G191" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H191" s="0">
         <x:v>1586603352</x:v>
       </x:c>
-      <x:c r="I187" s="0">
+      <x:c r="I191" s="0">
         <x:v>0.1745</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/yeni-is-anlasmalari/data/yeni-is-anlasmalari.xlsx
+++ b/app/borsa/yeni-is-anlasmalari/data/yeni-is-anlasmalari.xlsx
@@ -46,13 +46,16 @@
     <x:t>SDTTR</x:t>
   </x:si>
   <x:si>
+    <x:t>2026-05-13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>USD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YEOTK</x:t>
+  </x:si>
+  <x:si>
     <x:t>2026-05-12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>USD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YEOTK</x:t>
   </x:si>
   <x:si>
     <x:t>SMRTG</x:t>
@@ -802,7 +805,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I191"/>
+  <x:dimension ref="A1:I193"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -839,16 +842,16 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>269.5</x:v>
+        <x:v>274.5</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>-5.5</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>4950000</x:v>
+        <x:v>6450000</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
         <x:v>11</x:v>
@@ -860,7 +863,7 @@
         <x:v>2443327017</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>0.0916</x:v>
+        <x:v>0.1197</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -868,16 +871,16 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>94.85</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>8.6</x:v>
+        <x:v>5.15</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>1950000</x:v>
+        <x:v>16093186</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
         <x:v>11</x:v>
@@ -889,24 +892,24 @@
         <x:v>18658831210</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>0.0047</x:v>
+        <x:v>0.0391</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
       <x:c r="A4" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B4" s="0">
+        <x:v>274.5</x:v>
+      </x:c>
+      <x:c r="C4" s="0">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B4" s="0">
-        <x:v>11.41</x:v>
-      </x:c>
-      <x:c r="C4" s="0">
-        <x:v>0.77</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
       <x:c r="E4" s="0">
-        <x:v>10201876</x:v>
+        <x:v>4950000</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
         <x:v>11</x:v>
@@ -915,27 +918,27 @@
         <x:v>2026.03</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>9721975029</x:v>
+        <x:v>2443327017</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>0.0474</x:v>
+        <x:v>0.0916</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
       <x:c r="A5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>28.78</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>-0.58</x:v>
+        <x:v>5.15</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>459000</x:v>
+        <x:v>1950000</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
         <x:v>11</x:v>
@@ -944,27 +947,27 @@
         <x:v>2026.03</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>7727514294</x:v>
+        <x:v>18658831210</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>0.0027</x:v>
+        <x:v>0.0047</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
       <x:c r="A6" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>30.7</x:v>
+        <x:v>12.55</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>1.14</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>17776799</x:v>
+        <x:v>10201876</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
         <x:v>11</x:v>
@@ -973,85 +976,85 @@
         <x:v>2026.03</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>433239437</x:v>
+        <x:v>9721975029</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>1.8545</x:v>
+        <x:v>0.0474</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
       <x:c r="A7" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>23.5</x:v>
+        <x:v>28.06</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>-1.18</x:v>
+        <x:v>-0.72</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>1816317</x:v>
+        <x:v>459000</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2026.03</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>2427624044</x:v>
+        <x:v>7727514294</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>0.0338</x:v>
+        <x:v>0.0027</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
       <x:c r="A8" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>94</x:v>
+        <x:v>29.82</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>-5.5</x:v>
+        <x:v>-0.88</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>3384000</x:v>
+        <x:v>17776799</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2026.03</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>433239437</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>0.0627</x:v>
+        <x:v>1.8545</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
       <x:c r="A9" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>4.11</x:v>
+        <x:v>22.8</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>-0.17</x:v>
+        <x:v>-0.7</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>1178000</x:v>
+        <x:v>1816317</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
         <x:v>11</x:v>
@@ -1060,56 +1063,56 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>2875634546</x:v>
+        <x:v>2427624044</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>0.0185</x:v>
+        <x:v>0.0338</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
       <x:c r="A10" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>8.1</x:v>
+        <x:v>90.75</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>-0.35</x:v>
+        <x:v>-3.25</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>1180000</x:v>
+        <x:v>3384000</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G10" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>2322993973</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>0.0268</x:v>
+        <x:v>0.0627</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
       <x:c r="A11" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>125</x:v>
+        <x:v>4.03</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>7.7</x:v>
+        <x:v>-0.08</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>1220000</x:v>
+        <x:v>1178000</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
         <x:v>11</x:v>
@@ -1118,39 +1121,39 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>2988208362</x:v>
+        <x:v>2875634546</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>0.0184</x:v>
+        <x:v>0.0185</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
       <x:c r="A12" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>28.78</x:v>
+        <x:v>8.08</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>-0.58</x:v>
+        <x:v>-0.02</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>26910</x:v>
+        <x:v>1180000</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G12" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>7297855153</x:v>
+        <x:v>2322993973</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>0.0002</x:v>
+        <x:v>0.0268</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -1158,16 +1161,16 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>59</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>0.3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>2517084</x:v>
+        <x:v>1220000</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
         <x:v>11</x:v>
@@ -1176,27 +1179,27 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>2988208362</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>0.0269</x:v>
+        <x:v>0.0184</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
       <x:c r="A14" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>23.5</x:v>
+        <x:v>28.06</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>-1.18</x:v>
+        <x:v>-0.72</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>9600000</x:v>
+        <x:v>26910</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
         <x:v>11</x:v>
@@ -1205,155 +1208,155 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>2427624044</x:v>
+        <x:v>7297855153</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>0.1785</x:v>
+        <x:v>0.0002</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
       <x:c r="A15" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B15" s="0">
+        <x:v>54.75</x:v>
+      </x:c>
+      <x:c r="C15" s="0">
+        <x:v>-4.25</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B15" s="0">
-        <x:v>325</x:v>
-      </x:c>
-      <x:c r="C15" s="0">
-        <x:v>13.75</x:v>
-      </x:c>
-      <x:c r="D15" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
       <x:c r="E15" s="0">
-        <x:v>9172451</x:v>
+        <x:v>2517084</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G15" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>709077088</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>0.0129</x:v>
+        <x:v>0.0269</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
       <x:c r="A16" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>40.2</x:v>
+        <x:v>22.8</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>0.2</x:v>
+        <x:v>-0.7</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>32493961</x:v>
+        <x:v>9600000</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>2026.03</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>17386730041</x:v>
+        <x:v>2427624044</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>0</x:v>
+        <x:v>0.1785</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
       <x:c r="A17" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>95.2</x:v>
+        <x:v>341.75</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>8.65</x:v>
+        <x:v>16.75</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>940002</x:v>
+        <x:v>9172451</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G17" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>709077088</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>0.0121</x:v>
+        <x:v>0.0129</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
       <x:c r="A18" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>135.4</x:v>
+        <x:v>38.34</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>-11.1</x:v>
+        <x:v>-1.86</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>920000</x:v>
+        <x:v>32493961</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2026.03</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>3150489640</x:v>
+        <x:v>17386730041</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>0.0154</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
       <x:c r="A19" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>94</x:v>
+        <x:v>95.5</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>-5.5</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>12100000</x:v>
+        <x:v>940002</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G19" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>0.005</x:v>
+        <x:v>0.0121</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1361,248 +1364,248 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>419.25</x:v>
+        <x:v>138.7</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>-12.5</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>125100000</x:v>
+        <x:v>920000</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>2026.03</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>184925592000</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>0.0304</x:v>
+        <x:v>0.0154</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
       <x:c r="A21" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>11.41</x:v>
+        <x:v>90.75</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>0.77</x:v>
+        <x:v>-3.25</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>32010000</x:v>
+        <x:v>12100000</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G21" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>10581001663</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>0.1592</x:v>
+        <x:v>0.005</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
       <x:c r="A22" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>28.78</x:v>
+        <x:v>412.75</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>-0.58</x:v>
+        <x:v>-6.5</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>76650</x:v>
+        <x:v>125100000</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2026.03</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>7297855153</x:v>
+        <x:v>184925592000</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>0.0005</x:v>
+        <x:v>0.0304</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
       <x:c r="A23" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>135.4</x:v>
+        <x:v>12.55</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>-11.1</x:v>
+        <x:v>1.14</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
         <x:v>35</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>915000</x:v>
+        <x:v>32010000</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G23" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>3150489640</x:v>
+        <x:v>10581001663</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>0.0153</x:v>
+        <x:v>0.1592</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
       <x:c r="A24" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>40.2</x:v>
+        <x:v>28.06</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>0.2</x:v>
+        <x:v>-0.72</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
         <x:v>35</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>2136645</x:v>
+        <x:v>76650</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>2026.03</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>17386730041</x:v>
+        <x:v>7297855153</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>0.0055</x:v>
+        <x:v>0.0005</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
       <x:c r="A25" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B25" s="0">
+        <x:v>138.7</x:v>
+      </x:c>
+      <x:c r="C25" s="0">
+        <x:v>3.3</x:v>
+      </x:c>
+      <x:c r="D25" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="B25" s="0">
-        <x:v>5.6</x:v>
-      </x:c>
-      <x:c r="C25" s="0">
-        <x:v>-0.52</x:v>
-      </x:c>
-      <x:c r="D25" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
       <x:c r="E25" s="0">
-        <x:v>132077304</x:v>
+        <x:v>915000</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G25" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>855070469</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>0.1545</x:v>
+        <x:v>0.0153</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
       <x:c r="A26" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>333.25</x:v>
+        <x:v>38.34</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>-6.25</x:v>
+        <x:v>-1.86</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>51531000</x:v>
+        <x:v>2136645</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2026.03</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>35290767390</x:v>
+        <x:v>17386730041</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>0.0656</x:v>
+        <x:v>0.0055</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
       <x:c r="A27" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>1172</x:v>
+        <x:v>5.27</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>41</x:v>
+        <x:v>-0.33</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>950978</x:v>
+        <x:v>132077304</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G27" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>1883544167</x:v>
+        <x:v>855070469</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>0.0227</x:v>
+        <x:v>0.1545</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
       <x:c r="A28" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>539.5</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>-57</x:v>
+        <x:v>1.75</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>100000000</x:v>
+        <x:v>51531000</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
         <x:v>11</x:v>
@@ -1611,143 +1614,143 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>71453576000</x:v>
+        <x:v>35290767390</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>0.0628</x:v>
+        <x:v>0.0656</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
       <x:c r="A29" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>95.2</x:v>
+        <x:v>1245</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>8.65</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>286071819</x:v>
+        <x:v>950978</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G29" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>1883544167</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>0.0818</x:v>
+        <x:v>0.0227</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
       <x:c r="A30" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>135.4</x:v>
+        <x:v>519.5</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>-11.1</x:v>
+        <x:v>-20</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>883793</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G30" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>3150489640</x:v>
+        <x:v>71453576000</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>0.0148</x:v>
+        <x:v>0.0628</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
       <x:c r="A31" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>59</x:v>
+        <x:v>95.5</x:v>
       </x:c>
       <x:c r="C31" s="0">
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>606770</x:v>
+        <x:v>286071819</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G31" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>0.0064</x:v>
+        <x:v>0.0818</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
       <x:c r="A32" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B32" s="0">
+        <x:v>138.7</x:v>
+      </x:c>
+      <x:c r="C32" s="0">
+        <x:v>3.3</x:v>
+      </x:c>
+      <x:c r="D32" s="0" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="B32" s="0">
-        <x:v>63.3</x:v>
-      </x:c>
-      <x:c r="C32" s="0">
-        <x:v>-2.7</x:v>
-      </x:c>
-      <x:c r="D32" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
       <x:c r="E32" s="0">
-        <x:v>505597002</x:v>
+        <x:v>883793</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G32" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>8121300519</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>0.0623</x:v>
+        <x:v>0.0148</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
       <x:c r="A33" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>59</x:v>
+        <x:v>54.75</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>0.3</x:v>
+        <x:v>-4.25</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>948000</x:v>
+        <x:v>606770</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
         <x:v>11</x:v>
@@ -1759,82 +1762,82 @@
         <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>0.0101</x:v>
+        <x:v>0.0064</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
       <x:c r="A34" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>94</x:v>
+        <x:v>61.1</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>-5.5</x:v>
+        <x:v>-2.2</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>622000</x:v>
+        <x:v>505597002</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G34" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>8121300519</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>0.0114</x:v>
+        <x:v>0.0623</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
       <x:c r="A35" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>4.11</x:v>
+        <x:v>54.75</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>-0.17</x:v>
+        <x:v>-4.25</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>983000</x:v>
+        <x:v>948000</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G35" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>2875634546</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>0.018</x:v>
+        <x:v>0.0101</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
       <x:c r="A36" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B36" s="0">
+        <x:v>90.75</x:v>
+      </x:c>
+      <x:c r="C36" s="0">
+        <x:v>-3.25</x:v>
+      </x:c>
+      <x:c r="D36" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="B36" s="0">
-        <x:v>76.8</x:v>
-      </x:c>
-      <x:c r="C36" s="0">
-        <x:v>0.3</x:v>
-      </x:c>
-      <x:c r="D36" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
       <x:c r="E36" s="0">
-        <x:v>3421818</x:v>
+        <x:v>622000</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
         <x:v>11</x:v>
@@ -1843,56 +1846,56 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>5948036961</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>0.0257</x:v>
+        <x:v>0.0114</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
       <x:c r="A37" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>49.6</x:v>
+        <x:v>4.03</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>-1.4</x:v>
+        <x:v>-0.08</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>697435</x:v>
+        <x:v>983000</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G37" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>4728937463</x:v>
+        <x:v>2875634546</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>0.0066</x:v>
+        <x:v>0.018</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
       <x:c r="A38" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>94.85</x:v>
+        <x:v>72.1</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>8.6</x:v>
+        <x:v>-4.7</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>4587145</x:v>
+        <x:v>3421818</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
         <x:v>11</x:v>
@@ -1901,27 +1904,27 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>16733157490</x:v>
+        <x:v>5948036961</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>0.0123</x:v>
+        <x:v>0.0257</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
       <x:c r="A39" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>50.25</x:v>
+        <x:v>47.46</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>-0.8</x:v>
+        <x:v>-2.14</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>43200000</x:v>
+        <x:v>697435</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
         <x:v>11</x:v>
@@ -1930,259 +1933,259 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>8236540064</x:v>
+        <x:v>4728937463</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>0.2345</x:v>
+        <x:v>0.0066</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
       <x:c r="A40" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>18.5</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>-0.87</x:v>
+        <x:v>5.15</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>1200000</x:v>
+        <x:v>4587145</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G40" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>3139850323</x:v>
+        <x:v>16733157490</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>0.0201</x:v>
+        <x:v>0.0123</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
       <x:c r="A41" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>63.3</x:v>
+        <x:v>52.15</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>-2.7</x:v>
+        <x:v>1.9</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>247902522</x:v>
+        <x:v>43200000</x:v>
       </x:c>
       <x:c r="F41" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G41" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>8121300519</x:v>
+        <x:v>8236540064</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>0.0305</x:v>
+        <x:v>0.2345</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
       <x:c r="A42" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>59</x:v>
+        <x:v>17.29</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>0.3</x:v>
+        <x:v>-1.21</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>366000</x:v>
+        <x:v>1200000</x:v>
       </x:c>
       <x:c r="F42" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G42" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>3139850323</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>0.0039</x:v>
+        <x:v>0.0201</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
       <x:c r="A43" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>325</x:v>
+        <x:v>61.1</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>13.75</x:v>
+        <x:v>-2.2</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>141051834</x:v>
+        <x:v>247902522</x:v>
       </x:c>
       <x:c r="F43" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G43" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>709077088</x:v>
+        <x:v>8121300519</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>0.1989</x:v>
+        <x:v>0.0305</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
       <x:c r="A44" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B44" s="0">
+        <x:v>54.75</x:v>
+      </x:c>
+      <x:c r="C44" s="0">
+        <x:v>-4.25</x:v>
+      </x:c>
+      <x:c r="D44" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="B44" s="0">
-        <x:v>4.94</x:v>
-      </x:c>
-      <x:c r="C44" s="0">
-        <x:v>-0.09</x:v>
-      </x:c>
-      <x:c r="D44" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="E44" s="0">
-        <x:v>5096500000</x:v>
+        <x:v>366000</x:v>
       </x:c>
       <x:c r="F44" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>19538660616</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>0.2608</x:v>
+        <x:v>0.0039</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
       <x:c r="A45" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B45" s="0">
+        <x:v>341.75</x:v>
+      </x:c>
+      <x:c r="C45" s="0">
+        <x:v>16.75</x:v>
+      </x:c>
+      <x:c r="D45" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="B45" s="0">
-        <x:v>4.94</x:v>
-      </x:c>
-      <x:c r="C45" s="0">
-        <x:v>-0.09</x:v>
-      </x:c>
-      <x:c r="D45" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="E45" s="0">
-        <x:v>5096500000</x:v>
+        <x:v>141051834</x:v>
       </x:c>
       <x:c r="F45" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>19538660616</x:v>
+        <x:v>709077088</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>0.2608</x:v>
+        <x:v>0.1989</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
       <x:c r="A46" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B46" s="0">
+        <x:v>4.76</x:v>
+      </x:c>
+      <x:c r="C46" s="0">
+        <x:v>-0.18</x:v>
+      </x:c>
+      <x:c r="D46" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E46" s="0">
+        <x:v>5096500000</x:v>
+      </x:c>
+      <x:c r="F46" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="B46" s="0">
-        <x:v>40.2</x:v>
-      </x:c>
-      <x:c r="C46" s="0">
-        <x:v>0.2</x:v>
-      </x:c>
-      <x:c r="D46" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E46" s="0">
-        <x:v>37500000</x:v>
-      </x:c>
-      <x:c r="F46" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="G46" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>16355768622</x:v>
+        <x:v>19538660616</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>0.1024</x:v>
+        <x:v>0.2608</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
       <x:c r="A47" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>269.5</x:v>
+        <x:v>4.76</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>-5.5</x:v>
+        <x:v>-0.18</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>2030000</x:v>
+        <x:v>5096500000</x:v>
       </x:c>
       <x:c r="F47" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>2159813703</x:v>
+        <x:v>19538660616</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>0.042</x:v>
+        <x:v>0.2608</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
       <x:c r="A48" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>94.85</x:v>
+        <x:v>38.34</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>8.6</x:v>
+        <x:v>-1.86</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>31146246</x:v>
+        <x:v>37500000</x:v>
       </x:c>
       <x:c r="F48" s="0" t="s">
         <x:v>11</x:v>
@@ -2191,88 +2194,88 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>16733157490</x:v>
+        <x:v>16355768622</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>0.0832</x:v>
+        <x:v>0.1024</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
       <x:c r="A49" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B49" s="0">
+        <x:v>274.5</x:v>
+      </x:c>
+      <x:c r="C49" s="0">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D49" s="0" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="B49" s="0">
-        <x:v>12.72</x:v>
-      </x:c>
-      <x:c r="C49" s="0">
-        <x:v>-0.52</x:v>
-      </x:c>
-      <x:c r="D49" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
       <x:c r="E49" s="0">
-        <x:v>1000000</x:v>
+        <x:v>2030000</x:v>
       </x:c>
       <x:c r="F49" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G49" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>7221187888</x:v>
+        <x:v>2159813703</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>0.0001</x:v>
+        <x:v>0.042</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
       <x:c r="A50" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B50" s="0">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C50" s="0">
+        <x:v>5.15</x:v>
+      </x:c>
+      <x:c r="D50" s="0" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="B50" s="0">
-        <x:v>12.72</x:v>
-      </x:c>
-      <x:c r="C50" s="0">
-        <x:v>-0.52</x:v>
-      </x:c>
-      <x:c r="D50" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
       <x:c r="E50" s="0">
-        <x:v>3150000</x:v>
+        <x:v>31146246</x:v>
       </x:c>
       <x:c r="F50" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G50" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>7221187888</x:v>
+        <x:v>16733157490</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>0.0227</x:v>
+        <x:v>0.0832</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
       <x:c r="A51" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>12.72</x:v>
+        <x:v>12.74</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>-0.52</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>2690000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="F51" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G51" s="0">
         <x:v>2025.12</x:v>
@@ -2281,82 +2284,82 @@
         <x:v>7221187888</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>0.0166</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
       <x:c r="A52" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>94.85</x:v>
+        <x:v>12.74</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>8.6</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>4103000</x:v>
+        <x:v>3150000</x:v>
       </x:c>
       <x:c r="F52" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G52" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>16733157490</x:v>
+        <x:v>7221187888</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>0.0109</x:v>
+        <x:v>0.0227</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:9">
       <x:c r="A53" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B53" s="0">
-        <x:v>135.4</x:v>
+        <x:v>12.74</x:v>
       </x:c>
       <x:c r="C53" s="0">
-        <x:v>-11.1</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E53" s="0">
-        <x:v>500000</x:v>
+        <x:v>2690000</x:v>
       </x:c>
       <x:c r="F53" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G53" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H53" s="0">
-        <x:v>3150489640</x:v>
+        <x:v>7221187888</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>0.0083</x:v>
+        <x:v>0.0166</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:9">
       <x:c r="A54" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B54" s="0">
-        <x:v>59</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C54" s="0">
-        <x:v>0.3</x:v>
+        <x:v>5.15</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E54" s="0">
-        <x:v>872928</x:v>
+        <x:v>4103000</x:v>
       </x:c>
       <x:c r="F54" s="0" t="s">
         <x:v>11</x:v>
@@ -2365,578 +2368,578 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>16733157490</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>0.0092</x:v>
+        <x:v>0.0109</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:9">
       <x:c r="A55" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B55" s="0">
-        <x:v>94</x:v>
+        <x:v>138.7</x:v>
       </x:c>
       <x:c r="C55" s="0">
-        <x:v>-5.5</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
       <x:c r="E55" s="0">
-        <x:v>21250000</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="F55" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G55" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H55" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>0.0087</x:v>
+        <x:v>0.0083</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:9">
       <x:c r="A56" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B56" s="0">
-        <x:v>63.3</x:v>
+        <x:v>54.75</x:v>
       </x:c>
       <x:c r="C56" s="0">
-        <x:v>-2.7</x:v>
+        <x:v>-4.25</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E56" s="0">
-        <x:v>67690912</x:v>
+        <x:v>872928</x:v>
       </x:c>
       <x:c r="F56" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G56" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H56" s="0">
-        <x:v>8121300519</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>0.0083</x:v>
+        <x:v>0.0092</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:9">
       <x:c r="A57" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B57" s="0">
-        <x:v>40.2</x:v>
+        <x:v>90.75</x:v>
       </x:c>
       <x:c r="C57" s="0">
-        <x:v>0.2</x:v>
+        <x:v>-3.25</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="E57" s="0">
-        <x:v>65458848</x:v>
+        <x:v>21250000</x:v>
       </x:c>
       <x:c r="F57" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G57" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H57" s="0">
-        <x:v>16355768622</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>0.1784</x:v>
+        <x:v>0.0087</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:9">
       <x:c r="A58" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B58" s="0">
+        <x:v>61.1</x:v>
+      </x:c>
+      <x:c r="C58" s="0">
+        <x:v>-2.2</x:v>
+      </x:c>
+      <x:c r="D58" s="0" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="B58" s="0">
-        <x:v>25.32</x:v>
-      </x:c>
-      <x:c r="C58" s="0">
-        <x:v>0.24</x:v>
-      </x:c>
-      <x:c r="D58" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
       <x:c r="E58" s="0">
-        <x:v>689500000</x:v>
+        <x:v>67690912</x:v>
       </x:c>
       <x:c r="F58" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G58" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H58" s="0">
-        <x:v>884571536</x:v>
+        <x:v>8121300519</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>0.7795</x:v>
+        <x:v>0.0083</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:9">
       <x:c r="A59" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B59" s="0">
-        <x:v>8.1</x:v>
+        <x:v>38.34</x:v>
       </x:c>
       <x:c r="C59" s="0">
-        <x:v>-0.35</x:v>
+        <x:v>-1.86</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E59" s="0">
-        <x:v>3024490</x:v>
+        <x:v>65458848</x:v>
       </x:c>
       <x:c r="F59" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G59" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H59" s="0">
-        <x:v>2322993973</x:v>
+        <x:v>16355768622</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>0.0671</x:v>
+        <x:v>0.1784</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:9">
       <x:c r="A60" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B60" s="0">
-        <x:v>8.1</x:v>
+        <x:v>24.52</x:v>
       </x:c>
       <x:c r="C60" s="0">
-        <x:v>-0.35</x:v>
+        <x:v>-0.8</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E60" s="0">
-        <x:v>4510336</x:v>
+        <x:v>689500000</x:v>
       </x:c>
       <x:c r="F60" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G60" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H60" s="0">
-        <x:v>2322993973</x:v>
+        <x:v>884571536</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>0.0865</x:v>
+        <x:v>0.7795</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:9">
       <x:c r="A61" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B61" s="0">
-        <x:v>61.35</x:v>
+        <x:v>8.08</x:v>
       </x:c>
       <x:c r="C61" s="0">
-        <x:v>0</x:v>
+        <x:v>-0.02</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E61" s="0">
-        <x:v>205000000</x:v>
+        <x:v>3024490</x:v>
       </x:c>
       <x:c r="F61" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G61" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H61" s="0">
-        <x:v>20597209000</x:v>
+        <x:v>2322993973</x:v>
       </x:c>
       <x:c r="I61" s="0">
-        <x:v>0.4434</x:v>
+        <x:v>0.0671</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:9">
       <x:c r="A62" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B62" s="0">
-        <x:v>320</x:v>
+        <x:v>8.08</x:v>
       </x:c>
       <x:c r="C62" s="0">
-        <x:v>4.5</x:v>
+        <x:v>-0.02</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E62" s="0">
-        <x:v>305000000</x:v>
+        <x:v>4510336</x:v>
       </x:c>
       <x:c r="F62" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G62" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H62" s="0">
-        <x:v>400439646</x:v>
+        <x:v>2322993973</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>0.7617</x:v>
+        <x:v>0.0865</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:9">
       <x:c r="A63" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B63" s="0">
-        <x:v>95.2</x:v>
+        <x:v>60.7</x:v>
       </x:c>
       <x:c r="C63" s="0">
-        <x:v>8.65</x:v>
+        <x:v>-0.65</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E63" s="0">
-        <x:v>11700000</x:v>
+        <x:v>205000000</x:v>
       </x:c>
       <x:c r="F63" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G63" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H63" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>20597209000</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>0.1718</x:v>
+        <x:v>0.4434</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:9">
       <x:c r="A64" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B64" s="0">
-        <x:v>269.5</x:v>
+        <x:v>311.5</x:v>
       </x:c>
       <x:c r="C64" s="0">
-        <x:v>-5.5</x:v>
+        <x:v>-8.5</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E64" s="0">
-        <x:v>1900000</x:v>
+        <x:v>305000000</x:v>
       </x:c>
       <x:c r="F64" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G64" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H64" s="0">
-        <x:v>2159813703</x:v>
+        <x:v>400439646</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>0.0391</x:v>
+        <x:v>0.7617</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:9">
       <x:c r="A65" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B65" s="0">
-        <x:v>4.11</x:v>
+        <x:v>95.5</x:v>
       </x:c>
       <x:c r="C65" s="0">
-        <x:v>-0.17</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E65" s="0">
-        <x:v>1670000</x:v>
+        <x:v>11700000</x:v>
       </x:c>
       <x:c r="F65" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G65" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H65" s="0">
-        <x:v>2875634546</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I65" s="0">
-        <x:v>0.0298</x:v>
+        <x:v>0.1718</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:9">
       <x:c r="A66" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B66" s="0">
-        <x:v>25.32</x:v>
+        <x:v>274.5</x:v>
       </x:c>
       <x:c r="C66" s="0">
-        <x:v>0.24</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
         <x:v>65</x:v>
       </x:c>
       <x:c r="E66" s="0">
-        <x:v>48895800</x:v>
+        <x:v>1900000</x:v>
       </x:c>
       <x:c r="F66" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G66" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H66" s="0">
-        <x:v>884571536</x:v>
+        <x:v>2159813703</x:v>
       </x:c>
       <x:c r="I66" s="0">
-        <x:v>0.0553</x:v>
+        <x:v>0.0391</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:9">
       <x:c r="A67" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B67" s="0">
-        <x:v>25.32</x:v>
+        <x:v>4.03</x:v>
       </x:c>
       <x:c r="C67" s="0">
-        <x:v>0.24</x:v>
+        <x:v>-0.08</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
         <x:v>65</x:v>
       </x:c>
       <x:c r="E67" s="0">
-        <x:v>689500000</x:v>
+        <x:v>1670000</x:v>
       </x:c>
       <x:c r="F67" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G67" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H67" s="0">
-        <x:v>884571536</x:v>
+        <x:v>2875634546</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>0.7795</x:v>
+        <x:v>0.0298</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:9">
       <x:c r="A68" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B68" s="0">
+        <x:v>24.52</x:v>
+      </x:c>
+      <x:c r="C68" s="0">
+        <x:v>-0.8</x:v>
+      </x:c>
+      <x:c r="D68" s="0" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="B68" s="0">
-        <x:v>48.58</x:v>
-      </x:c>
-      <x:c r="C68" s="0">
-        <x:v>-1.02</x:v>
-      </x:c>
-      <x:c r="D68" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
       <x:c r="E68" s="0">
-        <x:v>3102911</x:v>
+        <x:v>48895800</x:v>
       </x:c>
       <x:c r="F68" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G68" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H68" s="0">
-        <x:v>2907014564</x:v>
+        <x:v>884571536</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>0.0475</x:v>
+        <x:v>0.0553</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:9">
       <x:c r="A69" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B69" s="0">
-        <x:v>24.7</x:v>
+        <x:v>24.52</x:v>
       </x:c>
       <x:c r="C69" s="0">
-        <x:v>-1.68</x:v>
+        <x:v>-0.8</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E69" s="0">
-        <x:v>13000000</x:v>
+        <x:v>689500000</x:v>
       </x:c>
       <x:c r="F69" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G69" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H69" s="0">
-        <x:v>11834942581</x:v>
+        <x:v>884571536</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>0.0563</x:v>
+        <x:v>0.7795</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:9">
       <x:c r="A70" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B70" s="0">
-        <x:v>76.8</x:v>
+        <x:v>47.24</x:v>
       </x:c>
       <x:c r="C70" s="0">
-        <x:v>0.3</x:v>
+        <x:v>-1.34</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E70" s="0">
-        <x:v>6800000</x:v>
+        <x:v>3102911</x:v>
       </x:c>
       <x:c r="F70" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G70" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H70" s="0">
-        <x:v>5948036961</x:v>
+        <x:v>2907014564</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>0.0583</x:v>
+        <x:v>0.0475</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:9">
       <x:c r="A71" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B71" s="0">
-        <x:v>61.35</x:v>
+        <x:v>24.76</x:v>
       </x:c>
       <x:c r="C71" s="0">
-        <x:v>0</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E71" s="0">
-        <x:v>36750000</x:v>
+        <x:v>13000000</x:v>
       </x:c>
       <x:c r="F71" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G71" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H71" s="0">
-        <x:v>20597209000</x:v>
+        <x:v>11834942581</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>0.0793</x:v>
+        <x:v>0.0563</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:9">
       <x:c r="A72" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B72" s="0">
-        <x:v>1172</x:v>
+        <x:v>72.1</x:v>
       </x:c>
       <x:c r="C72" s="0">
-        <x:v>41</x:v>
+        <x:v>-4.7</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="E72" s="0">
-        <x:v>3867260</x:v>
+        <x:v>6800000</x:v>
       </x:c>
       <x:c r="F72" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G72" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H72" s="0">
-        <x:v>1883544167</x:v>
+        <x:v>5948036961</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>0.0912</x:v>
+        <x:v>0.0583</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:9">
       <x:c r="A73" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B73" s="0">
-        <x:v>70.15</x:v>
+        <x:v>60.7</x:v>
       </x:c>
       <x:c r="C73" s="0">
-        <x:v>-0.95</x:v>
+        <x:v>-0.65</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E73" s="0">
-        <x:v>1498029716</x:v>
+        <x:v>36750000</x:v>
       </x:c>
       <x:c r="F73" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G73" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H73" s="0">
-        <x:v>12030341104</x:v>
+        <x:v>20597209000</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>0.1245</x:v>
+        <x:v>0.0793</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:9">
       <x:c r="A74" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B74" s="0">
-        <x:v>40.2</x:v>
+        <x:v>1245</x:v>
       </x:c>
       <x:c r="C74" s="0">
-        <x:v>0.2</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E74" s="0">
-        <x:v>48000000</x:v>
+        <x:v>3867260</x:v>
       </x:c>
       <x:c r="F74" s="0" t="s">
         <x:v>11</x:v>
@@ -2945,56 +2948,56 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H74" s="0">
-        <x:v>16355768622</x:v>
+        <x:v>1883544167</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>0.1301</x:v>
+        <x:v>0.0912</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:9">
       <x:c r="A75" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B75" s="0">
-        <x:v>95.2</x:v>
+        <x:v>66.85</x:v>
       </x:c>
       <x:c r="C75" s="0">
-        <x:v>8.65</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
         <x:v>72</x:v>
       </x:c>
       <x:c r="E75" s="0">
-        <x:v>279699629</x:v>
+        <x:v>1498029716</x:v>
       </x:c>
       <x:c r="F75" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G75" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H75" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>12030341104</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>0.08</x:v>
+        <x:v>0.1245</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:9">
       <x:c r="A76" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B76" s="0">
-        <x:v>16</x:v>
+        <x:v>38.34</x:v>
       </x:c>
       <x:c r="C76" s="0">
-        <x:v>-0.98</x:v>
+        <x:v>-1.86</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
         <x:v>72</x:v>
       </x:c>
       <x:c r="E76" s="0">
-        <x:v>7971822</x:v>
+        <x:v>48000000</x:v>
       </x:c>
       <x:c r="F76" s="0" t="s">
         <x:v>11</x:v>
@@ -3003,126 +3006,126 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H76" s="0">
-        <x:v>4675369372</x:v>
+        <x:v>16355768622</x:v>
       </x:c>
       <x:c r="I76" s="0">
-        <x:v>0.0756</x:v>
+        <x:v>0.1301</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:9">
       <x:c r="A77" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B77" s="0">
-        <x:v>59</x:v>
+        <x:v>95.5</x:v>
       </x:c>
       <x:c r="C77" s="0">
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E77" s="0">
-        <x:v>1104000</x:v>
+        <x:v>279699629</x:v>
       </x:c>
       <x:c r="F77" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G77" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H77" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>0.0116</x:v>
+        <x:v>0.08</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:9">
       <x:c r="A78" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B78" s="0">
-        <x:v>25.32</x:v>
+        <x:v>17.6</x:v>
       </x:c>
       <x:c r="C78" s="0">
-        <x:v>0.24</x:v>
+        <x:v>1.6</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E78" s="0">
-        <x:v>48895800</x:v>
+        <x:v>7971822</x:v>
       </x:c>
       <x:c r="F78" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G78" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H78" s="0">
-        <x:v>884571536</x:v>
+        <x:v>4675369372</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>0.0553</x:v>
+        <x:v>0.0756</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:9">
       <x:c r="A79" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B79" s="0">
-        <x:v>3.56</x:v>
+        <x:v>54.75</x:v>
       </x:c>
       <x:c r="C79" s="0">
-        <x:v>0.05</x:v>
+        <x:v>-4.25</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E79" s="0">
-        <x:v>191089413</x:v>
+        <x:v>1104000</x:v>
       </x:c>
       <x:c r="F79" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G79" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H79" s="0">
-        <x:v>9665356715</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>0.0198</x:v>
+        <x:v>0.0116</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:9">
       <x:c r="A80" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B80" s="0">
-        <x:v>3.56</x:v>
+        <x:v>24.52</x:v>
       </x:c>
       <x:c r="C80" s="0">
-        <x:v>0.05</x:v>
+        <x:v>-0.8</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E80" s="0">
-        <x:v>605627160</x:v>
+        <x:v>48895800</x:v>
       </x:c>
       <x:c r="F80" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G80" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H80" s="0">
-        <x:v>9665356715</x:v>
+        <x:v>884571536</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>0.0627</x:v>
+        <x:v>0.0553</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:9">
@@ -3130,190 +3133,190 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B81" s="0">
-        <x:v>25.76</x:v>
+        <x:v>3.5</x:v>
       </x:c>
       <x:c r="C81" s="0">
-        <x:v>-0.22</x:v>
+        <x:v>-0.06</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E81" s="0">
-        <x:v>2356546000</x:v>
+        <x:v>191089413</x:v>
       </x:c>
       <x:c r="F81" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G81" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H81" s="0">
-        <x:v>7708004248</x:v>
+        <x:v>9665356715</x:v>
       </x:c>
       <x:c r="I81" s="0">
-        <x:v>0.3057</x:v>
+        <x:v>0.0198</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:9">
       <x:c r="A82" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B82" s="0">
-        <x:v>18.5</x:v>
+        <x:v>3.5</x:v>
       </x:c>
       <x:c r="C82" s="0">
-        <x:v>-0.87</x:v>
+        <x:v>-0.06</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E82" s="0">
-        <x:v>431250</x:v>
+        <x:v>605627160</x:v>
       </x:c>
       <x:c r="F82" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G82" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H82" s="0">
-        <x:v>3139850323</x:v>
+        <x:v>9665356715</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>0.0071</x:v>
+        <x:v>0.0627</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:9">
       <x:c r="A83" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B83" s="0">
-        <x:v>18.5</x:v>
+        <x:v>25.1</x:v>
       </x:c>
       <x:c r="C83" s="0">
-        <x:v>-0.87</x:v>
+        <x:v>-0.66</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E83" s="0">
-        <x:v>800000</x:v>
+        <x:v>2356546000</x:v>
       </x:c>
       <x:c r="F83" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G83" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H83" s="0">
-        <x:v>3139850323</x:v>
+        <x:v>7708004248</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>0.0131</x:v>
+        <x:v>0.3057</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:9">
       <x:c r="A84" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B84" s="0">
-        <x:v>63.3</x:v>
+        <x:v>17.29</x:v>
       </x:c>
       <x:c r="C84" s="0">
-        <x:v>-2.7</x:v>
+        <x:v>-1.21</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E84" s="0">
-        <x:v>127172130</x:v>
+        <x:v>431250</x:v>
       </x:c>
       <x:c r="F84" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G84" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H84" s="0">
-        <x:v>8121300519</x:v>
+        <x:v>3139850323</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>0.0157</x:v>
+        <x:v>0.0071</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:9">
       <x:c r="A85" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B85" s="0">
-        <x:v>49.6</x:v>
+        <x:v>17.29</x:v>
       </x:c>
       <x:c r="C85" s="0">
-        <x:v>-1.4</x:v>
+        <x:v>-1.21</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E85" s="0">
-        <x:v>42625000</x:v>
+        <x:v>800000</x:v>
       </x:c>
       <x:c r="F85" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G85" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H85" s="0">
-        <x:v>4728937463</x:v>
+        <x:v>3139850323</x:v>
       </x:c>
       <x:c r="I85" s="0">
-        <x:v>0.3994</x:v>
+        <x:v>0.0131</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:9">
       <x:c r="A86" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B86" s="0">
-        <x:v>94</x:v>
+        <x:v>61.1</x:v>
       </x:c>
       <x:c r="C86" s="0">
-        <x:v>-5.5</x:v>
+        <x:v>-2.2</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
         <x:v>77</x:v>
       </x:c>
       <x:c r="E86" s="0">
-        <x:v>1486000</x:v>
+        <x:v>127172130</x:v>
       </x:c>
       <x:c r="F86" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G86" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H86" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>8121300519</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>0.027</x:v>
+        <x:v>0.0157</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:9">
       <x:c r="A87" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B87" s="0">
-        <x:v>333.25</x:v>
+        <x:v>47.46</x:v>
       </x:c>
       <x:c r="C87" s="0">
-        <x:v>-6.25</x:v>
+        <x:v>-2.14</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
         <x:v>77</x:v>
       </x:c>
       <x:c r="E87" s="0">
-        <x:v>768864700</x:v>
+        <x:v>42625000</x:v>
       </x:c>
       <x:c r="F87" s="0" t="s">
         <x:v>11</x:v>
@@ -3322,27 +3325,27 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H87" s="0">
-        <x:v>35290767390</x:v>
+        <x:v>4728937463</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>0.9648</x:v>
+        <x:v>0.3994</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:9">
       <x:c r="A88" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B88" s="0">
-        <x:v>94.85</x:v>
+        <x:v>90.75</x:v>
       </x:c>
       <x:c r="C88" s="0">
-        <x:v>8.6</x:v>
+        <x:v>-3.25</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E88" s="0">
-        <x:v>15938617</x:v>
+        <x:v>1486000</x:v>
       </x:c>
       <x:c r="F88" s="0" t="s">
         <x:v>11</x:v>
@@ -3351,56 +3354,56 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H88" s="0">
-        <x:v>16733157490</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>0.0422</x:v>
+        <x:v>0.027</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:9">
       <x:c r="A89" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B89" s="0">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="C89" s="0">
+        <x:v>1.75</x:v>
+      </x:c>
+      <x:c r="D89" s="0" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="B89" s="0">
-        <x:v>14.86</x:v>
-      </x:c>
-      <x:c r="C89" s="0">
-        <x:v>0.02</x:v>
-      </x:c>
-      <x:c r="D89" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
       <x:c r="E89" s="0">
-        <x:v>30438120</x:v>
+        <x:v>768864700</x:v>
       </x:c>
       <x:c r="F89" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G89" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H89" s="0">
-        <x:v>3159124121</x:v>
+        <x:v>35290767390</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>0</x:v>
+        <x:v>0.9648</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:9">
       <x:c r="A90" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B90" s="0">
-        <x:v>269.5</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C90" s="0">
-        <x:v>-5.5</x:v>
+        <x:v>5.15</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E90" s="0">
-        <x:v>3900000</x:v>
+        <x:v>15938617</x:v>
       </x:c>
       <x:c r="F90" s="0" t="s">
         <x:v>11</x:v>
@@ -3409,53 +3412,53 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H90" s="0">
-        <x:v>2159813703</x:v>
+        <x:v>16733157490</x:v>
       </x:c>
       <x:c r="I90" s="0">
-        <x:v>0.0797</x:v>
+        <x:v>0.0422</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:9">
       <x:c r="A91" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B91" s="0">
-        <x:v>269.5</x:v>
+        <x:v>14.56</x:v>
       </x:c>
       <x:c r="C91" s="0">
-        <x:v>-5.5</x:v>
+        <x:v>-0.3</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="E91" s="0">
-        <x:v>2104908</x:v>
+        <x:v>30438120</x:v>
       </x:c>
       <x:c r="F91" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G91" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H91" s="0">
-        <x:v>2159813703</x:v>
+        <x:v>3159124121</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>0.043</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:9">
       <x:c r="A92" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B92" s="0">
-        <x:v>28.78</x:v>
+        <x:v>274.5</x:v>
       </x:c>
       <x:c r="C92" s="0">
-        <x:v>-0.58</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E92" s="0">
         <x:v>3900000</x:v>
@@ -3467,126 +3470,126 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H92" s="0">
-        <x:v>7297855153</x:v>
+        <x:v>2159813703</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>0.0236</x:v>
+        <x:v>0.0797</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:9">
       <x:c r="A93" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B93" s="0">
-        <x:v>5.6</x:v>
+        <x:v>274.5</x:v>
       </x:c>
       <x:c r="C93" s="0">
-        <x:v>-0.52</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
         <x:v>81</x:v>
       </x:c>
       <x:c r="E93" s="0">
-        <x:v>496968445</x:v>
+        <x:v>2104908</x:v>
       </x:c>
       <x:c r="F93" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G93" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H93" s="0">
-        <x:v>855070469</x:v>
+        <x:v>2159813703</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>0.5812</x:v>
+        <x:v>0.043</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:9">
       <x:c r="A94" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B94" s="0">
-        <x:v>11.31</x:v>
+        <x:v>28.06</x:v>
       </x:c>
       <x:c r="C94" s="0">
-        <x:v>-0.32</x:v>
+        <x:v>-0.72</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
         <x:v>81</x:v>
       </x:c>
       <x:c r="E94" s="0">
-        <x:v>108750000</x:v>
+        <x:v>3900000</x:v>
       </x:c>
       <x:c r="F94" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G94" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H94" s="0">
-        <x:v>1982520183</x:v>
+        <x:v>7297855153</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>0.0549</x:v>
+        <x:v>0.0236</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:9">
       <x:c r="A95" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B95" s="0">
-        <x:v>135.4</x:v>
+        <x:v>5.27</x:v>
       </x:c>
       <x:c r="C95" s="0">
-        <x:v>-11.1</x:v>
+        <x:v>-0.33</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E95" s="0">
-        <x:v>1605197</x:v>
+        <x:v>496968445</x:v>
       </x:c>
       <x:c r="F95" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G95" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H95" s="0">
-        <x:v>0</x:v>
+        <x:v>855070469</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>0</x:v>
+        <x:v>0.5812</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:9">
       <x:c r="A96" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B96" s="0">
-        <x:v>419.25</x:v>
+        <x:v>11.33</x:v>
       </x:c>
       <x:c r="C96" s="0">
-        <x:v>-12.5</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E96" s="0">
-        <x:v>54600000</x:v>
+        <x:v>108750000</x:v>
       </x:c>
       <x:c r="F96" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G96" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H96" s="0">
-        <x:v>180444938000</x:v>
+        <x:v>1982520183</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>0.0133</x:v>
+        <x:v>0.0549</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:9">
@@ -3594,45 +3597,45 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B97" s="0">
-        <x:v>419.25</x:v>
+        <x:v>138.7</x:v>
       </x:c>
       <x:c r="C97" s="0">
-        <x:v>-12.5</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="E97" s="0">
-        <x:v>111850000</x:v>
+        <x:v>1605197</x:v>
       </x:c>
       <x:c r="F97" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G97" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H97" s="0">
-        <x:v>180444938000</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>0.0273</x:v>
+        <x:v>0.0257</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:9">
       <x:c r="A98" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B98" s="0">
-        <x:v>59</x:v>
+        <x:v>412.75</x:v>
       </x:c>
       <x:c r="C98" s="0">
-        <x:v>0.3</x:v>
+        <x:v>-6.5</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E98" s="0">
-        <x:v>803090</x:v>
+        <x:v>54600000</x:v>
       </x:c>
       <x:c r="F98" s="0" t="s">
         <x:v>11</x:v>
@@ -3641,56 +3644,56 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H98" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>180444938000</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>0.0084</x:v>
+        <x:v>0.0133</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:9">
       <x:c r="A99" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B99" s="0">
-        <x:v>25.76</x:v>
+        <x:v>412.75</x:v>
       </x:c>
       <x:c r="C99" s="0">
-        <x:v>-0.22</x:v>
+        <x:v>-6.5</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
         <x:v>85</x:v>
       </x:c>
       <x:c r="E99" s="0">
-        <x:v>2356546000</x:v>
+        <x:v>111850000</x:v>
       </x:c>
       <x:c r="F99" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G99" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H99" s="0">
-        <x:v>7708004248</x:v>
+        <x:v>180444938000</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>0.3057</x:v>
+        <x:v>0.0273</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:9">
       <x:c r="A100" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B100" s="0">
-        <x:v>1172</x:v>
+        <x:v>54.75</x:v>
       </x:c>
       <x:c r="C100" s="0">
-        <x:v>41</x:v>
+        <x:v>-4.25</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E100" s="0">
-        <x:v>875400</x:v>
+        <x:v>803090</x:v>
       </x:c>
       <x:c r="F100" s="0" t="s">
         <x:v>11</x:v>
@@ -3699,752 +3702,752 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H100" s="0">
-        <x:v>1883544167</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>0.0205</x:v>
+        <x:v>0.0084</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:9">
       <x:c r="A101" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B101" s="0">
-        <x:v>26.34</x:v>
+        <x:v>25.1</x:v>
       </x:c>
       <x:c r="C101" s="0">
         <x:v>-0.66</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E101" s="0">
-        <x:v>330000000</x:v>
+        <x:v>2356546000</x:v>
       </x:c>
       <x:c r="F101" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G101" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H101" s="0">
-        <x:v>5287314404</x:v>
+        <x:v>7708004248</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>0.0624</x:v>
+        <x:v>0.3057</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:9">
       <x:c r="A102" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B102" s="0">
-        <x:v>95.2</x:v>
+        <x:v>1245</x:v>
       </x:c>
       <x:c r="C102" s="0">
-        <x:v>8.65</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E102" s="0">
-        <x:v>11700000</x:v>
+        <x:v>875400</x:v>
       </x:c>
       <x:c r="F102" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G102" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H102" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>1883544167</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>0.1705</x:v>
+        <x:v>0.0205</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:9">
       <x:c r="A103" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B103" s="0">
-        <x:v>11.41</x:v>
+        <x:v>25.74</x:v>
       </x:c>
       <x:c r="C103" s="0">
-        <x:v>0.77</x:v>
+        <x:v>-0.6</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
         <x:v>89</x:v>
       </x:c>
       <x:c r="E103" s="0">
-        <x:v>4000000000</x:v>
+        <x:v>330000000</x:v>
       </x:c>
       <x:c r="F103" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G103" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H103" s="0">
-        <x:v>10581001663</x:v>
+        <x:v>5287314404</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>0.378</x:v>
+        <x:v>0.0624</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:9">
       <x:c r="A104" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B104" s="0">
-        <x:v>18.5</x:v>
+        <x:v>95.5</x:v>
       </x:c>
       <x:c r="C104" s="0">
-        <x:v>-0.87</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
       <x:c r="E104" s="0">
-        <x:v>1086598</x:v>
+        <x:v>11700000</x:v>
       </x:c>
       <x:c r="F104" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G104" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H104" s="0">
-        <x:v>2020891371</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I104" s="0">
-        <x:v>0.0274</x:v>
+        <x:v>0.1705</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:9">
       <x:c r="A105" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B105" s="0">
-        <x:v>16</x:v>
+        <x:v>12.55</x:v>
       </x:c>
       <x:c r="C105" s="0">
-        <x:v>-0.98</x:v>
+        <x:v>1.14</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E105" s="0">
-        <x:v>216000000</x:v>
+        <x:v>4000000000</x:v>
       </x:c>
       <x:c r="F105" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G105" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H105" s="0">
-        <x:v>3025063909</x:v>
+        <x:v>10581001663</x:v>
       </x:c>
       <x:c r="I105" s="0">
-        <x:v>0.0714</x:v>
+        <x:v>0.378</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:9">
       <x:c r="A106" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B106" s="0">
-        <x:v>59</x:v>
+        <x:v>17.29</x:v>
       </x:c>
       <x:c r="C106" s="0">
-        <x:v>0.3</x:v>
+        <x:v>-1.21</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
         <x:v>91</x:v>
       </x:c>
       <x:c r="E106" s="0">
-        <x:v>7292916</x:v>
+        <x:v>1086598</x:v>
       </x:c>
       <x:c r="F106" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G106" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H106" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>2020891371</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>0.0758</x:v>
+        <x:v>0.0274</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:9">
       <x:c r="A107" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B107" s="0">
-        <x:v>30.7</x:v>
+        <x:v>17.6</x:v>
       </x:c>
       <x:c r="C107" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>1.6</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
         <x:v>92</x:v>
       </x:c>
       <x:c r="E107" s="0">
-        <x:v>250000</x:v>
+        <x:v>216000000</x:v>
       </x:c>
       <x:c r="F107" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G107" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H107" s="0">
-        <x:v>448686813</x:v>
+        <x:v>3025063909</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>0.0006</x:v>
+        <x:v>0.0714</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:9">
       <x:c r="A108" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B108" s="0">
-        <x:v>94.85</x:v>
+        <x:v>54.75</x:v>
       </x:c>
       <x:c r="C108" s="0">
-        <x:v>8.6</x:v>
+        <x:v>-4.25</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
         <x:v>92</x:v>
       </x:c>
       <x:c r="E108" s="0">
-        <x:v>36900000</x:v>
+        <x:v>7292916</x:v>
       </x:c>
       <x:c r="F108" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G108" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H108" s="0">
-        <x:v>10597063406</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I108" s="0">
-        <x:v>0.1527</x:v>
+        <x:v>0.0758</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:9">
       <x:c r="A109" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B109" s="0">
+        <x:v>29.82</x:v>
+      </x:c>
+      <x:c r="C109" s="0">
+        <x:v>-0.88</x:v>
+      </x:c>
+      <x:c r="D109" s="0" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="B109" s="0">
-        <x:v>66.5</x:v>
-      </x:c>
-      <x:c r="C109" s="0">
-        <x:v>-5.25</x:v>
-      </x:c>
-      <x:c r="D109" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
       <x:c r="E109" s="0">
-        <x:v>3800000</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="F109" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G109" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H109" s="0">
-        <x:v>832031190</x:v>
+        <x:v>448686813</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>0.2002</x:v>
+        <x:v>0.0006</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:9">
       <x:c r="A110" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B110" s="0">
-        <x:v>5.6</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C110" s="0">
-        <x:v>-0.52</x:v>
+        <x:v>5.15</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E110" s="0">
-        <x:v>2100000</x:v>
+        <x:v>36900000</x:v>
       </x:c>
       <x:c r="F110" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G110" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H110" s="0">
-        <x:v>855070469</x:v>
+        <x:v>10597063406</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>0.1076</x:v>
+        <x:v>0.1527</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:9">
       <x:c r="A111" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B111" s="0">
-        <x:v>59</x:v>
+        <x:v>63.1</x:v>
       </x:c>
       <x:c r="C111" s="0">
-        <x:v>0.3</x:v>
+        <x:v>-3.4</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
         <x:v>95</x:v>
       </x:c>
       <x:c r="E111" s="0">
-        <x:v>22928077</x:v>
+        <x:v>3800000</x:v>
       </x:c>
       <x:c r="F111" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G111" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H111" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>832031190</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>0.2378</x:v>
+        <x:v>0.2002</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:9">
       <x:c r="A112" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B112" s="0">
+        <x:v>5.27</x:v>
+      </x:c>
+      <x:c r="C112" s="0">
+        <x:v>-0.33</x:v>
+      </x:c>
+      <x:c r="D112" s="0" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="B112" s="0">
-        <x:v>31.36</x:v>
-      </x:c>
-      <x:c r="C112" s="0">
-        <x:v>0.18</x:v>
-      </x:c>
-      <x:c r="D112" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
       <x:c r="E112" s="0">
-        <x:v>547462013</x:v>
+        <x:v>2100000</x:v>
       </x:c>
       <x:c r="F112" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G112" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H112" s="0">
-        <x:v>0</x:v>
+        <x:v>855070469</x:v>
       </x:c>
       <x:c r="I112" s="0">
-        <x:v>0</x:v>
+        <x:v>0.1076</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:9">
       <x:c r="A113" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B113" s="0">
+        <x:v>54.75</x:v>
+      </x:c>
+      <x:c r="C113" s="0">
+        <x:v>-4.25</x:v>
+      </x:c>
+      <x:c r="D113" s="0" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="B113" s="0">
-        <x:v>31.36</x:v>
-      </x:c>
-      <x:c r="C113" s="0">
-        <x:v>0.18</x:v>
-      </x:c>
-      <x:c r="D113" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
       <x:c r="E113" s="0">
-        <x:v>10567948</x:v>
+        <x:v>22928077</x:v>
       </x:c>
       <x:c r="F113" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G113" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H113" s="0">
-        <x:v>0</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I113" s="0">
-        <x:v>0</x:v>
+        <x:v>0.2378</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:9">
       <x:c r="A114" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B114" s="0">
-        <x:v>95.2</x:v>
+        <x:v>30.02</x:v>
       </x:c>
       <x:c r="C114" s="0">
-        <x:v>8.65</x:v>
+        <x:v>-1.34</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E114" s="0">
-        <x:v>8300000</x:v>
+        <x:v>547462013</x:v>
       </x:c>
       <x:c r="F114" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G114" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H114" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>0.1228</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:9">
       <x:c r="A115" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B115" s="0">
-        <x:v>61.35</x:v>
+        <x:v>30.02</x:v>
       </x:c>
       <x:c r="C115" s="0">
+        <x:v>-1.34</x:v>
+      </x:c>
+      <x:c r="D115" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="E115" s="0">
+        <x:v>10567948</x:v>
+      </x:c>
+      <x:c r="F115" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G115" s="0">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D115" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="E115" s="0">
-        <x:v>3000000</x:v>
-      </x:c>
-      <x:c r="F115" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G115" s="0">
-        <x:v>2025.12</x:v>
-      </x:c>
       <x:c r="H115" s="0">
-        <x:v>20597209000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I115" s="0">
-        <x:v>0.0064</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:9">
       <x:c r="A116" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B116" s="0">
+        <x:v>95.5</x:v>
+      </x:c>
+      <x:c r="C116" s="0">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="D116" s="0" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="B116" s="0">
-        <x:v>38.66</x:v>
-      </x:c>
-      <x:c r="C116" s="0">
-        <x:v>-1.84</x:v>
-      </x:c>
-      <x:c r="D116" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
       <x:c r="E116" s="0">
-        <x:v>26640000</x:v>
+        <x:v>8300000</x:v>
       </x:c>
       <x:c r="F116" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G116" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H116" s="0">
-        <x:v>3277373640</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I116" s="0">
-        <x:v>0.356</x:v>
+        <x:v>0.1228</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:9">
       <x:c r="A117" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B117" s="0">
-        <x:v>6.55</x:v>
+        <x:v>60.7</x:v>
       </x:c>
       <x:c r="C117" s="0">
-        <x:v>-0.07</x:v>
+        <x:v>-0.65</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E117" s="0">
-        <x:v>13107198</x:v>
+        <x:v>3000000</x:v>
       </x:c>
       <x:c r="F117" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G117" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H117" s="0">
-        <x:v>1627872951</x:v>
+        <x:v>20597209000</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>0.0081</x:v>
+        <x:v>0.0064</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:9">
       <x:c r="A118" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B118" s="0">
-        <x:v>95.2</x:v>
+        <x:v>40.7</x:v>
       </x:c>
       <x:c r="C118" s="0">
-        <x:v>8.65</x:v>
+        <x:v>2.04</x:v>
       </x:c>
       <x:c r="D118" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E118" s="0">
-        <x:v>237500000</x:v>
+        <x:v>26640000</x:v>
       </x:c>
       <x:c r="F118" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G118" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H118" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>3277373640</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>0.0679</x:v>
+        <x:v>0.356</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:9">
       <x:c r="A119" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B119" s="0">
-        <x:v>63.3</x:v>
+        <x:v>6.13</x:v>
       </x:c>
       <x:c r="C119" s="0">
-        <x:v>-2.7</x:v>
+        <x:v>-0.42</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E119" s="0">
-        <x:v>147892538</x:v>
+        <x:v>13107198</x:v>
       </x:c>
       <x:c r="F119" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G119" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H119" s="0">
-        <x:v>7257990064</x:v>
+        <x:v>1627872951</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>0.0204</x:v>
+        <x:v>0.0081</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:9">
       <x:c r="A120" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B120" s="0">
-        <x:v>58.8</x:v>
+        <x:v>95.5</x:v>
       </x:c>
       <x:c r="C120" s="0">
-        <x:v>1.15</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
         <x:v>102</x:v>
       </x:c>
       <x:c r="E120" s="0">
-        <x:v>988848</x:v>
+        <x:v>237500000</x:v>
       </x:c>
       <x:c r="F120" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G120" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H120" s="0">
-        <x:v>12999679000</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>0.0033</x:v>
+        <x:v>0.0679</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:9">
       <x:c r="A121" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B121" s="0">
-        <x:v>94.85</x:v>
+        <x:v>61.1</x:v>
       </x:c>
       <x:c r="C121" s="0">
-        <x:v>8.6</x:v>
+        <x:v>-2.2</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E121" s="0">
-        <x:v>47300000</x:v>
+        <x:v>147892538</x:v>
       </x:c>
       <x:c r="F121" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G121" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H121" s="0">
-        <x:v>10597063406</x:v>
+        <x:v>7257990064</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>0.2309</x:v>
+        <x:v>0.0204</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:9">
       <x:c r="A122" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B122" s="0">
-        <x:v>4.11</x:v>
+        <x:v>59.6</x:v>
       </x:c>
       <x:c r="C122" s="0">
-        <x:v>-0.17</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E122" s="0">
-        <x:v>758600</x:v>
+        <x:v>988848</x:v>
       </x:c>
       <x:c r="F122" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G122" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H122" s="0">
-        <x:v>1960468575</x:v>
+        <x:v>12999679000</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0.0033</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:9">
       <x:c r="A123" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B123" s="0">
-        <x:v>4.11</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C123" s="0">
-        <x:v>-0.17</x:v>
+        <x:v>5.15</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E123" s="0">
-        <x:v>758600</x:v>
+        <x:v>47300000</x:v>
       </x:c>
       <x:c r="F123" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G123" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H123" s="0">
-        <x:v>1960468575</x:v>
+        <x:v>10597063406</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>0.0004</x:v>
+        <x:v>0.2309</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:9">
       <x:c r="A124" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B124" s="0">
-        <x:v>1172</x:v>
+        <x:v>4.03</x:v>
       </x:c>
       <x:c r="C124" s="0">
-        <x:v>41</x:v>
+        <x:v>-0.08</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E124" s="0">
-        <x:v>576665</x:v>
+        <x:v>758600</x:v>
       </x:c>
       <x:c r="F124" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G124" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H124" s="0">
-        <x:v>1586603352</x:v>
+        <x:v>1960468575</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>0.0159</x:v>
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:9">
       <x:c r="A125" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B125" s="0">
+        <x:v>4.03</x:v>
+      </x:c>
+      <x:c r="C125" s="0">
+        <x:v>-0.08</x:v>
+      </x:c>
+      <x:c r="D125" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="E125" s="0">
+        <x:v>758600</x:v>
+      </x:c>
+      <x:c r="F125" s="0" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="B125" s="0">
-        <x:v>88.15</x:v>
-      </x:c>
-      <x:c r="C125" s="0">
-        <x:v>-5.1</x:v>
-      </x:c>
-      <x:c r="D125" s="0" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="E125" s="0">
-        <x:v>8000000</x:v>
-      </x:c>
-      <x:c r="F125" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="G125" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H125" s="0">
-        <x:v>20999579110</x:v>
+        <x:v>1960468575</x:v>
       </x:c>
       <x:c r="I125" s="0">
-        <x:v>0.0166</x:v>
+        <x:v>0.0004</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:9">
       <x:c r="A126" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B126" s="0">
-        <x:v>94</x:v>
+        <x:v>1245</x:v>
       </x:c>
       <x:c r="C126" s="0">
-        <x:v>-5.5</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E126" s="0">
-        <x:v>850000</x:v>
+        <x:v>576665</x:v>
       </x:c>
       <x:c r="F126" s="0" t="s">
         <x:v>11</x:v>
@@ -4453,230 +4456,230 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H126" s="0">
-        <x:v>1781510191</x:v>
+        <x:v>1586603352</x:v>
       </x:c>
       <x:c r="I126" s="0">
-        <x:v>0.0208</x:v>
+        <x:v>0.0159</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:9">
       <x:c r="A127" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B127" s="0">
-        <x:v>18.5</x:v>
+        <x:v>86.15</x:v>
       </x:c>
       <x:c r="C127" s="0">
-        <x:v>-0.87</x:v>
+        <x:v>-2</x:v>
       </x:c>
       <x:c r="D127" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E127" s="0">
-        <x:v>10149200</x:v>
+        <x:v>8000000</x:v>
       </x:c>
       <x:c r="F127" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G127" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H127" s="0">
-        <x:v>2020891371</x:v>
+        <x:v>20999579110</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>0.2601</x:v>
+        <x:v>0.0166</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:9">
       <x:c r="A128" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B128" s="0">
-        <x:v>135.4</x:v>
+        <x:v>90.75</x:v>
       </x:c>
       <x:c r="C128" s="0">
-        <x:v>-11.1</x:v>
+        <x:v>-3.25</x:v>
       </x:c>
       <x:c r="D128" s="0" t="s">
         <x:v>108</x:v>
       </x:c>
       <x:c r="E128" s="0">
-        <x:v>10500000</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="F128" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G128" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H128" s="0">
-        <x:v>1742315226</x:v>
+        <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>0.3121</x:v>
+        <x:v>0.0208</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:9">
       <x:c r="A129" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B129" s="0">
-        <x:v>94</x:v>
+        <x:v>17.29</x:v>
       </x:c>
       <x:c r="C129" s="0">
-        <x:v>-5.5</x:v>
+        <x:v>-1.21</x:v>
       </x:c>
       <x:c r="D129" s="0" t="s">
         <x:v>109</x:v>
       </x:c>
       <x:c r="E129" s="0">
-        <x:v>366956541</x:v>
+        <x:v>10149200</x:v>
       </x:c>
       <x:c r="F129" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G129" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H129" s="0">
-        <x:v>1781510191</x:v>
+        <x:v>2020891371</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>0.206</x:v>
+        <x:v>0.2601</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:9">
       <x:c r="A130" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B130" s="0">
-        <x:v>63.3</x:v>
+        <x:v>138.7</x:v>
       </x:c>
       <x:c r="C130" s="0">
-        <x:v>-2.7</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="D130" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E130" s="0">
-        <x:v>61158155</x:v>
+        <x:v>10500000</x:v>
       </x:c>
       <x:c r="F130" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G130" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H130" s="0">
-        <x:v>7257990064</x:v>
+        <x:v>1742315226</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>0.0084</x:v>
+        <x:v>0.3121</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:9">
       <x:c r="A131" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B131" s="0">
-        <x:v>125</x:v>
+        <x:v>90.75</x:v>
       </x:c>
       <x:c r="C131" s="0">
-        <x:v>7.7</x:v>
+        <x:v>-3.25</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
         <x:v>110</x:v>
       </x:c>
       <x:c r="E131" s="0">
-        <x:v>1000000</x:v>
+        <x:v>366956541</x:v>
       </x:c>
       <x:c r="F131" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G131" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H131" s="0">
-        <x:v>1688731509</x:v>
+        <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I131" s="0">
-        <x:v>0.0307</x:v>
+        <x:v>0.206</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:9">
       <x:c r="A132" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B132" s="0">
-        <x:v>125</x:v>
+        <x:v>61.1</x:v>
       </x:c>
       <x:c r="C132" s="0">
-        <x:v>7.7</x:v>
+        <x:v>-2.2</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E132" s="0">
-        <x:v>1050000</x:v>
+        <x:v>61158155</x:v>
       </x:c>
       <x:c r="F132" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G132" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H132" s="0">
-        <x:v>1688731509</x:v>
+        <x:v>7257990064</x:v>
       </x:c>
       <x:c r="I132" s="0">
-        <x:v>0.0271</x:v>
+        <x:v>0.0084</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:9">
       <x:c r="A133" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B133" s="0">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="C133" s="0">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D133" s="0" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="B133" s="0">
-        <x:v>45.46</x:v>
-      </x:c>
-      <x:c r="C133" s="0">
-        <x:v>0.46</x:v>
-      </x:c>
-      <x:c r="D133" s="0" t="s">
-        <x:v>112</x:v>
-      </x:c>
       <x:c r="E133" s="0">
-        <x:v>109053804</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="F133" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G133" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H133" s="0">
-        <x:v>1942491524</x:v>
+        <x:v>1688731509</x:v>
       </x:c>
       <x:c r="I133" s="0">
-        <x:v>0.0561</x:v>
+        <x:v>0.0307</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:9">
       <x:c r="A134" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B134" s="0">
-        <x:v>10.02</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C134" s="0">
-        <x:v>-0.37</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D134" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E134" s="0">
-        <x:v>62315119</x:v>
+        <x:v>1050000</x:v>
       </x:c>
       <x:c r="F134" s="0" t="s">
         <x:v>11</x:v>
@@ -4685,56 +4688,56 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H134" s="0">
-        <x:v>12026414029</x:v>
+        <x:v>1688731509</x:v>
       </x:c>
       <x:c r="I134" s="0">
-        <x:v>0.2257</x:v>
+        <x:v>0.0271</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:9">
       <x:c r="A135" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B135" s="0">
-        <x:v>269.5</x:v>
+        <x:v>42.5</x:v>
       </x:c>
       <x:c r="C135" s="0">
-        <x:v>-5.5</x:v>
+        <x:v>-2.96</x:v>
       </x:c>
       <x:c r="D135" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E135" s="0">
-        <x:v>896400</x:v>
+        <x:v>109053804</x:v>
       </x:c>
       <x:c r="F135" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G135" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H135" s="0">
-        <x:v>1364716456</x:v>
+        <x:v>1942491524</x:v>
       </x:c>
       <x:c r="I135" s="0">
-        <x:v>0.0285</x:v>
+        <x:v>0.0561</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:9">
       <x:c r="A136" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B136" s="0">
-        <x:v>726.5</x:v>
+        <x:v>9.32</x:v>
       </x:c>
       <x:c r="C136" s="0">
-        <x:v>66</x:v>
+        <x:v>-0.7</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E136" s="0">
-        <x:v>3370000</x:v>
+        <x:v>62315119</x:v>
       </x:c>
       <x:c r="F136" s="0" t="s">
         <x:v>11</x:v>
@@ -4743,56 +4746,56 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H136" s="0">
-        <x:v>1865697176</x:v>
+        <x:v>12026414029</x:v>
       </x:c>
       <x:c r="I136" s="0">
-        <x:v>0.0785</x:v>
+        <x:v>0.2257</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:9">
       <x:c r="A137" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B137" s="0">
-        <x:v>61.35</x:v>
+        <x:v>274.5</x:v>
       </x:c>
       <x:c r="C137" s="0">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D137" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E137" s="0">
-        <x:v>750561215</x:v>
+        <x:v>896400</x:v>
       </x:c>
       <x:c r="F137" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G137" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H137" s="0">
-        <x:v>16507905000</x:v>
+        <x:v>1364716456</x:v>
       </x:c>
       <x:c r="I137" s="0">
-        <x:v>0.0455</x:v>
+        <x:v>0.0285</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:9">
       <x:c r="A138" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B138" s="0">
-        <x:v>88.15</x:v>
+        <x:v>799</x:v>
       </x:c>
       <x:c r="C138" s="0">
-        <x:v>-5.1</x:v>
+        <x:v>72.5</x:v>
       </x:c>
       <x:c r="D138" s="0" t="s">
         <x:v>117</x:v>
       </x:c>
       <x:c r="E138" s="0">
-        <x:v>20000000</x:v>
+        <x:v>3370000</x:v>
       </x:c>
       <x:c r="F138" s="0" t="s">
         <x:v>11</x:v>
@@ -4801,56 +4804,56 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H138" s="0">
-        <x:v>20999579110</x:v>
+        <x:v>1865697176</x:v>
       </x:c>
       <x:c r="I138" s="0">
-        <x:v>0.0413</x:v>
+        <x:v>0.0785</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:9">
       <x:c r="A139" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B139" s="0">
+        <x:v>60.7</x:v>
+      </x:c>
+      <x:c r="C139" s="0">
+        <x:v>-0.65</x:v>
+      </x:c>
+      <x:c r="D139" s="0" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="B139" s="0">
-        <x:v>35.76</x:v>
-      </x:c>
-      <x:c r="C139" s="0">
-        <x:v>-0.9</x:v>
-      </x:c>
-      <x:c r="D139" s="0" t="s">
-        <x:v>119</x:v>
-      </x:c>
       <x:c r="E139" s="0">
-        <x:v>750000000</x:v>
+        <x:v>750561215</x:v>
       </x:c>
       <x:c r="F139" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G139" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H139" s="0">
-        <x:v>0</x:v>
+        <x:v>16507905000</x:v>
       </x:c>
       <x:c r="I139" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0455</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:9">
       <x:c r="A140" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B140" s="0">
-        <x:v>94.85</x:v>
+        <x:v>86.15</x:v>
       </x:c>
       <x:c r="C140" s="0">
-        <x:v>8.6</x:v>
+        <x:v>-2</x:v>
       </x:c>
       <x:c r="D140" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E140" s="0">
-        <x:v>111232418</x:v>
+        <x:v>20000000</x:v>
       </x:c>
       <x:c r="F140" s="0" t="s">
         <x:v>11</x:v>
@@ -4859,56 +4862,56 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H140" s="0">
-        <x:v>10597063406</x:v>
+        <x:v>20999579110</x:v>
       </x:c>
       <x:c r="I140" s="0">
-        <x:v>0.4554</x:v>
+        <x:v>0.0413</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:9">
       <x:c r="A141" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B141" s="0">
-        <x:v>40.2</x:v>
+        <x:v>34.98</x:v>
       </x:c>
       <x:c r="C141" s="0">
-        <x:v>0.2</x:v>
+        <x:v>-0.78</x:v>
       </x:c>
       <x:c r="D141" s="0" t="s">
         <x:v>120</x:v>
       </x:c>
       <x:c r="E141" s="0">
-        <x:v>51384996</x:v>
+        <x:v>750000000</x:v>
       </x:c>
       <x:c r="F141" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G141" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H141" s="0">
-        <x:v>11899043692</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I141" s="0">
-        <x:v>0.1873</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:9">
       <x:c r="A142" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B142" s="0">
-        <x:v>40.2</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C142" s="0">
-        <x:v>0.2</x:v>
+        <x:v>5.15</x:v>
       </x:c>
       <x:c r="D142" s="0" t="s">
         <x:v>120</x:v>
       </x:c>
       <x:c r="E142" s="0">
-        <x:v>3602451</x:v>
+        <x:v>111232418</x:v>
       </x:c>
       <x:c r="F142" s="0" t="s">
         <x:v>11</x:v>
@@ -4917,27 +4920,27 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H142" s="0">
-        <x:v>11899043692</x:v>
+        <x:v>10597063406</x:v>
       </x:c>
       <x:c r="I142" s="0">
-        <x:v>0.0131</x:v>
+        <x:v>0.4554</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:9">
       <x:c r="A143" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B143" s="0">
-        <x:v>40.2</x:v>
+        <x:v>38.34</x:v>
       </x:c>
       <x:c r="C143" s="0">
-        <x:v>0.2</x:v>
+        <x:v>-1.86</x:v>
       </x:c>
       <x:c r="D143" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E143" s="0">
-        <x:v>24226465</x:v>
+        <x:v>51384996</x:v>
       </x:c>
       <x:c r="F143" s="0" t="s">
         <x:v>11</x:v>
@@ -4949,256 +4952,256 @@
         <x:v>11899043692</x:v>
       </x:c>
       <x:c r="I143" s="0">
-        <x:v>0.0883</x:v>
+        <x:v>0.1873</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:9">
       <x:c r="A144" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B144" s="0">
-        <x:v>59</x:v>
+        <x:v>38.34</x:v>
       </x:c>
       <x:c r="C144" s="0">
-        <x:v>0.3</x:v>
+        <x:v>-1.86</x:v>
       </x:c>
       <x:c r="D144" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E144" s="0">
-        <x:v>12900000</x:v>
+        <x:v>3602451</x:v>
       </x:c>
       <x:c r="F144" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G144" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H144" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>11899043692</x:v>
       </x:c>
       <x:c r="I144" s="0">
-        <x:v>0.0052</x:v>
+        <x:v>0.0131</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:9">
       <x:c r="A145" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B145" s="0">
-        <x:v>333.25</x:v>
+        <x:v>38.34</x:v>
       </x:c>
       <x:c r="C145" s="0">
-        <x:v>-6.25</x:v>
+        <x:v>-1.86</x:v>
       </x:c>
       <x:c r="D145" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E145" s="0">
-        <x:v>53250000</x:v>
+        <x:v>24226465</x:v>
       </x:c>
       <x:c r="F145" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G145" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H145" s="0">
-        <x:v>24073631758</x:v>
+        <x:v>11899043692</x:v>
       </x:c>
       <x:c r="I145" s="0">
-        <x:v>0.115</x:v>
+        <x:v>0.0883</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:9">
       <x:c r="A146" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B146" s="0">
-        <x:v>31.36</x:v>
+        <x:v>54.75</x:v>
       </x:c>
       <x:c r="C146" s="0">
-        <x:v>0.18</x:v>
+        <x:v>-4.25</x:v>
       </x:c>
       <x:c r="D146" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E146" s="0">
-        <x:v>6860140</x:v>
+        <x:v>12900000</x:v>
       </x:c>
       <x:c r="F146" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G146" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H146" s="0">
-        <x:v>0</x:v>
+        <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I146" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0052</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:9">
       <x:c r="A147" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B147" s="0">
-        <x:v>95.2</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="C147" s="0">
-        <x:v>8.65</x:v>
+        <x:v>1.75</x:v>
       </x:c>
       <x:c r="D147" s="0" t="s">
         <x:v>121</x:v>
       </x:c>
       <x:c r="E147" s="0">
-        <x:v>230000000</x:v>
+        <x:v>53250000</x:v>
       </x:c>
       <x:c r="F147" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G147" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H147" s="0">
-        <x:v>2941310980</x:v>
+        <x:v>24073631758</x:v>
       </x:c>
       <x:c r="I147" s="0">
-        <x:v>0.0782</x:v>
+        <x:v>0.115</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:9">
       <x:c r="A148" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B148" s="0">
-        <x:v>726.5</x:v>
+        <x:v>30.02</x:v>
       </x:c>
       <x:c r="C148" s="0">
-        <x:v>66</x:v>
+        <x:v>-1.34</x:v>
       </x:c>
       <x:c r="D148" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E148" s="0">
-        <x:v>4700000</x:v>
+        <x:v>6860140</x:v>
       </x:c>
       <x:c r="F148" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G148" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H148" s="0">
-        <x:v>1865697176</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I148" s="0">
-        <x:v>0.1092</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:9">
       <x:c r="A149" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B149" s="0">
-        <x:v>31.36</x:v>
+        <x:v>95.5</x:v>
       </x:c>
       <x:c r="C149" s="0">
-        <x:v>0.18</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D149" s="0" t="s">
         <x:v>122</x:v>
       </x:c>
       <x:c r="E149" s="0">
-        <x:v>256000000</x:v>
+        <x:v>230000000</x:v>
       </x:c>
       <x:c r="F149" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G149" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H149" s="0">
-        <x:v>0</x:v>
+        <x:v>2941310980</x:v>
       </x:c>
       <x:c r="I149" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0782</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:9">
       <x:c r="A150" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B150" s="0">
-        <x:v>40.2</x:v>
+        <x:v>30.02</x:v>
       </x:c>
       <x:c r="C150" s="0">
-        <x:v>0.2</x:v>
+        <x:v>-1.34</x:v>
       </x:c>
       <x:c r="D150" s="0" t="s">
         <x:v>123</x:v>
       </x:c>
       <x:c r="E150" s="0">
-        <x:v>10724896</x:v>
+        <x:v>256000000</x:v>
       </x:c>
       <x:c r="F150" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G150" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H150" s="0">
-        <x:v>11899043692</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I150" s="0">
-        <x:v>0.039</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:9">
       <x:c r="A151" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B151" s="0">
-        <x:v>25.32</x:v>
+        <x:v>799</x:v>
       </x:c>
       <x:c r="C151" s="0">
-        <x:v>0.24</x:v>
+        <x:v>72.5</x:v>
       </x:c>
       <x:c r="D151" s="0" t="s">
         <x:v>123</x:v>
       </x:c>
       <x:c r="E151" s="0">
-        <x:v>31000000</x:v>
+        <x:v>4700000</x:v>
       </x:c>
       <x:c r="F151" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G151" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H151" s="0">
-        <x:v>813967617</x:v>
+        <x:v>1865697176</x:v>
       </x:c>
       <x:c r="I151" s="0">
-        <x:v>0.0381</x:v>
+        <x:v>0.1092</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:9">
       <x:c r="A152" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B152" s="0">
-        <x:v>50.25</x:v>
+        <x:v>38.34</x:v>
       </x:c>
       <x:c r="C152" s="0">
-        <x:v>-0.8</x:v>
+        <x:v>-1.86</x:v>
       </x:c>
       <x:c r="D152" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E152" s="0">
-        <x:v>13500000</x:v>
+        <x:v>10724896</x:v>
       </x:c>
       <x:c r="F152" s="0" t="s">
         <x:v>11</x:v>
@@ -5207,56 +5210,56 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H152" s="0">
-        <x:v>6483809984</x:v>
+        <x:v>11899043692</x:v>
       </x:c>
       <x:c r="I152" s="0">
-        <x:v>0.09</x:v>
+        <x:v>0.039</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:9">
       <x:c r="A153" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B153" s="0">
-        <x:v>45.46</x:v>
+        <x:v>24.52</x:v>
       </x:c>
       <x:c r="C153" s="0">
-        <x:v>0.46</x:v>
+        <x:v>-0.8</x:v>
       </x:c>
       <x:c r="D153" s="0" t="s">
         <x:v>124</x:v>
       </x:c>
       <x:c r="E153" s="0">
-        <x:v>29886357</x:v>
+        <x:v>31000000</x:v>
       </x:c>
       <x:c r="F153" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G153" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H153" s="0">
-        <x:v>1942491524</x:v>
+        <x:v>813967617</x:v>
       </x:c>
       <x:c r="I153" s="0">
-        <x:v>0.0154</x:v>
+        <x:v>0.0381</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:9">
       <x:c r="A154" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B154" s="0">
-        <x:v>419.25</x:v>
+        <x:v>52.15</x:v>
       </x:c>
       <x:c r="C154" s="0">
-        <x:v>-12.5</x:v>
+        <x:v>1.9</x:v>
       </x:c>
       <x:c r="D154" s="0" t="s">
         <x:v>124</x:v>
       </x:c>
       <x:c r="E154" s="0">
-        <x:v>171000000</x:v>
+        <x:v>13500000</x:v>
       </x:c>
       <x:c r="F154" s="0" t="s">
         <x:v>11</x:v>
@@ -5265,56 +5268,56 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H154" s="0">
-        <x:v>130147715000</x:v>
+        <x:v>6483809984</x:v>
       </x:c>
       <x:c r="I154" s="0">
-        <x:v>0.0568</x:v>
+        <x:v>0.09</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:9">
       <x:c r="A155" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B155" s="0">
-        <x:v>135.4</x:v>
+        <x:v>42.5</x:v>
       </x:c>
       <x:c r="C155" s="0">
-        <x:v>-11.1</x:v>
+        <x:v>-2.96</x:v>
       </x:c>
       <x:c r="D155" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E155" s="0">
-        <x:v>1890000</x:v>
+        <x:v>29886357</x:v>
       </x:c>
       <x:c r="F155" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G155" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H155" s="0">
-        <x:v>1742315226</x:v>
+        <x:v>1942491524</x:v>
       </x:c>
       <x:c r="I155" s="0">
-        <x:v>0.0549</x:v>
+        <x:v>0.0154</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:9">
       <x:c r="A156" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B156" s="0">
+        <x:v>412.75</x:v>
+      </x:c>
+      <x:c r="C156" s="0">
+        <x:v>-6.5</x:v>
+      </x:c>
+      <x:c r="D156" s="0" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="B156" s="0">
-        <x:v>13.59</x:v>
-      </x:c>
-      <x:c r="C156" s="0">
-        <x:v>-0.35</x:v>
-      </x:c>
-      <x:c r="D156" s="0" t="s">
-        <x:v>124</x:v>
-      </x:c>
       <x:c r="E156" s="0">
-        <x:v>892825</x:v>
+        <x:v>171000000</x:v>
       </x:c>
       <x:c r="F156" s="0" t="s">
         <x:v>11</x:v>
@@ -5323,39 +5326,39 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H156" s="0">
-        <x:v>3015442704</x:v>
+        <x:v>130147715000</x:v>
       </x:c>
       <x:c r="I156" s="0">
-        <x:v>0.0128</x:v>
+        <x:v>0.0568</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:9">
       <x:c r="A157" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B157" s="0">
-        <x:v>59</x:v>
+        <x:v>138.7</x:v>
       </x:c>
       <x:c r="C157" s="0">
-        <x:v>0.3</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="D157" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E157" s="0">
-        <x:v>361176</x:v>
+        <x:v>1890000</x:v>
       </x:c>
       <x:c r="F157" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G157" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H157" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>1742315226</x:v>
       </x:c>
       <x:c r="I157" s="0">
-        <x:v>0.0063</x:v>
+        <x:v>0.0549</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:9">
@@ -5363,16 +5366,16 @@
         <x:v>126</x:v>
       </x:c>
       <x:c r="B158" s="0">
-        <x:v>24.8</x:v>
+        <x:v>13.46</x:v>
       </x:c>
       <x:c r="C158" s="0">
-        <x:v>-1.24</x:v>
+        <x:v>-0.13</x:v>
       </x:c>
       <x:c r="D158" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E158" s="0">
-        <x:v>1060000</x:v>
+        <x:v>892825</x:v>
       </x:c>
       <x:c r="F158" s="0" t="s">
         <x:v>11</x:v>
@@ -5381,56 +5384,56 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H158" s="0">
-        <x:v>1194839266</x:v>
+        <x:v>3015442704</x:v>
       </x:c>
       <x:c r="I158" s="0">
-        <x:v>0.0384</x:v>
+        <x:v>0.0128</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:9">
       <x:c r="A159" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B159" s="0">
-        <x:v>52.35</x:v>
+        <x:v>54.75</x:v>
       </x:c>
       <x:c r="C159" s="0">
-        <x:v>-0.75</x:v>
+        <x:v>-4.25</x:v>
       </x:c>
       <x:c r="D159" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E159" s="0">
-        <x:v>259417800</x:v>
+        <x:v>361176</x:v>
       </x:c>
       <x:c r="F159" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G159" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H159" s="0">
-        <x:v>2741117556</x:v>
+        <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I159" s="0">
-        <x:v>0.0946</x:v>
+        <x:v>0.0063</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:9">
       <x:c r="A160" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B160" s="0">
-        <x:v>66.5</x:v>
+        <x:v>24.84</x:v>
       </x:c>
       <x:c r="C160" s="0">
-        <x:v>-5.25</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="D160" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E160" s="0">
-        <x:v>523788</x:v>
+        <x:v>1060000</x:v>
       </x:c>
       <x:c r="F160" s="0" t="s">
         <x:v>11</x:v>
@@ -5439,56 +5442,56 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H160" s="0">
-        <x:v>832031190</x:v>
+        <x:v>1194839266</x:v>
       </x:c>
       <x:c r="I160" s="0">
-        <x:v>0.0272</x:v>
+        <x:v>0.0384</x:v>
       </x:c>
     </x:row>
     <x:row r="161" spans="1:9">
       <x:c r="A161" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B161" s="0">
-        <x:v>66.5</x:v>
+        <x:v>52.45</x:v>
       </x:c>
       <x:c r="C161" s="0">
-        <x:v>-5.25</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="D161" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E161" s="0">
-        <x:v>1415270</x:v>
+        <x:v>259417800</x:v>
       </x:c>
       <x:c r="F161" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G161" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H161" s="0">
-        <x:v>832031190</x:v>
+        <x:v>2741117556</x:v>
       </x:c>
       <x:c r="I161" s="0">
-        <x:v>0.0736</x:v>
+        <x:v>0.0946</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:9">
       <x:c r="A162" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B162" s="0">
-        <x:v>88.15</x:v>
+        <x:v>63.1</x:v>
       </x:c>
       <x:c r="C162" s="0">
-        <x:v>-5.1</x:v>
+        <x:v>-3.4</x:v>
       </x:c>
       <x:c r="D162" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E162" s="0">
-        <x:v>25000000</x:v>
+        <x:v>523788</x:v>
       </x:c>
       <x:c r="F162" s="0" t="s">
         <x:v>11</x:v>
@@ -5497,27 +5500,27 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H162" s="0">
-        <x:v>20999579110</x:v>
+        <x:v>832031190</x:v>
       </x:c>
       <x:c r="I162" s="0">
-        <x:v>0.0515</x:v>
+        <x:v>0.0272</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:9">
       <x:c r="A163" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B163" s="0">
-        <x:v>6.55</x:v>
+        <x:v>63.1</x:v>
       </x:c>
       <x:c r="C163" s="0">
-        <x:v>-0.07</x:v>
+        <x:v>-3.4</x:v>
       </x:c>
       <x:c r="D163" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E163" s="0">
-        <x:v>25000</x:v>
+        <x:v>1415270</x:v>
       </x:c>
       <x:c r="F163" s="0" t="s">
         <x:v>11</x:v>
@@ -5526,143 +5529,143 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H163" s="0">
-        <x:v>1627872951</x:v>
+        <x:v>832031190</x:v>
       </x:c>
       <x:c r="I163" s="0">
-        <x:v>0.0007</x:v>
+        <x:v>0.0736</x:v>
       </x:c>
     </x:row>
     <x:row r="164" spans="1:9">
       <x:c r="A164" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B164" s="0">
-        <x:v>23.26</x:v>
+        <x:v>86.15</x:v>
       </x:c>
       <x:c r="C164" s="0">
-        <x:v>1.64</x:v>
+        <x:v>-2</x:v>
       </x:c>
       <x:c r="D164" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E164" s="0">
-        <x:v>1500000</x:v>
+        <x:v>25000000</x:v>
       </x:c>
       <x:c r="F164" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G164" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H164" s="0">
-        <x:v>774677961</x:v>
+        <x:v>20999579110</x:v>
       </x:c>
       <x:c r="I164" s="0">
-        <x:v>0.0019</x:v>
+        <x:v>0.0515</x:v>
       </x:c>
     </x:row>
     <x:row r="165" spans="1:9">
       <x:c r="A165" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B165" s="0">
-        <x:v>11.41</x:v>
+        <x:v>6.13</x:v>
       </x:c>
       <x:c r="C165" s="0">
-        <x:v>0.77</x:v>
+        <x:v>-0.42</x:v>
       </x:c>
       <x:c r="D165" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="E165" s="0">
-        <x:v>13833310</x:v>
+        <x:v>25000</x:v>
       </x:c>
       <x:c r="F165" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G165" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H165" s="0">
-        <x:v>9028523851</x:v>
+        <x:v>1627872951</x:v>
       </x:c>
       <x:c r="I165" s="0">
-        <x:v>0.0776</x:v>
+        <x:v>0.0007</x:v>
       </x:c>
     </x:row>
     <x:row r="166" spans="1:9">
       <x:c r="A166" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B166" s="0">
-        <x:v>76.8</x:v>
+        <x:v>20.94</x:v>
       </x:c>
       <x:c r="C166" s="0">
-        <x:v>0.3</x:v>
+        <x:v>-2.32</x:v>
       </x:c>
       <x:c r="D166" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="E166" s="0">
-        <x:v>3419000</x:v>
+        <x:v>1500000</x:v>
       </x:c>
       <x:c r="F166" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G166" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H166" s="0">
-        <x:v>3895315496</x:v>
+        <x:v>774677961</x:v>
       </x:c>
       <x:c r="I166" s="0">
-        <x:v>0.0379</x:v>
+        <x:v>0.0019</x:v>
       </x:c>
     </x:row>
     <x:row r="167" spans="1:9">
       <x:c r="A167" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B167" s="0">
-        <x:v>726.5</x:v>
+        <x:v>12.55</x:v>
       </x:c>
       <x:c r="C167" s="0">
-        <x:v>66</x:v>
+        <x:v>1.14</x:v>
       </x:c>
       <x:c r="D167" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="E167" s="0">
-        <x:v>3700000</x:v>
+        <x:v>13833310</x:v>
       </x:c>
       <x:c r="F167" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G167" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H167" s="0">
-        <x:v>1865697176</x:v>
+        <x:v>9028523851</x:v>
       </x:c>
       <x:c r="I167" s="0">
-        <x:v>0.0857</x:v>
+        <x:v>0.0776</x:v>
       </x:c>
     </x:row>
     <x:row r="168" spans="1:9">
       <x:c r="A168" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B168" s="0">
-        <x:v>50.25</x:v>
+        <x:v>72.1</x:v>
       </x:c>
       <x:c r="C168" s="0">
-        <x:v>-0.8</x:v>
+        <x:v>-4.7</x:v>
       </x:c>
       <x:c r="D168" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="E168" s="0">
-        <x:v>16000000</x:v>
+        <x:v>3419000</x:v>
       </x:c>
       <x:c r="F168" s="0" t="s">
         <x:v>11</x:v>
@@ -5671,27 +5674,27 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H168" s="0">
-        <x:v>6483809984</x:v>
+        <x:v>3895315496</x:v>
       </x:c>
       <x:c r="I168" s="0">
-        <x:v>0.1067</x:v>
+        <x:v>0.0379</x:v>
       </x:c>
     </x:row>
     <x:row r="169" spans="1:9">
       <x:c r="A169" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B169" s="0">
-        <x:v>59</x:v>
+        <x:v>52.15</x:v>
       </x:c>
       <x:c r="C169" s="0">
-        <x:v>0.3</x:v>
+        <x:v>1.9</x:v>
       </x:c>
       <x:c r="D169" s="0" t="s">
         <x:v>132</x:v>
       </x:c>
       <x:c r="E169" s="0">
-        <x:v>906840</x:v>
+        <x:v>16000000</x:v>
       </x:c>
       <x:c r="F169" s="0" t="s">
         <x:v>11</x:v>
@@ -5700,143 +5703,143 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H169" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>6483809984</x:v>
       </x:c>
       <x:c r="I169" s="0">
-        <x:v>0.0159</x:v>
+        <x:v>0.1067</x:v>
       </x:c>
     </x:row>
     <x:row r="170" spans="1:9">
       <x:c r="A170" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B170" s="0">
-        <x:v>3.56</x:v>
+        <x:v>799</x:v>
       </x:c>
       <x:c r="C170" s="0">
-        <x:v>0.05</x:v>
+        <x:v>72.5</x:v>
       </x:c>
       <x:c r="D170" s="0" t="s">
         <x:v>132</x:v>
       </x:c>
       <x:c r="E170" s="0">
-        <x:v>895039950</x:v>
+        <x:v>3700000</x:v>
       </x:c>
       <x:c r="F170" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G170" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H170" s="0">
-        <x:v>7382591324</x:v>
+        <x:v>1865697176</x:v>
       </x:c>
       <x:c r="I170" s="0">
-        <x:v>0.1212</x:v>
+        <x:v>0.0857</x:v>
       </x:c>
     </x:row>
     <x:row r="171" spans="1:9">
       <x:c r="A171" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B171" s="0">
-        <x:v>52.35</x:v>
+        <x:v>54.75</x:v>
       </x:c>
       <x:c r="C171" s="0">
-        <x:v>-0.75</x:v>
+        <x:v>-4.25</x:v>
       </x:c>
       <x:c r="D171" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="E171" s="0">
-        <x:v>575933040</x:v>
+        <x:v>906840</x:v>
       </x:c>
       <x:c r="F171" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G171" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H171" s="0">
-        <x:v>2741117556</x:v>
+        <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I171" s="0">
-        <x:v>0.2101</x:v>
+        <x:v>0.0159</x:v>
       </x:c>
     </x:row>
     <x:row r="172" spans="1:9">
       <x:c r="A172" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B172" s="0">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="C172" s="0">
+        <x:v>-0.06</x:v>
+      </x:c>
+      <x:c r="D172" s="0" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="B172" s="0">
-        <x:v>12.77</x:v>
-      </x:c>
-      <x:c r="C172" s="0">
-        <x:v>-0.24</x:v>
-      </x:c>
-      <x:c r="D172" s="0" t="s">
-        <x:v>132</x:v>
-      </x:c>
       <x:c r="E172" s="0">
-        <x:v>559000</x:v>
+        <x:v>895039950</x:v>
       </x:c>
       <x:c r="F172" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G172" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H172" s="0">
-        <x:v>2865374550</x:v>
+        <x:v>7382591324</x:v>
       </x:c>
       <x:c r="I172" s="0">
-        <x:v>0.0084</x:v>
+        <x:v>0.1212</x:v>
       </x:c>
     </x:row>
     <x:row r="173" spans="1:9">
       <x:c r="A173" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B173" s="0">
-        <x:v>61.35</x:v>
+        <x:v>52.45</x:v>
       </x:c>
       <x:c r="C173" s="0">
-        <x:v>0</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="D173" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="E173" s="0">
-        <x:v>8900056</x:v>
+        <x:v>575933040</x:v>
       </x:c>
       <x:c r="F173" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G173" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H173" s="0">
-        <x:v>16507905000</x:v>
+        <x:v>2741117556</x:v>
       </x:c>
       <x:c r="I173" s="0">
-        <x:v>0.0233</x:v>
+        <x:v>0.2101</x:v>
       </x:c>
     </x:row>
     <x:row r="174" spans="1:9">
       <x:c r="A174" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B174" s="0">
-        <x:v>333.25</x:v>
+        <x:v>12.85</x:v>
       </x:c>
       <x:c r="C174" s="0">
-        <x:v>-6.25</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="D174" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="E174" s="0">
-        <x:v>164306000</x:v>
+        <x:v>559000</x:v>
       </x:c>
       <x:c r="F174" s="0" t="s">
         <x:v>11</x:v>
@@ -5845,27 +5848,27 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H174" s="0">
-        <x:v>24073631758</x:v>
+        <x:v>2865374550</x:v>
       </x:c>
       <x:c r="I174" s="0">
-        <x:v>0.2943</x:v>
+        <x:v>0.0084</x:v>
       </x:c>
     </x:row>
     <x:row r="175" spans="1:9">
       <x:c r="A175" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B175" s="0">
-        <x:v>52.5</x:v>
+        <x:v>60.7</x:v>
       </x:c>
       <x:c r="C175" s="0">
-        <x:v>-1.8</x:v>
+        <x:v>-0.65</x:v>
       </x:c>
       <x:c r="D175" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="E175" s="0">
-        <x:v>275000</x:v>
+        <x:v>8900056</x:v>
       </x:c>
       <x:c r="F175" s="0" t="s">
         <x:v>11</x:v>
@@ -5874,56 +5877,56 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H175" s="0">
-        <x:v>580678850</x:v>
+        <x:v>16507905000</x:v>
       </x:c>
       <x:c r="I175" s="0">
-        <x:v>0.0204</x:v>
+        <x:v>0.0233</x:v>
       </x:c>
     </x:row>
     <x:row r="176" spans="1:9">
       <x:c r="A176" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B176" s="0">
-        <x:v>52.35</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="C176" s="0">
-        <x:v>-0.75</x:v>
+        <x:v>1.75</x:v>
       </x:c>
       <x:c r="D176" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="E176" s="0">
-        <x:v>231651480</x:v>
+        <x:v>164306000</x:v>
       </x:c>
       <x:c r="F176" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G176" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H176" s="0">
-        <x:v>2741117556</x:v>
+        <x:v>24073631758</x:v>
       </x:c>
       <x:c r="I176" s="0">
-        <x:v>0.0845</x:v>
+        <x:v>0.2943</x:v>
       </x:c>
     </x:row>
     <x:row r="177" spans="1:9">
       <x:c r="A177" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B177" s="0">
-        <x:v>16</x:v>
+        <x:v>51.75</x:v>
       </x:c>
       <x:c r="C177" s="0">
-        <x:v>-0.98</x:v>
+        <x:v>-0.75</x:v>
       </x:c>
       <x:c r="D177" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="E177" s="0">
-        <x:v>31860000</x:v>
+        <x:v>275000</x:v>
       </x:c>
       <x:c r="F177" s="0" t="s">
         <x:v>11</x:v>
@@ -5932,230 +5935,230 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H177" s="0">
-        <x:v>3025063909</x:v>
+        <x:v>580678850</x:v>
       </x:c>
       <x:c r="I177" s="0">
-        <x:v>0.4539</x:v>
+        <x:v>0.0204</x:v>
       </x:c>
     </x:row>
     <x:row r="178" spans="1:9">
       <x:c r="A178" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B178" s="0">
-        <x:v>94</x:v>
+        <x:v>52.45</x:v>
       </x:c>
       <x:c r="C178" s="0">
-        <x:v>-5.5</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="D178" s="0" t="s">
         <x:v>137</x:v>
       </x:c>
       <x:c r="E178" s="0">
-        <x:v>41650000</x:v>
+        <x:v>231651480</x:v>
       </x:c>
       <x:c r="F178" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G178" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H178" s="0">
-        <x:v>1781510191</x:v>
+        <x:v>2741117556</x:v>
       </x:c>
       <x:c r="I178" s="0">
-        <x:v>0.0234</x:v>
+        <x:v>0.0845</x:v>
       </x:c>
     </x:row>
     <x:row r="179" spans="1:9">
       <x:c r="A179" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B179" s="0">
-        <x:v>18.5</x:v>
+        <x:v>17.6</x:v>
       </x:c>
       <x:c r="C179" s="0">
-        <x:v>-0.87</x:v>
+        <x:v>1.6</x:v>
       </x:c>
       <x:c r="D179" s="0" t="s">
         <x:v>138</x:v>
       </x:c>
       <x:c r="E179" s="0">
-        <x:v>815000</x:v>
+        <x:v>31860000</x:v>
       </x:c>
       <x:c r="F179" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G179" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H179" s="0">
-        <x:v>2020891371</x:v>
+        <x:v>3025063909</x:v>
       </x:c>
       <x:c r="I179" s="0">
-        <x:v>0.0202</x:v>
+        <x:v>0.4539</x:v>
       </x:c>
     </x:row>
     <x:row r="180" spans="1:9">
       <x:c r="A180" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B180" s="0">
-        <x:v>95.2</x:v>
+        <x:v>90.75</x:v>
       </x:c>
       <x:c r="C180" s="0">
-        <x:v>8.65</x:v>
+        <x:v>-3.25</x:v>
       </x:c>
       <x:c r="D180" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="E180" s="0">
-        <x:v>8300000</x:v>
+        <x:v>41650000</x:v>
       </x:c>
       <x:c r="F180" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G180" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H180" s="0">
-        <x:v>2941310980</x:v>
+        <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I180" s="0">
-        <x:v>0.1417</x:v>
+        <x:v>0.0234</x:v>
       </x:c>
     </x:row>
     <x:row r="181" spans="1:9">
       <x:c r="A181" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B181" s="0">
-        <x:v>4.39</x:v>
+        <x:v>17.29</x:v>
       </x:c>
       <x:c r="C181" s="0">
-        <x:v>-0.06</x:v>
+        <x:v>-1.21</x:v>
       </x:c>
       <x:c r="D181" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="E181" s="0">
-        <x:v>13000000</x:v>
+        <x:v>815000</x:v>
       </x:c>
       <x:c r="F181" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G181" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H181" s="0">
-        <x:v>1416740879</x:v>
+        <x:v>2020891371</x:v>
       </x:c>
       <x:c r="I181" s="0">
-        <x:v>0.4613</x:v>
+        <x:v>0.0202</x:v>
       </x:c>
     </x:row>
     <x:row r="182" spans="1:9">
       <x:c r="A182" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B182" s="0">
-        <x:v>135.4</x:v>
+        <x:v>95.5</x:v>
       </x:c>
       <x:c r="C182" s="0">
-        <x:v>-11.1</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D182" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="E182" s="0">
-        <x:v>1999793</x:v>
+        <x:v>8300000</x:v>
       </x:c>
       <x:c r="F182" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G182" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H182" s="0">
-        <x:v>1742315226</x:v>
+        <x:v>2941310980</x:v>
       </x:c>
       <x:c r="I182" s="0">
-        <x:v>0.0494</x:v>
+        <x:v>0.1417</x:v>
       </x:c>
     </x:row>
     <x:row r="183" spans="1:9">
       <x:c r="A183" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B183" s="0">
-        <x:v>59</x:v>
+        <x:v>4.23</x:v>
       </x:c>
       <x:c r="C183" s="0">
-        <x:v>0.3</x:v>
+        <x:v>-0.16</x:v>
       </x:c>
       <x:c r="D183" s="0" t="s">
         <x:v>142</x:v>
       </x:c>
       <x:c r="E183" s="0">
-        <x:v>1859145</x:v>
+        <x:v>13000000</x:v>
       </x:c>
       <x:c r="F183" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G183" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H183" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>1416740879</x:v>
       </x:c>
       <x:c r="I183" s="0">
-        <x:v>0.0324</x:v>
+        <x:v>0.4613</x:v>
       </x:c>
     </x:row>
     <x:row r="184" spans="1:9">
       <x:c r="A184" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B184" s="0">
-        <x:v>3.56</x:v>
+        <x:v>138.7</x:v>
       </x:c>
       <x:c r="C184" s="0">
-        <x:v>0.05</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="D184" s="0" t="s">
         <x:v>143</x:v>
       </x:c>
       <x:c r="E184" s="0">
-        <x:v>689661000</x:v>
+        <x:v>1999793</x:v>
       </x:c>
       <x:c r="F184" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G184" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H184" s="0">
-        <x:v>7382591324</x:v>
+        <x:v>1742315226</x:v>
       </x:c>
       <x:c r="I184" s="0">
-        <x:v>0.0934</x:v>
+        <x:v>0.0494</x:v>
       </x:c>
     </x:row>
     <x:row r="185" spans="1:9">
       <x:c r="A185" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B185" s="0">
-        <x:v>59</x:v>
+        <x:v>54.75</x:v>
       </x:c>
       <x:c r="C185" s="0">
-        <x:v>0.3</x:v>
+        <x:v>-4.25</x:v>
       </x:c>
       <x:c r="D185" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="E185" s="0">
-        <x:v>1902000</x:v>
+        <x:v>1859145</x:v>
       </x:c>
       <x:c r="F185" s="0" t="s">
         <x:v>11</x:v>
@@ -6167,53 +6170,53 @@
         <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I185" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0324</x:v>
       </x:c>
     </x:row>
     <x:row r="186" spans="1:9">
       <x:c r="A186" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B186" s="0">
-        <x:v>94</x:v>
+        <x:v>3.5</x:v>
       </x:c>
       <x:c r="C186" s="0">
-        <x:v>-5.5</x:v>
+        <x:v>-0.06</x:v>
       </x:c>
       <x:c r="D186" s="0" t="s">
         <x:v>144</x:v>
       </x:c>
       <x:c r="E186" s="0">
-        <x:v>56520000</x:v>
+        <x:v>689661000</x:v>
       </x:c>
       <x:c r="F186" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G186" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H186" s="0">
-        <x:v>1781510191</x:v>
+        <x:v>7382591324</x:v>
       </x:c>
       <x:c r="I186" s="0">
-        <x:v>0.0317</x:v>
+        <x:v>0.0934</x:v>
       </x:c>
     </x:row>
     <x:row r="187" spans="1:9">
       <x:c r="A187" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B187" s="0">
-        <x:v>94</x:v>
+        <x:v>54.75</x:v>
       </x:c>
       <x:c r="C187" s="0">
-        <x:v>-5.5</x:v>
+        <x:v>-4.25</x:v>
       </x:c>
       <x:c r="D187" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E187" s="0">
-        <x:v>888325</x:v>
+        <x:v>1902000</x:v>
       </x:c>
       <x:c r="F187" s="0" t="s">
         <x:v>11</x:v>
@@ -6222,7 +6225,7 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H187" s="0">
-        <x:v>1781510191</x:v>
+        <x:v>2467243928</x:v>
       </x:c>
       <x:c r="I187" s="0">
         <x:v>0</x:v>
@@ -6230,77 +6233,77 @@
     </x:row>
     <x:row r="188" spans="1:9">
       <x:c r="A188" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B188" s="0">
-        <x:v>11.41</x:v>
+        <x:v>90.75</x:v>
       </x:c>
       <x:c r="C188" s="0">
-        <x:v>0.77</x:v>
+        <x:v>-3.25</x:v>
       </x:c>
       <x:c r="D188" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E188" s="0">
-        <x:v>5581810</x:v>
+        <x:v>56520000</x:v>
       </x:c>
       <x:c r="F188" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G188" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H188" s="0">
-        <x:v>9028523851</x:v>
+        <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I188" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0317</x:v>
       </x:c>
     </x:row>
     <x:row r="189" spans="1:9">
       <x:c r="A189" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B189" s="0">
-        <x:v>59</x:v>
+        <x:v>90.75</x:v>
       </x:c>
       <x:c r="C189" s="0">
-        <x:v>0.3</x:v>
+        <x:v>-3.25</x:v>
       </x:c>
       <x:c r="D189" s="0" t="s">
         <x:v>145</x:v>
       </x:c>
       <x:c r="E189" s="0">
-        <x:v>504000000</x:v>
+        <x:v>888325</x:v>
       </x:c>
       <x:c r="F189" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G189" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H189" s="0">
-        <x:v>2467243928</x:v>
+        <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I189" s="0">
-        <x:v>0.2043</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="190" spans="1:9">
       <x:c r="A190" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B190" s="0">
-        <x:v>333.25</x:v>
+        <x:v>12.55</x:v>
       </x:c>
       <x:c r="C190" s="0">
-        <x:v>-6.25</x:v>
+        <x:v>1.14</x:v>
       </x:c>
       <x:c r="D190" s="0" t="s">
         <x:v>145</x:v>
       </x:c>
       <x:c r="E190" s="0">
-        <x:v>21500032</x:v>
+        <x:v>5581810</x:v>
       </x:c>
       <x:c r="F190" s="0" t="s">
         <x:v>11</x:v>
@@ -6309,38 +6312,96 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H190" s="0">
-        <x:v>24073631758</x:v>
+        <x:v>9028523851</x:v>
       </x:c>
       <x:c r="I190" s="0">
-        <x:v>0.0383</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="191" spans="1:9">
       <x:c r="A191" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B191" s="0">
+        <x:v>54.75</x:v>
+      </x:c>
+      <x:c r="C191" s="0">
+        <x:v>-4.25</x:v>
+      </x:c>
+      <x:c r="D191" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="E191" s="0">
+        <x:v>504000000</x:v>
+      </x:c>
+      <x:c r="F191" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G191" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H191" s="0">
+        <x:v>2467243928</x:v>
+      </x:c>
+      <x:c r="I191" s="0">
+        <x:v>0.2043</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192" spans="1:9">
+      <x:c r="A192" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="B191" s="0">
-        <x:v>1172</x:v>
-      </x:c>
-      <x:c r="C191" s="0">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D191" s="0" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="E191" s="0">
+      <x:c r="B192" s="0">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="C192" s="0">
+        <x:v>1.75</x:v>
+      </x:c>
+      <x:c r="D192" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="E192" s="0">
+        <x:v>21500032</x:v>
+      </x:c>
+      <x:c r="F192" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G192" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H192" s="0">
+        <x:v>24073631758</x:v>
+      </x:c>
+      <x:c r="I192" s="0">
+        <x:v>0.0383</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193" spans="1:9">
+      <x:c r="A193" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B193" s="0">
+        <x:v>1245</x:v>
+      </x:c>
+      <x:c r="C193" s="0">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D193" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="E193" s="0">
         <x:v>6455151</x:v>
       </x:c>
-      <x:c r="F191" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G191" s="0">
-        <x:v>2025.09</x:v>
-      </x:c>
-      <x:c r="H191" s="0">
+      <x:c r="F193" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G193" s="0">
+        <x:v>2025.09</x:v>
+      </x:c>
+      <x:c r="H193" s="0">
         <x:v>1586603352</x:v>
       </x:c>
-      <x:c r="I191" s="0">
+      <x:c r="I193" s="0">
         <x:v>0.1745</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/yeni-is-anlasmalari/data/yeni-is-anlasmalari.xlsx
+++ b/app/borsa/yeni-is-anlasmalari/data/yeni-is-anlasmalari.xlsx
@@ -46,10 +46,13 @@
     <x:t>SDTTR</x:t>
   </x:si>
   <x:si>
+    <x:t>2026-05-14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>USD</x:t>
+  </x:si>
+  <x:si>
     <x:t>2026-05-13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>USD</x:t>
   </x:si>
   <x:si>
     <x:t>YEOTK</x:t>
@@ -805,7 +808,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I193"/>
+  <x:dimension ref="A1:I194"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -842,16 +845,16 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>274.5</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>5</x:v>
+        <x:v>-9.5</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>6450000</x:v>
+        <x:v>562500</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
         <x:v>11</x:v>
@@ -863,24 +866,24 @@
         <x:v>2443327017</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>0.1197</x:v>
+        <x:v>0.0104</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
       <x:c r="A3" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B3" s="0">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="C3" s="0">
+        <x:v>-9.5</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B3" s="0">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="C3" s="0">
-        <x:v>5.15</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
       <x:c r="E3" s="0">
-        <x:v>16093186</x:v>
+        <x:v>6450000</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
         <x:v>11</x:v>
@@ -889,27 +892,27 @@
         <x:v>2026.03</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>18658831210</x:v>
+        <x:v>2443327017</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>0.0391</x:v>
+        <x:v>0.1197</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
       <x:c r="A4" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>274.5</x:v>
+        <x:v>101.5</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>5</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>4950000</x:v>
+        <x:v>16093186</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
         <x:v>11</x:v>
@@ -918,27 +921,27 @@
         <x:v>2026.03</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>2443327017</x:v>
+        <x:v>18658831210</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>0.0916</x:v>
+        <x:v>0.0391</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
       <x:c r="A5" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>100</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>5.15</x:v>
+        <x:v>-9.5</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>1950000</x:v>
+        <x:v>4950000</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
         <x:v>11</x:v>
@@ -947,27 +950,27 @@
         <x:v>2026.03</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>18658831210</x:v>
+        <x:v>2443327017</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>0.0047</x:v>
+        <x:v>0.0916</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
       <x:c r="A6" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B6" s="0">
+        <x:v>101.5</x:v>
+      </x:c>
+      <x:c r="C6" s="0">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B6" s="0">
-        <x:v>12.55</x:v>
-      </x:c>
-      <x:c r="C6" s="0">
-        <x:v>1.14</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
       <x:c r="E6" s="0">
-        <x:v>10201876</x:v>
+        <x:v>1950000</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
         <x:v>11</x:v>
@@ -976,27 +979,27 @@
         <x:v>2026.03</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>9721975029</x:v>
+        <x:v>18658831210</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>0.0474</x:v>
+        <x:v>0.0047</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
       <x:c r="A7" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B7" s="0">
+        <x:v>12.77</x:v>
+      </x:c>
+      <x:c r="C7" s="0">
+        <x:v>0.22</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B7" s="0">
-        <x:v>28.06</x:v>
-      </x:c>
-      <x:c r="C7" s="0">
-        <x:v>-0.72</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
       <x:c r="E7" s="0">
-        <x:v>459000</x:v>
+        <x:v>10201876</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
         <x:v>11</x:v>
@@ -1005,10 +1008,10 @@
         <x:v>2026.03</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>7727514294</x:v>
+        <x:v>9721975029</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>0.0027</x:v>
+        <x:v>0.0474</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -1016,16 +1019,16 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>29.82</x:v>
+        <x:v>27.88</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>-0.88</x:v>
+        <x:v>-0.18</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>17776799</x:v>
+        <x:v>459000</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
         <x:v>11</x:v>
@@ -1034,10 +1037,10 @@
         <x:v>2026.03</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>433239437</x:v>
+        <x:v>7727514294</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>1.8545</x:v>
+        <x:v>0.0027</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -1045,45 +1048,45 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>22.8</x:v>
+        <x:v>29.58</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>-0.7</x:v>
+        <x:v>-0.24</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>1816317</x:v>
+        <x:v>17776799</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2026.03</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>2427624044</x:v>
+        <x:v>433239437</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>0.0338</x:v>
+        <x:v>1.8545</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
       <x:c r="A10" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B10" s="0">
+        <x:v>23.74</x:v>
+      </x:c>
+      <x:c r="C10" s="0">
+        <x:v>0.94</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B10" s="0">
-        <x:v>90.75</x:v>
-      </x:c>
-      <x:c r="C10" s="0">
-        <x:v>-3.25</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
       <x:c r="E10" s="0">
-        <x:v>3384000</x:v>
+        <x:v>1816317</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
         <x:v>11</x:v>
@@ -1092,10 +1095,10 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>2427624044</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>0.0627</x:v>
+        <x:v>0.0338</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -1103,16 +1106,16 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>4.03</x:v>
+        <x:v>96.8</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>-0.08</x:v>
+        <x:v>6.05</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>1178000</x:v>
+        <x:v>3384000</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
         <x:v>11</x:v>
@@ -1121,10 +1124,10 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>2875634546</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>0.0185</x:v>
+        <x:v>0.0627</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -1132,74 +1135,74 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>8.08</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>0.07</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>1180000</x:v>
+        <x:v>1178000</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G12" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>2322993973</x:v>
+        <x:v>2875634546</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>0.0268</x:v>
+        <x:v>0.0185</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
       <x:c r="A13" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B13" s="0">
+        <x:v>7.95</x:v>
+      </x:c>
+      <x:c r="C13" s="0">
+        <x:v>-0.13</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E13" s="0">
+        <x:v>1180000</x:v>
+      </x:c>
+      <x:c r="F13" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B13" s="0">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="C13" s="0">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D13" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="E13" s="0">
-        <x:v>1220000</x:v>
-      </x:c>
-      <x:c r="F13" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="G13" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>2988208362</x:v>
+        <x:v>2322993973</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>0.0184</x:v>
+        <x:v>0.0268</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
       <x:c r="A14" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>28.06</x:v>
+        <x:v>123.9</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>-0.72</x:v>
+        <x:v>-5.1</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>26910</x:v>
+        <x:v>1220000</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
         <x:v>11</x:v>
@@ -1208,27 +1211,27 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>7297855153</x:v>
+        <x:v>2988208362</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>0.0002</x:v>
+        <x:v>0.0184</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
       <x:c r="A15" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>54.75</x:v>
+        <x:v>27.88</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>-4.25</x:v>
+        <x:v>-0.18</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>2517084</x:v>
+        <x:v>26910</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
         <x:v>11</x:v>
@@ -1237,27 +1240,27 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>7297855153</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>0.0269</x:v>
+        <x:v>0.0002</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
       <x:c r="A16" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>22.8</x:v>
+        <x:v>59.55</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>-0.7</x:v>
+        <x:v>4.8</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>9600000</x:v>
+        <x:v>2517084</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
         <x:v>11</x:v>
@@ -1266,358 +1269,358 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>2427624044</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>0.1785</x:v>
+        <x:v>0.0269</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
       <x:c r="A17" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B17" s="0">
+        <x:v>23.74</x:v>
+      </x:c>
+      <x:c r="C17" s="0">
+        <x:v>0.94</x:v>
+      </x:c>
+      <x:c r="D17" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="B17" s="0">
-        <x:v>341.75</x:v>
-      </x:c>
-      <x:c r="C17" s="0">
-        <x:v>16.75</x:v>
-      </x:c>
-      <x:c r="D17" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="E17" s="0">
-        <x:v>9172451</x:v>
+        <x:v>9600000</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G17" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>709077088</x:v>
+        <x:v>2427624044</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>0.0129</x:v>
+        <x:v>0.1785</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
       <x:c r="A18" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B18" s="0">
+        <x:v>358</x:v>
+      </x:c>
+      <x:c r="C18" s="0">
+        <x:v>16.25</x:v>
+      </x:c>
+      <x:c r="D18" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E18" s="0">
+        <x:v>9172451</x:v>
+      </x:c>
+      <x:c r="F18" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="B18" s="0">
-        <x:v>38.34</x:v>
-      </x:c>
-      <x:c r="C18" s="0">
-        <x:v>-1.86</x:v>
-      </x:c>
-      <x:c r="D18" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E18" s="0">
-        <x:v>32493961</x:v>
-      </x:c>
-      <x:c r="F18" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="G18" s="0">
-        <x:v>2026.03</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>17386730041</x:v>
+        <x:v>709077088</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0129</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
       <x:c r="A19" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B19" s="0">
+        <x:v>39.46</x:v>
+      </x:c>
+      <x:c r="C19" s="0">
+        <x:v>1.12</x:v>
+      </x:c>
+      <x:c r="D19" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="B19" s="0">
-        <x:v>95.5</x:v>
-      </x:c>
-      <x:c r="C19" s="0">
-        <x:v>0.3</x:v>
-      </x:c>
-      <x:c r="D19" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
       <x:c r="E19" s="0">
-        <x:v>940002</x:v>
+        <x:v>32493961</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2026.03</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>17386730041</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>0.0121</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
       <x:c r="A20" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B20" s="0">
+        <x:v>97.3</x:v>
+      </x:c>
+      <x:c r="C20" s="0">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="D20" s="0" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="B20" s="0">
-        <x:v>138.7</x:v>
-      </x:c>
-      <x:c r="C20" s="0">
-        <x:v>3.3</x:v>
-      </x:c>
-      <x:c r="D20" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
       <x:c r="E20" s="0">
-        <x:v>920000</x:v>
+        <x:v>940002</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G20" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>3150489640</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>0.0154</x:v>
+        <x:v>0.0121</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
       <x:c r="A21" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>90.75</x:v>
+        <x:v>152.5</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>-3.25</x:v>
+        <x:v>13.8</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>12100000</x:v>
+        <x:v>920000</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G21" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>0.005</x:v>
+        <x:v>0.0154</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
       <x:c r="A22" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>412.75</x:v>
+        <x:v>96.8</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>-6.5</x:v>
+        <x:v>6.05</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>125100000</x:v>
+        <x:v>12100000</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>2026.03</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>184925592000</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>0.0304</x:v>
+        <x:v>0.005</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
       <x:c r="A23" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>12.55</x:v>
+        <x:v>415.5</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>1.14</x:v>
+        <x:v>2.75</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>32010000</x:v>
+        <x:v>125100000</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2026.03</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>10581001663</x:v>
+        <x:v>184925592000</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>0.1592</x:v>
+        <x:v>0.0304</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
       <x:c r="A24" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>28.06</x:v>
+        <x:v>12.77</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>-0.72</x:v>
+        <x:v>0.22</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>76650</x:v>
+        <x:v>32010000</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G24" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>7297855153</x:v>
+        <x:v>10581001663</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>0.0005</x:v>
+        <x:v>0.1592</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
       <x:c r="A25" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>138.7</x:v>
+        <x:v>27.88</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>3.3</x:v>
+        <x:v>-0.18</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>915000</x:v>
+        <x:v>76650</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G25" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>3150489640</x:v>
+        <x:v>7297855153</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>0.0153</x:v>
+        <x:v>0.0005</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
       <x:c r="A26" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>38.34</x:v>
+        <x:v>152.5</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>-1.86</x:v>
+        <x:v>13.8</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>2136645</x:v>
+        <x:v>915000</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>2026.03</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>17386730041</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>0.0055</x:v>
+        <x:v>0.0153</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
       <x:c r="A27" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B27" s="0">
+        <x:v>39.46</x:v>
+      </x:c>
+      <x:c r="C27" s="0">
+        <x:v>1.12</x:v>
+      </x:c>
+      <x:c r="D27" s="0" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="B27" s="0">
-        <x:v>5.27</x:v>
-      </x:c>
-      <x:c r="C27" s="0">
-        <x:v>-0.33</x:v>
-      </x:c>
-      <x:c r="D27" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
       <x:c r="E27" s="0">
-        <x:v>132077304</x:v>
+        <x:v>2136645</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2026.03</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>855070469</x:v>
+        <x:v>17386730041</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>0.1545</x:v>
+        <x:v>0.0055</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
       <x:c r="A28" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B28" s="0">
+        <x:v>5.31</x:v>
+      </x:c>
+      <x:c r="C28" s="0">
+        <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="D28" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="B28" s="0">
-        <x:v>335</x:v>
-      </x:c>
-      <x:c r="C28" s="0">
-        <x:v>1.75</x:v>
-      </x:c>
-      <x:c r="D28" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
       <x:c r="E28" s="0">
-        <x:v>51531000</x:v>
+        <x:v>132077304</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G28" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>35290767390</x:v>
+        <x:v>855070469</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>0.0656</x:v>
+        <x:v>0.1545</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1625,16 +1628,16 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>1245</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>73</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>950978</x:v>
+        <x:v>51531000</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
         <x:v>11</x:v>
@@ -1643,10 +1646,10 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>1883544167</x:v>
+        <x:v>35290767390</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>0.0227</x:v>
+        <x:v>0.0656</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1654,16 +1657,16 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>519.5</x:v>
+        <x:v>1276</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>-20</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>100000000</x:v>
+        <x:v>950978</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
         <x:v>11</x:v>
@@ -1672,172 +1675,172 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>71453576000</x:v>
+        <x:v>1883544167</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>0.0628</x:v>
+        <x:v>0.0227</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
       <x:c r="A31" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>95.5</x:v>
+        <x:v>534.5</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>0.3</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>286071819</x:v>
+        <x:v>100000000</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G31" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>71453576000</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>0.0818</x:v>
+        <x:v>0.0628</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
       <x:c r="A32" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>138.7</x:v>
+        <x:v>97.3</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>3.3</x:v>
+        <x:v>1.8</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>883793</x:v>
+        <x:v>286071819</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G32" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>3150489640</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>0.0148</x:v>
+        <x:v>0.0818</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
       <x:c r="A33" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>54.75</x:v>
+        <x:v>152.5</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>-4.25</x:v>
+        <x:v>13.8</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>606770</x:v>
+        <x:v>883793</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G33" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>0.0064</x:v>
+        <x:v>0.0148</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
       <x:c r="A34" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B34" s="0">
+        <x:v>59.55</x:v>
+      </x:c>
+      <x:c r="C34" s="0">
+        <x:v>4.8</x:v>
+      </x:c>
+      <x:c r="D34" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="B34" s="0">
-        <x:v>61.1</x:v>
-      </x:c>
-      <x:c r="C34" s="0">
-        <x:v>-2.2</x:v>
-      </x:c>
-      <x:c r="D34" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
       <x:c r="E34" s="0">
-        <x:v>505597002</x:v>
+        <x:v>606770</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G34" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>8121300519</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>0.0623</x:v>
+        <x:v>0.0064</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
       <x:c r="A35" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>54.75</x:v>
+        <x:v>65.05</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>-4.25</x:v>
+        <x:v>3.95</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>948000</x:v>
+        <x:v>505597002</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G35" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>8121300519</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>0.0101</x:v>
+        <x:v>0.0623</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
       <x:c r="A36" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>90.75</x:v>
+        <x:v>59.55</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>-3.25</x:v>
+        <x:v>4.8</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>622000</x:v>
+        <x:v>948000</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
         <x:v>11</x:v>
@@ -1846,10 +1849,10 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>0.0114</x:v>
+        <x:v>0.0101</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1857,74 +1860,74 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>4.03</x:v>
+        <x:v>96.8</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>-0.08</x:v>
+        <x:v>6.05</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>983000</x:v>
+        <x:v>622000</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G37" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>2875634546</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>0.018</x:v>
+        <x:v>0.0114</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
       <x:c r="A38" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B38" s="0">
+        <x:v>4.1</x:v>
+      </x:c>
+      <x:c r="C38" s="0">
+        <x:v>0.07</x:v>
+      </x:c>
+      <x:c r="D38" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="B38" s="0">
-        <x:v>72.1</x:v>
-      </x:c>
-      <x:c r="C38" s="0">
-        <x:v>-4.7</x:v>
-      </x:c>
-      <x:c r="D38" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
       <x:c r="E38" s="0">
-        <x:v>3421818</x:v>
+        <x:v>983000</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G38" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>5948036961</x:v>
+        <x:v>2875634546</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>0.0257</x:v>
+        <x:v>0.018</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
       <x:c r="A39" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B39" s="0">
+        <x:v>74.95</x:v>
+      </x:c>
+      <x:c r="C39" s="0">
+        <x:v>2.85</x:v>
+      </x:c>
+      <x:c r="D39" s="0" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="B39" s="0">
-        <x:v>47.46</x:v>
-      </x:c>
-      <x:c r="C39" s="0">
-        <x:v>-2.14</x:v>
-      </x:c>
-      <x:c r="D39" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
       <x:c r="E39" s="0">
-        <x:v>697435</x:v>
+        <x:v>3421818</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
         <x:v>11</x:v>
@@ -1933,27 +1936,27 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>4728937463</x:v>
+        <x:v>5948036961</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>0.0066</x:v>
+        <x:v>0.0257</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
       <x:c r="A40" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>100</x:v>
+        <x:v>52.2</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>5.15</x:v>
+        <x:v>4.74</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>4587145</x:v>
+        <x:v>697435</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
         <x:v>11</x:v>
@@ -1962,27 +1965,27 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>16733157490</x:v>
+        <x:v>4728937463</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>0.0123</x:v>
+        <x:v>0.0066</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
       <x:c r="A41" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B41" s="0">
+        <x:v>101.5</x:v>
+      </x:c>
+      <x:c r="C41" s="0">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="D41" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="B41" s="0">
-        <x:v>52.15</x:v>
-      </x:c>
-      <x:c r="C41" s="0">
-        <x:v>1.9</x:v>
-      </x:c>
-      <x:c r="D41" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
       <x:c r="E41" s="0">
-        <x:v>43200000</x:v>
+        <x:v>4587145</x:v>
       </x:c>
       <x:c r="F41" s="0" t="s">
         <x:v>11</x:v>
@@ -1991,175 +1994,175 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>8236540064</x:v>
+        <x:v>16733157490</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>0.2345</x:v>
+        <x:v>0.0123</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
       <x:c r="A42" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B42" s="0">
+        <x:v>55.85</x:v>
+      </x:c>
+      <x:c r="C42" s="0">
+        <x:v>3.7</x:v>
+      </x:c>
+      <x:c r="D42" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="B42" s="0">
-        <x:v>17.29</x:v>
-      </x:c>
-      <x:c r="C42" s="0">
-        <x:v>-1.21</x:v>
-      </x:c>
-      <x:c r="D42" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
       <x:c r="E42" s="0">
-        <x:v>1200000</x:v>
+        <x:v>43200000</x:v>
       </x:c>
       <x:c r="F42" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G42" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>3139850323</x:v>
+        <x:v>8236540064</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>0.0201</x:v>
+        <x:v>0.2345</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
       <x:c r="A43" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>61.1</x:v>
+        <x:v>17.26</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>-2.2</x:v>
+        <x:v>-0.03</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>247902522</x:v>
+        <x:v>1200000</x:v>
       </x:c>
       <x:c r="F43" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G43" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>8121300519</x:v>
+        <x:v>3139850323</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>0.0305</x:v>
+        <x:v>0.0201</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
       <x:c r="A44" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>54.75</x:v>
+        <x:v>65.05</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>-4.25</x:v>
+        <x:v>3.95</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>366000</x:v>
+        <x:v>247902522</x:v>
       </x:c>
       <x:c r="F44" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G44" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>8121300519</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>0.0039</x:v>
+        <x:v>0.0305</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
       <x:c r="A45" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>341.75</x:v>
+        <x:v>59.55</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>16.75</x:v>
+        <x:v>4.8</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>141051834</x:v>
+        <x:v>366000</x:v>
       </x:c>
       <x:c r="F45" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G45" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>709077088</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>0.1989</x:v>
+        <x:v>0.0039</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
       <x:c r="A46" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B46" s="0">
+        <x:v>358</x:v>
+      </x:c>
+      <x:c r="C46" s="0">
+        <x:v>16.25</x:v>
+      </x:c>
+      <x:c r="D46" s="0" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="B46" s="0">
-        <x:v>4.76</x:v>
-      </x:c>
-      <x:c r="C46" s="0">
-        <x:v>-0.18</x:v>
-      </x:c>
-      <x:c r="D46" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
       <x:c r="E46" s="0">
-        <x:v>5096500000</x:v>
+        <x:v>141051834</x:v>
       </x:c>
       <x:c r="F46" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>19538660616</x:v>
+        <x:v>709077088</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>0.2608</x:v>
+        <x:v>0.1989</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
       <x:c r="A47" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B47" s="0">
+        <x:v>4.91</x:v>
+      </x:c>
+      <x:c r="C47" s="0">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="D47" s="0" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="B47" s="0">
-        <x:v>4.76</x:v>
-      </x:c>
-      <x:c r="C47" s="0">
-        <x:v>-0.18</x:v>
-      </x:c>
-      <x:c r="D47" s="0" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="E47" s="0">
         <x:v>5096500000</x:v>
       </x:c>
       <x:c r="F47" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G47" s="0">
         <x:v>2025.09</x:v>
@@ -2173,48 +2176,48 @@
     </x:row>
     <x:row r="48" spans="1:9">
       <x:c r="A48" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B48" s="0">
+        <x:v>4.91</x:v>
+      </x:c>
+      <x:c r="C48" s="0">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="D48" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E48" s="0">
+        <x:v>5096500000</x:v>
+      </x:c>
+      <x:c r="F48" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="B48" s="0">
-        <x:v>38.34</x:v>
-      </x:c>
-      <x:c r="C48" s="0">
-        <x:v>-1.86</x:v>
-      </x:c>
-      <x:c r="D48" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E48" s="0">
-        <x:v>37500000</x:v>
-      </x:c>
-      <x:c r="F48" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="G48" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>16355768622</x:v>
+        <x:v>19538660616</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>0.1024</x:v>
+        <x:v>0.2608</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
       <x:c r="A49" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>274.5</x:v>
+        <x:v>39.46</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>5</x:v>
+        <x:v>1.12</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>2030000</x:v>
+        <x:v>37500000</x:v>
       </x:c>
       <x:c r="F49" s="0" t="s">
         <x:v>11</x:v>
@@ -2223,27 +2226,27 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>2159813703</x:v>
+        <x:v>16355768622</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>0.042</x:v>
+        <x:v>0.1024</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
       <x:c r="A50" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>100</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>5.15</x:v>
+        <x:v>-9.5</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>31146246</x:v>
+        <x:v>2030000</x:v>
       </x:c>
       <x:c r="F50" s="0" t="s">
         <x:v>11</x:v>
@@ -2252,59 +2255,59 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>16733157490</x:v>
+        <x:v>2159813703</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>0.0832</x:v>
+        <x:v>0.042</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
       <x:c r="A51" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B51" s="0">
+        <x:v>101.5</x:v>
+      </x:c>
+      <x:c r="C51" s="0">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="D51" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="B51" s="0">
-        <x:v>12.74</x:v>
-      </x:c>
-      <x:c r="C51" s="0">
-        <x:v>0.02</x:v>
-      </x:c>
-      <x:c r="D51" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
       <x:c r="E51" s="0">
-        <x:v>1000000</x:v>
+        <x:v>31146246</x:v>
       </x:c>
       <x:c r="F51" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G51" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>7221187888</x:v>
+        <x:v>16733157490</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>0.0001</x:v>
+        <x:v>0.0832</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
       <x:c r="A52" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>12.74</x:v>
+        <x:v>13.01</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0.27</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>3150000</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="F52" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G52" s="0">
         <x:v>2025.12</x:v>
@@ -2313,27 +2316,27 @@
         <x:v>7221187888</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>0.0227</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:9">
       <x:c r="A53" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B53" s="0">
-        <x:v>12.74</x:v>
+        <x:v>13.01</x:v>
       </x:c>
       <x:c r="C53" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0.27</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E53" s="0">
-        <x:v>2690000</x:v>
+        <x:v>3150000</x:v>
       </x:c>
       <x:c r="F53" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G53" s="0">
         <x:v>2025.12</x:v>
@@ -2342,24 +2345,24 @@
         <x:v>7221187888</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>0.0166</x:v>
+        <x:v>0.0227</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:9">
       <x:c r="A54" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B54" s="0">
-        <x:v>100</x:v>
+        <x:v>13.01</x:v>
       </x:c>
       <x:c r="C54" s="0">
-        <x:v>5.15</x:v>
+        <x:v>0.27</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E54" s="0">
-        <x:v>4103000</x:v>
+        <x:v>2690000</x:v>
       </x:c>
       <x:c r="F54" s="0" t="s">
         <x:v>11</x:v>
@@ -2368,233 +2371,233 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>16733157490</x:v>
+        <x:v>7221187888</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>0.0109</x:v>
+        <x:v>0.0166</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:9">
       <x:c r="A55" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B55" s="0">
-        <x:v>138.7</x:v>
+        <x:v>101.5</x:v>
       </x:c>
       <x:c r="C55" s="0">
-        <x:v>3.3</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E55" s="0">
-        <x:v>500000</x:v>
+        <x:v>4103000</x:v>
       </x:c>
       <x:c r="F55" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G55" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H55" s="0">
-        <x:v>3150489640</x:v>
+        <x:v>16733157490</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>0.0083</x:v>
+        <x:v>0.0109</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:9">
       <x:c r="A56" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B56" s="0">
-        <x:v>54.75</x:v>
+        <x:v>152.5</x:v>
       </x:c>
       <x:c r="C56" s="0">
-        <x:v>-4.25</x:v>
+        <x:v>13.8</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E56" s="0">
-        <x:v>872928</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="F56" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G56" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H56" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>3150489640</x:v>
       </x:c>
       <x:c r="I56" s="0">
-        <x:v>0.0092</x:v>
+        <x:v>0.0083</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:9">
       <x:c r="A57" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B57" s="0">
-        <x:v>90.75</x:v>
+        <x:v>59.55</x:v>
       </x:c>
       <x:c r="C57" s="0">
-        <x:v>-3.25</x:v>
+        <x:v>4.8</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
       <x:c r="E57" s="0">
-        <x:v>21250000</x:v>
+        <x:v>872928</x:v>
       </x:c>
       <x:c r="F57" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G57" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H57" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I57" s="0">
-        <x:v>0.0087</x:v>
+        <x:v>0.0092</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:9">
       <x:c r="A58" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B58" s="0">
-        <x:v>61.1</x:v>
+        <x:v>96.8</x:v>
       </x:c>
       <x:c r="C58" s="0">
-        <x:v>-2.2</x:v>
+        <x:v>6.05</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
         <x:v>60</x:v>
       </x:c>
       <x:c r="E58" s="0">
-        <x:v>67690912</x:v>
+        <x:v>21250000</x:v>
       </x:c>
       <x:c r="F58" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G58" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H58" s="0">
-        <x:v>8121300519</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I58" s="0">
-        <x:v>0.0083</x:v>
+        <x:v>0.0087</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:9">
       <x:c r="A59" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B59" s="0">
+        <x:v>65.05</x:v>
+      </x:c>
+      <x:c r="C59" s="0">
+        <x:v>3.95</x:v>
+      </x:c>
+      <x:c r="D59" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E59" s="0">
+        <x:v>67690912</x:v>
+      </x:c>
+      <x:c r="F59" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="B59" s="0">
-        <x:v>38.34</x:v>
-      </x:c>
-      <x:c r="C59" s="0">
-        <x:v>-1.86</x:v>
-      </x:c>
-      <x:c r="D59" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="E59" s="0">
-        <x:v>65458848</x:v>
-      </x:c>
-      <x:c r="F59" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="G59" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H59" s="0">
-        <x:v>16355768622</x:v>
+        <x:v>8121300519</x:v>
       </x:c>
       <x:c r="I59" s="0">
-        <x:v>0.1784</x:v>
+        <x:v>0.0083</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:9">
       <x:c r="A60" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B60" s="0">
+        <x:v>39.46</x:v>
+      </x:c>
+      <x:c r="C60" s="0">
+        <x:v>1.12</x:v>
+      </x:c>
+      <x:c r="D60" s="0" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="B60" s="0">
-        <x:v>24.52</x:v>
-      </x:c>
-      <x:c r="C60" s="0">
-        <x:v>-0.8</x:v>
-      </x:c>
-      <x:c r="D60" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
       <x:c r="E60" s="0">
-        <x:v>689500000</x:v>
+        <x:v>65458848</x:v>
       </x:c>
       <x:c r="F60" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G60" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H60" s="0">
-        <x:v>884571536</x:v>
+        <x:v>16355768622</x:v>
       </x:c>
       <x:c r="I60" s="0">
-        <x:v>0.7795</x:v>
+        <x:v>0.1784</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:9">
       <x:c r="A61" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B61" s="0">
-        <x:v>8.08</x:v>
+        <x:v>26.96</x:v>
       </x:c>
       <x:c r="C61" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>2.44</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E61" s="0">
-        <x:v>3024490</x:v>
+        <x:v>689500000</x:v>
       </x:c>
       <x:c r="F61" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G61" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H61" s="0">
-        <x:v>2322993973</x:v>
+        <x:v>884571536</x:v>
       </x:c>
       <x:c r="I61" s="0">
-        <x:v>0.0671</x:v>
+        <x:v>0.7795</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:9">
       <x:c r="A62" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B62" s="0">
-        <x:v>8.08</x:v>
+        <x:v>7.95</x:v>
       </x:c>
       <x:c r="C62" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>-0.13</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E62" s="0">
-        <x:v>4510336</x:v>
+        <x:v>3024490</x:v>
       </x:c>
       <x:c r="F62" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G62" s="0">
         <x:v>2025.12</x:v>
@@ -2603,24 +2606,24 @@
         <x:v>2322993973</x:v>
       </x:c>
       <x:c r="I62" s="0">
-        <x:v>0.0865</x:v>
+        <x:v>0.0671</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:9">
       <x:c r="A63" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B63" s="0">
-        <x:v>60.7</x:v>
+        <x:v>7.95</x:v>
       </x:c>
       <x:c r="C63" s="0">
-        <x:v>-0.65</x:v>
+        <x:v>-0.13</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E63" s="0">
-        <x:v>205000000</x:v>
+        <x:v>4510336</x:v>
       </x:c>
       <x:c r="F63" s="0" t="s">
         <x:v>11</x:v>
@@ -2629,175 +2632,175 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H63" s="0">
-        <x:v>20597209000</x:v>
+        <x:v>2322993973</x:v>
       </x:c>
       <x:c r="I63" s="0">
-        <x:v>0.4434</x:v>
+        <x:v>0.0865</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:9">
       <x:c r="A64" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B64" s="0">
+        <x:v>64.5</x:v>
+      </x:c>
+      <x:c r="C64" s="0">
+        <x:v>3.8</x:v>
+      </x:c>
+      <x:c r="D64" s="0" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="B64" s="0">
-        <x:v>311.5</x:v>
-      </x:c>
-      <x:c r="C64" s="0">
-        <x:v>-8.5</x:v>
-      </x:c>
-      <x:c r="D64" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
       <x:c r="E64" s="0">
-        <x:v>305000000</x:v>
+        <x:v>205000000</x:v>
       </x:c>
       <x:c r="F64" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G64" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H64" s="0">
-        <x:v>400439646</x:v>
+        <x:v>20597209000</x:v>
       </x:c>
       <x:c r="I64" s="0">
-        <x:v>0.7617</x:v>
+        <x:v>0.4434</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:9">
       <x:c r="A65" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B65" s="0">
-        <x:v>95.5</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="C65" s="0">
-        <x:v>0.3</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E65" s="0">
-        <x:v>11700000</x:v>
+        <x:v>305000000</x:v>
       </x:c>
       <x:c r="F65" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G65" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H65" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>400439646</x:v>
       </x:c>
       <x:c r="I65" s="0">
-        <x:v>0.1718</x:v>
+        <x:v>0.7617</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:9">
       <x:c r="A66" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B66" s="0">
-        <x:v>274.5</x:v>
+        <x:v>97.3</x:v>
       </x:c>
       <x:c r="C66" s="0">
-        <x:v>5</x:v>
+        <x:v>1.8</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E66" s="0">
-        <x:v>1900000</x:v>
+        <x:v>11700000</x:v>
       </x:c>
       <x:c r="F66" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G66" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H66" s="0">
-        <x:v>2159813703</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I66" s="0">
-        <x:v>0.0391</x:v>
+        <x:v>0.1718</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:9">
       <x:c r="A67" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B67" s="0">
-        <x:v>4.03</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="C67" s="0">
-        <x:v>-0.08</x:v>
+        <x:v>-9.5</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E67" s="0">
-        <x:v>1670000</x:v>
+        <x:v>1900000</x:v>
       </x:c>
       <x:c r="F67" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G67" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H67" s="0">
-        <x:v>2875634546</x:v>
+        <x:v>2159813703</x:v>
       </x:c>
       <x:c r="I67" s="0">
-        <x:v>0.0298</x:v>
+        <x:v>0.0391</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:9">
       <x:c r="A68" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B68" s="0">
-        <x:v>24.52</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="C68" s="0">
-        <x:v>-0.8</x:v>
+        <x:v>0.07</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
         <x:v>66</x:v>
       </x:c>
       <x:c r="E68" s="0">
-        <x:v>48895800</x:v>
+        <x:v>1670000</x:v>
       </x:c>
       <x:c r="F68" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G68" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H68" s="0">
-        <x:v>884571536</x:v>
+        <x:v>2875634546</x:v>
       </x:c>
       <x:c r="I68" s="0">
-        <x:v>0.0553</x:v>
+        <x:v>0.0298</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:9">
       <x:c r="A69" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B69" s="0">
-        <x:v>24.52</x:v>
+        <x:v>26.96</x:v>
       </x:c>
       <x:c r="C69" s="0">
-        <x:v>-0.8</x:v>
+        <x:v>2.44</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E69" s="0">
-        <x:v>689500000</x:v>
+        <x:v>48895800</x:v>
       </x:c>
       <x:c r="F69" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G69" s="0">
         <x:v>2025.12</x:v>
@@ -2806,36 +2809,36 @@
         <x:v>884571536</x:v>
       </x:c>
       <x:c r="I69" s="0">
-        <x:v>0.7795</x:v>
+        <x:v>0.0553</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:9">
       <x:c r="A70" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B70" s="0">
+        <x:v>26.96</x:v>
+      </x:c>
+      <x:c r="C70" s="0">
+        <x:v>2.44</x:v>
+      </x:c>
+      <x:c r="D70" s="0" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="B70" s="0">
-        <x:v>47.24</x:v>
-      </x:c>
-      <x:c r="C70" s="0">
-        <x:v>-1.34</x:v>
-      </x:c>
-      <x:c r="D70" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
       <x:c r="E70" s="0">
-        <x:v>3102911</x:v>
+        <x:v>689500000</x:v>
       </x:c>
       <x:c r="F70" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G70" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H70" s="0">
-        <x:v>2907014564</x:v>
+        <x:v>884571536</x:v>
       </x:c>
       <x:c r="I70" s="0">
-        <x:v>0.0475</x:v>
+        <x:v>0.7795</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:9">
@@ -2843,103 +2846,103 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B71" s="0">
-        <x:v>24.76</x:v>
+        <x:v>47.84</x:v>
       </x:c>
       <x:c r="C71" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E71" s="0">
-        <x:v>13000000</x:v>
+        <x:v>3102911</x:v>
       </x:c>
       <x:c r="F71" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G71" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H71" s="0">
-        <x:v>11834942581</x:v>
+        <x:v>2907014564</x:v>
       </x:c>
       <x:c r="I71" s="0">
-        <x:v>0.0563</x:v>
+        <x:v>0.0475</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:9">
       <x:c r="A72" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B72" s="0">
-        <x:v>72.1</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C72" s="0">
-        <x:v>-4.7</x:v>
+        <x:v>0.24</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E72" s="0">
-        <x:v>6800000</x:v>
+        <x:v>13000000</x:v>
       </x:c>
       <x:c r="F72" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G72" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H72" s="0">
-        <x:v>5948036961</x:v>
+        <x:v>11834942581</x:v>
       </x:c>
       <x:c r="I72" s="0">
-        <x:v>0.0583</x:v>
+        <x:v>0.0563</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:9">
       <x:c r="A73" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B73" s="0">
-        <x:v>60.7</x:v>
+        <x:v>74.95</x:v>
       </x:c>
       <x:c r="C73" s="0">
-        <x:v>-0.65</x:v>
+        <x:v>2.85</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E73" s="0">
-        <x:v>36750000</x:v>
+        <x:v>6800000</x:v>
       </x:c>
       <x:c r="F73" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G73" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H73" s="0">
-        <x:v>20597209000</x:v>
+        <x:v>5948036961</x:v>
       </x:c>
       <x:c r="I73" s="0">
-        <x:v>0.0793</x:v>
+        <x:v>0.0583</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:9">
       <x:c r="A74" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B74" s="0">
-        <x:v>1245</x:v>
+        <x:v>64.5</x:v>
       </x:c>
       <x:c r="C74" s="0">
-        <x:v>73</x:v>
+        <x:v>3.8</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
         <x:v>70</x:v>
       </x:c>
       <x:c r="E74" s="0">
-        <x:v>3867260</x:v>
+        <x:v>36750000</x:v>
       </x:c>
       <x:c r="F74" s="0" t="s">
         <x:v>11</x:v>
@@ -2948,143 +2951,143 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H74" s="0">
-        <x:v>1883544167</x:v>
+        <x:v>20597209000</x:v>
       </x:c>
       <x:c r="I74" s="0">
-        <x:v>0.0912</x:v>
+        <x:v>0.0793</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:9">
       <x:c r="A75" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B75" s="0">
+        <x:v>1276</x:v>
+      </x:c>
+      <x:c r="C75" s="0">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D75" s="0" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="B75" s="0">
-        <x:v>66.85</x:v>
-      </x:c>
-      <x:c r="C75" s="0">
-        <x:v>-3.3</x:v>
-      </x:c>
-      <x:c r="D75" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
       <x:c r="E75" s="0">
-        <x:v>1498029716</x:v>
+        <x:v>3867260</x:v>
       </x:c>
       <x:c r="F75" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G75" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H75" s="0">
-        <x:v>12030341104</x:v>
+        <x:v>1883544167</x:v>
       </x:c>
       <x:c r="I75" s="0">
-        <x:v>0.1245</x:v>
+        <x:v>0.0912</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:9">
       <x:c r="A76" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B76" s="0">
+        <x:v>67.35</x:v>
+      </x:c>
+      <x:c r="C76" s="0">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="D76" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="E76" s="0">
+        <x:v>1498029716</x:v>
+      </x:c>
+      <x:c r="F76" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="B76" s="0">
-        <x:v>38.34</x:v>
-      </x:c>
-      <x:c r="C76" s="0">
-        <x:v>-1.86</x:v>
-      </x:c>
-      <x:c r="D76" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="E76" s="0">
-        <x:v>48000000</x:v>
-      </x:c>
-      <x:c r="F76" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="G76" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H76" s="0">
-        <x:v>16355768622</x:v>
+        <x:v>12030341104</x:v>
       </x:c>
       <x:c r="I76" s="0">
-        <x:v>0.1301</x:v>
+        <x:v>0.1245</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:9">
       <x:c r="A77" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B77" s="0">
-        <x:v>95.5</x:v>
+        <x:v>39.46</x:v>
       </x:c>
       <x:c r="C77" s="0">
-        <x:v>0.3</x:v>
+        <x:v>1.12</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
         <x:v>73</x:v>
       </x:c>
       <x:c r="E77" s="0">
-        <x:v>279699629</x:v>
+        <x:v>48000000</x:v>
       </x:c>
       <x:c r="F77" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G77" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H77" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>16355768622</x:v>
       </x:c>
       <x:c r="I77" s="0">
-        <x:v>0.08</x:v>
+        <x:v>0.1301</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:9">
       <x:c r="A78" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B78" s="0">
+        <x:v>97.3</x:v>
+      </x:c>
+      <x:c r="C78" s="0">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="D78" s="0" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="B78" s="0">
-        <x:v>17.6</x:v>
-      </x:c>
-      <x:c r="C78" s="0">
-        <x:v>1.6</x:v>
-      </x:c>
-      <x:c r="D78" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
       <x:c r="E78" s="0">
-        <x:v>7971822</x:v>
+        <x:v>279699629</x:v>
       </x:c>
       <x:c r="F78" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G78" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H78" s="0">
-        <x:v>4675369372</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I78" s="0">
-        <x:v>0.0756</x:v>
+        <x:v>0.08</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:9">
       <x:c r="A79" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B79" s="0">
-        <x:v>54.75</x:v>
+        <x:v>19.36</x:v>
       </x:c>
       <x:c r="C79" s="0">
-        <x:v>-4.25</x:v>
+        <x:v>1.76</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E79" s="0">
-        <x:v>1104000</x:v>
+        <x:v>7971822</x:v>
       </x:c>
       <x:c r="F79" s="0" t="s">
         <x:v>11</x:v>
@@ -3093,88 +3096,88 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H79" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>4675369372</x:v>
       </x:c>
       <x:c r="I79" s="0">
-        <x:v>0.0116</x:v>
+        <x:v>0.0756</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:9">
       <x:c r="A80" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B80" s="0">
-        <x:v>24.52</x:v>
+        <x:v>59.55</x:v>
       </x:c>
       <x:c r="C80" s="0">
-        <x:v>-0.8</x:v>
+        <x:v>4.8</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E80" s="0">
-        <x:v>48895800</x:v>
+        <x:v>1104000</x:v>
       </x:c>
       <x:c r="F80" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G80" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H80" s="0">
-        <x:v>884571536</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I80" s="0">
-        <x:v>0.0553</x:v>
+        <x:v>0.0116</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:9">
       <x:c r="A81" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B81" s="0">
-        <x:v>3.5</x:v>
+        <x:v>26.96</x:v>
       </x:c>
       <x:c r="C81" s="0">
-        <x:v>-0.06</x:v>
+        <x:v>2.44</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E81" s="0">
-        <x:v>191089413</x:v>
+        <x:v>48895800</x:v>
       </x:c>
       <x:c r="F81" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G81" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H81" s="0">
-        <x:v>9665356715</x:v>
+        <x:v>884571536</x:v>
       </x:c>
       <x:c r="I81" s="0">
-        <x:v>0.0198</x:v>
+        <x:v>0.0553</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:9">
       <x:c r="A82" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B82" s="0">
-        <x:v>3.5</x:v>
+        <x:v>3.56</x:v>
       </x:c>
       <x:c r="C82" s="0">
-        <x:v>-0.06</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E82" s="0">
-        <x:v>605627160</x:v>
+        <x:v>191089413</x:v>
       </x:c>
       <x:c r="F82" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G82" s="0">
         <x:v>2025.12</x:v>
@@ -3183,7 +3186,7 @@
         <x:v>9665356715</x:v>
       </x:c>
       <x:c r="I82" s="0">
-        <x:v>0.0627</x:v>
+        <x:v>0.0198</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:9">
@@ -3191,77 +3194,77 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="B83" s="0">
-        <x:v>25.1</x:v>
+        <x:v>3.56</x:v>
       </x:c>
       <x:c r="C83" s="0">
-        <x:v>-0.66</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E83" s="0">
-        <x:v>2356546000</x:v>
+        <x:v>605627160</x:v>
       </x:c>
       <x:c r="F83" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G83" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H83" s="0">
-        <x:v>7708004248</x:v>
+        <x:v>9665356715</x:v>
       </x:c>
       <x:c r="I83" s="0">
-        <x:v>0.3057</x:v>
+        <x:v>0.0627</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:9">
       <x:c r="A84" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B84" s="0">
-        <x:v>17.29</x:v>
+        <x:v>25.08</x:v>
       </x:c>
       <x:c r="C84" s="0">
-        <x:v>-1.21</x:v>
+        <x:v>-0.02</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E84" s="0">
-        <x:v>431250</x:v>
+        <x:v>2356546000</x:v>
       </x:c>
       <x:c r="F84" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G84" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H84" s="0">
-        <x:v>3139850323</x:v>
+        <x:v>7708004248</x:v>
       </x:c>
       <x:c r="I84" s="0">
-        <x:v>0.0071</x:v>
+        <x:v>0.3057</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:9">
       <x:c r="A85" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B85" s="0">
-        <x:v>17.29</x:v>
+        <x:v>17.26</x:v>
       </x:c>
       <x:c r="C85" s="0">
-        <x:v>-1.21</x:v>
+        <x:v>-0.03</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E85" s="0">
-        <x:v>800000</x:v>
+        <x:v>431250</x:v>
       </x:c>
       <x:c r="F85" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G85" s="0">
         <x:v>2025.12</x:v>
@@ -3270,82 +3273,82 @@
         <x:v>3139850323</x:v>
       </x:c>
       <x:c r="I85" s="0">
-        <x:v>0.0131</x:v>
+        <x:v>0.0071</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:9">
       <x:c r="A86" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B86" s="0">
-        <x:v>61.1</x:v>
+        <x:v>17.26</x:v>
       </x:c>
       <x:c r="C86" s="0">
-        <x:v>-2.2</x:v>
+        <x:v>-0.03</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E86" s="0">
-        <x:v>127172130</x:v>
+        <x:v>800000</x:v>
       </x:c>
       <x:c r="F86" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G86" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H86" s="0">
-        <x:v>8121300519</x:v>
+        <x:v>3139850323</x:v>
       </x:c>
       <x:c r="I86" s="0">
-        <x:v>0.0157</x:v>
+        <x:v>0.0131</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:9">
       <x:c r="A87" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B87" s="0">
-        <x:v>47.46</x:v>
+        <x:v>65.05</x:v>
       </x:c>
       <x:c r="C87" s="0">
-        <x:v>-2.14</x:v>
+        <x:v>3.95</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E87" s="0">
-        <x:v>42625000</x:v>
+        <x:v>127172130</x:v>
       </x:c>
       <x:c r="F87" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G87" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H87" s="0">
-        <x:v>4728937463</x:v>
+        <x:v>8121300519</x:v>
       </x:c>
       <x:c r="I87" s="0">
-        <x:v>0.3994</x:v>
+        <x:v>0.0157</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:9">
       <x:c r="A88" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B88" s="0">
-        <x:v>90.75</x:v>
+        <x:v>52.2</x:v>
       </x:c>
       <x:c r="C88" s="0">
-        <x:v>-3.25</x:v>
+        <x:v>4.74</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E88" s="0">
-        <x:v>1486000</x:v>
+        <x:v>42625000</x:v>
       </x:c>
       <x:c r="F88" s="0" t="s">
         <x:v>11</x:v>
@@ -3354,27 +3357,27 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H88" s="0">
-        <x:v>2437633702</x:v>
+        <x:v>4728937463</x:v>
       </x:c>
       <x:c r="I88" s="0">
-        <x:v>0.027</x:v>
+        <x:v>0.3994</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:9">
       <x:c r="A89" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B89" s="0">
-        <x:v>335</x:v>
+        <x:v>96.8</x:v>
       </x:c>
       <x:c r="C89" s="0">
-        <x:v>1.75</x:v>
+        <x:v>6.05</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E89" s="0">
-        <x:v>768864700</x:v>
+        <x:v>1486000</x:v>
       </x:c>
       <x:c r="F89" s="0" t="s">
         <x:v>11</x:v>
@@ -3383,27 +3386,27 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H89" s="0">
-        <x:v>35290767390</x:v>
+        <x:v>2437633702</x:v>
       </x:c>
       <x:c r="I89" s="0">
-        <x:v>0.9648</x:v>
+        <x:v>0.027</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:9">
       <x:c r="A90" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B90" s="0">
-        <x:v>100</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="C90" s="0">
-        <x:v>5.15</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E90" s="0">
-        <x:v>15938617</x:v>
+        <x:v>768864700</x:v>
       </x:c>
       <x:c r="F90" s="0" t="s">
         <x:v>11</x:v>
@@ -3412,68 +3415,68 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H90" s="0">
-        <x:v>16733157490</x:v>
+        <x:v>35290767390</x:v>
       </x:c>
       <x:c r="I90" s="0">
-        <x:v>0.0422</x:v>
+        <x:v>0.9648</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:9">
       <x:c r="A91" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B91" s="0">
+        <x:v>101.5</x:v>
+      </x:c>
+      <x:c r="C91" s="0">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="D91" s="0" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="B91" s="0">
-        <x:v>14.56</x:v>
-      </x:c>
-      <x:c r="C91" s="0">
-        <x:v>-0.3</x:v>
-      </x:c>
-      <x:c r="D91" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
       <x:c r="E91" s="0">
-        <x:v>30438120</x:v>
+        <x:v>15938617</x:v>
       </x:c>
       <x:c r="F91" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G91" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H91" s="0">
-        <x:v>3159124121</x:v>
+        <x:v>16733157490</x:v>
       </x:c>
       <x:c r="I91" s="0">
-        <x:v>0</x:v>
+        <x:v>0.0422</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:9">
       <x:c r="A92" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B92" s="0">
-        <x:v>274.5</x:v>
+        <x:v>15.01</x:v>
       </x:c>
       <x:c r="C92" s="0">
-        <x:v>5</x:v>
+        <x:v>0.45</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
         <x:v>81</x:v>
       </x:c>
       <x:c r="E92" s="0">
-        <x:v>3900000</x:v>
+        <x:v>30438120</x:v>
       </x:c>
       <x:c r="F92" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G92" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H92" s="0">
-        <x:v>2159813703</x:v>
+        <x:v>3159124121</x:v>
       </x:c>
       <x:c r="I92" s="0">
-        <x:v>0.0797</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:9">
@@ -3481,16 +3484,16 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B93" s="0">
-        <x:v>274.5</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="C93" s="0">
-        <x:v>5</x:v>
+        <x:v>-9.5</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E93" s="0">
-        <x:v>2104908</x:v>
+        <x:v>3900000</x:v>
       </x:c>
       <x:c r="F93" s="0" t="s">
         <x:v>11</x:v>
@@ -3502,24 +3505,24 @@
         <x:v>2159813703</x:v>
       </x:c>
       <x:c r="I93" s="0">
-        <x:v>0.043</x:v>
+        <x:v>0.0797</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:9">
       <x:c r="A94" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B94" s="0">
-        <x:v>28.06</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="C94" s="0">
-        <x:v>-0.72</x:v>
+        <x:v>-9.5</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E94" s="0">
-        <x:v>3900000</x:v>
+        <x:v>2104908</x:v>
       </x:c>
       <x:c r="F94" s="0" t="s">
         <x:v>11</x:v>
@@ -3528,97 +3531,97 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H94" s="0">
-        <x:v>7297855153</x:v>
+        <x:v>2159813703</x:v>
       </x:c>
       <x:c r="I94" s="0">
-        <x:v>0.0236</x:v>
+        <x:v>0.043</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:9">
       <x:c r="A95" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B95" s="0">
-        <x:v>5.27</x:v>
+        <x:v>27.88</x:v>
       </x:c>
       <x:c r="C95" s="0">
-        <x:v>-0.33</x:v>
+        <x:v>-0.18</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
         <x:v>82</x:v>
       </x:c>
       <x:c r="E95" s="0">
-        <x:v>496968445</x:v>
+        <x:v>3900000</x:v>
       </x:c>
       <x:c r="F95" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G95" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H95" s="0">
-        <x:v>855070469</x:v>
+        <x:v>7297855153</x:v>
       </x:c>
       <x:c r="I95" s="0">
-        <x:v>0.5812</x:v>
+        <x:v>0.0236</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:9">
       <x:c r="A96" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B96" s="0">
+        <x:v>5.31</x:v>
+      </x:c>
+      <x:c r="C96" s="0">
+        <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="D96" s="0" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="B96" s="0">
-        <x:v>11.33</x:v>
-      </x:c>
-      <x:c r="C96" s="0">
-        <x:v>0.02</x:v>
-      </x:c>
-      <x:c r="D96" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
       <x:c r="E96" s="0">
-        <x:v>108750000</x:v>
+        <x:v>496968445</x:v>
       </x:c>
       <x:c r="F96" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G96" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H96" s="0">
-        <x:v>1982520183</x:v>
+        <x:v>855070469</x:v>
       </x:c>
       <x:c r="I96" s="0">
-        <x:v>0.0549</x:v>
+        <x:v>0.5812</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:9">
       <x:c r="A97" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B97" s="0">
-        <x:v>138.7</x:v>
+        <x:v>10.83</x:v>
       </x:c>
       <x:c r="C97" s="0">
-        <x:v>3.3</x:v>
+        <x:v>-0.5</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E97" s="0">
-        <x:v>1605197</x:v>
+        <x:v>108750000</x:v>
       </x:c>
       <x:c r="F97" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G97" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H97" s="0">
-        <x:v>3150489640</x:v>
+        <x:v>1982520183</x:v>
       </x:c>
       <x:c r="I97" s="0">
-        <x:v>0.0257</x:v>
+        <x:v>0.0549</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:9">
@@ -3626,45 +3629,45 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B98" s="0">
-        <x:v>412.75</x:v>
+        <x:v>152.5</x:v>
       </x:c>
       <x:c r="C98" s="0">
-        <x:v>-6.5</x:v>
+        <x:v>13.8</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
         <x:v>85</x:v>
       </x:c>
       <x:c r="E98" s="0">
-        <x:v>54600000</x:v>
+        <x:v>1605197</x:v>
       </x:c>
       <x:c r="F98" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G98" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H98" s="0">
-        <x:v>180444938000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I98" s="0">
-        <x:v>0.0133</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:9">
       <x:c r="A99" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B99" s="0">
-        <x:v>412.75</x:v>
+        <x:v>415.5</x:v>
       </x:c>
       <x:c r="C99" s="0">
-        <x:v>-6.5</x:v>
+        <x:v>2.75</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E99" s="0">
-        <x:v>111850000</x:v>
+        <x:v>54600000</x:v>
       </x:c>
       <x:c r="F99" s="0" t="s">
         <x:v>11</x:v>
@@ -3676,24 +3679,24 @@
         <x:v>180444938000</x:v>
       </x:c>
       <x:c r="I99" s="0">
-        <x:v>0.0273</x:v>
+        <x:v>0.0133</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:9">
       <x:c r="A100" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B100" s="0">
-        <x:v>54.75</x:v>
+        <x:v>415.5</x:v>
       </x:c>
       <x:c r="C100" s="0">
-        <x:v>-4.25</x:v>
+        <x:v>2.75</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E100" s="0">
-        <x:v>803090</x:v>
+        <x:v>111850000</x:v>
       </x:c>
       <x:c r="F100" s="0" t="s">
         <x:v>11</x:v>
@@ -3702,317 +3705,317 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H100" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>180444938000</x:v>
       </x:c>
       <x:c r="I100" s="0">
-        <x:v>0.0084</x:v>
+        <x:v>0.0273</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:9">
       <x:c r="A101" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B101" s="0">
-        <x:v>25.1</x:v>
+        <x:v>59.55</x:v>
       </x:c>
       <x:c r="C101" s="0">
-        <x:v>-0.66</x:v>
+        <x:v>4.8</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
         <x:v>86</x:v>
       </x:c>
       <x:c r="E101" s="0">
-        <x:v>2356546000</x:v>
+        <x:v>803090</x:v>
       </x:c>
       <x:c r="F101" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G101" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H101" s="0">
-        <x:v>7708004248</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I101" s="0">
-        <x:v>0.3057</x:v>
+        <x:v>0.0084</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:9">
       <x:c r="A102" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B102" s="0">
-        <x:v>1245</x:v>
+        <x:v>25.08</x:v>
       </x:c>
       <x:c r="C102" s="0">
-        <x:v>73</x:v>
+        <x:v>-0.02</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
         <x:v>87</x:v>
       </x:c>
       <x:c r="E102" s="0">
-        <x:v>875400</x:v>
+        <x:v>2356546000</x:v>
       </x:c>
       <x:c r="F102" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G102" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H102" s="0">
-        <x:v>1883544167</x:v>
+        <x:v>7708004248</x:v>
       </x:c>
       <x:c r="I102" s="0">
-        <x:v>0.0205</x:v>
+        <x:v>0.3057</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:9">
       <x:c r="A103" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B103" s="0">
+        <x:v>1276</x:v>
+      </x:c>
+      <x:c r="C103" s="0">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D103" s="0" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="B103" s="0">
-        <x:v>25.74</x:v>
-      </x:c>
-      <x:c r="C103" s="0">
-        <x:v>-0.6</x:v>
-      </x:c>
-      <x:c r="D103" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
       <x:c r="E103" s="0">
-        <x:v>330000000</x:v>
+        <x:v>875400</x:v>
       </x:c>
       <x:c r="F103" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G103" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H103" s="0">
-        <x:v>5287314404</x:v>
+        <x:v>1883544167</x:v>
       </x:c>
       <x:c r="I103" s="0">
-        <x:v>0.0624</x:v>
+        <x:v>0.0205</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:9">
       <x:c r="A104" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B104" s="0">
-        <x:v>95.5</x:v>
+        <x:v>25.8</x:v>
       </x:c>
       <x:c r="C104" s="0">
-        <x:v>0.3</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
       <x:c r="E104" s="0">
-        <x:v>11700000</x:v>
+        <x:v>330000000</x:v>
       </x:c>
       <x:c r="F104" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G104" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H104" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>5287314404</x:v>
       </x:c>
       <x:c r="I104" s="0">
-        <x:v>0.1705</x:v>
+        <x:v>0.0624</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:9">
       <x:c r="A105" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B105" s="0">
-        <x:v>12.55</x:v>
+        <x:v>97.3</x:v>
       </x:c>
       <x:c r="C105" s="0">
-        <x:v>1.14</x:v>
+        <x:v>1.8</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E105" s="0">
-        <x:v>4000000000</x:v>
+        <x:v>11700000</x:v>
       </x:c>
       <x:c r="F105" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G105" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H105" s="0">
-        <x:v>10581001663</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I105" s="0">
-        <x:v>0.378</x:v>
+        <x:v>0.1705</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:9">
       <x:c r="A106" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B106" s="0">
-        <x:v>17.29</x:v>
+        <x:v>12.77</x:v>
       </x:c>
       <x:c r="C106" s="0">
-        <x:v>-1.21</x:v>
+        <x:v>0.22</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
         <x:v>91</x:v>
       </x:c>
       <x:c r="E106" s="0">
-        <x:v>1086598</x:v>
+        <x:v>4000000000</x:v>
       </x:c>
       <x:c r="F106" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G106" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H106" s="0">
-        <x:v>2020891371</x:v>
+        <x:v>10581001663</x:v>
       </x:c>
       <x:c r="I106" s="0">
-        <x:v>0.0274</x:v>
+        <x:v>0.378</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:9">
       <x:c r="A107" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B107" s="0">
-        <x:v>17.6</x:v>
+        <x:v>17.26</x:v>
       </x:c>
       <x:c r="C107" s="0">
-        <x:v>1.6</x:v>
+        <x:v>-0.03</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
         <x:v>92</x:v>
       </x:c>
       <x:c r="E107" s="0">
-        <x:v>216000000</x:v>
+        <x:v>1086598</x:v>
       </x:c>
       <x:c r="F107" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G107" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H107" s="0">
-        <x:v>3025063909</x:v>
+        <x:v>2020891371</x:v>
       </x:c>
       <x:c r="I107" s="0">
-        <x:v>0.0714</x:v>
+        <x:v>0.0274</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:9">
       <x:c r="A108" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B108" s="0">
-        <x:v>54.75</x:v>
+        <x:v>19.36</x:v>
       </x:c>
       <x:c r="C108" s="0">
-        <x:v>-4.25</x:v>
+        <x:v>1.76</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E108" s="0">
-        <x:v>7292916</x:v>
+        <x:v>216000000</x:v>
       </x:c>
       <x:c r="F108" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G108" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H108" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>3025063909</x:v>
       </x:c>
       <x:c r="I108" s="0">
-        <x:v>0.0758</x:v>
+        <x:v>0.0714</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:9">
       <x:c r="A109" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B109" s="0">
-        <x:v>29.82</x:v>
+        <x:v>59.55</x:v>
       </x:c>
       <x:c r="C109" s="0">
-        <x:v>-0.88</x:v>
+        <x:v>4.8</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
         <x:v>93</x:v>
       </x:c>
       <x:c r="E109" s="0">
-        <x:v>250000</x:v>
+        <x:v>7292916</x:v>
       </x:c>
       <x:c r="F109" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G109" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H109" s="0">
-        <x:v>448686813</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I109" s="0">
-        <x:v>0.0006</x:v>
+        <x:v>0.0758</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:9">
       <x:c r="A110" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B110" s="0">
-        <x:v>100</x:v>
+        <x:v>29.58</x:v>
       </x:c>
       <x:c r="C110" s="0">
-        <x:v>5.15</x:v>
+        <x:v>-0.24</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E110" s="0">
-        <x:v>36900000</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="F110" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G110" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H110" s="0">
-        <x:v>10597063406</x:v>
+        <x:v>448686813</x:v>
       </x:c>
       <x:c r="I110" s="0">
-        <x:v>0.1527</x:v>
+        <x:v>0.0006</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:9">
       <x:c r="A111" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B111" s="0">
+        <x:v>101.5</x:v>
+      </x:c>
+      <x:c r="C111" s="0">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="D111" s="0" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="B111" s="0">
-        <x:v>63.1</x:v>
-      </x:c>
-      <x:c r="C111" s="0">
-        <x:v>-3.4</x:v>
-      </x:c>
-      <x:c r="D111" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
       <x:c r="E111" s="0">
-        <x:v>3800000</x:v>
+        <x:v>36900000</x:v>
       </x:c>
       <x:c r="F111" s="0" t="s">
         <x:v>11</x:v>
@@ -4021,56 +4024,56 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H111" s="0">
-        <x:v>832031190</x:v>
+        <x:v>10597063406</x:v>
       </x:c>
       <x:c r="I111" s="0">
-        <x:v>0.2002</x:v>
+        <x:v>0.1527</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:9">
       <x:c r="A112" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B112" s="0">
-        <x:v>5.27</x:v>
+        <x:v>65.15</x:v>
       </x:c>
       <x:c r="C112" s="0">
-        <x:v>-0.33</x:v>
+        <x:v>2.05</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
         <x:v>96</x:v>
       </x:c>
       <x:c r="E112" s="0">
-        <x:v>2100000</x:v>
+        <x:v>3800000</x:v>
       </x:c>
       <x:c r="F112" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G112" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H112" s="0">
-        <x:v>855070469</x:v>
+        <x:v>832031190</x:v>
       </x:c>
       <x:c r="I112" s="0">
-        <x:v>0.1076</x:v>
+        <x:v>0.2002</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:9">
       <x:c r="A113" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B113" s="0">
-        <x:v>54.75</x:v>
+        <x:v>5.31</x:v>
       </x:c>
       <x:c r="C113" s="0">
-        <x:v>-4.25</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E113" s="0">
-        <x:v>22928077</x:v>
+        <x:v>2100000</x:v>
       </x:c>
       <x:c r="F113" s="0" t="s">
         <x:v>11</x:v>
@@ -4079,59 +4082,59 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H113" s="0">
-        <x:v>4224605448</x:v>
+        <x:v>855070469</x:v>
       </x:c>
       <x:c r="I113" s="0">
-        <x:v>0.2378</x:v>
+        <x:v>0.1076</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:9">
       <x:c r="A114" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B114" s="0">
+        <x:v>59.55</x:v>
+      </x:c>
+      <x:c r="C114" s="0">
+        <x:v>4.8</x:v>
+      </x:c>
+      <x:c r="D114" s="0" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="B114" s="0">
-        <x:v>30.02</x:v>
-      </x:c>
-      <x:c r="C114" s="0">
-        <x:v>-1.34</x:v>
-      </x:c>
-      <x:c r="D114" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
       <x:c r="E114" s="0">
-        <x:v>547462013</x:v>
+        <x:v>22928077</x:v>
       </x:c>
       <x:c r="F114" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G114" s="0">
-        <x:v>0</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H114" s="0">
-        <x:v>0</x:v>
+        <x:v>4224605448</x:v>
       </x:c>
       <x:c r="I114" s="0">
-        <x:v>0</x:v>
+        <x:v>0.2378</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:9">
       <x:c r="A115" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B115" s="0">
+        <x:v>33.02</x:v>
+      </x:c>
+      <x:c r="C115" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D115" s="0" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="B115" s="0">
-        <x:v>30.02</x:v>
-      </x:c>
-      <x:c r="C115" s="0">
-        <x:v>-1.34</x:v>
-      </x:c>
-      <x:c r="D115" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
       <x:c r="E115" s="0">
-        <x:v>10567948</x:v>
+        <x:v>547462013</x:v>
       </x:c>
       <x:c r="F115" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G115" s="0">
         <x:v>0</x:v>
@@ -4145,77 +4148,77 @@
     </x:row>
     <x:row r="116" spans="1:9">
       <x:c r="A116" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B116" s="0">
-        <x:v>95.5</x:v>
+        <x:v>33.02</x:v>
       </x:c>
       <x:c r="C116" s="0">
-        <x:v>0.3</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D116" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E116" s="0">
-        <x:v>8300000</x:v>
+        <x:v>10567948</x:v>
       </x:c>
       <x:c r="F116" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G116" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H116" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I116" s="0">
-        <x:v>0.1228</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:9">
       <x:c r="A117" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B117" s="0">
-        <x:v>60.7</x:v>
+        <x:v>97.3</x:v>
       </x:c>
       <x:c r="C117" s="0">
-        <x:v>-0.65</x:v>
+        <x:v>1.8</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E117" s="0">
-        <x:v>3000000</x:v>
+        <x:v>8300000</x:v>
       </x:c>
       <x:c r="F117" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G117" s="0">
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H117" s="0">
-        <x:v>20597209000</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I117" s="0">
-        <x:v>0.0064</x:v>
+        <x:v>0.1228</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:9">
       <x:c r="A118" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B118" s="0">
+        <x:v>64.5</x:v>
+      </x:c>
+      <x:c r="C118" s="0">
+        <x:v>3.8</x:v>
+      </x:c>
+      <x:c r="D118" s="0" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="B118" s="0">
-        <x:v>40.7</x:v>
-      </x:c>
-      <x:c r="C118" s="0">
-        <x:v>2.04</x:v>
-      </x:c>
-      <x:c r="D118" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
       <x:c r="E118" s="0">
-        <x:v>26640000</x:v>
+        <x:v>3000000</x:v>
       </x:c>
       <x:c r="F118" s="0" t="s">
         <x:v>11</x:v>
@@ -4224,10 +4227,10 @@
         <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H118" s="0">
-        <x:v>3277373640</x:v>
+        <x:v>20597209000</x:v>
       </x:c>
       <x:c r="I118" s="0">
-        <x:v>0.356</x:v>
+        <x:v>0.0064</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:9">
@@ -4235,193 +4238,193 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="B119" s="0">
-        <x:v>6.13</x:v>
+        <x:v>43.5</x:v>
       </x:c>
       <x:c r="C119" s="0">
-        <x:v>-0.42</x:v>
+        <x:v>2.8</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E119" s="0">
-        <x:v>13107198</x:v>
+        <x:v>26640000</x:v>
       </x:c>
       <x:c r="F119" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G119" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H119" s="0">
-        <x:v>1627872951</x:v>
+        <x:v>3277373640</x:v>
       </x:c>
       <x:c r="I119" s="0">
-        <x:v>0.0081</x:v>
+        <x:v>0.356</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:9">
       <x:c r="A120" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B120" s="0">
-        <x:v>95.5</x:v>
+        <x:v>6.3</x:v>
       </x:c>
       <x:c r="C120" s="0">
-        <x:v>0.3</x:v>
+        <x:v>0.17</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
         <x:v>102</x:v>
       </x:c>
       <x:c r="E120" s="0">
-        <x:v>237500000</x:v>
+        <x:v>13107198</x:v>
       </x:c>
       <x:c r="F120" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G120" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H120" s="0">
-        <x:v>3495512127</x:v>
+        <x:v>1627872951</x:v>
       </x:c>
       <x:c r="I120" s="0">
-        <x:v>0.0679</x:v>
+        <x:v>0.0081</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:9">
       <x:c r="A121" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B121" s="0">
-        <x:v>61.1</x:v>
+        <x:v>97.3</x:v>
       </x:c>
       <x:c r="C121" s="0">
-        <x:v>-2.2</x:v>
+        <x:v>1.8</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
         <x:v>103</x:v>
       </x:c>
       <x:c r="E121" s="0">
-        <x:v>147892538</x:v>
+        <x:v>237500000</x:v>
       </x:c>
       <x:c r="F121" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G121" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H121" s="0">
-        <x:v>7257990064</x:v>
+        <x:v>3495512127</x:v>
       </x:c>
       <x:c r="I121" s="0">
-        <x:v>0.0204</x:v>
+        <x:v>0.0679</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:9">
       <x:c r="A122" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B122" s="0">
+        <x:v>65.05</x:v>
+      </x:c>
+      <x:c r="C122" s="0">
+        <x:v>3.95</x:v>
+      </x:c>
+      <x:c r="D122" s="0" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="B122" s="0">
-        <x:v>59.6</x:v>
-      </x:c>
-      <x:c r="C122" s="0">
-        <x:v>0.8</x:v>
-      </x:c>
-      <x:c r="D122" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
       <x:c r="E122" s="0">
-        <x:v>988848</x:v>
+        <x:v>147892538</x:v>
       </x:c>
       <x:c r="F122" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G122" s="0">
-        <x:v>2025.12</x:v>
+        <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H122" s="0">
-        <x:v>12999679000</x:v>
+        <x:v>7257990064</x:v>
       </x:c>
       <x:c r="I122" s="0">
-        <x:v>0.0033</x:v>
+        <x:v>0.0204</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:9">
       <x:c r="A123" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B123" s="0">
-        <x:v>100</x:v>
+        <x:v>64.15</x:v>
       </x:c>
       <x:c r="C123" s="0">
-        <x:v>5.15</x:v>
+        <x:v>4.55</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E123" s="0">
-        <x:v>47300000</x:v>
+        <x:v>988848</x:v>
       </x:c>
       <x:c r="F123" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G123" s="0">
-        <x:v>2025.09</x:v>
+        <x:v>2025.12</x:v>
       </x:c>
       <x:c r="H123" s="0">
-        <x:v>10597063406</x:v>
+        <x:v>12999679000</x:v>
       </x:c>
       <x:c r="I123" s="0">
-        <x:v>0.2309</x:v>
+        <x:v>0.0033</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:9">
       <x:c r="A124" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B124" s="0">
-        <x:v>4.03</x:v>
+        <x:v>101.5</x:v>
       </x:c>
       <x:c r="C124" s="0">
-        <x:v>-0.08</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E124" s="0">
-        <x:v>758600</x:v>
+        <x:v>47300000</x:v>
       </x:c>
       <x:c r="F124" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G124" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H124" s="0">
-        <x:v>1960468575</x:v>
+        <x:v>10597063406</x:v>
       </x:c>
       <x:c r="I124" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0.2309</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:9">
       <x:c r="A125" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B125" s="0">
-        <x:v>4.03</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="C125" s="0">
-        <x:v>-0.08</x:v>
+        <x:v>0.07</x:v>
       </x:c>
       <x:c r="D125" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E125" s="0">
         <x:v>758600</x:v>
       </x:c>
       <x:c r="F125" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G125" s="0">
         <x:v>2025.09</x:v>
@@ -4430,53 +4433,53 @@
         <x:v>1960468575</x:v>
       </x:c>
       <x:c r="I125" s="0">
-        <x:v>0.0004</x:v>
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:9">
       <x:c r="A126" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B126" s="0">
-        <x:v>1245</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="C126" s="0">
-        <x:v>73</x:v>
+        <x:v>0.07</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E126" s="0">
-        <x:v>576665</x:v>
+        <x:v>758600</x:v>
       </x:c>
       <x:c r="F126" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="G126" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H126" s="0">
-        <x:v>1586603352</x:v>
+        <x:v>1960468575</x:v>
       </x:c>
       <x:c r="I126" s="0">
-        <x:v>0.0159</x:v>
+        <x:v>0.0004</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:9">
       <x:c r="A127" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B127" s="0">
-        <x:v>86.15</x:v>
+        <x:v>1276</x:v>
       </x:c>
       <x:c r="C127" s="0">
-        <x:v>-2</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D127" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E127" s="0">
-        <x:v>8000000</x:v>
+        <x:v>576665</x:v>
       </x:c>
       <x:c r="F127" s="0" t="s">
         <x:v>11</x:v>
@@ -4485,27 +4488,27 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H127" s="0">
-        <x:v>20999579110</x:v>
+        <x:v>1586603352</x:v>
       </x:c>
       <x:c r="I127" s="0">
-        <x:v>0.0166</x:v>
+        <x:v>0.0159</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:9">
       <x:c r="A128" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B128" s="0">
-        <x:v>90.75</x:v>
+        <x:v>88.3</x:v>
       </x:c>
       <x:c r="C128" s="0">
-        <x:v>-3.25</x:v>
+        <x:v>2.15</x:v>
       </x:c>
       <x:c r="D128" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E128" s="0">
-        <x:v>850000</x:v>
+        <x:v>8000000</x:v>
       </x:c>
       <x:c r="F128" s="0" t="s">
         <x:v>11</x:v>
@@ -4514,175 +4517,175 @@
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H128" s="0">
-        <x:v>1781510191</x:v>
+        <x:v>20999579110</x:v>
       </x:c>
       <x:c r="I128" s="0">
-        <x:v>0.0208</x:v>
+        <x:v>0.0166</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:9">
       <x:c r="A129" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B129" s="0">
-        <x:v>17.29</x:v>
+        <x:v>96.8</x:v>
       </x:c>
       <x:c r="C129" s="0">
-        <x:v>-1.21</x:v>
+        <x:v>6.05</x:v>
       </x:c>
       <x:c r="D129" s="0" t="s">
         <x:v>109</x:v>
       </x:c>
       <x:c r="E129" s="0">
-        <x:v>10149200</x:v>
+        <x:v>850000</x:v>
       </x:c>
       <x:c r="F129" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G129" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H129" s="0">
-        <x:v>2020891371</x:v>
+        <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I129" s="0">
-        <x:v>0.2601</x:v>
+        <x:v>0.0208</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:9">
       <x:c r="A130" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B130" s="0">
-        <x:v>138.7</x:v>
+        <x:v>17.26</x:v>
       </x:c>
       <x:c r="C130" s="0">
-        <x:v>3.3</x:v>
+        <x:v>-0.03</x:v>
       </x:c>
       <x:c r="D130" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E130" s="0">
-        <x:v>10500000</x:v>
+        <x:v>10149200</x:v>
       </x:c>
       <x:c r="F130" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G130" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H130" s="0">
-        <x:v>1742315226</x:v>
+        <x:v>2020891371</x:v>
       </x:c>
       <x:c r="I130" s="0">
-        <x:v>0.3121</x:v>
+        <x:v>0.2601</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:9">
       <x:c r="A131" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B131" s="0">
-        <x:v>90.75</x:v>
+        <x:v>152.5</x:v>
       </x:c>
       <x:c r="C131" s="0">
-        <x:v>-3.25</x:v>
+        <x:v>13.8</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
         <x:v>110</x:v>
       </x:c>
       <x:c r="E131" s="0">
-        <x:v>366956541</x:v>
+        <x:v>10500000</x:v>
       </x:c>
       <x:c r="F131" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G131" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H131" s="0">
-        <x:v>1781510191</x:v>
+        <x:v>1742315226</x:v>
       </x:c>
       <x:c r="I131" s="0">
-        <x:v>0.206</x:v>
+        <x:v>0.3121</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:9">
       <x:c r="A132" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B132" s="0">
-        <x:v>61.1</x:v>
+        <x:v>96.8</x:v>
       </x:c>
       <x:c r="C132" s="0">
-        <x:v>-2.2</x:v>
+        <x:v>6.05</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="E132" s="0">
-        <x:v>61158155</x:v>
+        <x:v>366956541</x:v>
       </x:c>
       <x:c r="F132" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G132" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H132" s="0">
-        <x:v>7257990064</x:v>
+        <x:v>1781510191</x:v>
       </x:c>
       <x:c r="I132" s="0">
-        <x:v>0.0084</x:v>
+        <x:v>0.206</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:9">
       <x:c r="A133" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B133" s="0">
-        <x:v>129</x:v>
+        <x:v>65.05</x:v>
       </x:c>
       <x:c r="C133" s="0">
-        <x:v>4</x:v>
+        <x:v>3.95</x:v>
       </x:c>
       <x:c r="D133" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E133" s="0">
-        <x:v>1000000</x:v>
+        <x:v>61158155</x:v>
       </x:c>
       <x:c r="F133" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G133" s="0">
         <x:v>2025.09</x:v>
       </x:c>
       <x:c r="H133" s="0">
-        <x:v>1688731509</x:v>
+        <x:v>7257990064</x:v>
       </x:c>
       